--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="D4" s="0">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E4" s="0">
         <v>4</v>
@@ -482,7 +482,7 @@
         <v>3</v>
       </c>
       <c r="G4" s="0">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H4" s="1">
         <v>230</v>
@@ -537,7 +537,7 @@
         </is>
       </c>
       <c r="D6" s="0">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E6" s="0">
         <v>4</v>
@@ -546,7 +546,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="0">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H6" s="1">
         <v>200</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="D10" s="0">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E10" s="0">
         <v>4</v>
@@ -674,7 +674,7 @@
         <v>7</v>
       </c>
       <c r="G10" s="0">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H10" s="1">
         <v>270</v>
@@ -697,10 +697,10 @@
         </is>
       </c>
       <c r="D11" s="0">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E11" s="0">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F11" s="0">
         <v>0</v>
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="D12" s="0">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E12" s="0">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F12" s="0">
         <v>18</v>
@@ -764,13 +764,13 @@
         <v>3</v>
       </c>
       <c r="E13" s="0">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F13" s="0">
         <v>0</v>
       </c>
       <c r="G13" s="0">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H13" s="1">
         <v>230</v>
@@ -921,10 +921,10 @@
         </is>
       </c>
       <c r="D18" s="0">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E18" s="0">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F18" s="0">
         <v>60</v>
@@ -953,10 +953,10 @@
         </is>
       </c>
       <c r="D19" s="0">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E19" s="0">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="F19" s="0">
         <v>0</v>
@@ -1040,60 +1040,60 @@
       </c>
       <c r="B22" s="0" t="inlineStr">
         <is>
-          <t>WESTLAKE</t>
+          <t>MATADOR</t>
         </is>
       </c>
       <c r="C22" s="0" t="inlineStr">
         <is>
-          <t>WL175/70R14</t>
+          <t>MT175/70R14</t>
         </is>
       </c>
       <c r="D22" s="0">
-        <v>51</v>
+        <v>4</v>
       </c>
       <c r="E22" s="0">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="F22" s="0">
         <v>0</v>
       </c>
       <c r="G22" s="0">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H22" s="1">
-        <v>200</v>
+        <v>230</v>
       </c>
     </row>
     <row outlineLevel="0" r="23">
       <c r="A23" s="0" t="inlineStr">
         <is>
-          <t>185/55R15</t>
+          <t>175/70R14</t>
         </is>
       </c>
       <c r="B23" s="0" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>WESTLAKE</t>
         </is>
       </c>
       <c r="C23" s="0" t="inlineStr">
         <is>
-          <t>BR185/55R15</t>
+          <t>WL175/70R14</t>
         </is>
       </c>
       <c r="D23" s="0">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="E23" s="0">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="F23" s="0">
         <v>0</v>
       </c>
       <c r="G23" s="0">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="H23" s="1">
-        <v>370</v>
+        <v>200</v>
       </c>
     </row>
     <row outlineLevel="0" r="24">
@@ -1104,28 +1104,28 @@
       </c>
       <c r="B24" s="0" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C24" s="0" t="inlineStr">
         <is>
-          <t>GD185/55R15</t>
+          <t>BR185/55R15</t>
         </is>
       </c>
       <c r="D24" s="0">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="E24" s="0">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F24" s="0">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="G24" s="0">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H24" s="1">
-        <v>340</v>
+        <v>370</v>
       </c>
     </row>
     <row outlineLevel="0" r="25">
@@ -1136,28 +1136,28 @@
       </c>
       <c r="B25" s="0" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C25" s="0" t="inlineStr">
         <is>
-          <t>RD185/55R15</t>
+          <t>GD185/55R15</t>
         </is>
       </c>
       <c r="D25" s="0">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="E25" s="0">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F25" s="0">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G25" s="0">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H25" s="1">
-        <v>270</v>
+        <v>340</v>
       </c>
     </row>
     <row outlineLevel="0" r="26">
@@ -1264,28 +1264,28 @@
       </c>
       <c r="B29" s="0" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>MATADOR</t>
         </is>
       </c>
       <c r="C29" s="0" t="inlineStr">
         <is>
-          <t>RD185/60R15</t>
+          <t>MT185/60R15</t>
         </is>
       </c>
       <c r="D29" s="0">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E29" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F29" s="0">
         <v>0</v>
       </c>
       <c r="G29" s="0">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H29" s="1">
-        <v>230</v>
+        <v>280</v>
       </c>
     </row>
     <row outlineLevel="0" r="30">
@@ -1296,25 +1296,25 @@
       </c>
       <c r="B30" s="0" t="inlineStr">
         <is>
-          <t>WESTLAKE</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C30" s="0" t="inlineStr">
         <is>
-          <t>WL185/60R15</t>
+          <t>RD185/60R15</t>
         </is>
       </c>
       <c r="D30" s="0">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E30" s="0">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F30" s="0">
         <v>0</v>
       </c>
       <c r="G30" s="0">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H30" s="1">
         <v>230</v>
@@ -1323,97 +1323,97 @@
     <row outlineLevel="0" r="31">
       <c r="A31" s="0" t="inlineStr">
         <is>
-          <t>185/60R16</t>
+          <t>185/60R15</t>
         </is>
       </c>
       <c r="B31" s="0" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>WESTLAKE</t>
         </is>
       </c>
       <c r="C31" s="0" t="inlineStr">
         <is>
-          <t>GD185/60R16</t>
+          <t>WL185/60R15</t>
         </is>
       </c>
       <c r="D31" s="0">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E31" s="0">
         <v>4</v>
       </c>
       <c r="F31" s="0">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G31" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H31" s="1">
-        <v>420</v>
+        <v>230</v>
       </c>
     </row>
     <row outlineLevel="0" r="32">
       <c r="A32" s="0" t="inlineStr">
         <is>
-          <t>185/65R14</t>
+          <t>185/60R16</t>
         </is>
       </c>
       <c r="B32" s="0" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C32" s="0" t="inlineStr">
         <is>
-          <t>RD185/65R14</t>
+          <t>GD185/60R16</t>
         </is>
       </c>
       <c r="D32" s="0">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E32" s="0">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F32" s="0">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G32" s="0">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H32" s="1">
-        <v>200</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="33">
       <c r="A33" s="0" t="inlineStr">
         <is>
-          <t>185/65R15</t>
+          <t>185/65R14</t>
         </is>
       </c>
       <c r="B33" s="0" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C33" s="0" t="inlineStr">
         <is>
-          <t>CT185/65R15</t>
+          <t>RD185/65R14</t>
         </is>
       </c>
       <c r="D33" s="0">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E33" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F33" s="0">
         <v>0</v>
       </c>
       <c r="G33" s="0">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H33" s="1">
-        <v>400</v>
+        <v>200</v>
       </c>
     </row>
     <row outlineLevel="0" r="34">
@@ -1424,28 +1424,28 @@
       </c>
       <c r="B34" s="0" t="inlineStr">
         <is>
-          <t>DOUBLESTAR</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C34" s="0" t="inlineStr">
         <is>
-          <t>DS185/65R15</t>
+          <t>CT185/65R15</t>
         </is>
       </c>
       <c r="D34" s="0">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E34" s="0">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F34" s="0">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G34" s="0">
         <v>0</v>
       </c>
       <c r="H34" s="1">
-        <v>210</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="35">
@@ -1456,28 +1456,28 @@
       </c>
       <c r="B35" s="0" t="inlineStr">
         <is>
-          <t>FULDA</t>
+          <t>DOUBLESTAR</t>
         </is>
       </c>
       <c r="C35" s="0" t="inlineStr">
         <is>
-          <t>FL185/65R15</t>
+          <t>DS185/65R15</t>
         </is>
       </c>
       <c r="D35" s="0">
-        <v>136</v>
+        <v>7</v>
       </c>
       <c r="E35" s="0">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="F35" s="0">
-        <v>109</v>
+        <v>5</v>
       </c>
       <c r="G35" s="0">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H35" s="1">
-        <v>245</v>
+        <v>210</v>
       </c>
     </row>
     <row outlineLevel="0" r="36">
@@ -1488,28 +1488,28 @@
       </c>
       <c r="B36" s="0" t="inlineStr">
         <is>
-          <t>GOODRIDE</t>
+          <t>FULDA</t>
         </is>
       </c>
       <c r="C36" s="0" t="inlineStr">
         <is>
-          <t>GR185/65R15</t>
+          <t>FL185/65R15</t>
         </is>
       </c>
       <c r="D36" s="0">
+        <v>136</v>
+      </c>
+      <c r="E36" s="0">
+        <v>16</v>
+      </c>
+      <c r="F36" s="0">
+        <v>109</v>
+      </c>
+      <c r="G36" s="0">
         <v>11</v>
       </c>
-      <c r="E36" s="0">
-        <v>4</v>
-      </c>
-      <c r="F36" s="0">
-        <v>3</v>
-      </c>
-      <c r="G36" s="0">
-        <v>4</v>
-      </c>
       <c r="H36" s="1">
-        <v>230</v>
+        <v>245</v>
       </c>
     </row>
     <row outlineLevel="0" r="37">
@@ -1520,28 +1520,28 @@
       </c>
       <c r="B37" s="0" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>GOODRIDE</t>
         </is>
       </c>
       <c r="C37" s="0" t="inlineStr">
         <is>
-          <t>GD185/65R15</t>
+          <t>GR185/65R15</t>
         </is>
       </c>
       <c r="D37" s="0">
-        <v>71</v>
+        <v>11</v>
       </c>
       <c r="E37" s="0">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F37" s="0">
-        <v>49</v>
+        <v>3</v>
       </c>
       <c r="G37" s="0">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H37" s="1">
-        <v>260</v>
+        <v>230</v>
       </c>
     </row>
     <row outlineLevel="0" r="38">
@@ -1552,28 +1552,28 @@
       </c>
       <c r="B38" s="0" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C38" s="0" t="inlineStr">
         <is>
-          <t>HK185/65R15</t>
+          <t>GD185/65R15</t>
         </is>
       </c>
       <c r="D38" s="0">
-        <v>5</v>
+        <v>67</v>
       </c>
       <c r="E38" s="0">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F38" s="0">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="G38" s="0">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H38" s="1">
-        <v>250</v>
+        <v>260</v>
       </c>
     </row>
     <row outlineLevel="0" r="39">
@@ -1584,16 +1584,16 @@
       </c>
       <c r="B39" s="0" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C39" s="0" t="inlineStr">
         <is>
-          <t>LF185/65R15</t>
+          <t>HK185/65R15</t>
         </is>
       </c>
       <c r="D39" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E39" s="0">
         <v>4</v>
@@ -1602,7 +1602,7 @@
         <v>0</v>
       </c>
       <c r="G39" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H39" s="1">
         <v>250</v>
@@ -1616,28 +1616,28 @@
       </c>
       <c r="B40" s="0" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C40" s="0" t="inlineStr">
         <is>
-          <t>RD185/65R15</t>
+          <t>LF185/65R15</t>
         </is>
       </c>
       <c r="D40" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E40" s="0">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F40" s="0">
         <v>0</v>
       </c>
       <c r="G40" s="0">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H40" s="1">
-        <v>200</v>
+        <v>250</v>
       </c>
     </row>
     <row outlineLevel="0" r="41">
@@ -1648,28 +1648,28 @@
       </c>
       <c r="B41" s="0" t="inlineStr">
         <is>
-          <t>SEMPERIT</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C41" s="0" t="inlineStr">
         <is>
-          <t>SP185/65R15</t>
+          <t>RD185/65R15</t>
         </is>
       </c>
       <c r="D41" s="0">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="E41" s="0">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F41" s="0">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="G41" s="0">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H41" s="1">
-        <v>250</v>
+        <v>200</v>
       </c>
     </row>
     <row outlineLevel="0" r="42">
@@ -1680,60 +1680,60 @@
       </c>
       <c r="B42" s="0" t="inlineStr">
         <is>
-          <t>WESTLAKE</t>
+          <t>SEMPERIT</t>
         </is>
       </c>
       <c r="C42" s="0" t="inlineStr">
         <is>
-          <t>WL185/65R15</t>
+          <t>SP185/65R15</t>
         </is>
       </c>
       <c r="D42" s="0">
-        <v>98</v>
+        <v>30</v>
       </c>
       <c r="E42" s="0">
-        <v>86</v>
+        <v>5</v>
       </c>
       <c r="F42" s="0">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G42" s="0">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="H42" s="1">
-        <v>220</v>
+        <v>250</v>
       </c>
     </row>
     <row outlineLevel="0" r="43">
       <c r="A43" s="0" t="inlineStr">
         <is>
-          <t>185/70R14</t>
+          <t>185/65R15</t>
         </is>
       </c>
       <c r="B43" s="0" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>WESTLAKE</t>
         </is>
       </c>
       <c r="C43" s="0" t="inlineStr">
         <is>
-          <t>RD185/70R14</t>
+          <t>WL185/65R15</t>
         </is>
       </c>
       <c r="D43" s="0">
-        <v>2</v>
+        <v>94</v>
       </c>
       <c r="E43" s="0">
-        <v>1</v>
+        <v>86</v>
       </c>
       <c r="F43" s="0">
         <v>0</v>
       </c>
       <c r="G43" s="0">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H43" s="1">
-        <v>230</v>
+        <v>220</v>
       </c>
     </row>
     <row outlineLevel="0" r="44">
@@ -1744,28 +1744,28 @@
       </c>
       <c r="B44" s="0" t="inlineStr">
         <is>
-          <t>SEMPERIT</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C44" s="0" t="inlineStr">
         <is>
-          <t>SP185/70R14</t>
+          <t>RD185/70R14</t>
         </is>
       </c>
       <c r="D44" s="0">
         <v>2</v>
       </c>
       <c r="E44" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F44" s="0">
         <v>0</v>
       </c>
       <c r="G44" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H44" s="1">
-        <v>280</v>
+        <v>230</v>
       </c>
     </row>
     <row outlineLevel="0" r="45">
@@ -1776,60 +1776,60 @@
       </c>
       <c r="B45" s="0" t="inlineStr">
         <is>
-          <t>WESTLAKE</t>
+          <t>SEMPERIT</t>
         </is>
       </c>
       <c r="C45" s="0" t="inlineStr">
         <is>
-          <t>WL185/70R14</t>
+          <t>SP185/70R14</t>
         </is>
       </c>
       <c r="D45" s="0">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E45" s="0">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F45" s="0">
         <v>0</v>
       </c>
       <c r="G45" s="0">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H45" s="1">
-        <v>220</v>
+        <v>280</v>
       </c>
     </row>
     <row outlineLevel="0" r="46">
       <c r="A46" s="0" t="inlineStr">
         <is>
-          <t>195/50R15</t>
+          <t>185/70R14</t>
         </is>
       </c>
       <c r="B46" s="0" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>WESTLAKE</t>
         </is>
       </c>
       <c r="C46" s="0" t="inlineStr">
         <is>
-          <t>GD195/50R15</t>
+          <t>WL185/70R14</t>
         </is>
       </c>
       <c r="D46" s="0">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E46" s="0">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F46" s="0">
         <v>0</v>
       </c>
       <c r="G46" s="0">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H46" s="1">
-        <v>290</v>
+        <v>220</v>
       </c>
     </row>
     <row outlineLevel="0" r="47">
@@ -1840,28 +1840,28 @@
       </c>
       <c r="B47" s="0" t="inlineStr">
         <is>
-          <t>SEMPERIT</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C47" s="0" t="inlineStr">
         <is>
-          <t>SP195/50R15</t>
+          <t>GD195/50R15</t>
         </is>
       </c>
       <c r="D47" s="0">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="E47" s="0">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F47" s="0">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G47" s="0">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H47" s="1">
-        <v>260</v>
+        <v>290</v>
       </c>
     </row>
     <row outlineLevel="0" r="48">
@@ -1872,66 +1872,66 @@
       </c>
       <c r="B48" s="0" t="inlineStr">
         <is>
-          <t>WESTLAKE</t>
+          <t>SEMPERIT</t>
         </is>
       </c>
       <c r="C48" s="0" t="inlineStr">
         <is>
-          <t>WL195/50R15</t>
+          <t>SP195/50R15</t>
         </is>
       </c>
       <c r="D48" s="0">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="E48" s="0">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F48" s="0">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G48" s="0">
         <v>4</v>
       </c>
       <c r="H48" s="1">
-        <v>225</v>
+        <v>260</v>
       </c>
     </row>
     <row outlineLevel="0" r="49">
       <c r="A49" s="0" t="inlineStr">
         <is>
-          <t>195/50R16</t>
+          <t>195/50R15</t>
         </is>
       </c>
       <c r="B49" s="0" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>WESTLAKE</t>
         </is>
       </c>
       <c r="C49" s="0" t="inlineStr">
         <is>
-          <t>GD195/50R16</t>
+          <t>WL195/50R15</t>
         </is>
       </c>
       <c r="D49" s="0">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E49" s="0">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F49" s="0">
         <v>0</v>
       </c>
       <c r="G49" s="0">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H49" s="1">
-        <v>330</v>
+        <v>225</v>
       </c>
     </row>
     <row outlineLevel="0" r="50">
       <c r="A50" s="0" t="inlineStr">
         <is>
-          <t>195/55R16</t>
+          <t>195/50R16</t>
         </is>
       </c>
       <c r="B50" s="0" t="inlineStr">
@@ -1941,23 +1941,23 @@
       </c>
       <c r="C50" s="0" t="inlineStr">
         <is>
-          <t>GD195/55R16</t>
+          <t>GD195/50R16</t>
         </is>
       </c>
       <c r="D50" s="0">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="E50" s="0">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F50" s="0">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G50" s="0">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H50" s="1">
-        <v>350</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="51">
@@ -1968,28 +1968,28 @@
       </c>
       <c r="B51" s="0" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C51" s="0" t="inlineStr">
         <is>
-          <t>HK195/55R16</t>
+          <t>GD195/55R16</t>
         </is>
       </c>
       <c r="D51" s="0">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E51" s="0">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F51" s="0">
         <v>13</v>
       </c>
       <c r="G51" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H51" s="1">
-        <v>290</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="52">
@@ -2000,28 +2000,28 @@
       </c>
       <c r="B52" s="0" t="inlineStr">
         <is>
-          <t>LASSA</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C52" s="0" t="inlineStr">
         <is>
-          <t>LS195/55R16</t>
+          <t>HK195/55R16</t>
         </is>
       </c>
       <c r="D52" s="0">
+        <v>16</v>
+      </c>
+      <c r="E52" s="0">
+        <v>0</v>
+      </c>
+      <c r="F52" s="0">
+        <v>13</v>
+      </c>
+      <c r="G52" s="0">
         <v>3</v>
       </c>
-      <c r="E52" s="0">
-        <v>3</v>
-      </c>
-      <c r="F52" s="0">
-        <v>0</v>
-      </c>
-      <c r="G52" s="0">
-        <v>0</v>
-      </c>
       <c r="H52" s="1">
-        <v>280</v>
+        <v>290</v>
       </c>
     </row>
     <row outlineLevel="0" r="53">
@@ -2032,19 +2032,19 @@
       </c>
       <c r="B53" s="0" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>LASSA</t>
         </is>
       </c>
       <c r="C53" s="0" t="inlineStr">
         <is>
-          <t>NX195/55R16</t>
+          <t>LS195/55R16</t>
         </is>
       </c>
       <c r="D53" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E53" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F53" s="0">
         <v>0</v>
@@ -2053,7 +2053,7 @@
         <v>0</v>
       </c>
       <c r="H53" s="1">
-        <v>300</v>
+        <v>280</v>
       </c>
     </row>
     <row outlineLevel="0" r="54">
@@ -2064,92 +2064,92 @@
       </c>
       <c r="B54" s="0" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C54" s="0" t="inlineStr">
         <is>
-          <t>RD195/55R16</t>
+          <t>NX195/55R16</t>
         </is>
       </c>
       <c r="D54" s="0">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E54" s="0">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F54" s="0">
         <v>0</v>
       </c>
       <c r="G54" s="0">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H54" s="1">
-        <v>250</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="55">
       <c r="A55" s="0" t="inlineStr">
         <is>
-          <t>195/60R16</t>
+          <t>195/55R16</t>
         </is>
       </c>
       <c r="B55" s="0" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C55" s="0" t="inlineStr">
         <is>
-          <t>GD195/60R16</t>
+          <t>RD195/55R16</t>
         </is>
       </c>
       <c r="D55" s="0">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="E55" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F55" s="0">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="G55" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H55" s="1">
-        <v>355</v>
+        <v>250</v>
       </c>
     </row>
     <row outlineLevel="0" r="56">
       <c r="A56" s="0" t="inlineStr">
         <is>
-          <t>195/65R15</t>
+          <t>195/60R16</t>
         </is>
       </c>
       <c r="B56" s="0" t="inlineStr">
         <is>
-          <t>DOUBLESTAR</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C56" s="0" t="inlineStr">
         <is>
-          <t>DS195/65R15</t>
+          <t>GD195/60R16</t>
         </is>
       </c>
       <c r="D56" s="0">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="E56" s="0">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F56" s="0">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="G56" s="0">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H56" s="1">
-        <v>230</v>
+        <v>355</v>
       </c>
     </row>
     <row outlineLevel="0" r="57">
@@ -2160,22 +2160,22 @@
       </c>
       <c r="B57" s="0" t="inlineStr">
         <is>
-          <t>GOODRIDE</t>
+          <t>DOUBLESTAR</t>
         </is>
       </c>
       <c r="C57" s="0" t="inlineStr">
         <is>
-          <t>GR195/65R15</t>
+          <t>DS195/65R15</t>
         </is>
       </c>
       <c r="D57" s="0">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E57" s="0">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F57" s="0">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G57" s="0">
         <v>0</v>
@@ -2192,28 +2192,28 @@
       </c>
       <c r="B58" s="0" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODRIDE</t>
         </is>
       </c>
       <c r="C58" s="0" t="inlineStr">
         <is>
-          <t>HK195/65R15</t>
+          <t>GR195/65R15</t>
         </is>
       </c>
       <c r="D58" s="0">
         <v>4</v>
       </c>
       <c r="E58" s="0">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F58" s="0">
         <v>0</v>
       </c>
       <c r="G58" s="0">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H58" s="1">
-        <v>260</v>
+        <v>230</v>
       </c>
     </row>
     <row outlineLevel="0" r="59">
@@ -2224,28 +2224,28 @@
       </c>
       <c r="B59" s="0" t="inlineStr">
         <is>
-          <t>LASSA</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C59" s="0" t="inlineStr">
         <is>
-          <t>LS195/65R15</t>
+          <t>HK195/65R15</t>
         </is>
       </c>
       <c r="D59" s="0">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E59" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F59" s="0">
         <v>0</v>
       </c>
       <c r="G59" s="0">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H59" s="1">
-        <v>250</v>
+        <v>260</v>
       </c>
     </row>
     <row outlineLevel="0" r="60">
@@ -2256,19 +2256,19 @@
       </c>
       <c r="B60" s="0" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>LASSA</t>
         </is>
       </c>
       <c r="C60" s="0" t="inlineStr">
         <is>
-          <t>NX195/65R15</t>
+          <t>LS195/65R15</t>
         </is>
       </c>
       <c r="D60" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E60" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F60" s="0">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="H60" s="1">
-        <v>230</v>
+        <v>250</v>
       </c>
     </row>
     <row outlineLevel="0" r="61">
@@ -2288,25 +2288,25 @@
       </c>
       <c r="B61" s="0" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C61" s="0" t="inlineStr">
         <is>
-          <t>RD195/65R15</t>
+          <t>NX195/65R15</t>
         </is>
       </c>
       <c r="D61" s="0">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="E61" s="0">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F61" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G61" s="0">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H61" s="1">
         <v>230</v>
@@ -2320,140 +2320,140 @@
       </c>
       <c r="B62" s="0" t="inlineStr">
         <is>
-          <t>SEMPERIT</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C62" s="0" t="inlineStr">
         <is>
-          <t>SP195/65R15</t>
+          <t>RD195/65R15</t>
         </is>
       </c>
       <c r="D62" s="0">
-        <v>96</v>
+        <v>15</v>
       </c>
       <c r="E62" s="0">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F62" s="0">
-        <v>75</v>
+        <v>1</v>
       </c>
       <c r="G62" s="0">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H62" s="1">
-        <v>250</v>
+        <v>230</v>
       </c>
     </row>
     <row outlineLevel="0" r="63">
       <c r="A63" s="0" t="inlineStr">
         <is>
-          <t>195/70R15C</t>
+          <t>195/65R15</t>
         </is>
       </c>
       <c r="B63" s="0" t="inlineStr">
         <is>
-          <t>DAYTON</t>
+          <t>SEMPERIT</t>
         </is>
       </c>
       <c r="C63" s="0" t="inlineStr">
         <is>
-          <t>DT195/70R15C</t>
+          <t>SP195/65R15</t>
         </is>
       </c>
       <c r="D63" s="0">
-        <v>2</v>
+        <v>96</v>
       </c>
       <c r="E63" s="0">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F63" s="0">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="G63" s="0">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="H63" s="1">
-        <v>280</v>
+        <v>250</v>
       </c>
     </row>
     <row outlineLevel="0" r="64">
       <c r="A64" s="0" t="inlineStr">
         <is>
-          <t>195/75R16C</t>
+          <t>195/70R15C</t>
         </is>
       </c>
       <c r="B64" s="0" t="inlineStr">
         <is>
-          <t>GOODRIDE</t>
+          <t>DAYTON</t>
         </is>
       </c>
       <c r="C64" s="0" t="inlineStr">
         <is>
-          <t>GR195/75R16C</t>
+          <t>DT195/70R15C</t>
         </is>
       </c>
       <c r="D64" s="0">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E64" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F64" s="0">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G64" s="0">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H64" s="1">
-        <v>350</v>
+        <v>280</v>
       </c>
     </row>
     <row outlineLevel="0" r="65">
       <c r="A65" s="0" t="inlineStr">
         <is>
-          <t>195R15C</t>
+          <t>195/75R16C</t>
         </is>
       </c>
       <c r="B65" s="0" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>GOODRIDE</t>
         </is>
       </c>
       <c r="C65" s="0" t="inlineStr">
         <is>
-          <t>RD195R15C</t>
+          <t>GR195/75R16C</t>
         </is>
       </c>
       <c r="D65" s="0">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E65" s="0">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F65" s="0">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G65" s="0">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H65" s="1">
-        <v>250</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="66">
       <c r="A66" s="0" t="inlineStr">
         <is>
-          <t>205/45R17</t>
+          <t>195R15C</t>
         </is>
       </c>
       <c r="B66" s="0" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C66" s="0" t="inlineStr">
         <is>
-          <t>CT205/45R17</t>
+          <t>RD195R15C</t>
         </is>
       </c>
       <c r="D66" s="0">
@@ -2469,7 +2469,7 @@
         <v>0</v>
       </c>
       <c r="H66" s="1">
-        <v>550</v>
+        <v>250</v>
       </c>
     </row>
     <row outlineLevel="0" r="67">
@@ -2480,28 +2480,28 @@
       </c>
       <c r="B67" s="0" t="inlineStr">
         <is>
-          <t>FULDA</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C67" s="0" t="inlineStr">
         <is>
-          <t>FL205/45R17</t>
+          <t>CT205/45R17</t>
         </is>
       </c>
       <c r="D67" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E67" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F67" s="0">
         <v>0</v>
       </c>
       <c r="G67" s="0">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H67" s="1">
-        <v>380</v>
+        <v>550</v>
       </c>
     </row>
     <row outlineLevel="0" r="68">
@@ -2512,28 +2512,28 @@
       </c>
       <c r="B68" s="0" t="inlineStr">
         <is>
-          <t>GOODRIDE</t>
+          <t>FULDA</t>
         </is>
       </c>
       <c r="C68" s="0" t="inlineStr">
         <is>
-          <t>GR205/45R17</t>
+          <t>FL205/45R17</t>
         </is>
       </c>
       <c r="D68" s="0">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E68" s="0">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F68" s="0">
         <v>0</v>
       </c>
       <c r="G68" s="0">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H68" s="1">
-        <v>300</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="69">
@@ -2544,28 +2544,28 @@
       </c>
       <c r="B69" s="0" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>GOODRIDE</t>
         </is>
       </c>
       <c r="C69" s="0" t="inlineStr">
         <is>
-          <t>GD205/45R17</t>
+          <t>GR205/45R17</t>
         </is>
       </c>
       <c r="D69" s="0">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="E69" s="0">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F69" s="0">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G69" s="0">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H69" s="1">
-        <v>450</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="70">
@@ -2576,28 +2576,28 @@
       </c>
       <c r="B70" s="0" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C70" s="0" t="inlineStr">
         <is>
-          <t>NX205/45R17</t>
+          <t>GD205/45R17</t>
         </is>
       </c>
       <c r="D70" s="0">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="E70" s="0">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F70" s="0">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G70" s="0">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H70" s="1">
-        <v>380</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="71">
@@ -2608,83 +2608,83 @@
       </c>
       <c r="B71" s="0" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C71" s="0" t="inlineStr">
         <is>
-          <t>RD205/45R17</t>
+          <t>NX205/45R17</t>
         </is>
       </c>
       <c r="D71" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E71" s="0">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F71" s="0">
         <v>0</v>
       </c>
       <c r="G71" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H71" s="1">
-        <v>300</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="72">
       <c r="A72" s="0" t="inlineStr">
         <is>
-          <t>205/50R17</t>
+          <t>205/45R17</t>
         </is>
       </c>
       <c r="B72" s="0" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C72" s="0" t="inlineStr">
         <is>
-          <t>CT205/50R17</t>
+          <t>RD205/45R17</t>
         </is>
       </c>
       <c r="D72" s="0">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E72" s="0">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F72" s="0">
         <v>0</v>
       </c>
       <c r="G72" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H72" s="1">
-        <v>450</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="73">
       <c r="A73" s="0" t="inlineStr">
         <is>
-          <t>205/55R16</t>
+          <t>205/50R17</t>
         </is>
       </c>
       <c r="B73" s="0" t="inlineStr">
         <is>
-          <t>AMINE</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C73" s="0" t="inlineStr">
         <is>
-          <t>AM205/55R16</t>
+          <t>CT205/50R17</t>
         </is>
       </c>
       <c r="D73" s="0">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E73" s="0">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F73" s="0">
         <v>0</v>
@@ -2693,7 +2693,7 @@
         <v>0</v>
       </c>
       <c r="H73" s="1">
-        <v>240</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="74">
@@ -2704,19 +2704,19 @@
       </c>
       <c r="B74" s="0" t="inlineStr">
         <is>
-          <t>DOUBLESTAR</t>
+          <t>AMINE</t>
         </is>
       </c>
       <c r="C74" s="0" t="inlineStr">
         <is>
-          <t>DS205/55R16</t>
+          <t>AM205/55R16</t>
         </is>
       </c>
       <c r="D74" s="0">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E74" s="0">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F74" s="0">
         <v>0</v>
@@ -2725,7 +2725,7 @@
         <v>0</v>
       </c>
       <c r="H74" s="1">
-        <v>230</v>
+        <v>240</v>
       </c>
     </row>
     <row outlineLevel="0" r="75">
@@ -2736,28 +2736,28 @@
       </c>
       <c r="B75" s="0" t="inlineStr">
         <is>
-          <t>FULDA</t>
+          <t>DOUBLESTAR</t>
         </is>
       </c>
       <c r="C75" s="0" t="inlineStr">
         <is>
-          <t>FL205/55R16</t>
+          <t>DS205/55R16</t>
         </is>
       </c>
       <c r="D75" s="0">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="E75" s="0">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F75" s="0">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="G75" s="0">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H75" s="1">
-        <v>250</v>
+        <v>230</v>
       </c>
     </row>
     <row outlineLevel="0" r="76">
@@ -2768,25 +2768,25 @@
       </c>
       <c r="B76" s="0" t="inlineStr">
         <is>
-          <t>GOODRIDE</t>
+          <t>FULDA</t>
         </is>
       </c>
       <c r="C76" s="0" t="inlineStr">
         <is>
-          <t>GR205/55R16</t>
+          <t>FL205/55R16</t>
         </is>
       </c>
       <c r="D76" s="0">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="E76" s="0">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F76" s="0">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G76" s="0">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H76" s="1">
         <v>250</v>
@@ -2800,28 +2800,28 @@
       </c>
       <c r="B77" s="0" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>GOODRIDE</t>
         </is>
       </c>
       <c r="C77" s="0" t="inlineStr">
         <is>
-          <t>GD205/55R16</t>
+          <t>GR205/55R16</t>
         </is>
       </c>
       <c r="D77" s="0">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E77" s="0">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F77" s="0">
         <v>0</v>
       </c>
       <c r="G77" s="0">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H77" s="1">
-        <v>280</v>
+        <v>250</v>
       </c>
     </row>
     <row outlineLevel="0" r="78">
@@ -2832,28 +2832,28 @@
       </c>
       <c r="B78" s="0" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C78" s="0" t="inlineStr">
         <is>
-          <t>HK205/55R16</t>
+          <t>GD205/55R16</t>
         </is>
       </c>
       <c r="D78" s="0">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E78" s="0">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F78" s="0">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G78" s="0">
         <v>4</v>
       </c>
       <c r="H78" s="1">
-        <v>260</v>
+        <v>280</v>
       </c>
     </row>
     <row outlineLevel="0" r="79">
@@ -2864,48 +2864,48 @@
       </c>
       <c r="B79" s="0" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C79" s="0" t="inlineStr">
         <is>
-          <t>RD205/55R16</t>
+          <t>HK205/55R16</t>
         </is>
       </c>
       <c r="D79" s="0">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="E79" s="0">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F79" s="0">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G79" s="0">
         <v>4</v>
       </c>
       <c r="H79" s="1">
-        <v>230</v>
+        <v>260</v>
       </c>
     </row>
     <row outlineLevel="0" r="80">
       <c r="A80" s="0" t="inlineStr">
         <is>
-          <t>205/55R16RF</t>
+          <t>205/55R16</t>
         </is>
       </c>
       <c r="B80" s="0" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C80" s="0" t="inlineStr">
         <is>
-          <t>GD205/55R16RF</t>
+          <t>RD205/55R16</t>
         </is>
       </c>
       <c r="D80" s="0">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E80" s="0">
         <v>0</v>
@@ -2914,16 +2914,16 @@
         <v>0</v>
       </c>
       <c r="G80" s="0">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H80" s="1">
-        <v>480</v>
+        <v>230</v>
       </c>
     </row>
     <row outlineLevel="0" r="81">
       <c r="A81" s="0" t="inlineStr">
         <is>
-          <t>205/55R17</t>
+          <t>205/55R16RF</t>
         </is>
       </c>
       <c r="B81" s="0" t="inlineStr">
@@ -2933,23 +2933,23 @@
       </c>
       <c r="C81" s="0" t="inlineStr">
         <is>
-          <t>GD205/55R17</t>
+          <t>GD205/55R16RF</t>
         </is>
       </c>
       <c r="D81" s="0">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="E81" s="0">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F81" s="0">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G81" s="0">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H81" s="1">
-        <v>450</v>
+        <v>480</v>
       </c>
     </row>
     <row outlineLevel="0" r="82">
@@ -2960,51 +2960,51 @@
       </c>
       <c r="B82" s="0" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C82" s="0" t="inlineStr">
         <is>
-          <t>NX205/55R17</t>
+          <t>GD205/55R17</t>
         </is>
       </c>
       <c r="D82" s="0">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="E82" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F82" s="0">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G82" s="0">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H82" s="1">
-        <v>400</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="83">
       <c r="A83" s="0" t="inlineStr">
         <is>
-          <t>205/60R16</t>
+          <t>205/55R17</t>
         </is>
       </c>
       <c r="B83" s="0" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C83" s="0" t="inlineStr">
         <is>
-          <t>DL205/60R16</t>
+          <t>NX205/55R17</t>
         </is>
       </c>
       <c r="D83" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E83" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F83" s="0">
         <v>0</v>
@@ -3013,7 +3013,7 @@
         <v>0</v>
       </c>
       <c r="H83" s="1">
-        <v>330</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="84">
@@ -3024,28 +3024,28 @@
       </c>
       <c r="B84" s="0" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C84" s="0" t="inlineStr">
         <is>
-          <t>GD205/60R16</t>
+          <t>DL205/60R16</t>
         </is>
       </c>
       <c r="D84" s="0">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="E84" s="0">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F84" s="0">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G84" s="0">
         <v>0</v>
       </c>
       <c r="H84" s="1">
-        <v>380</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="85">
@@ -3056,28 +3056,28 @@
       </c>
       <c r="B85" s="0" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C85" s="0" t="inlineStr">
         <is>
-          <t>HK205/60R16</t>
+          <t>GD205/60R16</t>
         </is>
       </c>
       <c r="D85" s="0">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E85" s="0">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F85" s="0">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="G85" s="0">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H85" s="1">
-        <v>300</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="86">
@@ -3088,25 +3088,25 @@
       </c>
       <c r="B86" s="0" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C86" s="0" t="inlineStr">
         <is>
-          <t>LF205/60R16</t>
+          <t>HK205/60R16</t>
         </is>
       </c>
       <c r="D86" s="0">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E86" s="0">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F86" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G86" s="0">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H86" s="1">
         <v>300</v>
@@ -3115,24 +3115,24 @@
     <row outlineLevel="0" r="87">
       <c r="A87" s="0" t="inlineStr">
         <is>
-          <t>205/65R15</t>
+          <t>205/60R16</t>
         </is>
       </c>
       <c r="B87" s="0" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C87" s="0" t="inlineStr">
         <is>
-          <t>HK205/65R15</t>
+          <t>LF205/60R16</t>
         </is>
       </c>
       <c r="D87" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E87" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F87" s="0">
         <v>0</v>
@@ -3141,30 +3141,30 @@
         <v>0</v>
       </c>
       <c r="H87" s="1">
-        <v>270</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="88">
       <c r="A88" s="0" t="inlineStr">
         <is>
-          <t>205/65R16</t>
+          <t>205/65R15</t>
         </is>
       </c>
       <c r="B88" s="0" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C88" s="0" t="inlineStr">
         <is>
-          <t>BR205/65R16</t>
+          <t>HK205/65R15</t>
         </is>
       </c>
       <c r="D88" s="0">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E88" s="0">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F88" s="0">
         <v>0</v>
@@ -3173,7 +3173,7 @@
         <v>0</v>
       </c>
       <c r="H88" s="1">
-        <v>420</v>
+        <v>270</v>
       </c>
     </row>
     <row outlineLevel="0" r="89">
@@ -3184,19 +3184,19 @@
       </c>
       <c r="B89" s="0" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C89" s="0" t="inlineStr">
         <is>
-          <t>HK205/65R16</t>
+          <t>BR205/65R16</t>
         </is>
       </c>
       <c r="D89" s="0">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E89" s="0">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F89" s="0">
         <v>0</v>
@@ -3205,39 +3205,39 @@
         <v>0</v>
       </c>
       <c r="H89" s="1">
-        <v>380</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="90">
       <c r="A90" s="0" t="inlineStr">
         <is>
-          <t>215/40R18</t>
+          <t>205/65R16</t>
         </is>
       </c>
       <c r="B90" s="0" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C90" s="0" t="inlineStr">
         <is>
-          <t>GD215/40R18</t>
+          <t>HK205/65R16</t>
         </is>
       </c>
       <c r="D90" s="0">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E90" s="0">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F90" s="0">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G90" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H90" s="1">
-        <v>600</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="91">
@@ -3248,44 +3248,44 @@
       </c>
       <c r="B91" s="0" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C91" s="0" t="inlineStr">
         <is>
-          <t>HK215/40R18</t>
+          <t>GD215/40R18</t>
         </is>
       </c>
       <c r="D91" s="0">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E91" s="0">
         <v>4</v>
       </c>
       <c r="F91" s="0">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G91" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H91" s="1">
-        <v>490</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="92">
       <c r="A92" s="0" t="inlineStr">
         <is>
-          <t>215/45R16</t>
+          <t>215/40R18</t>
         </is>
       </c>
       <c r="B92" s="0" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C92" s="0" t="inlineStr">
         <is>
-          <t>GD215/45R16</t>
+          <t>HK215/40R18</t>
         </is>
       </c>
       <c r="D92" s="0">
@@ -3301,13 +3301,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="1">
-        <v>450</v>
+        <v>490</v>
       </c>
     </row>
     <row outlineLevel="0" r="93">
       <c r="A93" s="0" t="inlineStr">
         <is>
-          <t>215/45R17</t>
+          <t>215/45R16</t>
         </is>
       </c>
       <c r="B93" s="0" t="inlineStr">
@@ -3317,14 +3317,14 @@
       </c>
       <c r="C93" s="0" t="inlineStr">
         <is>
-          <t>GD215/45R17</t>
+          <t>GD215/45R16</t>
         </is>
       </c>
       <c r="D93" s="0">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E93" s="0">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F93" s="0">
         <v>0</v>
@@ -3333,7 +3333,7 @@
         <v>0</v>
       </c>
       <c r="H93" s="1">
-        <v>400</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="94">
@@ -3344,25 +3344,25 @@
       </c>
       <c r="B94" s="0" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C94" s="0" t="inlineStr">
         <is>
-          <t>HK215/45R17</t>
+          <t>GD215/45R17</t>
         </is>
       </c>
       <c r="D94" s="0">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="E94" s="0">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F94" s="0">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G94" s="0">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H94" s="1">
         <v>400</v>
@@ -3376,28 +3376,28 @@
       </c>
       <c r="B95" s="0" t="inlineStr">
         <is>
-          <t>IRIS</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C95" s="0" t="inlineStr">
         <is>
-          <t>IR215/45R17</t>
+          <t>HK215/45R17</t>
         </is>
       </c>
       <c r="D95" s="0">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="E95" s="0">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F95" s="0">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G95" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H95" s="1">
-        <v>300</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="96">
@@ -3408,28 +3408,28 @@
       </c>
       <c r="B96" s="0" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>IRIS</t>
         </is>
       </c>
       <c r="C96" s="0" t="inlineStr">
         <is>
-          <t>LF215/45R17</t>
+          <t>IR215/45R17</t>
         </is>
       </c>
       <c r="D96" s="0">
         <v>1</v>
       </c>
       <c r="E96" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F96" s="0">
         <v>0</v>
       </c>
       <c r="G96" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H96" s="1">
-        <v>350</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="97">
@@ -3440,83 +3440,83 @@
       </c>
       <c r="B97" s="0" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C97" s="0" t="inlineStr">
         <is>
-          <t>NX215/45R17</t>
+          <t>LF215/45R17</t>
         </is>
       </c>
       <c r="D97" s="0">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E97" s="0">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F97" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G97" s="0">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H97" s="1">
-        <v>380</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="98">
       <c r="A98" s="0" t="inlineStr">
         <is>
-          <t>215/45R18</t>
+          <t>215/45R17</t>
         </is>
       </c>
       <c r="B98" s="0" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C98" s="0" t="inlineStr">
         <is>
-          <t>GD215/45R18</t>
+          <t>NX215/45R17</t>
         </is>
       </c>
       <c r="D98" s="0">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E98" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F98" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G98" s="0">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H98" s="1">
-        <v>550</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="99">
       <c r="A99" s="0" t="inlineStr">
         <is>
-          <t>215/50R17</t>
+          <t>215/45R18</t>
         </is>
       </c>
       <c r="B99" s="0" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C99" s="0" t="inlineStr">
         <is>
-          <t>BR215/50R17</t>
+          <t>GD215/45R18</t>
         </is>
       </c>
       <c r="D99" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E99" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F99" s="0">
         <v>0</v>
@@ -3525,7 +3525,7 @@
         <v>0</v>
       </c>
       <c r="H99" s="1">
-        <v>450</v>
+        <v>550</v>
       </c>
     </row>
     <row outlineLevel="0" r="100">
@@ -3536,28 +3536,28 @@
       </c>
       <c r="B100" s="0" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C100" s="0" t="inlineStr">
         <is>
-          <t>GD215/50R17</t>
+          <t>BR215/50R17</t>
         </is>
       </c>
       <c r="D100" s="0">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E100" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F100" s="0">
         <v>0</v>
       </c>
       <c r="G100" s="0">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H100" s="1">
-        <v>470</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="101">
@@ -3568,28 +3568,28 @@
       </c>
       <c r="B101" s="0" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C101" s="0" t="inlineStr">
         <is>
-          <t>HK215/50R17</t>
+          <t>GD215/50R17</t>
         </is>
       </c>
       <c r="D101" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E101" s="0">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F101" s="0">
         <v>0</v>
       </c>
       <c r="G101" s="0">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H101" s="1">
-        <v>400</v>
+        <v>470</v>
       </c>
     </row>
     <row outlineLevel="0" r="102">
@@ -3600,19 +3600,19 @@
       </c>
       <c r="B102" s="0" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C102" s="0" t="inlineStr">
         <is>
-          <t>LF215/50R17</t>
+          <t>HK215/50R17</t>
         </is>
       </c>
       <c r="D102" s="0">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E102" s="0">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F102" s="0">
         <v>0</v>
@@ -3621,30 +3621,30 @@
         <v>0</v>
       </c>
       <c r="H102" s="1">
-        <v>420</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="103">
       <c r="A103" s="0" t="inlineStr">
         <is>
-          <t>215/50R18</t>
+          <t>215/50R17</t>
         </is>
       </c>
       <c r="B103" s="0" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C103" s="0" t="inlineStr">
         <is>
-          <t>GD215/50R18</t>
+          <t>LF215/50R17</t>
         </is>
       </c>
       <c r="D103" s="0">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E103" s="0">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F103" s="0">
         <v>0</v>
@@ -3653,13 +3653,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="1">
-        <v>600</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="104">
       <c r="A104" s="0" t="inlineStr">
         <is>
-          <t>215/55R16</t>
+          <t>215/50R18</t>
         </is>
       </c>
       <c r="B104" s="0" t="inlineStr">
@@ -3669,14 +3669,14 @@
       </c>
       <c r="C104" s="0" t="inlineStr">
         <is>
-          <t>GD215/55R16</t>
+          <t>GD215/50R18</t>
         </is>
       </c>
       <c r="D104" s="0">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E104" s="0">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F104" s="0">
         <v>0</v>
@@ -3685,7 +3685,7 @@
         <v>0</v>
       </c>
       <c r="H104" s="1">
-        <v>440</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="105">
@@ -3696,12 +3696,12 @@
       </c>
       <c r="B105" s="0" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C105" s="0" t="inlineStr">
         <is>
-          <t>LF215/55R16</t>
+          <t>GD215/55R16</t>
         </is>
       </c>
       <c r="D105" s="0">
@@ -3717,23 +3717,23 @@
         <v>0</v>
       </c>
       <c r="H105" s="1">
-        <v>350</v>
+        <v>440</v>
       </c>
     </row>
     <row outlineLevel="0" r="106">
       <c r="A106" s="0" t="inlineStr">
         <is>
-          <t>215/55R17</t>
+          <t>215/55R16</t>
         </is>
       </c>
       <c r="B106" s="0" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C106" s="0" t="inlineStr">
         <is>
-          <t>BR215/55R17</t>
+          <t>LF215/55R16</t>
         </is>
       </c>
       <c r="D106" s="0">
@@ -3749,7 +3749,7 @@
         <v>0</v>
       </c>
       <c r="H106" s="1">
-        <v>480</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="107">
@@ -3760,19 +3760,19 @@
       </c>
       <c r="B107" s="0" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C107" s="0" t="inlineStr">
         <is>
-          <t>HK215/55R17</t>
+          <t>BR215/55R17</t>
         </is>
       </c>
       <c r="D107" s="0">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E107" s="0">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F107" s="0">
         <v>0</v>
@@ -3781,23 +3781,23 @@
         <v>0</v>
       </c>
       <c r="H107" s="1">
-        <v>420</v>
+        <v>480</v>
       </c>
     </row>
     <row outlineLevel="0" r="108">
       <c r="A108" s="0" t="inlineStr">
         <is>
-          <t>215/55R18</t>
+          <t>215/55R17</t>
         </is>
       </c>
       <c r="B108" s="0" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C108" s="0" t="inlineStr">
         <is>
-          <t>GD215/55R18</t>
+          <t>HK215/55R17</t>
         </is>
       </c>
       <c r="D108" s="0">
@@ -3813,23 +3813,23 @@
         <v>0</v>
       </c>
       <c r="H108" s="1">
-        <v>580</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="109">
       <c r="A109" s="0" t="inlineStr">
         <is>
-          <t>215/60R16</t>
+          <t>215/55R18</t>
         </is>
       </c>
       <c r="B109" s="0" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C109" s="0" t="inlineStr">
         <is>
-          <t>BR215/60R16</t>
+          <t>GD215/55R18</t>
         </is>
       </c>
       <c r="D109" s="0">
@@ -3845,7 +3845,7 @@
         <v>0</v>
       </c>
       <c r="H109" s="1">
-        <v>350</v>
+        <v>580</v>
       </c>
     </row>
     <row outlineLevel="0" r="110">
@@ -3856,25 +3856,25 @@
       </c>
       <c r="B110" s="0" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C110" s="0" t="inlineStr">
         <is>
-          <t>DL215/60R16</t>
+          <t>BR215/60R16</t>
         </is>
       </c>
       <c r="D110" s="0">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E110" s="0">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F110" s="0">
         <v>0</v>
       </c>
       <c r="G110" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H110" s="1">
         <v>350</v>
@@ -3888,28 +3888,28 @@
       </c>
       <c r="B111" s="0" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C111" s="0" t="inlineStr">
         <is>
-          <t>HK215/60R16</t>
+          <t>DL215/60R16</t>
         </is>
       </c>
       <c r="D111" s="0">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E111" s="0">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F111" s="0">
         <v>0</v>
       </c>
       <c r="G111" s="0">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H111" s="1">
-        <v>330</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="112">
@@ -3920,25 +3920,25 @@
       </c>
       <c r="B112" s="0" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C112" s="0" t="inlineStr">
         <is>
-          <t>NX215/60R16</t>
+          <t>HK215/60R16</t>
         </is>
       </c>
       <c r="D112" s="0">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E112" s="0">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F112" s="0">
         <v>0</v>
       </c>
       <c r="G112" s="0">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H112" s="1">
         <v>330</v>
@@ -3947,65 +3947,65 @@
     <row outlineLevel="0" r="113">
       <c r="A113" s="0" t="inlineStr">
         <is>
-          <t>215/60R17</t>
+          <t>215/60R16</t>
         </is>
       </c>
       <c r="B113" s="0" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C113" s="0" t="inlineStr">
         <is>
-          <t>RD215/60R17</t>
+          <t>NX215/60R16</t>
         </is>
       </c>
       <c r="D113" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E113" s="0">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F113" s="0">
         <v>0</v>
       </c>
       <c r="G113" s="0">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H113" s="1">
-        <v>300</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="114">
       <c r="A114" s="0" t="inlineStr">
         <is>
-          <t>215/65R16</t>
+          <t>215/60R17</t>
         </is>
       </c>
       <c r="B114" s="0" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C114" s="0" t="inlineStr">
         <is>
-          <t>GD215/65R16</t>
+          <t>RD215/60R17</t>
         </is>
       </c>
       <c r="D114" s="0">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E114" s="0">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F114" s="0">
         <v>0</v>
       </c>
       <c r="G114" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H114" s="1">
-        <v>380</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="115">
@@ -4016,83 +4016,83 @@
       </c>
       <c r="B115" s="0" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C115" s="0" t="inlineStr">
         <is>
-          <t>HK215/65R16</t>
+          <t>GD215/65R16</t>
         </is>
       </c>
       <c r="D115" s="0">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E115" s="0">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F115" s="0">
         <v>0</v>
       </c>
       <c r="G115" s="0">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H115" s="1">
-        <v>330</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="116">
       <c r="A116" s="0" t="inlineStr">
         <is>
-          <t>215/65R17</t>
+          <t>215/65R16</t>
         </is>
       </c>
       <c r="B116" s="0" t="inlineStr">
         <is>
-          <t>MICHELIN</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C116" s="0" t="inlineStr">
         <is>
-          <t>MC215/65R17</t>
+          <t>HK215/65R16</t>
         </is>
       </c>
       <c r="D116" s="0">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E116" s="0">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F116" s="0">
         <v>0</v>
       </c>
       <c r="G116" s="0">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H116" s="1">
-        <v>600</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="117">
       <c r="A117" s="0" t="inlineStr">
         <is>
-          <t>225/40R18</t>
+          <t>215/65R17</t>
         </is>
       </c>
       <c r="B117" s="0" t="inlineStr">
         <is>
-          <t>BARUM</t>
+          <t>MICHELIN</t>
         </is>
       </c>
       <c r="C117" s="0" t="inlineStr">
         <is>
-          <t>BM225/40R18</t>
+          <t>MC215/65R17</t>
         </is>
       </c>
       <c r="D117" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E117" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F117" s="0">
         <v>0</v>
@@ -4101,7 +4101,7 @@
         <v>0</v>
       </c>
       <c r="H117" s="1">
-        <v>420</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="118">
@@ -4112,28 +4112,28 @@
       </c>
       <c r="B118" s="0" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>BARUM</t>
         </is>
       </c>
       <c r="C118" s="0" t="inlineStr">
         <is>
-          <t>GD225/40R18</t>
+          <t>BM225/40R18</t>
         </is>
       </c>
       <c r="D118" s="0">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="E118" s="0">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F118" s="0">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G118" s="0">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H118" s="1">
-        <v>480</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="119">
@@ -4144,28 +4144,28 @@
       </c>
       <c r="B119" s="0" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C119" s="0" t="inlineStr">
         <is>
-          <t>HK225/40R18</t>
+          <t>GD225/40R18</t>
         </is>
       </c>
       <c r="D119" s="0">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="E119" s="0">
         <v>4</v>
       </c>
       <c r="F119" s="0">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G119" s="0">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H119" s="1">
-        <v>450</v>
+        <v>480</v>
       </c>
     </row>
     <row outlineLevel="0" r="120">
@@ -4176,28 +4176,28 @@
       </c>
       <c r="B120" s="0" t="inlineStr">
         <is>
-          <t>LASSA</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C120" s="0" t="inlineStr">
         <is>
-          <t>LS225/40R18</t>
+          <t>HK225/40R18</t>
         </is>
       </c>
       <c r="D120" s="0">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E120" s="0">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F120" s="0">
         <v>0</v>
       </c>
       <c r="G120" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H120" s="1">
-        <v>330</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="121">
@@ -4208,28 +4208,28 @@
       </c>
       <c r="B121" s="0" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>LASSA</t>
         </is>
       </c>
       <c r="C121" s="0" t="inlineStr">
         <is>
-          <t>NX225/40R18</t>
+          <t>LS225/40R18</t>
         </is>
       </c>
       <c r="D121" s="0">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E121" s="0">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F121" s="0">
         <v>0</v>
       </c>
       <c r="G121" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H121" s="1">
-        <v>400</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="122">
@@ -4240,19 +4240,19 @@
       </c>
       <c r="B122" s="0" t="inlineStr">
         <is>
-          <t>SEMPERIT</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C122" s="0" t="inlineStr">
         <is>
-          <t>SP225/40R18</t>
+          <t>NX225/40R18</t>
         </is>
       </c>
       <c r="D122" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E122" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F122" s="0">
         <v>0</v>
@@ -4261,30 +4261,30 @@
         <v>0</v>
       </c>
       <c r="H122" s="1">
-        <v>450</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="123">
       <c r="A123" s="0" t="inlineStr">
         <is>
-          <t>225/40R18RF</t>
+          <t>225/40R18</t>
         </is>
       </c>
       <c r="B123" s="0" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>SEMPERIT</t>
         </is>
       </c>
       <c r="C123" s="0" t="inlineStr">
         <is>
-          <t>GD225/40R18RF</t>
+          <t>SP225/40R18</t>
         </is>
       </c>
       <c r="D123" s="0">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E123" s="0">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F123" s="0">
         <v>0</v>
@@ -4293,30 +4293,30 @@
         <v>0</v>
       </c>
       <c r="H123" s="1">
-        <v>590</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="124">
       <c r="A124" s="0" t="inlineStr">
         <is>
-          <t>225/45R17</t>
+          <t>225/40R18RF</t>
         </is>
       </c>
       <c r="B124" s="0" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C124" s="0" t="inlineStr">
         <is>
-          <t>CT225/45R17</t>
+          <t>GD225/40R18RF</t>
         </is>
       </c>
       <c r="D124" s="0">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E124" s="0">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F124" s="0">
         <v>0</v>
@@ -4325,7 +4325,7 @@
         <v>0</v>
       </c>
       <c r="H124" s="1">
-        <v>400</v>
+        <v>590</v>
       </c>
     </row>
     <row outlineLevel="0" r="125">
@@ -4336,28 +4336,28 @@
       </c>
       <c r="B125" s="0" t="inlineStr">
         <is>
-          <t>FULDA</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C125" s="0" t="inlineStr">
         <is>
-          <t>FL225/45R17</t>
+          <t>CT225/45R17</t>
         </is>
       </c>
       <c r="D125" s="0">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="E125" s="0">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F125" s="0">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G125" s="0">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H125" s="1">
-        <v>350</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="126">
@@ -4368,28 +4368,28 @@
       </c>
       <c r="B126" s="0" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>FULDA</t>
         </is>
       </c>
       <c r="C126" s="0" t="inlineStr">
         <is>
-          <t>GD225/45R17</t>
+          <t>FL225/45R17</t>
         </is>
       </c>
       <c r="D126" s="0">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E126" s="0">
         <v>6</v>
       </c>
       <c r="F126" s="0">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G126" s="0">
         <v>4</v>
       </c>
       <c r="H126" s="1">
-        <v>380</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="127">
@@ -4400,60 +4400,60 @@
       </c>
       <c r="B127" s="0" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C127" s="0" t="inlineStr">
         <is>
-          <t>HK225/45R17</t>
+          <t>GD225/45R17</t>
         </is>
       </c>
       <c r="D127" s="0">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="E127" s="0">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F127" s="0">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G127" s="0">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H127" s="1">
-        <v>350</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="128">
       <c r="A128" s="0" t="inlineStr">
         <is>
-          <t>225/45R18</t>
+          <t>225/45R17</t>
         </is>
       </c>
       <c r="B128" s="0" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C128" s="0" t="inlineStr">
         <is>
-          <t>DL225/45R18</t>
+          <t>HK225/45R17</t>
         </is>
       </c>
       <c r="D128" s="0">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E128" s="0">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F128" s="0">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G128" s="0">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H128" s="1">
-        <v>500</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="129">
@@ -4464,28 +4464,28 @@
       </c>
       <c r="B129" s="0" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C129" s="0" t="inlineStr">
         <is>
-          <t>GD225/45R18</t>
+          <t>DL225/45R18</t>
         </is>
       </c>
       <c r="D129" s="0">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E129" s="0">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F129" s="0">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G129" s="0">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H129" s="1">
-        <v>550</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="130">
@@ -4496,28 +4496,28 @@
       </c>
       <c r="B130" s="0" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C130" s="0" t="inlineStr">
         <is>
-          <t>HK225/45R18</t>
+          <t>GD225/45R18</t>
         </is>
       </c>
       <c r="D130" s="0">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E130" s="0">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F130" s="0">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G130" s="0">
         <v>0</v>
       </c>
       <c r="H130" s="1">
-        <v>450</v>
+        <v>550</v>
       </c>
     </row>
     <row outlineLevel="0" r="131">
@@ -4528,19 +4528,19 @@
       </c>
       <c r="B131" s="0" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C131" s="0" t="inlineStr">
         <is>
-          <t>LF225/45R18</t>
+          <t>HK225/45R18</t>
         </is>
       </c>
       <c r="D131" s="0">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E131" s="0">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F131" s="0">
         <v>0</v>
@@ -4549,71 +4549,71 @@
         <v>0</v>
       </c>
       <c r="H131" s="1">
-        <v>420</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="132">
       <c r="A132" s="0" t="inlineStr">
         <is>
-          <t>225/45R18RF</t>
+          <t>225/45R18</t>
         </is>
       </c>
       <c r="B132" s="0" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C132" s="0" t="inlineStr">
         <is>
-          <t>GD225/45R18RF</t>
+          <t>LF225/45R18</t>
         </is>
       </c>
       <c r="D132" s="0">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E132" s="0">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F132" s="0">
         <v>0</v>
       </c>
       <c r="G132" s="0">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H132" s="1">
-        <v>720</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="133">
       <c r="A133" s="0" t="inlineStr">
         <is>
-          <t>225/45R19</t>
+          <t>225/45R18RF</t>
         </is>
       </c>
       <c r="B133" s="0" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C133" s="0" t="inlineStr">
         <is>
-          <t>CT225/45R19</t>
+          <t>GD225/45R18RF</t>
         </is>
       </c>
       <c r="D133" s="0">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E133" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F133" s="0">
         <v>0</v>
       </c>
       <c r="G133" s="0">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H133" s="1">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row outlineLevel="0" r="134">
@@ -4624,12 +4624,12 @@
       </c>
       <c r="B134" s="0" t="inlineStr">
         <is>
-          <t>LASSA</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C134" s="0" t="inlineStr">
         <is>
-          <t>LS225/45R19</t>
+          <t>CT225/45R19</t>
         </is>
       </c>
       <c r="D134" s="0">
@@ -4645,7 +4645,7 @@
         <v>0</v>
       </c>
       <c r="H134" s="1">
-        <v>520</v>
+        <v>780</v>
       </c>
     </row>
     <row outlineLevel="0" r="135">
@@ -4697,10 +4697,10 @@
         </is>
       </c>
       <c r="D136" s="0">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E136" s="0">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F136" s="0">
         <v>8</v>
@@ -6553,13 +6553,13 @@
         </is>
       </c>
       <c r="D194" s="0">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E194" s="0">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F194" s="0">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G194" s="0">
         <v>0</v>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FA60994-4C12-4EDF-BD5B-E4CFC82D11B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A38046E4-9083-4B8F-85F3-0FFDCB7C06EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1434,7 +1434,7 @@
         <v>9</v>
       </c>
       <c r="D2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E2">
         <v>4</v>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Desktop\speed-pneu\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A38046E4-9083-4B8F-85F3-0FFDCB7C06EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63F556D3-7537-40FF-8C06-56D8FCB6C4F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="15375" windowHeight="7875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PAPERS" sheetId="1" r:id="rId1"/>
@@ -2188,10 +2188,10 @@
         <v>63</v>
       </c>
       <c r="D31">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E31">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F31">
         <v>0</v>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -496,7 +496,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H197"/>
+  <dimension ref="A1:H196"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col customWidth="true" min="1" max="1" width="13.8359375"/>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="D23" s="5">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E23" s="5">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F23" s="5">
         <v>0</v>
@@ -2602,17 +2602,17 @@
     <row outlineLevel="0" r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>195R15C</t>
+          <t>205/45R17</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>RD195R15C</t>
+          <t>CT205/45R17</t>
         </is>
       </c>
       <c r="D66" s="5">
@@ -2628,7 +2628,7 @@
         <v>0</v>
       </c>
       <c r="H66" s="6">
-        <v>250</v>
+        <v>550</v>
       </c>
     </row>
     <row outlineLevel="0" r="67">
@@ -2639,28 +2639,28 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>FULDA</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>CT205/45R17</t>
+          <t>FL205/45R17</t>
         </is>
       </c>
       <c r="D67" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E67" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F67" s="5">
         <v>0</v>
       </c>
       <c r="G67" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H67" s="6">
-        <v>550</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="68">
@@ -2671,28 +2671,28 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>FULDA</t>
+          <t>GOODRIDE</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>FL205/45R17</t>
+          <t>GR205/45R17</t>
         </is>
       </c>
       <c r="D68" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E68" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F68" s="5">
         <v>0</v>
       </c>
       <c r="G68" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H68" s="6">
-        <v>380</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="69">
@@ -2703,28 +2703,28 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>GOODRIDE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>GR205/45R17</t>
+          <t>GD205/45R17</t>
         </is>
       </c>
       <c r="D69" s="5">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="E69" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F69" s="5">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G69" s="5">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H69" s="6">
-        <v>300</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="70">
@@ -2735,28 +2735,28 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>GD205/45R17</t>
+          <t>NX205/45R17</t>
         </is>
       </c>
       <c r="D70" s="5">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="E70" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F70" s="5">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G70" s="5">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H70" s="6">
-        <v>450</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="71">
@@ -2767,83 +2767,83 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>NX205/45R17</t>
+          <t>RD205/45R17</t>
         </is>
       </c>
       <c r="D71" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E71" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F71" s="5">
         <v>0</v>
       </c>
       <c r="G71" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H71" s="6">
-        <v>380</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>205/45R17</t>
+          <t>205/50R17</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>RD205/45R17</t>
+          <t>CT205/50R17</t>
         </is>
       </c>
       <c r="D72" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E72" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F72" s="5">
         <v>0</v>
       </c>
       <c r="G72" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H72" s="6">
-        <v>300</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>205/50R17</t>
+          <t>205/55R16</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>AMINE</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>CT205/50R17</t>
+          <t>AM205/55R16</t>
         </is>
       </c>
       <c r="D73" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E73" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F73" s="5">
         <v>0</v>
@@ -2852,7 +2852,7 @@
         <v>0</v>
       </c>
       <c r="H73" s="6">
-        <v>450</v>
+        <v>240</v>
       </c>
     </row>
     <row outlineLevel="0" r="74">
@@ -2863,19 +2863,19 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>AMINE</t>
+          <t>DOUBLESTAR</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>AM205/55R16</t>
+          <t>DS205/55R16</t>
         </is>
       </c>
       <c r="D74" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E74" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F74" s="5">
         <v>0</v>
@@ -2884,7 +2884,7 @@
         <v>0</v>
       </c>
       <c r="H74" s="6">
-        <v>240</v>
+        <v>230</v>
       </c>
     </row>
     <row outlineLevel="0" r="75">
@@ -2895,28 +2895,28 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>DOUBLESTAR</t>
+          <t>FULDA</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>DS205/55R16</t>
+          <t>FL205/55R16</t>
         </is>
       </c>
       <c r="D75" s="5">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="E75" s="5">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F75" s="5">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G75" s="5">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H75" s="6">
-        <v>230</v>
+        <v>250</v>
       </c>
     </row>
     <row outlineLevel="0" r="76">
@@ -2927,25 +2927,25 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>FULDA</t>
+          <t>GOODRIDE</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>FL205/55R16</t>
+          <t>GR205/55R16</t>
         </is>
       </c>
       <c r="D76" s="5">
-        <v>45</v>
+        <v>1</v>
       </c>
       <c r="E76" s="5">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F76" s="5">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="G76" s="5">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H76" s="6">
         <v>250</v>
@@ -2959,28 +2959,28 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>GOODRIDE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>GR205/55R16</t>
+          <t>GD205/55R16</t>
         </is>
       </c>
       <c r="D77" s="5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E77" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F77" s="5">
         <v>0</v>
       </c>
       <c r="G77" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H77" s="6">
-        <v>250</v>
+        <v>280</v>
       </c>
     </row>
     <row outlineLevel="0" r="78">
@@ -2991,28 +2991,28 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>GD205/55R16</t>
+          <t>HK205/55R16</t>
         </is>
       </c>
       <c r="D78" s="5">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E78" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F78" s="5">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G78" s="5">
         <v>4</v>
       </c>
       <c r="H78" s="6">
-        <v>280</v>
+        <v>260</v>
       </c>
     </row>
     <row outlineLevel="0" r="79">
@@ -3023,48 +3023,48 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>HK205/55R16</t>
+          <t>RD205/55R16</t>
         </is>
       </c>
       <c r="D79" s="5">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="E79" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F79" s="5">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G79" s="5">
         <v>4</v>
       </c>
       <c r="H79" s="6">
-        <v>260</v>
+        <v>230</v>
       </c>
     </row>
     <row outlineLevel="0" r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>205/55R16</t>
+          <t>205/55R16RF</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>RD205/55R16</t>
+          <t>GD205/55R16RF</t>
         </is>
       </c>
       <c r="D80" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E80" s="5">
         <v>0</v>
@@ -3073,16 +3073,16 @@
         <v>0</v>
       </c>
       <c r="G80" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H80" s="6">
-        <v>230</v>
+        <v>480</v>
       </c>
     </row>
     <row outlineLevel="0" r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>205/55R16RF</t>
+          <t>205/55R17</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
@@ -3092,23 +3092,23 @@
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>GD205/55R16RF</t>
+          <t>GD205/55R17</t>
         </is>
       </c>
       <c r="D81" s="5">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="E81" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F81" s="5">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G81" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H81" s="6">
-        <v>480</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="82">
@@ -3119,51 +3119,51 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>GD205/55R17</t>
+          <t>NX205/55R17</t>
         </is>
       </c>
       <c r="D82" s="5">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="E82" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F82" s="5">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G82" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H82" s="6">
-        <v>450</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>205/55R17</t>
+          <t>205/60R16</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>NX205/55R17</t>
+          <t>DL205/60R16</t>
         </is>
       </c>
       <c r="D83" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E83" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F83" s="5">
         <v>0</v>
@@ -3172,7 +3172,7 @@
         <v>0</v>
       </c>
       <c r="H83" s="6">
-        <v>400</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="84">
@@ -3183,28 +3183,28 @@
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>DL205/60R16</t>
+          <t>GD205/60R16</t>
         </is>
       </c>
       <c r="D84" s="5">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="E84" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F84" s="5">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G84" s="5">
         <v>0</v>
       </c>
       <c r="H84" s="6">
-        <v>330</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="85">
@@ -3215,28 +3215,28 @@
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>GD205/60R16</t>
+          <t>HK205/60R16</t>
         </is>
       </c>
       <c r="D85" s="5">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E85" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F85" s="5">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="G85" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H85" s="6">
-        <v>380</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="86">
@@ -3247,25 +3247,25 @@
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>HK205/60R16</t>
+          <t>LF205/60R16</t>
         </is>
       </c>
       <c r="D86" s="5">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E86" s="5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F86" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G86" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H86" s="6">
         <v>300</v>
@@ -3274,24 +3274,24 @@
     <row outlineLevel="0" r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>205/60R16</t>
+          <t>205/65R15</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>LF205/60R16</t>
+          <t>HK205/65R15</t>
         </is>
       </c>
       <c r="D87" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E87" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F87" s="5">
         <v>0</v>
@@ -3300,30 +3300,30 @@
         <v>0</v>
       </c>
       <c r="H87" s="6">
-        <v>300</v>
+        <v>270</v>
       </c>
     </row>
     <row outlineLevel="0" r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>205/65R15</t>
+          <t>205/65R16</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>HK205/65R15</t>
+          <t>BR205/65R16</t>
         </is>
       </c>
       <c r="D88" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E88" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F88" s="5">
         <v>0</v>
@@ -3332,7 +3332,7 @@
         <v>0</v>
       </c>
       <c r="H88" s="6">
-        <v>270</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="89">
@@ -3343,19 +3343,19 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>BR205/65R16</t>
+          <t>HK205/65R16</t>
         </is>
       </c>
       <c r="D89" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E89" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F89" s="5">
         <v>0</v>
@@ -3364,39 +3364,39 @@
         <v>0</v>
       </c>
       <c r="H89" s="6">
-        <v>420</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>205/65R16</t>
+          <t>215/40R18</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>HK205/65R16</t>
+          <t>GD215/40R18</t>
         </is>
       </c>
       <c r="D90" s="5">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E90" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F90" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G90" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H90" s="6">
-        <v>380</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="91">
@@ -3407,44 +3407,44 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>GD215/40R18</t>
+          <t>HK215/40R18</t>
         </is>
       </c>
       <c r="D91" s="5">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E91" s="5">
         <v>4</v>
       </c>
       <c r="F91" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G91" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H91" s="6">
-        <v>600</v>
+        <v>490</v>
       </c>
     </row>
     <row outlineLevel="0" r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>215/40R18</t>
+          <t>215/45R16</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>HK215/40R18</t>
+          <t>GD215/45R16</t>
         </is>
       </c>
       <c r="D92" s="5">
@@ -3460,13 +3460,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="6">
-        <v>490</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>215/45R16</t>
+          <t>215/45R17</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
@@ -3476,14 +3476,14 @@
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>GD215/45R16</t>
+          <t>GD215/45R17</t>
         </is>
       </c>
       <c r="D93" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E93" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F93" s="5">
         <v>0</v>
@@ -3492,7 +3492,7 @@
         <v>0</v>
       </c>
       <c r="H93" s="6">
-        <v>450</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="94">
@@ -3503,25 +3503,25 @@
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>GD215/45R17</t>
+          <t>HK215/45R17</t>
         </is>
       </c>
       <c r="D94" s="5">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="E94" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F94" s="5">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G94" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H94" s="6">
         <v>400</v>
@@ -3535,28 +3535,28 @@
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>IRIS</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>HK215/45R17</t>
+          <t>IR215/45R17</t>
         </is>
       </c>
       <c r="D95" s="5">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="E95" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F95" s="5">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G95" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H95" s="6">
-        <v>400</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="96">
@@ -3567,28 +3567,28 @@
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>IRIS</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>IR215/45R17</t>
+          <t>LF215/45R17</t>
         </is>
       </c>
       <c r="D96" s="5">
         <v>1</v>
       </c>
       <c r="E96" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F96" s="5">
         <v>0</v>
       </c>
       <c r="G96" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H96" s="6">
-        <v>300</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="97">
@@ -3599,83 +3599,83 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>LF215/45R17</t>
+          <t>NX215/45R17</t>
         </is>
       </c>
       <c r="D97" s="5">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E97" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F97" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G97" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H97" s="6">
-        <v>350</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="98">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>215/45R17</t>
+          <t>215/45R18</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>NX215/45R17</t>
+          <t>GD215/45R18</t>
         </is>
       </c>
       <c r="D98" s="5">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E98" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F98" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G98" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H98" s="6">
-        <v>380</v>
+        <v>550</v>
       </c>
     </row>
     <row outlineLevel="0" r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>215/45R18</t>
+          <t>215/50R17</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>GD215/45R18</t>
+          <t>BR215/50R17</t>
         </is>
       </c>
       <c r="D99" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E99" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F99" s="5">
         <v>0</v>
@@ -3684,7 +3684,7 @@
         <v>0</v>
       </c>
       <c r="H99" s="6">
-        <v>550</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="100">
@@ -3695,28 +3695,28 @@
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>BR215/50R17</t>
+          <t>GD215/50R17</t>
         </is>
       </c>
       <c r="D100" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E100" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F100" s="5">
         <v>0</v>
       </c>
       <c r="G100" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H100" s="6">
-        <v>450</v>
+        <v>470</v>
       </c>
     </row>
     <row outlineLevel="0" r="101">
@@ -3727,28 +3727,28 @@
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>GD215/50R17</t>
+          <t>HK215/50R17</t>
         </is>
       </c>
       <c r="D101" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E101" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F101" s="5">
         <v>0</v>
       </c>
       <c r="G101" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H101" s="6">
-        <v>470</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="102">
@@ -3759,19 +3759,19 @@
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>HK215/50R17</t>
+          <t>LF215/50R17</t>
         </is>
       </c>
       <c r="D102" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E102" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F102" s="5">
         <v>0</v>
@@ -3780,30 +3780,30 @@
         <v>0</v>
       </c>
       <c r="H102" s="6">
-        <v>400</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>215/50R17</t>
+          <t>215/50R18</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>LF215/50R17</t>
+          <t>GD215/50R18</t>
         </is>
       </c>
       <c r="D103" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E103" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F103" s="5">
         <v>0</v>
@@ -3812,13 +3812,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="6">
-        <v>420</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="104">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>215/50R18</t>
+          <t>215/55R16</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
@@ -3828,14 +3828,14 @@
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>GD215/50R18</t>
+          <t>GD215/55R16</t>
         </is>
       </c>
       <c r="D104" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E104" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F104" s="5">
         <v>0</v>
@@ -3844,7 +3844,7 @@
         <v>0</v>
       </c>
       <c r="H104" s="6">
-        <v>600</v>
+        <v>440</v>
       </c>
     </row>
     <row outlineLevel="0" r="105">
@@ -3855,12 +3855,12 @@
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>GD215/55R16</t>
+          <t>LF215/55R16</t>
         </is>
       </c>
       <c r="D105" s="5">
@@ -3876,23 +3876,23 @@
         <v>0</v>
       </c>
       <c r="H105" s="6">
-        <v>440</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="106">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>215/55R16</t>
+          <t>215/55R17</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>LF215/55R16</t>
+          <t>BR215/55R17</t>
         </is>
       </c>
       <c r="D106" s="5">
@@ -3908,7 +3908,7 @@
         <v>0</v>
       </c>
       <c r="H106" s="6">
-        <v>350</v>
+        <v>480</v>
       </c>
     </row>
     <row outlineLevel="0" r="107">
@@ -3919,19 +3919,19 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>BR215/55R17</t>
+          <t>HK215/55R17</t>
         </is>
       </c>
       <c r="D107" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E107" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F107" s="5">
         <v>0</v>
@@ -3940,23 +3940,23 @@
         <v>0</v>
       </c>
       <c r="H107" s="6">
-        <v>480</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="108">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>215/55R17</t>
+          <t>215/55R18</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>HK215/55R17</t>
+          <t>GD215/55R18</t>
         </is>
       </c>
       <c r="D108" s="5">
@@ -3972,23 +3972,23 @@
         <v>0</v>
       </c>
       <c r="H108" s="6">
-        <v>420</v>
+        <v>580</v>
       </c>
     </row>
     <row outlineLevel="0" r="109">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>215/55R18</t>
+          <t>215/60R16</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>GD215/55R18</t>
+          <t>BR215/60R16</t>
         </is>
       </c>
       <c r="D109" s="5">
@@ -4004,7 +4004,7 @@
         <v>0</v>
       </c>
       <c r="H109" s="6">
-        <v>580</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="110">
@@ -4015,25 +4015,25 @@
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>BR215/60R16</t>
+          <t>DL215/60R16</t>
         </is>
       </c>
       <c r="D110" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E110" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F110" s="5">
         <v>0</v>
       </c>
       <c r="G110" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H110" s="6">
         <v>350</v>
@@ -4047,28 +4047,28 @@
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>DL215/60R16</t>
+          <t>HK215/60R16</t>
         </is>
       </c>
       <c r="D111" s="5">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E111" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F111" s="5">
         <v>0</v>
       </c>
       <c r="G111" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H111" s="6">
-        <v>350</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="112">
@@ -4079,25 +4079,25 @@
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>HK215/60R16</t>
+          <t>NX215/60R16</t>
         </is>
       </c>
       <c r="D112" s="5">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E112" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F112" s="5">
         <v>0</v>
       </c>
       <c r="G112" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H112" s="6">
         <v>330</v>
@@ -4106,65 +4106,65 @@
     <row outlineLevel="0" r="113">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>215/60R16</t>
+          <t>215/60R17</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>NX215/60R16</t>
+          <t>RD215/60R17</t>
         </is>
       </c>
       <c r="D113" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E113" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F113" s="5">
         <v>0</v>
       </c>
       <c r="G113" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H113" s="6">
-        <v>330</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="114">
       <c r="A114" s="4" t="inlineStr">
         <is>
-          <t>215/60R17</t>
+          <t>215/65R16</t>
         </is>
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>RD215/60R17</t>
+          <t>GD215/65R16</t>
         </is>
       </c>
       <c r="D114" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E114" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F114" s="5">
         <v>0</v>
       </c>
       <c r="G114" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H114" s="6">
-        <v>300</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="115">
@@ -4175,83 +4175,83 @@
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>GD215/65R16</t>
+          <t>HK215/65R16</t>
         </is>
       </c>
       <c r="D115" s="5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E115" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F115" s="5">
         <v>0</v>
       </c>
       <c r="G115" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H115" s="6">
-        <v>380</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="116">
       <c r="A116" s="4" t="inlineStr">
         <is>
-          <t>215/65R16</t>
+          <t>215/65R17</t>
         </is>
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>MICHELIN</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>HK215/65R16</t>
+          <t>MC215/65R17</t>
         </is>
       </c>
       <c r="D116" s="5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E116" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F116" s="5">
         <v>0</v>
       </c>
       <c r="G116" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H116" s="6">
-        <v>330</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="117">
       <c r="A117" s="4" t="inlineStr">
         <is>
-          <t>215/65R17</t>
+          <t>225/40R18</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>MICHELIN</t>
+          <t>BARUM</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>MC215/65R17</t>
+          <t>BM225/40R18</t>
         </is>
       </c>
       <c r="D117" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E117" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F117" s="5">
         <v>0</v>
@@ -4260,7 +4260,7 @@
         <v>0</v>
       </c>
       <c r="H117" s="6">
-        <v>600</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="118">
@@ -4271,28 +4271,28 @@
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>BARUM</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>BM225/40R18</t>
+          <t>GD225/40R18</t>
         </is>
       </c>
       <c r="D118" s="5">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="E118" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F118" s="5">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G118" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H118" s="6">
-        <v>420</v>
+        <v>480</v>
       </c>
     </row>
     <row outlineLevel="0" r="119">
@@ -4303,28 +4303,28 @@
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>GD225/40R18</t>
+          <t>HK225/40R18</t>
         </is>
       </c>
       <c r="D119" s="5">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="E119" s="5">
         <v>4</v>
       </c>
       <c r="F119" s="5">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G119" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H119" s="6">
-        <v>480</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="120">
@@ -4335,28 +4335,28 @@
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>LASSA</t>
         </is>
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>HK225/40R18</t>
+          <t>LS225/40R18</t>
         </is>
       </c>
       <c r="D120" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E120" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F120" s="5">
         <v>0</v>
       </c>
       <c r="G120" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H120" s="6">
-        <v>450</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="121">
@@ -4367,28 +4367,28 @@
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>LASSA</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>LS225/40R18</t>
+          <t>NX225/40R18</t>
         </is>
       </c>
       <c r="D121" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E121" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F121" s="5">
         <v>0</v>
       </c>
       <c r="G121" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H121" s="6">
-        <v>330</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="122">
@@ -4399,19 +4399,19 @@
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>SEMPERIT</t>
         </is>
       </c>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>NX225/40R18</t>
+          <t>SP225/40R18</t>
         </is>
       </c>
       <c r="D122" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E122" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F122" s="5">
         <v>0</v>
@@ -4420,30 +4420,30 @@
         <v>0</v>
       </c>
       <c r="H122" s="6">
-        <v>400</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="123">
       <c r="A123" s="4" t="inlineStr">
         <is>
-          <t>225/40R18</t>
+          <t>225/40R18RF</t>
         </is>
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>SEMPERIT</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>SP225/40R18</t>
+          <t>GD225/40R18RF</t>
         </is>
       </c>
       <c r="D123" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E123" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F123" s="5">
         <v>0</v>
@@ -4452,30 +4452,30 @@
         <v>0</v>
       </c>
       <c r="H123" s="6">
-        <v>450</v>
+        <v>590</v>
       </c>
     </row>
     <row outlineLevel="0" r="124">
       <c r="A124" s="4" t="inlineStr">
         <is>
-          <t>225/40R18RF</t>
+          <t>225/45R17</t>
         </is>
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>GD225/40R18RF</t>
+          <t>CT225/45R17</t>
         </is>
       </c>
       <c r="D124" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E124" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F124" s="5">
         <v>0</v>
@@ -4484,7 +4484,7 @@
         <v>0</v>
       </c>
       <c r="H124" s="6">
-        <v>590</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="125">
@@ -4495,28 +4495,28 @@
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>FULDA</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>CT225/45R17</t>
+          <t>FL225/45R17</t>
         </is>
       </c>
       <c r="D125" s="5">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="E125" s="5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F125" s="5">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G125" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H125" s="6">
-        <v>400</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="126">
@@ -4527,28 +4527,28 @@
       </c>
       <c r="B126" s="4" t="inlineStr">
         <is>
-          <t>FULDA</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C126" s="4" t="inlineStr">
         <is>
-          <t>FL225/45R17</t>
+          <t>GD225/45R17</t>
         </is>
       </c>
       <c r="D126" s="5">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E126" s="5">
         <v>6</v>
       </c>
       <c r="F126" s="5">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G126" s="5">
         <v>4</v>
       </c>
       <c r="H126" s="6">
-        <v>350</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="127">
@@ -4559,60 +4559,60 @@
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>GD225/45R17</t>
+          <t>HK225/45R17</t>
         </is>
       </c>
       <c r="D127" s="5">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="E127" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F127" s="5">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="G127" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H127" s="6">
-        <v>380</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="128">
       <c r="A128" s="4" t="inlineStr">
         <is>
-          <t>225/45R17</t>
+          <t>225/45R18</t>
         </is>
       </c>
       <c r="B128" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C128" s="4" t="inlineStr">
         <is>
-          <t>HK225/45R17</t>
+          <t>DL225/45R18</t>
         </is>
       </c>
       <c r="D128" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E128" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F128" s="5">
         <v>0</v>
       </c>
       <c r="G128" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H128" s="6">
-        <v>350</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="129">
@@ -4623,28 +4623,28 @@
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>DL225/45R18</t>
+          <t>GD225/45R18</t>
         </is>
       </c>
       <c r="D129" s="5">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E129" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F129" s="5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G129" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H129" s="6">
-        <v>500</v>
+        <v>550</v>
       </c>
     </row>
     <row outlineLevel="0" r="130">
@@ -4655,28 +4655,28 @@
       </c>
       <c r="B130" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C130" s="4" t="inlineStr">
         <is>
-          <t>GD225/45R18</t>
+          <t>HK225/45R18</t>
         </is>
       </c>
       <c r="D130" s="5">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E130" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F130" s="5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G130" s="5">
         <v>0</v>
       </c>
       <c r="H130" s="6">
-        <v>550</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="131">
@@ -4687,19 +4687,19 @@
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>HK225/45R18</t>
+          <t>LF225/45R18</t>
         </is>
       </c>
       <c r="D131" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E131" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F131" s="5">
         <v>0</v>
@@ -4708,103 +4708,103 @@
         <v>0</v>
       </c>
       <c r="H131" s="6">
-        <v>450</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="132">
       <c r="A132" s="4" t="inlineStr">
         <is>
-          <t>225/45R18</t>
+          <t>225/45R18RF</t>
         </is>
       </c>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C132" s="4" t="inlineStr">
         <is>
-          <t>LF225/45R18</t>
+          <t>GD225/45R18RF</t>
         </is>
       </c>
       <c r="D132" s="5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E132" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F132" s="5">
         <v>0</v>
       </c>
       <c r="G132" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H132" s="6">
-        <v>420</v>
+        <v>720</v>
       </c>
     </row>
     <row outlineLevel="0" r="133">
       <c r="A133" s="4" t="inlineStr">
         <is>
-          <t>225/45R18RF</t>
+          <t>225/45R19</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>GD225/45R18RF</t>
+          <t>CT225/45R19</t>
         </is>
       </c>
       <c r="D133" s="5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E133" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F133" s="5">
         <v>0</v>
       </c>
       <c r="G133" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H133" s="6">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row outlineLevel="0" r="134">
       <c r="A134" s="4" t="inlineStr">
         <is>
-          <t>225/45R19</t>
+          <t>225/50R17</t>
         </is>
       </c>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C134" s="4" t="inlineStr">
         <is>
-          <t>CT225/45R19</t>
+          <t>GD225/50R17</t>
         </is>
       </c>
       <c r="D134" s="5">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E134" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F134" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G134" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H134" s="6">
-        <v>780</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="135">
@@ -4815,60 +4815,60 @@
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>GD225/50R17</t>
+          <t>HK225/50R17</t>
         </is>
       </c>
       <c r="D135" s="5">
+        <v>13</v>
+      </c>
+      <c r="E135" s="5">
+        <v>3</v>
+      </c>
+      <c r="F135" s="5">
         <v>8</v>
       </c>
-      <c r="E135" s="5">
-        <v>4</v>
-      </c>
-      <c r="F135" s="5">
-        <v>2</v>
-      </c>
       <c r="G135" s="5">
         <v>2</v>
       </c>
       <c r="H135" s="6">
-        <v>500</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="136">
       <c r="A136" s="4" t="inlineStr">
         <is>
-          <t>225/50R17</t>
+          <t>225/55R16</t>
         </is>
       </c>
       <c r="B136" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C136" s="4" t="inlineStr">
         <is>
-          <t>HK225/50R17</t>
+          <t>DL225/55R16</t>
         </is>
       </c>
       <c r="D136" s="5">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E136" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F136" s="5">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G136" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H136" s="6">
-        <v>400</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="137">
@@ -4879,19 +4879,19 @@
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>DL225/55R16</t>
+          <t>GD225/55R16</t>
         </is>
       </c>
       <c r="D137" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E137" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F137" s="5">
         <v>0</v>
@@ -4900,30 +4900,30 @@
         <v>0</v>
       </c>
       <c r="H137" s="6">
-        <v>450</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="138">
       <c r="A138" s="4" t="inlineStr">
         <is>
-          <t>225/55R16</t>
+          <t>225/55R17</t>
         </is>
       </c>
       <c r="B138" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C138" s="4" t="inlineStr">
         <is>
-          <t>GD225/55R16</t>
+          <t>HK225/55R17</t>
         </is>
       </c>
       <c r="D138" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E138" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F138" s="5">
         <v>0</v>
@@ -4932,71 +4932,71 @@
         <v>0</v>
       </c>
       <c r="H138" s="6">
-        <v>420</v>
+        <v>430</v>
       </c>
     </row>
     <row outlineLevel="0" r="139">
       <c r="A139" s="4" t="inlineStr">
         <is>
-          <t>225/55R17</t>
+          <t>225/55R17RF</t>
         </is>
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>HK225/55R17</t>
+          <t>GD225/55R17RF</t>
         </is>
       </c>
       <c r="D139" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E139" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F139" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G139" s="5">
         <v>0</v>
       </c>
       <c r="H139" s="6">
-        <v>430</v>
+        <v>700</v>
       </c>
     </row>
     <row outlineLevel="0" r="140">
       <c r="A140" s="4" t="inlineStr">
         <is>
-          <t>225/55R17RF</t>
+          <t>225/55R18</t>
         </is>
       </c>
       <c r="B140" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C140" s="4" t="inlineStr">
         <is>
-          <t>GD225/55R17RF</t>
+          <t>HK225/55R18</t>
         </is>
       </c>
       <c r="D140" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E140" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F140" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G140" s="5">
         <v>0</v>
       </c>
       <c r="H140" s="6">
-        <v>700</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="141">
@@ -5007,19 +5007,19 @@
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>KUMHO</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>HK225/55R18</t>
+          <t>KM225/55R18</t>
         </is>
       </c>
       <c r="D141" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E141" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F141" s="5">
         <v>0</v>
@@ -5028,30 +5028,30 @@
         <v>0</v>
       </c>
       <c r="H141" s="6">
-        <v>500</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="142">
       <c r="A142" s="4" t="inlineStr">
         <is>
-          <t>225/55R18</t>
+          <t>225/55R19</t>
         </is>
       </c>
       <c r="B142" s="4" t="inlineStr">
         <is>
-          <t>KUMHO</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C142" s="4" t="inlineStr">
         <is>
-          <t>KM225/55R18</t>
+          <t>BR225/55R19</t>
         </is>
       </c>
       <c r="D142" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E142" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F142" s="5">
         <v>0</v>
@@ -5060,7 +5060,7 @@
         <v>0</v>
       </c>
       <c r="H142" s="6">
-        <v>450</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="143">
@@ -5071,19 +5071,19 @@
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>BR225/55R19</t>
+          <t>GD225/55R19</t>
         </is>
       </c>
       <c r="D143" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E143" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F143" s="5">
         <v>0</v>
@@ -5098,21 +5098,21 @@
     <row outlineLevel="0" r="144">
       <c r="A144" s="4" t="inlineStr">
         <is>
-          <t>225/55R19</t>
+          <t>225/60R17</t>
         </is>
       </c>
       <c r="B144" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C144" s="4" t="inlineStr">
         <is>
-          <t>GD225/55R19</t>
+          <t>HK225/60R17</t>
         </is>
       </c>
       <c r="D144" s="5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E144" s="5">
         <v>4</v>
@@ -5121,65 +5121,65 @@
         <v>0</v>
       </c>
       <c r="G144" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H144" s="6">
-        <v>750</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="145">
       <c r="A145" s="4" t="inlineStr">
         <is>
-          <t>225/60R17</t>
+          <t>225/60R18</t>
         </is>
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>HK225/60R17</t>
+          <t>GD225/60R18</t>
         </is>
       </c>
       <c r="D145" s="5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E145" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F145" s="5">
         <v>0</v>
       </c>
       <c r="G145" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H145" s="6">
-        <v>400</v>
+        <v>700</v>
       </c>
     </row>
     <row outlineLevel="0" r="146">
       <c r="A146" s="4" t="inlineStr">
         <is>
-          <t>225/60R18</t>
+          <t>225/65R17</t>
         </is>
       </c>
       <c r="B146" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C146" s="4" t="inlineStr">
         <is>
-          <t>GD225/60R18</t>
+          <t>RD225/65R17</t>
         </is>
       </c>
       <c r="D146" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E146" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F146" s="5">
         <v>0</v>
@@ -5188,13 +5188,13 @@
         <v>0</v>
       </c>
       <c r="H146" s="6">
-        <v>700</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="147">
       <c r="A147" s="4" t="inlineStr">
         <is>
-          <t>225/65R17</t>
+          <t>225/75R15C</t>
         </is>
       </c>
       <c r="B147" s="4" t="inlineStr">
@@ -5204,29 +5204,29 @@
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>RD225/65R17</t>
+          <t>RD225/75R15C</t>
         </is>
       </c>
       <c r="D147" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E147" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F147" s="5">
         <v>0</v>
       </c>
       <c r="G147" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H147" s="6">
-        <v>450</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="148">
       <c r="A148" s="4" t="inlineStr">
         <is>
-          <t>225/75R15C</t>
+          <t>235/35R19</t>
         </is>
       </c>
       <c r="B148" s="4" t="inlineStr">
@@ -5236,61 +5236,61 @@
       </c>
       <c r="C148" s="4" t="inlineStr">
         <is>
-          <t>RD225/75R15C</t>
+          <t>RD235/35R19</t>
         </is>
       </c>
       <c r="D148" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E148" s="5">
         <v>0</v>
       </c>
       <c r="F148" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G148" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H148" s="6">
-        <v>330</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="149">
       <c r="A149" s="4" t="inlineStr">
         <is>
-          <t>235/35R19</t>
+          <t>235/40R19</t>
         </is>
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>RD235/35R19</t>
+          <t>GD235/40R19</t>
         </is>
       </c>
       <c r="D149" s="5">
         <v>4</v>
       </c>
       <c r="E149" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F149" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G149" s="5">
         <v>0</v>
       </c>
       <c r="H149" s="6">
-        <v>600</v>
+        <v>850</v>
       </c>
     </row>
     <row outlineLevel="0" r="150">
       <c r="A150" s="4" t="inlineStr">
         <is>
-          <t>235/40R19</t>
+          <t>235/45R18</t>
         </is>
       </c>
       <c r="B150" s="4" t="inlineStr">
@@ -5300,7 +5300,7 @@
       </c>
       <c r="C150" s="4" t="inlineStr">
         <is>
-          <t>GD235/40R19</t>
+          <t>GD235/45R18</t>
         </is>
       </c>
       <c r="D150" s="5">
@@ -5316,30 +5316,30 @@
         <v>0</v>
       </c>
       <c r="H150" s="6">
-        <v>850</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="151">
       <c r="A151" s="4" t="inlineStr">
         <is>
-          <t>235/45R18</t>
+          <t>235/50R18</t>
         </is>
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>GD235/45R18</t>
+          <t>HK235/50R18</t>
         </is>
       </c>
       <c r="D151" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E151" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F151" s="5">
         <v>0</v>
@@ -5348,30 +5348,30 @@
         <v>0</v>
       </c>
       <c r="H151" s="6">
-        <v>600</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="152">
       <c r="A152" s="4" t="inlineStr">
         <is>
-          <t>235/50R18</t>
+          <t>235/50R19</t>
         </is>
       </c>
       <c r="B152" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C152" s="4" t="inlineStr">
         <is>
-          <t>HK235/50R18</t>
+          <t>GD235/50R19</t>
         </is>
       </c>
       <c r="D152" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E152" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F152" s="5">
         <v>0</v>
@@ -5380,13 +5380,13 @@
         <v>0</v>
       </c>
       <c r="H152" s="6">
-        <v>500</v>
+        <v>800</v>
       </c>
     </row>
     <row outlineLevel="0" r="153">
       <c r="A153" s="4" t="inlineStr">
         <is>
-          <t>235/50R19</t>
+          <t>235/50R20</t>
         </is>
       </c>
       <c r="B153" s="4" t="inlineStr">
@@ -5396,78 +5396,78 @@
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>GD235/50R19</t>
+          <t>GD235/50R20</t>
         </is>
       </c>
       <c r="D153" s="5">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E153" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F153" s="5">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G153" s="5">
         <v>0</v>
       </c>
       <c r="H153" s="6">
-        <v>800</v>
+        <v>1180</v>
       </c>
     </row>
     <row outlineLevel="0" r="154">
       <c r="A154" s="4" t="inlineStr">
         <is>
-          <t>235/50R20</t>
+          <t>235/55R17</t>
         </is>
       </c>
       <c r="B154" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C154" s="4" t="inlineStr">
         <is>
-          <t>GD235/50R20</t>
+          <t>BR235/55R17</t>
         </is>
       </c>
       <c r="D154" s="5">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E154" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F154" s="5">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G154" s="5">
         <v>0</v>
       </c>
       <c r="H154" s="6">
-        <v>1180</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="155">
       <c r="A155" s="4" t="inlineStr">
         <is>
-          <t>235/55R17</t>
+          <t>235/55R18</t>
         </is>
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>BR235/55R17</t>
+          <t>HK235/55R18</t>
         </is>
       </c>
       <c r="D155" s="5">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E155" s="5">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F155" s="5">
         <v>0</v>
@@ -5476,30 +5476,30 @@
         <v>0</v>
       </c>
       <c r="H155" s="6">
-        <v>450</v>
+        <v>480</v>
       </c>
     </row>
     <row outlineLevel="0" r="156">
       <c r="A156" s="4" t="inlineStr">
         <is>
-          <t>235/55R18</t>
+          <t>235/55R19</t>
         </is>
       </c>
       <c r="B156" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C156" s="4" t="inlineStr">
         <is>
-          <t>HK235/55R18</t>
+          <t>GD235/55R19</t>
         </is>
       </c>
       <c r="D156" s="5">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E156" s="5">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F156" s="5">
         <v>0</v>
@@ -5508,7 +5508,7 @@
         <v>0</v>
       </c>
       <c r="H156" s="6">
-        <v>480</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="157">
@@ -5519,19 +5519,19 @@
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>GD235/55R19</t>
+          <t>HK235/55R19</t>
         </is>
       </c>
       <c r="D157" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E157" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F157" s="5">
         <v>0</v>
@@ -5540,7 +5540,7 @@
         <v>0</v>
       </c>
       <c r="H157" s="6">
-        <v>750</v>
+        <v>630</v>
       </c>
     </row>
     <row outlineLevel="0" r="158">
@@ -5551,12 +5551,12 @@
       </c>
       <c r="B158" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C158" s="4" t="inlineStr">
         <is>
-          <t>HK235/55R19</t>
+          <t>LF235/55R19</t>
         </is>
       </c>
       <c r="D158" s="5">
@@ -5572,7 +5572,7 @@
         <v>0</v>
       </c>
       <c r="H158" s="6">
-        <v>630</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="159">
@@ -5583,19 +5583,19 @@
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>LF235/55R19</t>
+          <t>NX235/55R19</t>
         </is>
       </c>
       <c r="D159" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E159" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F159" s="5">
         <v>0</v>
@@ -5604,7 +5604,7 @@
         <v>0</v>
       </c>
       <c r="H159" s="6">
-        <v>500</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="160">
@@ -5615,66 +5615,66 @@
       </c>
       <c r="B160" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C160" s="4" t="inlineStr">
         <is>
-          <t>NX235/55R19</t>
+          <t>RD235/55R19</t>
         </is>
       </c>
       <c r="D160" s="5">
         <v>2</v>
       </c>
       <c r="E160" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F160" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G160" s="5">
         <v>0</v>
       </c>
       <c r="H160" s="6">
-        <v>600</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="161">
       <c r="A161" s="4" t="inlineStr">
         <is>
-          <t>235/55R19</t>
+          <t>235/60R16</t>
         </is>
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>RD235/55R19</t>
+          <t>HK235/60R16</t>
         </is>
       </c>
       <c r="D161" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E161" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F161" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G161" s="5">
         <v>0</v>
       </c>
       <c r="H161" s="6">
-        <v>500</v>
+        <v>430</v>
       </c>
     </row>
     <row outlineLevel="0" r="162">
       <c r="A162" s="4" t="inlineStr">
         <is>
-          <t>235/60R16</t>
+          <t>235/60R17</t>
         </is>
       </c>
       <c r="B162" s="4" t="inlineStr">
@@ -5684,55 +5684,55 @@
       </c>
       <c r="C162" s="4" t="inlineStr">
         <is>
-          <t>HK235/60R16</t>
+          <t>HK235/60R17</t>
         </is>
       </c>
       <c r="D162" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E162" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F162" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G162" s="5">
         <v>0</v>
       </c>
       <c r="H162" s="6">
-        <v>430</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="163">
       <c r="A163" s="4" t="inlineStr">
         <is>
-          <t>235/60R17</t>
+          <t>235/60R18</t>
         </is>
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>HK235/60R17</t>
+          <t>GD235/60R18</t>
         </is>
       </c>
       <c r="D163" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E163" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F163" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G163" s="5">
         <v>0</v>
       </c>
       <c r="H163" s="6">
-        <v>500</v>
+        <v>680</v>
       </c>
     </row>
     <row outlineLevel="0" r="164">
@@ -5743,12 +5743,12 @@
       </c>
       <c r="B164" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C164" s="4" t="inlineStr">
         <is>
-          <t>GD235/60R18</t>
+          <t>HK235/60R18</t>
         </is>
       </c>
       <c r="D164" s="5">
@@ -5764,30 +5764,30 @@
         <v>0</v>
       </c>
       <c r="H164" s="6">
-        <v>680</v>
+        <v>480</v>
       </c>
     </row>
     <row outlineLevel="0" r="165">
       <c r="A165" s="4" t="inlineStr">
         <is>
-          <t>235/60R18</t>
+          <t>245/40R17</t>
         </is>
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>HK235/60R18</t>
+          <t>GD245/40R17</t>
         </is>
       </c>
       <c r="D165" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E165" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F165" s="5">
         <v>0</v>
@@ -5796,13 +5796,13 @@
         <v>0</v>
       </c>
       <c r="H165" s="6">
-        <v>480</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="166">
       <c r="A166" s="4" t="inlineStr">
         <is>
-          <t>245/40R17</t>
+          <t>245/40R18</t>
         </is>
       </c>
       <c r="B166" s="4" t="inlineStr">
@@ -5812,43 +5812,43 @@
       </c>
       <c r="C166" s="4" t="inlineStr">
         <is>
-          <t>GD245/40R17</t>
+          <t>GD245/40R18</t>
         </is>
       </c>
       <c r="D166" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E166" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F166" s="5">
         <v>0</v>
       </c>
       <c r="G166" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H166" s="6">
-        <v>400</v>
+        <v>620</v>
       </c>
     </row>
     <row outlineLevel="0" r="167">
       <c r="A167" s="4" t="inlineStr">
         <is>
-          <t>245/40R18</t>
+          <t>245/40R19</t>
         </is>
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>GD245/40R18</t>
+          <t>HK245/40R19</t>
         </is>
       </c>
       <c r="D167" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E167" s="5">
         <v>4</v>
@@ -5857,97 +5857,97 @@
         <v>0</v>
       </c>
       <c r="G167" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H167" s="6">
-        <v>620</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="168">
       <c r="A168" s="4" t="inlineStr">
         <is>
-          <t>245/40R19</t>
+          <t>245/40R20</t>
         </is>
       </c>
       <c r="B168" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C168" s="4" t="inlineStr">
         <is>
-          <t>HK245/40R19</t>
+          <t>CT245/40R20</t>
         </is>
       </c>
       <c r="D168" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E168" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F168" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G168" s="5">
         <v>0</v>
       </c>
       <c r="H168" s="6">
-        <v>750</v>
+        <v>1050</v>
       </c>
     </row>
     <row outlineLevel="0" r="169">
       <c r="A169" s="4" t="inlineStr">
         <is>
-          <t>245/40R20</t>
+          <t>245/45R17</t>
         </is>
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>CT245/40R20</t>
+          <t>HK245/45R17</t>
         </is>
       </c>
       <c r="D169" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E169" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F169" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G169" s="5">
         <v>0</v>
       </c>
       <c r="H169" s="6">
-        <v>1050</v>
+        <v>430</v>
       </c>
     </row>
     <row outlineLevel="0" r="170">
       <c r="A170" s="4" t="inlineStr">
         <is>
-          <t>245/45R17</t>
+          <t>245/45R18</t>
         </is>
       </c>
       <c r="B170" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C170" s="4" t="inlineStr">
         <is>
-          <t>HK245/45R17</t>
+          <t>CT245/45R18</t>
         </is>
       </c>
       <c r="D170" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E170" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F170" s="5">
         <v>0</v>
@@ -5956,7 +5956,7 @@
         <v>0</v>
       </c>
       <c r="H170" s="6">
-        <v>430</v>
+        <v>650</v>
       </c>
     </row>
     <row outlineLevel="0" r="171">
@@ -5967,19 +5967,19 @@
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t>CT245/45R18</t>
+          <t>GD245/45R18</t>
         </is>
       </c>
       <c r="D171" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E171" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F171" s="5">
         <v>0</v>
@@ -5988,7 +5988,7 @@
         <v>0</v>
       </c>
       <c r="H171" s="6">
-        <v>650</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="172">
@@ -5999,19 +5999,19 @@
       </c>
       <c r="B172" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C172" s="4" t="inlineStr">
         <is>
-          <t>GD245/45R18</t>
+          <t>HK245/45R18</t>
         </is>
       </c>
       <c r="D172" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E172" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F172" s="5">
         <v>0</v>
@@ -6020,30 +6020,30 @@
         <v>0</v>
       </c>
       <c r="H172" s="6">
-        <v>600</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="173">
       <c r="A173" s="4" t="inlineStr">
         <is>
-          <t>245/45R18</t>
+          <t>245/45R18RF</t>
         </is>
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>HK245/45R18</t>
+          <t>GD245/45R18RF</t>
         </is>
       </c>
       <c r="D173" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E173" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F173" s="5">
         <v>0</v>
@@ -6052,23 +6052,23 @@
         <v>0</v>
       </c>
       <c r="H173" s="6">
-        <v>500</v>
+        <v>720</v>
       </c>
     </row>
     <row outlineLevel="0" r="174">
       <c r="A174" s="4" t="inlineStr">
         <is>
-          <t>245/45R18RF</t>
+          <t>245/45R19</t>
         </is>
       </c>
       <c r="B174" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C174" s="4" t="inlineStr">
         <is>
-          <t>GD245/45R18RF</t>
+          <t>BR245/45R19</t>
         </is>
       </c>
       <c r="D174" s="5">
@@ -6084,7 +6084,7 @@
         <v>0</v>
       </c>
       <c r="H174" s="6">
-        <v>720</v>
+        <v>790</v>
       </c>
     </row>
     <row outlineLevel="0" r="175">
@@ -6095,44 +6095,44 @@
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>BR245/45R19</t>
+          <t>RD245/45R19</t>
         </is>
       </c>
       <c r="D175" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E175" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F175" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G175" s="5">
         <v>0</v>
       </c>
       <c r="H175" s="6">
-        <v>790</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="176">
       <c r="A176" s="4" t="inlineStr">
         <is>
-          <t>245/45R19</t>
+          <t>245/45R20</t>
         </is>
       </c>
       <c r="B176" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C176" s="4" t="inlineStr">
         <is>
-          <t>RD245/45R19</t>
+          <t>HK245/45R20</t>
         </is>
       </c>
       <c r="D176" s="5">
@@ -6148,59 +6148,59 @@
         <v>0</v>
       </c>
       <c r="H176" s="6">
-        <v>450</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="177">
       <c r="A177" s="4" t="inlineStr">
         <is>
-          <t>245/45R20</t>
+          <t>245/65R17</t>
         </is>
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>HK245/45R20</t>
+          <t>NX245/65R17</t>
         </is>
       </c>
       <c r="D177" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E177" s="5">
         <v>0</v>
       </c>
       <c r="F177" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G177" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H177" s="6">
-        <v>750</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="178">
       <c r="A178" s="4" t="inlineStr">
         <is>
-          <t>245/65R17</t>
+          <t>245/70R16</t>
         </is>
       </c>
       <c r="B178" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>LASSA</t>
         </is>
       </c>
       <c r="C178" s="4" t="inlineStr">
         <is>
-          <t>NX245/65R17</t>
+          <t>LS245/70R16</t>
         </is>
       </c>
       <c r="D178" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E178" s="5">
         <v>0</v>
@@ -6209,65 +6209,65 @@
         <v>0</v>
       </c>
       <c r="G178" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H178" s="6">
-        <v>600</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="179">
       <c r="A179" s="4" t="inlineStr">
         <is>
-          <t>245/70R16</t>
+          <t>255/35R19</t>
         </is>
       </c>
       <c r="B179" s="4" t="inlineStr">
         <is>
-          <t>LASSA</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C179" s="4" t="inlineStr">
         <is>
-          <t>LS245/70R16</t>
+          <t>DL255/35R19</t>
         </is>
       </c>
       <c r="D179" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E179" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F179" s="5">
         <v>0</v>
       </c>
       <c r="G179" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H179" s="6">
-        <v>500</v>
+        <v>700</v>
       </c>
     </row>
     <row outlineLevel="0" r="180">
       <c r="A180" s="4" t="inlineStr">
         <is>
-          <t>255/35R19</t>
+          <t>255/35R19RF</t>
         </is>
       </c>
       <c r="B180" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C180" s="4" t="inlineStr">
         <is>
-          <t>DL255/35R19</t>
+          <t>CT255/35R19RF</t>
         </is>
       </c>
       <c r="D180" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E180" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F180" s="5">
         <v>0</v>
@@ -6276,7 +6276,7 @@
         <v>0</v>
       </c>
       <c r="H180" s="6">
-        <v>700</v>
+        <v>950</v>
       </c>
     </row>
     <row outlineLevel="0" r="181">
@@ -6287,19 +6287,19 @@
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C181" s="4" t="inlineStr">
         <is>
-          <t>CT255/35R19RF</t>
+          <t>GD255/35R19RF</t>
         </is>
       </c>
       <c r="D181" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E181" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F181" s="5">
         <v>0</v>
@@ -6314,39 +6314,39 @@
     <row outlineLevel="0" r="182">
       <c r="A182" s="4" t="inlineStr">
         <is>
-          <t>255/35R19RF</t>
+          <t>255/50R19</t>
         </is>
       </c>
       <c r="B182" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C182" s="4" t="inlineStr">
         <is>
-          <t>GD255/35R19RF</t>
+          <t>CT255/50R19</t>
         </is>
       </c>
       <c r="D182" s="5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E182" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F182" s="5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G182" s="5">
         <v>0</v>
       </c>
       <c r="H182" s="6">
-        <v>950</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="183">
       <c r="A183" s="4" t="inlineStr">
         <is>
-          <t>255/50R19</t>
+          <t>255/50R20</t>
         </is>
       </c>
       <c r="B183" s="4" t="inlineStr">
@@ -6356,29 +6356,29 @@
       </c>
       <c r="C183" s="4" t="inlineStr">
         <is>
-          <t>CT255/50R19</t>
+          <t>CT255/50R20</t>
         </is>
       </c>
       <c r="D183" s="5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E183" s="5">
         <v>0</v>
       </c>
       <c r="F183" s="5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G183" s="5">
         <v>0</v>
       </c>
       <c r="H183" s="6">
-        <v>750</v>
+        <v>900</v>
       </c>
     </row>
     <row outlineLevel="0" r="184">
       <c r="A184" s="4" t="inlineStr">
         <is>
-          <t>255/50R20</t>
+          <t>255/55R19</t>
         </is>
       </c>
       <c r="B184" s="4" t="inlineStr">
@@ -6388,23 +6388,23 @@
       </c>
       <c r="C184" s="4" t="inlineStr">
         <is>
-          <t>CT255/50R20</t>
+          <t>CT255/55R19</t>
         </is>
       </c>
       <c r="D184" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E184" s="5">
         <v>0</v>
       </c>
       <c r="F184" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G184" s="5">
         <v>0</v>
       </c>
       <c r="H184" s="6">
-        <v>900</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="185">
@@ -6415,34 +6415,34 @@
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C185" s="4" t="inlineStr">
         <is>
-          <t>CT255/55R19</t>
+          <t>DL255/55R19</t>
         </is>
       </c>
       <c r="D185" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E185" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F185" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G185" s="5">
         <v>0</v>
       </c>
       <c r="H185" s="6">
-        <v>750</v>
+        <v>700</v>
       </c>
     </row>
     <row outlineLevel="0" r="186">
       <c r="A186" s="4" t="inlineStr">
         <is>
-          <t>255/55R19</t>
+          <t>255/70R15</t>
         </is>
       </c>
       <c r="B186" s="4" t="inlineStr">
@@ -6452,43 +6452,43 @@
       </c>
       <c r="C186" s="4" t="inlineStr">
         <is>
-          <t>DL255/55R19</t>
+          <t>DL255/70R15</t>
         </is>
       </c>
       <c r="D186" s="5">
         <v>2</v>
       </c>
       <c r="E186" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F186" s="5">
         <v>0</v>
       </c>
       <c r="G186" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H186" s="6">
-        <v>700</v>
+        <v>550</v>
       </c>
     </row>
     <row outlineLevel="0" r="187">
       <c r="A187" s="4" t="inlineStr">
         <is>
-          <t>255/70R15</t>
+          <t>255/70R16</t>
         </is>
       </c>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C187" s="4" t="inlineStr">
         <is>
-          <t>DL255/70R15</t>
+          <t>RD255/70R16</t>
         </is>
       </c>
       <c r="D187" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E187" s="5">
         <v>0</v>
@@ -6497,48 +6497,48 @@
         <v>0</v>
       </c>
       <c r="G187" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H187" s="6">
-        <v>550</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="188">
       <c r="A188" s="4" t="inlineStr">
         <is>
-          <t>255/70R16</t>
+          <t>265/35R18</t>
         </is>
       </c>
       <c r="B188" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C188" s="4" t="inlineStr">
         <is>
-          <t>RD255/70R16</t>
+          <t>GD265/35R18</t>
         </is>
       </c>
       <c r="D188" s="5">
         <v>1</v>
       </c>
       <c r="E188" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F188" s="5">
         <v>0</v>
       </c>
       <c r="G188" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H188" s="6">
-        <v>500</v>
+        <v>700</v>
       </c>
     </row>
     <row outlineLevel="0" r="189">
       <c r="A189" s="4" t="inlineStr">
         <is>
-          <t>265/35R18</t>
+          <t>265/50R20</t>
         </is>
       </c>
       <c r="B189" s="4" t="inlineStr">
@@ -6548,29 +6548,29 @@
       </c>
       <c r="C189" s="4" t="inlineStr">
         <is>
-          <t>GD265/35R18</t>
+          <t>GD265/50R20</t>
         </is>
       </c>
       <c r="D189" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E189" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F189" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G189" s="5">
         <v>0</v>
       </c>
       <c r="H189" s="6">
-        <v>700</v>
+        <v>1150</v>
       </c>
     </row>
     <row outlineLevel="0" r="190">
       <c r="A190" s="4" t="inlineStr">
         <is>
-          <t>265/50R20</t>
+          <t>275/35R19RF</t>
         </is>
       </c>
       <c r="B190" s="4" t="inlineStr">
@@ -6580,71 +6580,71 @@
       </c>
       <c r="C190" s="4" t="inlineStr">
         <is>
-          <t>GD265/50R20</t>
+          <t>GD275/35R19RF</t>
         </is>
       </c>
       <c r="D190" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E190" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F190" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G190" s="5">
         <v>0</v>
       </c>
       <c r="H190" s="6">
-        <v>1150</v>
+        <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="191">
       <c r="A191" s="4" t="inlineStr">
         <is>
-          <t>275/35R19RF</t>
+          <t>275/35R20</t>
         </is>
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C191" s="4" t="inlineStr">
         <is>
-          <t>GD275/35R19RF</t>
+          <t>CT275/35R20</t>
         </is>
       </c>
       <c r="D191" s="5">
         <v>2</v>
       </c>
       <c r="E191" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F191" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G191" s="5">
         <v>0</v>
       </c>
       <c r="H191" s="6">
-        <v>1</v>
+        <v>980</v>
       </c>
     </row>
     <row outlineLevel="0" r="192">
       <c r="A192" s="4" t="inlineStr">
         <is>
-          <t>275/35R20</t>
+          <t>275/40R20</t>
         </is>
       </c>
       <c r="B192" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C192" s="4" t="inlineStr">
         <is>
-          <t>CT275/35R20</t>
+          <t>HK275/40R20</t>
         </is>
       </c>
       <c r="D192" s="5">
@@ -6660,23 +6660,23 @@
         <v>0</v>
       </c>
       <c r="H192" s="6">
-        <v>980</v>
+        <v>770</v>
       </c>
     </row>
     <row outlineLevel="0" r="193">
       <c r="A193" s="4" t="inlineStr">
         <is>
-          <t>275/40R20</t>
+          <t>275/50R21</t>
         </is>
       </c>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C193" s="4" t="inlineStr">
         <is>
-          <t>HK275/40R20</t>
+          <t>GD275/50R21</t>
         </is>
       </c>
       <c r="D193" s="5">
@@ -6692,23 +6692,23 @@
         <v>0</v>
       </c>
       <c r="H193" s="6">
-        <v>770</v>
+        <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="194">
       <c r="A194" s="4" t="inlineStr">
         <is>
-          <t>275/50R21</t>
+          <t>295/35R21</t>
         </is>
       </c>
       <c r="B194" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C194" s="4" t="inlineStr">
         <is>
-          <t>GD275/50R21</t>
+          <t>CT295/35R21</t>
         </is>
       </c>
       <c r="D194" s="5">
@@ -6724,7 +6724,7 @@
         <v>0</v>
       </c>
       <c r="H194" s="6">
-        <v>1</v>
+        <v>1150</v>
       </c>
     </row>
     <row outlineLevel="0" r="195">
@@ -6735,91 +6735,59 @@
       </c>
       <c r="B195" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C195" s="4" t="inlineStr">
         <is>
-          <t>CT295/35R21</t>
+          <t>GD295/35R21</t>
         </is>
       </c>
       <c r="D195" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E195" s="5">
         <v>0</v>
       </c>
       <c r="F195" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G195" s="5">
         <v>0</v>
       </c>
       <c r="H195" s="6">
-        <v>1150</v>
+        <v>980</v>
       </c>
     </row>
     <row outlineLevel="0" r="196">
       <c r="A196" s="4" t="inlineStr">
         <is>
-          <t>295/35R21</t>
+          <t>500R12</t>
         </is>
       </c>
       <c r="B196" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C196" s="4" t="inlineStr">
         <is>
-          <t>GD295/35R21</t>
+          <t>RD500R12</t>
         </is>
       </c>
       <c r="D196" s="5">
         <v>3</v>
       </c>
       <c r="E196" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F196" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G196" s="5">
         <v>0</v>
       </c>
       <c r="H196" s="6">
-        <v>980</v>
-      </c>
-    </row>
-    <row outlineLevel="0" r="197">
-      <c r="A197" s="4" t="inlineStr">
-        <is>
-          <t>500R12</t>
-        </is>
-      </c>
-      <c r="B197" s="4" t="inlineStr">
-        <is>
-          <t>RADIAL</t>
-        </is>
-      </c>
-      <c r="C197" s="4" t="inlineStr">
-        <is>
-          <t>RD500R12</t>
-        </is>
-      </c>
-      <c r="D197" s="5">
-        <v>3</v>
-      </c>
-      <c r="E197" s="5">
-        <v>3</v>
-      </c>
-      <c r="F197" s="5">
-        <v>0</v>
-      </c>
-      <c r="G197" s="5">
-        <v>0</v>
-      </c>
-      <c r="H197" s="6">
         <v>300</v>
       </c>
     </row>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="D8" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E8" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F8" s="5">
         <v>0</v>
@@ -1464,7 +1464,7 @@
         </is>
       </c>
       <c r="D30" s="5">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E30" s="5">
         <v>3</v>
@@ -1473,7 +1473,7 @@
         <v>0</v>
       </c>
       <c r="G30" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H30" s="6">
         <v>230</v>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="D31" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E31" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F31" s="5">
         <v>0</v>
@@ -2264,7 +2264,7 @@
         </is>
       </c>
       <c r="D55" s="5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E55" s="5">
         <v>5</v>
@@ -2273,7 +2273,7 @@
         <v>0</v>
       </c>
       <c r="G55" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H55" s="6">
         <v>250</v>
@@ -4376,10 +4376,10 @@
         </is>
       </c>
       <c r="D121" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E121" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F121" s="5">
         <v>0</v>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -496,7 +496,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H196"/>
+  <dimension ref="A1:H195"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col customWidth="true" min="1" max="1" width="13.8359375"/>
@@ -696,10 +696,10 @@
         </is>
       </c>
       <c r="D6" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E6" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F6" s="5">
         <v>0</v>
@@ -760,16 +760,16 @@
         </is>
       </c>
       <c r="D8" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E8" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F8" s="5">
         <v>0</v>
       </c>
       <c r="G8" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H8" s="6">
         <v>180</v>
@@ -920,10 +920,10 @@
         </is>
       </c>
       <c r="D13" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E13" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F13" s="5">
         <v>0</v>
@@ -1130,24 +1130,24 @@
     <row outlineLevel="0" r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>175/65R15</t>
+          <t>175/70R13</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>DOUBLESTAR</t>
+          <t>WESTLAKE</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>DS175/65R15</t>
+          <t>WL175/70R13</t>
         </is>
       </c>
       <c r="D20" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E20" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F20" s="5">
         <v>0</v>
@@ -1162,17 +1162,17 @@
     <row outlineLevel="0" r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>175/70R13</t>
+          <t>175/70R14</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>WESTLAKE</t>
+          <t>MATADOR</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>WL175/70R13</t>
+          <t>MT175/70R14</t>
         </is>
       </c>
       <c r="D21" s="5">
@@ -1188,7 +1188,7 @@
         <v>0</v>
       </c>
       <c r="H21" s="6">
-        <v>200</v>
+        <v>230</v>
       </c>
     </row>
     <row outlineLevel="0" r="22">
@@ -1199,60 +1199,60 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>MATADOR</t>
+          <t>WESTLAKE</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>MT175/70R14</t>
+          <t>WL175/70R14</t>
         </is>
       </c>
       <c r="D22" s="5">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="E22" s="5">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="F22" s="5">
         <v>0</v>
       </c>
       <c r="G22" s="5">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="H22" s="6">
-        <v>230</v>
+        <v>200</v>
       </c>
     </row>
     <row outlineLevel="0" r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>175/70R14</t>
+          <t>185/55R15</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>WESTLAKE</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>WL175/70R14</t>
+          <t>BR185/55R15</t>
         </is>
       </c>
       <c r="D23" s="5">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="E23" s="5">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="F23" s="5">
         <v>0</v>
       </c>
       <c r="G23" s="5">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H23" s="6">
-        <v>200</v>
+        <v>370</v>
       </c>
     </row>
     <row outlineLevel="0" r="24">
@@ -1263,34 +1263,34 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>BR185/55R15</t>
+          <t>GD185/55R15</t>
         </is>
       </c>
       <c r="D24" s="5">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="E24" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F24" s="5">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G24" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H24" s="6">
-        <v>370</v>
+        <v>340</v>
       </c>
     </row>
     <row outlineLevel="0" r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>185/55R15</t>
+          <t>185/55R16</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
@@ -1300,29 +1300,29 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>GD185/55R15</t>
+          <t>GD185/55R16</t>
         </is>
       </c>
       <c r="D25" s="5">
-        <v>39</v>
+        <v>3</v>
       </c>
       <c r="E25" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F25" s="5">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="G25" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H25" s="6">
-        <v>340</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>185/55R16</t>
+          <t>185/60R14</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
@@ -1332,23 +1332,23 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>GD185/55R16</t>
+          <t>GD185/60R14</t>
         </is>
       </c>
       <c r="D26" s="5">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="E26" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F26" s="5">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G26" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H26" s="6">
-        <v>420</v>
+        <v>230</v>
       </c>
     </row>
     <row outlineLevel="0" r="27">
@@ -1359,25 +1359,25 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>GD185/60R14</t>
+          <t>NX185/60R14</t>
         </is>
       </c>
       <c r="D27" s="5">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="E27" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F27" s="5">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G27" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H27" s="6">
         <v>230</v>
@@ -1386,24 +1386,24 @@
     <row outlineLevel="0" r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>185/60R14</t>
+          <t>185/60R15</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>MATADOR</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>NX185/60R14</t>
+          <t>MT185/60R15</t>
         </is>
       </c>
       <c r="D28" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E28" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F28" s="5">
         <v>0</v>
@@ -1412,7 +1412,7 @@
         <v>0</v>
       </c>
       <c r="H28" s="6">
-        <v>230</v>
+        <v>280</v>
       </c>
     </row>
     <row outlineLevel="0" r="29">
@@ -1423,28 +1423,28 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>MATADOR</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>MT185/60R15</t>
+          <t>RD185/60R15</t>
         </is>
       </c>
       <c r="D29" s="5">
         <v>4</v>
       </c>
       <c r="E29" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F29" s="5">
         <v>0</v>
       </c>
       <c r="G29" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H29" s="6">
-        <v>280</v>
+        <v>230</v>
       </c>
     </row>
     <row outlineLevel="0" r="30">
@@ -1455,25 +1455,25 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>WESTLAKE</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>RD185/60R15</t>
+          <t>WL185/60R15</t>
         </is>
       </c>
       <c r="D30" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E30" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F30" s="5">
         <v>0</v>
       </c>
       <c r="G30" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H30" s="6">
         <v>230</v>
@@ -1482,97 +1482,97 @@
     <row outlineLevel="0" r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>185/60R15</t>
+          <t>185/60R16</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>WESTLAKE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>WL185/60R15</t>
+          <t>GD185/60R16</t>
         </is>
       </c>
       <c r="D31" s="5">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E31" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F31" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G31" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H31" s="6">
-        <v>230</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>185/60R16</t>
+          <t>185/65R14</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>GD185/60R16</t>
+          <t>RD185/65R14</t>
         </is>
       </c>
       <c r="D32" s="5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E32" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F32" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G32" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H32" s="6">
-        <v>420</v>
+        <v>200</v>
       </c>
     </row>
     <row outlineLevel="0" r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>185/65R14</t>
+          <t>185/65R15</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>RD185/65R14</t>
+          <t>CT185/65R15</t>
         </is>
       </c>
       <c r="D33" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E33" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F33" s="5">
         <v>0</v>
       </c>
       <c r="G33" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H33" s="6">
-        <v>200</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="34">
@@ -1583,28 +1583,28 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>DOUBLESTAR</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>CT185/65R15</t>
+          <t>DS185/65R15</t>
         </is>
       </c>
       <c r="D34" s="5">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E34" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F34" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G34" s="5">
         <v>0</v>
       </c>
       <c r="H34" s="6">
-        <v>400</v>
+        <v>210</v>
       </c>
     </row>
     <row outlineLevel="0" r="35">
@@ -1615,28 +1615,28 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>DOUBLESTAR</t>
+          <t>FULDA</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>DS185/65R15</t>
+          <t>FL185/65R15</t>
         </is>
       </c>
       <c r="D35" s="5">
-        <v>7</v>
+        <v>136</v>
       </c>
       <c r="E35" s="5">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="F35" s="5">
-        <v>5</v>
+        <v>109</v>
       </c>
       <c r="G35" s="5">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="H35" s="6">
-        <v>210</v>
+        <v>245</v>
       </c>
     </row>
     <row outlineLevel="0" r="36">
@@ -1647,28 +1647,28 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>FULDA</t>
+          <t>GOODRIDE</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>FL185/65R15</t>
+          <t>GR185/65R15</t>
         </is>
       </c>
       <c r="D36" s="5">
-        <v>136</v>
+        <v>11</v>
       </c>
       <c r="E36" s="5">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="F36" s="5">
-        <v>109</v>
+        <v>3</v>
       </c>
       <c r="G36" s="5">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="H36" s="6">
-        <v>245</v>
+        <v>230</v>
       </c>
     </row>
     <row outlineLevel="0" r="37">
@@ -1679,28 +1679,28 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>GOODRIDE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>GR185/65R15</t>
+          <t>GD185/65R15</t>
         </is>
       </c>
       <c r="D37" s="5">
-        <v>11</v>
+        <v>66</v>
       </c>
       <c r="E37" s="5">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="F37" s="5">
-        <v>3</v>
+        <v>49</v>
       </c>
       <c r="G37" s="5">
         <v>4</v>
       </c>
       <c r="H37" s="6">
-        <v>230</v>
+        <v>260</v>
       </c>
     </row>
     <row outlineLevel="0" r="38">
@@ -1711,28 +1711,28 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>GD185/65R15</t>
+          <t>HK185/65R15</t>
         </is>
       </c>
       <c r="D38" s="5">
-        <v>67</v>
+        <v>5</v>
       </c>
       <c r="E38" s="5">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F38" s="5">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="G38" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H38" s="6">
-        <v>260</v>
+        <v>250</v>
       </c>
     </row>
     <row outlineLevel="0" r="39">
@@ -1743,16 +1743,16 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>HK185/65R15</t>
+          <t>LF185/65R15</t>
         </is>
       </c>
       <c r="D39" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E39" s="5">
         <v>4</v>
@@ -1761,7 +1761,7 @@
         <v>0</v>
       </c>
       <c r="G39" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H39" s="6">
         <v>250</v>
@@ -1775,28 +1775,28 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>LF185/65R15</t>
+          <t>RD185/65R15</t>
         </is>
       </c>
       <c r="D40" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E40" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F40" s="5">
         <v>0</v>
       </c>
       <c r="G40" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H40" s="6">
-        <v>250</v>
+        <v>200</v>
       </c>
     </row>
     <row outlineLevel="0" r="41">
@@ -1807,28 +1807,28 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>SEMPERIT</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>RD185/65R15</t>
+          <t>SP185/65R15</t>
         </is>
       </c>
       <c r="D41" s="5">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="E41" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F41" s="5">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G41" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H41" s="6">
-        <v>200</v>
+        <v>250</v>
       </c>
     </row>
     <row outlineLevel="0" r="42">
@@ -1839,60 +1839,60 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>SEMPERIT</t>
+          <t>WESTLAKE</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>SP185/65R15</t>
+          <t>WL185/65R15</t>
         </is>
       </c>
       <c r="D42" s="5">
-        <v>30</v>
+        <v>94</v>
       </c>
       <c r="E42" s="5">
-        <v>5</v>
+        <v>86</v>
       </c>
       <c r="F42" s="5">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="G42" s="5">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H42" s="6">
-        <v>250</v>
+        <v>220</v>
       </c>
     </row>
     <row outlineLevel="0" r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>185/65R15</t>
+          <t>185/70R14</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>WESTLAKE</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>WL185/65R15</t>
+          <t>RD185/70R14</t>
         </is>
       </c>
       <c r="D43" s="5">
-        <v>94</v>
+        <v>2</v>
       </c>
       <c r="E43" s="5">
-        <v>86</v>
+        <v>1</v>
       </c>
       <c r="F43" s="5">
         <v>0</v>
       </c>
       <c r="G43" s="5">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H43" s="6">
-        <v>220</v>
+        <v>230</v>
       </c>
     </row>
     <row outlineLevel="0" r="44">
@@ -1903,28 +1903,28 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>SEMPERIT</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>RD185/70R14</t>
+          <t>SP185/70R14</t>
         </is>
       </c>
       <c r="D44" s="5">
         <v>2</v>
       </c>
       <c r="E44" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F44" s="5">
         <v>0</v>
       </c>
       <c r="G44" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H44" s="6">
-        <v>230</v>
+        <v>280</v>
       </c>
     </row>
     <row outlineLevel="0" r="45">
@@ -1935,60 +1935,60 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>SEMPERIT</t>
+          <t>WESTLAKE</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>SP185/70R14</t>
+          <t>WL185/70R14</t>
         </is>
       </c>
       <c r="D45" s="5">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E45" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F45" s="5">
         <v>0</v>
       </c>
       <c r="G45" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H45" s="6">
-        <v>280</v>
+        <v>220</v>
       </c>
     </row>
     <row outlineLevel="0" r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>185/70R14</t>
+          <t>195/50R15</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>WESTLAKE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>WL185/70R14</t>
+          <t>GD195/50R15</t>
         </is>
       </c>
       <c r="D46" s="5">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E46" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F46" s="5">
         <v>0</v>
       </c>
       <c r="G46" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H46" s="6">
-        <v>220</v>
+        <v>290</v>
       </c>
     </row>
     <row outlineLevel="0" r="47">
@@ -1999,28 +1999,28 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>SEMPERIT</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>GD195/50R15</t>
+          <t>SP195/50R15</t>
         </is>
       </c>
       <c r="D47" s="5">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="E47" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F47" s="5">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G47" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H47" s="6">
-        <v>290</v>
+        <v>260</v>
       </c>
     </row>
     <row outlineLevel="0" r="48">
@@ -2031,66 +2031,66 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>SEMPERIT</t>
+          <t>WESTLAKE</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>SP195/50R15</t>
+          <t>WL195/50R15</t>
         </is>
       </c>
       <c r="D48" s="5">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="E48" s="5">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F48" s="5">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G48" s="5">
         <v>4</v>
       </c>
       <c r="H48" s="6">
-        <v>260</v>
+        <v>225</v>
       </c>
     </row>
     <row outlineLevel="0" r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>195/50R15</t>
+          <t>195/50R16</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>WESTLAKE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>WL195/50R15</t>
+          <t>GD195/50R16</t>
         </is>
       </c>
       <c r="D49" s="5">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E49" s="5">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F49" s="5">
         <v>0</v>
       </c>
       <c r="G49" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H49" s="6">
-        <v>225</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>195/50R16</t>
+          <t>195/55R16</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
@@ -2100,23 +2100,23 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>GD195/50R16</t>
+          <t>GD195/55R16</t>
         </is>
       </c>
       <c r="D50" s="5">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="E50" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F50" s="5">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G50" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H50" s="6">
-        <v>330</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="51">
@@ -2127,28 +2127,28 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>GD195/55R16</t>
+          <t>HK195/55R16</t>
         </is>
       </c>
       <c r="D51" s="5">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E51" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F51" s="5">
         <v>13</v>
       </c>
       <c r="G51" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H51" s="6">
-        <v>350</v>
+        <v>290</v>
       </c>
     </row>
     <row outlineLevel="0" r="52">
@@ -2159,28 +2159,28 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>LASSA</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>HK195/55R16</t>
+          <t>LS195/55R16</t>
         </is>
       </c>
       <c r="D52" s="5">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="E52" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F52" s="5">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G52" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H52" s="6">
-        <v>290</v>
+        <v>280</v>
       </c>
     </row>
     <row outlineLevel="0" r="53">
@@ -2191,19 +2191,19 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>LASSA</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>LS195/55R16</t>
+          <t>NX195/55R16</t>
         </is>
       </c>
       <c r="D53" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E53" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F53" s="5">
         <v>0</v>
@@ -2212,7 +2212,7 @@
         <v>0</v>
       </c>
       <c r="H53" s="6">
-        <v>280</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="54">
@@ -2223,92 +2223,92 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>NX195/55R16</t>
+          <t>RD195/55R16</t>
         </is>
       </c>
       <c r="D54" s="5">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E54" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F54" s="5">
         <v>0</v>
       </c>
       <c r="G54" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H54" s="6">
-        <v>300</v>
+        <v>250</v>
       </c>
     </row>
     <row outlineLevel="0" r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>195/55R16</t>
+          <t>195/60R16</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>RD195/55R16</t>
+          <t>GD195/60R16</t>
         </is>
       </c>
       <c r="D55" s="5">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="E55" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F55" s="5">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G55" s="5">
         <v>3</v>
       </c>
       <c r="H55" s="6">
-        <v>250</v>
+        <v>355</v>
       </c>
     </row>
     <row outlineLevel="0" r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>195/60R16</t>
+          <t>195/65R15</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>DOUBLESTAR</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>GD195/60R16</t>
+          <t>DS195/65R15</t>
         </is>
       </c>
       <c r="D56" s="5">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="E56" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F56" s="5">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="G56" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H56" s="6">
-        <v>355</v>
+        <v>230</v>
       </c>
     </row>
     <row outlineLevel="0" r="57">
@@ -2319,22 +2319,22 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>DOUBLESTAR</t>
+          <t>GOODRIDE</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>DS195/65R15</t>
+          <t>GR195/65R15</t>
         </is>
       </c>
       <c r="D57" s="5">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E57" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F57" s="5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G57" s="5">
         <v>0</v>
@@ -2351,28 +2351,28 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>GOODRIDE</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>GR195/65R15</t>
+          <t>HK195/65R15</t>
         </is>
       </c>
       <c r="D58" s="5">
         <v>4</v>
       </c>
       <c r="E58" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F58" s="5">
         <v>0</v>
       </c>
       <c r="G58" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H58" s="6">
-        <v>230</v>
+        <v>260</v>
       </c>
     </row>
     <row outlineLevel="0" r="59">
@@ -2383,28 +2383,28 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>LASSA</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>HK195/65R15</t>
+          <t>LS195/65R15</t>
         </is>
       </c>
       <c r="D59" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E59" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F59" s="5">
         <v>0</v>
       </c>
       <c r="G59" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H59" s="6">
-        <v>260</v>
+        <v>250</v>
       </c>
     </row>
     <row outlineLevel="0" r="60">
@@ -2415,19 +2415,19 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>LASSA</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>LS195/65R15</t>
+          <t>NX195/65R15</t>
         </is>
       </c>
       <c r="D60" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E60" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F60" s="5">
         <v>0</v>
@@ -2436,7 +2436,7 @@
         <v>0</v>
       </c>
       <c r="H60" s="6">
-        <v>250</v>
+        <v>230</v>
       </c>
     </row>
     <row outlineLevel="0" r="61">
@@ -2447,25 +2447,25 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>NX195/65R15</t>
+          <t>RD195/65R15</t>
         </is>
       </c>
       <c r="D61" s="5">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E61" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F61" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G61" s="5">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H61" s="6">
         <v>230</v>
@@ -2479,124 +2479,124 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>SEMPERIT</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>RD195/65R15</t>
+          <t>SP195/65R15</t>
         </is>
       </c>
       <c r="D62" s="5">
-        <v>15</v>
+        <v>96</v>
       </c>
       <c r="E62" s="5">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F62" s="5">
-        <v>1</v>
+        <v>75</v>
       </c>
       <c r="G62" s="5">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="H62" s="6">
-        <v>230</v>
+        <v>250</v>
       </c>
     </row>
     <row outlineLevel="0" r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>195/65R15</t>
+          <t>195/70R15C</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>SEMPERIT</t>
+          <t>DAYTON</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>SP195/65R15</t>
+          <t>DT195/70R15C</t>
         </is>
       </c>
       <c r="D63" s="5">
-        <v>96</v>
+        <v>2</v>
       </c>
       <c r="E63" s="5">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F63" s="5">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="G63" s="5">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H63" s="6">
-        <v>250</v>
+        <v>280</v>
       </c>
     </row>
     <row outlineLevel="0" r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>195/70R15C</t>
+          <t>195/75R16C</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>DAYTON</t>
+          <t>GOODRIDE</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>DT195/70R15C</t>
+          <t>GR195/75R16C</t>
         </is>
       </c>
       <c r="D64" s="5">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E64" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F64" s="5">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G64" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H64" s="6">
-        <v>280</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>195/75R16C</t>
+          <t>205/45R17</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>GOODRIDE</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>GR195/75R16C</t>
+          <t>CT205/45R17</t>
         </is>
       </c>
       <c r="D65" s="5">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E65" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F65" s="5">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G65" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H65" s="6">
-        <v>350</v>
+        <v>550</v>
       </c>
     </row>
     <row outlineLevel="0" r="66">
@@ -2607,28 +2607,28 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>FULDA</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>CT205/45R17</t>
+          <t>FL205/45R17</t>
         </is>
       </c>
       <c r="D66" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E66" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F66" s="5">
         <v>0</v>
       </c>
       <c r="G66" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H66" s="6">
-        <v>550</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="67">
@@ -2639,28 +2639,28 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>FULDA</t>
+          <t>GOODRIDE</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>FL205/45R17</t>
+          <t>GR205/45R17</t>
         </is>
       </c>
       <c r="D67" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E67" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F67" s="5">
         <v>0</v>
       </c>
       <c r="G67" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H67" s="6">
-        <v>380</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="68">
@@ -2671,28 +2671,28 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>GOODRIDE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>GR205/45R17</t>
+          <t>GD205/45R17</t>
         </is>
       </c>
       <c r="D68" s="5">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="E68" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F68" s="5">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G68" s="5">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H68" s="6">
-        <v>300</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="69">
@@ -2703,28 +2703,28 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>GD205/45R17</t>
+          <t>NX205/45R17</t>
         </is>
       </c>
       <c r="D69" s="5">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="E69" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F69" s="5">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G69" s="5">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H69" s="6">
-        <v>450</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="70">
@@ -2735,83 +2735,83 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>NX205/45R17</t>
+          <t>RD205/45R17</t>
         </is>
       </c>
       <c r="D70" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E70" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F70" s="5">
         <v>0</v>
       </c>
       <c r="G70" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H70" s="6">
-        <v>380</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>205/45R17</t>
+          <t>205/50R17</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>RD205/45R17</t>
+          <t>CT205/50R17</t>
         </is>
       </c>
       <c r="D71" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E71" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F71" s="5">
         <v>0</v>
       </c>
       <c r="G71" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H71" s="6">
-        <v>300</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>205/50R17</t>
+          <t>205/55R16</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>AMINE</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>CT205/50R17</t>
+          <t>AM205/55R16</t>
         </is>
       </c>
       <c r="D72" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E72" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F72" s="5">
         <v>0</v>
@@ -2820,7 +2820,7 @@
         <v>0</v>
       </c>
       <c r="H72" s="6">
-        <v>450</v>
+        <v>240</v>
       </c>
     </row>
     <row outlineLevel="0" r="73">
@@ -2831,19 +2831,19 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>AMINE</t>
+          <t>DOUBLESTAR</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>AM205/55R16</t>
+          <t>DS205/55R16</t>
         </is>
       </c>
       <c r="D73" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E73" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F73" s="5">
         <v>0</v>
@@ -2852,7 +2852,7 @@
         <v>0</v>
       </c>
       <c r="H73" s="6">
-        <v>240</v>
+        <v>230</v>
       </c>
     </row>
     <row outlineLevel="0" r="74">
@@ -2863,28 +2863,28 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>DOUBLESTAR</t>
+          <t>FULDA</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>DS205/55R16</t>
+          <t>FL205/55R16</t>
         </is>
       </c>
       <c r="D74" s="5">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="E74" s="5">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F74" s="5">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G74" s="5">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H74" s="6">
-        <v>230</v>
+        <v>250</v>
       </c>
     </row>
     <row outlineLevel="0" r="75">
@@ -2895,25 +2895,25 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>FULDA</t>
+          <t>GOODRIDE</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>FL205/55R16</t>
+          <t>GR205/55R16</t>
         </is>
       </c>
       <c r="D75" s="5">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="E75" s="5">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F75" s="5">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="G75" s="5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H75" s="6">
         <v>250</v>
@@ -2927,28 +2927,28 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>GOODRIDE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>GR205/55R16</t>
+          <t>GD205/55R16</t>
         </is>
       </c>
       <c r="D76" s="5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E76" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F76" s="5">
         <v>0</v>
       </c>
       <c r="G76" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H76" s="6">
-        <v>250</v>
+        <v>280</v>
       </c>
     </row>
     <row outlineLevel="0" r="77">
@@ -2959,28 +2959,28 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>GD205/55R16</t>
+          <t>HK205/55R16</t>
         </is>
       </c>
       <c r="D77" s="5">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E77" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F77" s="5">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G77" s="5">
         <v>4</v>
       </c>
       <c r="H77" s="6">
-        <v>280</v>
+        <v>260</v>
       </c>
     </row>
     <row outlineLevel="0" r="78">
@@ -2991,48 +2991,48 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>HK205/55R16</t>
+          <t>RD205/55R16</t>
         </is>
       </c>
       <c r="D78" s="5">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="E78" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F78" s="5">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G78" s="5">
         <v>4</v>
       </c>
       <c r="H78" s="6">
-        <v>260</v>
+        <v>230</v>
       </c>
     </row>
     <row outlineLevel="0" r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>205/55R16</t>
+          <t>205/55R16RF</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>RD205/55R16</t>
+          <t>GD205/55R16RF</t>
         </is>
       </c>
       <c r="D79" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E79" s="5">
         <v>0</v>
@@ -3041,16 +3041,16 @@
         <v>0</v>
       </c>
       <c r="G79" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H79" s="6">
-        <v>230</v>
+        <v>480</v>
       </c>
     </row>
     <row outlineLevel="0" r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>205/55R16RF</t>
+          <t>205/55R17</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
@@ -3060,23 +3060,23 @@
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>GD205/55R16RF</t>
+          <t>GD205/55R17</t>
         </is>
       </c>
       <c r="D80" s="5">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="E80" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F80" s="5">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G80" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H80" s="6">
-        <v>480</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="81">
@@ -3087,51 +3087,51 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>GD205/55R17</t>
+          <t>NX205/55R17</t>
         </is>
       </c>
       <c r="D81" s="5">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="E81" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F81" s="5">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G81" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H81" s="6">
-        <v>450</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>205/55R17</t>
+          <t>205/60R16</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>NX205/55R17</t>
+          <t>DL205/60R16</t>
         </is>
       </c>
       <c r="D82" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E82" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F82" s="5">
         <v>0</v>
@@ -3140,7 +3140,7 @@
         <v>0</v>
       </c>
       <c r="H82" s="6">
-        <v>400</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="83">
@@ -3151,28 +3151,28 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>DL205/60R16</t>
+          <t>GD205/60R16</t>
         </is>
       </c>
       <c r="D83" s="5">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="E83" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F83" s="5">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G83" s="5">
         <v>0</v>
       </c>
       <c r="H83" s="6">
-        <v>330</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="84">
@@ -3183,28 +3183,28 @@
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>GD205/60R16</t>
+          <t>HK205/60R16</t>
         </is>
       </c>
       <c r="D84" s="5">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E84" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F84" s="5">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="G84" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H84" s="6">
-        <v>380</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="85">
@@ -3215,25 +3215,25 @@
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>HK205/60R16</t>
+          <t>LF205/60R16</t>
         </is>
       </c>
       <c r="D85" s="5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E85" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F85" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G85" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H85" s="6">
         <v>300</v>
@@ -3242,24 +3242,24 @@
     <row outlineLevel="0" r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>205/60R16</t>
+          <t>205/65R15</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>LF205/60R16</t>
+          <t>HK205/65R15</t>
         </is>
       </c>
       <c r="D86" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E86" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F86" s="5">
         <v>0</v>
@@ -3268,30 +3268,30 @@
         <v>0</v>
       </c>
       <c r="H86" s="6">
-        <v>300</v>
+        <v>270</v>
       </c>
     </row>
     <row outlineLevel="0" r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>205/65R15</t>
+          <t>205/65R16</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>HK205/65R15</t>
+          <t>BR205/65R16</t>
         </is>
       </c>
       <c r="D87" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E87" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F87" s="5">
         <v>0</v>
@@ -3300,7 +3300,7 @@
         <v>0</v>
       </c>
       <c r="H87" s="6">
-        <v>270</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="88">
@@ -3311,19 +3311,19 @@
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>BR205/65R16</t>
+          <t>HK205/65R16</t>
         </is>
       </c>
       <c r="D88" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E88" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F88" s="5">
         <v>0</v>
@@ -3332,39 +3332,39 @@
         <v>0</v>
       </c>
       <c r="H88" s="6">
-        <v>420</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>205/65R16</t>
+          <t>215/40R18</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>HK205/65R16</t>
+          <t>GD215/40R18</t>
         </is>
       </c>
       <c r="D89" s="5">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E89" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F89" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G89" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H89" s="6">
-        <v>380</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="90">
@@ -3375,44 +3375,44 @@
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>GD215/40R18</t>
+          <t>HK215/40R18</t>
         </is>
       </c>
       <c r="D90" s="5">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E90" s="5">
         <v>4</v>
       </c>
       <c r="F90" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G90" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H90" s="6">
-        <v>600</v>
+        <v>490</v>
       </c>
     </row>
     <row outlineLevel="0" r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>215/40R18</t>
+          <t>215/45R16</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>HK215/40R18</t>
+          <t>GD215/45R16</t>
         </is>
       </c>
       <c r="D91" s="5">
@@ -3428,13 +3428,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="6">
-        <v>490</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>215/45R16</t>
+          <t>215/45R17</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
@@ -3444,14 +3444,14 @@
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>GD215/45R16</t>
+          <t>GD215/45R17</t>
         </is>
       </c>
       <c r="D92" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E92" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F92" s="5">
         <v>0</v>
@@ -3460,7 +3460,7 @@
         <v>0</v>
       </c>
       <c r="H92" s="6">
-        <v>450</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="93">
@@ -3471,25 +3471,25 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>GD215/45R17</t>
+          <t>HK215/45R17</t>
         </is>
       </c>
       <c r="D93" s="5">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="E93" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F93" s="5">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G93" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H93" s="6">
         <v>400</v>
@@ -3503,28 +3503,28 @@
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>IRIS</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>HK215/45R17</t>
+          <t>IR215/45R17</t>
         </is>
       </c>
       <c r="D94" s="5">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="E94" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F94" s="5">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G94" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H94" s="6">
-        <v>400</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="95">
@@ -3535,28 +3535,28 @@
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>IRIS</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>IR215/45R17</t>
+          <t>LF215/45R17</t>
         </is>
       </c>
       <c r="D95" s="5">
         <v>1</v>
       </c>
       <c r="E95" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F95" s="5">
         <v>0</v>
       </c>
       <c r="G95" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H95" s="6">
-        <v>300</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="96">
@@ -3567,83 +3567,83 @@
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>LF215/45R17</t>
+          <t>NX215/45R17</t>
         </is>
       </c>
       <c r="D96" s="5">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E96" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F96" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G96" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H96" s="6">
-        <v>350</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>215/45R17</t>
+          <t>215/45R18</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>NX215/45R17</t>
+          <t>GD215/45R18</t>
         </is>
       </c>
       <c r="D97" s="5">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E97" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F97" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G97" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H97" s="6">
-        <v>380</v>
+        <v>550</v>
       </c>
     </row>
     <row outlineLevel="0" r="98">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>215/45R18</t>
+          <t>215/50R17</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>GD215/45R18</t>
+          <t>BR215/50R17</t>
         </is>
       </c>
       <c r="D98" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E98" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F98" s="5">
         <v>0</v>
@@ -3652,7 +3652,7 @@
         <v>0</v>
       </c>
       <c r="H98" s="6">
-        <v>550</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="99">
@@ -3663,28 +3663,28 @@
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>BR215/50R17</t>
+          <t>GD215/50R17</t>
         </is>
       </c>
       <c r="D99" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E99" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F99" s="5">
         <v>0</v>
       </c>
       <c r="G99" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H99" s="6">
-        <v>450</v>
+        <v>470</v>
       </c>
     </row>
     <row outlineLevel="0" r="100">
@@ -3695,28 +3695,28 @@
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>GD215/50R17</t>
+          <t>HK215/50R17</t>
         </is>
       </c>
       <c r="D100" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E100" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F100" s="5">
         <v>0</v>
       </c>
       <c r="G100" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H100" s="6">
-        <v>470</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="101">
@@ -3727,19 +3727,19 @@
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>HK215/50R17</t>
+          <t>LF215/50R17</t>
         </is>
       </c>
       <c r="D101" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E101" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F101" s="5">
         <v>0</v>
@@ -3748,30 +3748,30 @@
         <v>0</v>
       </c>
       <c r="H101" s="6">
-        <v>400</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="102">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>215/50R17</t>
+          <t>215/50R18</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>LF215/50R17</t>
+          <t>GD215/50R18</t>
         </is>
       </c>
       <c r="D102" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E102" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F102" s="5">
         <v>0</v>
@@ -3780,13 +3780,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="6">
-        <v>420</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>215/50R18</t>
+          <t>215/55R16</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
@@ -3796,14 +3796,14 @@
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>GD215/50R18</t>
+          <t>GD215/55R16</t>
         </is>
       </c>
       <c r="D103" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E103" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F103" s="5">
         <v>0</v>
@@ -3812,7 +3812,7 @@
         <v>0</v>
       </c>
       <c r="H103" s="6">
-        <v>600</v>
+        <v>440</v>
       </c>
     </row>
     <row outlineLevel="0" r="104">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>GD215/55R16</t>
+          <t>LF215/55R16</t>
         </is>
       </c>
       <c r="D104" s="5">
@@ -3844,23 +3844,23 @@
         <v>0</v>
       </c>
       <c r="H104" s="6">
-        <v>440</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>215/55R16</t>
+          <t>215/55R17</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>LF215/55R16</t>
+          <t>BR215/55R17</t>
         </is>
       </c>
       <c r="D105" s="5">
@@ -3876,7 +3876,7 @@
         <v>0</v>
       </c>
       <c r="H105" s="6">
-        <v>350</v>
+        <v>480</v>
       </c>
     </row>
     <row outlineLevel="0" r="106">
@@ -3887,19 +3887,19 @@
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>BR215/55R17</t>
+          <t>HK215/55R17</t>
         </is>
       </c>
       <c r="D106" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E106" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F106" s="5">
         <v>0</v>
@@ -3908,23 +3908,23 @@
         <v>0</v>
       </c>
       <c r="H106" s="6">
-        <v>480</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>215/55R17</t>
+          <t>215/55R18</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>HK215/55R17</t>
+          <t>GD215/55R18</t>
         </is>
       </c>
       <c r="D107" s="5">
@@ -3940,23 +3940,23 @@
         <v>0</v>
       </c>
       <c r="H107" s="6">
-        <v>420</v>
+        <v>580</v>
       </c>
     </row>
     <row outlineLevel="0" r="108">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>215/55R18</t>
+          <t>215/60R16</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>GD215/55R18</t>
+          <t>BR215/60R16</t>
         </is>
       </c>
       <c r="D108" s="5">
@@ -3972,7 +3972,7 @@
         <v>0</v>
       </c>
       <c r="H108" s="6">
-        <v>580</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="109">
@@ -3983,25 +3983,25 @@
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>BR215/60R16</t>
+          <t>DL215/60R16</t>
         </is>
       </c>
       <c r="D109" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E109" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F109" s="5">
         <v>0</v>
       </c>
       <c r="G109" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H109" s="6">
         <v>350</v>
@@ -4015,28 +4015,28 @@
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>DL215/60R16</t>
+          <t>HK215/60R16</t>
         </is>
       </c>
       <c r="D110" s="5">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E110" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F110" s="5">
         <v>0</v>
       </c>
       <c r="G110" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H110" s="6">
-        <v>350</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="111">
@@ -4047,25 +4047,25 @@
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>HK215/60R16</t>
+          <t>NX215/60R16</t>
         </is>
       </c>
       <c r="D111" s="5">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E111" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F111" s="5">
         <v>0</v>
       </c>
       <c r="G111" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H111" s="6">
         <v>330</v>
@@ -4074,65 +4074,65 @@
     <row outlineLevel="0" r="112">
       <c r="A112" s="4" t="inlineStr">
         <is>
-          <t>215/60R16</t>
+          <t>215/60R17</t>
         </is>
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>NX215/60R16</t>
+          <t>RD215/60R17</t>
         </is>
       </c>
       <c r="D112" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E112" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F112" s="5">
         <v>0</v>
       </c>
       <c r="G112" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H112" s="6">
-        <v>330</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="113">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>215/60R17</t>
+          <t>215/65R16</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>RD215/60R17</t>
+          <t>GD215/65R16</t>
         </is>
       </c>
       <c r="D113" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E113" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F113" s="5">
         <v>0</v>
       </c>
       <c r="G113" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H113" s="6">
-        <v>300</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="114">
@@ -4143,83 +4143,83 @@
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>GD215/65R16</t>
+          <t>HK215/65R16</t>
         </is>
       </c>
       <c r="D114" s="5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E114" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F114" s="5">
         <v>0</v>
       </c>
       <c r="G114" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H114" s="6">
-        <v>380</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="115">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t>215/65R16</t>
+          <t>215/65R17</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>MICHELIN</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>HK215/65R16</t>
+          <t>MC215/65R17</t>
         </is>
       </c>
       <c r="D115" s="5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E115" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F115" s="5">
         <v>0</v>
       </c>
       <c r="G115" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H115" s="6">
-        <v>330</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="116">
       <c r="A116" s="4" t="inlineStr">
         <is>
-          <t>215/65R17</t>
+          <t>225/40R18</t>
         </is>
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>MICHELIN</t>
+          <t>BARUM</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>MC215/65R17</t>
+          <t>BM225/40R18</t>
         </is>
       </c>
       <c r="D116" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E116" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F116" s="5">
         <v>0</v>
@@ -4228,7 +4228,7 @@
         <v>0</v>
       </c>
       <c r="H116" s="6">
-        <v>600</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="117">
@@ -4239,28 +4239,28 @@
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>BARUM</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>BM225/40R18</t>
+          <t>GD225/40R18</t>
         </is>
       </c>
       <c r="D117" s="5">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="E117" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F117" s="5">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G117" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H117" s="6">
-        <v>420</v>
+        <v>480</v>
       </c>
     </row>
     <row outlineLevel="0" r="118">
@@ -4271,28 +4271,28 @@
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>GD225/40R18</t>
+          <t>HK225/40R18</t>
         </is>
       </c>
       <c r="D118" s="5">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="E118" s="5">
         <v>4</v>
       </c>
       <c r="F118" s="5">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G118" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H118" s="6">
-        <v>480</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="119">
@@ -4303,28 +4303,28 @@
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>LASSA</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>HK225/40R18</t>
+          <t>LS225/40R18</t>
         </is>
       </c>
       <c r="D119" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E119" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F119" s="5">
         <v>0</v>
       </c>
       <c r="G119" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H119" s="6">
-        <v>450</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="120">
@@ -4335,28 +4335,28 @@
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>LASSA</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>LS225/40R18</t>
+          <t>NX225/40R18</t>
         </is>
       </c>
       <c r="D120" s="5">
         <v>1</v>
       </c>
       <c r="E120" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F120" s="5">
         <v>0</v>
       </c>
       <c r="G120" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H120" s="6">
-        <v>330</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="121">
@@ -4367,19 +4367,19 @@
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>SEMPERIT</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>NX225/40R18</t>
+          <t>SP225/40R18</t>
         </is>
       </c>
       <c r="D121" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E121" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F121" s="5">
         <v>0</v>
@@ -4388,30 +4388,30 @@
         <v>0</v>
       </c>
       <c r="H121" s="6">
-        <v>400</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="122">
       <c r="A122" s="4" t="inlineStr">
         <is>
-          <t>225/40R18</t>
+          <t>225/40R18RF</t>
         </is>
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>SEMPERIT</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>SP225/40R18</t>
+          <t>GD225/40R18RF</t>
         </is>
       </c>
       <c r="D122" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E122" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F122" s="5">
         <v>0</v>
@@ -4420,30 +4420,30 @@
         <v>0</v>
       </c>
       <c r="H122" s="6">
-        <v>450</v>
+        <v>590</v>
       </c>
     </row>
     <row outlineLevel="0" r="123">
       <c r="A123" s="4" t="inlineStr">
         <is>
-          <t>225/40R18RF</t>
+          <t>225/45R17</t>
         </is>
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>GD225/40R18RF</t>
+          <t>CT225/45R17</t>
         </is>
       </c>
       <c r="D123" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E123" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F123" s="5">
         <v>0</v>
@@ -4452,7 +4452,7 @@
         <v>0</v>
       </c>
       <c r="H123" s="6">
-        <v>590</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="124">
@@ -4463,28 +4463,28 @@
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>FULDA</t>
         </is>
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>CT225/45R17</t>
+          <t>FL225/45R17</t>
         </is>
       </c>
       <c r="D124" s="5">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="E124" s="5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F124" s="5">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G124" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H124" s="6">
-        <v>400</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="125">
@@ -4495,28 +4495,28 @@
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>FULDA</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>FL225/45R17</t>
+          <t>GD225/45R17</t>
         </is>
       </c>
       <c r="D125" s="5">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E125" s="5">
         <v>6</v>
       </c>
       <c r="F125" s="5">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G125" s="5">
         <v>4</v>
       </c>
       <c r="H125" s="6">
-        <v>350</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="126">
@@ -4527,60 +4527,60 @@
       </c>
       <c r="B126" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C126" s="4" t="inlineStr">
         <is>
-          <t>GD225/45R17</t>
+          <t>HK225/45R17</t>
         </is>
       </c>
       <c r="D126" s="5">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="E126" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F126" s="5">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="G126" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H126" s="6">
-        <v>380</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="127">
       <c r="A127" s="4" t="inlineStr">
         <is>
-          <t>225/45R17</t>
+          <t>225/45R18</t>
         </is>
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>HK225/45R17</t>
+          <t>DL225/45R18</t>
         </is>
       </c>
       <c r="D127" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E127" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F127" s="5">
         <v>0</v>
       </c>
       <c r="G127" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H127" s="6">
-        <v>350</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="128">
@@ -4591,28 +4591,28 @@
       </c>
       <c r="B128" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C128" s="4" t="inlineStr">
         <is>
-          <t>DL225/45R18</t>
+          <t>GD225/45R18</t>
         </is>
       </c>
       <c r="D128" s="5">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E128" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F128" s="5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G128" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H128" s="6">
-        <v>500</v>
+        <v>550</v>
       </c>
     </row>
     <row outlineLevel="0" r="129">
@@ -4623,28 +4623,28 @@
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>GD225/45R18</t>
+          <t>HK225/45R18</t>
         </is>
       </c>
       <c r="D129" s="5">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E129" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F129" s="5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G129" s="5">
         <v>0</v>
       </c>
       <c r="H129" s="6">
-        <v>550</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="130">
@@ -4655,19 +4655,19 @@
       </c>
       <c r="B130" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C130" s="4" t="inlineStr">
         <is>
-          <t>HK225/45R18</t>
+          <t>LF225/45R18</t>
         </is>
       </c>
       <c r="D130" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E130" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F130" s="5">
         <v>0</v>
@@ -4676,103 +4676,103 @@
         <v>0</v>
       </c>
       <c r="H130" s="6">
-        <v>450</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="131">
       <c r="A131" s="4" t="inlineStr">
         <is>
-          <t>225/45R18</t>
+          <t>225/45R18RF</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>LF225/45R18</t>
+          <t>GD225/45R18RF</t>
         </is>
       </c>
       <c r="D131" s="5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E131" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F131" s="5">
         <v>0</v>
       </c>
       <c r="G131" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H131" s="6">
-        <v>420</v>
+        <v>720</v>
       </c>
     </row>
     <row outlineLevel="0" r="132">
       <c r="A132" s="4" t="inlineStr">
         <is>
-          <t>225/45R18RF</t>
+          <t>225/45R19</t>
         </is>
       </c>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C132" s="4" t="inlineStr">
         <is>
-          <t>GD225/45R18RF</t>
+          <t>CT225/45R19</t>
         </is>
       </c>
       <c r="D132" s="5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E132" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F132" s="5">
         <v>0</v>
       </c>
       <c r="G132" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H132" s="6">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row outlineLevel="0" r="133">
       <c r="A133" s="4" t="inlineStr">
         <is>
-          <t>225/45R19</t>
+          <t>225/50R17</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>CT225/45R19</t>
+          <t>GD225/50R17</t>
         </is>
       </c>
       <c r="D133" s="5">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E133" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F133" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G133" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H133" s="6">
-        <v>780</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="134">
@@ -4783,60 +4783,60 @@
       </c>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C134" s="4" t="inlineStr">
         <is>
-          <t>GD225/50R17</t>
+          <t>HK225/50R17</t>
         </is>
       </c>
       <c r="D134" s="5">
+        <v>13</v>
+      </c>
+      <c r="E134" s="5">
+        <v>3</v>
+      </c>
+      <c r="F134" s="5">
         <v>8</v>
       </c>
-      <c r="E134" s="5">
-        <v>4</v>
-      </c>
-      <c r="F134" s="5">
-        <v>2</v>
-      </c>
       <c r="G134" s="5">
         <v>2</v>
       </c>
       <c r="H134" s="6">
-        <v>500</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="135">
       <c r="A135" s="4" t="inlineStr">
         <is>
-          <t>225/50R17</t>
+          <t>225/55R16</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>HK225/50R17</t>
+          <t>DL225/55R16</t>
         </is>
       </c>
       <c r="D135" s="5">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E135" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F135" s="5">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G135" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H135" s="6">
-        <v>400</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="136">
@@ -4847,19 +4847,19 @@
       </c>
       <c r="B136" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C136" s="4" t="inlineStr">
         <is>
-          <t>DL225/55R16</t>
+          <t>GD225/55R16</t>
         </is>
       </c>
       <c r="D136" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E136" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F136" s="5">
         <v>0</v>
@@ -4868,30 +4868,30 @@
         <v>0</v>
       </c>
       <c r="H136" s="6">
-        <v>450</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="137">
       <c r="A137" s="4" t="inlineStr">
         <is>
-          <t>225/55R16</t>
+          <t>225/55R17</t>
         </is>
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>GD225/55R16</t>
+          <t>HK225/55R17</t>
         </is>
       </c>
       <c r="D137" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E137" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F137" s="5">
         <v>0</v>
@@ -4900,71 +4900,71 @@
         <v>0</v>
       </c>
       <c r="H137" s="6">
-        <v>420</v>
+        <v>430</v>
       </c>
     </row>
     <row outlineLevel="0" r="138">
       <c r="A138" s="4" t="inlineStr">
         <is>
-          <t>225/55R17</t>
+          <t>225/55R17RF</t>
         </is>
       </c>
       <c r="B138" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C138" s="4" t="inlineStr">
         <is>
-          <t>HK225/55R17</t>
+          <t>GD225/55R17RF</t>
         </is>
       </c>
       <c r="D138" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E138" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F138" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G138" s="5">
         <v>0</v>
       </c>
       <c r="H138" s="6">
-        <v>430</v>
+        <v>700</v>
       </c>
     </row>
     <row outlineLevel="0" r="139">
       <c r="A139" s="4" t="inlineStr">
         <is>
-          <t>225/55R17RF</t>
+          <t>225/55R18</t>
         </is>
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>GD225/55R17RF</t>
+          <t>HK225/55R18</t>
         </is>
       </c>
       <c r="D139" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E139" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F139" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G139" s="5">
         <v>0</v>
       </c>
       <c r="H139" s="6">
-        <v>700</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="140">
@@ -4975,19 +4975,19 @@
       </c>
       <c r="B140" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>KUMHO</t>
         </is>
       </c>
       <c r="C140" s="4" t="inlineStr">
         <is>
-          <t>HK225/55R18</t>
+          <t>KM225/55R18</t>
         </is>
       </c>
       <c r="D140" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E140" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F140" s="5">
         <v>0</v>
@@ -4996,30 +4996,30 @@
         <v>0</v>
       </c>
       <c r="H140" s="6">
-        <v>500</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="141">
       <c r="A141" s="4" t="inlineStr">
         <is>
-          <t>225/55R18</t>
+          <t>225/55R19</t>
         </is>
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>KUMHO</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>KM225/55R18</t>
+          <t>BR225/55R19</t>
         </is>
       </c>
       <c r="D141" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E141" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F141" s="5">
         <v>0</v>
@@ -5028,7 +5028,7 @@
         <v>0</v>
       </c>
       <c r="H141" s="6">
-        <v>450</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="142">
@@ -5039,19 +5039,19 @@
       </c>
       <c r="B142" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C142" s="4" t="inlineStr">
         <is>
-          <t>BR225/55R19</t>
+          <t>GD225/55R19</t>
         </is>
       </c>
       <c r="D142" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E142" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F142" s="5">
         <v>0</v>
@@ -5066,21 +5066,21 @@
     <row outlineLevel="0" r="143">
       <c r="A143" s="4" t="inlineStr">
         <is>
-          <t>225/55R19</t>
+          <t>225/60R17</t>
         </is>
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>GD225/55R19</t>
+          <t>HK225/60R17</t>
         </is>
       </c>
       <c r="D143" s="5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E143" s="5">
         <v>4</v>
@@ -5089,65 +5089,65 @@
         <v>0</v>
       </c>
       <c r="G143" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H143" s="6">
-        <v>750</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="144">
       <c r="A144" s="4" t="inlineStr">
         <is>
-          <t>225/60R17</t>
+          <t>225/60R18</t>
         </is>
       </c>
       <c r="B144" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C144" s="4" t="inlineStr">
         <is>
-          <t>HK225/60R17</t>
+          <t>GD225/60R18</t>
         </is>
       </c>
       <c r="D144" s="5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E144" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F144" s="5">
         <v>0</v>
       </c>
       <c r="G144" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H144" s="6">
-        <v>400</v>
+        <v>700</v>
       </c>
     </row>
     <row outlineLevel="0" r="145">
       <c r="A145" s="4" t="inlineStr">
         <is>
-          <t>225/60R18</t>
+          <t>225/65R17</t>
         </is>
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>GD225/60R18</t>
+          <t>RD225/65R17</t>
         </is>
       </c>
       <c r="D145" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E145" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F145" s="5">
         <v>0</v>
@@ -5156,13 +5156,13 @@
         <v>0</v>
       </c>
       <c r="H145" s="6">
-        <v>700</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="146">
       <c r="A146" s="4" t="inlineStr">
         <is>
-          <t>225/65R17</t>
+          <t>225/75R15C</t>
         </is>
       </c>
       <c r="B146" s="4" t="inlineStr">
@@ -5172,29 +5172,29 @@
       </c>
       <c r="C146" s="4" t="inlineStr">
         <is>
-          <t>RD225/65R17</t>
+          <t>RD225/75R15C</t>
         </is>
       </c>
       <c r="D146" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E146" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F146" s="5">
         <v>0</v>
       </c>
       <c r="G146" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H146" s="6">
-        <v>450</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="147">
       <c r="A147" s="4" t="inlineStr">
         <is>
-          <t>225/75R15C</t>
+          <t>235/35R19</t>
         </is>
       </c>
       <c r="B147" s="4" t="inlineStr">
@@ -5204,61 +5204,61 @@
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>RD225/75R15C</t>
+          <t>RD235/35R19</t>
         </is>
       </c>
       <c r="D147" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E147" s="5">
         <v>0</v>
       </c>
       <c r="F147" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G147" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H147" s="6">
-        <v>330</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="148">
       <c r="A148" s="4" t="inlineStr">
         <is>
-          <t>235/35R19</t>
+          <t>235/40R19</t>
         </is>
       </c>
       <c r="B148" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C148" s="4" t="inlineStr">
         <is>
-          <t>RD235/35R19</t>
+          <t>GD235/40R19</t>
         </is>
       </c>
       <c r="D148" s="5">
         <v>4</v>
       </c>
       <c r="E148" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F148" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G148" s="5">
         <v>0</v>
       </c>
       <c r="H148" s="6">
-        <v>600</v>
+        <v>850</v>
       </c>
     </row>
     <row outlineLevel="0" r="149">
       <c r="A149" s="4" t="inlineStr">
         <is>
-          <t>235/40R19</t>
+          <t>235/45R18</t>
         </is>
       </c>
       <c r="B149" s="4" t="inlineStr">
@@ -5268,7 +5268,7 @@
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>GD235/40R19</t>
+          <t>GD235/45R18</t>
         </is>
       </c>
       <c r="D149" s="5">
@@ -5284,30 +5284,30 @@
         <v>0</v>
       </c>
       <c r="H149" s="6">
-        <v>850</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="150">
       <c r="A150" s="4" t="inlineStr">
         <is>
-          <t>235/45R18</t>
+          <t>235/50R18</t>
         </is>
       </c>
       <c r="B150" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C150" s="4" t="inlineStr">
         <is>
-          <t>GD235/45R18</t>
+          <t>HK235/50R18</t>
         </is>
       </c>
       <c r="D150" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E150" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F150" s="5">
         <v>0</v>
@@ -5316,30 +5316,30 @@
         <v>0</v>
       </c>
       <c r="H150" s="6">
-        <v>600</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="151">
       <c r="A151" s="4" t="inlineStr">
         <is>
-          <t>235/50R18</t>
+          <t>235/50R19</t>
         </is>
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>HK235/50R18</t>
+          <t>GD235/50R19</t>
         </is>
       </c>
       <c r="D151" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E151" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F151" s="5">
         <v>0</v>
@@ -5348,13 +5348,13 @@
         <v>0</v>
       </c>
       <c r="H151" s="6">
-        <v>500</v>
+        <v>800</v>
       </c>
     </row>
     <row outlineLevel="0" r="152">
       <c r="A152" s="4" t="inlineStr">
         <is>
-          <t>235/50R19</t>
+          <t>235/50R20</t>
         </is>
       </c>
       <c r="B152" s="4" t="inlineStr">
@@ -5364,78 +5364,78 @@
       </c>
       <c r="C152" s="4" t="inlineStr">
         <is>
-          <t>GD235/50R19</t>
+          <t>GD235/50R20</t>
         </is>
       </c>
       <c r="D152" s="5">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E152" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F152" s="5">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G152" s="5">
         <v>0</v>
       </c>
       <c r="H152" s="6">
-        <v>800</v>
+        <v>1180</v>
       </c>
     </row>
     <row outlineLevel="0" r="153">
       <c r="A153" s="4" t="inlineStr">
         <is>
-          <t>235/50R20</t>
+          <t>235/55R17</t>
         </is>
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>GD235/50R20</t>
+          <t>BR235/55R17</t>
         </is>
       </c>
       <c r="D153" s="5">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E153" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F153" s="5">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G153" s="5">
         <v>0</v>
       </c>
       <c r="H153" s="6">
-        <v>1180</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="154">
       <c r="A154" s="4" t="inlineStr">
         <is>
-          <t>235/55R17</t>
+          <t>235/55R18</t>
         </is>
       </c>
       <c r="B154" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C154" s="4" t="inlineStr">
         <is>
-          <t>BR235/55R17</t>
+          <t>HK235/55R18</t>
         </is>
       </c>
       <c r="D154" s="5">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E154" s="5">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F154" s="5">
         <v>0</v>
@@ -5444,30 +5444,30 @@
         <v>0</v>
       </c>
       <c r="H154" s="6">
-        <v>450</v>
+        <v>480</v>
       </c>
     </row>
     <row outlineLevel="0" r="155">
       <c r="A155" s="4" t="inlineStr">
         <is>
-          <t>235/55R18</t>
+          <t>235/55R19</t>
         </is>
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>HK235/55R18</t>
+          <t>GD235/55R19</t>
         </is>
       </c>
       <c r="D155" s="5">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E155" s="5">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F155" s="5">
         <v>0</v>
@@ -5476,7 +5476,7 @@
         <v>0</v>
       </c>
       <c r="H155" s="6">
-        <v>480</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="156">
@@ -5487,19 +5487,19 @@
       </c>
       <c r="B156" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C156" s="4" t="inlineStr">
         <is>
-          <t>GD235/55R19</t>
+          <t>HK235/55R19</t>
         </is>
       </c>
       <c r="D156" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E156" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F156" s="5">
         <v>0</v>
@@ -5508,7 +5508,7 @@
         <v>0</v>
       </c>
       <c r="H156" s="6">
-        <v>750</v>
+        <v>630</v>
       </c>
     </row>
     <row outlineLevel="0" r="157">
@@ -5519,12 +5519,12 @@
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>HK235/55R19</t>
+          <t>LF235/55R19</t>
         </is>
       </c>
       <c r="D157" s="5">
@@ -5540,7 +5540,7 @@
         <v>0</v>
       </c>
       <c r="H157" s="6">
-        <v>630</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="158">
@@ -5551,19 +5551,19 @@
       </c>
       <c r="B158" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C158" s="4" t="inlineStr">
         <is>
-          <t>LF235/55R19</t>
+          <t>NX235/55R19</t>
         </is>
       </c>
       <c r="D158" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E158" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F158" s="5">
         <v>0</v>
@@ -5572,7 +5572,7 @@
         <v>0</v>
       </c>
       <c r="H158" s="6">
-        <v>500</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="159">
@@ -5583,66 +5583,66 @@
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>NX235/55R19</t>
+          <t>RD235/55R19</t>
         </is>
       </c>
       <c r="D159" s="5">
         <v>2</v>
       </c>
       <c r="E159" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F159" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G159" s="5">
         <v>0</v>
       </c>
       <c r="H159" s="6">
-        <v>600</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="160">
       <c r="A160" s="4" t="inlineStr">
         <is>
-          <t>235/55R19</t>
+          <t>235/60R16</t>
         </is>
       </c>
       <c r="B160" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C160" s="4" t="inlineStr">
         <is>
-          <t>RD235/55R19</t>
+          <t>HK235/60R16</t>
         </is>
       </c>
       <c r="D160" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E160" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F160" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G160" s="5">
         <v>0</v>
       </c>
       <c r="H160" s="6">
-        <v>500</v>
+        <v>430</v>
       </c>
     </row>
     <row outlineLevel="0" r="161">
       <c r="A161" s="4" t="inlineStr">
         <is>
-          <t>235/60R16</t>
+          <t>235/60R17</t>
         </is>
       </c>
       <c r="B161" s="4" t="inlineStr">
@@ -5652,55 +5652,55 @@
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>HK235/60R16</t>
+          <t>HK235/60R17</t>
         </is>
       </c>
       <c r="D161" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E161" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F161" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G161" s="5">
         <v>0</v>
       </c>
       <c r="H161" s="6">
-        <v>430</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="162">
       <c r="A162" s="4" t="inlineStr">
         <is>
-          <t>235/60R17</t>
+          <t>235/60R18</t>
         </is>
       </c>
       <c r="B162" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C162" s="4" t="inlineStr">
         <is>
-          <t>HK235/60R17</t>
+          <t>GD235/60R18</t>
         </is>
       </c>
       <c r="D162" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E162" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F162" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G162" s="5">
         <v>0</v>
       </c>
       <c r="H162" s="6">
-        <v>500</v>
+        <v>680</v>
       </c>
     </row>
     <row outlineLevel="0" r="163">
@@ -5711,12 +5711,12 @@
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>GD235/60R18</t>
+          <t>HK235/60R18</t>
         </is>
       </c>
       <c r="D163" s="5">
@@ -5732,30 +5732,30 @@
         <v>0</v>
       </c>
       <c r="H163" s="6">
-        <v>680</v>
+        <v>480</v>
       </c>
     </row>
     <row outlineLevel="0" r="164">
       <c r="A164" s="4" t="inlineStr">
         <is>
-          <t>235/60R18</t>
+          <t>245/40R17</t>
         </is>
       </c>
       <c r="B164" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C164" s="4" t="inlineStr">
         <is>
-          <t>HK235/60R18</t>
+          <t>GD245/40R17</t>
         </is>
       </c>
       <c r="D164" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E164" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F164" s="5">
         <v>0</v>
@@ -5764,13 +5764,13 @@
         <v>0</v>
       </c>
       <c r="H164" s="6">
-        <v>480</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="165">
       <c r="A165" s="4" t="inlineStr">
         <is>
-          <t>245/40R17</t>
+          <t>245/40R18</t>
         </is>
       </c>
       <c r="B165" s="4" t="inlineStr">
@@ -5780,43 +5780,43 @@
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>GD245/40R17</t>
+          <t>GD245/40R18</t>
         </is>
       </c>
       <c r="D165" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E165" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F165" s="5">
         <v>0</v>
       </c>
       <c r="G165" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H165" s="6">
-        <v>400</v>
+        <v>620</v>
       </c>
     </row>
     <row outlineLevel="0" r="166">
       <c r="A166" s="4" t="inlineStr">
         <is>
-          <t>245/40R18</t>
+          <t>245/40R19</t>
         </is>
       </c>
       <c r="B166" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C166" s="4" t="inlineStr">
         <is>
-          <t>GD245/40R18</t>
+          <t>HK245/40R19</t>
         </is>
       </c>
       <c r="D166" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E166" s="5">
         <v>4</v>
@@ -5825,97 +5825,97 @@
         <v>0</v>
       </c>
       <c r="G166" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H166" s="6">
-        <v>620</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="167">
       <c r="A167" s="4" t="inlineStr">
         <is>
-          <t>245/40R19</t>
+          <t>245/40R20</t>
         </is>
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>HK245/40R19</t>
+          <t>CT245/40R20</t>
         </is>
       </c>
       <c r="D167" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E167" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F167" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G167" s="5">
         <v>0</v>
       </c>
       <c r="H167" s="6">
-        <v>750</v>
+        <v>1050</v>
       </c>
     </row>
     <row outlineLevel="0" r="168">
       <c r="A168" s="4" t="inlineStr">
         <is>
-          <t>245/40R20</t>
+          <t>245/45R17</t>
         </is>
       </c>
       <c r="B168" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C168" s="4" t="inlineStr">
         <is>
-          <t>CT245/40R20</t>
+          <t>HK245/45R17</t>
         </is>
       </c>
       <c r="D168" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E168" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F168" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G168" s="5">
         <v>0</v>
       </c>
       <c r="H168" s="6">
-        <v>1050</v>
+        <v>430</v>
       </c>
     </row>
     <row outlineLevel="0" r="169">
       <c r="A169" s="4" t="inlineStr">
         <is>
-          <t>245/45R17</t>
+          <t>245/45R18</t>
         </is>
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>HK245/45R17</t>
+          <t>CT245/45R18</t>
         </is>
       </c>
       <c r="D169" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E169" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F169" s="5">
         <v>0</v>
@@ -5924,7 +5924,7 @@
         <v>0</v>
       </c>
       <c r="H169" s="6">
-        <v>430</v>
+        <v>650</v>
       </c>
     </row>
     <row outlineLevel="0" r="170">
@@ -5935,19 +5935,19 @@
       </c>
       <c r="B170" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C170" s="4" t="inlineStr">
         <is>
-          <t>CT245/45R18</t>
+          <t>GD245/45R18</t>
         </is>
       </c>
       <c r="D170" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E170" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F170" s="5">
         <v>0</v>
@@ -5956,7 +5956,7 @@
         <v>0</v>
       </c>
       <c r="H170" s="6">
-        <v>650</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="171">
@@ -5967,19 +5967,19 @@
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t>GD245/45R18</t>
+          <t>HK245/45R18</t>
         </is>
       </c>
       <c r="D171" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E171" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F171" s="5">
         <v>0</v>
@@ -5988,30 +5988,30 @@
         <v>0</v>
       </c>
       <c r="H171" s="6">
-        <v>600</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="172">
       <c r="A172" s="4" t="inlineStr">
         <is>
-          <t>245/45R18</t>
+          <t>245/45R18RF</t>
         </is>
       </c>
       <c r="B172" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C172" s="4" t="inlineStr">
         <is>
-          <t>HK245/45R18</t>
+          <t>GD245/45R18RF</t>
         </is>
       </c>
       <c r="D172" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E172" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F172" s="5">
         <v>0</v>
@@ -6020,23 +6020,23 @@
         <v>0</v>
       </c>
       <c r="H172" s="6">
-        <v>500</v>
+        <v>720</v>
       </c>
     </row>
     <row outlineLevel="0" r="173">
       <c r="A173" s="4" t="inlineStr">
         <is>
-          <t>245/45R18RF</t>
+          <t>245/45R19</t>
         </is>
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>GD245/45R18RF</t>
+          <t>BR245/45R19</t>
         </is>
       </c>
       <c r="D173" s="5">
@@ -6052,7 +6052,7 @@
         <v>0</v>
       </c>
       <c r="H173" s="6">
-        <v>720</v>
+        <v>790</v>
       </c>
     </row>
     <row outlineLevel="0" r="174">
@@ -6063,44 +6063,44 @@
       </c>
       <c r="B174" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C174" s="4" t="inlineStr">
         <is>
-          <t>BR245/45R19</t>
+          <t>RD245/45R19</t>
         </is>
       </c>
       <c r="D174" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E174" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F174" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G174" s="5">
         <v>0</v>
       </c>
       <c r="H174" s="6">
-        <v>790</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="175">
       <c r="A175" s="4" t="inlineStr">
         <is>
-          <t>245/45R19</t>
+          <t>245/45R20</t>
         </is>
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>RD245/45R19</t>
+          <t>HK245/45R20</t>
         </is>
       </c>
       <c r="D175" s="5">
@@ -6116,59 +6116,59 @@
         <v>0</v>
       </c>
       <c r="H175" s="6">
-        <v>450</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="176">
       <c r="A176" s="4" t="inlineStr">
         <is>
-          <t>245/45R20</t>
+          <t>245/65R17</t>
         </is>
       </c>
       <c r="B176" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C176" s="4" t="inlineStr">
         <is>
-          <t>HK245/45R20</t>
+          <t>NX245/65R17</t>
         </is>
       </c>
       <c r="D176" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E176" s="5">
         <v>0</v>
       </c>
       <c r="F176" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G176" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H176" s="6">
-        <v>750</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="177">
       <c r="A177" s="4" t="inlineStr">
         <is>
-          <t>245/65R17</t>
+          <t>245/70R16</t>
         </is>
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>LASSA</t>
         </is>
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>NX245/65R17</t>
+          <t>LS245/70R16</t>
         </is>
       </c>
       <c r="D177" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E177" s="5">
         <v>0</v>
@@ -6177,65 +6177,65 @@
         <v>0</v>
       </c>
       <c r="G177" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H177" s="6">
-        <v>600</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="178">
       <c r="A178" s="4" t="inlineStr">
         <is>
-          <t>245/70R16</t>
+          <t>255/35R19</t>
         </is>
       </c>
       <c r="B178" s="4" t="inlineStr">
         <is>
-          <t>LASSA</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C178" s="4" t="inlineStr">
         <is>
-          <t>LS245/70R16</t>
+          <t>DL255/35R19</t>
         </is>
       </c>
       <c r="D178" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E178" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F178" s="5">
         <v>0</v>
       </c>
       <c r="G178" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H178" s="6">
-        <v>500</v>
+        <v>700</v>
       </c>
     </row>
     <row outlineLevel="0" r="179">
       <c r="A179" s="4" t="inlineStr">
         <is>
-          <t>255/35R19</t>
+          <t>255/35R19RF</t>
         </is>
       </c>
       <c r="B179" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C179" s="4" t="inlineStr">
         <is>
-          <t>DL255/35R19</t>
+          <t>CT255/35R19RF</t>
         </is>
       </c>
       <c r="D179" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E179" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F179" s="5">
         <v>0</v>
@@ -6244,7 +6244,7 @@
         <v>0</v>
       </c>
       <c r="H179" s="6">
-        <v>700</v>
+        <v>950</v>
       </c>
     </row>
     <row outlineLevel="0" r="180">
@@ -6255,19 +6255,19 @@
       </c>
       <c r="B180" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C180" s="4" t="inlineStr">
         <is>
-          <t>CT255/35R19RF</t>
+          <t>GD255/35R19RF</t>
         </is>
       </c>
       <c r="D180" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E180" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F180" s="5">
         <v>0</v>
@@ -6282,39 +6282,39 @@
     <row outlineLevel="0" r="181">
       <c r="A181" s="4" t="inlineStr">
         <is>
-          <t>255/35R19RF</t>
+          <t>255/50R19</t>
         </is>
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C181" s="4" t="inlineStr">
         <is>
-          <t>GD255/35R19RF</t>
+          <t>CT255/50R19</t>
         </is>
       </c>
       <c r="D181" s="5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E181" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F181" s="5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G181" s="5">
         <v>0</v>
       </c>
       <c r="H181" s="6">
-        <v>950</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="182">
       <c r="A182" s="4" t="inlineStr">
         <is>
-          <t>255/50R19</t>
+          <t>255/50R20</t>
         </is>
       </c>
       <c r="B182" s="4" t="inlineStr">
@@ -6324,29 +6324,29 @@
       </c>
       <c r="C182" s="4" t="inlineStr">
         <is>
-          <t>CT255/50R19</t>
+          <t>CT255/50R20</t>
         </is>
       </c>
       <c r="D182" s="5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E182" s="5">
         <v>0</v>
       </c>
       <c r="F182" s="5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G182" s="5">
         <v>0</v>
       </c>
       <c r="H182" s="6">
-        <v>750</v>
+        <v>900</v>
       </c>
     </row>
     <row outlineLevel="0" r="183">
       <c r="A183" s="4" t="inlineStr">
         <is>
-          <t>255/50R20</t>
+          <t>255/55R19</t>
         </is>
       </c>
       <c r="B183" s="4" t="inlineStr">
@@ -6356,23 +6356,23 @@
       </c>
       <c r="C183" s="4" t="inlineStr">
         <is>
-          <t>CT255/50R20</t>
+          <t>CT255/55R19</t>
         </is>
       </c>
       <c r="D183" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E183" s="5">
         <v>0</v>
       </c>
       <c r="F183" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G183" s="5">
         <v>0</v>
       </c>
       <c r="H183" s="6">
-        <v>900</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="184">
@@ -6383,34 +6383,34 @@
       </c>
       <c r="B184" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C184" s="4" t="inlineStr">
         <is>
-          <t>CT255/55R19</t>
+          <t>DL255/55R19</t>
         </is>
       </c>
       <c r="D184" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E184" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F184" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G184" s="5">
         <v>0</v>
       </c>
       <c r="H184" s="6">
-        <v>750</v>
+        <v>700</v>
       </c>
     </row>
     <row outlineLevel="0" r="185">
       <c r="A185" s="4" t="inlineStr">
         <is>
-          <t>255/55R19</t>
+          <t>255/70R15</t>
         </is>
       </c>
       <c r="B185" s="4" t="inlineStr">
@@ -6420,43 +6420,43 @@
       </c>
       <c r="C185" s="4" t="inlineStr">
         <is>
-          <t>DL255/55R19</t>
+          <t>DL255/70R15</t>
         </is>
       </c>
       <c r="D185" s="5">
         <v>2</v>
       </c>
       <c r="E185" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F185" s="5">
         <v>0</v>
       </c>
       <c r="G185" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H185" s="6">
-        <v>700</v>
+        <v>550</v>
       </c>
     </row>
     <row outlineLevel="0" r="186">
       <c r="A186" s="4" t="inlineStr">
         <is>
-          <t>255/70R15</t>
+          <t>255/70R16</t>
         </is>
       </c>
       <c r="B186" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C186" s="4" t="inlineStr">
         <is>
-          <t>DL255/70R15</t>
+          <t>RD255/70R16</t>
         </is>
       </c>
       <c r="D186" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E186" s="5">
         <v>0</v>
@@ -6465,48 +6465,48 @@
         <v>0</v>
       </c>
       <c r="G186" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H186" s="6">
-        <v>550</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="187">
       <c r="A187" s="4" t="inlineStr">
         <is>
-          <t>255/70R16</t>
+          <t>265/35R18</t>
         </is>
       </c>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C187" s="4" t="inlineStr">
         <is>
-          <t>RD255/70R16</t>
+          <t>GD265/35R18</t>
         </is>
       </c>
       <c r="D187" s="5">
         <v>1</v>
       </c>
       <c r="E187" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F187" s="5">
         <v>0</v>
       </c>
       <c r="G187" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H187" s="6">
-        <v>500</v>
+        <v>700</v>
       </c>
     </row>
     <row outlineLevel="0" r="188">
       <c r="A188" s="4" t="inlineStr">
         <is>
-          <t>265/35R18</t>
+          <t>265/50R20</t>
         </is>
       </c>
       <c r="B188" s="4" t="inlineStr">
@@ -6516,29 +6516,29 @@
       </c>
       <c r="C188" s="4" t="inlineStr">
         <is>
-          <t>GD265/35R18</t>
+          <t>GD265/50R20</t>
         </is>
       </c>
       <c r="D188" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E188" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F188" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G188" s="5">
         <v>0</v>
       </c>
       <c r="H188" s="6">
-        <v>700</v>
+        <v>1150</v>
       </c>
     </row>
     <row outlineLevel="0" r="189">
       <c r="A189" s="4" t="inlineStr">
         <is>
-          <t>265/50R20</t>
+          <t>275/35R19RF</t>
         </is>
       </c>
       <c r="B189" s="4" t="inlineStr">
@@ -6548,71 +6548,71 @@
       </c>
       <c r="C189" s="4" t="inlineStr">
         <is>
-          <t>GD265/50R20</t>
+          <t>GD275/35R19RF</t>
         </is>
       </c>
       <c r="D189" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E189" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F189" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G189" s="5">
         <v>0</v>
       </c>
       <c r="H189" s="6">
-        <v>1150</v>
+        <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="190">
       <c r="A190" s="4" t="inlineStr">
         <is>
-          <t>275/35R19RF</t>
+          <t>275/35R20</t>
         </is>
       </c>
       <c r="B190" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C190" s="4" t="inlineStr">
         <is>
-          <t>GD275/35R19RF</t>
+          <t>CT275/35R20</t>
         </is>
       </c>
       <c r="D190" s="5">
         <v>2</v>
       </c>
       <c r="E190" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F190" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G190" s="5">
         <v>0</v>
       </c>
       <c r="H190" s="6">
-        <v>1</v>
+        <v>980</v>
       </c>
     </row>
     <row outlineLevel="0" r="191">
       <c r="A191" s="4" t="inlineStr">
         <is>
-          <t>275/35R20</t>
+          <t>275/40R20</t>
         </is>
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C191" s="4" t="inlineStr">
         <is>
-          <t>CT275/35R20</t>
+          <t>HK275/40R20</t>
         </is>
       </c>
       <c r="D191" s="5">
@@ -6628,23 +6628,23 @@
         <v>0</v>
       </c>
       <c r="H191" s="6">
-        <v>980</v>
+        <v>770</v>
       </c>
     </row>
     <row outlineLevel="0" r="192">
       <c r="A192" s="4" t="inlineStr">
         <is>
-          <t>275/40R20</t>
+          <t>275/50R21</t>
         </is>
       </c>
       <c r="B192" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C192" s="4" t="inlineStr">
         <is>
-          <t>HK275/40R20</t>
+          <t>GD275/50R21</t>
         </is>
       </c>
       <c r="D192" s="5">
@@ -6660,23 +6660,23 @@
         <v>0</v>
       </c>
       <c r="H192" s="6">
-        <v>770</v>
+        <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="193">
       <c r="A193" s="4" t="inlineStr">
         <is>
-          <t>275/50R21</t>
+          <t>295/35R21</t>
         </is>
       </c>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C193" s="4" t="inlineStr">
         <is>
-          <t>GD275/50R21</t>
+          <t>CT295/35R21</t>
         </is>
       </c>
       <c r="D193" s="5">
@@ -6692,7 +6692,7 @@
         <v>0</v>
       </c>
       <c r="H193" s="6">
-        <v>1</v>
+        <v>1150</v>
       </c>
     </row>
     <row outlineLevel="0" r="194">
@@ -6703,91 +6703,59 @@
       </c>
       <c r="B194" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C194" s="4" t="inlineStr">
         <is>
-          <t>CT295/35R21</t>
+          <t>GD295/35R21</t>
         </is>
       </c>
       <c r="D194" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E194" s="5">
         <v>0</v>
       </c>
       <c r="F194" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G194" s="5">
         <v>0</v>
       </c>
       <c r="H194" s="6">
-        <v>1150</v>
+        <v>980</v>
       </c>
     </row>
     <row outlineLevel="0" r="195">
       <c r="A195" s="4" t="inlineStr">
         <is>
-          <t>295/35R21</t>
+          <t>500R12</t>
         </is>
       </c>
       <c r="B195" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C195" s="4" t="inlineStr">
         <is>
-          <t>GD295/35R21</t>
+          <t>RD500R12</t>
         </is>
       </c>
       <c r="D195" s="5">
         <v>3</v>
       </c>
       <c r="E195" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F195" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G195" s="5">
         <v>0</v>
       </c>
       <c r="H195" s="6">
-        <v>980</v>
-      </c>
-    </row>
-    <row outlineLevel="0" r="196">
-      <c r="A196" s="4" t="inlineStr">
-        <is>
-          <t>500R12</t>
-        </is>
-      </c>
-      <c r="B196" s="4" t="inlineStr">
-        <is>
-          <t>RADIAL</t>
-        </is>
-      </c>
-      <c r="C196" s="4" t="inlineStr">
-        <is>
-          <t>RD500R12</t>
-        </is>
-      </c>
-      <c r="D196" s="5">
-        <v>3</v>
-      </c>
-      <c r="E196" s="5">
-        <v>3</v>
-      </c>
-      <c r="F196" s="5">
-        <v>0</v>
-      </c>
-      <c r="G196" s="5">
-        <v>0</v>
-      </c>
-      <c r="H196" s="6">
         <v>300</v>
       </c>
     </row>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -496,7 +496,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H195"/>
+  <dimension ref="A1:H194"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col customWidth="true" min="1" max="1" width="13.8359375"/>
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="D6" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E6" s="5">
         <v>3</v>
@@ -705,7 +705,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" s="6">
         <v>200</v>
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="D17" s="5">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E17" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F17" s="5">
         <v>1</v>
@@ -1080,10 +1080,10 @@
         </is>
       </c>
       <c r="D18" s="5">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E18" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F18" s="5">
         <v>60</v>
@@ -1112,10 +1112,10 @@
         </is>
       </c>
       <c r="D19" s="5">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E19" s="5">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F19" s="5">
         <v>0</v>
@@ -1208,10 +1208,10 @@
         </is>
       </c>
       <c r="D22" s="5">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E22" s="5">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F22" s="5">
         <v>0</v>
@@ -1688,10 +1688,10 @@
         </is>
       </c>
       <c r="D37" s="5">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E37" s="5">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F37" s="5">
         <v>49</v>
@@ -1903,60 +1903,60 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>SEMPERIT</t>
+          <t>WESTLAKE</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>SP185/70R14</t>
+          <t>WL185/70R14</t>
         </is>
       </c>
       <c r="D44" s="5">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E44" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F44" s="5">
         <v>0</v>
       </c>
       <c r="G44" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H44" s="6">
-        <v>280</v>
+        <v>220</v>
       </c>
     </row>
     <row outlineLevel="0" r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>185/70R14</t>
+          <t>195/50R15</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>WESTLAKE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>WL185/70R14</t>
+          <t>GD195/50R15</t>
         </is>
       </c>
       <c r="D45" s="5">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E45" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F45" s="5">
         <v>0</v>
       </c>
       <c r="G45" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H45" s="6">
-        <v>220</v>
+        <v>290</v>
       </c>
     </row>
     <row outlineLevel="0" r="46">
@@ -1967,28 +1967,28 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>SEMPERIT</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>GD195/50R15</t>
+          <t>SP195/50R15</t>
         </is>
       </c>
       <c r="D46" s="5">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="E46" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F46" s="5">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G46" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H46" s="6">
-        <v>290</v>
+        <v>260</v>
       </c>
     </row>
     <row outlineLevel="0" r="47">
@@ -1999,66 +1999,66 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>SEMPERIT</t>
+          <t>WESTLAKE</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>SP195/50R15</t>
+          <t>WL195/50R15</t>
         </is>
       </c>
       <c r="D47" s="5">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="E47" s="5">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F47" s="5">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G47" s="5">
         <v>4</v>
       </c>
       <c r="H47" s="6">
-        <v>260</v>
+        <v>225</v>
       </c>
     </row>
     <row outlineLevel="0" r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>195/50R15</t>
+          <t>195/50R16</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>WESTLAKE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>WL195/50R15</t>
+          <t>GD195/50R16</t>
         </is>
       </c>
       <c r="D48" s="5">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E48" s="5">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F48" s="5">
         <v>0</v>
       </c>
       <c r="G48" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H48" s="6">
-        <v>225</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>195/50R16</t>
+          <t>195/55R16</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
@@ -2068,23 +2068,23 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>GD195/50R16</t>
+          <t>GD195/55R16</t>
         </is>
       </c>
       <c r="D49" s="5">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="E49" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F49" s="5">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G49" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H49" s="6">
-        <v>330</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="50">
@@ -2095,28 +2095,28 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>GD195/55R16</t>
+          <t>HK195/55R16</t>
         </is>
       </c>
       <c r="D50" s="5">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E50" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F50" s="5">
         <v>13</v>
       </c>
       <c r="G50" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H50" s="6">
-        <v>350</v>
+        <v>290</v>
       </c>
     </row>
     <row outlineLevel="0" r="51">
@@ -2127,28 +2127,28 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>LASSA</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>HK195/55R16</t>
+          <t>LS195/55R16</t>
         </is>
       </c>
       <c r="D51" s="5">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="E51" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F51" s="5">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G51" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H51" s="6">
-        <v>290</v>
+        <v>280</v>
       </c>
     </row>
     <row outlineLevel="0" r="52">
@@ -2159,19 +2159,19 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>LASSA</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>LS195/55R16</t>
+          <t>NX195/55R16</t>
         </is>
       </c>
       <c r="D52" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E52" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F52" s="5">
         <v>0</v>
@@ -2180,7 +2180,7 @@
         <v>0</v>
       </c>
       <c r="H52" s="6">
-        <v>280</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="53">
@@ -2191,92 +2191,92 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>NX195/55R16</t>
+          <t>RD195/55R16</t>
         </is>
       </c>
       <c r="D53" s="5">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E53" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F53" s="5">
         <v>0</v>
       </c>
       <c r="G53" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H53" s="6">
-        <v>300</v>
+        <v>250</v>
       </c>
     </row>
     <row outlineLevel="0" r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>195/55R16</t>
+          <t>195/60R16</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>RD195/55R16</t>
+          <t>GD195/60R16</t>
         </is>
       </c>
       <c r="D54" s="5">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="E54" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F54" s="5">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G54" s="5">
         <v>3</v>
       </c>
       <c r="H54" s="6">
-        <v>250</v>
+        <v>355</v>
       </c>
     </row>
     <row outlineLevel="0" r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>195/60R16</t>
+          <t>195/65R15</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>DOUBLESTAR</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>GD195/60R16</t>
+          <t>DS195/65R15</t>
         </is>
       </c>
       <c r="D55" s="5">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="E55" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F55" s="5">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="G55" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H55" s="6">
-        <v>355</v>
+        <v>230</v>
       </c>
     </row>
     <row outlineLevel="0" r="56">
@@ -2287,22 +2287,22 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>DOUBLESTAR</t>
+          <t>GOODRIDE</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>DS195/65R15</t>
+          <t>GR195/65R15</t>
         </is>
       </c>
       <c r="D56" s="5">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E56" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F56" s="5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G56" s="5">
         <v>0</v>
@@ -2319,28 +2319,28 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>GOODRIDE</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>GR195/65R15</t>
+          <t>HK195/65R15</t>
         </is>
       </c>
       <c r="D57" s="5">
         <v>4</v>
       </c>
       <c r="E57" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F57" s="5">
         <v>0</v>
       </c>
       <c r="G57" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H57" s="6">
-        <v>230</v>
+        <v>260</v>
       </c>
     </row>
     <row outlineLevel="0" r="58">
@@ -2351,28 +2351,28 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>LASSA</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>HK195/65R15</t>
+          <t>LS195/65R15</t>
         </is>
       </c>
       <c r="D58" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E58" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F58" s="5">
         <v>0</v>
       </c>
       <c r="G58" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H58" s="6">
-        <v>260</v>
+        <v>250</v>
       </c>
     </row>
     <row outlineLevel="0" r="59">
@@ -2383,19 +2383,19 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>LASSA</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>LS195/65R15</t>
+          <t>NX195/65R15</t>
         </is>
       </c>
       <c r="D59" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E59" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F59" s="5">
         <v>0</v>
@@ -2404,7 +2404,7 @@
         <v>0</v>
       </c>
       <c r="H59" s="6">
-        <v>250</v>
+        <v>230</v>
       </c>
     </row>
     <row outlineLevel="0" r="60">
@@ -2415,25 +2415,25 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>NX195/65R15</t>
+          <t>RD195/65R15</t>
         </is>
       </c>
       <c r="D60" s="5">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E60" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F60" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G60" s="5">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H60" s="6">
         <v>230</v>
@@ -2447,124 +2447,124 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>SEMPERIT</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>RD195/65R15</t>
+          <t>SP195/65R15</t>
         </is>
       </c>
       <c r="D61" s="5">
-        <v>15</v>
+        <v>96</v>
       </c>
       <c r="E61" s="5">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F61" s="5">
-        <v>1</v>
+        <v>75</v>
       </c>
       <c r="G61" s="5">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="H61" s="6">
-        <v>230</v>
+        <v>250</v>
       </c>
     </row>
     <row outlineLevel="0" r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>195/65R15</t>
+          <t>195/70R15C</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>SEMPERIT</t>
+          <t>DAYTON</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>SP195/65R15</t>
+          <t>DT195/70R15C</t>
         </is>
       </c>
       <c r="D62" s="5">
-        <v>96</v>
+        <v>2</v>
       </c>
       <c r="E62" s="5">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F62" s="5">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="G62" s="5">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H62" s="6">
-        <v>250</v>
+        <v>280</v>
       </c>
     </row>
     <row outlineLevel="0" r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>195/70R15C</t>
+          <t>195/75R16C</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>DAYTON</t>
+          <t>GOODRIDE</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>DT195/70R15C</t>
+          <t>GR195/75R16C</t>
         </is>
       </c>
       <c r="D63" s="5">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E63" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F63" s="5">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G63" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H63" s="6">
-        <v>280</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>195/75R16C</t>
+          <t>205/45R17</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>GOODRIDE</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>GR195/75R16C</t>
+          <t>CT205/45R17</t>
         </is>
       </c>
       <c r="D64" s="5">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E64" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F64" s="5">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G64" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H64" s="6">
-        <v>350</v>
+        <v>550</v>
       </c>
     </row>
     <row outlineLevel="0" r="65">
@@ -2575,28 +2575,28 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>FULDA</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>CT205/45R17</t>
+          <t>FL205/45R17</t>
         </is>
       </c>
       <c r="D65" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E65" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F65" s="5">
         <v>0</v>
       </c>
       <c r="G65" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H65" s="6">
-        <v>550</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="66">
@@ -2607,28 +2607,28 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>FULDA</t>
+          <t>GOODRIDE</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>FL205/45R17</t>
+          <t>GR205/45R17</t>
         </is>
       </c>
       <c r="D66" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E66" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F66" s="5">
         <v>0</v>
       </c>
       <c r="G66" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H66" s="6">
-        <v>380</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="67">
@@ -2639,28 +2639,28 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>GOODRIDE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>GR205/45R17</t>
+          <t>GD205/45R17</t>
         </is>
       </c>
       <c r="D67" s="5">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="E67" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F67" s="5">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G67" s="5">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H67" s="6">
-        <v>300</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="68">
@@ -2671,28 +2671,28 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>GD205/45R17</t>
+          <t>NX205/45R17</t>
         </is>
       </c>
       <c r="D68" s="5">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="E68" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F68" s="5">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G68" s="5">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H68" s="6">
-        <v>450</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="69">
@@ -2703,83 +2703,83 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>NX205/45R17</t>
+          <t>RD205/45R17</t>
         </is>
       </c>
       <c r="D69" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E69" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F69" s="5">
         <v>0</v>
       </c>
       <c r="G69" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H69" s="6">
-        <v>380</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>205/45R17</t>
+          <t>205/50R17</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>RD205/45R17</t>
+          <t>CT205/50R17</t>
         </is>
       </c>
       <c r="D70" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E70" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F70" s="5">
         <v>0</v>
       </c>
       <c r="G70" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H70" s="6">
-        <v>300</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>205/50R17</t>
+          <t>205/55R16</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>AMINE</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>CT205/50R17</t>
+          <t>AM205/55R16</t>
         </is>
       </c>
       <c r="D71" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E71" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F71" s="5">
         <v>0</v>
@@ -2788,7 +2788,7 @@
         <v>0</v>
       </c>
       <c r="H71" s="6">
-        <v>450</v>
+        <v>240</v>
       </c>
     </row>
     <row outlineLevel="0" r="72">
@@ -2799,19 +2799,19 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>AMINE</t>
+          <t>DOUBLESTAR</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>AM205/55R16</t>
+          <t>DS205/55R16</t>
         </is>
       </c>
       <c r="D72" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E72" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F72" s="5">
         <v>0</v>
@@ -2820,7 +2820,7 @@
         <v>0</v>
       </c>
       <c r="H72" s="6">
-        <v>240</v>
+        <v>230</v>
       </c>
     </row>
     <row outlineLevel="0" r="73">
@@ -2831,28 +2831,28 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>DOUBLESTAR</t>
+          <t>FULDA</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>DS205/55R16</t>
+          <t>FL205/55R16</t>
         </is>
       </c>
       <c r="D73" s="5">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="E73" s="5">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F73" s="5">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G73" s="5">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H73" s="6">
-        <v>230</v>
+        <v>250</v>
       </c>
     </row>
     <row outlineLevel="0" r="74">
@@ -2863,25 +2863,25 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>FULDA</t>
+          <t>GOODRIDE</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>FL205/55R16</t>
+          <t>GR205/55R16</t>
         </is>
       </c>
       <c r="D74" s="5">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="E74" s="5">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F74" s="5">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="G74" s="5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H74" s="6">
         <v>250</v>
@@ -2895,28 +2895,28 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>GOODRIDE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>GR205/55R16</t>
+          <t>GD205/55R16</t>
         </is>
       </c>
       <c r="D75" s="5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E75" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F75" s="5">
         <v>0</v>
       </c>
       <c r="G75" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H75" s="6">
-        <v>250</v>
+        <v>280</v>
       </c>
     </row>
     <row outlineLevel="0" r="76">
@@ -2927,28 +2927,28 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>GD205/55R16</t>
+          <t>HK205/55R16</t>
         </is>
       </c>
       <c r="D76" s="5">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E76" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F76" s="5">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G76" s="5">
         <v>4</v>
       </c>
       <c r="H76" s="6">
-        <v>280</v>
+        <v>260</v>
       </c>
     </row>
     <row outlineLevel="0" r="77">
@@ -2959,48 +2959,48 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>HK205/55R16</t>
+          <t>RD205/55R16</t>
         </is>
       </c>
       <c r="D77" s="5">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="E77" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F77" s="5">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G77" s="5">
         <v>4</v>
       </c>
       <c r="H77" s="6">
-        <v>260</v>
+        <v>230</v>
       </c>
     </row>
     <row outlineLevel="0" r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>205/55R16</t>
+          <t>205/55R16RF</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>RD205/55R16</t>
+          <t>GD205/55R16RF</t>
         </is>
       </c>
       <c r="D78" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E78" s="5">
         <v>0</v>
@@ -3009,16 +3009,16 @@
         <v>0</v>
       </c>
       <c r="G78" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H78" s="6">
-        <v>230</v>
+        <v>480</v>
       </c>
     </row>
     <row outlineLevel="0" r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>205/55R16RF</t>
+          <t>205/55R17</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
@@ -3028,23 +3028,23 @@
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>GD205/55R16RF</t>
+          <t>GD205/55R17</t>
         </is>
       </c>
       <c r="D79" s="5">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="E79" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F79" s="5">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G79" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H79" s="6">
-        <v>480</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="80">
@@ -3055,51 +3055,51 @@
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>GD205/55R17</t>
+          <t>NX205/55R17</t>
         </is>
       </c>
       <c r="D80" s="5">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="E80" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F80" s="5">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G80" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H80" s="6">
-        <v>450</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>205/55R17</t>
+          <t>205/60R16</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>NX205/55R17</t>
+          <t>DL205/60R16</t>
         </is>
       </c>
       <c r="D81" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E81" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F81" s="5">
         <v>0</v>
@@ -3108,7 +3108,7 @@
         <v>0</v>
       </c>
       <c r="H81" s="6">
-        <v>400</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="82">
@@ -3119,28 +3119,28 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>DL205/60R16</t>
+          <t>GD205/60R16</t>
         </is>
       </c>
       <c r="D82" s="5">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="E82" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F82" s="5">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G82" s="5">
         <v>0</v>
       </c>
       <c r="H82" s="6">
-        <v>330</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="83">
@@ -3151,28 +3151,28 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>GD205/60R16</t>
+          <t>HK205/60R16</t>
         </is>
       </c>
       <c r="D83" s="5">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E83" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F83" s="5">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="G83" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H83" s="6">
-        <v>380</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="84">
@@ -3183,25 +3183,25 @@
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>HK205/60R16</t>
+          <t>LF205/60R16</t>
         </is>
       </c>
       <c r="D84" s="5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E84" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F84" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G84" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H84" s="6">
         <v>300</v>
@@ -3210,17 +3210,17 @@
     <row outlineLevel="0" r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>205/60R16</t>
+          <t>205/65R15</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>LF205/60R16</t>
+          <t>HK205/65R15</t>
         </is>
       </c>
       <c r="D85" s="5">
@@ -3236,30 +3236,30 @@
         <v>0</v>
       </c>
       <c r="H85" s="6">
-        <v>300</v>
+        <v>270</v>
       </c>
     </row>
     <row outlineLevel="0" r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>205/65R15</t>
+          <t>205/65R16</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>HK205/65R15</t>
+          <t>BR205/65R16</t>
         </is>
       </c>
       <c r="D86" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E86" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F86" s="5">
         <v>0</v>
@@ -3268,7 +3268,7 @@
         <v>0</v>
       </c>
       <c r="H86" s="6">
-        <v>270</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="87">
@@ -3279,19 +3279,19 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>BR205/65R16</t>
+          <t>HK205/65R16</t>
         </is>
       </c>
       <c r="D87" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E87" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F87" s="5">
         <v>0</v>
@@ -3300,39 +3300,39 @@
         <v>0</v>
       </c>
       <c r="H87" s="6">
-        <v>420</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>205/65R16</t>
+          <t>215/40R18</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>HK205/65R16</t>
+          <t>GD215/40R18</t>
         </is>
       </c>
       <c r="D88" s="5">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E88" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F88" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G88" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H88" s="6">
-        <v>380</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="89">
@@ -3343,44 +3343,44 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>GD215/40R18</t>
+          <t>HK215/40R18</t>
         </is>
       </c>
       <c r="D89" s="5">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E89" s="5">
         <v>4</v>
       </c>
       <c r="F89" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G89" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H89" s="6">
-        <v>600</v>
+        <v>490</v>
       </c>
     </row>
     <row outlineLevel="0" r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>215/40R18</t>
+          <t>215/45R16</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>HK215/40R18</t>
+          <t>GD215/45R16</t>
         </is>
       </c>
       <c r="D90" s="5">
@@ -3396,13 +3396,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="6">
-        <v>490</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>215/45R16</t>
+          <t>215/45R17</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
@@ -3412,14 +3412,14 @@
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>GD215/45R16</t>
+          <t>GD215/45R17</t>
         </is>
       </c>
       <c r="D91" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E91" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F91" s="5">
         <v>0</v>
@@ -3428,7 +3428,7 @@
         <v>0</v>
       </c>
       <c r="H91" s="6">
-        <v>450</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="92">
@@ -3439,25 +3439,25 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>GD215/45R17</t>
+          <t>HK215/45R17</t>
         </is>
       </c>
       <c r="D92" s="5">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="E92" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F92" s="5">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G92" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H92" s="6">
         <v>400</v>
@@ -3471,28 +3471,28 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>IRIS</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>HK215/45R17</t>
+          <t>IR215/45R17</t>
         </is>
       </c>
       <c r="D93" s="5">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="E93" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F93" s="5">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G93" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H93" s="6">
-        <v>400</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="94">
@@ -3503,28 +3503,28 @@
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>IRIS</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>IR215/45R17</t>
+          <t>LF215/45R17</t>
         </is>
       </c>
       <c r="D94" s="5">
         <v>1</v>
       </c>
       <c r="E94" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F94" s="5">
         <v>0</v>
       </c>
       <c r="G94" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H94" s="6">
-        <v>300</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="95">
@@ -3535,83 +3535,83 @@
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>LF215/45R17</t>
+          <t>NX215/45R17</t>
         </is>
       </c>
       <c r="D95" s="5">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E95" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F95" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G95" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H95" s="6">
-        <v>350</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="96">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>215/45R17</t>
+          <t>215/45R18</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>NX215/45R17</t>
+          <t>GD215/45R18</t>
         </is>
       </c>
       <c r="D96" s="5">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E96" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F96" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G96" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H96" s="6">
-        <v>380</v>
+        <v>550</v>
       </c>
     </row>
     <row outlineLevel="0" r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>215/45R18</t>
+          <t>215/50R17</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>GD215/45R18</t>
+          <t>BR215/50R17</t>
         </is>
       </c>
       <c r="D97" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E97" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F97" s="5">
         <v>0</v>
@@ -3620,7 +3620,7 @@
         <v>0</v>
       </c>
       <c r="H97" s="6">
-        <v>550</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="98">
@@ -3631,28 +3631,28 @@
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>BR215/50R17</t>
+          <t>GD215/50R17</t>
         </is>
       </c>
       <c r="D98" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E98" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F98" s="5">
         <v>0</v>
       </c>
       <c r="G98" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H98" s="6">
-        <v>450</v>
+        <v>470</v>
       </c>
     </row>
     <row outlineLevel="0" r="99">
@@ -3663,28 +3663,28 @@
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>GD215/50R17</t>
+          <t>HK215/50R17</t>
         </is>
       </c>
       <c r="D99" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E99" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F99" s="5">
         <v>0</v>
       </c>
       <c r="G99" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H99" s="6">
-        <v>470</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="100">
@@ -3695,19 +3695,19 @@
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>HK215/50R17</t>
+          <t>LF215/50R17</t>
         </is>
       </c>
       <c r="D100" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E100" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F100" s="5">
         <v>0</v>
@@ -3716,30 +3716,30 @@
         <v>0</v>
       </c>
       <c r="H100" s="6">
-        <v>400</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>215/50R17</t>
+          <t>215/50R18</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>LF215/50R17</t>
+          <t>GD215/50R18</t>
         </is>
       </c>
       <c r="D101" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E101" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F101" s="5">
         <v>0</v>
@@ -3748,13 +3748,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="6">
-        <v>420</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="102">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>215/50R18</t>
+          <t>215/55R16</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
@@ -3764,14 +3764,14 @@
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>GD215/50R18</t>
+          <t>GD215/55R16</t>
         </is>
       </c>
       <c r="D102" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E102" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F102" s="5">
         <v>0</v>
@@ -3780,7 +3780,7 @@
         <v>0</v>
       </c>
       <c r="H102" s="6">
-        <v>600</v>
+        <v>440</v>
       </c>
     </row>
     <row outlineLevel="0" r="103">
@@ -3791,12 +3791,12 @@
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>GD215/55R16</t>
+          <t>LF215/55R16</t>
         </is>
       </c>
       <c r="D103" s="5">
@@ -3812,23 +3812,23 @@
         <v>0</v>
       </c>
       <c r="H103" s="6">
-        <v>440</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="104">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>215/55R16</t>
+          <t>215/55R17</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>LF215/55R16</t>
+          <t>BR215/55R17</t>
         </is>
       </c>
       <c r="D104" s="5">
@@ -3844,7 +3844,7 @@
         <v>0</v>
       </c>
       <c r="H104" s="6">
-        <v>350</v>
+        <v>480</v>
       </c>
     </row>
     <row outlineLevel="0" r="105">
@@ -3855,19 +3855,19 @@
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>BR215/55R17</t>
+          <t>HK215/55R17</t>
         </is>
       </c>
       <c r="D105" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E105" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F105" s="5">
         <v>0</v>
@@ -3876,23 +3876,23 @@
         <v>0</v>
       </c>
       <c r="H105" s="6">
-        <v>480</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="106">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>215/55R17</t>
+          <t>215/55R18</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>HK215/55R17</t>
+          <t>GD215/55R18</t>
         </is>
       </c>
       <c r="D106" s="5">
@@ -3908,23 +3908,23 @@
         <v>0</v>
       </c>
       <c r="H106" s="6">
-        <v>420</v>
+        <v>580</v>
       </c>
     </row>
     <row outlineLevel="0" r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>215/55R18</t>
+          <t>215/60R16</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>GD215/55R18</t>
+          <t>BR215/60R16</t>
         </is>
       </c>
       <c r="D107" s="5">
@@ -3940,7 +3940,7 @@
         <v>0</v>
       </c>
       <c r="H107" s="6">
-        <v>580</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="108">
@@ -3951,25 +3951,25 @@
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>BR215/60R16</t>
+          <t>DL215/60R16</t>
         </is>
       </c>
       <c r="D108" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E108" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F108" s="5">
         <v>0</v>
       </c>
       <c r="G108" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H108" s="6">
         <v>350</v>
@@ -3983,28 +3983,28 @@
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>DL215/60R16</t>
+          <t>HK215/60R16</t>
         </is>
       </c>
       <c r="D109" s="5">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E109" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F109" s="5">
         <v>0</v>
       </c>
       <c r="G109" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H109" s="6">
-        <v>350</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="110">
@@ -4015,25 +4015,25 @@
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>HK215/60R16</t>
+          <t>NX215/60R16</t>
         </is>
       </c>
       <c r="D110" s="5">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E110" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F110" s="5">
         <v>0</v>
       </c>
       <c r="G110" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H110" s="6">
         <v>330</v>
@@ -4042,65 +4042,65 @@
     <row outlineLevel="0" r="111">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>215/60R16</t>
+          <t>215/60R17</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>NX215/60R16</t>
+          <t>RD215/60R17</t>
         </is>
       </c>
       <c r="D111" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E111" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F111" s="5">
         <v>0</v>
       </c>
       <c r="G111" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H111" s="6">
-        <v>330</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="112">
       <c r="A112" s="4" t="inlineStr">
         <is>
-          <t>215/60R17</t>
+          <t>215/65R16</t>
         </is>
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>RD215/60R17</t>
+          <t>GD215/65R16</t>
         </is>
       </c>
       <c r="D112" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E112" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F112" s="5">
         <v>0</v>
       </c>
       <c r="G112" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H112" s="6">
-        <v>300</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="113">
@@ -4111,83 +4111,83 @@
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>GD215/65R16</t>
+          <t>HK215/65R16</t>
         </is>
       </c>
       <c r="D113" s="5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E113" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F113" s="5">
         <v>0</v>
       </c>
       <c r="G113" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H113" s="6">
-        <v>380</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="114">
       <c r="A114" s="4" t="inlineStr">
         <is>
-          <t>215/65R16</t>
+          <t>215/65R17</t>
         </is>
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>MICHELIN</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>HK215/65R16</t>
+          <t>MC215/65R17</t>
         </is>
       </c>
       <c r="D114" s="5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E114" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F114" s="5">
         <v>0</v>
       </c>
       <c r="G114" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H114" s="6">
-        <v>330</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="115">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t>215/65R17</t>
+          <t>225/40R18</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>MICHELIN</t>
+          <t>BARUM</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>MC215/65R17</t>
+          <t>BM225/40R18</t>
         </is>
       </c>
       <c r="D115" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E115" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F115" s="5">
         <v>0</v>
@@ -4196,7 +4196,7 @@
         <v>0</v>
       </c>
       <c r="H115" s="6">
-        <v>600</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="116">
@@ -4207,28 +4207,28 @@
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>BARUM</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>BM225/40R18</t>
+          <t>GD225/40R18</t>
         </is>
       </c>
       <c r="D116" s="5">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="E116" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F116" s="5">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G116" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H116" s="6">
-        <v>420</v>
+        <v>480</v>
       </c>
     </row>
     <row outlineLevel="0" r="117">
@@ -4239,28 +4239,28 @@
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>GD225/40R18</t>
+          <t>HK225/40R18</t>
         </is>
       </c>
       <c r="D117" s="5">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="E117" s="5">
         <v>4</v>
       </c>
       <c r="F117" s="5">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G117" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H117" s="6">
-        <v>480</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="118">
@@ -4271,28 +4271,28 @@
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>LASSA</t>
         </is>
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>HK225/40R18</t>
+          <t>LS225/40R18</t>
         </is>
       </c>
       <c r="D118" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E118" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F118" s="5">
         <v>0</v>
       </c>
       <c r="G118" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H118" s="6">
-        <v>450</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="119">
@@ -4303,28 +4303,28 @@
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>LASSA</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>LS225/40R18</t>
+          <t>NX225/40R18</t>
         </is>
       </c>
       <c r="D119" s="5">
         <v>1</v>
       </c>
       <c r="E119" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F119" s="5">
         <v>0</v>
       </c>
       <c r="G119" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H119" s="6">
-        <v>330</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="120">
@@ -4335,19 +4335,19 @@
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>SEMPERIT</t>
         </is>
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>NX225/40R18</t>
+          <t>SP225/40R18</t>
         </is>
       </c>
       <c r="D120" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E120" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F120" s="5">
         <v>0</v>
@@ -4356,30 +4356,30 @@
         <v>0</v>
       </c>
       <c r="H120" s="6">
-        <v>400</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="121">
       <c r="A121" s="4" t="inlineStr">
         <is>
-          <t>225/40R18</t>
+          <t>225/40R18RF</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>SEMPERIT</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>SP225/40R18</t>
+          <t>GD225/40R18RF</t>
         </is>
       </c>
       <c r="D121" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E121" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F121" s="5">
         <v>0</v>
@@ -4388,30 +4388,30 @@
         <v>0</v>
       </c>
       <c r="H121" s="6">
-        <v>450</v>
+        <v>590</v>
       </c>
     </row>
     <row outlineLevel="0" r="122">
       <c r="A122" s="4" t="inlineStr">
         <is>
-          <t>225/40R18RF</t>
+          <t>225/45R17</t>
         </is>
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>GD225/40R18RF</t>
+          <t>CT225/45R17</t>
         </is>
       </c>
       <c r="D122" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E122" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F122" s="5">
         <v>0</v>
@@ -4420,7 +4420,7 @@
         <v>0</v>
       </c>
       <c r="H122" s="6">
-        <v>590</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="123">
@@ -4431,28 +4431,28 @@
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>FULDA</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>CT225/45R17</t>
+          <t>FL225/45R17</t>
         </is>
       </c>
       <c r="D123" s="5">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="E123" s="5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F123" s="5">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G123" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H123" s="6">
-        <v>400</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="124">
@@ -4463,28 +4463,28 @@
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>FULDA</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>FL225/45R17</t>
+          <t>GD225/45R17</t>
         </is>
       </c>
       <c r="D124" s="5">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E124" s="5">
         <v>6</v>
       </c>
       <c r="F124" s="5">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G124" s="5">
         <v>4</v>
       </c>
       <c r="H124" s="6">
-        <v>350</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="125">
@@ -4495,60 +4495,60 @@
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>GD225/45R17</t>
+          <t>HK225/45R17</t>
         </is>
       </c>
       <c r="D125" s="5">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="E125" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F125" s="5">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="G125" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H125" s="6">
-        <v>380</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="126">
       <c r="A126" s="4" t="inlineStr">
         <is>
-          <t>225/45R17</t>
+          <t>225/45R18</t>
         </is>
       </c>
       <c r="B126" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C126" s="4" t="inlineStr">
         <is>
-          <t>HK225/45R17</t>
+          <t>DL225/45R18</t>
         </is>
       </c>
       <c r="D126" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E126" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F126" s="5">
         <v>0</v>
       </c>
       <c r="G126" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H126" s="6">
-        <v>350</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="127">
@@ -4559,28 +4559,28 @@
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>DL225/45R18</t>
+          <t>GD225/45R18</t>
         </is>
       </c>
       <c r="D127" s="5">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E127" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F127" s="5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G127" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H127" s="6">
-        <v>500</v>
+        <v>550</v>
       </c>
     </row>
     <row outlineLevel="0" r="128">
@@ -4591,28 +4591,28 @@
       </c>
       <c r="B128" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C128" s="4" t="inlineStr">
         <is>
-          <t>GD225/45R18</t>
+          <t>HK225/45R18</t>
         </is>
       </c>
       <c r="D128" s="5">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E128" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F128" s="5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G128" s="5">
         <v>0</v>
       </c>
       <c r="H128" s="6">
-        <v>550</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="129">
@@ -4623,19 +4623,19 @@
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>HK225/45R18</t>
+          <t>LF225/45R18</t>
         </is>
       </c>
       <c r="D129" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E129" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F129" s="5">
         <v>0</v>
@@ -4644,103 +4644,103 @@
         <v>0</v>
       </c>
       <c r="H129" s="6">
-        <v>450</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="130">
       <c r="A130" s="4" t="inlineStr">
         <is>
-          <t>225/45R18</t>
+          <t>225/45R18RF</t>
         </is>
       </c>
       <c r="B130" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C130" s="4" t="inlineStr">
         <is>
-          <t>LF225/45R18</t>
+          <t>GD225/45R18RF</t>
         </is>
       </c>
       <c r="D130" s="5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E130" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F130" s="5">
         <v>0</v>
       </c>
       <c r="G130" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H130" s="6">
-        <v>420</v>
+        <v>720</v>
       </c>
     </row>
     <row outlineLevel="0" r="131">
       <c r="A131" s="4" t="inlineStr">
         <is>
-          <t>225/45R18RF</t>
+          <t>225/45R19</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>GD225/45R18RF</t>
+          <t>CT225/45R19</t>
         </is>
       </c>
       <c r="D131" s="5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E131" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F131" s="5">
         <v>0</v>
       </c>
       <c r="G131" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H131" s="6">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row outlineLevel="0" r="132">
       <c r="A132" s="4" t="inlineStr">
         <is>
-          <t>225/45R19</t>
+          <t>225/50R17</t>
         </is>
       </c>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C132" s="4" t="inlineStr">
         <is>
-          <t>CT225/45R19</t>
+          <t>GD225/50R17</t>
         </is>
       </c>
       <c r="D132" s="5">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E132" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F132" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G132" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H132" s="6">
-        <v>780</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="133">
@@ -4751,60 +4751,60 @@
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>GD225/50R17</t>
+          <t>HK225/50R17</t>
         </is>
       </c>
       <c r="D133" s="5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E133" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F133" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G133" s="5">
         <v>2</v>
       </c>
       <c r="H133" s="6">
-        <v>500</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="134">
       <c r="A134" s="4" t="inlineStr">
         <is>
-          <t>225/50R17</t>
+          <t>225/55R16</t>
         </is>
       </c>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C134" s="4" t="inlineStr">
         <is>
-          <t>HK225/50R17</t>
+          <t>DL225/55R16</t>
         </is>
       </c>
       <c r="D134" s="5">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E134" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F134" s="5">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G134" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H134" s="6">
-        <v>400</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="135">
@@ -4815,19 +4815,19 @@
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>DL225/55R16</t>
+          <t>GD225/55R16</t>
         </is>
       </c>
       <c r="D135" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E135" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F135" s="5">
         <v>0</v>
@@ -4836,30 +4836,30 @@
         <v>0</v>
       </c>
       <c r="H135" s="6">
-        <v>450</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="136">
       <c r="A136" s="4" t="inlineStr">
         <is>
-          <t>225/55R16</t>
+          <t>225/55R17</t>
         </is>
       </c>
       <c r="B136" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C136" s="4" t="inlineStr">
         <is>
-          <t>GD225/55R16</t>
+          <t>HK225/55R17</t>
         </is>
       </c>
       <c r="D136" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E136" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F136" s="5">
         <v>0</v>
@@ -4868,71 +4868,71 @@
         <v>0</v>
       </c>
       <c r="H136" s="6">
-        <v>420</v>
+        <v>430</v>
       </c>
     </row>
     <row outlineLevel="0" r="137">
       <c r="A137" s="4" t="inlineStr">
         <is>
-          <t>225/55R17</t>
+          <t>225/55R17RF</t>
         </is>
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>HK225/55R17</t>
+          <t>GD225/55R17RF</t>
         </is>
       </c>
       <c r="D137" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E137" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F137" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G137" s="5">
         <v>0</v>
       </c>
       <c r="H137" s="6">
-        <v>430</v>
+        <v>700</v>
       </c>
     </row>
     <row outlineLevel="0" r="138">
       <c r="A138" s="4" t="inlineStr">
         <is>
-          <t>225/55R17RF</t>
+          <t>225/55R18</t>
         </is>
       </c>
       <c r="B138" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C138" s="4" t="inlineStr">
         <is>
-          <t>GD225/55R17RF</t>
+          <t>HK225/55R18</t>
         </is>
       </c>
       <c r="D138" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E138" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F138" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G138" s="5">
         <v>0</v>
       </c>
       <c r="H138" s="6">
-        <v>700</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="139">
@@ -4943,19 +4943,19 @@
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>KUMHO</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>HK225/55R18</t>
+          <t>KM225/55R18</t>
         </is>
       </c>
       <c r="D139" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E139" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F139" s="5">
         <v>0</v>
@@ -4964,30 +4964,30 @@
         <v>0</v>
       </c>
       <c r="H139" s="6">
-        <v>500</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="140">
       <c r="A140" s="4" t="inlineStr">
         <is>
-          <t>225/55R18</t>
+          <t>225/55R19</t>
         </is>
       </c>
       <c r="B140" s="4" t="inlineStr">
         <is>
-          <t>KUMHO</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C140" s="4" t="inlineStr">
         <is>
-          <t>KM225/55R18</t>
+          <t>BR225/55R19</t>
         </is>
       </c>
       <c r="D140" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E140" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F140" s="5">
         <v>0</v>
@@ -4996,7 +4996,7 @@
         <v>0</v>
       </c>
       <c r="H140" s="6">
-        <v>450</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="141">
@@ -5007,19 +5007,19 @@
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>BR225/55R19</t>
+          <t>GD225/55R19</t>
         </is>
       </c>
       <c r="D141" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E141" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F141" s="5">
         <v>0</v>
@@ -5034,21 +5034,21 @@
     <row outlineLevel="0" r="142">
       <c r="A142" s="4" t="inlineStr">
         <is>
-          <t>225/55R19</t>
+          <t>225/60R17</t>
         </is>
       </c>
       <c r="B142" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C142" s="4" t="inlineStr">
         <is>
-          <t>GD225/55R19</t>
+          <t>HK225/60R17</t>
         </is>
       </c>
       <c r="D142" s="5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E142" s="5">
         <v>4</v>
@@ -5057,65 +5057,65 @@
         <v>0</v>
       </c>
       <c r="G142" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H142" s="6">
-        <v>750</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="143">
       <c r="A143" s="4" t="inlineStr">
         <is>
-          <t>225/60R17</t>
+          <t>225/60R18</t>
         </is>
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>HK225/60R17</t>
+          <t>GD225/60R18</t>
         </is>
       </c>
       <c r="D143" s="5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E143" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F143" s="5">
         <v>0</v>
       </c>
       <c r="G143" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H143" s="6">
-        <v>400</v>
+        <v>700</v>
       </c>
     </row>
     <row outlineLevel="0" r="144">
       <c r="A144" s="4" t="inlineStr">
         <is>
-          <t>225/60R18</t>
+          <t>225/65R17</t>
         </is>
       </c>
       <c r="B144" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C144" s="4" t="inlineStr">
         <is>
-          <t>GD225/60R18</t>
+          <t>RD225/65R17</t>
         </is>
       </c>
       <c r="D144" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E144" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F144" s="5">
         <v>0</v>
@@ -5124,13 +5124,13 @@
         <v>0</v>
       </c>
       <c r="H144" s="6">
-        <v>700</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="145">
       <c r="A145" s="4" t="inlineStr">
         <is>
-          <t>225/65R17</t>
+          <t>225/75R15C</t>
         </is>
       </c>
       <c r="B145" s="4" t="inlineStr">
@@ -5140,29 +5140,29 @@
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>RD225/65R17</t>
+          <t>RD225/75R15C</t>
         </is>
       </c>
       <c r="D145" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E145" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F145" s="5">
         <v>0</v>
       </c>
       <c r="G145" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H145" s="6">
-        <v>450</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="146">
       <c r="A146" s="4" t="inlineStr">
         <is>
-          <t>225/75R15C</t>
+          <t>235/35R19</t>
         </is>
       </c>
       <c r="B146" s="4" t="inlineStr">
@@ -5172,61 +5172,61 @@
       </c>
       <c r="C146" s="4" t="inlineStr">
         <is>
-          <t>RD225/75R15C</t>
+          <t>RD235/35R19</t>
         </is>
       </c>
       <c r="D146" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E146" s="5">
         <v>0</v>
       </c>
       <c r="F146" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G146" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H146" s="6">
-        <v>330</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="147">
       <c r="A147" s="4" t="inlineStr">
         <is>
-          <t>235/35R19</t>
+          <t>235/40R19</t>
         </is>
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>RD235/35R19</t>
+          <t>GD235/40R19</t>
         </is>
       </c>
       <c r="D147" s="5">
         <v>4</v>
       </c>
       <c r="E147" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F147" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G147" s="5">
         <v>0</v>
       </c>
       <c r="H147" s="6">
-        <v>600</v>
+        <v>850</v>
       </c>
     </row>
     <row outlineLevel="0" r="148">
       <c r="A148" s="4" t="inlineStr">
         <is>
-          <t>235/40R19</t>
+          <t>235/45R18</t>
         </is>
       </c>
       <c r="B148" s="4" t="inlineStr">
@@ -5236,7 +5236,7 @@
       </c>
       <c r="C148" s="4" t="inlineStr">
         <is>
-          <t>GD235/40R19</t>
+          <t>GD235/45R18</t>
         </is>
       </c>
       <c r="D148" s="5">
@@ -5252,30 +5252,30 @@
         <v>0</v>
       </c>
       <c r="H148" s="6">
-        <v>850</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="149">
       <c r="A149" s="4" t="inlineStr">
         <is>
-          <t>235/45R18</t>
+          <t>235/50R18</t>
         </is>
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>GD235/45R18</t>
+          <t>HK235/50R18</t>
         </is>
       </c>
       <c r="D149" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E149" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F149" s="5">
         <v>0</v>
@@ -5284,30 +5284,30 @@
         <v>0</v>
       </c>
       <c r="H149" s="6">
-        <v>600</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="150">
       <c r="A150" s="4" t="inlineStr">
         <is>
-          <t>235/50R18</t>
+          <t>235/50R19</t>
         </is>
       </c>
       <c r="B150" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C150" s="4" t="inlineStr">
         <is>
-          <t>HK235/50R18</t>
+          <t>GD235/50R19</t>
         </is>
       </c>
       <c r="D150" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E150" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F150" s="5">
         <v>0</v>
@@ -5316,13 +5316,13 @@
         <v>0</v>
       </c>
       <c r="H150" s="6">
-        <v>500</v>
+        <v>800</v>
       </c>
     </row>
     <row outlineLevel="0" r="151">
       <c r="A151" s="4" t="inlineStr">
         <is>
-          <t>235/50R19</t>
+          <t>235/50R20</t>
         </is>
       </c>
       <c r="B151" s="4" t="inlineStr">
@@ -5332,78 +5332,78 @@
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>GD235/50R19</t>
+          <t>GD235/50R20</t>
         </is>
       </c>
       <c r="D151" s="5">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E151" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F151" s="5">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G151" s="5">
         <v>0</v>
       </c>
       <c r="H151" s="6">
-        <v>800</v>
+        <v>1180</v>
       </c>
     </row>
     <row outlineLevel="0" r="152">
       <c r="A152" s="4" t="inlineStr">
         <is>
-          <t>235/50R20</t>
+          <t>235/55R17</t>
         </is>
       </c>
       <c r="B152" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C152" s="4" t="inlineStr">
         <is>
-          <t>GD235/50R20</t>
+          <t>BR235/55R17</t>
         </is>
       </c>
       <c r="D152" s="5">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E152" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F152" s="5">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G152" s="5">
         <v>0</v>
       </c>
       <c r="H152" s="6">
-        <v>1180</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="153">
       <c r="A153" s="4" t="inlineStr">
         <is>
-          <t>235/55R17</t>
+          <t>235/55R18</t>
         </is>
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>BR235/55R17</t>
+          <t>HK235/55R18</t>
         </is>
       </c>
       <c r="D153" s="5">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E153" s="5">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F153" s="5">
         <v>0</v>
@@ -5412,30 +5412,30 @@
         <v>0</v>
       </c>
       <c r="H153" s="6">
-        <v>450</v>
+        <v>480</v>
       </c>
     </row>
     <row outlineLevel="0" r="154">
       <c r="A154" s="4" t="inlineStr">
         <is>
-          <t>235/55R18</t>
+          <t>235/55R19</t>
         </is>
       </c>
       <c r="B154" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C154" s="4" t="inlineStr">
         <is>
-          <t>HK235/55R18</t>
+          <t>GD235/55R19</t>
         </is>
       </c>
       <c r="D154" s="5">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E154" s="5">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F154" s="5">
         <v>0</v>
@@ -5444,7 +5444,7 @@
         <v>0</v>
       </c>
       <c r="H154" s="6">
-        <v>480</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="155">
@@ -5455,19 +5455,19 @@
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>GD235/55R19</t>
+          <t>HK235/55R19</t>
         </is>
       </c>
       <c r="D155" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E155" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F155" s="5">
         <v>0</v>
@@ -5476,7 +5476,7 @@
         <v>0</v>
       </c>
       <c r="H155" s="6">
-        <v>750</v>
+        <v>630</v>
       </c>
     </row>
     <row outlineLevel="0" r="156">
@@ -5487,12 +5487,12 @@
       </c>
       <c r="B156" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C156" s="4" t="inlineStr">
         <is>
-          <t>HK235/55R19</t>
+          <t>LF235/55R19</t>
         </is>
       </c>
       <c r="D156" s="5">
@@ -5508,7 +5508,7 @@
         <v>0</v>
       </c>
       <c r="H156" s="6">
-        <v>630</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="157">
@@ -5519,19 +5519,19 @@
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>LF235/55R19</t>
+          <t>NX235/55R19</t>
         </is>
       </c>
       <c r="D157" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E157" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F157" s="5">
         <v>0</v>
@@ -5540,7 +5540,7 @@
         <v>0</v>
       </c>
       <c r="H157" s="6">
-        <v>500</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="158">
@@ -5551,66 +5551,66 @@
       </c>
       <c r="B158" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C158" s="4" t="inlineStr">
         <is>
-          <t>NX235/55R19</t>
+          <t>RD235/55R19</t>
         </is>
       </c>
       <c r="D158" s="5">
         <v>2</v>
       </c>
       <c r="E158" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F158" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G158" s="5">
         <v>0</v>
       </c>
       <c r="H158" s="6">
-        <v>600</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="159">
       <c r="A159" s="4" t="inlineStr">
         <is>
-          <t>235/55R19</t>
+          <t>235/60R16</t>
         </is>
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>RD235/55R19</t>
+          <t>HK235/60R16</t>
         </is>
       </c>
       <c r="D159" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E159" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F159" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G159" s="5">
         <v>0</v>
       </c>
       <c r="H159" s="6">
-        <v>500</v>
+        <v>430</v>
       </c>
     </row>
     <row outlineLevel="0" r="160">
       <c r="A160" s="4" t="inlineStr">
         <is>
-          <t>235/60R16</t>
+          <t>235/60R17</t>
         </is>
       </c>
       <c r="B160" s="4" t="inlineStr">
@@ -5620,55 +5620,55 @@
       </c>
       <c r="C160" s="4" t="inlineStr">
         <is>
-          <t>HK235/60R16</t>
+          <t>HK235/60R17</t>
         </is>
       </c>
       <c r="D160" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E160" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F160" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G160" s="5">
         <v>0</v>
       </c>
       <c r="H160" s="6">
-        <v>430</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="161">
       <c r="A161" s="4" t="inlineStr">
         <is>
-          <t>235/60R17</t>
+          <t>235/60R18</t>
         </is>
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>HK235/60R17</t>
+          <t>GD235/60R18</t>
         </is>
       </c>
       <c r="D161" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E161" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F161" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G161" s="5">
         <v>0</v>
       </c>
       <c r="H161" s="6">
-        <v>500</v>
+        <v>680</v>
       </c>
     </row>
     <row outlineLevel="0" r="162">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="B162" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C162" s="4" t="inlineStr">
         <is>
-          <t>GD235/60R18</t>
+          <t>HK235/60R18</t>
         </is>
       </c>
       <c r="D162" s="5">
@@ -5700,30 +5700,30 @@
         <v>0</v>
       </c>
       <c r="H162" s="6">
-        <v>680</v>
+        <v>480</v>
       </c>
     </row>
     <row outlineLevel="0" r="163">
       <c r="A163" s="4" t="inlineStr">
         <is>
-          <t>235/60R18</t>
+          <t>245/40R17</t>
         </is>
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>HK235/60R18</t>
+          <t>GD245/40R17</t>
         </is>
       </c>
       <c r="D163" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E163" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F163" s="5">
         <v>0</v>
@@ -5732,13 +5732,13 @@
         <v>0</v>
       </c>
       <c r="H163" s="6">
-        <v>480</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="164">
       <c r="A164" s="4" t="inlineStr">
         <is>
-          <t>245/40R17</t>
+          <t>245/40R18</t>
         </is>
       </c>
       <c r="B164" s="4" t="inlineStr">
@@ -5748,43 +5748,43 @@
       </c>
       <c r="C164" s="4" t="inlineStr">
         <is>
-          <t>GD245/40R17</t>
+          <t>GD245/40R18</t>
         </is>
       </c>
       <c r="D164" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E164" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F164" s="5">
         <v>0</v>
       </c>
       <c r="G164" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H164" s="6">
-        <v>400</v>
+        <v>620</v>
       </c>
     </row>
     <row outlineLevel="0" r="165">
       <c r="A165" s="4" t="inlineStr">
         <is>
-          <t>245/40R18</t>
+          <t>245/40R19</t>
         </is>
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>GD245/40R18</t>
+          <t>HK245/40R19</t>
         </is>
       </c>
       <c r="D165" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E165" s="5">
         <v>4</v>
@@ -5793,97 +5793,97 @@
         <v>0</v>
       </c>
       <c r="G165" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H165" s="6">
-        <v>620</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="166">
       <c r="A166" s="4" t="inlineStr">
         <is>
-          <t>245/40R19</t>
+          <t>245/40R20</t>
         </is>
       </c>
       <c r="B166" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C166" s="4" t="inlineStr">
         <is>
-          <t>HK245/40R19</t>
+          <t>CT245/40R20</t>
         </is>
       </c>
       <c r="D166" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E166" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F166" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G166" s="5">
         <v>0</v>
       </c>
       <c r="H166" s="6">
-        <v>750</v>
+        <v>1050</v>
       </c>
     </row>
     <row outlineLevel="0" r="167">
       <c r="A167" s="4" t="inlineStr">
         <is>
-          <t>245/40R20</t>
+          <t>245/45R17</t>
         </is>
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>CT245/40R20</t>
+          <t>HK245/45R17</t>
         </is>
       </c>
       <c r="D167" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E167" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F167" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G167" s="5">
         <v>0</v>
       </c>
       <c r="H167" s="6">
-        <v>1050</v>
+        <v>430</v>
       </c>
     </row>
     <row outlineLevel="0" r="168">
       <c r="A168" s="4" t="inlineStr">
         <is>
-          <t>245/45R17</t>
+          <t>245/45R18</t>
         </is>
       </c>
       <c r="B168" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C168" s="4" t="inlineStr">
         <is>
-          <t>HK245/45R17</t>
+          <t>CT245/45R18</t>
         </is>
       </c>
       <c r="D168" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E168" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F168" s="5">
         <v>0</v>
@@ -5892,7 +5892,7 @@
         <v>0</v>
       </c>
       <c r="H168" s="6">
-        <v>430</v>
+        <v>650</v>
       </c>
     </row>
     <row outlineLevel="0" r="169">
@@ -5903,19 +5903,19 @@
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>CT245/45R18</t>
+          <t>GD245/45R18</t>
         </is>
       </c>
       <c r="D169" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E169" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F169" s="5">
         <v>0</v>
@@ -5924,7 +5924,7 @@
         <v>0</v>
       </c>
       <c r="H169" s="6">
-        <v>650</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="170">
@@ -5935,19 +5935,19 @@
       </c>
       <c r="B170" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C170" s="4" t="inlineStr">
         <is>
-          <t>GD245/45R18</t>
+          <t>HK245/45R18</t>
         </is>
       </c>
       <c r="D170" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E170" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F170" s="5">
         <v>0</v>
@@ -5956,30 +5956,30 @@
         <v>0</v>
       </c>
       <c r="H170" s="6">
-        <v>600</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="171">
       <c r="A171" s="4" t="inlineStr">
         <is>
-          <t>245/45R18</t>
+          <t>245/45R18RF</t>
         </is>
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t>HK245/45R18</t>
+          <t>GD245/45R18RF</t>
         </is>
       </c>
       <c r="D171" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E171" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F171" s="5">
         <v>0</v>
@@ -5988,23 +5988,23 @@
         <v>0</v>
       </c>
       <c r="H171" s="6">
-        <v>500</v>
+        <v>720</v>
       </c>
     </row>
     <row outlineLevel="0" r="172">
       <c r="A172" s="4" t="inlineStr">
         <is>
-          <t>245/45R18RF</t>
+          <t>245/45R19</t>
         </is>
       </c>
       <c r="B172" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C172" s="4" t="inlineStr">
         <is>
-          <t>GD245/45R18RF</t>
+          <t>BR245/45R19</t>
         </is>
       </c>
       <c r="D172" s="5">
@@ -6020,7 +6020,7 @@
         <v>0</v>
       </c>
       <c r="H172" s="6">
-        <v>720</v>
+        <v>790</v>
       </c>
     </row>
     <row outlineLevel="0" r="173">
@@ -6031,44 +6031,44 @@
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>BR245/45R19</t>
+          <t>RD245/45R19</t>
         </is>
       </c>
       <c r="D173" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E173" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F173" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G173" s="5">
         <v>0</v>
       </c>
       <c r="H173" s="6">
-        <v>790</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="174">
       <c r="A174" s="4" t="inlineStr">
         <is>
-          <t>245/45R19</t>
+          <t>245/45R20</t>
         </is>
       </c>
       <c r="B174" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C174" s="4" t="inlineStr">
         <is>
-          <t>RD245/45R19</t>
+          <t>HK245/45R20</t>
         </is>
       </c>
       <c r="D174" s="5">
@@ -6084,59 +6084,59 @@
         <v>0</v>
       </c>
       <c r="H174" s="6">
-        <v>450</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="175">
       <c r="A175" s="4" t="inlineStr">
         <is>
-          <t>245/45R20</t>
+          <t>245/65R17</t>
         </is>
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>HK245/45R20</t>
+          <t>NX245/65R17</t>
         </is>
       </c>
       <c r="D175" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E175" s="5">
         <v>0</v>
       </c>
       <c r="F175" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G175" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H175" s="6">
-        <v>750</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="176">
       <c r="A176" s="4" t="inlineStr">
         <is>
-          <t>245/65R17</t>
+          <t>245/70R16</t>
         </is>
       </c>
       <c r="B176" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>LASSA</t>
         </is>
       </c>
       <c r="C176" s="4" t="inlineStr">
         <is>
-          <t>NX245/65R17</t>
+          <t>LS245/70R16</t>
         </is>
       </c>
       <c r="D176" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E176" s="5">
         <v>0</v>
@@ -6145,65 +6145,65 @@
         <v>0</v>
       </c>
       <c r="G176" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H176" s="6">
-        <v>600</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="177">
       <c r="A177" s="4" t="inlineStr">
         <is>
-          <t>245/70R16</t>
+          <t>255/35R19</t>
         </is>
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>LASSA</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>LS245/70R16</t>
+          <t>DL255/35R19</t>
         </is>
       </c>
       <c r="D177" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E177" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F177" s="5">
         <v>0</v>
       </c>
       <c r="G177" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H177" s="6">
-        <v>500</v>
+        <v>700</v>
       </c>
     </row>
     <row outlineLevel="0" r="178">
       <c r="A178" s="4" t="inlineStr">
         <is>
-          <t>255/35R19</t>
+          <t>255/35R19RF</t>
         </is>
       </c>
       <c r="B178" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C178" s="4" t="inlineStr">
         <is>
-          <t>DL255/35R19</t>
+          <t>CT255/35R19RF</t>
         </is>
       </c>
       <c r="D178" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E178" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F178" s="5">
         <v>0</v>
@@ -6212,7 +6212,7 @@
         <v>0</v>
       </c>
       <c r="H178" s="6">
-        <v>700</v>
+        <v>950</v>
       </c>
     </row>
     <row outlineLevel="0" r="179">
@@ -6223,19 +6223,19 @@
       </c>
       <c r="B179" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C179" s="4" t="inlineStr">
         <is>
-          <t>CT255/35R19RF</t>
+          <t>GD255/35R19RF</t>
         </is>
       </c>
       <c r="D179" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E179" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F179" s="5">
         <v>0</v>
@@ -6250,39 +6250,39 @@
     <row outlineLevel="0" r="180">
       <c r="A180" s="4" t="inlineStr">
         <is>
-          <t>255/35R19RF</t>
+          <t>255/50R19</t>
         </is>
       </c>
       <c r="B180" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C180" s="4" t="inlineStr">
         <is>
-          <t>GD255/35R19RF</t>
+          <t>CT255/50R19</t>
         </is>
       </c>
       <c r="D180" s="5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E180" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F180" s="5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G180" s="5">
         <v>0</v>
       </c>
       <c r="H180" s="6">
-        <v>950</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="181">
       <c r="A181" s="4" t="inlineStr">
         <is>
-          <t>255/50R19</t>
+          <t>255/50R20</t>
         </is>
       </c>
       <c r="B181" s="4" t="inlineStr">
@@ -6292,29 +6292,29 @@
       </c>
       <c r="C181" s="4" t="inlineStr">
         <is>
-          <t>CT255/50R19</t>
+          <t>CT255/50R20</t>
         </is>
       </c>
       <c r="D181" s="5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E181" s="5">
         <v>0</v>
       </c>
       <c r="F181" s="5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G181" s="5">
         <v>0</v>
       </c>
       <c r="H181" s="6">
-        <v>750</v>
+        <v>900</v>
       </c>
     </row>
     <row outlineLevel="0" r="182">
       <c r="A182" s="4" t="inlineStr">
         <is>
-          <t>255/50R20</t>
+          <t>255/55R19</t>
         </is>
       </c>
       <c r="B182" s="4" t="inlineStr">
@@ -6324,23 +6324,23 @@
       </c>
       <c r="C182" s="4" t="inlineStr">
         <is>
-          <t>CT255/50R20</t>
+          <t>CT255/55R19</t>
         </is>
       </c>
       <c r="D182" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E182" s="5">
         <v>0</v>
       </c>
       <c r="F182" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G182" s="5">
         <v>0</v>
       </c>
       <c r="H182" s="6">
-        <v>900</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="183">
@@ -6351,34 +6351,34 @@
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C183" s="4" t="inlineStr">
         <is>
-          <t>CT255/55R19</t>
+          <t>DL255/55R19</t>
         </is>
       </c>
       <c r="D183" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E183" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F183" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G183" s="5">
         <v>0</v>
       </c>
       <c r="H183" s="6">
-        <v>750</v>
+        <v>700</v>
       </c>
     </row>
     <row outlineLevel="0" r="184">
       <c r="A184" s="4" t="inlineStr">
         <is>
-          <t>255/55R19</t>
+          <t>255/70R15</t>
         </is>
       </c>
       <c r="B184" s="4" t="inlineStr">
@@ -6388,43 +6388,43 @@
       </c>
       <c r="C184" s="4" t="inlineStr">
         <is>
-          <t>DL255/55R19</t>
+          <t>DL255/70R15</t>
         </is>
       </c>
       <c r="D184" s="5">
         <v>2</v>
       </c>
       <c r="E184" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F184" s="5">
         <v>0</v>
       </c>
       <c r="G184" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H184" s="6">
-        <v>700</v>
+        <v>550</v>
       </c>
     </row>
     <row outlineLevel="0" r="185">
       <c r="A185" s="4" t="inlineStr">
         <is>
-          <t>255/70R15</t>
+          <t>255/70R16</t>
         </is>
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C185" s="4" t="inlineStr">
         <is>
-          <t>DL255/70R15</t>
+          <t>RD255/70R16</t>
         </is>
       </c>
       <c r="D185" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E185" s="5">
         <v>0</v>
@@ -6433,48 +6433,48 @@
         <v>0</v>
       </c>
       <c r="G185" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H185" s="6">
-        <v>550</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="186">
       <c r="A186" s="4" t="inlineStr">
         <is>
-          <t>255/70R16</t>
+          <t>265/35R18</t>
         </is>
       </c>
       <c r="B186" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C186" s="4" t="inlineStr">
         <is>
-          <t>RD255/70R16</t>
+          <t>GD265/35R18</t>
         </is>
       </c>
       <c r="D186" s="5">
         <v>1</v>
       </c>
       <c r="E186" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F186" s="5">
         <v>0</v>
       </c>
       <c r="G186" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H186" s="6">
-        <v>500</v>
+        <v>700</v>
       </c>
     </row>
     <row outlineLevel="0" r="187">
       <c r="A187" s="4" t="inlineStr">
         <is>
-          <t>265/35R18</t>
+          <t>265/50R20</t>
         </is>
       </c>
       <c r="B187" s="4" t="inlineStr">
@@ -6484,29 +6484,29 @@
       </c>
       <c r="C187" s="4" t="inlineStr">
         <is>
-          <t>GD265/35R18</t>
+          <t>GD265/50R20</t>
         </is>
       </c>
       <c r="D187" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E187" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F187" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G187" s="5">
         <v>0</v>
       </c>
       <c r="H187" s="6">
-        <v>700</v>
+        <v>1150</v>
       </c>
     </row>
     <row outlineLevel="0" r="188">
       <c r="A188" s="4" t="inlineStr">
         <is>
-          <t>265/50R20</t>
+          <t>275/35R19RF</t>
         </is>
       </c>
       <c r="B188" s="4" t="inlineStr">
@@ -6516,71 +6516,71 @@
       </c>
       <c r="C188" s="4" t="inlineStr">
         <is>
-          <t>GD265/50R20</t>
+          <t>GD275/35R19RF</t>
         </is>
       </c>
       <c r="D188" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E188" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F188" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G188" s="5">
         <v>0</v>
       </c>
       <c r="H188" s="6">
-        <v>1150</v>
+        <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="189">
       <c r="A189" s="4" t="inlineStr">
         <is>
-          <t>275/35R19RF</t>
+          <t>275/35R20</t>
         </is>
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C189" s="4" t="inlineStr">
         <is>
-          <t>GD275/35R19RF</t>
+          <t>CT275/35R20</t>
         </is>
       </c>
       <c r="D189" s="5">
         <v>2</v>
       </c>
       <c r="E189" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F189" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G189" s="5">
         <v>0</v>
       </c>
       <c r="H189" s="6">
-        <v>1</v>
+        <v>980</v>
       </c>
     </row>
     <row outlineLevel="0" r="190">
       <c r="A190" s="4" t="inlineStr">
         <is>
-          <t>275/35R20</t>
+          <t>275/40R20</t>
         </is>
       </c>
       <c r="B190" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C190" s="4" t="inlineStr">
         <is>
-          <t>CT275/35R20</t>
+          <t>HK275/40R20</t>
         </is>
       </c>
       <c r="D190" s="5">
@@ -6596,23 +6596,23 @@
         <v>0</v>
       </c>
       <c r="H190" s="6">
-        <v>980</v>
+        <v>770</v>
       </c>
     </row>
     <row outlineLevel="0" r="191">
       <c r="A191" s="4" t="inlineStr">
         <is>
-          <t>275/40R20</t>
+          <t>275/50R21</t>
         </is>
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C191" s="4" t="inlineStr">
         <is>
-          <t>HK275/40R20</t>
+          <t>GD275/50R21</t>
         </is>
       </c>
       <c r="D191" s="5">
@@ -6628,23 +6628,23 @@
         <v>0</v>
       </c>
       <c r="H191" s="6">
-        <v>770</v>
+        <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="192">
       <c r="A192" s="4" t="inlineStr">
         <is>
-          <t>275/50R21</t>
+          <t>295/35R21</t>
         </is>
       </c>
       <c r="B192" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C192" s="4" t="inlineStr">
         <is>
-          <t>GD275/50R21</t>
+          <t>CT295/35R21</t>
         </is>
       </c>
       <c r="D192" s="5">
@@ -6660,7 +6660,7 @@
         <v>0</v>
       </c>
       <c r="H192" s="6">
-        <v>1</v>
+        <v>1150</v>
       </c>
     </row>
     <row outlineLevel="0" r="193">
@@ -6671,91 +6671,59 @@
       </c>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C193" s="4" t="inlineStr">
         <is>
-          <t>CT295/35R21</t>
+          <t>GD295/35R21</t>
         </is>
       </c>
       <c r="D193" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E193" s="5">
         <v>0</v>
       </c>
       <c r="F193" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G193" s="5">
         <v>0</v>
       </c>
       <c r="H193" s="6">
-        <v>1150</v>
+        <v>980</v>
       </c>
     </row>
     <row outlineLevel="0" r="194">
       <c r="A194" s="4" t="inlineStr">
         <is>
-          <t>295/35R21</t>
+          <t>500R12</t>
         </is>
       </c>
       <c r="B194" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C194" s="4" t="inlineStr">
         <is>
-          <t>GD295/35R21</t>
+          <t>RD500R12</t>
         </is>
       </c>
       <c r="D194" s="5">
         <v>3</v>
       </c>
       <c r="E194" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F194" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G194" s="5">
         <v>0</v>
       </c>
       <c r="H194" s="6">
-        <v>980</v>
-      </c>
-    </row>
-    <row outlineLevel="0" r="195">
-      <c r="A195" s="4" t="inlineStr">
-        <is>
-          <t>500R12</t>
-        </is>
-      </c>
-      <c r="B195" s="4" t="inlineStr">
-        <is>
-          <t>RADIAL</t>
-        </is>
-      </c>
-      <c r="C195" s="4" t="inlineStr">
-        <is>
-          <t>RD500R12</t>
-        </is>
-      </c>
-      <c r="D195" s="5">
-        <v>3</v>
-      </c>
-      <c r="E195" s="5">
-        <v>3</v>
-      </c>
-      <c r="F195" s="5">
-        <v>0</v>
-      </c>
-      <c r="G195" s="5">
-        <v>0</v>
-      </c>
-      <c r="H195" s="6">
         <v>300</v>
       </c>
     </row>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -496,7 +496,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H194"/>
+  <dimension ref="A1:H191"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col customWidth="true" min="1" max="1" width="13.8359375"/>
@@ -760,16 +760,16 @@
         </is>
       </c>
       <c r="D8" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E8" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F8" s="5">
         <v>0</v>
       </c>
       <c r="G8" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" s="6">
         <v>180</v>
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="D10" s="5">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E10" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F10" s="5">
         <v>7</v>
@@ -891,10 +891,10 @@
         <v>25</v>
       </c>
       <c r="E12" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F12" s="5">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G12" s="5">
         <v>4</v>
@@ -984,7 +984,7 @@
         </is>
       </c>
       <c r="D15" s="5">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E15" s="5">
         <v>6</v>
@@ -993,7 +993,7 @@
         <v>92</v>
       </c>
       <c r="G15" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H15" s="6">
         <v>220</v>
@@ -1083,10 +1083,10 @@
         <v>69</v>
       </c>
       <c r="E18" s="5">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F18" s="5">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G18" s="5">
         <v>5</v>
@@ -1208,10 +1208,10 @@
         </is>
       </c>
       <c r="D22" s="5">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E22" s="5">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F22" s="5">
         <v>0</v>
@@ -1450,97 +1450,97 @@
     <row outlineLevel="0" r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>185/60R15</t>
+          <t>185/60R16</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>WESTLAKE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>WL185/60R15</t>
+          <t>GD185/60R16</t>
         </is>
       </c>
       <c r="D30" s="5">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E30" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F30" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G30" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H30" s="6">
-        <v>230</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>185/60R16</t>
+          <t>185/65R14</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>GD185/60R16</t>
+          <t>RD185/65R14</t>
         </is>
       </c>
       <c r="D31" s="5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E31" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F31" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G31" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H31" s="6">
-        <v>420</v>
+        <v>200</v>
       </c>
     </row>
     <row outlineLevel="0" r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>185/65R14</t>
+          <t>185/65R15</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>RD185/65R14</t>
+          <t>CT185/65R15</t>
         </is>
       </c>
       <c r="D32" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E32" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F32" s="5">
         <v>0</v>
       </c>
       <c r="G32" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H32" s="6">
-        <v>200</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="33">
@@ -1551,28 +1551,28 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>DOUBLESTAR</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>CT185/65R15</t>
+          <t>DS185/65R15</t>
         </is>
       </c>
       <c r="D33" s="5">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E33" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F33" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G33" s="5">
         <v>0</v>
       </c>
       <c r="H33" s="6">
-        <v>400</v>
+        <v>210</v>
       </c>
     </row>
     <row outlineLevel="0" r="34">
@@ -1583,28 +1583,28 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>DOUBLESTAR</t>
+          <t>FULDA</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>DS185/65R15</t>
+          <t>FL185/65R15</t>
         </is>
       </c>
       <c r="D34" s="5">
-        <v>7</v>
+        <v>136</v>
       </c>
       <c r="E34" s="5">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="F34" s="5">
-        <v>5</v>
+        <v>109</v>
       </c>
       <c r="G34" s="5">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="H34" s="6">
-        <v>210</v>
+        <v>245</v>
       </c>
     </row>
     <row outlineLevel="0" r="35">
@@ -1615,28 +1615,28 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>FULDA</t>
+          <t>GOODRIDE</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>FL185/65R15</t>
+          <t>GR185/65R15</t>
         </is>
       </c>
       <c r="D35" s="5">
-        <v>136</v>
+        <v>11</v>
       </c>
       <c r="E35" s="5">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="F35" s="5">
-        <v>109</v>
+        <v>3</v>
       </c>
       <c r="G35" s="5">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="H35" s="6">
-        <v>245</v>
+        <v>230</v>
       </c>
     </row>
     <row outlineLevel="0" r="36">
@@ -1647,28 +1647,28 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>GOODRIDE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>GR185/65R15</t>
+          <t>GD185/65R15</t>
         </is>
       </c>
       <c r="D36" s="5">
+        <v>64</v>
+      </c>
+      <c r="E36" s="5">
         <v>11</v>
       </c>
-      <c r="E36" s="5">
-        <v>4</v>
-      </c>
       <c r="F36" s="5">
-        <v>3</v>
+        <v>49</v>
       </c>
       <c r="G36" s="5">
         <v>4</v>
       </c>
       <c r="H36" s="6">
-        <v>230</v>
+        <v>260</v>
       </c>
     </row>
     <row outlineLevel="0" r="37">
@@ -1679,28 +1679,28 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>GD185/65R15</t>
+          <t>HK185/65R15</t>
         </is>
       </c>
       <c r="D37" s="5">
-        <v>64</v>
+        <v>5</v>
       </c>
       <c r="E37" s="5">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F37" s="5">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="G37" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H37" s="6">
-        <v>260</v>
+        <v>250</v>
       </c>
     </row>
     <row outlineLevel="0" r="38">
@@ -1711,16 +1711,16 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>HK185/65R15</t>
+          <t>LF185/65R15</t>
         </is>
       </c>
       <c r="D38" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E38" s="5">
         <v>4</v>
@@ -1729,7 +1729,7 @@
         <v>0</v>
       </c>
       <c r="G38" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H38" s="6">
         <v>250</v>
@@ -1743,28 +1743,28 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>LF185/65R15</t>
+          <t>RD185/65R15</t>
         </is>
       </c>
       <c r="D39" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E39" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F39" s="5">
         <v>0</v>
       </c>
       <c r="G39" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H39" s="6">
-        <v>250</v>
+        <v>200</v>
       </c>
     </row>
     <row outlineLevel="0" r="40">
@@ -1775,28 +1775,28 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>SEMPERIT</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>RD185/65R15</t>
+          <t>SP185/65R15</t>
         </is>
       </c>
       <c r="D40" s="5">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="E40" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F40" s="5">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G40" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H40" s="6">
-        <v>200</v>
+        <v>250</v>
       </c>
     </row>
     <row outlineLevel="0" r="41">
@@ -1807,60 +1807,60 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>SEMPERIT</t>
+          <t>WESTLAKE</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>SP185/65R15</t>
+          <t>WL185/65R15</t>
         </is>
       </c>
       <c r="D41" s="5">
-        <v>30</v>
+        <v>91</v>
       </c>
       <c r="E41" s="5">
-        <v>5</v>
+        <v>85</v>
       </c>
       <c r="F41" s="5">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="G41" s="5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H41" s="6">
-        <v>250</v>
+        <v>220</v>
       </c>
     </row>
     <row outlineLevel="0" r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>185/65R15</t>
+          <t>185/70R14</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>WESTLAKE</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>WL185/65R15</t>
+          <t>RD185/70R14</t>
         </is>
       </c>
       <c r="D42" s="5">
-        <v>94</v>
+        <v>2</v>
       </c>
       <c r="E42" s="5">
-        <v>86</v>
+        <v>1</v>
       </c>
       <c r="F42" s="5">
         <v>0</v>
       </c>
       <c r="G42" s="5">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H42" s="6">
-        <v>220</v>
+        <v>230</v>
       </c>
     </row>
     <row outlineLevel="0" r="43">
@@ -1871,60 +1871,60 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>WESTLAKE</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>RD185/70R14</t>
+          <t>WL185/70R14</t>
         </is>
       </c>
       <c r="D43" s="5">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E43" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F43" s="5">
         <v>0</v>
       </c>
       <c r="G43" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H43" s="6">
-        <v>230</v>
+        <v>220</v>
       </c>
     </row>
     <row outlineLevel="0" r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>185/70R14</t>
+          <t>195/50R15</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>WESTLAKE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>WL185/70R14</t>
+          <t>GD195/50R15</t>
         </is>
       </c>
       <c r="D44" s="5">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E44" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F44" s="5">
         <v>0</v>
       </c>
       <c r="G44" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H44" s="6">
-        <v>220</v>
+        <v>290</v>
       </c>
     </row>
     <row outlineLevel="0" r="45">
@@ -1935,28 +1935,28 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>SEMPERIT</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>GD195/50R15</t>
+          <t>SP195/50R15</t>
         </is>
       </c>
       <c r="D45" s="5">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="E45" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F45" s="5">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G45" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H45" s="6">
-        <v>290</v>
+        <v>260</v>
       </c>
     </row>
     <row outlineLevel="0" r="46">
@@ -1967,66 +1967,66 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>SEMPERIT</t>
+          <t>WESTLAKE</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>SP195/50R15</t>
+          <t>WL195/50R15</t>
         </is>
       </c>
       <c r="D46" s="5">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="E46" s="5">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F46" s="5">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G46" s="5">
         <v>4</v>
       </c>
       <c r="H46" s="6">
-        <v>260</v>
+        <v>225</v>
       </c>
     </row>
     <row outlineLevel="0" r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>195/50R15</t>
+          <t>195/50R16</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>WESTLAKE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>WL195/50R15</t>
+          <t>GD195/50R16</t>
         </is>
       </c>
       <c r="D47" s="5">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E47" s="5">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F47" s="5">
         <v>0</v>
       </c>
       <c r="G47" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H47" s="6">
-        <v>225</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>195/50R16</t>
+          <t>195/55R16</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
@@ -2036,23 +2036,23 @@
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>GD195/50R16</t>
+          <t>GD195/55R16</t>
         </is>
       </c>
       <c r="D48" s="5">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E48" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F48" s="5">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G48" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H48" s="6">
-        <v>330</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="49">
@@ -2063,28 +2063,28 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>GD195/55R16</t>
+          <t>HK195/55R16</t>
         </is>
       </c>
       <c r="D49" s="5">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E49" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F49" s="5">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G49" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H49" s="6">
-        <v>350</v>
+        <v>290</v>
       </c>
     </row>
     <row outlineLevel="0" r="50">
@@ -2095,28 +2095,28 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>LASSA</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>HK195/55R16</t>
+          <t>LS195/55R16</t>
         </is>
       </c>
       <c r="D50" s="5">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="E50" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F50" s="5">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G50" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H50" s="6">
-        <v>290</v>
+        <v>280</v>
       </c>
     </row>
     <row outlineLevel="0" r="51">
@@ -2127,19 +2127,19 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>LASSA</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>LS195/55R16</t>
+          <t>NX195/55R16</t>
         </is>
       </c>
       <c r="D51" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E51" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F51" s="5">
         <v>0</v>
@@ -2148,7 +2148,7 @@
         <v>0</v>
       </c>
       <c r="H51" s="6">
-        <v>280</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="52">
@@ -2159,92 +2159,92 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>NX195/55R16</t>
+          <t>RD195/55R16</t>
         </is>
       </c>
       <c r="D52" s="5">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E52" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F52" s="5">
         <v>0</v>
       </c>
       <c r="G52" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H52" s="6">
-        <v>300</v>
+        <v>250</v>
       </c>
     </row>
     <row outlineLevel="0" r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>195/55R16</t>
+          <t>195/60R16</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>RD195/55R16</t>
+          <t>GD195/60R16</t>
         </is>
       </c>
       <c r="D53" s="5">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="E53" s="5">
         <v>4</v>
       </c>
       <c r="F53" s="5">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G53" s="5">
         <v>3</v>
       </c>
       <c r="H53" s="6">
-        <v>250</v>
+        <v>355</v>
       </c>
     </row>
     <row outlineLevel="0" r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>195/60R16</t>
+          <t>195/65R15</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>DOUBLESTAR</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>GD195/60R16</t>
+          <t>DS195/65R15</t>
         </is>
       </c>
       <c r="D54" s="5">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="E54" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F54" s="5">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="G54" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H54" s="6">
-        <v>355</v>
+        <v>230</v>
       </c>
     </row>
     <row outlineLevel="0" r="55">
@@ -2255,22 +2255,22 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>DOUBLESTAR</t>
+          <t>GOODRIDE</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>DS195/65R15</t>
+          <t>GR195/65R15</t>
         </is>
       </c>
       <c r="D55" s="5">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E55" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F55" s="5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G55" s="5">
         <v>0</v>
@@ -2287,28 +2287,28 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>GOODRIDE</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>GR195/65R15</t>
+          <t>HK195/65R15</t>
         </is>
       </c>
       <c r="D56" s="5">
         <v>4</v>
       </c>
       <c r="E56" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F56" s="5">
         <v>0</v>
       </c>
       <c r="G56" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H56" s="6">
-        <v>230</v>
+        <v>260</v>
       </c>
     </row>
     <row outlineLevel="0" r="57">
@@ -2319,28 +2319,28 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>LASSA</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>HK195/65R15</t>
+          <t>LS195/65R15</t>
         </is>
       </c>
       <c r="D57" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E57" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F57" s="5">
         <v>0</v>
       </c>
       <c r="G57" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H57" s="6">
-        <v>260</v>
+        <v>250</v>
       </c>
     </row>
     <row outlineLevel="0" r="58">
@@ -2351,19 +2351,19 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>LASSA</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>LS195/65R15</t>
+          <t>NX195/65R15</t>
         </is>
       </c>
       <c r="D58" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E58" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F58" s="5">
         <v>0</v>
@@ -2372,7 +2372,7 @@
         <v>0</v>
       </c>
       <c r="H58" s="6">
-        <v>250</v>
+        <v>230</v>
       </c>
     </row>
     <row outlineLevel="0" r="59">
@@ -2383,25 +2383,25 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>NX195/65R15</t>
+          <t>RD195/65R15</t>
         </is>
       </c>
       <c r="D59" s="5">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E59" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F59" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G59" s="5">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H59" s="6">
         <v>230</v>
@@ -2415,124 +2415,124 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>SEMPERIT</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>RD195/65R15</t>
+          <t>SP195/65R15</t>
         </is>
       </c>
       <c r="D60" s="5">
-        <v>15</v>
+        <v>96</v>
       </c>
       <c r="E60" s="5">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F60" s="5">
-        <v>1</v>
+        <v>73</v>
       </c>
       <c r="G60" s="5">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="H60" s="6">
-        <v>230</v>
+        <v>250</v>
       </c>
     </row>
     <row outlineLevel="0" r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>195/65R15</t>
+          <t>195/70R15C</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>SEMPERIT</t>
+          <t>DAYTON</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>SP195/65R15</t>
+          <t>DT195/70R15C</t>
         </is>
       </c>
       <c r="D61" s="5">
-        <v>96</v>
+        <v>2</v>
       </c>
       <c r="E61" s="5">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F61" s="5">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="G61" s="5">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H61" s="6">
-        <v>250</v>
+        <v>280</v>
       </c>
     </row>
     <row outlineLevel="0" r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>195/70R15C</t>
+          <t>195/75R16C</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>DAYTON</t>
+          <t>GOODRIDE</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>DT195/70R15C</t>
+          <t>GR195/75R16C</t>
         </is>
       </c>
       <c r="D62" s="5">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E62" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F62" s="5">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G62" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H62" s="6">
-        <v>280</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>195/75R16C</t>
+          <t>205/45R17</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>GOODRIDE</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>GR195/75R16C</t>
+          <t>CT205/45R17</t>
         </is>
       </c>
       <c r="D63" s="5">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E63" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F63" s="5">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G63" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H63" s="6">
-        <v>350</v>
+        <v>550</v>
       </c>
     </row>
     <row outlineLevel="0" r="64">
@@ -2543,28 +2543,28 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>FULDA</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>CT205/45R17</t>
+          <t>FL205/45R17</t>
         </is>
       </c>
       <c r="D64" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E64" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F64" s="5">
         <v>0</v>
       </c>
       <c r="G64" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H64" s="6">
-        <v>550</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="65">
@@ -2575,28 +2575,28 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>FULDA</t>
+          <t>GOODRIDE</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>FL205/45R17</t>
+          <t>GR205/45R17</t>
         </is>
       </c>
       <c r="D65" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E65" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F65" s="5">
         <v>0</v>
       </c>
       <c r="G65" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H65" s="6">
-        <v>380</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="66">
@@ -2607,28 +2607,28 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>GOODRIDE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>GR205/45R17</t>
+          <t>GD205/45R17</t>
         </is>
       </c>
       <c r="D66" s="5">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="E66" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F66" s="5">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G66" s="5">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H66" s="6">
-        <v>300</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="67">
@@ -2639,28 +2639,28 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>GD205/45R17</t>
+          <t>NX205/45R17</t>
         </is>
       </c>
       <c r="D67" s="5">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="E67" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F67" s="5">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G67" s="5">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H67" s="6">
-        <v>450</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="68">
@@ -2671,83 +2671,83 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>NX205/45R17</t>
+          <t>RD205/45R17</t>
         </is>
       </c>
       <c r="D68" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E68" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F68" s="5">
         <v>0</v>
       </c>
       <c r="G68" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H68" s="6">
-        <v>380</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>205/45R17</t>
+          <t>205/50R17</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>RD205/45R17</t>
+          <t>CT205/50R17</t>
         </is>
       </c>
       <c r="D69" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E69" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F69" s="5">
         <v>0</v>
       </c>
       <c r="G69" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H69" s="6">
-        <v>300</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>205/50R17</t>
+          <t>205/55R16</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>AMINE</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>CT205/50R17</t>
+          <t>AM205/55R16</t>
         </is>
       </c>
       <c r="D70" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E70" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F70" s="5">
         <v>0</v>
@@ -2756,7 +2756,7 @@
         <v>0</v>
       </c>
       <c r="H70" s="6">
-        <v>450</v>
+        <v>240</v>
       </c>
     </row>
     <row outlineLevel="0" r="71">
@@ -2767,19 +2767,19 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>AMINE</t>
+          <t>DOUBLESTAR</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>AM205/55R16</t>
+          <t>DS205/55R16</t>
         </is>
       </c>
       <c r="D71" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E71" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F71" s="5">
         <v>0</v>
@@ -2788,7 +2788,7 @@
         <v>0</v>
       </c>
       <c r="H71" s="6">
-        <v>240</v>
+        <v>230</v>
       </c>
     </row>
     <row outlineLevel="0" r="72">
@@ -2799,28 +2799,28 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>DOUBLESTAR</t>
+          <t>FULDA</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>DS205/55R16</t>
+          <t>FL205/55R16</t>
         </is>
       </c>
       <c r="D72" s="5">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="E72" s="5">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F72" s="5">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G72" s="5">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H72" s="6">
-        <v>230</v>
+        <v>250</v>
       </c>
     </row>
     <row outlineLevel="0" r="73">
@@ -2831,25 +2831,25 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>FULDA</t>
+          <t>GOODRIDE</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>FL205/55R16</t>
+          <t>GR205/55R16</t>
         </is>
       </c>
       <c r="D73" s="5">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="E73" s="5">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F73" s="5">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="G73" s="5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H73" s="6">
         <v>250</v>
@@ -2863,28 +2863,28 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>GOODRIDE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>GR205/55R16</t>
+          <t>GD205/55R16</t>
         </is>
       </c>
       <c r="D74" s="5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E74" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F74" s="5">
         <v>0</v>
       </c>
       <c r="G74" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H74" s="6">
-        <v>250</v>
+        <v>280</v>
       </c>
     </row>
     <row outlineLevel="0" r="75">
@@ -2895,28 +2895,28 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>GD205/55R16</t>
+          <t>HK205/55R16</t>
         </is>
       </c>
       <c r="D75" s="5">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E75" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F75" s="5">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G75" s="5">
         <v>4</v>
       </c>
       <c r="H75" s="6">
-        <v>280</v>
+        <v>260</v>
       </c>
     </row>
     <row outlineLevel="0" r="76">
@@ -2927,48 +2927,48 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>HK205/55R16</t>
+          <t>RD205/55R16</t>
         </is>
       </c>
       <c r="D76" s="5">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="E76" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F76" s="5">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G76" s="5">
         <v>4</v>
       </c>
       <c r="H76" s="6">
-        <v>260</v>
+        <v>230</v>
       </c>
     </row>
     <row outlineLevel="0" r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>205/55R16</t>
+          <t>205/55R16RF</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>RD205/55R16</t>
+          <t>GD205/55R16RF</t>
         </is>
       </c>
       <c r="D77" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E77" s="5">
         <v>0</v>
@@ -2977,16 +2977,16 @@
         <v>0</v>
       </c>
       <c r="G77" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H77" s="6">
-        <v>230</v>
+        <v>480</v>
       </c>
     </row>
     <row outlineLevel="0" r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>205/55R16RF</t>
+          <t>205/55R17</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
@@ -2996,23 +2996,23 @@
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>GD205/55R16RF</t>
+          <t>GD205/55R17</t>
         </is>
       </c>
       <c r="D78" s="5">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="E78" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F78" s="5">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G78" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H78" s="6">
-        <v>480</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="79">
@@ -3023,44 +3023,44 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>GD205/55R17</t>
+          <t>NX205/55R17</t>
         </is>
       </c>
       <c r="D79" s="5">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="E79" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F79" s="5">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G79" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H79" s="6">
-        <v>450</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>205/55R17</t>
+          <t>205/60R16</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>NX205/55R17</t>
+          <t>DL205/60R16</t>
         </is>
       </c>
       <c r="D80" s="5">
@@ -3076,7 +3076,7 @@
         <v>0</v>
       </c>
       <c r="H80" s="6">
-        <v>400</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="81">
@@ -3087,28 +3087,28 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>DL205/60R16</t>
+          <t>GD205/60R16</t>
         </is>
       </c>
       <c r="D81" s="5">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="E81" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F81" s="5">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G81" s="5">
         <v>0</v>
       </c>
       <c r="H81" s="6">
-        <v>330</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="82">
@@ -3119,28 +3119,28 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>GD205/60R16</t>
+          <t>HK205/60R16</t>
         </is>
       </c>
       <c r="D82" s="5">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E82" s="5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F82" s="5">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="G82" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H82" s="6">
-        <v>380</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="83">
@@ -3151,25 +3151,25 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>HK205/60R16</t>
+          <t>LF205/60R16</t>
         </is>
       </c>
       <c r="D83" s="5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E83" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F83" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G83" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H83" s="6">
         <v>300</v>
@@ -3178,17 +3178,17 @@
     <row outlineLevel="0" r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>205/60R16</t>
+          <t>205/65R15</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>LF205/60R16</t>
+          <t>HK205/65R15</t>
         </is>
       </c>
       <c r="D84" s="5">
@@ -3204,30 +3204,30 @@
         <v>0</v>
       </c>
       <c r="H84" s="6">
-        <v>300</v>
+        <v>270</v>
       </c>
     </row>
     <row outlineLevel="0" r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>205/65R15</t>
+          <t>205/65R16</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>HK205/65R15</t>
+          <t>BR205/65R16</t>
         </is>
       </c>
       <c r="D85" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E85" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F85" s="5">
         <v>0</v>
@@ -3236,7 +3236,7 @@
         <v>0</v>
       </c>
       <c r="H85" s="6">
-        <v>270</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="86">
@@ -3247,19 +3247,19 @@
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>BR205/65R16</t>
+          <t>HK205/65R16</t>
         </is>
       </c>
       <c r="D86" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E86" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F86" s="5">
         <v>0</v>
@@ -3268,39 +3268,39 @@
         <v>0</v>
       </c>
       <c r="H86" s="6">
-        <v>420</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>205/65R16</t>
+          <t>215/40R18</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>HK205/65R16</t>
+          <t>GD215/40R18</t>
         </is>
       </c>
       <c r="D87" s="5">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E87" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F87" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G87" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H87" s="6">
-        <v>380</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="88">
@@ -3311,44 +3311,44 @@
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>GD215/40R18</t>
+          <t>HK215/40R18</t>
         </is>
       </c>
       <c r="D88" s="5">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E88" s="5">
         <v>4</v>
       </c>
       <c r="F88" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G88" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H88" s="6">
-        <v>600</v>
+        <v>490</v>
       </c>
     </row>
     <row outlineLevel="0" r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>215/40R18</t>
+          <t>215/45R16</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>HK215/40R18</t>
+          <t>GD215/45R16</t>
         </is>
       </c>
       <c r="D89" s="5">
@@ -3364,13 +3364,13 @@
         <v>0</v>
       </c>
       <c r="H89" s="6">
-        <v>490</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>215/45R16</t>
+          <t>215/45R17</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
@@ -3380,14 +3380,14 @@
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>GD215/45R16</t>
+          <t>GD215/45R17</t>
         </is>
       </c>
       <c r="D90" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E90" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F90" s="5">
         <v>0</v>
@@ -3396,7 +3396,7 @@
         <v>0</v>
       </c>
       <c r="H90" s="6">
-        <v>450</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="91">
@@ -3407,25 +3407,25 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>GD215/45R17</t>
+          <t>HK215/45R17</t>
         </is>
       </c>
       <c r="D91" s="5">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="E91" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F91" s="5">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G91" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H91" s="6">
         <v>400</v>
@@ -3439,28 +3439,28 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>IRIS</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>HK215/45R17</t>
+          <t>IR215/45R17</t>
         </is>
       </c>
       <c r="D92" s="5">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="E92" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F92" s="5">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G92" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H92" s="6">
-        <v>400</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="93">
@@ -3471,28 +3471,28 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>IRIS</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>IR215/45R17</t>
+          <t>LF215/45R17</t>
         </is>
       </c>
       <c r="D93" s="5">
         <v>1</v>
       </c>
       <c r="E93" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F93" s="5">
         <v>0</v>
       </c>
       <c r="G93" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H93" s="6">
-        <v>300</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="94">
@@ -3503,83 +3503,83 @@
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>LF215/45R17</t>
+          <t>NX215/45R17</t>
         </is>
       </c>
       <c r="D94" s="5">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E94" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F94" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G94" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H94" s="6">
-        <v>350</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>215/45R17</t>
+          <t>215/45R18</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>NX215/45R17</t>
+          <t>GD215/45R18</t>
         </is>
       </c>
       <c r="D95" s="5">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E95" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F95" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G95" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H95" s="6">
-        <v>380</v>
+        <v>550</v>
       </c>
     </row>
     <row outlineLevel="0" r="96">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>215/45R18</t>
+          <t>215/50R17</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>GD215/45R18</t>
+          <t>BR215/50R17</t>
         </is>
       </c>
       <c r="D96" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E96" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F96" s="5">
         <v>0</v>
@@ -3588,7 +3588,7 @@
         <v>0</v>
       </c>
       <c r="H96" s="6">
-        <v>550</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="97">
@@ -3599,28 +3599,28 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>BR215/50R17</t>
+          <t>GD215/50R17</t>
         </is>
       </c>
       <c r="D97" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E97" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F97" s="5">
         <v>0</v>
       </c>
       <c r="G97" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H97" s="6">
-        <v>450</v>
+        <v>470</v>
       </c>
     </row>
     <row outlineLevel="0" r="98">
@@ -3631,28 +3631,28 @@
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>GD215/50R17</t>
+          <t>HK215/50R17</t>
         </is>
       </c>
       <c r="D98" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E98" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F98" s="5">
         <v>0</v>
       </c>
       <c r="G98" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H98" s="6">
-        <v>470</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="99">
@@ -3663,19 +3663,19 @@
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>HK215/50R17</t>
+          <t>LF215/50R17</t>
         </is>
       </c>
       <c r="D99" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E99" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F99" s="5">
         <v>0</v>
@@ -3684,30 +3684,30 @@
         <v>0</v>
       </c>
       <c r="H99" s="6">
-        <v>400</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="100">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>215/50R17</t>
+          <t>215/50R18</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>LF215/50R17</t>
+          <t>GD215/50R18</t>
         </is>
       </c>
       <c r="D100" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E100" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F100" s="5">
         <v>0</v>
@@ -3716,13 +3716,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="6">
-        <v>420</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>215/50R18</t>
+          <t>215/55R16</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
@@ -3732,14 +3732,14 @@
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>GD215/50R18</t>
+          <t>GD215/55R16</t>
         </is>
       </c>
       <c r="D101" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E101" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F101" s="5">
         <v>0</v>
@@ -3748,7 +3748,7 @@
         <v>0</v>
       </c>
       <c r="H101" s="6">
-        <v>600</v>
+        <v>440</v>
       </c>
     </row>
     <row outlineLevel="0" r="102">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>GD215/55R16</t>
+          <t>LF215/55R16</t>
         </is>
       </c>
       <c r="D102" s="5">
@@ -3780,23 +3780,23 @@
         <v>0</v>
       </c>
       <c r="H102" s="6">
-        <v>440</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>215/55R16</t>
+          <t>215/55R17</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>LF215/55R16</t>
+          <t>BR215/55R17</t>
         </is>
       </c>
       <c r="D103" s="5">
@@ -3812,7 +3812,7 @@
         <v>0</v>
       </c>
       <c r="H103" s="6">
-        <v>350</v>
+        <v>480</v>
       </c>
     </row>
     <row outlineLevel="0" r="104">
@@ -3823,19 +3823,19 @@
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>BR215/55R17</t>
+          <t>HK215/55R17</t>
         </is>
       </c>
       <c r="D104" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E104" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F104" s="5">
         <v>0</v>
@@ -3844,23 +3844,23 @@
         <v>0</v>
       </c>
       <c r="H104" s="6">
-        <v>480</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>215/55R17</t>
+          <t>215/55R18</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>HK215/55R17</t>
+          <t>GD215/55R18</t>
         </is>
       </c>
       <c r="D105" s="5">
@@ -3876,23 +3876,23 @@
         <v>0</v>
       </c>
       <c r="H105" s="6">
-        <v>420</v>
+        <v>580</v>
       </c>
     </row>
     <row outlineLevel="0" r="106">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>215/55R18</t>
+          <t>215/60R16</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>GD215/55R18</t>
+          <t>BR215/60R16</t>
         </is>
       </c>
       <c r="D106" s="5">
@@ -3908,7 +3908,7 @@
         <v>0</v>
       </c>
       <c r="H106" s="6">
-        <v>580</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="107">
@@ -3919,25 +3919,25 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>BR215/60R16</t>
+          <t>DL215/60R16</t>
         </is>
       </c>
       <c r="D107" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E107" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F107" s="5">
         <v>0</v>
       </c>
       <c r="G107" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H107" s="6">
         <v>350</v>
@@ -3951,28 +3951,28 @@
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>DL215/60R16</t>
+          <t>HK215/60R16</t>
         </is>
       </c>
       <c r="D108" s="5">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E108" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F108" s="5">
         <v>0</v>
       </c>
       <c r="G108" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H108" s="6">
-        <v>350</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="109">
@@ -3983,25 +3983,25 @@
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>HK215/60R16</t>
+          <t>NX215/60R16</t>
         </is>
       </c>
       <c r="D109" s="5">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E109" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F109" s="5">
         <v>0</v>
       </c>
       <c r="G109" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H109" s="6">
         <v>330</v>
@@ -4010,65 +4010,65 @@
     <row outlineLevel="0" r="110">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>215/60R16</t>
+          <t>215/60R17</t>
         </is>
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>NX215/60R16</t>
+          <t>RD215/60R17</t>
         </is>
       </c>
       <c r="D110" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E110" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F110" s="5">
         <v>0</v>
       </c>
       <c r="G110" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H110" s="6">
-        <v>330</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="111">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>215/60R17</t>
+          <t>215/65R16</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>RD215/60R17</t>
+          <t>GD215/65R16</t>
         </is>
       </c>
       <c r="D111" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E111" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F111" s="5">
         <v>0</v>
       </c>
       <c r="G111" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H111" s="6">
-        <v>300</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="112">
@@ -4079,76 +4079,76 @@
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>GD215/65R16</t>
+          <t>HK215/65R16</t>
         </is>
       </c>
       <c r="D112" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E112" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F112" s="5">
         <v>0</v>
       </c>
       <c r="G112" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H112" s="6">
-        <v>380</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="113">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>215/65R16</t>
+          <t>215/65R17</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>MICHELIN</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>HK215/65R16</t>
+          <t>MC215/65R17</t>
         </is>
       </c>
       <c r="D113" s="5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E113" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F113" s="5">
         <v>0</v>
       </c>
       <c r="G113" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H113" s="6">
-        <v>330</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="114">
       <c r="A114" s="4" t="inlineStr">
         <is>
-          <t>215/65R17</t>
+          <t>225/40R18</t>
         </is>
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>MICHELIN</t>
+          <t>BARUM</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>MC215/65R17</t>
+          <t>BM225/40R18</t>
         </is>
       </c>
       <c r="D114" s="5">
@@ -4164,7 +4164,7 @@
         <v>0</v>
       </c>
       <c r="H114" s="6">
-        <v>600</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="115">
@@ -4175,28 +4175,28 @@
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>BARUM</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>BM225/40R18</t>
+          <t>GD225/40R18</t>
         </is>
       </c>
       <c r="D115" s="5">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="E115" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F115" s="5">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G115" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H115" s="6">
-        <v>420</v>
+        <v>480</v>
       </c>
     </row>
     <row outlineLevel="0" r="116">
@@ -4207,28 +4207,28 @@
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>GD225/40R18</t>
+          <t>HK225/40R18</t>
         </is>
       </c>
       <c r="D116" s="5">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="E116" s="5">
         <v>4</v>
       </c>
       <c r="F116" s="5">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G116" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H116" s="6">
-        <v>480</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="117">
@@ -4239,28 +4239,28 @@
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>LASSA</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>HK225/40R18</t>
+          <t>LS225/40R18</t>
         </is>
       </c>
       <c r="D117" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E117" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F117" s="5">
         <v>0</v>
       </c>
       <c r="G117" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H117" s="6">
-        <v>450</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="118">
@@ -4271,28 +4271,28 @@
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>LASSA</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>LS225/40R18</t>
+          <t>NX225/40R18</t>
         </is>
       </c>
       <c r="D118" s="5">
         <v>1</v>
       </c>
       <c r="E118" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F118" s="5">
         <v>0</v>
       </c>
       <c r="G118" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H118" s="6">
-        <v>330</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="119">
@@ -4303,19 +4303,19 @@
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>SEMPERIT</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>NX225/40R18</t>
+          <t>SP225/40R18</t>
         </is>
       </c>
       <c r="D119" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E119" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F119" s="5">
         <v>0</v>
@@ -4324,30 +4324,30 @@
         <v>0</v>
       </c>
       <c r="H119" s="6">
-        <v>400</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="120">
       <c r="A120" s="4" t="inlineStr">
         <is>
-          <t>225/40R18</t>
+          <t>225/40R18RF</t>
         </is>
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>SEMPERIT</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>SP225/40R18</t>
+          <t>GD225/40R18RF</t>
         </is>
       </c>
       <c r="D120" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E120" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F120" s="5">
         <v>0</v>
@@ -4356,30 +4356,30 @@
         <v>0</v>
       </c>
       <c r="H120" s="6">
-        <v>450</v>
+        <v>590</v>
       </c>
     </row>
     <row outlineLevel="0" r="121">
       <c r="A121" s="4" t="inlineStr">
         <is>
-          <t>225/40R18RF</t>
+          <t>225/45R17</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>GD225/40R18RF</t>
+          <t>CT225/45R17</t>
         </is>
       </c>
       <c r="D121" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E121" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F121" s="5">
         <v>0</v>
@@ -4388,7 +4388,7 @@
         <v>0</v>
       </c>
       <c r="H121" s="6">
-        <v>590</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="122">
@@ -4399,28 +4399,28 @@
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>FULDA</t>
         </is>
       </c>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>CT225/45R17</t>
+          <t>FL225/45R17</t>
         </is>
       </c>
       <c r="D122" s="5">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="E122" s="5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F122" s="5">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G122" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H122" s="6">
-        <v>400</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="123">
@@ -4431,28 +4431,28 @@
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>FULDA</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>FL225/45R17</t>
+          <t>GD225/45R17</t>
         </is>
       </c>
       <c r="D123" s="5">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E123" s="5">
         <v>6</v>
       </c>
       <c r="F123" s="5">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G123" s="5">
         <v>4</v>
       </c>
       <c r="H123" s="6">
-        <v>350</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="124">
@@ -4463,60 +4463,60 @@
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>GD225/45R17</t>
+          <t>HK225/45R17</t>
         </is>
       </c>
       <c r="D124" s="5">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="E124" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F124" s="5">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="G124" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H124" s="6">
-        <v>380</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="125">
       <c r="A125" s="4" t="inlineStr">
         <is>
-          <t>225/45R17</t>
+          <t>225/45R18</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>HK225/45R17</t>
+          <t>DL225/45R18</t>
         </is>
       </c>
       <c r="D125" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E125" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F125" s="5">
         <v>0</v>
       </c>
       <c r="G125" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H125" s="6">
-        <v>350</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="126">
@@ -4527,28 +4527,28 @@
       </c>
       <c r="B126" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C126" s="4" t="inlineStr">
         <is>
-          <t>DL225/45R18</t>
+          <t>GD225/45R18</t>
         </is>
       </c>
       <c r="D126" s="5">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E126" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F126" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G126" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H126" s="6">
-        <v>500</v>
+        <v>550</v>
       </c>
     </row>
     <row outlineLevel="0" r="127">
@@ -4559,83 +4559,83 @@
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>GD225/45R18</t>
+          <t>LF225/45R18</t>
         </is>
       </c>
       <c r="D127" s="5">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E127" s="5">
         <v>4</v>
       </c>
       <c r="F127" s="5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G127" s="5">
         <v>0</v>
       </c>
       <c r="H127" s="6">
-        <v>550</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="128">
       <c r="A128" s="4" t="inlineStr">
         <is>
-          <t>225/45R18</t>
+          <t>225/45R18RF</t>
         </is>
       </c>
       <c r="B128" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C128" s="4" t="inlineStr">
         <is>
-          <t>HK225/45R18</t>
+          <t>GD225/45R18RF</t>
         </is>
       </c>
       <c r="D128" s="5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E128" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F128" s="5">
         <v>0</v>
       </c>
       <c r="G128" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H128" s="6">
-        <v>450</v>
+        <v>720</v>
       </c>
     </row>
     <row outlineLevel="0" r="129">
       <c r="A129" s="4" t="inlineStr">
         <is>
-          <t>225/45R18</t>
+          <t>225/45R19</t>
         </is>
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>LF225/45R18</t>
+          <t>CT225/45R19</t>
         </is>
       </c>
       <c r="D129" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E129" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F129" s="5">
         <v>0</v>
@@ -4644,13 +4644,13 @@
         <v>0</v>
       </c>
       <c r="H129" s="6">
-        <v>420</v>
+        <v>780</v>
       </c>
     </row>
     <row outlineLevel="0" r="130">
       <c r="A130" s="4" t="inlineStr">
         <is>
-          <t>225/45R18RF</t>
+          <t>225/50R17</t>
         </is>
       </c>
       <c r="B130" s="4" t="inlineStr">
@@ -4660,142 +4660,142 @@
       </c>
       <c r="C130" s="4" t="inlineStr">
         <is>
-          <t>GD225/45R18RF</t>
+          <t>GD225/50R17</t>
         </is>
       </c>
       <c r="D130" s="5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E130" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F130" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G130" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H130" s="6">
-        <v>720</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="131">
       <c r="A131" s="4" t="inlineStr">
         <is>
-          <t>225/45R19</t>
+          <t>225/50R17</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>CT225/45R19</t>
+          <t>HK225/50R17</t>
         </is>
       </c>
       <c r="D131" s="5">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E131" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F131" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G131" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H131" s="6">
-        <v>780</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="132">
       <c r="A132" s="4" t="inlineStr">
         <is>
-          <t>225/50R17</t>
+          <t>225/55R16</t>
         </is>
       </c>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C132" s="4" t="inlineStr">
         <is>
-          <t>GD225/50R17</t>
+          <t>DL225/55R16</t>
         </is>
       </c>
       <c r="D132" s="5">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E132" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F132" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G132" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H132" s="6">
-        <v>500</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="133">
       <c r="A133" s="4" t="inlineStr">
         <is>
-          <t>225/50R17</t>
+          <t>225/55R16</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>HK225/50R17</t>
+          <t>GD225/55R16</t>
         </is>
       </c>
       <c r="D133" s="5">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E133" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F133" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G133" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H133" s="6">
-        <v>400</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="134">
       <c r="A134" s="4" t="inlineStr">
         <is>
-          <t>225/55R16</t>
+          <t>225/55R17</t>
         </is>
       </c>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C134" s="4" t="inlineStr">
         <is>
-          <t>DL225/55R16</t>
+          <t>HK225/55R17</t>
         </is>
       </c>
       <c r="D134" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E134" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F134" s="5">
         <v>0</v>
@@ -4804,13 +4804,13 @@
         <v>0</v>
       </c>
       <c r="H134" s="6">
-        <v>450</v>
+        <v>430</v>
       </c>
     </row>
     <row outlineLevel="0" r="135">
       <c r="A135" s="4" t="inlineStr">
         <is>
-          <t>225/55R16</t>
+          <t>225/55R17RF</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
@@ -4820,29 +4820,29 @@
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>GD225/55R16</t>
+          <t>GD225/55R17RF</t>
         </is>
       </c>
       <c r="D135" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E135" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F135" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G135" s="5">
         <v>0</v>
       </c>
       <c r="H135" s="6">
-        <v>420</v>
+        <v>700</v>
       </c>
     </row>
     <row outlineLevel="0" r="136">
       <c r="A136" s="4" t="inlineStr">
         <is>
-          <t>225/55R17</t>
+          <t>225/55R18</t>
         </is>
       </c>
       <c r="B136" s="4" t="inlineStr">
@@ -4852,14 +4852,14 @@
       </c>
       <c r="C136" s="4" t="inlineStr">
         <is>
-          <t>HK225/55R17</t>
+          <t>HK225/55R18</t>
         </is>
       </c>
       <c r="D136" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E136" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F136" s="5">
         <v>0</v>
@@ -4868,55 +4868,55 @@
         <v>0</v>
       </c>
       <c r="H136" s="6">
-        <v>430</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="137">
       <c r="A137" s="4" t="inlineStr">
         <is>
-          <t>225/55R17RF</t>
+          <t>225/55R18</t>
         </is>
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>KUMHO</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>GD225/55R17RF</t>
+          <t>KM225/55R18</t>
         </is>
       </c>
       <c r="D137" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E137" s="5">
         <v>4</v>
       </c>
       <c r="F137" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G137" s="5">
         <v>0</v>
       </c>
       <c r="H137" s="6">
-        <v>700</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="138">
       <c r="A138" s="4" t="inlineStr">
         <is>
-          <t>225/55R18</t>
+          <t>225/55R19</t>
         </is>
       </c>
       <c r="B138" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C138" s="4" t="inlineStr">
         <is>
-          <t>HK225/55R18</t>
+          <t>BR225/55R19</t>
         </is>
       </c>
       <c r="D138" s="5">
@@ -4932,23 +4932,23 @@
         <v>0</v>
       </c>
       <c r="H138" s="6">
-        <v>500</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="139">
       <c r="A139" s="4" t="inlineStr">
         <is>
-          <t>225/55R18</t>
+          <t>225/55R19</t>
         </is>
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>KUMHO</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>KM225/55R18</t>
+          <t>GD225/55R19</t>
         </is>
       </c>
       <c r="D139" s="5">
@@ -4964,45 +4964,45 @@
         <v>0</v>
       </c>
       <c r="H139" s="6">
-        <v>450</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="140">
       <c r="A140" s="4" t="inlineStr">
         <is>
-          <t>225/55R19</t>
+          <t>225/60R17</t>
         </is>
       </c>
       <c r="B140" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C140" s="4" t="inlineStr">
         <is>
-          <t>BR225/55R19</t>
+          <t>HK225/60R17</t>
         </is>
       </c>
       <c r="D140" s="5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E140" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F140" s="5">
         <v>0</v>
       </c>
       <c r="G140" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H140" s="6">
-        <v>750</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="141">
       <c r="A141" s="4" t="inlineStr">
         <is>
-          <t>225/55R19</t>
+          <t>225/60R18</t>
         </is>
       </c>
       <c r="B141" s="4" t="inlineStr">
@@ -5012,14 +5012,14 @@
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>GD225/55R19</t>
+          <t>GD225/60R18</t>
         </is>
       </c>
       <c r="D141" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E141" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F141" s="5">
         <v>0</v>
@@ -5028,77 +5028,77 @@
         <v>0</v>
       </c>
       <c r="H141" s="6">
-        <v>750</v>
+        <v>700</v>
       </c>
     </row>
     <row outlineLevel="0" r="142">
       <c r="A142" s="4" t="inlineStr">
         <is>
-          <t>225/60R17</t>
+          <t>225/65R17</t>
         </is>
       </c>
       <c r="B142" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C142" s="4" t="inlineStr">
         <is>
-          <t>HK225/60R17</t>
+          <t>RD225/65R17</t>
         </is>
       </c>
       <c r="D142" s="5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E142" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F142" s="5">
         <v>0</v>
       </c>
       <c r="G142" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H142" s="6">
-        <v>400</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="143">
       <c r="A143" s="4" t="inlineStr">
         <is>
-          <t>225/60R18</t>
+          <t>225/75R15C</t>
         </is>
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>GD225/60R18</t>
+          <t>RD225/75R15C</t>
         </is>
       </c>
       <c r="D143" s="5">
         <v>1</v>
       </c>
       <c r="E143" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F143" s="5">
         <v>0</v>
       </c>
       <c r="G143" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H143" s="6">
-        <v>700</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="144">
       <c r="A144" s="4" t="inlineStr">
         <is>
-          <t>225/65R17</t>
+          <t>235/35R19</t>
         </is>
       </c>
       <c r="B144" s="4" t="inlineStr">
@@ -5108,81 +5108,81 @@
       </c>
       <c r="C144" s="4" t="inlineStr">
         <is>
-          <t>RD225/65R17</t>
+          <t>RD235/35R19</t>
         </is>
       </c>
       <c r="D144" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E144" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F144" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G144" s="5">
         <v>0</v>
       </c>
       <c r="H144" s="6">
-        <v>450</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="145">
       <c r="A145" s="4" t="inlineStr">
         <is>
-          <t>225/75R15C</t>
+          <t>235/40R19</t>
         </is>
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>RD225/75R15C</t>
+          <t>GD235/40R19</t>
         </is>
       </c>
       <c r="D145" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E145" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F145" s="5">
         <v>0</v>
       </c>
       <c r="G145" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H145" s="6">
-        <v>330</v>
+        <v>850</v>
       </c>
     </row>
     <row outlineLevel="0" r="146">
       <c r="A146" s="4" t="inlineStr">
         <is>
-          <t>235/35R19</t>
+          <t>235/45R18</t>
         </is>
       </c>
       <c r="B146" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C146" s="4" t="inlineStr">
         <is>
-          <t>RD235/35R19</t>
+          <t>GD235/45R18</t>
         </is>
       </c>
       <c r="D146" s="5">
         <v>4</v>
       </c>
       <c r="E146" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F146" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G146" s="5">
         <v>0</v>
@@ -5194,24 +5194,24 @@
     <row outlineLevel="0" r="147">
       <c r="A147" s="4" t="inlineStr">
         <is>
-          <t>235/40R19</t>
+          <t>235/50R18</t>
         </is>
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>GD235/40R19</t>
+          <t>HK235/50R18</t>
         </is>
       </c>
       <c r="D147" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E147" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F147" s="5">
         <v>0</v>
@@ -5220,13 +5220,13 @@
         <v>0</v>
       </c>
       <c r="H147" s="6">
-        <v>850</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="148">
       <c r="A148" s="4" t="inlineStr">
         <is>
-          <t>235/45R18</t>
+          <t>235/50R19</t>
         </is>
       </c>
       <c r="B148" s="4" t="inlineStr">
@@ -5236,7 +5236,7 @@
       </c>
       <c r="C148" s="4" t="inlineStr">
         <is>
-          <t>GD235/45R18</t>
+          <t>GD235/50R19</t>
         </is>
       </c>
       <c r="D148" s="5">
@@ -5252,62 +5252,62 @@
         <v>0</v>
       </c>
       <c r="H148" s="6">
-        <v>600</v>
+        <v>800</v>
       </c>
     </row>
     <row outlineLevel="0" r="149">
       <c r="A149" s="4" t="inlineStr">
         <is>
-          <t>235/50R18</t>
+          <t>235/50R20</t>
         </is>
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>HK235/50R18</t>
+          <t>GD235/50R20</t>
         </is>
       </c>
       <c r="D149" s="5">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E149" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F149" s="5">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G149" s="5">
         <v>0</v>
       </c>
       <c r="H149" s="6">
-        <v>500</v>
+        <v>1180</v>
       </c>
     </row>
     <row outlineLevel="0" r="150">
       <c r="A150" s="4" t="inlineStr">
         <is>
-          <t>235/50R19</t>
+          <t>235/55R17</t>
         </is>
       </c>
       <c r="B150" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C150" s="4" t="inlineStr">
         <is>
-          <t>GD235/50R19</t>
+          <t>BR235/55R17</t>
         </is>
       </c>
       <c r="D150" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E150" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F150" s="5">
         <v>0</v>
@@ -5316,62 +5316,62 @@
         <v>0</v>
       </c>
       <c r="H150" s="6">
-        <v>800</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="151">
       <c r="A151" s="4" t="inlineStr">
         <is>
-          <t>235/50R20</t>
+          <t>235/55R18</t>
         </is>
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>GD235/50R20</t>
+          <t>HK235/55R18</t>
         </is>
       </c>
       <c r="D151" s="5">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E151" s="5">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F151" s="5">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G151" s="5">
         <v>0</v>
       </c>
       <c r="H151" s="6">
-        <v>1180</v>
+        <v>480</v>
       </c>
     </row>
     <row outlineLevel="0" r="152">
       <c r="A152" s="4" t="inlineStr">
         <is>
-          <t>235/55R17</t>
+          <t>235/55R19</t>
         </is>
       </c>
       <c r="B152" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C152" s="4" t="inlineStr">
         <is>
-          <t>BR235/55R17</t>
+          <t>GD235/55R19</t>
         </is>
       </c>
       <c r="D152" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E152" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F152" s="5">
         <v>0</v>
@@ -5380,13 +5380,13 @@
         <v>0</v>
       </c>
       <c r="H152" s="6">
-        <v>450</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="153">
       <c r="A153" s="4" t="inlineStr">
         <is>
-          <t>235/55R18</t>
+          <t>235/55R19</t>
         </is>
       </c>
       <c r="B153" s="4" t="inlineStr">
@@ -5396,14 +5396,14 @@
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>HK235/55R18</t>
+          <t>HK235/55R19</t>
         </is>
       </c>
       <c r="D153" s="5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E153" s="5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F153" s="5">
         <v>0</v>
@@ -5412,7 +5412,7 @@
         <v>0</v>
       </c>
       <c r="H153" s="6">
-        <v>480</v>
+        <v>630</v>
       </c>
     </row>
     <row outlineLevel="0" r="154">
@@ -5423,19 +5423,19 @@
       </c>
       <c r="B154" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C154" s="4" t="inlineStr">
         <is>
-          <t>GD235/55R19</t>
+          <t>LF235/55R19</t>
         </is>
       </c>
       <c r="D154" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E154" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F154" s="5">
         <v>0</v>
@@ -5444,7 +5444,7 @@
         <v>0</v>
       </c>
       <c r="H154" s="6">
-        <v>750</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="155">
@@ -5455,19 +5455,19 @@
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>HK235/55R19</t>
+          <t>NX235/55R19</t>
         </is>
       </c>
       <c r="D155" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E155" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F155" s="5">
         <v>0</v>
@@ -5476,7 +5476,7 @@
         <v>0</v>
       </c>
       <c r="H155" s="6">
-        <v>630</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="156">
@@ -5487,22 +5487,22 @@
       </c>
       <c r="B156" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C156" s="4" t="inlineStr">
         <is>
-          <t>LF235/55R19</t>
+          <t>RD235/55R19</t>
         </is>
       </c>
       <c r="D156" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E156" s="5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F156" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G156" s="5">
         <v>0</v>
@@ -5514,24 +5514,24 @@
     <row outlineLevel="0" r="157">
       <c r="A157" s="4" t="inlineStr">
         <is>
-          <t>235/55R19</t>
+          <t>235/60R16</t>
         </is>
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>NX235/55R19</t>
+          <t>HK235/60R16</t>
         </is>
       </c>
       <c r="D157" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E157" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F157" s="5">
         <v>0</v>
@@ -5540,33 +5540,33 @@
         <v>0</v>
       </c>
       <c r="H157" s="6">
-        <v>600</v>
+        <v>430</v>
       </c>
     </row>
     <row outlineLevel="0" r="158">
       <c r="A158" s="4" t="inlineStr">
         <is>
-          <t>235/55R19</t>
+          <t>235/60R17</t>
         </is>
       </c>
       <c r="B158" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C158" s="4" t="inlineStr">
         <is>
-          <t>RD235/55R19</t>
+          <t>HK235/60R17</t>
         </is>
       </c>
       <c r="D158" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E158" s="5">
         <v>0</v>
       </c>
       <c r="F158" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G158" s="5">
         <v>0</v>
@@ -5578,24 +5578,24 @@
     <row outlineLevel="0" r="159">
       <c r="A159" s="4" t="inlineStr">
         <is>
-          <t>235/60R16</t>
+          <t>235/60R18</t>
         </is>
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>HK235/60R16</t>
+          <t>GD235/60R18</t>
         </is>
       </c>
       <c r="D159" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E159" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F159" s="5">
         <v>0</v>
@@ -5604,13 +5604,13 @@
         <v>0</v>
       </c>
       <c r="H159" s="6">
-        <v>430</v>
+        <v>680</v>
       </c>
     </row>
     <row outlineLevel="0" r="160">
       <c r="A160" s="4" t="inlineStr">
         <is>
-          <t>235/60R17</t>
+          <t>235/60R18</t>
         </is>
       </c>
       <c r="B160" s="4" t="inlineStr">
@@ -5620,29 +5620,29 @@
       </c>
       <c r="C160" s="4" t="inlineStr">
         <is>
-          <t>HK235/60R17</t>
+          <t>HK235/60R18</t>
         </is>
       </c>
       <c r="D160" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E160" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F160" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G160" s="5">
         <v>0</v>
       </c>
       <c r="H160" s="6">
-        <v>500</v>
+        <v>480</v>
       </c>
     </row>
     <row outlineLevel="0" r="161">
       <c r="A161" s="4" t="inlineStr">
         <is>
-          <t>235/60R18</t>
+          <t>245/40R17</t>
         </is>
       </c>
       <c r="B161" s="4" t="inlineStr">
@@ -5652,14 +5652,14 @@
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>GD235/60R18</t>
+          <t>GD245/40R17</t>
         </is>
       </c>
       <c r="D161" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E161" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F161" s="5">
         <v>0</v>
@@ -5668,27 +5668,27 @@
         <v>0</v>
       </c>
       <c r="H161" s="6">
-        <v>680</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="162">
       <c r="A162" s="4" t="inlineStr">
         <is>
-          <t>235/60R18</t>
+          <t>245/40R18</t>
         </is>
       </c>
       <c r="B162" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C162" s="4" t="inlineStr">
         <is>
-          <t>HK235/60R18</t>
+          <t>GD245/40R18</t>
         </is>
       </c>
       <c r="D162" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E162" s="5">
         <v>2</v>
@@ -5697,33 +5697,33 @@
         <v>0</v>
       </c>
       <c r="G162" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H162" s="6">
-        <v>480</v>
+        <v>620</v>
       </c>
     </row>
     <row outlineLevel="0" r="163">
       <c r="A163" s="4" t="inlineStr">
         <is>
-          <t>245/40R17</t>
+          <t>245/40R19</t>
         </is>
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>GD245/40R17</t>
+          <t>HK245/40R19</t>
         </is>
       </c>
       <c r="D163" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E163" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F163" s="5">
         <v>0</v>
@@ -5732,45 +5732,45 @@
         <v>0</v>
       </c>
       <c r="H163" s="6">
-        <v>400</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="164">
       <c r="A164" s="4" t="inlineStr">
         <is>
-          <t>245/40R18</t>
+          <t>245/40R20</t>
         </is>
       </c>
       <c r="B164" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C164" s="4" t="inlineStr">
         <is>
-          <t>GD245/40R18</t>
+          <t>CT245/40R20</t>
         </is>
       </c>
       <c r="D164" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E164" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F164" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G164" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H164" s="6">
-        <v>620</v>
+        <v>1050</v>
       </c>
     </row>
     <row outlineLevel="0" r="165">
       <c r="A165" s="4" t="inlineStr">
         <is>
-          <t>245/40R19</t>
+          <t>245/45R17</t>
         </is>
       </c>
       <c r="B165" s="4" t="inlineStr">
@@ -5780,7 +5780,7 @@
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>HK245/40R19</t>
+          <t>HK245/45R17</t>
         </is>
       </c>
       <c r="D165" s="5">
@@ -5796,13 +5796,13 @@
         <v>0</v>
       </c>
       <c r="H165" s="6">
-        <v>750</v>
+        <v>430</v>
       </c>
     </row>
     <row outlineLevel="0" r="166">
       <c r="A166" s="4" t="inlineStr">
         <is>
-          <t>245/40R20</t>
+          <t>245/45R18</t>
         </is>
       </c>
       <c r="B166" s="4" t="inlineStr">
@@ -5812,46 +5812,46 @@
       </c>
       <c r="C166" s="4" t="inlineStr">
         <is>
-          <t>CT245/40R20</t>
+          <t>CT245/45R18</t>
         </is>
       </c>
       <c r="D166" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E166" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F166" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G166" s="5">
         <v>0</v>
       </c>
       <c r="H166" s="6">
-        <v>1050</v>
+        <v>650</v>
       </c>
     </row>
     <row outlineLevel="0" r="167">
       <c r="A167" s="4" t="inlineStr">
         <is>
-          <t>245/45R17</t>
+          <t>245/45R18</t>
         </is>
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>HK245/45R17</t>
+          <t>GD245/45R18</t>
         </is>
       </c>
       <c r="D167" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E167" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F167" s="5">
         <v>0</v>
@@ -5860,7 +5860,7 @@
         <v>0</v>
       </c>
       <c r="H167" s="6">
-        <v>430</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="168">
@@ -5871,12 +5871,12 @@
       </c>
       <c r="B168" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C168" s="4" t="inlineStr">
         <is>
-          <t>CT245/45R18</t>
+          <t>HK245/45R18</t>
         </is>
       </c>
       <c r="D168" s="5">
@@ -5892,13 +5892,13 @@
         <v>0</v>
       </c>
       <c r="H168" s="6">
-        <v>650</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="169">
       <c r="A169" s="4" t="inlineStr">
         <is>
-          <t>245/45R18</t>
+          <t>245/45R18RF</t>
         </is>
       </c>
       <c r="B169" s="4" t="inlineStr">
@@ -5908,14 +5908,14 @@
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>GD245/45R18</t>
+          <t>GD245/45R18RF</t>
         </is>
       </c>
       <c r="D169" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E169" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F169" s="5">
         <v>0</v>
@@ -5924,30 +5924,30 @@
         <v>0</v>
       </c>
       <c r="H169" s="6">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row outlineLevel="0" r="170">
       <c r="A170" s="4" t="inlineStr">
         <is>
-          <t>245/45R18</t>
+          <t>245/45R19</t>
         </is>
       </c>
       <c r="B170" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C170" s="4" t="inlineStr">
         <is>
-          <t>HK245/45R18</t>
+          <t>BR245/45R19</t>
         </is>
       </c>
       <c r="D170" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E170" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F170" s="5">
         <v>0</v>
@@ -5956,119 +5956,119 @@
         <v>0</v>
       </c>
       <c r="H170" s="6">
-        <v>500</v>
+        <v>790</v>
       </c>
     </row>
     <row outlineLevel="0" r="171">
       <c r="A171" s="4" t="inlineStr">
         <is>
-          <t>245/45R18RF</t>
+          <t>245/45R19</t>
         </is>
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t>GD245/45R18RF</t>
+          <t>RD245/45R19</t>
         </is>
       </c>
       <c r="D171" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E171" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F171" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G171" s="5">
         <v>0</v>
       </c>
       <c r="H171" s="6">
-        <v>720</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="172">
       <c r="A172" s="4" t="inlineStr">
         <is>
-          <t>245/45R19</t>
+          <t>245/45R20</t>
         </is>
       </c>
       <c r="B172" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C172" s="4" t="inlineStr">
         <is>
-          <t>BR245/45R19</t>
+          <t>HK245/45R20</t>
         </is>
       </c>
       <c r="D172" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E172" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F172" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G172" s="5">
         <v>0</v>
       </c>
       <c r="H172" s="6">
-        <v>790</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="173">
       <c r="A173" s="4" t="inlineStr">
         <is>
-          <t>245/45R19</t>
+          <t>245/65R17</t>
         </is>
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>RD245/45R19</t>
+          <t>NX245/65R17</t>
         </is>
       </c>
       <c r="D173" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E173" s="5">
         <v>0</v>
       </c>
       <c r="F173" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G173" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H173" s="6">
-        <v>450</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="174">
       <c r="A174" s="4" t="inlineStr">
         <is>
-          <t>245/45R20</t>
+          <t>245/70R16</t>
         </is>
       </c>
       <c r="B174" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>LASSA</t>
         </is>
       </c>
       <c r="C174" s="4" t="inlineStr">
         <is>
-          <t>HK245/45R20</t>
+          <t>LS245/70R16</t>
         </is>
       </c>
       <c r="D174" s="5">
@@ -6078,93 +6078,93 @@
         <v>0</v>
       </c>
       <c r="F174" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G174" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H174" s="6">
-        <v>750</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="175">
       <c r="A175" s="4" t="inlineStr">
         <is>
-          <t>245/65R17</t>
+          <t>255/35R19</t>
         </is>
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>NX245/65R17</t>
+          <t>DL255/35R19</t>
         </is>
       </c>
       <c r="D175" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E175" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F175" s="5">
         <v>0</v>
       </c>
       <c r="G175" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H175" s="6">
-        <v>600</v>
+        <v>700</v>
       </c>
     </row>
     <row outlineLevel="0" r="176">
       <c r="A176" s="4" t="inlineStr">
         <is>
-          <t>245/70R16</t>
+          <t>255/35R19RF</t>
         </is>
       </c>
       <c r="B176" s="4" t="inlineStr">
         <is>
-          <t>LASSA</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C176" s="4" t="inlineStr">
         <is>
-          <t>LS245/70R16</t>
+          <t>CT255/35R19RF</t>
         </is>
       </c>
       <c r="D176" s="5">
         <v>2</v>
       </c>
       <c r="E176" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F176" s="5">
         <v>0</v>
       </c>
       <c r="G176" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H176" s="6">
-        <v>500</v>
+        <v>950</v>
       </c>
     </row>
     <row outlineLevel="0" r="177">
       <c r="A177" s="4" t="inlineStr">
         <is>
-          <t>255/35R19</t>
+          <t>255/35R19RF</t>
         </is>
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>DL255/35R19</t>
+          <t>GD255/35R19RF</t>
         </is>
       </c>
       <c r="D177" s="5">
@@ -6180,13 +6180,13 @@
         <v>0</v>
       </c>
       <c r="H177" s="6">
-        <v>700</v>
+        <v>950</v>
       </c>
     </row>
     <row outlineLevel="0" r="178">
       <c r="A178" s="4" t="inlineStr">
         <is>
-          <t>255/35R19RF</t>
+          <t>255/50R19</t>
         </is>
       </c>
       <c r="B178" s="4" t="inlineStr">
@@ -6196,61 +6196,61 @@
       </c>
       <c r="C178" s="4" t="inlineStr">
         <is>
-          <t>CT255/35R19RF</t>
+          <t>CT255/50R19</t>
         </is>
       </c>
       <c r="D178" s="5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E178" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F178" s="5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G178" s="5">
         <v>0</v>
       </c>
       <c r="H178" s="6">
-        <v>950</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="179">
       <c r="A179" s="4" t="inlineStr">
         <is>
-          <t>255/35R19RF</t>
+          <t>255/50R20</t>
         </is>
       </c>
       <c r="B179" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C179" s="4" t="inlineStr">
         <is>
-          <t>GD255/35R19RF</t>
+          <t>CT255/50R20</t>
         </is>
       </c>
       <c r="D179" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E179" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F179" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G179" s="5">
         <v>0</v>
       </c>
       <c r="H179" s="6">
-        <v>950</v>
+        <v>900</v>
       </c>
     </row>
     <row outlineLevel="0" r="180">
       <c r="A180" s="4" t="inlineStr">
         <is>
-          <t>255/50R19</t>
+          <t>255/55R19</t>
         </is>
       </c>
       <c r="B180" s="4" t="inlineStr">
@@ -6260,17 +6260,17 @@
       </c>
       <c r="C180" s="4" t="inlineStr">
         <is>
-          <t>CT255/50R19</t>
+          <t>CT255/55R19</t>
         </is>
       </c>
       <c r="D180" s="5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E180" s="5">
         <v>0</v>
       </c>
       <c r="F180" s="5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G180" s="5">
         <v>0</v>
@@ -6282,49 +6282,49 @@
     <row outlineLevel="0" r="181">
       <c r="A181" s="4" t="inlineStr">
         <is>
-          <t>255/50R20</t>
+          <t>255/55R19</t>
         </is>
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C181" s="4" t="inlineStr">
         <is>
-          <t>CT255/50R20</t>
+          <t>DL255/55R19</t>
         </is>
       </c>
       <c r="D181" s="5">
         <v>2</v>
       </c>
       <c r="E181" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F181" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G181" s="5">
         <v>0</v>
       </c>
       <c r="H181" s="6">
-        <v>900</v>
+        <v>700</v>
       </c>
     </row>
     <row outlineLevel="0" r="182">
       <c r="A182" s="4" t="inlineStr">
         <is>
-          <t>255/55R19</t>
+          <t>255/70R16</t>
         </is>
       </c>
       <c r="B182" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C182" s="4" t="inlineStr">
         <is>
-          <t>CT255/55R19</t>
+          <t>RD255/70R16</t>
         </is>
       </c>
       <c r="D182" s="5">
@@ -6334,36 +6334,36 @@
         <v>0</v>
       </c>
       <c r="F182" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G182" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H182" s="6">
-        <v>750</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="183">
       <c r="A183" s="4" t="inlineStr">
         <is>
-          <t>255/55R19</t>
+          <t>265/35R18</t>
         </is>
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C183" s="4" t="inlineStr">
         <is>
-          <t>DL255/55R19</t>
+          <t>GD265/35R18</t>
         </is>
       </c>
       <c r="D183" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E183" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F183" s="5">
         <v>0</v>
@@ -6378,135 +6378,135 @@
     <row outlineLevel="0" r="184">
       <c r="A184" s="4" t="inlineStr">
         <is>
-          <t>255/70R15</t>
+          <t>265/50R20</t>
         </is>
       </c>
       <c r="B184" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C184" s="4" t="inlineStr">
         <is>
-          <t>DL255/70R15</t>
+          <t>GD265/50R20</t>
         </is>
       </c>
       <c r="D184" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E184" s="5">
         <v>0</v>
       </c>
       <c r="F184" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G184" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H184" s="6">
-        <v>550</v>
+        <v>1150</v>
       </c>
     </row>
     <row outlineLevel="0" r="185">
       <c r="A185" s="4" t="inlineStr">
         <is>
-          <t>255/70R16</t>
+          <t>275/35R19RF</t>
         </is>
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C185" s="4" t="inlineStr">
         <is>
-          <t>RD255/70R16</t>
+          <t>GD275/35R19RF</t>
         </is>
       </c>
       <c r="D185" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E185" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F185" s="5">
         <v>0</v>
       </c>
       <c r="G185" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H185" s="6">
-        <v>500</v>
+        <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="186">
       <c r="A186" s="4" t="inlineStr">
         <is>
-          <t>265/35R18</t>
+          <t>275/35R20</t>
         </is>
       </c>
       <c r="B186" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C186" s="4" t="inlineStr">
         <is>
-          <t>GD265/35R18</t>
+          <t>CT275/35R20</t>
         </is>
       </c>
       <c r="D186" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E186" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F186" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G186" s="5">
         <v>0</v>
       </c>
       <c r="H186" s="6">
-        <v>700</v>
+        <v>980</v>
       </c>
     </row>
     <row outlineLevel="0" r="187">
       <c r="A187" s="4" t="inlineStr">
         <is>
-          <t>265/50R20</t>
+          <t>275/40R20</t>
         </is>
       </c>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C187" s="4" t="inlineStr">
         <is>
-          <t>GD265/50R20</t>
+          <t>HK275/40R20</t>
         </is>
       </c>
       <c r="D187" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E187" s="5">
         <v>0</v>
       </c>
       <c r="F187" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G187" s="5">
         <v>0</v>
       </c>
       <c r="H187" s="6">
-        <v>1150</v>
+        <v>770</v>
       </c>
     </row>
     <row outlineLevel="0" r="188">
       <c r="A188" s="4" t="inlineStr">
         <is>
-          <t>275/35R19RF</t>
+          <t>275/50R21</t>
         </is>
       </c>
       <c r="B188" s="4" t="inlineStr">
@@ -6516,17 +6516,17 @@
       </c>
       <c r="C188" s="4" t="inlineStr">
         <is>
-          <t>GD275/35R19RF</t>
+          <t>GD275/50R21</t>
         </is>
       </c>
       <c r="D188" s="5">
         <v>2</v>
       </c>
       <c r="E188" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F188" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G188" s="5">
         <v>0</v>
@@ -6538,7 +6538,7 @@
     <row outlineLevel="0" r="189">
       <c r="A189" s="4" t="inlineStr">
         <is>
-          <t>275/35R20</t>
+          <t>295/35R21</t>
         </is>
       </c>
       <c r="B189" s="4" t="inlineStr">
@@ -6548,7 +6548,7 @@
       </c>
       <c r="C189" s="4" t="inlineStr">
         <is>
-          <t>CT275/35R20</t>
+          <t>CT295/35R21</t>
         </is>
       </c>
       <c r="D189" s="5">
@@ -6564,166 +6564,70 @@
         <v>0</v>
       </c>
       <c r="H189" s="6">
-        <v>980</v>
+        <v>1150</v>
       </c>
     </row>
     <row outlineLevel="0" r="190">
       <c r="A190" s="4" t="inlineStr">
         <is>
-          <t>275/40R20</t>
+          <t>295/35R21</t>
         </is>
       </c>
       <c r="B190" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C190" s="4" t="inlineStr">
         <is>
-          <t>HK275/40R20</t>
+          <t>GD295/35R21</t>
         </is>
       </c>
       <c r="D190" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E190" s="5">
         <v>0</v>
       </c>
       <c r="F190" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G190" s="5">
         <v>0</v>
       </c>
       <c r="H190" s="6">
-        <v>770</v>
+        <v>980</v>
       </c>
     </row>
     <row outlineLevel="0" r="191">
       <c r="A191" s="4" t="inlineStr">
         <is>
-          <t>275/50R21</t>
+          <t>500R12</t>
         </is>
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C191" s="4" t="inlineStr">
         <is>
-          <t>GD275/50R21</t>
+          <t>RD500R12</t>
         </is>
       </c>
       <c r="D191" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E191" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F191" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G191" s="5">
         <v>0</v>
       </c>
       <c r="H191" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row outlineLevel="0" r="192">
-      <c r="A192" s="4" t="inlineStr">
-        <is>
-          <t>295/35R21</t>
-        </is>
-      </c>
-      <c r="B192" s="4" t="inlineStr">
-        <is>
-          <t>CONTINENTAL</t>
-        </is>
-      </c>
-      <c r="C192" s="4" t="inlineStr">
-        <is>
-          <t>CT295/35R21</t>
-        </is>
-      </c>
-      <c r="D192" s="5">
-        <v>2</v>
-      </c>
-      <c r="E192" s="5">
-        <v>0</v>
-      </c>
-      <c r="F192" s="5">
-        <v>2</v>
-      </c>
-      <c r="G192" s="5">
-        <v>0</v>
-      </c>
-      <c r="H192" s="6">
-        <v>1150</v>
-      </c>
-    </row>
-    <row outlineLevel="0" r="193">
-      <c r="A193" s="4" t="inlineStr">
-        <is>
-          <t>295/35R21</t>
-        </is>
-      </c>
-      <c r="B193" s="4" t="inlineStr">
-        <is>
-          <t>GOODYEAR</t>
-        </is>
-      </c>
-      <c r="C193" s="4" t="inlineStr">
-        <is>
-          <t>GD295/35R21</t>
-        </is>
-      </c>
-      <c r="D193" s="5">
-        <v>3</v>
-      </c>
-      <c r="E193" s="5">
-        <v>0</v>
-      </c>
-      <c r="F193" s="5">
-        <v>3</v>
-      </c>
-      <c r="G193" s="5">
-        <v>0</v>
-      </c>
-      <c r="H193" s="6">
-        <v>980</v>
-      </c>
-    </row>
-    <row outlineLevel="0" r="194">
-      <c r="A194" s="4" t="inlineStr">
-        <is>
-          <t>500R12</t>
-        </is>
-      </c>
-      <c r="B194" s="4" t="inlineStr">
-        <is>
-          <t>RADIAL</t>
-        </is>
-      </c>
-      <c r="C194" s="4" t="inlineStr">
-        <is>
-          <t>RD500R12</t>
-        </is>
-      </c>
-      <c r="D194" s="5">
-        <v>3</v>
-      </c>
-      <c r="E194" s="5">
-        <v>3</v>
-      </c>
-      <c r="F194" s="5">
-        <v>0</v>
-      </c>
-      <c r="G194" s="5">
-        <v>0</v>
-      </c>
-      <c r="H194" s="6">
         <v>300</v>
       </c>
     </row>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -5636,7 +5636,7 @@
         <v>0</v>
       </c>
       <c r="H160" s="6">
-        <v>480</v>
+        <v>550</v>
       </c>
     </row>
     <row outlineLevel="0" r="161">

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -1560,10 +1560,10 @@
         </is>
       </c>
       <c r="D33" s="5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E33" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F33" s="5">
         <v>5</v>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -856,10 +856,10 @@
         </is>
       </c>
       <c r="D11" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E11" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F11" s="5">
         <v>0</v>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="D24" s="5">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E24" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F24" s="5">
         <v>31</v>
@@ -1816,10 +1816,10 @@
         </is>
       </c>
       <c r="D41" s="5">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E41" s="5">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F41" s="5">
         <v>0</v>
@@ -4024,10 +4024,10 @@
         </is>
       </c>
       <c r="D110" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E110" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F110" s="5">
         <v>0</v>
@@ -4440,7 +4440,7 @@
         </is>
       </c>
       <c r="D123" s="5">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E123" s="5">
         <v>6</v>
@@ -4449,7 +4449,7 @@
         <v>19</v>
       </c>
       <c r="G123" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H123" s="6">
         <v>380</v>
@@ -5144,10 +5144,10 @@
         </is>
       </c>
       <c r="D145" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E145" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F145" s="5">
         <v>0</v>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -496,7 +496,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H191"/>
+  <dimension ref="A1:H193"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col customWidth="true" min="1" max="1" width="13.8359375"/>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="D8" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E8" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F8" s="5">
         <v>0</v>
@@ -920,10 +920,10 @@
         </is>
       </c>
       <c r="D13" s="5">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E13" s="5">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F13" s="5">
         <v>0</v>
@@ -1080,10 +1080,10 @@
         </is>
       </c>
       <c r="D18" s="5">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E18" s="5">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F18" s="5">
         <v>55</v>
@@ -1432,10 +1432,10 @@
         </is>
       </c>
       <c r="D29" s="5">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E29" s="5">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F29" s="5">
         <v>0</v>
@@ -1752,7 +1752,7 @@
         </is>
       </c>
       <c r="D39" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E39" s="5">
         <v>0</v>
@@ -1761,7 +1761,7 @@
         <v>0</v>
       </c>
       <c r="G39" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H39" s="6">
         <v>200</v>
@@ -2040,7 +2040,7 @@
         </is>
       </c>
       <c r="D48" s="5">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E48" s="5">
         <v>4</v>
@@ -2049,7 +2049,7 @@
         <v>13</v>
       </c>
       <c r="G48" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H48" s="6">
         <v>350</v>
@@ -2767,28 +2767,28 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>DOUBLESTAR</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>DS205/55R16</t>
+          <t>BR205/55R16</t>
         </is>
       </c>
       <c r="D71" s="5">
         <v>4</v>
       </c>
       <c r="E71" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F71" s="5">
         <v>0</v>
       </c>
       <c r="G71" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H71" s="6">
-        <v>230</v>
+        <v>290</v>
       </c>
     </row>
     <row outlineLevel="0" r="72">
@@ -2799,28 +2799,28 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>FULDA</t>
+          <t>DOUBLESTAR</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>FL205/55R16</t>
+          <t>DS205/55R16</t>
         </is>
       </c>
       <c r="D72" s="5">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="E72" s="5">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F72" s="5">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="G72" s="5">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H72" s="6">
-        <v>250</v>
+        <v>230</v>
       </c>
     </row>
     <row outlineLevel="0" r="73">
@@ -2831,25 +2831,25 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>GOODRIDE</t>
+          <t>FULDA</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>GR205/55R16</t>
+          <t>FL205/55R16</t>
         </is>
       </c>
       <c r="D73" s="5">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="E73" s="5">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F73" s="5">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G73" s="5">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H73" s="6">
         <v>250</v>
@@ -2863,28 +2863,28 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>GOODRIDE</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>GD205/55R16</t>
+          <t>GR205/55R16</t>
         </is>
       </c>
       <c r="D74" s="5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E74" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F74" s="5">
         <v>0</v>
       </c>
       <c r="G74" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H74" s="6">
-        <v>280</v>
+        <v>250</v>
       </c>
     </row>
     <row outlineLevel="0" r="75">
@@ -2895,28 +2895,28 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>HK205/55R16</t>
+          <t>GD205/55R16</t>
         </is>
       </c>
       <c r="D75" s="5">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E75" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F75" s="5">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G75" s="5">
         <v>4</v>
       </c>
       <c r="H75" s="6">
-        <v>260</v>
+        <v>280</v>
       </c>
     </row>
     <row outlineLevel="0" r="76">
@@ -2927,48 +2927,48 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>RD205/55R16</t>
+          <t>HK205/55R16</t>
         </is>
       </c>
       <c r="D76" s="5">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E76" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F76" s="5">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G76" s="5">
         <v>4</v>
       </c>
       <c r="H76" s="6">
-        <v>230</v>
+        <v>260</v>
       </c>
     </row>
     <row outlineLevel="0" r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>205/55R16RF</t>
+          <t>205/55R16</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>GD205/55R16RF</t>
+          <t>RD205/55R16</t>
         </is>
       </c>
       <c r="D77" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E77" s="5">
         <v>0</v>
@@ -2977,16 +2977,16 @@
         <v>0</v>
       </c>
       <c r="G77" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H77" s="6">
-        <v>480</v>
+        <v>230</v>
       </c>
     </row>
     <row outlineLevel="0" r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>205/55R17</t>
+          <t>205/55R16RF</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
@@ -2996,23 +2996,23 @@
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>GD205/55R17</t>
+          <t>GD205/55R16RF</t>
         </is>
       </c>
       <c r="D78" s="5">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="E78" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F78" s="5">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G78" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H78" s="6">
-        <v>450</v>
+        <v>480</v>
       </c>
     </row>
     <row outlineLevel="0" r="79">
@@ -3023,44 +3023,44 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>NX205/55R17</t>
+          <t>GD205/55R17</t>
         </is>
       </c>
       <c r="D79" s="5">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="E79" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F79" s="5">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G79" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H79" s="6">
-        <v>400</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>205/60R16</t>
+          <t>205/55R17</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>DL205/60R16</t>
+          <t>NX205/55R17</t>
         </is>
       </c>
       <c r="D80" s="5">
@@ -3076,7 +3076,7 @@
         <v>0</v>
       </c>
       <c r="H80" s="6">
-        <v>330</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="81">
@@ -3087,28 +3087,28 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>GD205/60R16</t>
+          <t>DL205/60R16</t>
         </is>
       </c>
       <c r="D81" s="5">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="E81" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F81" s="5">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G81" s="5">
         <v>0</v>
       </c>
       <c r="H81" s="6">
-        <v>380</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="82">
@@ -3119,28 +3119,28 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>HK205/60R16</t>
+          <t>GD205/60R16</t>
         </is>
       </c>
       <c r="D82" s="5">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E82" s="5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F82" s="5">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="G82" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H82" s="6">
-        <v>300</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="83">
@@ -3151,25 +3151,25 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>LF205/60R16</t>
+          <t>HK205/60R16</t>
         </is>
       </c>
       <c r="D83" s="5">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E83" s="5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F83" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G83" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H83" s="6">
         <v>300</v>
@@ -3178,17 +3178,17 @@
     <row outlineLevel="0" r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>205/65R15</t>
+          <t>205/60R16</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>HK205/65R15</t>
+          <t>LF205/60R16</t>
         </is>
       </c>
       <c r="D84" s="5">
@@ -3204,30 +3204,30 @@
         <v>0</v>
       </c>
       <c r="H84" s="6">
-        <v>270</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>205/65R16</t>
+          <t>205/65R15</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>BR205/65R16</t>
+          <t>HK205/65R15</t>
         </is>
       </c>
       <c r="D85" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E85" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F85" s="5">
         <v>0</v>
@@ -3236,7 +3236,7 @@
         <v>0</v>
       </c>
       <c r="H85" s="6">
-        <v>420</v>
+        <v>270</v>
       </c>
     </row>
     <row outlineLevel="0" r="86">
@@ -3247,19 +3247,19 @@
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>HK205/65R16</t>
+          <t>BR205/65R16</t>
         </is>
       </c>
       <c r="D86" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E86" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F86" s="5">
         <v>0</v>
@@ -3268,39 +3268,39 @@
         <v>0</v>
       </c>
       <c r="H86" s="6">
-        <v>380</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>215/40R18</t>
+          <t>205/65R16</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>GD215/40R18</t>
+          <t>HK205/65R16</t>
         </is>
       </c>
       <c r="D87" s="5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E87" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F87" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G87" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H87" s="6">
-        <v>600</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="88">
@@ -3311,44 +3311,44 @@
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>HK215/40R18</t>
+          <t>GD215/40R18</t>
         </is>
       </c>
       <c r="D88" s="5">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E88" s="5">
         <v>4</v>
       </c>
       <c r="F88" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G88" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H88" s="6">
-        <v>490</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>215/45R16</t>
+          <t>215/40R18</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>GD215/45R16</t>
+          <t>HK215/40R18</t>
         </is>
       </c>
       <c r="D89" s="5">
@@ -3364,13 +3364,13 @@
         <v>0</v>
       </c>
       <c r="H89" s="6">
-        <v>450</v>
+        <v>490</v>
       </c>
     </row>
     <row outlineLevel="0" r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>215/45R17</t>
+          <t>215/45R16</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
@@ -3380,14 +3380,14 @@
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>GD215/45R17</t>
+          <t>GD215/45R16</t>
         </is>
       </c>
       <c r="D90" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E90" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F90" s="5">
         <v>0</v>
@@ -3396,7 +3396,7 @@
         <v>0</v>
       </c>
       <c r="H90" s="6">
-        <v>400</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="91">
@@ -3407,25 +3407,25 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>HK215/45R17</t>
+          <t>GD215/45R17</t>
         </is>
       </c>
       <c r="D91" s="5">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="E91" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F91" s="5">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G91" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H91" s="6">
         <v>400</v>
@@ -3439,28 +3439,28 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>IRIS</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>IR215/45R17</t>
+          <t>HK215/45R17</t>
         </is>
       </c>
       <c r="D92" s="5">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="E92" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F92" s="5">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G92" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H92" s="6">
-        <v>300</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="93">
@@ -3471,28 +3471,28 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>IRIS</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>LF215/45R17</t>
+          <t>IR215/45R17</t>
         </is>
       </c>
       <c r="D93" s="5">
         <v>1</v>
       </c>
       <c r="E93" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F93" s="5">
         <v>0</v>
       </c>
       <c r="G93" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H93" s="6">
-        <v>350</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="94">
@@ -3503,83 +3503,83 @@
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>NX215/45R17</t>
+          <t>LF215/45R17</t>
         </is>
       </c>
       <c r="D94" s="5">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E94" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F94" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G94" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H94" s="6">
-        <v>380</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>215/45R18</t>
+          <t>215/45R17</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>GD215/45R18</t>
+          <t>NX215/45R17</t>
         </is>
       </c>
       <c r="D95" s="5">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E95" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F95" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G95" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H95" s="6">
-        <v>550</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="96">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>215/50R17</t>
+          <t>215/45R18</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>BR215/50R17</t>
+          <t>GD215/45R18</t>
         </is>
       </c>
       <c r="D96" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E96" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F96" s="5">
         <v>0</v>
@@ -3588,7 +3588,7 @@
         <v>0</v>
       </c>
       <c r="H96" s="6">
-        <v>450</v>
+        <v>550</v>
       </c>
     </row>
     <row outlineLevel="0" r="97">
@@ -3599,28 +3599,28 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>GD215/50R17</t>
+          <t>BR215/50R17</t>
         </is>
       </c>
       <c r="D97" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E97" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F97" s="5">
         <v>0</v>
       </c>
       <c r="G97" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H97" s="6">
-        <v>470</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="98">
@@ -3631,28 +3631,28 @@
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>HK215/50R17</t>
+          <t>GD215/50R17</t>
         </is>
       </c>
       <c r="D98" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E98" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F98" s="5">
         <v>0</v>
       </c>
       <c r="G98" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H98" s="6">
-        <v>400</v>
+        <v>470</v>
       </c>
     </row>
     <row outlineLevel="0" r="99">
@@ -3663,19 +3663,19 @@
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>LF215/50R17</t>
+          <t>HK215/50R17</t>
         </is>
       </c>
       <c r="D99" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E99" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F99" s="5">
         <v>0</v>
@@ -3684,30 +3684,30 @@
         <v>0</v>
       </c>
       <c r="H99" s="6">
-        <v>420</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="100">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>215/50R18</t>
+          <t>215/50R17</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>GD215/50R18</t>
+          <t>LF215/50R17</t>
         </is>
       </c>
       <c r="D100" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E100" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F100" s="5">
         <v>0</v>
@@ -3716,13 +3716,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="6">
-        <v>600</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>215/55R16</t>
+          <t>215/50R18</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
@@ -3732,14 +3732,14 @@
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>GD215/55R16</t>
+          <t>GD215/50R18</t>
         </is>
       </c>
       <c r="D101" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E101" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F101" s="5">
         <v>0</v>
@@ -3748,7 +3748,7 @@
         <v>0</v>
       </c>
       <c r="H101" s="6">
-        <v>440</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="102">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>LF215/55R16</t>
+          <t>GD215/55R16</t>
         </is>
       </c>
       <c r="D102" s="5">
@@ -3780,23 +3780,23 @@
         <v>0</v>
       </c>
       <c r="H102" s="6">
-        <v>350</v>
+        <v>440</v>
       </c>
     </row>
     <row outlineLevel="0" r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>215/55R17</t>
+          <t>215/55R16</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>BR215/55R17</t>
+          <t>LF215/55R16</t>
         </is>
       </c>
       <c r="D103" s="5">
@@ -3812,7 +3812,7 @@
         <v>0</v>
       </c>
       <c r="H103" s="6">
-        <v>480</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="104">
@@ -3823,19 +3823,19 @@
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>HK215/55R17</t>
+          <t>BR215/55R17</t>
         </is>
       </c>
       <c r="D104" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E104" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F104" s="5">
         <v>0</v>
@@ -3844,23 +3844,23 @@
         <v>0</v>
       </c>
       <c r="H104" s="6">
-        <v>420</v>
+        <v>480</v>
       </c>
     </row>
     <row outlineLevel="0" r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>215/55R18</t>
+          <t>215/55R17</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>GD215/55R18</t>
+          <t>HK215/55R17</t>
         </is>
       </c>
       <c r="D105" s="5">
@@ -3876,23 +3876,23 @@
         <v>0</v>
       </c>
       <c r="H105" s="6">
-        <v>580</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="106">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>215/60R16</t>
+          <t>215/55R18</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>BR215/60R16</t>
+          <t>GD215/55R18</t>
         </is>
       </c>
       <c r="D106" s="5">
@@ -3908,7 +3908,7 @@
         <v>0</v>
       </c>
       <c r="H106" s="6">
-        <v>350</v>
+        <v>580</v>
       </c>
     </row>
     <row outlineLevel="0" r="107">
@@ -3919,25 +3919,25 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>DL215/60R16</t>
+          <t>BR215/60R16</t>
         </is>
       </c>
       <c r="D107" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E107" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F107" s="5">
         <v>0</v>
       </c>
       <c r="G107" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H107" s="6">
         <v>350</v>
@@ -3951,28 +3951,28 @@
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>HK215/60R16</t>
+          <t>DL215/60R16</t>
         </is>
       </c>
       <c r="D108" s="5">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E108" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F108" s="5">
         <v>0</v>
       </c>
       <c r="G108" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H108" s="6">
-        <v>330</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="109">
@@ -3983,25 +3983,25 @@
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>NX215/60R16</t>
+          <t>HK215/60R16</t>
         </is>
       </c>
       <c r="D109" s="5">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E109" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F109" s="5">
         <v>0</v>
       </c>
       <c r="G109" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H109" s="6">
         <v>330</v>
@@ -4010,65 +4010,65 @@
     <row outlineLevel="0" r="110">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>215/60R17</t>
+          <t>215/60R16</t>
         </is>
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>RD215/60R17</t>
+          <t>NX215/60R16</t>
         </is>
       </c>
       <c r="D110" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E110" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F110" s="5">
         <v>0</v>
       </c>
       <c r="G110" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H110" s="6">
-        <v>300</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="111">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>215/65R16</t>
+          <t>215/60R17</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>GD215/65R16</t>
+          <t>RD215/60R17</t>
         </is>
       </c>
       <c r="D111" s="5">
         <v>1</v>
       </c>
       <c r="E111" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F111" s="5">
         <v>0</v>
       </c>
       <c r="G111" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H111" s="6">
-        <v>380</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="112">
@@ -4079,44 +4079,44 @@
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>HK215/65R16</t>
+          <t>GD215/65R16</t>
         </is>
       </c>
       <c r="D112" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E112" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F112" s="5">
         <v>0</v>
       </c>
       <c r="G112" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H112" s="6">
-        <v>330</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="113">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>215/65R17</t>
+          <t>215/65R16</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>MICHELIN</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>MC215/65R17</t>
+          <t>HK215/65R16</t>
         </is>
       </c>
       <c r="D113" s="5">
@@ -4132,23 +4132,23 @@
         <v>0</v>
       </c>
       <c r="H113" s="6">
-        <v>600</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="114">
       <c r="A114" s="4" t="inlineStr">
         <is>
-          <t>225/40R18</t>
+          <t>215/65R17</t>
         </is>
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>BARUM</t>
+          <t>MICHELIN</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>BM225/40R18</t>
+          <t>MC215/65R17</t>
         </is>
       </c>
       <c r="D114" s="5">
@@ -4164,39 +4164,39 @@
         <v>0</v>
       </c>
       <c r="H114" s="6">
-        <v>420</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="115">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t>225/40R18</t>
+          <t>215/70R15C</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>GD225/40R18</t>
+          <t>RD215/70R15C</t>
         </is>
       </c>
       <c r="D115" s="5">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="E115" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F115" s="5">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G115" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H115" s="6">
-        <v>480</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="116">
@@ -4207,19 +4207,19 @@
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>BARUM</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>HK225/40R18</t>
+          <t>BM225/40R18</t>
         </is>
       </c>
       <c r="D116" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E116" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F116" s="5">
         <v>0</v>
@@ -4228,7 +4228,7 @@
         <v>0</v>
       </c>
       <c r="H116" s="6">
-        <v>450</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="117">
@@ -4239,28 +4239,28 @@
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>LASSA</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>LS225/40R18</t>
+          <t>GD225/40R18</t>
         </is>
       </c>
       <c r="D117" s="5">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="E117" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F117" s="5">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G117" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H117" s="6">
-        <v>330</v>
+        <v>480</v>
       </c>
     </row>
     <row outlineLevel="0" r="118">
@@ -4271,19 +4271,19 @@
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>NX225/40R18</t>
+          <t>HK225/40R18</t>
         </is>
       </c>
       <c r="D118" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E118" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F118" s="5">
         <v>0</v>
@@ -4292,7 +4292,7 @@
         <v>0</v>
       </c>
       <c r="H118" s="6">
-        <v>400</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="119">
@@ -4303,51 +4303,51 @@
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>SEMPERIT</t>
+          <t>LASSA</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>SP225/40R18</t>
+          <t>LS225/40R18</t>
         </is>
       </c>
       <c r="D119" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E119" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F119" s="5">
         <v>0</v>
       </c>
       <c r="G119" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H119" s="6">
-        <v>450</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="120">
       <c r="A120" s="4" t="inlineStr">
         <is>
-          <t>225/40R18RF</t>
+          <t>225/40R18</t>
         </is>
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>GD225/40R18RF</t>
+          <t>NX225/40R18</t>
         </is>
       </c>
       <c r="D120" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E120" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F120" s="5">
         <v>0</v>
@@ -4356,30 +4356,30 @@
         <v>0</v>
       </c>
       <c r="H120" s="6">
-        <v>590</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="121">
       <c r="A121" s="4" t="inlineStr">
         <is>
-          <t>225/45R17</t>
+          <t>225/40R18</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>SEMPERIT</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>CT225/45R17</t>
+          <t>SP225/40R18</t>
         </is>
       </c>
       <c r="D121" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E121" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F121" s="5">
         <v>0</v>
@@ -4388,39 +4388,39 @@
         <v>0</v>
       </c>
       <c r="H121" s="6">
-        <v>400</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="122">
       <c r="A122" s="4" t="inlineStr">
         <is>
-          <t>225/45R17</t>
+          <t>225/40R18RF</t>
         </is>
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>FULDA</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>FL225/45R17</t>
+          <t>GD225/40R18RF</t>
         </is>
       </c>
       <c r="D122" s="5">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="E122" s="5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F122" s="5">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G122" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H122" s="6">
-        <v>350</v>
+        <v>590</v>
       </c>
     </row>
     <row outlineLevel="0" r="123">
@@ -4431,28 +4431,28 @@
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>GD225/45R17</t>
+          <t>CT225/45R17</t>
         </is>
       </c>
       <c r="D123" s="5">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="E123" s="5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F123" s="5">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="G123" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H123" s="6">
-        <v>380</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="124">
@@ -4463,25 +4463,25 @@
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>FULDA</t>
         </is>
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>HK225/45R17</t>
+          <t>FL225/45R17</t>
         </is>
       </c>
       <c r="D124" s="5">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="E124" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F124" s="5">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G124" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H124" s="6">
         <v>350</v>
@@ -4490,65 +4490,65 @@
     <row outlineLevel="0" r="125">
       <c r="A125" s="4" t="inlineStr">
         <is>
-          <t>225/45R18</t>
+          <t>225/45R17</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>DL225/45R18</t>
+          <t>GD225/45R17</t>
         </is>
       </c>
       <c r="D125" s="5">
+        <v>28</v>
+      </c>
+      <c r="E125" s="5">
+        <v>6</v>
+      </c>
+      <c r="F125" s="5">
+        <v>19</v>
+      </c>
+      <c r="G125" s="5">
         <v>3</v>
       </c>
-      <c r="E125" s="5">
-        <v>1</v>
-      </c>
-      <c r="F125" s="5">
-        <v>0</v>
-      </c>
-      <c r="G125" s="5">
-        <v>2</v>
-      </c>
       <c r="H125" s="6">
-        <v>500</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="126">
       <c r="A126" s="4" t="inlineStr">
         <is>
-          <t>225/45R18</t>
+          <t>225/45R17</t>
         </is>
       </c>
       <c r="B126" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C126" s="4" t="inlineStr">
         <is>
-          <t>GD225/45R18</t>
+          <t>HK225/45R17</t>
         </is>
       </c>
       <c r="D126" s="5">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E126" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F126" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G126" s="5">
         <v>0</v>
       </c>
       <c r="H126" s="6">
-        <v>550</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="127">
@@ -4559,34 +4559,34 @@
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>LF225/45R18</t>
+          <t>DL225/45R18</t>
         </is>
       </c>
       <c r="D127" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E127" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F127" s="5">
         <v>0</v>
       </c>
       <c r="G127" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H127" s="6">
-        <v>420</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="128">
       <c r="A128" s="4" t="inlineStr">
         <is>
-          <t>225/45R18RF</t>
+          <t>225/45R18</t>
         </is>
       </c>
       <c r="B128" s="4" t="inlineStr">
@@ -4596,46 +4596,46 @@
       </c>
       <c r="C128" s="4" t="inlineStr">
         <is>
-          <t>GD225/45R18RF</t>
+          <t>GD225/45R18</t>
         </is>
       </c>
       <c r="D128" s="5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E128" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F128" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G128" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H128" s="6">
-        <v>720</v>
+        <v>550</v>
       </c>
     </row>
     <row outlineLevel="0" r="129">
       <c r="A129" s="4" t="inlineStr">
         <is>
-          <t>225/45R19</t>
+          <t>225/45R18</t>
         </is>
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>CT225/45R19</t>
+          <t>LF225/45R18</t>
         </is>
       </c>
       <c r="D129" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E129" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F129" s="5">
         <v>0</v>
@@ -4644,13 +4644,13 @@
         <v>0</v>
       </c>
       <c r="H129" s="6">
-        <v>780</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="130">
       <c r="A130" s="4" t="inlineStr">
         <is>
-          <t>225/50R17</t>
+          <t>225/45R18RF</t>
         </is>
       </c>
       <c r="B130" s="4" t="inlineStr">
@@ -4660,142 +4660,142 @@
       </c>
       <c r="C130" s="4" t="inlineStr">
         <is>
-          <t>GD225/50R17</t>
+          <t>GD225/45R18RF</t>
         </is>
       </c>
       <c r="D130" s="5">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E130" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F130" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G130" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H130" s="6">
-        <v>500</v>
+        <v>720</v>
       </c>
     </row>
     <row outlineLevel="0" r="131">
       <c r="A131" s="4" t="inlineStr">
         <is>
-          <t>225/50R17</t>
+          <t>225/45R19</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>HK225/50R17</t>
+          <t>CT225/45R19</t>
         </is>
       </c>
       <c r="D131" s="5">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E131" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F131" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G131" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H131" s="6">
-        <v>400</v>
+        <v>780</v>
       </c>
     </row>
     <row outlineLevel="0" r="132">
       <c r="A132" s="4" t="inlineStr">
         <is>
-          <t>225/55R16</t>
+          <t>225/50R17</t>
         </is>
       </c>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C132" s="4" t="inlineStr">
         <is>
-          <t>DL225/55R16</t>
+          <t>GD225/50R17</t>
         </is>
       </c>
       <c r="D132" s="5">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E132" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F132" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G132" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H132" s="6">
-        <v>450</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="133">
       <c r="A133" s="4" t="inlineStr">
         <is>
-          <t>225/55R16</t>
+          <t>225/50R17</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>GD225/55R16</t>
+          <t>HK225/50R17</t>
         </is>
       </c>
       <c r="D133" s="5">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E133" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F133" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G133" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H133" s="6">
-        <v>420</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="134">
       <c r="A134" s="4" t="inlineStr">
         <is>
-          <t>225/55R17</t>
+          <t>225/55R16</t>
         </is>
       </c>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C134" s="4" t="inlineStr">
         <is>
-          <t>HK225/55R17</t>
+          <t>DL225/55R16</t>
         </is>
       </c>
       <c r="D134" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E134" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F134" s="5">
         <v>0</v>
@@ -4804,13 +4804,13 @@
         <v>0</v>
       </c>
       <c r="H134" s="6">
-        <v>430</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="135">
       <c r="A135" s="4" t="inlineStr">
         <is>
-          <t>225/55R17RF</t>
+          <t>225/55R16</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
@@ -4820,29 +4820,29 @@
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>GD225/55R17RF</t>
+          <t>GD225/55R16</t>
         </is>
       </c>
       <c r="D135" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E135" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F135" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G135" s="5">
         <v>0</v>
       </c>
       <c r="H135" s="6">
-        <v>700</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="136">
       <c r="A136" s="4" t="inlineStr">
         <is>
-          <t>225/55R18</t>
+          <t>225/55R17</t>
         </is>
       </c>
       <c r="B136" s="4" t="inlineStr">
@@ -4852,14 +4852,14 @@
       </c>
       <c r="C136" s="4" t="inlineStr">
         <is>
-          <t>HK225/55R18</t>
+          <t>HK225/55R17</t>
         </is>
       </c>
       <c r="D136" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E136" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F136" s="5">
         <v>0</v>
@@ -4868,55 +4868,55 @@
         <v>0</v>
       </c>
       <c r="H136" s="6">
-        <v>500</v>
+        <v>430</v>
       </c>
     </row>
     <row outlineLevel="0" r="137">
       <c r="A137" s="4" t="inlineStr">
         <is>
-          <t>225/55R18</t>
+          <t>225/55R17RF</t>
         </is>
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>KUMHO</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>KM225/55R18</t>
+          <t>GD225/55R17RF</t>
         </is>
       </c>
       <c r="D137" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E137" s="5">
         <v>4</v>
       </c>
       <c r="F137" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G137" s="5">
         <v>0</v>
       </c>
       <c r="H137" s="6">
-        <v>450</v>
+        <v>700</v>
       </c>
     </row>
     <row outlineLevel="0" r="138">
       <c r="A138" s="4" t="inlineStr">
         <is>
-          <t>225/55R19</t>
+          <t>225/55R18</t>
         </is>
       </c>
       <c r="B138" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C138" s="4" t="inlineStr">
         <is>
-          <t>BR225/55R19</t>
+          <t>HK225/55R18</t>
         </is>
       </c>
       <c r="D138" s="5">
@@ -4932,23 +4932,23 @@
         <v>0</v>
       </c>
       <c r="H138" s="6">
-        <v>750</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="139">
       <c r="A139" s="4" t="inlineStr">
         <is>
-          <t>225/55R19</t>
+          <t>225/55R18</t>
         </is>
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>KUMHO</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>GD225/55R19</t>
+          <t>KM225/55R18</t>
         </is>
       </c>
       <c r="D139" s="5">
@@ -4964,45 +4964,45 @@
         <v>0</v>
       </c>
       <c r="H139" s="6">
-        <v>750</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="140">
       <c r="A140" s="4" t="inlineStr">
         <is>
-          <t>225/60R17</t>
+          <t>225/55R19</t>
         </is>
       </c>
       <c r="B140" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C140" s="4" t="inlineStr">
         <is>
-          <t>HK225/60R17</t>
+          <t>BR225/55R19</t>
         </is>
       </c>
       <c r="D140" s="5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E140" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F140" s="5">
         <v>0</v>
       </c>
       <c r="G140" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H140" s="6">
-        <v>400</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="141">
       <c r="A141" s="4" t="inlineStr">
         <is>
-          <t>225/60R18</t>
+          <t>225/55R19</t>
         </is>
       </c>
       <c r="B141" s="4" t="inlineStr">
@@ -5012,14 +5012,14 @@
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>GD225/60R18</t>
+          <t>GD225/55R19</t>
         </is>
       </c>
       <c r="D141" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E141" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F141" s="5">
         <v>0</v>
@@ -5028,77 +5028,77 @@
         <v>0</v>
       </c>
       <c r="H141" s="6">
-        <v>700</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="142">
       <c r="A142" s="4" t="inlineStr">
         <is>
-          <t>225/65R17</t>
+          <t>225/60R17</t>
         </is>
       </c>
       <c r="B142" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C142" s="4" t="inlineStr">
         <is>
-          <t>RD225/65R17</t>
+          <t>HK225/60R17</t>
         </is>
       </c>
       <c r="D142" s="5">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E142" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F142" s="5">
         <v>0</v>
       </c>
       <c r="G142" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H142" s="6">
-        <v>450</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="143">
       <c r="A143" s="4" t="inlineStr">
         <is>
-          <t>225/75R15C</t>
+          <t>225/60R18</t>
         </is>
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>RD225/75R15C</t>
+          <t>GD225/60R18</t>
         </is>
       </c>
       <c r="D143" s="5">
         <v>1</v>
       </c>
       <c r="E143" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F143" s="5">
         <v>0</v>
       </c>
       <c r="G143" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H143" s="6">
-        <v>330</v>
+        <v>700</v>
       </c>
     </row>
     <row outlineLevel="0" r="144">
       <c r="A144" s="4" t="inlineStr">
         <is>
-          <t>235/35R19</t>
+          <t>225/65R17</t>
         </is>
       </c>
       <c r="B144" s="4" t="inlineStr">
@@ -5108,81 +5108,81 @@
       </c>
       <c r="C144" s="4" t="inlineStr">
         <is>
-          <t>RD235/35R19</t>
+          <t>RD225/65R17</t>
         </is>
       </c>
       <c r="D144" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E144" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F144" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G144" s="5">
         <v>0</v>
       </c>
       <c r="H144" s="6">
-        <v>600</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="145">
       <c r="A145" s="4" t="inlineStr">
         <is>
-          <t>235/40R19</t>
+          <t>225/75R15C</t>
         </is>
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>GD235/40R19</t>
+          <t>RD225/75R15C</t>
         </is>
       </c>
       <c r="D145" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E145" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F145" s="5">
         <v>0</v>
       </c>
       <c r="G145" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H145" s="6">
-        <v>850</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="146">
       <c r="A146" s="4" t="inlineStr">
         <is>
-          <t>235/45R18</t>
+          <t>235/35R19</t>
         </is>
       </c>
       <c r="B146" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C146" s="4" t="inlineStr">
         <is>
-          <t>GD235/45R18</t>
+          <t>RD235/35R19</t>
         </is>
       </c>
       <c r="D146" s="5">
         <v>4</v>
       </c>
       <c r="E146" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F146" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G146" s="5">
         <v>0</v>
@@ -5194,24 +5194,24 @@
     <row outlineLevel="0" r="147">
       <c r="A147" s="4" t="inlineStr">
         <is>
-          <t>235/50R18</t>
+          <t>235/40R19</t>
         </is>
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>HK235/50R18</t>
+          <t>GD235/40R19</t>
         </is>
       </c>
       <c r="D147" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E147" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F147" s="5">
         <v>0</v>
@@ -5220,13 +5220,13 @@
         <v>0</v>
       </c>
       <c r="H147" s="6">
-        <v>500</v>
+        <v>850</v>
       </c>
     </row>
     <row outlineLevel="0" r="148">
       <c r="A148" s="4" t="inlineStr">
         <is>
-          <t>235/50R19</t>
+          <t>235/45R18</t>
         </is>
       </c>
       <c r="B148" s="4" t="inlineStr">
@@ -5236,7 +5236,7 @@
       </c>
       <c r="C148" s="4" t="inlineStr">
         <is>
-          <t>GD235/50R19</t>
+          <t>GD235/45R18</t>
         </is>
       </c>
       <c r="D148" s="5">
@@ -5252,62 +5252,62 @@
         <v>0</v>
       </c>
       <c r="H148" s="6">
-        <v>800</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="149">
       <c r="A149" s="4" t="inlineStr">
         <is>
-          <t>235/50R20</t>
+          <t>235/50R18</t>
         </is>
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>GD235/50R20</t>
+          <t>HK235/50R18</t>
         </is>
       </c>
       <c r="D149" s="5">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E149" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F149" s="5">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G149" s="5">
         <v>0</v>
       </c>
       <c r="H149" s="6">
-        <v>1180</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="150">
       <c r="A150" s="4" t="inlineStr">
         <is>
-          <t>235/55R17</t>
+          <t>235/50R19</t>
         </is>
       </c>
       <c r="B150" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C150" s="4" t="inlineStr">
         <is>
-          <t>BR235/55R17</t>
+          <t>GD235/50R19</t>
         </is>
       </c>
       <c r="D150" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E150" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F150" s="5">
         <v>0</v>
@@ -5316,62 +5316,62 @@
         <v>0</v>
       </c>
       <c r="H150" s="6">
-        <v>450</v>
+        <v>800</v>
       </c>
     </row>
     <row outlineLevel="0" r="151">
       <c r="A151" s="4" t="inlineStr">
         <is>
-          <t>235/55R18</t>
+          <t>235/50R20</t>
         </is>
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>HK235/55R18</t>
+          <t>GD235/50R20</t>
         </is>
       </c>
       <c r="D151" s="5">
         <v>7</v>
       </c>
       <c r="E151" s="5">
+        <v>0</v>
+      </c>
+      <c r="F151" s="5">
         <v>7</v>
       </c>
-      <c r="F151" s="5">
-        <v>0</v>
-      </c>
       <c r="G151" s="5">
         <v>0</v>
       </c>
       <c r="H151" s="6">
-        <v>480</v>
+        <v>1180</v>
       </c>
     </row>
     <row outlineLevel="0" r="152">
       <c r="A152" s="4" t="inlineStr">
         <is>
-          <t>235/55R19</t>
+          <t>235/55R17</t>
         </is>
       </c>
       <c r="B152" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C152" s="4" t="inlineStr">
         <is>
-          <t>GD235/55R19</t>
+          <t>BR235/55R17</t>
         </is>
       </c>
       <c r="D152" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E152" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F152" s="5">
         <v>0</v>
@@ -5380,13 +5380,13 @@
         <v>0</v>
       </c>
       <c r="H152" s="6">
-        <v>750</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="153">
       <c r="A153" s="4" t="inlineStr">
         <is>
-          <t>235/55R19</t>
+          <t>235/55R18</t>
         </is>
       </c>
       <c r="B153" s="4" t="inlineStr">
@@ -5396,14 +5396,14 @@
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>HK235/55R19</t>
+          <t>HK235/55R18</t>
         </is>
       </c>
       <c r="D153" s="5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E153" s="5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F153" s="5">
         <v>0</v>
@@ -5412,7 +5412,7 @@
         <v>0</v>
       </c>
       <c r="H153" s="6">
-        <v>630</v>
+        <v>480</v>
       </c>
     </row>
     <row outlineLevel="0" r="154">
@@ -5423,19 +5423,19 @@
       </c>
       <c r="B154" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C154" s="4" t="inlineStr">
         <is>
-          <t>LF235/55R19</t>
+          <t>GD235/55R19</t>
         </is>
       </c>
       <c r="D154" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E154" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F154" s="5">
         <v>0</v>
@@ -5444,7 +5444,7 @@
         <v>0</v>
       </c>
       <c r="H154" s="6">
-        <v>500</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="155">
@@ -5455,19 +5455,19 @@
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>NX235/55R19</t>
+          <t>HK235/55R19</t>
         </is>
       </c>
       <c r="D155" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E155" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F155" s="5">
         <v>0</v>
@@ -5476,7 +5476,7 @@
         <v>0</v>
       </c>
       <c r="H155" s="6">
-        <v>600</v>
+        <v>630</v>
       </c>
     </row>
     <row outlineLevel="0" r="156">
@@ -5487,22 +5487,22 @@
       </c>
       <c r="B156" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C156" s="4" t="inlineStr">
         <is>
-          <t>RD235/55R19</t>
+          <t>LF235/55R19</t>
         </is>
       </c>
       <c r="D156" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E156" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F156" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G156" s="5">
         <v>0</v>
@@ -5514,24 +5514,24 @@
     <row outlineLevel="0" r="157">
       <c r="A157" s="4" t="inlineStr">
         <is>
-          <t>235/60R16</t>
+          <t>235/55R19</t>
         </is>
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>HK235/60R16</t>
+          <t>NX235/55R19</t>
         </is>
       </c>
       <c r="D157" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E157" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F157" s="5">
         <v>0</v>
@@ -5540,33 +5540,33 @@
         <v>0</v>
       </c>
       <c r="H157" s="6">
-        <v>430</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="158">
       <c r="A158" s="4" t="inlineStr">
         <is>
-          <t>235/60R17</t>
+          <t>235/55R19</t>
         </is>
       </c>
       <c r="B158" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C158" s="4" t="inlineStr">
         <is>
-          <t>HK235/60R17</t>
+          <t>RD235/55R19</t>
         </is>
       </c>
       <c r="D158" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E158" s="5">
         <v>0</v>
       </c>
       <c r="F158" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G158" s="5">
         <v>0</v>
@@ -5578,24 +5578,24 @@
     <row outlineLevel="0" r="159">
       <c r="A159" s="4" t="inlineStr">
         <is>
-          <t>235/60R18</t>
+          <t>235/60R16</t>
         </is>
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>GD235/60R18</t>
+          <t>HK235/60R16</t>
         </is>
       </c>
       <c r="D159" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E159" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F159" s="5">
         <v>0</v>
@@ -5604,13 +5604,13 @@
         <v>0</v>
       </c>
       <c r="H159" s="6">
-        <v>680</v>
+        <v>430</v>
       </c>
     </row>
     <row outlineLevel="0" r="160">
       <c r="A160" s="4" t="inlineStr">
         <is>
-          <t>235/60R18</t>
+          <t>235/60R17</t>
         </is>
       </c>
       <c r="B160" s="4" t="inlineStr">
@@ -5620,29 +5620,29 @@
       </c>
       <c r="C160" s="4" t="inlineStr">
         <is>
-          <t>HK235/60R18</t>
+          <t>HK235/60R17</t>
         </is>
       </c>
       <c r="D160" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E160" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F160" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G160" s="5">
         <v>0</v>
       </c>
       <c r="H160" s="6">
-        <v>550</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="161">
       <c r="A161" s="4" t="inlineStr">
         <is>
-          <t>245/40R17</t>
+          <t>235/60R18</t>
         </is>
       </c>
       <c r="B161" s="4" t="inlineStr">
@@ -5652,14 +5652,14 @@
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>GD245/40R17</t>
+          <t>GD235/60R18</t>
         </is>
       </c>
       <c r="D161" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E161" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F161" s="5">
         <v>0</v>
@@ -5668,27 +5668,27 @@
         <v>0</v>
       </c>
       <c r="H161" s="6">
-        <v>400</v>
+        <v>680</v>
       </c>
     </row>
     <row outlineLevel="0" r="162">
       <c r="A162" s="4" t="inlineStr">
         <is>
-          <t>245/40R18</t>
+          <t>235/60R18</t>
         </is>
       </c>
       <c r="B162" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C162" s="4" t="inlineStr">
         <is>
-          <t>GD245/40R18</t>
+          <t>HK235/60R18</t>
         </is>
       </c>
       <c r="D162" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E162" s="5">
         <v>2</v>
@@ -5697,33 +5697,33 @@
         <v>0</v>
       </c>
       <c r="G162" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H162" s="6">
-        <v>620</v>
+        <v>550</v>
       </c>
     </row>
     <row outlineLevel="0" r="163">
       <c r="A163" s="4" t="inlineStr">
         <is>
-          <t>245/40R19</t>
+          <t>245/40R17</t>
         </is>
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>HK245/40R19</t>
+          <t>GD245/40R17</t>
         </is>
       </c>
       <c r="D163" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E163" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F163" s="5">
         <v>0</v>
@@ -5732,45 +5732,45 @@
         <v>0</v>
       </c>
       <c r="H163" s="6">
-        <v>750</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="164">
       <c r="A164" s="4" t="inlineStr">
         <is>
-          <t>245/40R20</t>
+          <t>245/40R18</t>
         </is>
       </c>
       <c r="B164" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C164" s="4" t="inlineStr">
         <is>
-          <t>CT245/40R20</t>
+          <t>GD245/40R18</t>
         </is>
       </c>
       <c r="D164" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E164" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F164" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G164" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H164" s="6">
-        <v>1050</v>
+        <v>620</v>
       </c>
     </row>
     <row outlineLevel="0" r="165">
       <c r="A165" s="4" t="inlineStr">
         <is>
-          <t>245/45R17</t>
+          <t>245/40R19</t>
         </is>
       </c>
       <c r="B165" s="4" t="inlineStr">
@@ -5780,7 +5780,7 @@
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>HK245/45R17</t>
+          <t>HK245/40R19</t>
         </is>
       </c>
       <c r="D165" s="5">
@@ -5796,13 +5796,13 @@
         <v>0</v>
       </c>
       <c r="H165" s="6">
-        <v>430</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="166">
       <c r="A166" s="4" t="inlineStr">
         <is>
-          <t>245/45R18</t>
+          <t>245/40R20</t>
         </is>
       </c>
       <c r="B166" s="4" t="inlineStr">
@@ -5812,46 +5812,46 @@
       </c>
       <c r="C166" s="4" t="inlineStr">
         <is>
-          <t>CT245/45R18</t>
+          <t>CT245/40R20</t>
         </is>
       </c>
       <c r="D166" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E166" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F166" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G166" s="5">
         <v>0</v>
       </c>
       <c r="H166" s="6">
-        <v>650</v>
+        <v>1050</v>
       </c>
     </row>
     <row outlineLevel="0" r="167">
       <c r="A167" s="4" t="inlineStr">
         <is>
-          <t>245/45R18</t>
+          <t>245/45R17</t>
         </is>
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>GD245/45R18</t>
+          <t>HK245/45R17</t>
         </is>
       </c>
       <c r="D167" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E167" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F167" s="5">
         <v>0</v>
@@ -5860,7 +5860,7 @@
         <v>0</v>
       </c>
       <c r="H167" s="6">
-        <v>600</v>
+        <v>430</v>
       </c>
     </row>
     <row outlineLevel="0" r="168">
@@ -5871,12 +5871,12 @@
       </c>
       <c r="B168" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C168" s="4" t="inlineStr">
         <is>
-          <t>HK245/45R18</t>
+          <t>CT245/45R18</t>
         </is>
       </c>
       <c r="D168" s="5">
@@ -5892,13 +5892,13 @@
         <v>0</v>
       </c>
       <c r="H168" s="6">
-        <v>500</v>
+        <v>650</v>
       </c>
     </row>
     <row outlineLevel="0" r="169">
       <c r="A169" s="4" t="inlineStr">
         <is>
-          <t>245/45R18RF</t>
+          <t>245/45R18</t>
         </is>
       </c>
       <c r="B169" s="4" t="inlineStr">
@@ -5908,14 +5908,14 @@
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>GD245/45R18RF</t>
+          <t>GD245/45R18</t>
         </is>
       </c>
       <c r="D169" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E169" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F169" s="5">
         <v>0</v>
@@ -5924,30 +5924,30 @@
         <v>0</v>
       </c>
       <c r="H169" s="6">
-        <v>720</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="170">
       <c r="A170" s="4" t="inlineStr">
         <is>
-          <t>245/45R19</t>
+          <t>245/45R18</t>
         </is>
       </c>
       <c r="B170" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C170" s="4" t="inlineStr">
         <is>
-          <t>BR245/45R19</t>
+          <t>HK245/45R18</t>
         </is>
       </c>
       <c r="D170" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E170" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F170" s="5">
         <v>0</v>
@@ -5956,119 +5956,119 @@
         <v>0</v>
       </c>
       <c r="H170" s="6">
-        <v>790</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="171">
       <c r="A171" s="4" t="inlineStr">
         <is>
-          <t>245/45R19</t>
+          <t>245/45R18RF</t>
         </is>
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t>RD245/45R19</t>
+          <t>GD245/45R18RF</t>
         </is>
       </c>
       <c r="D171" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E171" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F171" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G171" s="5">
         <v>0</v>
       </c>
       <c r="H171" s="6">
-        <v>450</v>
+        <v>720</v>
       </c>
     </row>
     <row outlineLevel="0" r="172">
       <c r="A172" s="4" t="inlineStr">
         <is>
-          <t>245/45R20</t>
+          <t>245/45R19</t>
         </is>
       </c>
       <c r="B172" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C172" s="4" t="inlineStr">
         <is>
-          <t>HK245/45R20</t>
+          <t>BR245/45R19</t>
         </is>
       </c>
       <c r="D172" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E172" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F172" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G172" s="5">
         <v>0</v>
       </c>
       <c r="H172" s="6">
-        <v>750</v>
+        <v>790</v>
       </c>
     </row>
     <row outlineLevel="0" r="173">
       <c r="A173" s="4" t="inlineStr">
         <is>
-          <t>245/65R17</t>
+          <t>245/45R19</t>
         </is>
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>NX245/65R17</t>
+          <t>RD245/45R19</t>
         </is>
       </c>
       <c r="D173" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E173" s="5">
         <v>0</v>
       </c>
       <c r="F173" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G173" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H173" s="6">
-        <v>600</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="174">
       <c r="A174" s="4" t="inlineStr">
         <is>
-          <t>245/70R16</t>
+          <t>245/45R20</t>
         </is>
       </c>
       <c r="B174" s="4" t="inlineStr">
         <is>
-          <t>LASSA</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C174" s="4" t="inlineStr">
         <is>
-          <t>LS245/70R16</t>
+          <t>HK245/45R20</t>
         </is>
       </c>
       <c r="D174" s="5">
@@ -6078,93 +6078,93 @@
         <v>0</v>
       </c>
       <c r="F174" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G174" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H174" s="6">
-        <v>500</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="175">
       <c r="A175" s="4" t="inlineStr">
         <is>
-          <t>255/35R19</t>
+          <t>245/65R17</t>
         </is>
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>DL255/35R19</t>
+          <t>NX245/65R17</t>
         </is>
       </c>
       <c r="D175" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E175" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F175" s="5">
         <v>0</v>
       </c>
       <c r="G175" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H175" s="6">
-        <v>700</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="176">
       <c r="A176" s="4" t="inlineStr">
         <is>
-          <t>255/35R19RF</t>
+          <t>245/70R16</t>
         </is>
       </c>
       <c r="B176" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>LASSA</t>
         </is>
       </c>
       <c r="C176" s="4" t="inlineStr">
         <is>
-          <t>CT255/35R19RF</t>
+          <t>LS245/70R16</t>
         </is>
       </c>
       <c r="D176" s="5">
         <v>2</v>
       </c>
       <c r="E176" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F176" s="5">
         <v>0</v>
       </c>
       <c r="G176" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H176" s="6">
-        <v>950</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="177">
       <c r="A177" s="4" t="inlineStr">
         <is>
-          <t>255/35R19RF</t>
+          <t>255/35R19</t>
         </is>
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>GD255/35R19RF</t>
+          <t>DL255/35R19</t>
         </is>
       </c>
       <c r="D177" s="5">
@@ -6180,13 +6180,13 @@
         <v>0</v>
       </c>
       <c r="H177" s="6">
-        <v>950</v>
+        <v>700</v>
       </c>
     </row>
     <row outlineLevel="0" r="178">
       <c r="A178" s="4" t="inlineStr">
         <is>
-          <t>255/50R19</t>
+          <t>255/35R19RF</t>
         </is>
       </c>
       <c r="B178" s="4" t="inlineStr">
@@ -6196,61 +6196,61 @@
       </c>
       <c r="C178" s="4" t="inlineStr">
         <is>
-          <t>CT255/50R19</t>
+          <t>CT255/35R19RF</t>
         </is>
       </c>
       <c r="D178" s="5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E178" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F178" s="5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G178" s="5">
         <v>0</v>
       </c>
       <c r="H178" s="6">
-        <v>750</v>
+        <v>950</v>
       </c>
     </row>
     <row outlineLevel="0" r="179">
       <c r="A179" s="4" t="inlineStr">
         <is>
-          <t>255/50R20</t>
+          <t>255/35R19RF</t>
         </is>
       </c>
       <c r="B179" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C179" s="4" t="inlineStr">
         <is>
-          <t>CT255/50R20</t>
+          <t>GD255/35R19RF</t>
         </is>
       </c>
       <c r="D179" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E179" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F179" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G179" s="5">
         <v>0</v>
       </c>
       <c r="H179" s="6">
-        <v>900</v>
+        <v>950</v>
       </c>
     </row>
     <row outlineLevel="0" r="180">
       <c r="A180" s="4" t="inlineStr">
         <is>
-          <t>255/55R19</t>
+          <t>255/50R19</t>
         </is>
       </c>
       <c r="B180" s="4" t="inlineStr">
@@ -6260,17 +6260,17 @@
       </c>
       <c r="C180" s="4" t="inlineStr">
         <is>
-          <t>CT255/55R19</t>
+          <t>CT255/50R19</t>
         </is>
       </c>
       <c r="D180" s="5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E180" s="5">
         <v>0</v>
       </c>
       <c r="F180" s="5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G180" s="5">
         <v>0</v>
@@ -6282,49 +6282,49 @@
     <row outlineLevel="0" r="181">
       <c r="A181" s="4" t="inlineStr">
         <is>
-          <t>255/55R19</t>
+          <t>255/50R20</t>
         </is>
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C181" s="4" t="inlineStr">
         <is>
-          <t>DL255/55R19</t>
+          <t>CT255/50R20</t>
         </is>
       </c>
       <c r="D181" s="5">
         <v>2</v>
       </c>
       <c r="E181" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F181" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G181" s="5">
         <v>0</v>
       </c>
       <c r="H181" s="6">
-        <v>700</v>
+        <v>900</v>
       </c>
     </row>
     <row outlineLevel="0" r="182">
       <c r="A182" s="4" t="inlineStr">
         <is>
-          <t>255/70R16</t>
+          <t>255/55R19</t>
         </is>
       </c>
       <c r="B182" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C182" s="4" t="inlineStr">
         <is>
-          <t>RD255/70R16</t>
+          <t>CT255/55R19</t>
         </is>
       </c>
       <c r="D182" s="5">
@@ -6334,36 +6334,36 @@
         <v>0</v>
       </c>
       <c r="F182" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G182" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H182" s="6">
-        <v>500</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="183">
       <c r="A183" s="4" t="inlineStr">
         <is>
-          <t>265/35R18</t>
+          <t>255/55R19</t>
         </is>
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C183" s="4" t="inlineStr">
         <is>
-          <t>GD265/35R18</t>
+          <t>DL255/55R19</t>
         </is>
       </c>
       <c r="D183" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E183" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F183" s="5">
         <v>0</v>
@@ -6378,39 +6378,39 @@
     <row outlineLevel="0" r="184">
       <c r="A184" s="4" t="inlineStr">
         <is>
-          <t>265/50R20</t>
+          <t>255/70R16</t>
         </is>
       </c>
       <c r="B184" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C184" s="4" t="inlineStr">
         <is>
-          <t>GD265/50R20</t>
+          <t>RD255/70R16</t>
         </is>
       </c>
       <c r="D184" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E184" s="5">
         <v>0</v>
       </c>
       <c r="F184" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G184" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H184" s="6">
-        <v>1150</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="185">
       <c r="A185" s="4" t="inlineStr">
         <is>
-          <t>275/35R19RF</t>
+          <t>265/35R18</t>
         </is>
       </c>
       <c r="B185" s="4" t="inlineStr">
@@ -6420,14 +6420,14 @@
       </c>
       <c r="C185" s="4" t="inlineStr">
         <is>
-          <t>GD275/35R19RF</t>
+          <t>GD265/35R18</t>
         </is>
       </c>
       <c r="D185" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E185" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F185" s="5">
         <v>0</v>
@@ -6436,87 +6436,87 @@
         <v>0</v>
       </c>
       <c r="H185" s="6">
-        <v>1</v>
+        <v>700</v>
       </c>
     </row>
     <row outlineLevel="0" r="186">
       <c r="A186" s="4" t="inlineStr">
         <is>
-          <t>275/35R20</t>
+          <t>265/50R20</t>
         </is>
       </c>
       <c r="B186" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C186" s="4" t="inlineStr">
         <is>
-          <t>CT275/35R20</t>
+          <t>GD265/50R20</t>
         </is>
       </c>
       <c r="D186" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E186" s="5">
         <v>0</v>
       </c>
       <c r="F186" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G186" s="5">
         <v>0</v>
       </c>
       <c r="H186" s="6">
-        <v>980</v>
+        <v>1150</v>
       </c>
     </row>
     <row outlineLevel="0" r="187">
       <c r="A187" s="4" t="inlineStr">
         <is>
-          <t>275/40R20</t>
+          <t>275/35R19RF</t>
         </is>
       </c>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C187" s="4" t="inlineStr">
         <is>
-          <t>HK275/40R20</t>
+          <t>GD275/35R19RF</t>
         </is>
       </c>
       <c r="D187" s="5">
         <v>2</v>
       </c>
       <c r="E187" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F187" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G187" s="5">
         <v>0</v>
       </c>
       <c r="H187" s="6">
-        <v>770</v>
+        <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="188">
       <c r="A188" s="4" t="inlineStr">
         <is>
-          <t>275/50R21</t>
+          <t>275/35R20</t>
         </is>
       </c>
       <c r="B188" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C188" s="4" t="inlineStr">
         <is>
-          <t>GD275/50R21</t>
+          <t>CT275/35R20</t>
         </is>
       </c>
       <c r="D188" s="5">
@@ -6532,23 +6532,23 @@
         <v>0</v>
       </c>
       <c r="H188" s="6">
-        <v>1</v>
+        <v>980</v>
       </c>
     </row>
     <row outlineLevel="0" r="189">
       <c r="A189" s="4" t="inlineStr">
         <is>
-          <t>295/35R21</t>
+          <t>275/40R20</t>
         </is>
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C189" s="4" t="inlineStr">
         <is>
-          <t>CT295/35R21</t>
+          <t>HK275/40R20</t>
         </is>
       </c>
       <c r="D189" s="5">
@@ -6564,13 +6564,13 @@
         <v>0</v>
       </c>
       <c r="H189" s="6">
-        <v>1150</v>
+        <v>770</v>
       </c>
     </row>
     <row outlineLevel="0" r="190">
       <c r="A190" s="4" t="inlineStr">
         <is>
-          <t>295/35R21</t>
+          <t>275/50R21</t>
         </is>
       </c>
       <c r="B190" s="4" t="inlineStr">
@@ -6580,54 +6580,118 @@
       </c>
       <c r="C190" s="4" t="inlineStr">
         <is>
-          <t>GD295/35R21</t>
+          <t>GD275/50R21</t>
         </is>
       </c>
       <c r="D190" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E190" s="5">
         <v>0</v>
       </c>
       <c r="F190" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G190" s="5">
         <v>0</v>
       </c>
       <c r="H190" s="6">
-        <v>980</v>
+        <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="191">
       <c r="A191" s="4" t="inlineStr">
         <is>
+          <t>295/35R21</t>
+        </is>
+      </c>
+      <c r="B191" s="4" t="inlineStr">
+        <is>
+          <t>CONTINENTAL</t>
+        </is>
+      </c>
+      <c r="C191" s="4" t="inlineStr">
+        <is>
+          <t>CT295/35R21</t>
+        </is>
+      </c>
+      <c r="D191" s="5">
+        <v>2</v>
+      </c>
+      <c r="E191" s="5">
+        <v>0</v>
+      </c>
+      <c r="F191" s="5">
+        <v>2</v>
+      </c>
+      <c r="G191" s="5">
+        <v>0</v>
+      </c>
+      <c r="H191" s="6">
+        <v>1150</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="192">
+      <c r="A192" s="4" t="inlineStr">
+        <is>
+          <t>295/35R21</t>
+        </is>
+      </c>
+      <c r="B192" s="4" t="inlineStr">
+        <is>
+          <t>GOODYEAR</t>
+        </is>
+      </c>
+      <c r="C192" s="4" t="inlineStr">
+        <is>
+          <t>GD295/35R21</t>
+        </is>
+      </c>
+      <c r="D192" s="5">
+        <v>3</v>
+      </c>
+      <c r="E192" s="5">
+        <v>0</v>
+      </c>
+      <c r="F192" s="5">
+        <v>3</v>
+      </c>
+      <c r="G192" s="5">
+        <v>0</v>
+      </c>
+      <c r="H192" s="6">
+        <v>980</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="193">
+      <c r="A193" s="4" t="inlineStr">
+        <is>
           <t>500R12</t>
         </is>
       </c>
-      <c r="B191" s="4" t="inlineStr">
+      <c r="B193" s="4" t="inlineStr">
         <is>
           <t>RADIAL</t>
         </is>
       </c>
-      <c r="C191" s="4" t="inlineStr">
+      <c r="C193" s="4" t="inlineStr">
         <is>
           <t>RD500R12</t>
         </is>
       </c>
-      <c r="D191" s="5">
+      <c r="D193" s="5">
         <v>3</v>
       </c>
-      <c r="E191" s="5">
+      <c r="E193" s="5">
         <v>3</v>
       </c>
-      <c r="F191" s="5">
-        <v>0</v>
-      </c>
-      <c r="G191" s="5">
-        <v>0</v>
-      </c>
-      <c r="H191" s="6">
+      <c r="F193" s="5">
+        <v>0</v>
+      </c>
+      <c r="G193" s="5">
+        <v>0</v>
+      </c>
+      <c r="H193" s="6">
         <v>300</v>
       </c>
     </row>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -496,7 +496,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H193"/>
+  <dimension ref="A1:H192"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col customWidth="true" min="1" max="1" width="13.8359375"/>
@@ -923,13 +923,13 @@
         <v>10</v>
       </c>
       <c r="E13" s="5">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F13" s="5">
         <v>0</v>
       </c>
       <c r="G13" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H13" s="6">
         <v>230</v>
@@ -1435,13 +1435,13 @@
         <v>10</v>
       </c>
       <c r="E29" s="5">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F29" s="5">
         <v>0</v>
       </c>
       <c r="G29" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H29" s="6">
         <v>230</v>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="D31" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E31" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F31" s="5">
         <v>0</v>
@@ -1816,10 +1816,10 @@
         </is>
       </c>
       <c r="D41" s="5">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E41" s="5">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F41" s="5">
         <v>0</v>
@@ -1944,7 +1944,7 @@
         </is>
       </c>
       <c r="D45" s="5">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E45" s="5">
         <v>4</v>
@@ -1953,7 +1953,7 @@
         <v>15</v>
       </c>
       <c r="G45" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H45" s="6">
         <v>260</v>
@@ -1976,7 +1976,7 @@
         </is>
       </c>
       <c r="D46" s="5">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E46" s="5">
         <v>8</v>
@@ -1985,7 +1985,7 @@
         <v>0</v>
       </c>
       <c r="G46" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H46" s="6">
         <v>225</v>
@@ -2040,16 +2040,16 @@
         </is>
       </c>
       <c r="D48" s="5">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E48" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F48" s="5">
         <v>13</v>
       </c>
       <c r="G48" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H48" s="6">
         <v>350</v>
@@ -2200,10 +2200,10 @@
         </is>
       </c>
       <c r="D53" s="5">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E53" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F53" s="5">
         <v>27</v>
@@ -2296,10 +2296,10 @@
         </is>
       </c>
       <c r="D56" s="5">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E56" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F56" s="5">
         <v>0</v>
@@ -2442,65 +2442,65 @@
     <row outlineLevel="0" r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>195/70R15C</t>
+          <t>195/75R16C</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>DAYTON</t>
+          <t>GOODRIDE</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>DT195/70R15C</t>
+          <t>GR195/75R16C</t>
         </is>
       </c>
       <c r="D61" s="5">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E61" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F61" s="5">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G61" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H61" s="6">
-        <v>280</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>195/75R16C</t>
+          <t>205/45R17</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>GOODRIDE</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>GR195/75R16C</t>
+          <t>CT205/45R17</t>
         </is>
       </c>
       <c r="D62" s="5">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E62" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F62" s="5">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G62" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H62" s="6">
-        <v>350</v>
+        <v>550</v>
       </c>
     </row>
     <row outlineLevel="0" r="63">
@@ -2511,28 +2511,28 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>FULDA</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>CT205/45R17</t>
+          <t>FL205/45R17</t>
         </is>
       </c>
       <c r="D63" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E63" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F63" s="5">
         <v>0</v>
       </c>
       <c r="G63" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H63" s="6">
-        <v>550</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="64">
@@ -2543,28 +2543,28 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>FULDA</t>
+          <t>GOODRIDE</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>FL205/45R17</t>
+          <t>GR205/45R17</t>
         </is>
       </c>
       <c r="D64" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E64" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F64" s="5">
         <v>0</v>
       </c>
       <c r="G64" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H64" s="6">
-        <v>380</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="65">
@@ -2575,28 +2575,28 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>GOODRIDE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>GR205/45R17</t>
+          <t>GD205/45R17</t>
         </is>
       </c>
       <c r="D65" s="5">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="E65" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F65" s="5">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G65" s="5">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H65" s="6">
-        <v>300</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="66">
@@ -2607,28 +2607,28 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>GD205/45R17</t>
+          <t>NX205/45R17</t>
         </is>
       </c>
       <c r="D66" s="5">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="E66" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F66" s="5">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G66" s="5">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H66" s="6">
-        <v>450</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="67">
@@ -2639,83 +2639,83 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>NX205/45R17</t>
+          <t>RD205/45R17</t>
         </is>
       </c>
       <c r="D67" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E67" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F67" s="5">
         <v>0</v>
       </c>
       <c r="G67" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H67" s="6">
-        <v>380</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>205/45R17</t>
+          <t>205/50R17</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>RD205/45R17</t>
+          <t>CT205/50R17</t>
         </is>
       </c>
       <c r="D68" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E68" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F68" s="5">
         <v>0</v>
       </c>
       <c r="G68" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H68" s="6">
-        <v>300</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>205/50R17</t>
+          <t>205/55R16</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>AMINE</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>CT205/50R17</t>
+          <t>AM205/55R16</t>
         </is>
       </c>
       <c r="D69" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E69" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F69" s="5">
         <v>0</v>
@@ -2724,7 +2724,7 @@
         <v>0</v>
       </c>
       <c r="H69" s="6">
-        <v>450</v>
+        <v>240</v>
       </c>
     </row>
     <row outlineLevel="0" r="70">
@@ -2735,28 +2735,28 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>AMINE</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>AM205/55R16</t>
+          <t>BR205/55R16</t>
         </is>
       </c>
       <c r="D70" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E70" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F70" s="5">
         <v>0</v>
       </c>
       <c r="G70" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H70" s="6">
-        <v>240</v>
+        <v>290</v>
       </c>
     </row>
     <row outlineLevel="0" r="71">
@@ -2767,28 +2767,28 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>DOUBLESTAR</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>BR205/55R16</t>
+          <t>DS205/55R16</t>
         </is>
       </c>
       <c r="D71" s="5">
         <v>4</v>
       </c>
       <c r="E71" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F71" s="5">
         <v>0</v>
       </c>
       <c r="G71" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H71" s="6">
-        <v>290</v>
+        <v>230</v>
       </c>
     </row>
     <row outlineLevel="0" r="72">
@@ -2799,28 +2799,28 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>DOUBLESTAR</t>
+          <t>FULDA</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>DS205/55R16</t>
+          <t>FL205/55R16</t>
         </is>
       </c>
       <c r="D72" s="5">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="E72" s="5">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F72" s="5">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G72" s="5">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H72" s="6">
-        <v>230</v>
+        <v>250</v>
       </c>
     </row>
     <row outlineLevel="0" r="73">
@@ -2831,25 +2831,25 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>FULDA</t>
+          <t>GOODRIDE</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>FL205/55R16</t>
+          <t>GR205/55R16</t>
         </is>
       </c>
       <c r="D73" s="5">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="E73" s="5">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F73" s="5">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="G73" s="5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H73" s="6">
         <v>250</v>
@@ -2863,28 +2863,28 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>GOODRIDE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>GR205/55R16</t>
+          <t>GD205/55R16</t>
         </is>
       </c>
       <c r="D74" s="5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E74" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F74" s="5">
         <v>0</v>
       </c>
       <c r="G74" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H74" s="6">
-        <v>250</v>
+        <v>280</v>
       </c>
     </row>
     <row outlineLevel="0" r="75">
@@ -2895,28 +2895,28 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>GD205/55R16</t>
+          <t>HK205/55R16</t>
         </is>
       </c>
       <c r="D75" s="5">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E75" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F75" s="5">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G75" s="5">
         <v>4</v>
       </c>
       <c r="H75" s="6">
-        <v>280</v>
+        <v>260</v>
       </c>
     </row>
     <row outlineLevel="0" r="76">
@@ -2927,48 +2927,48 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>HK205/55R16</t>
+          <t>RD205/55R16</t>
         </is>
       </c>
       <c r="D76" s="5">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="E76" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F76" s="5">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G76" s="5">
         <v>4</v>
       </c>
       <c r="H76" s="6">
-        <v>260</v>
+        <v>230</v>
       </c>
     </row>
     <row outlineLevel="0" r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>205/55R16</t>
+          <t>205/55R16RF</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>RD205/55R16</t>
+          <t>GD205/55R16RF</t>
         </is>
       </c>
       <c r="D77" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E77" s="5">
         <v>0</v>
@@ -2977,16 +2977,16 @@
         <v>0</v>
       </c>
       <c r="G77" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H77" s="6">
-        <v>230</v>
+        <v>480</v>
       </c>
     </row>
     <row outlineLevel="0" r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>205/55R16RF</t>
+          <t>205/55R17</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
@@ -2996,23 +2996,23 @@
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>GD205/55R16RF</t>
+          <t>GD205/55R17</t>
         </is>
       </c>
       <c r="D78" s="5">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="E78" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F78" s="5">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G78" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H78" s="6">
-        <v>480</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="79">
@@ -3023,44 +3023,44 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>GD205/55R17</t>
+          <t>NX205/55R17</t>
         </is>
       </c>
       <c r="D79" s="5">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="E79" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F79" s="5">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G79" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H79" s="6">
-        <v>450</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>205/55R17</t>
+          <t>205/60R16</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>NX205/55R17</t>
+          <t>DL205/60R16</t>
         </is>
       </c>
       <c r="D80" s="5">
@@ -3076,7 +3076,7 @@
         <v>0</v>
       </c>
       <c r="H80" s="6">
-        <v>400</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="81">
@@ -3087,28 +3087,28 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>DL205/60R16</t>
+          <t>GD205/60R16</t>
         </is>
       </c>
       <c r="D81" s="5">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="E81" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F81" s="5">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G81" s="5">
         <v>0</v>
       </c>
       <c r="H81" s="6">
-        <v>330</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="82">
@@ -3119,28 +3119,28 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>GD205/60R16</t>
+          <t>HK205/60R16</t>
         </is>
       </c>
       <c r="D82" s="5">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E82" s="5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F82" s="5">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="G82" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H82" s="6">
-        <v>380</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="83">
@@ -3151,25 +3151,25 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>HK205/60R16</t>
+          <t>LF205/60R16</t>
         </is>
       </c>
       <c r="D83" s="5">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E83" s="5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F83" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G83" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H83" s="6">
         <v>300</v>
@@ -3178,17 +3178,17 @@
     <row outlineLevel="0" r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>205/60R16</t>
+          <t>205/65R15</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>LF205/60R16</t>
+          <t>HK205/65R15</t>
         </is>
       </c>
       <c r="D84" s="5">
@@ -3204,30 +3204,30 @@
         <v>0</v>
       </c>
       <c r="H84" s="6">
-        <v>300</v>
+        <v>270</v>
       </c>
     </row>
     <row outlineLevel="0" r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>205/65R15</t>
+          <t>205/65R16</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>HK205/65R15</t>
+          <t>BR205/65R16</t>
         </is>
       </c>
       <c r="D85" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E85" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F85" s="5">
         <v>0</v>
@@ -3236,7 +3236,7 @@
         <v>0</v>
       </c>
       <c r="H85" s="6">
-        <v>270</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="86">
@@ -3247,19 +3247,19 @@
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>BR205/65R16</t>
+          <t>HK205/65R16</t>
         </is>
       </c>
       <c r="D86" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E86" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F86" s="5">
         <v>0</v>
@@ -3268,39 +3268,39 @@
         <v>0</v>
       </c>
       <c r="H86" s="6">
-        <v>420</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>205/65R16</t>
+          <t>215/40R18</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>HK205/65R16</t>
+          <t>GD215/40R18</t>
         </is>
       </c>
       <c r="D87" s="5">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E87" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F87" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G87" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H87" s="6">
-        <v>380</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="88">
@@ -3311,44 +3311,44 @@
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>GD215/40R18</t>
+          <t>HK215/40R18</t>
         </is>
       </c>
       <c r="D88" s="5">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E88" s="5">
         <v>4</v>
       </c>
       <c r="F88" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G88" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H88" s="6">
-        <v>600</v>
+        <v>490</v>
       </c>
     </row>
     <row outlineLevel="0" r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>215/40R18</t>
+          <t>215/45R16</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>HK215/40R18</t>
+          <t>GD215/45R16</t>
         </is>
       </c>
       <c r="D89" s="5">
@@ -3364,13 +3364,13 @@
         <v>0</v>
       </c>
       <c r="H89" s="6">
-        <v>490</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>215/45R16</t>
+          <t>215/45R17</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
@@ -3380,14 +3380,14 @@
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>GD215/45R16</t>
+          <t>GD215/45R17</t>
         </is>
       </c>
       <c r="D90" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E90" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F90" s="5">
         <v>0</v>
@@ -3396,7 +3396,7 @@
         <v>0</v>
       </c>
       <c r="H90" s="6">
-        <v>450</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="91">
@@ -3407,25 +3407,25 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>GD215/45R17</t>
+          <t>HK215/45R17</t>
         </is>
       </c>
       <c r="D91" s="5">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E91" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F91" s="5">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G91" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H91" s="6">
         <v>400</v>
@@ -3439,28 +3439,28 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>IRIS</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>HK215/45R17</t>
+          <t>IR215/45R17</t>
         </is>
       </c>
       <c r="D92" s="5">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="E92" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F92" s="5">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G92" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H92" s="6">
-        <v>400</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="93">
@@ -3471,28 +3471,28 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>IRIS</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>IR215/45R17</t>
+          <t>LF215/45R17</t>
         </is>
       </c>
       <c r="D93" s="5">
         <v>1</v>
       </c>
       <c r="E93" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F93" s="5">
         <v>0</v>
       </c>
       <c r="G93" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H93" s="6">
-        <v>300</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="94">
@@ -3503,83 +3503,83 @@
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>LF215/45R17</t>
+          <t>NX215/45R17</t>
         </is>
       </c>
       <c r="D94" s="5">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E94" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F94" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G94" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H94" s="6">
-        <v>350</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>215/45R17</t>
+          <t>215/45R18</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>NX215/45R17</t>
+          <t>GD215/45R18</t>
         </is>
       </c>
       <c r="D95" s="5">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E95" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F95" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G95" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H95" s="6">
-        <v>380</v>
+        <v>550</v>
       </c>
     </row>
     <row outlineLevel="0" r="96">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>215/45R18</t>
+          <t>215/50R17</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>GD215/45R18</t>
+          <t>BR215/50R17</t>
         </is>
       </c>
       <c r="D96" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E96" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F96" s="5">
         <v>0</v>
@@ -3588,7 +3588,7 @@
         <v>0</v>
       </c>
       <c r="H96" s="6">
-        <v>550</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="97">
@@ -3599,28 +3599,28 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>BR215/50R17</t>
+          <t>GD215/50R17</t>
         </is>
       </c>
       <c r="D97" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E97" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F97" s="5">
         <v>0</v>
       </c>
       <c r="G97" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H97" s="6">
-        <v>450</v>
+        <v>470</v>
       </c>
     </row>
     <row outlineLevel="0" r="98">
@@ -3631,28 +3631,28 @@
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>GD215/50R17</t>
+          <t>HK215/50R17</t>
         </is>
       </c>
       <c r="D98" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E98" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F98" s="5">
         <v>0</v>
       </c>
       <c r="G98" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H98" s="6">
-        <v>470</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="99">
@@ -3663,19 +3663,19 @@
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>HK215/50R17</t>
+          <t>LF215/50R17</t>
         </is>
       </c>
       <c r="D99" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E99" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F99" s="5">
         <v>0</v>
@@ -3684,30 +3684,30 @@
         <v>0</v>
       </c>
       <c r="H99" s="6">
-        <v>400</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="100">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>215/50R17</t>
+          <t>215/50R18</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>LF215/50R17</t>
+          <t>GD215/50R18</t>
         </is>
       </c>
       <c r="D100" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E100" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F100" s="5">
         <v>0</v>
@@ -3716,13 +3716,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="6">
-        <v>420</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>215/50R18</t>
+          <t>215/55R16</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
@@ -3732,14 +3732,14 @@
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>GD215/50R18</t>
+          <t>GD215/55R16</t>
         </is>
       </c>
       <c r="D101" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E101" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F101" s="5">
         <v>0</v>
@@ -3748,7 +3748,7 @@
         <v>0</v>
       </c>
       <c r="H101" s="6">
-        <v>600</v>
+        <v>440</v>
       </c>
     </row>
     <row outlineLevel="0" r="102">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>GD215/55R16</t>
+          <t>LF215/55R16</t>
         </is>
       </c>
       <c r="D102" s="5">
@@ -3780,23 +3780,23 @@
         <v>0</v>
       </c>
       <c r="H102" s="6">
-        <v>440</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>215/55R16</t>
+          <t>215/55R17</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>LF215/55R16</t>
+          <t>BR215/55R17</t>
         </is>
       </c>
       <c r="D103" s="5">
@@ -3812,7 +3812,7 @@
         <v>0</v>
       </c>
       <c r="H103" s="6">
-        <v>350</v>
+        <v>480</v>
       </c>
     </row>
     <row outlineLevel="0" r="104">
@@ -3823,19 +3823,19 @@
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>BR215/55R17</t>
+          <t>HK215/55R17</t>
         </is>
       </c>
       <c r="D104" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E104" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F104" s="5">
         <v>0</v>
@@ -3844,23 +3844,23 @@
         <v>0</v>
       </c>
       <c r="H104" s="6">
-        <v>480</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>215/55R17</t>
+          <t>215/55R18</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>HK215/55R17</t>
+          <t>GD215/55R18</t>
         </is>
       </c>
       <c r="D105" s="5">
@@ -3876,23 +3876,23 @@
         <v>0</v>
       </c>
       <c r="H105" s="6">
-        <v>420</v>
+        <v>580</v>
       </c>
     </row>
     <row outlineLevel="0" r="106">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>215/55R18</t>
+          <t>215/60R16</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>GD215/55R18</t>
+          <t>BR215/60R16</t>
         </is>
       </c>
       <c r="D106" s="5">
@@ -3908,7 +3908,7 @@
         <v>0</v>
       </c>
       <c r="H106" s="6">
-        <v>580</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="107">
@@ -3919,25 +3919,25 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>BR215/60R16</t>
+          <t>DL215/60R16</t>
         </is>
       </c>
       <c r="D107" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E107" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F107" s="5">
         <v>0</v>
       </c>
       <c r="G107" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H107" s="6">
         <v>350</v>
@@ -3951,28 +3951,28 @@
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>DL215/60R16</t>
+          <t>HK215/60R16</t>
         </is>
       </c>
       <c r="D108" s="5">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E108" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F108" s="5">
         <v>0</v>
       </c>
       <c r="G108" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H108" s="6">
-        <v>350</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="109">
@@ -3983,25 +3983,25 @@
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>HK215/60R16</t>
+          <t>NX215/60R16</t>
         </is>
       </c>
       <c r="D109" s="5">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E109" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F109" s="5">
         <v>0</v>
       </c>
       <c r="G109" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H109" s="6">
         <v>330</v>
@@ -4010,65 +4010,65 @@
     <row outlineLevel="0" r="110">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>215/60R16</t>
+          <t>215/60R17</t>
         </is>
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>NX215/60R16</t>
+          <t>RD215/60R17</t>
         </is>
       </c>
       <c r="D110" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E110" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F110" s="5">
         <v>0</v>
       </c>
       <c r="G110" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H110" s="6">
-        <v>330</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="111">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>215/60R17</t>
+          <t>215/65R16</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>RD215/60R17</t>
+          <t>GD215/65R16</t>
         </is>
       </c>
       <c r="D111" s="5">
         <v>1</v>
       </c>
       <c r="E111" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F111" s="5">
         <v>0</v>
       </c>
       <c r="G111" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H111" s="6">
-        <v>300</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="112">
@@ -4079,44 +4079,44 @@
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>GD215/65R16</t>
+          <t>HK215/65R16</t>
         </is>
       </c>
       <c r="D112" s="5">
         <v>1</v>
       </c>
       <c r="E112" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F112" s="5">
         <v>0</v>
       </c>
       <c r="G112" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H112" s="6">
-        <v>380</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="113">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>215/65R16</t>
+          <t>215/65R17</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>MICHELIN</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>HK215/65R16</t>
+          <t>MC215/65R17</t>
         </is>
       </c>
       <c r="D113" s="5">
@@ -4132,30 +4132,30 @@
         <v>0</v>
       </c>
       <c r="H113" s="6">
-        <v>330</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="114">
       <c r="A114" s="4" t="inlineStr">
         <is>
-          <t>215/65R17</t>
+          <t>215/70R15C</t>
         </is>
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>MICHELIN</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>MC215/65R17</t>
+          <t>RD215/70R15C</t>
         </is>
       </c>
       <c r="D114" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E114" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F114" s="5">
         <v>0</v>
@@ -4164,30 +4164,30 @@
         <v>0</v>
       </c>
       <c r="H114" s="6">
-        <v>600</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="115">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t>215/70R15C</t>
+          <t>225/40R18</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>BARUM</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>RD215/70R15C</t>
+          <t>BM225/40R18</t>
         </is>
       </c>
       <c r="D115" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E115" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F115" s="5">
         <v>0</v>
@@ -4196,7 +4196,7 @@
         <v>0</v>
       </c>
       <c r="H115" s="6">
-        <v>330</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="116">
@@ -4207,28 +4207,28 @@
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>BARUM</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>BM225/40R18</t>
+          <t>GD225/40R18</t>
         </is>
       </c>
       <c r="D116" s="5">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="E116" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F116" s="5">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G116" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H116" s="6">
-        <v>420</v>
+        <v>480</v>
       </c>
     </row>
     <row outlineLevel="0" r="117">
@@ -4239,28 +4239,28 @@
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>GD225/40R18</t>
+          <t>HK225/40R18</t>
         </is>
       </c>
       <c r="D117" s="5">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="E117" s="5">
         <v>4</v>
       </c>
       <c r="F117" s="5">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G117" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H117" s="6">
-        <v>480</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="118">
@@ -4271,28 +4271,28 @@
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>LASSA</t>
         </is>
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>HK225/40R18</t>
+          <t>LS225/40R18</t>
         </is>
       </c>
       <c r="D118" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E118" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F118" s="5">
         <v>0</v>
       </c>
       <c r="G118" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H118" s="6">
-        <v>450</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="119">
@@ -4303,28 +4303,28 @@
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>LASSA</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>LS225/40R18</t>
+          <t>NX225/40R18</t>
         </is>
       </c>
       <c r="D119" s="5">
         <v>1</v>
       </c>
       <c r="E119" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F119" s="5">
         <v>0</v>
       </c>
       <c r="G119" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H119" s="6">
-        <v>330</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="120">
@@ -4335,19 +4335,19 @@
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>SEMPERIT</t>
         </is>
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>NX225/40R18</t>
+          <t>SP225/40R18</t>
         </is>
       </c>
       <c r="D120" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E120" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F120" s="5">
         <v>0</v>
@@ -4356,30 +4356,30 @@
         <v>0</v>
       </c>
       <c r="H120" s="6">
-        <v>400</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="121">
       <c r="A121" s="4" t="inlineStr">
         <is>
-          <t>225/40R18</t>
+          <t>225/40R18RF</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>SEMPERIT</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>SP225/40R18</t>
+          <t>GD225/40R18RF</t>
         </is>
       </c>
       <c r="D121" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E121" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F121" s="5">
         <v>0</v>
@@ -4388,30 +4388,30 @@
         <v>0</v>
       </c>
       <c r="H121" s="6">
-        <v>450</v>
+        <v>590</v>
       </c>
     </row>
     <row outlineLevel="0" r="122">
       <c r="A122" s="4" t="inlineStr">
         <is>
-          <t>225/40R18RF</t>
+          <t>225/45R17</t>
         </is>
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>GD225/40R18RF</t>
+          <t>CT225/45R17</t>
         </is>
       </c>
       <c r="D122" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E122" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F122" s="5">
         <v>0</v>
@@ -4420,7 +4420,7 @@
         <v>0</v>
       </c>
       <c r="H122" s="6">
-        <v>590</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="123">
@@ -4431,28 +4431,28 @@
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>FULDA</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>CT225/45R17</t>
+          <t>FL225/45R17</t>
         </is>
       </c>
       <c r="D123" s="5">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="E123" s="5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F123" s="5">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G123" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H123" s="6">
-        <v>400</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="124">
@@ -4463,28 +4463,28 @@
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>FULDA</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>FL225/45R17</t>
+          <t>GD225/45R17</t>
         </is>
       </c>
       <c r="D124" s="5">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E124" s="5">
         <v>6</v>
       </c>
       <c r="F124" s="5">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G124" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H124" s="6">
-        <v>350</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="125">
@@ -4495,60 +4495,60 @@
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>GD225/45R17</t>
+          <t>HK225/45R17</t>
         </is>
       </c>
       <c r="D125" s="5">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="E125" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F125" s="5">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="G125" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H125" s="6">
-        <v>380</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="126">
       <c r="A126" s="4" t="inlineStr">
         <is>
-          <t>225/45R17</t>
+          <t>225/45R18</t>
         </is>
       </c>
       <c r="B126" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C126" s="4" t="inlineStr">
         <is>
-          <t>HK225/45R17</t>
+          <t>DL225/45R18</t>
         </is>
       </c>
       <c r="D126" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E126" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F126" s="5">
         <v>0</v>
       </c>
       <c r="G126" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H126" s="6">
-        <v>350</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="127">
@@ -4559,28 +4559,28 @@
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>DL225/45R18</t>
+          <t>GD225/45R18</t>
         </is>
       </c>
       <c r="D127" s="5">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E127" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F127" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G127" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H127" s="6">
-        <v>500</v>
+        <v>550</v>
       </c>
     </row>
     <row outlineLevel="0" r="128">
@@ -4591,124 +4591,124 @@
       </c>
       <c r="B128" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C128" s="4" t="inlineStr">
         <is>
-          <t>GD225/45R18</t>
+          <t>LF225/45R18</t>
         </is>
       </c>
       <c r="D128" s="5">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E128" s="5">
         <v>4</v>
       </c>
       <c r="F128" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G128" s="5">
         <v>0</v>
       </c>
       <c r="H128" s="6">
-        <v>550</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="129">
       <c r="A129" s="4" t="inlineStr">
         <is>
-          <t>225/45R18</t>
+          <t>225/45R18RF</t>
         </is>
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>LF225/45R18</t>
+          <t>GD225/45R18RF</t>
         </is>
       </c>
       <c r="D129" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E129" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F129" s="5">
         <v>0</v>
       </c>
       <c r="G129" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H129" s="6">
-        <v>420</v>
+        <v>720</v>
       </c>
     </row>
     <row outlineLevel="0" r="130">
       <c r="A130" s="4" t="inlineStr">
         <is>
-          <t>225/45R18RF</t>
+          <t>225/45R19</t>
         </is>
       </c>
       <c r="B130" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C130" s="4" t="inlineStr">
         <is>
-          <t>GD225/45R18RF</t>
+          <t>CT225/45R19</t>
         </is>
       </c>
       <c r="D130" s="5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E130" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F130" s="5">
         <v>0</v>
       </c>
       <c r="G130" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H130" s="6">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row outlineLevel="0" r="131">
       <c r="A131" s="4" t="inlineStr">
         <is>
-          <t>225/45R19</t>
+          <t>225/50R17</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>CT225/45R19</t>
+          <t>GD225/50R17</t>
         </is>
       </c>
       <c r="D131" s="5">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E131" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F131" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G131" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H131" s="6">
-        <v>780</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="132">
@@ -4719,60 +4719,60 @@
       </c>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C132" s="4" t="inlineStr">
         <is>
-          <t>GD225/50R17</t>
+          <t>HK225/50R17</t>
         </is>
       </c>
       <c r="D132" s="5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E132" s="5">
         <v>4</v>
       </c>
       <c r="F132" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G132" s="5">
         <v>2</v>
       </c>
       <c r="H132" s="6">
-        <v>500</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="133">
       <c r="A133" s="4" t="inlineStr">
         <is>
-          <t>225/50R17</t>
+          <t>225/55R16</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>HK225/50R17</t>
+          <t>DL225/55R16</t>
         </is>
       </c>
       <c r="D133" s="5">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E133" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F133" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G133" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H133" s="6">
-        <v>400</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="134">
@@ -4783,19 +4783,19 @@
       </c>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C134" s="4" t="inlineStr">
         <is>
-          <t>DL225/55R16</t>
+          <t>GD225/55R16</t>
         </is>
       </c>
       <c r="D134" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E134" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F134" s="5">
         <v>0</v>
@@ -4804,30 +4804,30 @@
         <v>0</v>
       </c>
       <c r="H134" s="6">
-        <v>450</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="135">
       <c r="A135" s="4" t="inlineStr">
         <is>
-          <t>225/55R16</t>
+          <t>225/55R17</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>GD225/55R16</t>
+          <t>HK225/55R17</t>
         </is>
       </c>
       <c r="D135" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E135" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F135" s="5">
         <v>0</v>
@@ -4836,71 +4836,71 @@
         <v>0</v>
       </c>
       <c r="H135" s="6">
-        <v>420</v>
+        <v>430</v>
       </c>
     </row>
     <row outlineLevel="0" r="136">
       <c r="A136" s="4" t="inlineStr">
         <is>
-          <t>225/55R17</t>
+          <t>225/55R17RF</t>
         </is>
       </c>
       <c r="B136" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C136" s="4" t="inlineStr">
         <is>
-          <t>HK225/55R17</t>
+          <t>GD225/55R17RF</t>
         </is>
       </c>
       <c r="D136" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E136" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F136" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G136" s="5">
         <v>0</v>
       </c>
       <c r="H136" s="6">
-        <v>430</v>
+        <v>700</v>
       </c>
     </row>
     <row outlineLevel="0" r="137">
       <c r="A137" s="4" t="inlineStr">
         <is>
-          <t>225/55R17RF</t>
+          <t>225/55R18</t>
         </is>
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>GD225/55R17RF</t>
+          <t>HK225/55R18</t>
         </is>
       </c>
       <c r="D137" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E137" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F137" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G137" s="5">
         <v>0</v>
       </c>
       <c r="H137" s="6">
-        <v>700</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="138">
@@ -4911,19 +4911,19 @@
       </c>
       <c r="B138" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>KUMHO</t>
         </is>
       </c>
       <c r="C138" s="4" t="inlineStr">
         <is>
-          <t>HK225/55R18</t>
+          <t>KM225/55R18</t>
         </is>
       </c>
       <c r="D138" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E138" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F138" s="5">
         <v>0</v>
@@ -4932,30 +4932,30 @@
         <v>0</v>
       </c>
       <c r="H138" s="6">
-        <v>500</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="139">
       <c r="A139" s="4" t="inlineStr">
         <is>
-          <t>225/55R18</t>
+          <t>225/55R19</t>
         </is>
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>KUMHO</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>KM225/55R18</t>
+          <t>BR225/55R19</t>
         </is>
       </c>
       <c r="D139" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E139" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F139" s="5">
         <v>0</v>
@@ -4964,7 +4964,7 @@
         <v>0</v>
       </c>
       <c r="H139" s="6">
-        <v>450</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="140">
@@ -4975,19 +4975,19 @@
       </c>
       <c r="B140" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C140" s="4" t="inlineStr">
         <is>
-          <t>BR225/55R19</t>
+          <t>GD225/55R19</t>
         </is>
       </c>
       <c r="D140" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E140" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F140" s="5">
         <v>0</v>
@@ -5002,21 +5002,21 @@
     <row outlineLevel="0" r="141">
       <c r="A141" s="4" t="inlineStr">
         <is>
-          <t>225/55R19</t>
+          <t>225/60R17</t>
         </is>
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>GD225/55R19</t>
+          <t>HK225/60R17</t>
         </is>
       </c>
       <c r="D141" s="5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E141" s="5">
         <v>4</v>
@@ -5025,65 +5025,65 @@
         <v>0</v>
       </c>
       <c r="G141" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H141" s="6">
-        <v>750</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="142">
       <c r="A142" s="4" t="inlineStr">
         <is>
-          <t>225/60R17</t>
+          <t>225/60R18</t>
         </is>
       </c>
       <c r="B142" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C142" s="4" t="inlineStr">
         <is>
-          <t>HK225/60R17</t>
+          <t>GD225/60R18</t>
         </is>
       </c>
       <c r="D142" s="5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E142" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F142" s="5">
         <v>0</v>
       </c>
       <c r="G142" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H142" s="6">
-        <v>400</v>
+        <v>700</v>
       </c>
     </row>
     <row outlineLevel="0" r="143">
       <c r="A143" s="4" t="inlineStr">
         <is>
-          <t>225/60R18</t>
+          <t>225/65R17</t>
         </is>
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>GD225/60R18</t>
+          <t>RD225/65R17</t>
         </is>
       </c>
       <c r="D143" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E143" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F143" s="5">
         <v>0</v>
@@ -5092,13 +5092,13 @@
         <v>0</v>
       </c>
       <c r="H143" s="6">
-        <v>700</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="144">
       <c r="A144" s="4" t="inlineStr">
         <is>
-          <t>225/65R17</t>
+          <t>225/75R15C</t>
         </is>
       </c>
       <c r="B144" s="4" t="inlineStr">
@@ -5108,29 +5108,29 @@
       </c>
       <c r="C144" s="4" t="inlineStr">
         <is>
-          <t>RD225/65R17</t>
+          <t>RD225/75R15C</t>
         </is>
       </c>
       <c r="D144" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E144" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F144" s="5">
         <v>0</v>
       </c>
       <c r="G144" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H144" s="6">
-        <v>450</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="145">
       <c r="A145" s="4" t="inlineStr">
         <is>
-          <t>225/75R15C</t>
+          <t>235/35R19</t>
         </is>
       </c>
       <c r="B145" s="4" t="inlineStr">
@@ -5140,61 +5140,61 @@
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>RD225/75R15C</t>
+          <t>RD235/35R19</t>
         </is>
       </c>
       <c r="D145" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E145" s="5">
         <v>0</v>
       </c>
       <c r="F145" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G145" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H145" s="6">
-        <v>330</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="146">
       <c r="A146" s="4" t="inlineStr">
         <is>
-          <t>235/35R19</t>
+          <t>235/40R19</t>
         </is>
       </c>
       <c r="B146" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C146" s="4" t="inlineStr">
         <is>
-          <t>RD235/35R19</t>
+          <t>GD235/40R19</t>
         </is>
       </c>
       <c r="D146" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E146" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F146" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G146" s="5">
         <v>0</v>
       </c>
       <c r="H146" s="6">
-        <v>600</v>
+        <v>850</v>
       </c>
     </row>
     <row outlineLevel="0" r="147">
       <c r="A147" s="4" t="inlineStr">
         <is>
-          <t>235/40R19</t>
+          <t>235/45R18</t>
         </is>
       </c>
       <c r="B147" s="4" t="inlineStr">
@@ -5204,14 +5204,14 @@
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>GD235/40R19</t>
+          <t>GD235/45R18</t>
         </is>
       </c>
       <c r="D147" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E147" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F147" s="5">
         <v>0</v>
@@ -5220,30 +5220,30 @@
         <v>0</v>
       </c>
       <c r="H147" s="6">
-        <v>850</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="148">
       <c r="A148" s="4" t="inlineStr">
         <is>
-          <t>235/45R18</t>
+          <t>235/50R18</t>
         </is>
       </c>
       <c r="B148" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C148" s="4" t="inlineStr">
         <is>
-          <t>GD235/45R18</t>
+          <t>HK235/50R18</t>
         </is>
       </c>
       <c r="D148" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E148" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F148" s="5">
         <v>0</v>
@@ -5252,30 +5252,30 @@
         <v>0</v>
       </c>
       <c r="H148" s="6">
-        <v>600</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="149">
       <c r="A149" s="4" t="inlineStr">
         <is>
-          <t>235/50R18</t>
+          <t>235/50R19</t>
         </is>
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>HK235/50R18</t>
+          <t>GD235/50R19</t>
         </is>
       </c>
       <c r="D149" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E149" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F149" s="5">
         <v>0</v>
@@ -5284,13 +5284,13 @@
         <v>0</v>
       </c>
       <c r="H149" s="6">
-        <v>500</v>
+        <v>800</v>
       </c>
     </row>
     <row outlineLevel="0" r="150">
       <c r="A150" s="4" t="inlineStr">
         <is>
-          <t>235/50R19</t>
+          <t>235/50R20</t>
         </is>
       </c>
       <c r="B150" s="4" t="inlineStr">
@@ -5300,78 +5300,78 @@
       </c>
       <c r="C150" s="4" t="inlineStr">
         <is>
-          <t>GD235/50R19</t>
+          <t>GD235/50R20</t>
         </is>
       </c>
       <c r="D150" s="5">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E150" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F150" s="5">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G150" s="5">
         <v>0</v>
       </c>
       <c r="H150" s="6">
-        <v>800</v>
+        <v>1180</v>
       </c>
     </row>
     <row outlineLevel="0" r="151">
       <c r="A151" s="4" t="inlineStr">
         <is>
-          <t>235/50R20</t>
+          <t>235/55R17</t>
         </is>
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>GD235/50R20</t>
+          <t>BR235/55R17</t>
         </is>
       </c>
       <c r="D151" s="5">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E151" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F151" s="5">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G151" s="5">
         <v>0</v>
       </c>
       <c r="H151" s="6">
-        <v>1180</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="152">
       <c r="A152" s="4" t="inlineStr">
         <is>
-          <t>235/55R17</t>
+          <t>235/55R18</t>
         </is>
       </c>
       <c r="B152" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C152" s="4" t="inlineStr">
         <is>
-          <t>BR235/55R17</t>
+          <t>HK235/55R18</t>
         </is>
       </c>
       <c r="D152" s="5">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E152" s="5">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F152" s="5">
         <v>0</v>
@@ -5380,30 +5380,30 @@
         <v>0</v>
       </c>
       <c r="H152" s="6">
-        <v>450</v>
+        <v>480</v>
       </c>
     </row>
     <row outlineLevel="0" r="153">
       <c r="A153" s="4" t="inlineStr">
         <is>
-          <t>235/55R18</t>
+          <t>235/55R19</t>
         </is>
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>HK235/55R18</t>
+          <t>GD235/55R19</t>
         </is>
       </c>
       <c r="D153" s="5">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E153" s="5">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F153" s="5">
         <v>0</v>
@@ -5412,7 +5412,7 @@
         <v>0</v>
       </c>
       <c r="H153" s="6">
-        <v>480</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="154">
@@ -5423,19 +5423,19 @@
       </c>
       <c r="B154" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C154" s="4" t="inlineStr">
         <is>
-          <t>GD235/55R19</t>
+          <t>HK235/55R19</t>
         </is>
       </c>
       <c r="D154" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E154" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F154" s="5">
         <v>0</v>
@@ -5444,7 +5444,7 @@
         <v>0</v>
       </c>
       <c r="H154" s="6">
-        <v>750</v>
+        <v>630</v>
       </c>
     </row>
     <row outlineLevel="0" r="155">
@@ -5455,12 +5455,12 @@
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>HK235/55R19</t>
+          <t>LF235/55R19</t>
         </is>
       </c>
       <c r="D155" s="5">
@@ -5476,7 +5476,7 @@
         <v>0</v>
       </c>
       <c r="H155" s="6">
-        <v>630</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="156">
@@ -5487,19 +5487,19 @@
       </c>
       <c r="B156" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C156" s="4" t="inlineStr">
         <is>
-          <t>LF235/55R19</t>
+          <t>NX235/55R19</t>
         </is>
       </c>
       <c r="D156" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E156" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F156" s="5">
         <v>0</v>
@@ -5508,7 +5508,7 @@
         <v>0</v>
       </c>
       <c r="H156" s="6">
-        <v>500</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="157">
@@ -5519,66 +5519,66 @@
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>NX235/55R19</t>
+          <t>RD235/55R19</t>
         </is>
       </c>
       <c r="D157" s="5">
         <v>2</v>
       </c>
       <c r="E157" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F157" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G157" s="5">
         <v>0</v>
       </c>
       <c r="H157" s="6">
-        <v>600</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="158">
       <c r="A158" s="4" t="inlineStr">
         <is>
-          <t>235/55R19</t>
+          <t>235/60R16</t>
         </is>
       </c>
       <c r="B158" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C158" s="4" t="inlineStr">
         <is>
-          <t>RD235/55R19</t>
+          <t>HK235/60R16</t>
         </is>
       </c>
       <c r="D158" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E158" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F158" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G158" s="5">
         <v>0</v>
       </c>
       <c r="H158" s="6">
-        <v>500</v>
+        <v>430</v>
       </c>
     </row>
     <row outlineLevel="0" r="159">
       <c r="A159" s="4" t="inlineStr">
         <is>
-          <t>235/60R16</t>
+          <t>235/60R17</t>
         </is>
       </c>
       <c r="B159" s="4" t="inlineStr">
@@ -5588,55 +5588,55 @@
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>HK235/60R16</t>
+          <t>HK235/60R17</t>
         </is>
       </c>
       <c r="D159" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E159" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F159" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G159" s="5">
         <v>0</v>
       </c>
       <c r="H159" s="6">
-        <v>430</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="160">
       <c r="A160" s="4" t="inlineStr">
         <is>
-          <t>235/60R17</t>
+          <t>235/60R18</t>
         </is>
       </c>
       <c r="B160" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C160" s="4" t="inlineStr">
         <is>
-          <t>HK235/60R17</t>
+          <t>GD235/60R18</t>
         </is>
       </c>
       <c r="D160" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E160" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F160" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G160" s="5">
         <v>0</v>
       </c>
       <c r="H160" s="6">
-        <v>500</v>
+        <v>680</v>
       </c>
     </row>
     <row outlineLevel="0" r="161">
@@ -5647,12 +5647,12 @@
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>GD235/60R18</t>
+          <t>HK235/60R18</t>
         </is>
       </c>
       <c r="D161" s="5">
@@ -5668,30 +5668,30 @@
         <v>0</v>
       </c>
       <c r="H161" s="6">
-        <v>680</v>
+        <v>550</v>
       </c>
     </row>
     <row outlineLevel="0" r="162">
       <c r="A162" s="4" t="inlineStr">
         <is>
-          <t>235/60R18</t>
+          <t>245/40R17</t>
         </is>
       </c>
       <c r="B162" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C162" s="4" t="inlineStr">
         <is>
-          <t>HK235/60R18</t>
+          <t>GD245/40R17</t>
         </is>
       </c>
       <c r="D162" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E162" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F162" s="5">
         <v>0</v>
@@ -5700,13 +5700,13 @@
         <v>0</v>
       </c>
       <c r="H162" s="6">
-        <v>550</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="163">
       <c r="A163" s="4" t="inlineStr">
         <is>
-          <t>245/40R17</t>
+          <t>245/40R18</t>
         </is>
       </c>
       <c r="B163" s="4" t="inlineStr">
@@ -5716,142 +5716,142 @@
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>GD245/40R17</t>
+          <t>GD245/40R18</t>
         </is>
       </c>
       <c r="D163" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E163" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F163" s="5">
         <v>0</v>
       </c>
       <c r="G163" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H163" s="6">
-        <v>400</v>
+        <v>620</v>
       </c>
     </row>
     <row outlineLevel="0" r="164">
       <c r="A164" s="4" t="inlineStr">
         <is>
-          <t>245/40R18</t>
+          <t>245/40R19</t>
         </is>
       </c>
       <c r="B164" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C164" s="4" t="inlineStr">
         <is>
-          <t>GD245/40R18</t>
+          <t>HK245/40R19</t>
         </is>
       </c>
       <c r="D164" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E164" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F164" s="5">
         <v>0</v>
       </c>
       <c r="G164" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H164" s="6">
-        <v>620</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="165">
       <c r="A165" s="4" t="inlineStr">
         <is>
-          <t>245/40R19</t>
+          <t>245/40R20</t>
         </is>
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>HK245/40R19</t>
+          <t>CT245/40R20</t>
         </is>
       </c>
       <c r="D165" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E165" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F165" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G165" s="5">
         <v>0</v>
       </c>
       <c r="H165" s="6">
-        <v>750</v>
+        <v>1050</v>
       </c>
     </row>
     <row outlineLevel="0" r="166">
       <c r="A166" s="4" t="inlineStr">
         <is>
-          <t>245/40R20</t>
+          <t>245/45R17</t>
         </is>
       </c>
       <c r="B166" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C166" s="4" t="inlineStr">
         <is>
-          <t>CT245/40R20</t>
+          <t>HK245/45R17</t>
         </is>
       </c>
       <c r="D166" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E166" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F166" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G166" s="5">
         <v>0</v>
       </c>
       <c r="H166" s="6">
-        <v>1050</v>
+        <v>430</v>
       </c>
     </row>
     <row outlineLevel="0" r="167">
       <c r="A167" s="4" t="inlineStr">
         <is>
-          <t>245/45R17</t>
+          <t>245/45R18</t>
         </is>
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>HK245/45R17</t>
+          <t>CT245/45R18</t>
         </is>
       </c>
       <c r="D167" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E167" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F167" s="5">
         <v>0</v>
@@ -5860,7 +5860,7 @@
         <v>0</v>
       </c>
       <c r="H167" s="6">
-        <v>430</v>
+        <v>650</v>
       </c>
     </row>
     <row outlineLevel="0" r="168">
@@ -5871,19 +5871,19 @@
       </c>
       <c r="B168" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C168" s="4" t="inlineStr">
         <is>
-          <t>CT245/45R18</t>
+          <t>GD245/45R18</t>
         </is>
       </c>
       <c r="D168" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E168" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F168" s="5">
         <v>0</v>
@@ -5892,7 +5892,7 @@
         <v>0</v>
       </c>
       <c r="H168" s="6">
-        <v>650</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="169">
@@ -5903,19 +5903,19 @@
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>GD245/45R18</t>
+          <t>HK245/45R18</t>
         </is>
       </c>
       <c r="D169" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E169" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F169" s="5">
         <v>0</v>
@@ -5924,30 +5924,30 @@
         <v>0</v>
       </c>
       <c r="H169" s="6">
-        <v>600</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="170">
       <c r="A170" s="4" t="inlineStr">
         <is>
-          <t>245/45R18</t>
+          <t>245/45R18RF</t>
         </is>
       </c>
       <c r="B170" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C170" s="4" t="inlineStr">
         <is>
-          <t>HK245/45R18</t>
+          <t>GD245/45R18RF</t>
         </is>
       </c>
       <c r="D170" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E170" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F170" s="5">
         <v>0</v>
@@ -5956,23 +5956,23 @@
         <v>0</v>
       </c>
       <c r="H170" s="6">
-        <v>500</v>
+        <v>720</v>
       </c>
     </row>
     <row outlineLevel="0" r="171">
       <c r="A171" s="4" t="inlineStr">
         <is>
-          <t>245/45R18RF</t>
+          <t>245/45R19</t>
         </is>
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t>GD245/45R18RF</t>
+          <t>BR245/45R19</t>
         </is>
       </c>
       <c r="D171" s="5">
@@ -5988,7 +5988,7 @@
         <v>0</v>
       </c>
       <c r="H171" s="6">
-        <v>720</v>
+        <v>790</v>
       </c>
     </row>
     <row outlineLevel="0" r="172">
@@ -5999,44 +5999,44 @@
       </c>
       <c r="B172" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C172" s="4" t="inlineStr">
         <is>
-          <t>BR245/45R19</t>
+          <t>RD245/45R19</t>
         </is>
       </c>
       <c r="D172" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E172" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F172" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G172" s="5">
         <v>0</v>
       </c>
       <c r="H172" s="6">
-        <v>790</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="173">
       <c r="A173" s="4" t="inlineStr">
         <is>
-          <t>245/45R19</t>
+          <t>245/45R20</t>
         </is>
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>RD245/45R19</t>
+          <t>HK245/45R20</t>
         </is>
       </c>
       <c r="D173" s="5">
@@ -6052,59 +6052,59 @@
         <v>0</v>
       </c>
       <c r="H173" s="6">
-        <v>450</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="174">
       <c r="A174" s="4" t="inlineStr">
         <is>
-          <t>245/45R20</t>
+          <t>245/65R17</t>
         </is>
       </c>
       <c r="B174" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C174" s="4" t="inlineStr">
         <is>
-          <t>HK245/45R20</t>
+          <t>NX245/65R17</t>
         </is>
       </c>
       <c r="D174" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E174" s="5">
         <v>0</v>
       </c>
       <c r="F174" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G174" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H174" s="6">
-        <v>750</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="175">
       <c r="A175" s="4" t="inlineStr">
         <is>
-          <t>245/65R17</t>
+          <t>245/70R16</t>
         </is>
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>LASSA</t>
         </is>
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>NX245/65R17</t>
+          <t>LS245/70R16</t>
         </is>
       </c>
       <c r="D175" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E175" s="5">
         <v>0</v>
@@ -6113,65 +6113,65 @@
         <v>0</v>
       </c>
       <c r="G175" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H175" s="6">
-        <v>600</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="176">
       <c r="A176" s="4" t="inlineStr">
         <is>
-          <t>245/70R16</t>
+          <t>255/35R19</t>
         </is>
       </c>
       <c r="B176" s="4" t="inlineStr">
         <is>
-          <t>LASSA</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C176" s="4" t="inlineStr">
         <is>
-          <t>LS245/70R16</t>
+          <t>DL255/35R19</t>
         </is>
       </c>
       <c r="D176" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E176" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F176" s="5">
         <v>0</v>
       </c>
       <c r="G176" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H176" s="6">
-        <v>500</v>
+        <v>700</v>
       </c>
     </row>
     <row outlineLevel="0" r="177">
       <c r="A177" s="4" t="inlineStr">
         <is>
-          <t>255/35R19</t>
+          <t>255/35R19RF</t>
         </is>
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>DL255/35R19</t>
+          <t>CT255/35R19RF</t>
         </is>
       </c>
       <c r="D177" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E177" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F177" s="5">
         <v>0</v>
@@ -6180,7 +6180,7 @@
         <v>0</v>
       </c>
       <c r="H177" s="6">
-        <v>700</v>
+        <v>950</v>
       </c>
     </row>
     <row outlineLevel="0" r="178">
@@ -6191,19 +6191,19 @@
       </c>
       <c r="B178" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C178" s="4" t="inlineStr">
         <is>
-          <t>CT255/35R19RF</t>
+          <t>GD255/35R19RF</t>
         </is>
       </c>
       <c r="D178" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E178" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F178" s="5">
         <v>0</v>
@@ -6218,39 +6218,39 @@
     <row outlineLevel="0" r="179">
       <c r="A179" s="4" t="inlineStr">
         <is>
-          <t>255/35R19RF</t>
+          <t>255/50R19</t>
         </is>
       </c>
       <c r="B179" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C179" s="4" t="inlineStr">
         <is>
-          <t>GD255/35R19RF</t>
+          <t>CT255/50R19</t>
         </is>
       </c>
       <c r="D179" s="5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E179" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F179" s="5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G179" s="5">
         <v>0</v>
       </c>
       <c r="H179" s="6">
-        <v>950</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="180">
       <c r="A180" s="4" t="inlineStr">
         <is>
-          <t>255/50R19</t>
+          <t>255/50R20</t>
         </is>
       </c>
       <c r="B180" s="4" t="inlineStr">
@@ -6260,29 +6260,29 @@
       </c>
       <c r="C180" s="4" t="inlineStr">
         <is>
-          <t>CT255/50R19</t>
+          <t>CT255/50R20</t>
         </is>
       </c>
       <c r="D180" s="5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E180" s="5">
         <v>0</v>
       </c>
       <c r="F180" s="5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G180" s="5">
         <v>0</v>
       </c>
       <c r="H180" s="6">
-        <v>750</v>
+        <v>900</v>
       </c>
     </row>
     <row outlineLevel="0" r="181">
       <c r="A181" s="4" t="inlineStr">
         <is>
-          <t>255/50R20</t>
+          <t>255/55R19</t>
         </is>
       </c>
       <c r="B181" s="4" t="inlineStr">
@@ -6292,23 +6292,23 @@
       </c>
       <c r="C181" s="4" t="inlineStr">
         <is>
-          <t>CT255/50R20</t>
+          <t>CT255/55R19</t>
         </is>
       </c>
       <c r="D181" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E181" s="5">
         <v>0</v>
       </c>
       <c r="F181" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G181" s="5">
         <v>0</v>
       </c>
       <c r="H181" s="6">
-        <v>900</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="182">
@@ -6319,98 +6319,98 @@
       </c>
       <c r="B182" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C182" s="4" t="inlineStr">
         <is>
-          <t>CT255/55R19</t>
+          <t>DL255/55R19</t>
         </is>
       </c>
       <c r="D182" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E182" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F182" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G182" s="5">
         <v>0</v>
       </c>
       <c r="H182" s="6">
-        <v>750</v>
+        <v>700</v>
       </c>
     </row>
     <row outlineLevel="0" r="183">
       <c r="A183" s="4" t="inlineStr">
         <is>
-          <t>255/55R19</t>
+          <t>255/70R16</t>
         </is>
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C183" s="4" t="inlineStr">
         <is>
-          <t>DL255/55R19</t>
+          <t>RD255/70R16</t>
         </is>
       </c>
       <c r="D183" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E183" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F183" s="5">
         <v>0</v>
       </c>
       <c r="G183" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H183" s="6">
-        <v>700</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="184">
       <c r="A184" s="4" t="inlineStr">
         <is>
-          <t>255/70R16</t>
+          <t>265/35R18</t>
         </is>
       </c>
       <c r="B184" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C184" s="4" t="inlineStr">
         <is>
-          <t>RD255/70R16</t>
+          <t>GD265/35R18</t>
         </is>
       </c>
       <c r="D184" s="5">
         <v>1</v>
       </c>
       <c r="E184" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F184" s="5">
         <v>0</v>
       </c>
       <c r="G184" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H184" s="6">
-        <v>500</v>
+        <v>700</v>
       </c>
     </row>
     <row outlineLevel="0" r="185">
       <c r="A185" s="4" t="inlineStr">
         <is>
-          <t>265/35R18</t>
+          <t>265/50R20</t>
         </is>
       </c>
       <c r="B185" s="4" t="inlineStr">
@@ -6420,29 +6420,29 @@
       </c>
       <c r="C185" s="4" t="inlineStr">
         <is>
-          <t>GD265/35R18</t>
+          <t>GD265/50R20</t>
         </is>
       </c>
       <c r="D185" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E185" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F185" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G185" s="5">
         <v>0</v>
       </c>
       <c r="H185" s="6">
-        <v>700</v>
+        <v>1150</v>
       </c>
     </row>
     <row outlineLevel="0" r="186">
       <c r="A186" s="4" t="inlineStr">
         <is>
-          <t>265/50R20</t>
+          <t>275/35R19RF</t>
         </is>
       </c>
       <c r="B186" s="4" t="inlineStr">
@@ -6452,71 +6452,71 @@
       </c>
       <c r="C186" s="4" t="inlineStr">
         <is>
-          <t>GD265/50R20</t>
+          <t>GD275/35R19RF</t>
         </is>
       </c>
       <c r="D186" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E186" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F186" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G186" s="5">
         <v>0</v>
       </c>
       <c r="H186" s="6">
-        <v>1150</v>
+        <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="187">
       <c r="A187" s="4" t="inlineStr">
         <is>
-          <t>275/35R19RF</t>
+          <t>275/35R20</t>
         </is>
       </c>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C187" s="4" t="inlineStr">
         <is>
-          <t>GD275/35R19RF</t>
+          <t>CT275/35R20</t>
         </is>
       </c>
       <c r="D187" s="5">
         <v>2</v>
       </c>
       <c r="E187" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F187" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G187" s="5">
         <v>0</v>
       </c>
       <c r="H187" s="6">
-        <v>1</v>
+        <v>980</v>
       </c>
     </row>
     <row outlineLevel="0" r="188">
       <c r="A188" s="4" t="inlineStr">
         <is>
-          <t>275/35R20</t>
+          <t>275/40R20</t>
         </is>
       </c>
       <c r="B188" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C188" s="4" t="inlineStr">
         <is>
-          <t>CT275/35R20</t>
+          <t>HK275/40R20</t>
         </is>
       </c>
       <c r="D188" s="5">
@@ -6532,23 +6532,23 @@
         <v>0</v>
       </c>
       <c r="H188" s="6">
-        <v>980</v>
+        <v>770</v>
       </c>
     </row>
     <row outlineLevel="0" r="189">
       <c r="A189" s="4" t="inlineStr">
         <is>
-          <t>275/40R20</t>
+          <t>275/50R21</t>
         </is>
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C189" s="4" t="inlineStr">
         <is>
-          <t>HK275/40R20</t>
+          <t>GD275/50R21</t>
         </is>
       </c>
       <c r="D189" s="5">
@@ -6564,23 +6564,23 @@
         <v>0</v>
       </c>
       <c r="H189" s="6">
-        <v>770</v>
+        <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="190">
       <c r="A190" s="4" t="inlineStr">
         <is>
-          <t>275/50R21</t>
+          <t>295/35R21</t>
         </is>
       </c>
       <c r="B190" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C190" s="4" t="inlineStr">
         <is>
-          <t>GD275/50R21</t>
+          <t>CT295/35R21</t>
         </is>
       </c>
       <c r="D190" s="5">
@@ -6596,7 +6596,7 @@
         <v>0</v>
       </c>
       <c r="H190" s="6">
-        <v>1</v>
+        <v>1150</v>
       </c>
     </row>
     <row outlineLevel="0" r="191">
@@ -6607,91 +6607,59 @@
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C191" s="4" t="inlineStr">
         <is>
-          <t>CT295/35R21</t>
+          <t>GD295/35R21</t>
         </is>
       </c>
       <c r="D191" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E191" s="5">
         <v>0</v>
       </c>
       <c r="F191" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G191" s="5">
         <v>0</v>
       </c>
       <c r="H191" s="6">
-        <v>1150</v>
+        <v>980</v>
       </c>
     </row>
     <row outlineLevel="0" r="192">
       <c r="A192" s="4" t="inlineStr">
         <is>
-          <t>295/35R21</t>
+          <t>500R12</t>
         </is>
       </c>
       <c r="B192" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C192" s="4" t="inlineStr">
         <is>
-          <t>GD295/35R21</t>
+          <t>RD500R12</t>
         </is>
       </c>
       <c r="D192" s="5">
         <v>3</v>
       </c>
       <c r="E192" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F192" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G192" s="5">
         <v>0</v>
       </c>
       <c r="H192" s="6">
-        <v>980</v>
-      </c>
-    </row>
-    <row outlineLevel="0" r="193">
-      <c r="A193" s="4" t="inlineStr">
-        <is>
-          <t>500R12</t>
-        </is>
-      </c>
-      <c r="B193" s="4" t="inlineStr">
-        <is>
-          <t>RADIAL</t>
-        </is>
-      </c>
-      <c r="C193" s="4" t="inlineStr">
-        <is>
-          <t>RD500R12</t>
-        </is>
-      </c>
-      <c r="D193" s="5">
-        <v>3</v>
-      </c>
-      <c r="E193" s="5">
-        <v>3</v>
-      </c>
-      <c r="F193" s="5">
-        <v>0</v>
-      </c>
-      <c r="G193" s="5">
-        <v>0</v>
-      </c>
-      <c r="H193" s="6">
         <v>300</v>
       </c>
     </row>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -496,7 +496,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H192"/>
+  <dimension ref="A1:H194"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col customWidth="true" min="1" max="1" width="13.8359375"/>
@@ -1080,10 +1080,10 @@
         </is>
       </c>
       <c r="D18" s="5">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="E18" s="5">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F18" s="5">
         <v>55</v>
@@ -1208,10 +1208,10 @@
         </is>
       </c>
       <c r="D22" s="5">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E22" s="5">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F22" s="5">
         <v>0</v>
@@ -1272,7 +1272,7 @@
         </is>
       </c>
       <c r="D24" s="5">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E24" s="5">
         <v>3</v>
@@ -1281,7 +1281,7 @@
         <v>31</v>
       </c>
       <c r="G24" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H24" s="6">
         <v>340</v>
@@ -1339,10 +1339,10 @@
         <v>20</v>
       </c>
       <c r="E26" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F26" s="5">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G26" s="5">
         <v>4</v>
@@ -1976,7 +1976,7 @@
         </is>
       </c>
       <c r="D46" s="5">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E46" s="5">
         <v>8</v>
@@ -1985,7 +1985,7 @@
         <v>0</v>
       </c>
       <c r="G46" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H46" s="6">
         <v>225</v>
@@ -2043,10 +2043,10 @@
         <v>18</v>
       </c>
       <c r="E48" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F48" s="5">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G48" s="5">
         <v>4</v>
@@ -2203,10 +2203,10 @@
         <v>30</v>
       </c>
       <c r="E53" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F53" s="5">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="G53" s="5">
         <v>3</v>
@@ -2424,10 +2424,10 @@
         </is>
       </c>
       <c r="D60" s="5">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="E60" s="5">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F60" s="5">
         <v>73</v>
@@ -2907,10 +2907,10 @@
         <v>11</v>
       </c>
       <c r="E75" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F75" s="5">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G75" s="5">
         <v>4</v>
@@ -4143,51 +4143,51 @@
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>LINGLONG</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>RD215/70R15C</t>
+          <t>LG215/70R15C</t>
         </is>
       </c>
       <c r="D114" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E114" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F114" s="5">
         <v>0</v>
       </c>
       <c r="G114" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H114" s="6">
-        <v>330</v>
+        <v>370</v>
       </c>
     </row>
     <row outlineLevel="0" r="115">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t>225/40R18</t>
+          <t>215/70R15C</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>BARUM</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>BM225/40R18</t>
+          <t>RD215/70R15C</t>
         </is>
       </c>
       <c r="D115" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E115" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F115" s="5">
         <v>0</v>
@@ -4196,7 +4196,7 @@
         <v>0</v>
       </c>
       <c r="H115" s="6">
-        <v>420</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="116">
@@ -4207,28 +4207,28 @@
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>BARUM</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>GD225/40R18</t>
+          <t>BM225/40R18</t>
         </is>
       </c>
       <c r="D116" s="5">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="E116" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F116" s="5">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G116" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H116" s="6">
-        <v>480</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="117">
@@ -4239,28 +4239,28 @@
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>HK225/40R18</t>
+          <t>GD225/40R18</t>
         </is>
       </c>
       <c r="D117" s="5">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="E117" s="5">
         <v>4</v>
       </c>
       <c r="F117" s="5">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G117" s="5">
         <v>0</v>
       </c>
       <c r="H117" s="6">
-        <v>450</v>
+        <v>480</v>
       </c>
     </row>
     <row outlineLevel="0" r="118">
@@ -4271,28 +4271,28 @@
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>LASSA</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>LS225/40R18</t>
+          <t>HK225/40R18</t>
         </is>
       </c>
       <c r="D118" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E118" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F118" s="5">
         <v>0</v>
       </c>
       <c r="G118" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H118" s="6">
-        <v>330</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="119">
@@ -4303,28 +4303,28 @@
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>LASSA</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>NX225/40R18</t>
+          <t>LS225/40R18</t>
         </is>
       </c>
       <c r="D119" s="5">
         <v>1</v>
       </c>
       <c r="E119" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F119" s="5">
         <v>0</v>
       </c>
       <c r="G119" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H119" s="6">
-        <v>400</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="120">
@@ -4335,19 +4335,19 @@
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>SEMPERIT</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>SP225/40R18</t>
+          <t>NX225/40R18</t>
         </is>
       </c>
       <c r="D120" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E120" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F120" s="5">
         <v>0</v>
@@ -4356,30 +4356,30 @@
         <v>0</v>
       </c>
       <c r="H120" s="6">
-        <v>450</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="121">
       <c r="A121" s="4" t="inlineStr">
         <is>
-          <t>225/40R18RF</t>
+          <t>225/40R18</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>SEMPERIT</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>GD225/40R18RF</t>
+          <t>SP225/40R18</t>
         </is>
       </c>
       <c r="D121" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E121" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F121" s="5">
         <v>0</v>
@@ -4388,30 +4388,30 @@
         <v>0</v>
       </c>
       <c r="H121" s="6">
-        <v>590</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="122">
       <c r="A122" s="4" t="inlineStr">
         <is>
-          <t>225/45R17</t>
+          <t>225/40R18RF</t>
         </is>
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>CT225/45R17</t>
+          <t>GD225/40R18RF</t>
         </is>
       </c>
       <c r="D122" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E122" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F122" s="5">
         <v>0</v>
@@ -4420,7 +4420,7 @@
         <v>0</v>
       </c>
       <c r="H122" s="6">
-        <v>400</v>
+        <v>590</v>
       </c>
     </row>
     <row outlineLevel="0" r="123">
@@ -4431,28 +4431,28 @@
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>FULDA</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>FL225/45R17</t>
+          <t>CT225/45R17</t>
         </is>
       </c>
       <c r="D123" s="5">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="E123" s="5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F123" s="5">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G123" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H123" s="6">
-        <v>350</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="124">
@@ -4463,28 +4463,28 @@
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>FULDA</t>
         </is>
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>GD225/45R17</t>
+          <t>FL225/45R17</t>
         </is>
       </c>
       <c r="D124" s="5">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E124" s="5">
         <v>6</v>
       </c>
       <c r="F124" s="5">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G124" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H124" s="6">
-        <v>380</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="125">
@@ -4495,60 +4495,60 @@
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>HK225/45R17</t>
+          <t>GD225/45R17</t>
         </is>
       </c>
       <c r="D125" s="5">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="E125" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F125" s="5">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G125" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H125" s="6">
-        <v>350</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="126">
       <c r="A126" s="4" t="inlineStr">
         <is>
-          <t>225/45R18</t>
+          <t>225/45R17</t>
         </is>
       </c>
       <c r="B126" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C126" s="4" t="inlineStr">
         <is>
-          <t>DL225/45R18</t>
+          <t>HK225/45R17</t>
         </is>
       </c>
       <c r="D126" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E126" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F126" s="5">
         <v>0</v>
       </c>
       <c r="G126" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H126" s="6">
-        <v>500</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="127">
@@ -4559,28 +4559,28 @@
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>GD225/45R18</t>
+          <t>DL225/45R18</t>
         </is>
       </c>
       <c r="D127" s="5">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E127" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F127" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G127" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H127" s="6">
-        <v>550</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="128">
@@ -4591,124 +4591,124 @@
       </c>
       <c r="B128" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C128" s="4" t="inlineStr">
         <is>
-          <t>LF225/45R18</t>
+          <t>GD225/45R18</t>
         </is>
       </c>
       <c r="D128" s="5">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E128" s="5">
         <v>4</v>
       </c>
       <c r="F128" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G128" s="5">
         <v>0</v>
       </c>
       <c r="H128" s="6">
-        <v>420</v>
+        <v>550</v>
       </c>
     </row>
     <row outlineLevel="0" r="129">
       <c r="A129" s="4" t="inlineStr">
         <is>
-          <t>225/45R18RF</t>
+          <t>225/45R18</t>
         </is>
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>GD225/45R18RF</t>
+          <t>LF225/45R18</t>
         </is>
       </c>
       <c r="D129" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E129" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F129" s="5">
         <v>0</v>
       </c>
       <c r="G129" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H129" s="6">
-        <v>720</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="130">
       <c r="A130" s="4" t="inlineStr">
         <is>
-          <t>225/45R19</t>
+          <t>225/45R18RF</t>
         </is>
       </c>
       <c r="B130" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C130" s="4" t="inlineStr">
         <is>
-          <t>CT225/45R19</t>
+          <t>GD225/45R18RF</t>
         </is>
       </c>
       <c r="D130" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E130" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F130" s="5">
         <v>0</v>
       </c>
       <c r="G130" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H130" s="6">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row outlineLevel="0" r="131">
       <c r="A131" s="4" t="inlineStr">
         <is>
-          <t>225/50R17</t>
+          <t>225/45R19</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>GD225/50R17</t>
+          <t>CT225/45R19</t>
         </is>
       </c>
       <c r="D131" s="5">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E131" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F131" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G131" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H131" s="6">
-        <v>500</v>
+        <v>780</v>
       </c>
     </row>
     <row outlineLevel="0" r="132">
@@ -4719,60 +4719,60 @@
       </c>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C132" s="4" t="inlineStr">
         <is>
-          <t>HK225/50R17</t>
+          <t>GD225/50R17</t>
         </is>
       </c>
       <c r="D132" s="5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E132" s="5">
         <v>4</v>
       </c>
       <c r="F132" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G132" s="5">
         <v>2</v>
       </c>
       <c r="H132" s="6">
-        <v>400</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="133">
       <c r="A133" s="4" t="inlineStr">
         <is>
-          <t>225/55R16</t>
+          <t>225/50R17</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>DL225/55R16</t>
+          <t>HK225/50R17</t>
         </is>
       </c>
       <c r="D133" s="5">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E133" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F133" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G133" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H133" s="6">
-        <v>450</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="134">
@@ -4783,19 +4783,19 @@
       </c>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C134" s="4" t="inlineStr">
         <is>
-          <t>GD225/55R16</t>
+          <t>DL225/55R16</t>
         </is>
       </c>
       <c r="D134" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E134" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F134" s="5">
         <v>0</v>
@@ -4804,30 +4804,30 @@
         <v>0</v>
       </c>
       <c r="H134" s="6">
-        <v>420</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="135">
       <c r="A135" s="4" t="inlineStr">
         <is>
-          <t>225/55R17</t>
+          <t>225/55R16</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>HK225/55R17</t>
+          <t>GD225/55R16</t>
         </is>
       </c>
       <c r="D135" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E135" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F135" s="5">
         <v>0</v>
@@ -4836,71 +4836,71 @@
         <v>0</v>
       </c>
       <c r="H135" s="6">
-        <v>430</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="136">
       <c r="A136" s="4" t="inlineStr">
         <is>
-          <t>225/55R17RF</t>
+          <t>225/55R17</t>
         </is>
       </c>
       <c r="B136" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C136" s="4" t="inlineStr">
         <is>
-          <t>GD225/55R17RF</t>
+          <t>HK225/55R17</t>
         </is>
       </c>
       <c r="D136" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E136" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F136" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G136" s="5">
         <v>0</v>
       </c>
       <c r="H136" s="6">
-        <v>700</v>
+        <v>430</v>
       </c>
     </row>
     <row outlineLevel="0" r="137">
       <c r="A137" s="4" t="inlineStr">
         <is>
-          <t>225/55R18</t>
+          <t>225/55R17RF</t>
         </is>
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>HK225/55R18</t>
+          <t>GD225/55R17RF</t>
         </is>
       </c>
       <c r="D137" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E137" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F137" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G137" s="5">
         <v>0</v>
       </c>
       <c r="H137" s="6">
-        <v>500</v>
+        <v>700</v>
       </c>
     </row>
     <row outlineLevel="0" r="138">
@@ -4911,19 +4911,19 @@
       </c>
       <c r="B138" s="4" t="inlineStr">
         <is>
-          <t>KUMHO</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C138" s="4" t="inlineStr">
         <is>
-          <t>KM225/55R18</t>
+          <t>HK225/55R18</t>
         </is>
       </c>
       <c r="D138" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E138" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F138" s="5">
         <v>0</v>
@@ -4932,30 +4932,30 @@
         <v>0</v>
       </c>
       <c r="H138" s="6">
-        <v>450</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="139">
       <c r="A139" s="4" t="inlineStr">
         <is>
-          <t>225/55R19</t>
+          <t>225/55R18</t>
         </is>
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>KUMHO</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>BR225/55R19</t>
+          <t>KM225/55R18</t>
         </is>
       </c>
       <c r="D139" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E139" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F139" s="5">
         <v>0</v>
@@ -4964,7 +4964,7 @@
         <v>0</v>
       </c>
       <c r="H139" s="6">
-        <v>750</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="140">
@@ -4975,19 +4975,19 @@
       </c>
       <c r="B140" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C140" s="4" t="inlineStr">
         <is>
-          <t>GD225/55R19</t>
+          <t>BR225/55R19</t>
         </is>
       </c>
       <c r="D140" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E140" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F140" s="5">
         <v>0</v>
@@ -5002,21 +5002,21 @@
     <row outlineLevel="0" r="141">
       <c r="A141" s="4" t="inlineStr">
         <is>
-          <t>225/60R17</t>
+          <t>225/55R19</t>
         </is>
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>HK225/60R17</t>
+          <t>GD225/55R19</t>
         </is>
       </c>
       <c r="D141" s="5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E141" s="5">
         <v>4</v>
@@ -5025,65 +5025,65 @@
         <v>0</v>
       </c>
       <c r="G141" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H141" s="6">
-        <v>400</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="142">
       <c r="A142" s="4" t="inlineStr">
         <is>
-          <t>225/60R18</t>
+          <t>225/60R17</t>
         </is>
       </c>
       <c r="B142" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C142" s="4" t="inlineStr">
         <is>
-          <t>GD225/60R18</t>
+          <t>HK225/60R17</t>
         </is>
       </c>
       <c r="D142" s="5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E142" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F142" s="5">
         <v>0</v>
       </c>
       <c r="G142" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H142" s="6">
-        <v>700</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="143">
       <c r="A143" s="4" t="inlineStr">
         <is>
-          <t>225/65R17</t>
+          <t>225/60R18</t>
         </is>
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>RD225/65R17</t>
+          <t>GD225/60R18</t>
         </is>
       </c>
       <c r="D143" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E143" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F143" s="5">
         <v>0</v>
@@ -5092,13 +5092,13 @@
         <v>0</v>
       </c>
       <c r="H143" s="6">
-        <v>450</v>
+        <v>700</v>
       </c>
     </row>
     <row outlineLevel="0" r="144">
       <c r="A144" s="4" t="inlineStr">
         <is>
-          <t>225/75R15C</t>
+          <t>225/65R17</t>
         </is>
       </c>
       <c r="B144" s="4" t="inlineStr">
@@ -5108,39 +5108,39 @@
       </c>
       <c r="C144" s="4" t="inlineStr">
         <is>
-          <t>RD225/75R15C</t>
+          <t>RD225/65R17</t>
         </is>
       </c>
       <c r="D144" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E144" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F144" s="5">
         <v>0</v>
       </c>
       <c r="G144" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H144" s="6">
-        <v>330</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="145">
       <c r="A145" s="4" t="inlineStr">
         <is>
-          <t>235/35R19</t>
+          <t>225/70R15C</t>
         </is>
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>MATADOR</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>RD235/35R19</t>
+          <t>MT225/70R15C</t>
         </is>
       </c>
       <c r="D145" s="5">
@@ -5150,71 +5150,71 @@
         <v>0</v>
       </c>
       <c r="F145" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G145" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H145" s="6">
-        <v>600</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="146">
       <c r="A146" s="4" t="inlineStr">
         <is>
-          <t>235/40R19</t>
+          <t>225/75R15C</t>
         </is>
       </c>
       <c r="B146" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C146" s="4" t="inlineStr">
         <is>
-          <t>GD235/40R19</t>
+          <t>RD225/75R15C</t>
         </is>
       </c>
       <c r="D146" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E146" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F146" s="5">
         <v>0</v>
       </c>
       <c r="G146" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H146" s="6">
-        <v>850</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="147">
       <c r="A147" s="4" t="inlineStr">
         <is>
-          <t>235/45R18</t>
+          <t>235/35R19</t>
         </is>
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>GD235/45R18</t>
+          <t>RD235/35R19</t>
         </is>
       </c>
       <c r="D147" s="5">
         <v>4</v>
       </c>
       <c r="E147" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F147" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G147" s="5">
         <v>0</v>
@@ -5226,24 +5226,24 @@
     <row outlineLevel="0" r="148">
       <c r="A148" s="4" t="inlineStr">
         <is>
-          <t>235/50R18</t>
+          <t>235/40R19</t>
         </is>
       </c>
       <c r="B148" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C148" s="4" t="inlineStr">
         <is>
-          <t>HK235/50R18</t>
+          <t>GD235/40R19</t>
         </is>
       </c>
       <c r="D148" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E148" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F148" s="5">
         <v>0</v>
@@ -5252,13 +5252,13 @@
         <v>0</v>
       </c>
       <c r="H148" s="6">
-        <v>500</v>
+        <v>850</v>
       </c>
     </row>
     <row outlineLevel="0" r="149">
       <c r="A149" s="4" t="inlineStr">
         <is>
-          <t>235/50R19</t>
+          <t>235/45R18</t>
         </is>
       </c>
       <c r="B149" s="4" t="inlineStr">
@@ -5268,7 +5268,7 @@
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>GD235/50R19</t>
+          <t>GD235/45R18</t>
         </is>
       </c>
       <c r="D149" s="5">
@@ -5284,62 +5284,62 @@
         <v>0</v>
       </c>
       <c r="H149" s="6">
-        <v>800</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="150">
       <c r="A150" s="4" t="inlineStr">
         <is>
-          <t>235/50R20</t>
+          <t>235/50R18</t>
         </is>
       </c>
       <c r="B150" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C150" s="4" t="inlineStr">
         <is>
-          <t>GD235/50R20</t>
+          <t>HK235/50R18</t>
         </is>
       </c>
       <c r="D150" s="5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E150" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F150" s="5">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G150" s="5">
         <v>0</v>
       </c>
       <c r="H150" s="6">
-        <v>1180</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="151">
       <c r="A151" s="4" t="inlineStr">
         <is>
-          <t>235/55R17</t>
+          <t>235/50R19</t>
         </is>
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>BR235/55R17</t>
+          <t>GD235/50R19</t>
         </is>
       </c>
       <c r="D151" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E151" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F151" s="5">
         <v>0</v>
@@ -5348,62 +5348,62 @@
         <v>0</v>
       </c>
       <c r="H151" s="6">
-        <v>450</v>
+        <v>800</v>
       </c>
     </row>
     <row outlineLevel="0" r="152">
       <c r="A152" s="4" t="inlineStr">
         <is>
-          <t>235/55R18</t>
+          <t>235/50R20</t>
         </is>
       </c>
       <c r="B152" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C152" s="4" t="inlineStr">
         <is>
-          <t>HK235/55R18</t>
+          <t>GD235/50R20</t>
         </is>
       </c>
       <c r="D152" s="5">
         <v>7</v>
       </c>
       <c r="E152" s="5">
+        <v>0</v>
+      </c>
+      <c r="F152" s="5">
         <v>7</v>
       </c>
-      <c r="F152" s="5">
-        <v>0</v>
-      </c>
       <c r="G152" s="5">
         <v>0</v>
       </c>
       <c r="H152" s="6">
-        <v>480</v>
+        <v>1180</v>
       </c>
     </row>
     <row outlineLevel="0" r="153">
       <c r="A153" s="4" t="inlineStr">
         <is>
-          <t>235/55R19</t>
+          <t>235/55R17</t>
         </is>
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>GD235/55R19</t>
+          <t>BR235/55R17</t>
         </is>
       </c>
       <c r="D153" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E153" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F153" s="5">
         <v>0</v>
@@ -5412,13 +5412,13 @@
         <v>0</v>
       </c>
       <c r="H153" s="6">
-        <v>750</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="154">
       <c r="A154" s="4" t="inlineStr">
         <is>
-          <t>235/55R19</t>
+          <t>235/55R18</t>
         </is>
       </c>
       <c r="B154" s="4" t="inlineStr">
@@ -5428,14 +5428,14 @@
       </c>
       <c r="C154" s="4" t="inlineStr">
         <is>
-          <t>HK235/55R19</t>
+          <t>HK235/55R18</t>
         </is>
       </c>
       <c r="D154" s="5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E154" s="5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F154" s="5">
         <v>0</v>
@@ -5444,7 +5444,7 @@
         <v>0</v>
       </c>
       <c r="H154" s="6">
-        <v>630</v>
+        <v>480</v>
       </c>
     </row>
     <row outlineLevel="0" r="155">
@@ -5455,19 +5455,19 @@
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>LF235/55R19</t>
+          <t>GD235/55R19</t>
         </is>
       </c>
       <c r="D155" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E155" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F155" s="5">
         <v>0</v>
@@ -5476,7 +5476,7 @@
         <v>0</v>
       </c>
       <c r="H155" s="6">
-        <v>500</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="156">
@@ -5487,19 +5487,19 @@
       </c>
       <c r="B156" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C156" s="4" t="inlineStr">
         <is>
-          <t>NX235/55R19</t>
+          <t>HK235/55R19</t>
         </is>
       </c>
       <c r="D156" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E156" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F156" s="5">
         <v>0</v>
@@ -5508,7 +5508,7 @@
         <v>0</v>
       </c>
       <c r="H156" s="6">
-        <v>600</v>
+        <v>630</v>
       </c>
     </row>
     <row outlineLevel="0" r="157">
@@ -5519,22 +5519,22 @@
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>RD235/55R19</t>
+          <t>LF235/55R19</t>
         </is>
       </c>
       <c r="D157" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E157" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F157" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G157" s="5">
         <v>0</v>
@@ -5546,24 +5546,24 @@
     <row outlineLevel="0" r="158">
       <c r="A158" s="4" t="inlineStr">
         <is>
-          <t>235/60R16</t>
+          <t>235/55R19</t>
         </is>
       </c>
       <c r="B158" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C158" s="4" t="inlineStr">
         <is>
-          <t>HK235/60R16</t>
+          <t>NX235/55R19</t>
         </is>
       </c>
       <c r="D158" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E158" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F158" s="5">
         <v>0</v>
@@ -5572,33 +5572,33 @@
         <v>0</v>
       </c>
       <c r="H158" s="6">
-        <v>430</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="159">
       <c r="A159" s="4" t="inlineStr">
         <is>
-          <t>235/60R17</t>
+          <t>235/55R19</t>
         </is>
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>HK235/60R17</t>
+          <t>RD235/55R19</t>
         </is>
       </c>
       <c r="D159" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E159" s="5">
         <v>0</v>
       </c>
       <c r="F159" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G159" s="5">
         <v>0</v>
@@ -5610,24 +5610,24 @@
     <row outlineLevel="0" r="160">
       <c r="A160" s="4" t="inlineStr">
         <is>
-          <t>235/60R18</t>
+          <t>235/60R16</t>
         </is>
       </c>
       <c r="B160" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C160" s="4" t="inlineStr">
         <is>
-          <t>GD235/60R18</t>
+          <t>HK235/60R16</t>
         </is>
       </c>
       <c r="D160" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E160" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F160" s="5">
         <v>0</v>
@@ -5636,13 +5636,13 @@
         <v>0</v>
       </c>
       <c r="H160" s="6">
-        <v>680</v>
+        <v>430</v>
       </c>
     </row>
     <row outlineLevel="0" r="161">
       <c r="A161" s="4" t="inlineStr">
         <is>
-          <t>235/60R18</t>
+          <t>235/60R17</t>
         </is>
       </c>
       <c r="B161" s="4" t="inlineStr">
@@ -5652,29 +5652,29 @@
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>HK235/60R18</t>
+          <t>HK235/60R17</t>
         </is>
       </c>
       <c r="D161" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E161" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F161" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G161" s="5">
         <v>0</v>
       </c>
       <c r="H161" s="6">
-        <v>550</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="162">
       <c r="A162" s="4" t="inlineStr">
         <is>
-          <t>245/40R17</t>
+          <t>235/60R18</t>
         </is>
       </c>
       <c r="B162" s="4" t="inlineStr">
@@ -5684,14 +5684,14 @@
       </c>
       <c r="C162" s="4" t="inlineStr">
         <is>
-          <t>GD245/40R17</t>
+          <t>GD235/60R18</t>
         </is>
       </c>
       <c r="D162" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E162" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F162" s="5">
         <v>0</v>
@@ -5700,27 +5700,27 @@
         <v>0</v>
       </c>
       <c r="H162" s="6">
-        <v>400</v>
+        <v>680</v>
       </c>
     </row>
     <row outlineLevel="0" r="163">
       <c r="A163" s="4" t="inlineStr">
         <is>
-          <t>245/40R18</t>
+          <t>235/60R18</t>
         </is>
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>GD245/40R18</t>
+          <t>HK235/60R18</t>
         </is>
       </c>
       <c r="D163" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E163" s="5">
         <v>2</v>
@@ -5729,33 +5729,33 @@
         <v>0</v>
       </c>
       <c r="G163" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H163" s="6">
-        <v>620</v>
+        <v>550</v>
       </c>
     </row>
     <row outlineLevel="0" r="164">
       <c r="A164" s="4" t="inlineStr">
         <is>
-          <t>245/40R19</t>
+          <t>245/40R17</t>
         </is>
       </c>
       <c r="B164" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C164" s="4" t="inlineStr">
         <is>
-          <t>HK245/40R19</t>
+          <t>GD245/40R17</t>
         </is>
       </c>
       <c r="D164" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E164" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F164" s="5">
         <v>0</v>
@@ -5764,45 +5764,45 @@
         <v>0</v>
       </c>
       <c r="H164" s="6">
-        <v>750</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="165">
       <c r="A165" s="4" t="inlineStr">
         <is>
-          <t>245/40R20</t>
+          <t>245/40R18</t>
         </is>
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>CT245/40R20</t>
+          <t>GD245/40R18</t>
         </is>
       </c>
       <c r="D165" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E165" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F165" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G165" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H165" s="6">
-        <v>1050</v>
+        <v>620</v>
       </c>
     </row>
     <row outlineLevel="0" r="166">
       <c r="A166" s="4" t="inlineStr">
         <is>
-          <t>245/45R17</t>
+          <t>245/40R19</t>
         </is>
       </c>
       <c r="B166" s="4" t="inlineStr">
@@ -5812,7 +5812,7 @@
       </c>
       <c r="C166" s="4" t="inlineStr">
         <is>
-          <t>HK245/45R17</t>
+          <t>HK245/40R19</t>
         </is>
       </c>
       <c r="D166" s="5">
@@ -5828,13 +5828,13 @@
         <v>0</v>
       </c>
       <c r="H166" s="6">
-        <v>430</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="167">
       <c r="A167" s="4" t="inlineStr">
         <is>
-          <t>245/45R18</t>
+          <t>245/40R20</t>
         </is>
       </c>
       <c r="B167" s="4" t="inlineStr">
@@ -5844,46 +5844,46 @@
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>CT245/45R18</t>
+          <t>CT245/40R20</t>
         </is>
       </c>
       <c r="D167" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E167" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F167" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G167" s="5">
         <v>0</v>
       </c>
       <c r="H167" s="6">
-        <v>650</v>
+        <v>1050</v>
       </c>
     </row>
     <row outlineLevel="0" r="168">
       <c r="A168" s="4" t="inlineStr">
         <is>
-          <t>245/45R18</t>
+          <t>245/45R17</t>
         </is>
       </c>
       <c r="B168" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C168" s="4" t="inlineStr">
         <is>
-          <t>GD245/45R18</t>
+          <t>HK245/45R17</t>
         </is>
       </c>
       <c r="D168" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E168" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F168" s="5">
         <v>0</v>
@@ -5892,7 +5892,7 @@
         <v>0</v>
       </c>
       <c r="H168" s="6">
-        <v>600</v>
+        <v>430</v>
       </c>
     </row>
     <row outlineLevel="0" r="169">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>HK245/45R18</t>
+          <t>CT245/45R18</t>
         </is>
       </c>
       <c r="D169" s="5">
@@ -5924,13 +5924,13 @@
         <v>0</v>
       </c>
       <c r="H169" s="6">
-        <v>500</v>
+        <v>650</v>
       </c>
     </row>
     <row outlineLevel="0" r="170">
       <c r="A170" s="4" t="inlineStr">
         <is>
-          <t>245/45R18RF</t>
+          <t>245/45R18</t>
         </is>
       </c>
       <c r="B170" s="4" t="inlineStr">
@@ -5940,14 +5940,14 @@
       </c>
       <c r="C170" s="4" t="inlineStr">
         <is>
-          <t>GD245/45R18RF</t>
+          <t>GD245/45R18</t>
         </is>
       </c>
       <c r="D170" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E170" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F170" s="5">
         <v>0</v>
@@ -5956,30 +5956,30 @@
         <v>0</v>
       </c>
       <c r="H170" s="6">
-        <v>720</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="171">
       <c r="A171" s="4" t="inlineStr">
         <is>
-          <t>245/45R19</t>
+          <t>245/45R18</t>
         </is>
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t>BR245/45R19</t>
+          <t>HK245/45R18</t>
         </is>
       </c>
       <c r="D171" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E171" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F171" s="5">
         <v>0</v>
@@ -5988,119 +5988,119 @@
         <v>0</v>
       </c>
       <c r="H171" s="6">
-        <v>790</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="172">
       <c r="A172" s="4" t="inlineStr">
         <is>
-          <t>245/45R19</t>
+          <t>245/45R18RF</t>
         </is>
       </c>
       <c r="B172" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C172" s="4" t="inlineStr">
         <is>
-          <t>RD245/45R19</t>
+          <t>GD245/45R18RF</t>
         </is>
       </c>
       <c r="D172" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E172" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F172" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G172" s="5">
         <v>0</v>
       </c>
       <c r="H172" s="6">
-        <v>450</v>
+        <v>720</v>
       </c>
     </row>
     <row outlineLevel="0" r="173">
       <c r="A173" s="4" t="inlineStr">
         <is>
-          <t>245/45R20</t>
+          <t>245/45R19</t>
         </is>
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>HK245/45R20</t>
+          <t>BR245/45R19</t>
         </is>
       </c>
       <c r="D173" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E173" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F173" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G173" s="5">
         <v>0</v>
       </c>
       <c r="H173" s="6">
-        <v>750</v>
+        <v>790</v>
       </c>
     </row>
     <row outlineLevel="0" r="174">
       <c r="A174" s="4" t="inlineStr">
         <is>
-          <t>245/65R17</t>
+          <t>245/45R19</t>
         </is>
       </c>
       <c r="B174" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C174" s="4" t="inlineStr">
         <is>
-          <t>NX245/65R17</t>
+          <t>RD245/45R19</t>
         </is>
       </c>
       <c r="D174" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E174" s="5">
         <v>0</v>
       </c>
       <c r="F174" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G174" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H174" s="6">
-        <v>600</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="175">
       <c r="A175" s="4" t="inlineStr">
         <is>
-          <t>245/70R16</t>
+          <t>245/45R20</t>
         </is>
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>LASSA</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>LS245/70R16</t>
+          <t>HK245/45R20</t>
         </is>
       </c>
       <c r="D175" s="5">
@@ -6110,93 +6110,93 @@
         <v>0</v>
       </c>
       <c r="F175" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G175" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H175" s="6">
-        <v>500</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="176">
       <c r="A176" s="4" t="inlineStr">
         <is>
-          <t>255/35R19</t>
+          <t>245/65R17</t>
         </is>
       </c>
       <c r="B176" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C176" s="4" t="inlineStr">
         <is>
-          <t>DL255/35R19</t>
+          <t>NX245/65R17</t>
         </is>
       </c>
       <c r="D176" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E176" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F176" s="5">
         <v>0</v>
       </c>
       <c r="G176" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H176" s="6">
-        <v>700</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="177">
       <c r="A177" s="4" t="inlineStr">
         <is>
-          <t>255/35R19RF</t>
+          <t>245/70R16</t>
         </is>
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>LASSA</t>
         </is>
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>CT255/35R19RF</t>
+          <t>LS245/70R16</t>
         </is>
       </c>
       <c r="D177" s="5">
         <v>2</v>
       </c>
       <c r="E177" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F177" s="5">
         <v>0</v>
       </c>
       <c r="G177" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H177" s="6">
-        <v>950</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="178">
       <c r="A178" s="4" t="inlineStr">
         <is>
-          <t>255/35R19RF</t>
+          <t>255/35R19</t>
         </is>
       </c>
       <c r="B178" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C178" s="4" t="inlineStr">
         <is>
-          <t>GD255/35R19RF</t>
+          <t>DL255/35R19</t>
         </is>
       </c>
       <c r="D178" s="5">
@@ -6212,13 +6212,13 @@
         <v>0</v>
       </c>
       <c r="H178" s="6">
-        <v>950</v>
+        <v>700</v>
       </c>
     </row>
     <row outlineLevel="0" r="179">
       <c r="A179" s="4" t="inlineStr">
         <is>
-          <t>255/50R19</t>
+          <t>255/35R19RF</t>
         </is>
       </c>
       <c r="B179" s="4" t="inlineStr">
@@ -6228,61 +6228,61 @@
       </c>
       <c r="C179" s="4" t="inlineStr">
         <is>
-          <t>CT255/50R19</t>
+          <t>CT255/35R19RF</t>
         </is>
       </c>
       <c r="D179" s="5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E179" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F179" s="5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G179" s="5">
         <v>0</v>
       </c>
       <c r="H179" s="6">
-        <v>750</v>
+        <v>950</v>
       </c>
     </row>
     <row outlineLevel="0" r="180">
       <c r="A180" s="4" t="inlineStr">
         <is>
-          <t>255/50R20</t>
+          <t>255/35R19RF</t>
         </is>
       </c>
       <c r="B180" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C180" s="4" t="inlineStr">
         <is>
-          <t>CT255/50R20</t>
+          <t>GD255/35R19RF</t>
         </is>
       </c>
       <c r="D180" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E180" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F180" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G180" s="5">
         <v>0</v>
       </c>
       <c r="H180" s="6">
-        <v>900</v>
+        <v>950</v>
       </c>
     </row>
     <row outlineLevel="0" r="181">
       <c r="A181" s="4" t="inlineStr">
         <is>
-          <t>255/55R19</t>
+          <t>255/50R19</t>
         </is>
       </c>
       <c r="B181" s="4" t="inlineStr">
@@ -6292,17 +6292,17 @@
       </c>
       <c r="C181" s="4" t="inlineStr">
         <is>
-          <t>CT255/55R19</t>
+          <t>CT255/50R19</t>
         </is>
       </c>
       <c r="D181" s="5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E181" s="5">
         <v>0</v>
       </c>
       <c r="F181" s="5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G181" s="5">
         <v>0</v>
@@ -6314,49 +6314,49 @@
     <row outlineLevel="0" r="182">
       <c r="A182" s="4" t="inlineStr">
         <is>
-          <t>255/55R19</t>
+          <t>255/50R20</t>
         </is>
       </c>
       <c r="B182" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C182" s="4" t="inlineStr">
         <is>
-          <t>DL255/55R19</t>
+          <t>CT255/50R20</t>
         </is>
       </c>
       <c r="D182" s="5">
         <v>2</v>
       </c>
       <c r="E182" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F182" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G182" s="5">
         <v>0</v>
       </c>
       <c r="H182" s="6">
-        <v>700</v>
+        <v>900</v>
       </c>
     </row>
     <row outlineLevel="0" r="183">
       <c r="A183" s="4" t="inlineStr">
         <is>
-          <t>255/70R16</t>
+          <t>255/55R19</t>
         </is>
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C183" s="4" t="inlineStr">
         <is>
-          <t>RD255/70R16</t>
+          <t>CT255/55R19</t>
         </is>
       </c>
       <c r="D183" s="5">
@@ -6366,36 +6366,36 @@
         <v>0</v>
       </c>
       <c r="F183" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G183" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H183" s="6">
-        <v>500</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="184">
       <c r="A184" s="4" t="inlineStr">
         <is>
-          <t>265/35R18</t>
+          <t>255/55R19</t>
         </is>
       </c>
       <c r="B184" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C184" s="4" t="inlineStr">
         <is>
-          <t>GD265/35R18</t>
+          <t>DL255/55R19</t>
         </is>
       </c>
       <c r="D184" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E184" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F184" s="5">
         <v>0</v>
@@ -6410,39 +6410,39 @@
     <row outlineLevel="0" r="185">
       <c r="A185" s="4" t="inlineStr">
         <is>
-          <t>265/50R20</t>
+          <t>255/70R16</t>
         </is>
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C185" s="4" t="inlineStr">
         <is>
-          <t>GD265/50R20</t>
+          <t>RD255/70R16</t>
         </is>
       </c>
       <c r="D185" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E185" s="5">
         <v>0</v>
       </c>
       <c r="F185" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G185" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H185" s="6">
-        <v>1150</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="186">
       <c r="A186" s="4" t="inlineStr">
         <is>
-          <t>275/35R19RF</t>
+          <t>265/35R18</t>
         </is>
       </c>
       <c r="B186" s="4" t="inlineStr">
@@ -6452,14 +6452,14 @@
       </c>
       <c r="C186" s="4" t="inlineStr">
         <is>
-          <t>GD275/35R19RF</t>
+          <t>GD265/35R18</t>
         </is>
       </c>
       <c r="D186" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E186" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F186" s="5">
         <v>0</v>
@@ -6468,87 +6468,87 @@
         <v>0</v>
       </c>
       <c r="H186" s="6">
-        <v>1</v>
+        <v>700</v>
       </c>
     </row>
     <row outlineLevel="0" r="187">
       <c r="A187" s="4" t="inlineStr">
         <is>
-          <t>275/35R20</t>
+          <t>265/50R20</t>
         </is>
       </c>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C187" s="4" t="inlineStr">
         <is>
-          <t>CT275/35R20</t>
+          <t>GD265/50R20</t>
         </is>
       </c>
       <c r="D187" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E187" s="5">
         <v>0</v>
       </c>
       <c r="F187" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G187" s="5">
         <v>0</v>
       </c>
       <c r="H187" s="6">
-        <v>980</v>
+        <v>1150</v>
       </c>
     </row>
     <row outlineLevel="0" r="188">
       <c r="A188" s="4" t="inlineStr">
         <is>
-          <t>275/40R20</t>
+          <t>275/35R19RF</t>
         </is>
       </c>
       <c r="B188" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C188" s="4" t="inlineStr">
         <is>
-          <t>HK275/40R20</t>
+          <t>GD275/35R19RF</t>
         </is>
       </c>
       <c r="D188" s="5">
         <v>2</v>
       </c>
       <c r="E188" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F188" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G188" s="5">
         <v>0</v>
       </c>
       <c r="H188" s="6">
-        <v>770</v>
+        <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="189">
       <c r="A189" s="4" t="inlineStr">
         <is>
-          <t>275/50R21</t>
+          <t>275/35R20</t>
         </is>
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C189" s="4" t="inlineStr">
         <is>
-          <t>GD275/50R21</t>
+          <t>CT275/35R20</t>
         </is>
       </c>
       <c r="D189" s="5">
@@ -6564,23 +6564,23 @@
         <v>0</v>
       </c>
       <c r="H189" s="6">
-        <v>1</v>
+        <v>980</v>
       </c>
     </row>
     <row outlineLevel="0" r="190">
       <c r="A190" s="4" t="inlineStr">
         <is>
-          <t>295/35R21</t>
+          <t>275/40R20</t>
         </is>
       </c>
       <c r="B190" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C190" s="4" t="inlineStr">
         <is>
-          <t>CT295/35R21</t>
+          <t>HK275/40R20</t>
         </is>
       </c>
       <c r="D190" s="5">
@@ -6596,13 +6596,13 @@
         <v>0</v>
       </c>
       <c r="H190" s="6">
-        <v>1150</v>
+        <v>770</v>
       </c>
     </row>
     <row outlineLevel="0" r="191">
       <c r="A191" s="4" t="inlineStr">
         <is>
-          <t>295/35R21</t>
+          <t>275/50R21</t>
         </is>
       </c>
       <c r="B191" s="4" t="inlineStr">
@@ -6612,54 +6612,118 @@
       </c>
       <c r="C191" s="4" t="inlineStr">
         <is>
-          <t>GD295/35R21</t>
+          <t>GD275/50R21</t>
         </is>
       </c>
       <c r="D191" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E191" s="5">
         <v>0</v>
       </c>
       <c r="F191" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G191" s="5">
         <v>0</v>
       </c>
       <c r="H191" s="6">
-        <v>980</v>
+        <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="192">
       <c r="A192" s="4" t="inlineStr">
         <is>
+          <t>295/35R21</t>
+        </is>
+      </c>
+      <c r="B192" s="4" t="inlineStr">
+        <is>
+          <t>CONTINENTAL</t>
+        </is>
+      </c>
+      <c r="C192" s="4" t="inlineStr">
+        <is>
+          <t>CT295/35R21</t>
+        </is>
+      </c>
+      <c r="D192" s="5">
+        <v>2</v>
+      </c>
+      <c r="E192" s="5">
+        <v>0</v>
+      </c>
+      <c r="F192" s="5">
+        <v>2</v>
+      </c>
+      <c r="G192" s="5">
+        <v>0</v>
+      </c>
+      <c r="H192" s="6">
+        <v>1150</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="193">
+      <c r="A193" s="4" t="inlineStr">
+        <is>
+          <t>295/35R21</t>
+        </is>
+      </c>
+      <c r="B193" s="4" t="inlineStr">
+        <is>
+          <t>GOODYEAR</t>
+        </is>
+      </c>
+      <c r="C193" s="4" t="inlineStr">
+        <is>
+          <t>GD295/35R21</t>
+        </is>
+      </c>
+      <c r="D193" s="5">
+        <v>3</v>
+      </c>
+      <c r="E193" s="5">
+        <v>0</v>
+      </c>
+      <c r="F193" s="5">
+        <v>3</v>
+      </c>
+      <c r="G193" s="5">
+        <v>0</v>
+      </c>
+      <c r="H193" s="6">
+        <v>980</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="194">
+      <c r="A194" s="4" t="inlineStr">
+        <is>
           <t>500R12</t>
         </is>
       </c>
-      <c r="B192" s="4" t="inlineStr">
+      <c r="B194" s="4" t="inlineStr">
         <is>
           <t>RADIAL</t>
         </is>
       </c>
-      <c r="C192" s="4" t="inlineStr">
+      <c r="C194" s="4" t="inlineStr">
         <is>
           <t>RD500R12</t>
         </is>
       </c>
-      <c r="D192" s="5">
+      <c r="D194" s="5">
         <v>3</v>
       </c>
-      <c r="E192" s="5">
+      <c r="E194" s="5">
         <v>3</v>
       </c>
-      <c r="F192" s="5">
-        <v>0</v>
-      </c>
-      <c r="G192" s="5">
-        <v>0</v>
-      </c>
-      <c r="H192" s="6">
+      <c r="F194" s="5">
+        <v>0</v>
+      </c>
+      <c r="G194" s="5">
+        <v>0</v>
+      </c>
+      <c r="H194" s="6">
         <v>300</v>
       </c>
     </row>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -496,7 +496,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H194"/>
+  <dimension ref="A1:H195"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col customWidth="true" min="1" max="1" width="13.8359375"/>
@@ -600,10 +600,10 @@
         </is>
       </c>
       <c r="D3" s="5">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E3" s="5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F3" s="5">
         <v>0</v>
@@ -728,10 +728,10 @@
         </is>
       </c>
       <c r="D7" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E7" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F7" s="5">
         <v>0</v>
@@ -760,16 +760,16 @@
         </is>
       </c>
       <c r="D8" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E8" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F8" s="5">
         <v>0</v>
       </c>
       <c r="G8" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H8" s="6">
         <v>180</v>
@@ -984,10 +984,10 @@
         </is>
       </c>
       <c r="D15" s="5">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E15" s="5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F15" s="5">
         <v>92</v>
@@ -1080,13 +1080,13 @@
         </is>
       </c>
       <c r="D18" s="5">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E18" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F18" s="5">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G18" s="5">
         <v>5</v>
@@ -1112,10 +1112,10 @@
         </is>
       </c>
       <c r="D19" s="5">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E19" s="5">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F19" s="5">
         <v>0</v>
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="D22" s="5">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E22" s="5">
         <v>34</v>
@@ -1217,7 +1217,7 @@
         <v>0</v>
       </c>
       <c r="G22" s="5">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H22" s="6">
         <v>200</v>
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="D26" s="5">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E26" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F26" s="5">
         <v>11</v>
@@ -1816,10 +1816,10 @@
         </is>
       </c>
       <c r="D41" s="5">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E41" s="5">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F41" s="5">
         <v>0</v>
@@ -2040,7 +2040,7 @@
         </is>
       </c>
       <c r="D48" s="5">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E48" s="5">
         <v>4</v>
@@ -2049,7 +2049,7 @@
         <v>10</v>
       </c>
       <c r="G48" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H48" s="6">
         <v>350</v>
@@ -2424,13 +2424,13 @@
         </is>
       </c>
       <c r="D60" s="5">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E60" s="5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F60" s="5">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="G60" s="5">
         <v>13</v>
@@ -2904,7 +2904,7 @@
         </is>
       </c>
       <c r="D75" s="5">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E75" s="5">
         <v>4</v>
@@ -2913,7 +2913,7 @@
         <v>3</v>
       </c>
       <c r="G75" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H75" s="6">
         <v>260</v>
@@ -3128,7 +3128,7 @@
         </is>
       </c>
       <c r="D82" s="5">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E82" s="5">
         <v>6</v>
@@ -3137,7 +3137,7 @@
         <v>1</v>
       </c>
       <c r="G82" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H82" s="6">
         <v>300</v>
@@ -3224,10 +3224,10 @@
         </is>
       </c>
       <c r="D85" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E85" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F85" s="5">
         <v>0</v>
@@ -3291,10 +3291,10 @@
         <v>7</v>
       </c>
       <c r="E87" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F87" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G87" s="5">
         <v>1</v>
@@ -4504,10 +4504,10 @@
         </is>
       </c>
       <c r="D125" s="5">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E125" s="5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F125" s="5">
         <v>19</v>
@@ -4600,13 +4600,13 @@
         </is>
       </c>
       <c r="D128" s="5">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E128" s="5">
         <v>4</v>
       </c>
       <c r="F128" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G128" s="5">
         <v>0</v>
@@ -4664,7 +4664,7 @@
         </is>
       </c>
       <c r="D130" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E130" s="5">
         <v>2</v>
@@ -4673,7 +4673,7 @@
         <v>0</v>
       </c>
       <c r="G130" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H130" s="6">
         <v>720</v>
@@ -4719,28 +4719,28 @@
       </c>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C132" s="4" t="inlineStr">
         <is>
-          <t>GD225/50R17</t>
+          <t>BR225/50R17</t>
         </is>
       </c>
       <c r="D132" s="5">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E132" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F132" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G132" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H132" s="6">
-        <v>500</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="133">
@@ -4751,60 +4751,60 @@
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>HK225/50R17</t>
+          <t>GD225/50R17</t>
         </is>
       </c>
       <c r="D133" s="5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E133" s="5">
         <v>4</v>
       </c>
       <c r="F133" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G133" s="5">
         <v>2</v>
       </c>
       <c r="H133" s="6">
-        <v>400</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="134">
       <c r="A134" s="4" t="inlineStr">
         <is>
-          <t>225/55R16</t>
+          <t>225/50R17</t>
         </is>
       </c>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C134" s="4" t="inlineStr">
         <is>
-          <t>DL225/55R16</t>
+          <t>HK225/50R17</t>
         </is>
       </c>
       <c r="D134" s="5">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E134" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F134" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G134" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H134" s="6">
-        <v>450</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="135">
@@ -4815,19 +4815,19 @@
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>GD225/55R16</t>
+          <t>DL225/55R16</t>
         </is>
       </c>
       <c r="D135" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E135" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F135" s="5">
         <v>0</v>
@@ -4836,30 +4836,30 @@
         <v>0</v>
       </c>
       <c r="H135" s="6">
-        <v>420</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="136">
       <c r="A136" s="4" t="inlineStr">
         <is>
-          <t>225/55R17</t>
+          <t>225/55R16</t>
         </is>
       </c>
       <c r="B136" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C136" s="4" t="inlineStr">
         <is>
-          <t>HK225/55R17</t>
+          <t>GD225/55R16</t>
         </is>
       </c>
       <c r="D136" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E136" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F136" s="5">
         <v>0</v>
@@ -4868,71 +4868,71 @@
         <v>0</v>
       </c>
       <c r="H136" s="6">
-        <v>430</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="137">
       <c r="A137" s="4" t="inlineStr">
         <is>
-          <t>225/55R17RF</t>
+          <t>225/55R17</t>
         </is>
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>GD225/55R17RF</t>
+          <t>HK225/55R17</t>
         </is>
       </c>
       <c r="D137" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E137" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F137" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G137" s="5">
         <v>0</v>
       </c>
       <c r="H137" s="6">
-        <v>700</v>
+        <v>430</v>
       </c>
     </row>
     <row outlineLevel="0" r="138">
       <c r="A138" s="4" t="inlineStr">
         <is>
-          <t>225/55R18</t>
+          <t>225/55R17RF</t>
         </is>
       </c>
       <c r="B138" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C138" s="4" t="inlineStr">
         <is>
-          <t>HK225/55R18</t>
+          <t>GD225/55R17RF</t>
         </is>
       </c>
       <c r="D138" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E138" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F138" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G138" s="5">
         <v>0</v>
       </c>
       <c r="H138" s="6">
-        <v>500</v>
+        <v>700</v>
       </c>
     </row>
     <row outlineLevel="0" r="139">
@@ -4943,19 +4943,19 @@
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>KUMHO</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>KM225/55R18</t>
+          <t>HK225/55R18</t>
         </is>
       </c>
       <c r="D139" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E139" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F139" s="5">
         <v>0</v>
@@ -4964,30 +4964,30 @@
         <v>0</v>
       </c>
       <c r="H139" s="6">
-        <v>450</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="140">
       <c r="A140" s="4" t="inlineStr">
         <is>
-          <t>225/55R19</t>
+          <t>225/55R18</t>
         </is>
       </c>
       <c r="B140" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>KUMHO</t>
         </is>
       </c>
       <c r="C140" s="4" t="inlineStr">
         <is>
-          <t>BR225/55R19</t>
+          <t>KM225/55R18</t>
         </is>
       </c>
       <c r="D140" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E140" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F140" s="5">
         <v>0</v>
@@ -4996,7 +4996,7 @@
         <v>0</v>
       </c>
       <c r="H140" s="6">
-        <v>750</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="141">
@@ -5007,19 +5007,19 @@
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>GD225/55R19</t>
+          <t>BR225/55R19</t>
         </is>
       </c>
       <c r="D141" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E141" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F141" s="5">
         <v>0</v>
@@ -5034,21 +5034,21 @@
     <row outlineLevel="0" r="142">
       <c r="A142" s="4" t="inlineStr">
         <is>
-          <t>225/60R17</t>
+          <t>225/55R19</t>
         </is>
       </c>
       <c r="B142" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C142" s="4" t="inlineStr">
         <is>
-          <t>HK225/60R17</t>
+          <t>GD225/55R19</t>
         </is>
       </c>
       <c r="D142" s="5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E142" s="5">
         <v>4</v>
@@ -5057,65 +5057,65 @@
         <v>0</v>
       </c>
       <c r="G142" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H142" s="6">
-        <v>400</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="143">
       <c r="A143" s="4" t="inlineStr">
         <is>
-          <t>225/60R18</t>
+          <t>225/60R17</t>
         </is>
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>GD225/60R18</t>
+          <t>HK225/60R17</t>
         </is>
       </c>
       <c r="D143" s="5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E143" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F143" s="5">
         <v>0</v>
       </c>
       <c r="G143" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H143" s="6">
-        <v>700</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="144">
       <c r="A144" s="4" t="inlineStr">
         <is>
-          <t>225/65R17</t>
+          <t>225/60R18</t>
         </is>
       </c>
       <c r="B144" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C144" s="4" t="inlineStr">
         <is>
-          <t>RD225/65R17</t>
+          <t>GD225/60R18</t>
         </is>
       </c>
       <c r="D144" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E144" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F144" s="5">
         <v>0</v>
@@ -5124,36 +5124,36 @@
         <v>0</v>
       </c>
       <c r="H144" s="6">
-        <v>450</v>
+        <v>700</v>
       </c>
     </row>
     <row outlineLevel="0" r="145">
       <c r="A145" s="4" t="inlineStr">
         <is>
-          <t>225/70R15C</t>
+          <t>225/65R17</t>
         </is>
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>MATADOR</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>MT225/70R15C</t>
+          <t>RD225/65R17</t>
         </is>
       </c>
       <c r="D145" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E145" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F145" s="5">
         <v>0</v>
       </c>
       <c r="G145" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H145" s="6">
         <v>450</v>
@@ -5162,21 +5162,21 @@
     <row outlineLevel="0" r="146">
       <c r="A146" s="4" t="inlineStr">
         <is>
-          <t>225/75R15C</t>
+          <t>225/70R15C</t>
         </is>
       </c>
       <c r="B146" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>MATADOR</t>
         </is>
       </c>
       <c r="C146" s="4" t="inlineStr">
         <is>
-          <t>RD225/75R15C</t>
+          <t>MT225/70R15C</t>
         </is>
       </c>
       <c r="D146" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E146" s="5">
         <v>0</v>
@@ -5185,16 +5185,16 @@
         <v>0</v>
       </c>
       <c r="G146" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H146" s="6">
-        <v>330</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="147">
       <c r="A147" s="4" t="inlineStr">
         <is>
-          <t>235/35R19</t>
+          <t>225/75R15C</t>
         </is>
       </c>
       <c r="B147" s="4" t="inlineStr">
@@ -5204,61 +5204,61 @@
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>RD235/35R19</t>
+          <t>RD225/75R15C</t>
         </is>
       </c>
       <c r="D147" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E147" s="5">
         <v>0</v>
       </c>
       <c r="F147" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G147" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H147" s="6">
-        <v>600</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="148">
       <c r="A148" s="4" t="inlineStr">
         <is>
-          <t>235/40R19</t>
+          <t>235/35R19</t>
         </is>
       </c>
       <c r="B148" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C148" s="4" t="inlineStr">
         <is>
-          <t>GD235/40R19</t>
+          <t>RD235/35R19</t>
         </is>
       </c>
       <c r="D148" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E148" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F148" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G148" s="5">
         <v>0</v>
       </c>
       <c r="H148" s="6">
-        <v>850</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="149">
       <c r="A149" s="4" t="inlineStr">
         <is>
-          <t>235/45R18</t>
+          <t>235/40R19</t>
         </is>
       </c>
       <c r="B149" s="4" t="inlineStr">
@@ -5268,14 +5268,14 @@
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>GD235/45R18</t>
+          <t>GD235/40R19</t>
         </is>
       </c>
       <c r="D149" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E149" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F149" s="5">
         <v>0</v>
@@ -5284,30 +5284,30 @@
         <v>0</v>
       </c>
       <c r="H149" s="6">
-        <v>600</v>
+        <v>850</v>
       </c>
     </row>
     <row outlineLevel="0" r="150">
       <c r="A150" s="4" t="inlineStr">
         <is>
-          <t>235/50R18</t>
+          <t>235/45R18</t>
         </is>
       </c>
       <c r="B150" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C150" s="4" t="inlineStr">
         <is>
-          <t>HK235/50R18</t>
+          <t>GD235/45R18</t>
         </is>
       </c>
       <c r="D150" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E150" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F150" s="5">
         <v>0</v>
@@ -5316,30 +5316,30 @@
         <v>0</v>
       </c>
       <c r="H150" s="6">
-        <v>500</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="151">
       <c r="A151" s="4" t="inlineStr">
         <is>
-          <t>235/50R19</t>
+          <t>235/50R18</t>
         </is>
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>GD235/50R19</t>
+          <t>HK235/50R18</t>
         </is>
       </c>
       <c r="D151" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E151" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F151" s="5">
         <v>0</v>
@@ -5348,13 +5348,13 @@
         <v>0</v>
       </c>
       <c r="H151" s="6">
-        <v>800</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="152">
       <c r="A152" s="4" t="inlineStr">
         <is>
-          <t>235/50R20</t>
+          <t>235/50R19</t>
         </is>
       </c>
       <c r="B152" s="4" t="inlineStr">
@@ -5364,78 +5364,78 @@
       </c>
       <c r="C152" s="4" t="inlineStr">
         <is>
-          <t>GD235/50R20</t>
+          <t>GD235/50R19</t>
         </is>
       </c>
       <c r="D152" s="5">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E152" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F152" s="5">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G152" s="5">
         <v>0</v>
       </c>
       <c r="H152" s="6">
-        <v>1180</v>
+        <v>800</v>
       </c>
     </row>
     <row outlineLevel="0" r="153">
       <c r="A153" s="4" t="inlineStr">
         <is>
-          <t>235/55R17</t>
+          <t>235/50R20</t>
         </is>
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>BR235/55R17</t>
+          <t>GD235/50R20</t>
         </is>
       </c>
       <c r="D153" s="5">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E153" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F153" s="5">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G153" s="5">
         <v>0</v>
       </c>
       <c r="H153" s="6">
-        <v>450</v>
+        <v>1180</v>
       </c>
     </row>
     <row outlineLevel="0" r="154">
       <c r="A154" s="4" t="inlineStr">
         <is>
-          <t>235/55R18</t>
+          <t>235/55R17</t>
         </is>
       </c>
       <c r="B154" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C154" s="4" t="inlineStr">
         <is>
-          <t>HK235/55R18</t>
+          <t>BR235/55R17</t>
         </is>
       </c>
       <c r="D154" s="5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E154" s="5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F154" s="5">
         <v>0</v>
@@ -5444,30 +5444,30 @@
         <v>0</v>
       </c>
       <c r="H154" s="6">
-        <v>480</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="155">
       <c r="A155" s="4" t="inlineStr">
         <is>
-          <t>235/55R19</t>
+          <t>235/55R18</t>
         </is>
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>GD235/55R19</t>
+          <t>HK235/55R18</t>
         </is>
       </c>
       <c r="D155" s="5">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E155" s="5">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F155" s="5">
         <v>0</v>
@@ -5476,7 +5476,7 @@
         <v>0</v>
       </c>
       <c r="H155" s="6">
-        <v>750</v>
+        <v>480</v>
       </c>
     </row>
     <row outlineLevel="0" r="156">
@@ -5487,19 +5487,19 @@
       </c>
       <c r="B156" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C156" s="4" t="inlineStr">
         <is>
-          <t>HK235/55R19</t>
+          <t>GD235/55R19</t>
         </is>
       </c>
       <c r="D156" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E156" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F156" s="5">
         <v>0</v>
@@ -5508,7 +5508,7 @@
         <v>0</v>
       </c>
       <c r="H156" s="6">
-        <v>630</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="157">
@@ -5519,12 +5519,12 @@
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>LF235/55R19</t>
+          <t>HK235/55R19</t>
         </is>
       </c>
       <c r="D157" s="5">
@@ -5540,7 +5540,7 @@
         <v>0</v>
       </c>
       <c r="H157" s="6">
-        <v>500</v>
+        <v>630</v>
       </c>
     </row>
     <row outlineLevel="0" r="158">
@@ -5551,19 +5551,19 @@
       </c>
       <c r="B158" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C158" s="4" t="inlineStr">
         <is>
-          <t>NX235/55R19</t>
+          <t>LF235/55R19</t>
         </is>
       </c>
       <c r="D158" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E158" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F158" s="5">
         <v>0</v>
@@ -5572,7 +5572,7 @@
         <v>0</v>
       </c>
       <c r="H158" s="6">
-        <v>600</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="159">
@@ -5583,66 +5583,66 @@
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>RD235/55R19</t>
+          <t>NX235/55R19</t>
         </is>
       </c>
       <c r="D159" s="5">
         <v>2</v>
       </c>
       <c r="E159" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F159" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G159" s="5">
         <v>0</v>
       </c>
       <c r="H159" s="6">
-        <v>500</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="160">
       <c r="A160" s="4" t="inlineStr">
         <is>
-          <t>235/60R16</t>
+          <t>235/55R19</t>
         </is>
       </c>
       <c r="B160" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C160" s="4" t="inlineStr">
         <is>
-          <t>HK235/60R16</t>
+          <t>RD235/55R19</t>
         </is>
       </c>
       <c r="D160" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E160" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F160" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G160" s="5">
         <v>0</v>
       </c>
       <c r="H160" s="6">
-        <v>430</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="161">
       <c r="A161" s="4" t="inlineStr">
         <is>
-          <t>235/60R17</t>
+          <t>235/60R16</t>
         </is>
       </c>
       <c r="B161" s="4" t="inlineStr">
@@ -5652,55 +5652,55 @@
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>HK235/60R17</t>
+          <t>HK235/60R16</t>
         </is>
       </c>
       <c r="D161" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E161" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F161" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G161" s="5">
         <v>0</v>
       </c>
       <c r="H161" s="6">
-        <v>500</v>
+        <v>430</v>
       </c>
     </row>
     <row outlineLevel="0" r="162">
       <c r="A162" s="4" t="inlineStr">
         <is>
-          <t>235/60R18</t>
+          <t>235/60R17</t>
         </is>
       </c>
       <c r="B162" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C162" s="4" t="inlineStr">
         <is>
-          <t>GD235/60R18</t>
+          <t>HK235/60R17</t>
         </is>
       </c>
       <c r="D162" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E162" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F162" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G162" s="5">
         <v>0</v>
       </c>
       <c r="H162" s="6">
-        <v>680</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="163">
@@ -5711,12 +5711,12 @@
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>HK235/60R18</t>
+          <t>GD235/60R18</t>
         </is>
       </c>
       <c r="D163" s="5">
@@ -5732,30 +5732,30 @@
         <v>0</v>
       </c>
       <c r="H163" s="6">
-        <v>550</v>
+        <v>680</v>
       </c>
     </row>
     <row outlineLevel="0" r="164">
       <c r="A164" s="4" t="inlineStr">
         <is>
-          <t>245/40R17</t>
+          <t>235/60R18</t>
         </is>
       </c>
       <c r="B164" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C164" s="4" t="inlineStr">
         <is>
-          <t>GD245/40R17</t>
+          <t>HK235/60R18</t>
         </is>
       </c>
       <c r="D164" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E164" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F164" s="5">
         <v>0</v>
@@ -5764,13 +5764,13 @@
         <v>0</v>
       </c>
       <c r="H164" s="6">
-        <v>400</v>
+        <v>550</v>
       </c>
     </row>
     <row outlineLevel="0" r="165">
       <c r="A165" s="4" t="inlineStr">
         <is>
-          <t>245/40R18</t>
+          <t>245/40R17</t>
         </is>
       </c>
       <c r="B165" s="4" t="inlineStr">
@@ -5780,142 +5780,142 @@
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>GD245/40R18</t>
+          <t>GD245/40R17</t>
         </is>
       </c>
       <c r="D165" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E165" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F165" s="5">
         <v>0</v>
       </c>
       <c r="G165" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H165" s="6">
-        <v>620</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="166">
       <c r="A166" s="4" t="inlineStr">
         <is>
-          <t>245/40R19</t>
+          <t>245/40R18</t>
         </is>
       </c>
       <c r="B166" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C166" s="4" t="inlineStr">
         <is>
-          <t>HK245/40R19</t>
+          <t>GD245/40R18</t>
         </is>
       </c>
       <c r="D166" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E166" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F166" s="5">
         <v>0</v>
       </c>
       <c r="G166" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H166" s="6">
-        <v>750</v>
+        <v>620</v>
       </c>
     </row>
     <row outlineLevel="0" r="167">
       <c r="A167" s="4" t="inlineStr">
         <is>
-          <t>245/40R20</t>
+          <t>245/40R19</t>
         </is>
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>CT245/40R20</t>
+          <t>HK245/40R19</t>
         </is>
       </c>
       <c r="D167" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E167" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F167" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G167" s="5">
         <v>0</v>
       </c>
       <c r="H167" s="6">
-        <v>1050</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="168">
       <c r="A168" s="4" t="inlineStr">
         <is>
-          <t>245/45R17</t>
+          <t>245/40R20</t>
         </is>
       </c>
       <c r="B168" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C168" s="4" t="inlineStr">
         <is>
-          <t>HK245/45R17</t>
+          <t>CT245/40R20</t>
         </is>
       </c>
       <c r="D168" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E168" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F168" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G168" s="5">
         <v>0</v>
       </c>
       <c r="H168" s="6">
-        <v>430</v>
+        <v>1050</v>
       </c>
     </row>
     <row outlineLevel="0" r="169">
       <c r="A169" s="4" t="inlineStr">
         <is>
-          <t>245/45R18</t>
+          <t>245/45R17</t>
         </is>
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>CT245/45R18</t>
+          <t>HK245/45R17</t>
         </is>
       </c>
       <c r="D169" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E169" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F169" s="5">
         <v>0</v>
@@ -5924,7 +5924,7 @@
         <v>0</v>
       </c>
       <c r="H169" s="6">
-        <v>650</v>
+        <v>430</v>
       </c>
     </row>
     <row outlineLevel="0" r="170">
@@ -5935,19 +5935,19 @@
       </c>
       <c r="B170" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C170" s="4" t="inlineStr">
         <is>
-          <t>GD245/45R18</t>
+          <t>CT245/45R18</t>
         </is>
       </c>
       <c r="D170" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E170" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F170" s="5">
         <v>0</v>
@@ -5956,7 +5956,7 @@
         <v>0</v>
       </c>
       <c r="H170" s="6">
-        <v>600</v>
+        <v>650</v>
       </c>
     </row>
     <row outlineLevel="0" r="171">
@@ -5967,19 +5967,19 @@
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t>HK245/45R18</t>
+          <t>GD245/45R18</t>
         </is>
       </c>
       <c r="D171" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E171" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F171" s="5">
         <v>0</v>
@@ -5988,30 +5988,30 @@
         <v>0</v>
       </c>
       <c r="H171" s="6">
-        <v>500</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="172">
       <c r="A172" s="4" t="inlineStr">
         <is>
-          <t>245/45R18RF</t>
+          <t>245/45R18</t>
         </is>
       </c>
       <c r="B172" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C172" s="4" t="inlineStr">
         <is>
-          <t>GD245/45R18RF</t>
+          <t>HK245/45R18</t>
         </is>
       </c>
       <c r="D172" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E172" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F172" s="5">
         <v>0</v>
@@ -6020,23 +6020,23 @@
         <v>0</v>
       </c>
       <c r="H172" s="6">
-        <v>720</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="173">
       <c r="A173" s="4" t="inlineStr">
         <is>
-          <t>245/45R19</t>
+          <t>245/45R18RF</t>
         </is>
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>BR245/45R19</t>
+          <t>GD245/45R18RF</t>
         </is>
       </c>
       <c r="D173" s="5">
@@ -6052,7 +6052,7 @@
         <v>0</v>
       </c>
       <c r="H173" s="6">
-        <v>790</v>
+        <v>720</v>
       </c>
     </row>
     <row outlineLevel="0" r="174">
@@ -6063,44 +6063,44 @@
       </c>
       <c r="B174" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C174" s="4" t="inlineStr">
         <is>
-          <t>RD245/45R19</t>
+          <t>BR245/45R19</t>
         </is>
       </c>
       <c r="D174" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E174" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F174" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G174" s="5">
         <v>0</v>
       </c>
       <c r="H174" s="6">
-        <v>450</v>
+        <v>790</v>
       </c>
     </row>
     <row outlineLevel="0" r="175">
       <c r="A175" s="4" t="inlineStr">
         <is>
-          <t>245/45R20</t>
+          <t>245/45R19</t>
         </is>
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>HK245/45R20</t>
+          <t>RD245/45R19</t>
         </is>
       </c>
       <c r="D175" s="5">
@@ -6116,59 +6116,59 @@
         <v>0</v>
       </c>
       <c r="H175" s="6">
-        <v>750</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="176">
       <c r="A176" s="4" t="inlineStr">
         <is>
-          <t>245/65R17</t>
+          <t>245/45R20</t>
         </is>
       </c>
       <c r="B176" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C176" s="4" t="inlineStr">
         <is>
-          <t>NX245/65R17</t>
+          <t>HK245/45R20</t>
         </is>
       </c>
       <c r="D176" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E176" s="5">
         <v>0</v>
       </c>
       <c r="F176" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G176" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H176" s="6">
-        <v>600</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="177">
       <c r="A177" s="4" t="inlineStr">
         <is>
-          <t>245/70R16</t>
+          <t>245/65R17</t>
         </is>
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>LASSA</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>LS245/70R16</t>
+          <t>NX245/65R17</t>
         </is>
       </c>
       <c r="D177" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E177" s="5">
         <v>0</v>
@@ -6177,65 +6177,65 @@
         <v>0</v>
       </c>
       <c r="G177" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H177" s="6">
-        <v>500</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="178">
       <c r="A178" s="4" t="inlineStr">
         <is>
-          <t>255/35R19</t>
+          <t>245/70R16</t>
         </is>
       </c>
       <c r="B178" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>LASSA</t>
         </is>
       </c>
       <c r="C178" s="4" t="inlineStr">
         <is>
-          <t>DL255/35R19</t>
+          <t>LS245/70R16</t>
         </is>
       </c>
       <c r="D178" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E178" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F178" s="5">
         <v>0</v>
       </c>
       <c r="G178" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H178" s="6">
-        <v>700</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="179">
       <c r="A179" s="4" t="inlineStr">
         <is>
-          <t>255/35R19RF</t>
+          <t>255/35R19</t>
         </is>
       </c>
       <c r="B179" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C179" s="4" t="inlineStr">
         <is>
-          <t>CT255/35R19RF</t>
+          <t>DL255/35R19</t>
         </is>
       </c>
       <c r="D179" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E179" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F179" s="5">
         <v>0</v>
@@ -6244,7 +6244,7 @@
         <v>0</v>
       </c>
       <c r="H179" s="6">
-        <v>950</v>
+        <v>700</v>
       </c>
     </row>
     <row outlineLevel="0" r="180">
@@ -6255,19 +6255,19 @@
       </c>
       <c r="B180" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C180" s="4" t="inlineStr">
         <is>
-          <t>GD255/35R19RF</t>
+          <t>CT255/35R19RF</t>
         </is>
       </c>
       <c r="D180" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E180" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F180" s="5">
         <v>0</v>
@@ -6282,39 +6282,39 @@
     <row outlineLevel="0" r="181">
       <c r="A181" s="4" t="inlineStr">
         <is>
-          <t>255/50R19</t>
+          <t>255/35R19RF</t>
         </is>
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C181" s="4" t="inlineStr">
         <is>
-          <t>CT255/50R19</t>
+          <t>GD255/35R19RF</t>
         </is>
       </c>
       <c r="D181" s="5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E181" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F181" s="5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G181" s="5">
         <v>0</v>
       </c>
       <c r="H181" s="6">
-        <v>750</v>
+        <v>950</v>
       </c>
     </row>
     <row outlineLevel="0" r="182">
       <c r="A182" s="4" t="inlineStr">
         <is>
-          <t>255/50R20</t>
+          <t>255/50R19</t>
         </is>
       </c>
       <c r="B182" s="4" t="inlineStr">
@@ -6324,29 +6324,29 @@
       </c>
       <c r="C182" s="4" t="inlineStr">
         <is>
-          <t>CT255/50R20</t>
+          <t>CT255/50R19</t>
         </is>
       </c>
       <c r="D182" s="5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E182" s="5">
         <v>0</v>
       </c>
       <c r="F182" s="5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G182" s="5">
         <v>0</v>
       </c>
       <c r="H182" s="6">
-        <v>900</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="183">
       <c r="A183" s="4" t="inlineStr">
         <is>
-          <t>255/55R19</t>
+          <t>255/50R20</t>
         </is>
       </c>
       <c r="B183" s="4" t="inlineStr">
@@ -6356,23 +6356,23 @@
       </c>
       <c r="C183" s="4" t="inlineStr">
         <is>
-          <t>CT255/55R19</t>
+          <t>CT255/50R20</t>
         </is>
       </c>
       <c r="D183" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E183" s="5">
         <v>0</v>
       </c>
       <c r="F183" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G183" s="5">
         <v>0</v>
       </c>
       <c r="H183" s="6">
-        <v>750</v>
+        <v>900</v>
       </c>
     </row>
     <row outlineLevel="0" r="184">
@@ -6383,98 +6383,98 @@
       </c>
       <c r="B184" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C184" s="4" t="inlineStr">
         <is>
-          <t>DL255/55R19</t>
+          <t>CT255/55R19</t>
         </is>
       </c>
       <c r="D184" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E184" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F184" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G184" s="5">
         <v>0</v>
       </c>
       <c r="H184" s="6">
-        <v>700</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="185">
       <c r="A185" s="4" t="inlineStr">
         <is>
-          <t>255/70R16</t>
+          <t>255/55R19</t>
         </is>
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C185" s="4" t="inlineStr">
         <is>
-          <t>RD255/70R16</t>
+          <t>DL255/55R19</t>
         </is>
       </c>
       <c r="D185" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E185" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F185" s="5">
         <v>0</v>
       </c>
       <c r="G185" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H185" s="6">
-        <v>500</v>
+        <v>700</v>
       </c>
     </row>
     <row outlineLevel="0" r="186">
       <c r="A186" s="4" t="inlineStr">
         <is>
-          <t>265/35R18</t>
+          <t>255/70R16</t>
         </is>
       </c>
       <c r="B186" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C186" s="4" t="inlineStr">
         <is>
-          <t>GD265/35R18</t>
+          <t>RD255/70R16</t>
         </is>
       </c>
       <c r="D186" s="5">
         <v>1</v>
       </c>
       <c r="E186" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F186" s="5">
         <v>0</v>
       </c>
       <c r="G186" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H186" s="6">
-        <v>700</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="187">
       <c r="A187" s="4" t="inlineStr">
         <is>
-          <t>265/50R20</t>
+          <t>265/35R18</t>
         </is>
       </c>
       <c r="B187" s="4" t="inlineStr">
@@ -6484,29 +6484,29 @@
       </c>
       <c r="C187" s="4" t="inlineStr">
         <is>
-          <t>GD265/50R20</t>
+          <t>GD265/35R18</t>
         </is>
       </c>
       <c r="D187" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E187" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F187" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G187" s="5">
         <v>0</v>
       </c>
       <c r="H187" s="6">
-        <v>1150</v>
+        <v>700</v>
       </c>
     </row>
     <row outlineLevel="0" r="188">
       <c r="A188" s="4" t="inlineStr">
         <is>
-          <t>275/35R19RF</t>
+          <t>265/50R20</t>
         </is>
       </c>
       <c r="B188" s="4" t="inlineStr">
@@ -6516,71 +6516,71 @@
       </c>
       <c r="C188" s="4" t="inlineStr">
         <is>
-          <t>GD275/35R19RF</t>
+          <t>GD265/50R20</t>
         </is>
       </c>
       <c r="D188" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E188" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F188" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G188" s="5">
         <v>0</v>
       </c>
       <c r="H188" s="6">
-        <v>1</v>
+        <v>1150</v>
       </c>
     </row>
     <row outlineLevel="0" r="189">
       <c r="A189" s="4" t="inlineStr">
         <is>
-          <t>275/35R20</t>
+          <t>275/35R19RF</t>
         </is>
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C189" s="4" t="inlineStr">
         <is>
-          <t>CT275/35R20</t>
+          <t>GD275/35R19RF</t>
         </is>
       </c>
       <c r="D189" s="5">
         <v>2</v>
       </c>
       <c r="E189" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F189" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G189" s="5">
         <v>0</v>
       </c>
       <c r="H189" s="6">
-        <v>980</v>
+        <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="190">
       <c r="A190" s="4" t="inlineStr">
         <is>
-          <t>275/40R20</t>
+          <t>275/35R20</t>
         </is>
       </c>
       <c r="B190" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C190" s="4" t="inlineStr">
         <is>
-          <t>HK275/40R20</t>
+          <t>CT275/35R20</t>
         </is>
       </c>
       <c r="D190" s="5">
@@ -6596,23 +6596,23 @@
         <v>0</v>
       </c>
       <c r="H190" s="6">
-        <v>770</v>
+        <v>980</v>
       </c>
     </row>
     <row outlineLevel="0" r="191">
       <c r="A191" s="4" t="inlineStr">
         <is>
-          <t>275/50R21</t>
+          <t>275/40R20</t>
         </is>
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C191" s="4" t="inlineStr">
         <is>
-          <t>GD275/50R21</t>
+          <t>HK275/40R20</t>
         </is>
       </c>
       <c r="D191" s="5">
@@ -6628,23 +6628,23 @@
         <v>0</v>
       </c>
       <c r="H191" s="6">
-        <v>1</v>
+        <v>770</v>
       </c>
     </row>
     <row outlineLevel="0" r="192">
       <c r="A192" s="4" t="inlineStr">
         <is>
-          <t>295/35R21</t>
+          <t>275/50R21</t>
         </is>
       </c>
       <c r="B192" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C192" s="4" t="inlineStr">
         <is>
-          <t>CT295/35R21</t>
+          <t>GD275/50R21</t>
         </is>
       </c>
       <c r="D192" s="5">
@@ -6660,7 +6660,7 @@
         <v>0</v>
       </c>
       <c r="H192" s="6">
-        <v>1150</v>
+        <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="193">
@@ -6671,59 +6671,91 @@
       </c>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C193" s="4" t="inlineStr">
         <is>
-          <t>GD295/35R21</t>
+          <t>CT295/35R21</t>
         </is>
       </c>
       <c r="D193" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E193" s="5">
         <v>0</v>
       </c>
       <c r="F193" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G193" s="5">
         <v>0</v>
       </c>
       <c r="H193" s="6">
-        <v>980</v>
+        <v>1150</v>
       </c>
     </row>
     <row outlineLevel="0" r="194">
       <c r="A194" s="4" t="inlineStr">
         <is>
-          <t>500R12</t>
+          <t>295/35R21</t>
         </is>
       </c>
       <c r="B194" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C194" s="4" t="inlineStr">
         <is>
-          <t>RD500R12</t>
+          <t>GD295/35R21</t>
         </is>
       </c>
       <c r="D194" s="5">
         <v>3</v>
       </c>
       <c r="E194" s="5">
+        <v>0</v>
+      </c>
+      <c r="F194" s="5">
         <v>3</v>
       </c>
-      <c r="F194" s="5">
-        <v>0</v>
-      </c>
       <c r="G194" s="5">
         <v>0</v>
       </c>
       <c r="H194" s="6">
+        <v>980</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="195">
+      <c r="A195" s="4" t="inlineStr">
+        <is>
+          <t>500R12</t>
+        </is>
+      </c>
+      <c r="B195" s="4" t="inlineStr">
+        <is>
+          <t>RADIAL</t>
+        </is>
+      </c>
+      <c r="C195" s="4" t="inlineStr">
+        <is>
+          <t>RD500R12</t>
+        </is>
+      </c>
+      <c r="D195" s="5">
+        <v>3</v>
+      </c>
+      <c r="E195" s="5">
+        <v>3</v>
+      </c>
+      <c r="F195" s="5">
+        <v>0</v>
+      </c>
+      <c r="G195" s="5">
+        <v>0</v>
+      </c>
+      <c r="H195" s="6">
         <v>300</v>
       </c>
     </row>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -496,7 +496,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H195"/>
+  <dimension ref="A1:H194"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col customWidth="true" min="1" max="1" width="13.8359375"/>
@@ -568,10 +568,10 @@
         </is>
       </c>
       <c r="D2" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E2" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F2" s="5">
         <v>0</v>
@@ -888,10 +888,10 @@
         </is>
       </c>
       <c r="D12" s="5">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E12" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F12" s="5">
         <v>17</v>
@@ -1743,28 +1743,28 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>SEMPERIT</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>RD185/65R15</t>
+          <t>SP185/65R15</t>
         </is>
       </c>
       <c r="D39" s="5">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="E39" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F39" s="5">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G39" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H39" s="6">
-        <v>200</v>
+        <v>250</v>
       </c>
     </row>
     <row outlineLevel="0" r="40">
@@ -1775,60 +1775,60 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>SEMPERIT</t>
+          <t>WESTLAKE</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>SP185/65R15</t>
+          <t>WL185/65R15</t>
         </is>
       </c>
       <c r="D40" s="5">
-        <v>30</v>
+        <v>82</v>
       </c>
       <c r="E40" s="5">
-        <v>5</v>
+        <v>76</v>
       </c>
       <c r="F40" s="5">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="G40" s="5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H40" s="6">
-        <v>250</v>
+        <v>220</v>
       </c>
     </row>
     <row outlineLevel="0" r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>185/65R15</t>
+          <t>185/70R14</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>WESTLAKE</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>WL185/65R15</t>
+          <t>RD185/70R14</t>
         </is>
       </c>
       <c r="D41" s="5">
-        <v>87</v>
+        <v>2</v>
       </c>
       <c r="E41" s="5">
-        <v>81</v>
+        <v>1</v>
       </c>
       <c r="F41" s="5">
         <v>0</v>
       </c>
       <c r="G41" s="5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H41" s="6">
-        <v>220</v>
+        <v>230</v>
       </c>
     </row>
     <row outlineLevel="0" r="42">
@@ -1839,60 +1839,60 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>WESTLAKE</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>RD185/70R14</t>
+          <t>WL185/70R14</t>
         </is>
       </c>
       <c r="D42" s="5">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E42" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F42" s="5">
         <v>0</v>
       </c>
       <c r="G42" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H42" s="6">
-        <v>230</v>
+        <v>220</v>
       </c>
     </row>
     <row outlineLevel="0" r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>185/70R14</t>
+          <t>195/50R15</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>WESTLAKE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>WL185/70R14</t>
+          <t>GD195/50R15</t>
         </is>
       </c>
       <c r="D43" s="5">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E43" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F43" s="5">
         <v>0</v>
       </c>
       <c r="G43" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H43" s="6">
-        <v>220</v>
+        <v>290</v>
       </c>
     </row>
     <row outlineLevel="0" r="44">
@@ -1903,28 +1903,28 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>SEMPERIT</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>GD195/50R15</t>
+          <t>SP195/50R15</t>
         </is>
       </c>
       <c r="D44" s="5">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="E44" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F44" s="5">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G44" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H44" s="6">
-        <v>290</v>
+        <v>260</v>
       </c>
     </row>
     <row outlineLevel="0" r="45">
@@ -1935,66 +1935,66 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>SEMPERIT</t>
+          <t>WESTLAKE</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>SP195/50R15</t>
+          <t>WL195/50R15</t>
         </is>
       </c>
       <c r="D45" s="5">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E45" s="5">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F45" s="5">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G45" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H45" s="6">
-        <v>260</v>
+        <v>225</v>
       </c>
     </row>
     <row outlineLevel="0" r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>195/50R15</t>
+          <t>195/50R16</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>WESTLAKE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>WL195/50R15</t>
+          <t>GD195/50R16</t>
         </is>
       </c>
       <c r="D46" s="5">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E46" s="5">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F46" s="5">
         <v>0</v>
       </c>
       <c r="G46" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H46" s="6">
-        <v>225</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>195/50R16</t>
+          <t>195/55R16</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
@@ -2004,23 +2004,23 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>GD195/50R16</t>
+          <t>GD195/55R16</t>
         </is>
       </c>
       <c r="D47" s="5">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="E47" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F47" s="5">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G47" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H47" s="6">
-        <v>330</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="48">
@@ -2031,28 +2031,28 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>GD195/55R16</t>
+          <t>HK195/55R16</t>
         </is>
       </c>
       <c r="D48" s="5">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E48" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F48" s="5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G48" s="5">
         <v>2</v>
       </c>
       <c r="H48" s="6">
-        <v>350</v>
+        <v>290</v>
       </c>
     </row>
     <row outlineLevel="0" r="49">
@@ -2063,28 +2063,28 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>LASSA</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>HK195/55R16</t>
+          <t>LS195/55R16</t>
         </is>
       </c>
       <c r="D49" s="5">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="E49" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F49" s="5">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G49" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H49" s="6">
-        <v>290</v>
+        <v>280</v>
       </c>
     </row>
     <row outlineLevel="0" r="50">
@@ -2095,19 +2095,19 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>LASSA</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>LS195/55R16</t>
+          <t>NX195/55R16</t>
         </is>
       </c>
       <c r="D50" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E50" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F50" s="5">
         <v>0</v>
@@ -2116,7 +2116,7 @@
         <v>0</v>
       </c>
       <c r="H50" s="6">
-        <v>280</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="51">
@@ -2127,92 +2127,92 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>NX195/55R16</t>
+          <t>RD195/55R16</t>
         </is>
       </c>
       <c r="D51" s="5">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E51" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F51" s="5">
         <v>0</v>
       </c>
       <c r="G51" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H51" s="6">
-        <v>300</v>
+        <v>250</v>
       </c>
     </row>
     <row outlineLevel="0" r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>195/55R16</t>
+          <t>195/60R16</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>RD195/55R16</t>
+          <t>GD195/60R16</t>
         </is>
       </c>
       <c r="D52" s="5">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="E52" s="5">
         <v>4</v>
       </c>
       <c r="F52" s="5">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G52" s="5">
         <v>3</v>
       </c>
       <c r="H52" s="6">
-        <v>250</v>
+        <v>355</v>
       </c>
     </row>
     <row outlineLevel="0" r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>195/60R16</t>
+          <t>195/65R15</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>DOUBLESTAR</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>GD195/60R16</t>
+          <t>DS195/65R15</t>
         </is>
       </c>
       <c r="D53" s="5">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="E53" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F53" s="5">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="G53" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H53" s="6">
-        <v>355</v>
+        <v>230</v>
       </c>
     </row>
     <row outlineLevel="0" r="54">
@@ -2223,22 +2223,22 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>DOUBLESTAR</t>
+          <t>GOODRIDE</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>DS195/65R15</t>
+          <t>GR195/65R15</t>
         </is>
       </c>
       <c r="D54" s="5">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E54" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F54" s="5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G54" s="5">
         <v>0</v>
@@ -2255,28 +2255,28 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>GOODRIDE</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>GR195/65R15</t>
+          <t>HK195/65R15</t>
         </is>
       </c>
       <c r="D55" s="5">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E55" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F55" s="5">
         <v>0</v>
       </c>
       <c r="G55" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H55" s="6">
-        <v>230</v>
+        <v>260</v>
       </c>
     </row>
     <row outlineLevel="0" r="56">
@@ -2287,28 +2287,28 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>LASSA</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>HK195/65R15</t>
+          <t>LS195/65R15</t>
         </is>
       </c>
       <c r="D56" s="5">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E56" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F56" s="5">
         <v>0</v>
       </c>
       <c r="G56" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H56" s="6">
-        <v>260</v>
+        <v>250</v>
       </c>
     </row>
     <row outlineLevel="0" r="57">
@@ -2319,19 +2319,19 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>LASSA</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>LS195/65R15</t>
+          <t>NX195/65R15</t>
         </is>
       </c>
       <c r="D57" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E57" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F57" s="5">
         <v>0</v>
@@ -2340,7 +2340,7 @@
         <v>0</v>
       </c>
       <c r="H57" s="6">
-        <v>250</v>
+        <v>230</v>
       </c>
     </row>
     <row outlineLevel="0" r="58">
@@ -2351,25 +2351,25 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>NX195/65R15</t>
+          <t>RD195/65R15</t>
         </is>
       </c>
       <c r="D58" s="5">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E58" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F58" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G58" s="5">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H58" s="6">
         <v>230</v>
@@ -2383,92 +2383,92 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>SEMPERIT</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>RD195/65R15</t>
+          <t>SP195/65R15</t>
         </is>
       </c>
       <c r="D59" s="5">
-        <v>15</v>
+        <v>89</v>
       </c>
       <c r="E59" s="5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F59" s="5">
-        <v>1</v>
+        <v>69</v>
       </c>
       <c r="G59" s="5">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="H59" s="6">
-        <v>230</v>
+        <v>250</v>
       </c>
     </row>
     <row outlineLevel="0" r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>195/65R15</t>
+          <t>195/75R16C</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>SEMPERIT</t>
+          <t>GOODRIDE</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>SP195/65R15</t>
+          <t>GR195/75R16C</t>
         </is>
       </c>
       <c r="D60" s="5">
-        <v>89</v>
+        <v>12</v>
       </c>
       <c r="E60" s="5">
+        <v>3</v>
+      </c>
+      <c r="F60" s="5">
         <v>7</v>
       </c>
-      <c r="F60" s="5">
-        <v>69</v>
-      </c>
       <c r="G60" s="5">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="H60" s="6">
-        <v>250</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>195/75R16C</t>
+          <t>205/45R17</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>GOODRIDE</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>GR195/75R16C</t>
+          <t>CT205/45R17</t>
         </is>
       </c>
       <c r="D61" s="5">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E61" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F61" s="5">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G61" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H61" s="6">
-        <v>350</v>
+        <v>550</v>
       </c>
     </row>
     <row outlineLevel="0" r="62">
@@ -2479,28 +2479,28 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>FULDA</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>CT205/45R17</t>
+          <t>FL205/45R17</t>
         </is>
       </c>
       <c r="D62" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E62" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F62" s="5">
         <v>0</v>
       </c>
       <c r="G62" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H62" s="6">
-        <v>550</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="63">
@@ -2511,28 +2511,28 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>FULDA</t>
+          <t>GOODRIDE</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>FL205/45R17</t>
+          <t>GR205/45R17</t>
         </is>
       </c>
       <c r="D63" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E63" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F63" s="5">
         <v>0</v>
       </c>
       <c r="G63" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H63" s="6">
-        <v>380</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="64">
@@ -2543,28 +2543,28 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>GOODRIDE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>GR205/45R17</t>
+          <t>GD205/45R17</t>
         </is>
       </c>
       <c r="D64" s="5">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="E64" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F64" s="5">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G64" s="5">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H64" s="6">
-        <v>300</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="65">
@@ -2575,28 +2575,28 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>GD205/45R17</t>
+          <t>NX205/45R17</t>
         </is>
       </c>
       <c r="D65" s="5">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="E65" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F65" s="5">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G65" s="5">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H65" s="6">
-        <v>450</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="66">
@@ -2607,83 +2607,83 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>NX205/45R17</t>
+          <t>RD205/45R17</t>
         </is>
       </c>
       <c r="D66" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E66" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F66" s="5">
         <v>0</v>
       </c>
       <c r="G66" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H66" s="6">
-        <v>380</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>205/45R17</t>
+          <t>205/50R17</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>RD205/45R17</t>
+          <t>CT205/50R17</t>
         </is>
       </c>
       <c r="D67" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E67" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F67" s="5">
         <v>0</v>
       </c>
       <c r="G67" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H67" s="6">
-        <v>300</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>205/50R17</t>
+          <t>205/55R16</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>AMINE</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>CT205/50R17</t>
+          <t>AM205/55R16</t>
         </is>
       </c>
       <c r="D68" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E68" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F68" s="5">
         <v>0</v>
@@ -2692,7 +2692,7 @@
         <v>0</v>
       </c>
       <c r="H68" s="6">
-        <v>450</v>
+        <v>240</v>
       </c>
     </row>
     <row outlineLevel="0" r="69">
@@ -2703,28 +2703,28 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>AMINE</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>AM205/55R16</t>
+          <t>BR205/55R16</t>
         </is>
       </c>
       <c r="D69" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E69" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F69" s="5">
         <v>0</v>
       </c>
       <c r="G69" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H69" s="6">
-        <v>240</v>
+        <v>290</v>
       </c>
     </row>
     <row outlineLevel="0" r="70">
@@ -2735,28 +2735,28 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>DOUBLESTAR</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>BR205/55R16</t>
+          <t>DS205/55R16</t>
         </is>
       </c>
       <c r="D70" s="5">
         <v>4</v>
       </c>
       <c r="E70" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F70" s="5">
         <v>0</v>
       </c>
       <c r="G70" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H70" s="6">
-        <v>290</v>
+        <v>230</v>
       </c>
     </row>
     <row outlineLevel="0" r="71">
@@ -2767,28 +2767,28 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>DOUBLESTAR</t>
+          <t>FULDA</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>DS205/55R16</t>
+          <t>FL205/55R16</t>
         </is>
       </c>
       <c r="D71" s="5">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="E71" s="5">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F71" s="5">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G71" s="5">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H71" s="6">
-        <v>230</v>
+        <v>250</v>
       </c>
     </row>
     <row outlineLevel="0" r="72">
@@ -2799,25 +2799,25 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>FULDA</t>
+          <t>GOODRIDE</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>FL205/55R16</t>
+          <t>GR205/55R16</t>
         </is>
       </c>
       <c r="D72" s="5">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="E72" s="5">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F72" s="5">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="G72" s="5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H72" s="6">
         <v>250</v>
@@ -2831,28 +2831,28 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>GOODRIDE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>GR205/55R16</t>
+          <t>GD205/55R16</t>
         </is>
       </c>
       <c r="D73" s="5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E73" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F73" s="5">
         <v>0</v>
       </c>
       <c r="G73" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H73" s="6">
-        <v>250</v>
+        <v>280</v>
       </c>
     </row>
     <row outlineLevel="0" r="74">
@@ -2863,28 +2863,28 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>GD205/55R16</t>
+          <t>HK205/55R16</t>
         </is>
       </c>
       <c r="D74" s="5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E74" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F74" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G74" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H74" s="6">
-        <v>280</v>
+        <v>260</v>
       </c>
     </row>
     <row outlineLevel="0" r="75">
@@ -2895,48 +2895,48 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>HK205/55R16</t>
+          <t>RD205/55R16</t>
         </is>
       </c>
       <c r="D75" s="5">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E75" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F75" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G75" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H75" s="6">
-        <v>260</v>
+        <v>230</v>
       </c>
     </row>
     <row outlineLevel="0" r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>205/55R16</t>
+          <t>205/55R16RF</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>RD205/55R16</t>
+          <t>GD205/55R16RF</t>
         </is>
       </c>
       <c r="D76" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E76" s="5">
         <v>0</v>
@@ -2945,16 +2945,16 @@
         <v>0</v>
       </c>
       <c r="G76" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H76" s="6">
-        <v>230</v>
+        <v>480</v>
       </c>
     </row>
     <row outlineLevel="0" r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>205/55R16RF</t>
+          <t>205/55R17</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
@@ -2964,23 +2964,23 @@
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>GD205/55R16RF</t>
+          <t>GD205/55R17</t>
         </is>
       </c>
       <c r="D77" s="5">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="E77" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F77" s="5">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G77" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H77" s="6">
-        <v>480</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="78">
@@ -2991,44 +2991,44 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>GD205/55R17</t>
+          <t>NX205/55R17</t>
         </is>
       </c>
       <c r="D78" s="5">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="E78" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F78" s="5">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G78" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H78" s="6">
-        <v>450</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>205/55R17</t>
+          <t>205/60R16</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>NX205/55R17</t>
+          <t>DL205/60R16</t>
         </is>
       </c>
       <c r="D79" s="5">
@@ -3044,7 +3044,7 @@
         <v>0</v>
       </c>
       <c r="H79" s="6">
-        <v>400</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="80">
@@ -3055,28 +3055,28 @@
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>DL205/60R16</t>
+          <t>GD205/60R16</t>
         </is>
       </c>
       <c r="D80" s="5">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="E80" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F80" s="5">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G80" s="5">
         <v>0</v>
       </c>
       <c r="H80" s="6">
-        <v>330</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="81">
@@ -3087,28 +3087,28 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>GD205/60R16</t>
+          <t>HK205/60R16</t>
         </is>
       </c>
       <c r="D81" s="5">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E81" s="5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F81" s="5">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="G81" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H81" s="6">
-        <v>380</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="82">
@@ -3119,25 +3119,25 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>HK205/60R16</t>
+          <t>LF205/60R16</t>
         </is>
       </c>
       <c r="D82" s="5">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E82" s="5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F82" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G82" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H82" s="6">
         <v>300</v>
@@ -3146,17 +3146,17 @@
     <row outlineLevel="0" r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>205/60R16</t>
+          <t>205/65R15</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>LF205/60R16</t>
+          <t>HK205/65R15</t>
         </is>
       </c>
       <c r="D83" s="5">
@@ -3172,30 +3172,30 @@
         <v>0</v>
       </c>
       <c r="H83" s="6">
-        <v>300</v>
+        <v>270</v>
       </c>
     </row>
     <row outlineLevel="0" r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>205/65R15</t>
+          <t>205/65R16</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>HK205/65R15</t>
+          <t>BR205/65R16</t>
         </is>
       </c>
       <c r="D84" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E84" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F84" s="5">
         <v>0</v>
@@ -3204,7 +3204,7 @@
         <v>0</v>
       </c>
       <c r="H84" s="6">
-        <v>270</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="85">
@@ -3215,19 +3215,19 @@
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>BR205/65R16</t>
+          <t>HK205/65R16</t>
         </is>
       </c>
       <c r="D85" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E85" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F85" s="5">
         <v>0</v>
@@ -3236,39 +3236,39 @@
         <v>0</v>
       </c>
       <c r="H85" s="6">
-        <v>420</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>205/65R16</t>
+          <t>215/40R18</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>HK205/65R16</t>
+          <t>GD215/40R18</t>
         </is>
       </c>
       <c r="D86" s="5">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E86" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F86" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G86" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H86" s="6">
-        <v>380</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="87">
@@ -3279,44 +3279,44 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>GD215/40R18</t>
+          <t>HK215/40R18</t>
         </is>
       </c>
       <c r="D87" s="5">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E87" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F87" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G87" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H87" s="6">
-        <v>600</v>
+        <v>490</v>
       </c>
     </row>
     <row outlineLevel="0" r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>215/40R18</t>
+          <t>215/45R16</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>HK215/40R18</t>
+          <t>GD215/45R16</t>
         </is>
       </c>
       <c r="D88" s="5">
@@ -3332,13 +3332,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="6">
-        <v>490</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>215/45R16</t>
+          <t>215/45R17</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
@@ -3348,14 +3348,14 @@
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>GD215/45R16</t>
+          <t>GD215/45R17</t>
         </is>
       </c>
       <c r="D89" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E89" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F89" s="5">
         <v>0</v>
@@ -3364,7 +3364,7 @@
         <v>0</v>
       </c>
       <c r="H89" s="6">
-        <v>450</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="90">
@@ -3375,25 +3375,25 @@
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>GD215/45R17</t>
+          <t>HK215/45R17</t>
         </is>
       </c>
       <c r="D90" s="5">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E90" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F90" s="5">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G90" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H90" s="6">
         <v>400</v>
@@ -3407,28 +3407,28 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>IRIS</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>HK215/45R17</t>
+          <t>IR215/45R17</t>
         </is>
       </c>
       <c r="D91" s="5">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="E91" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F91" s="5">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G91" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H91" s="6">
-        <v>400</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="92">
@@ -3439,28 +3439,28 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>IRIS</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>IR215/45R17</t>
+          <t>LF215/45R17</t>
         </is>
       </c>
       <c r="D92" s="5">
         <v>1</v>
       </c>
       <c r="E92" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F92" s="5">
         <v>0</v>
       </c>
       <c r="G92" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H92" s="6">
-        <v>300</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="93">
@@ -3471,83 +3471,83 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>LF215/45R17</t>
+          <t>NX215/45R17</t>
         </is>
       </c>
       <c r="D93" s="5">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E93" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F93" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G93" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H93" s="6">
-        <v>350</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>215/45R17</t>
+          <t>215/45R18</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>NX215/45R17</t>
+          <t>GD215/45R18</t>
         </is>
       </c>
       <c r="D94" s="5">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E94" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F94" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G94" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H94" s="6">
-        <v>380</v>
+        <v>550</v>
       </c>
     </row>
     <row outlineLevel="0" r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>215/45R18</t>
+          <t>215/50R17</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>GD215/45R18</t>
+          <t>BR215/50R17</t>
         </is>
       </c>
       <c r="D95" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E95" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F95" s="5">
         <v>0</v>
@@ -3556,7 +3556,7 @@
         <v>0</v>
       </c>
       <c r="H95" s="6">
-        <v>550</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="96">
@@ -3567,28 +3567,28 @@
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>BR215/50R17</t>
+          <t>GD215/50R17</t>
         </is>
       </c>
       <c r="D96" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E96" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F96" s="5">
         <v>0</v>
       </c>
       <c r="G96" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H96" s="6">
-        <v>450</v>
+        <v>470</v>
       </c>
     </row>
     <row outlineLevel="0" r="97">
@@ -3599,28 +3599,28 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>GD215/50R17</t>
+          <t>HK215/50R17</t>
         </is>
       </c>
       <c r="D97" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E97" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F97" s="5">
         <v>0</v>
       </c>
       <c r="G97" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H97" s="6">
-        <v>470</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="98">
@@ -3631,19 +3631,19 @@
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>HK215/50R17</t>
+          <t>LF215/50R17</t>
         </is>
       </c>
       <c r="D98" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E98" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F98" s="5">
         <v>0</v>
@@ -3652,30 +3652,30 @@
         <v>0</v>
       </c>
       <c r="H98" s="6">
-        <v>400</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>215/50R17</t>
+          <t>215/50R18</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>LF215/50R17</t>
+          <t>GD215/50R18</t>
         </is>
       </c>
       <c r="D99" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E99" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F99" s="5">
         <v>0</v>
@@ -3684,13 +3684,13 @@
         <v>0</v>
       </c>
       <c r="H99" s="6">
-        <v>420</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="100">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>215/50R18</t>
+          <t>215/55R16</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
@@ -3700,14 +3700,14 @@
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>GD215/50R18</t>
+          <t>GD215/55R16</t>
         </is>
       </c>
       <c r="D100" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E100" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F100" s="5">
         <v>0</v>
@@ -3716,7 +3716,7 @@
         <v>0</v>
       </c>
       <c r="H100" s="6">
-        <v>600</v>
+        <v>440</v>
       </c>
     </row>
     <row outlineLevel="0" r="101">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>GD215/55R16</t>
+          <t>LF215/55R16</t>
         </is>
       </c>
       <c r="D101" s="5">
@@ -3748,23 +3748,23 @@
         <v>0</v>
       </c>
       <c r="H101" s="6">
-        <v>440</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="102">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>215/55R16</t>
+          <t>215/55R17</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>LF215/55R16</t>
+          <t>BR215/55R17</t>
         </is>
       </c>
       <c r="D102" s="5">
@@ -3780,7 +3780,7 @@
         <v>0</v>
       </c>
       <c r="H102" s="6">
-        <v>350</v>
+        <v>480</v>
       </c>
     </row>
     <row outlineLevel="0" r="103">
@@ -3791,19 +3791,19 @@
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>BR215/55R17</t>
+          <t>HK215/55R17</t>
         </is>
       </c>
       <c r="D103" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E103" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F103" s="5">
         <v>0</v>
@@ -3812,30 +3812,30 @@
         <v>0</v>
       </c>
       <c r="H103" s="6">
-        <v>480</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="104">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>215/55R17</t>
+          <t>215/55R18</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>HK215/55R17</t>
+          <t>GD215/55R18</t>
         </is>
       </c>
       <c r="D104" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E104" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F104" s="5">
         <v>0</v>
@@ -3844,23 +3844,23 @@
         <v>0</v>
       </c>
       <c r="H104" s="6">
-        <v>420</v>
+        <v>580</v>
       </c>
     </row>
     <row outlineLevel="0" r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>215/55R18</t>
+          <t>215/60R16</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>GD215/55R18</t>
+          <t>BR215/60R16</t>
         </is>
       </c>
       <c r="D105" s="5">
@@ -3876,7 +3876,7 @@
         <v>0</v>
       </c>
       <c r="H105" s="6">
-        <v>580</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="106">
@@ -3887,25 +3887,25 @@
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>BR215/60R16</t>
+          <t>DL215/60R16</t>
         </is>
       </c>
       <c r="D106" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E106" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F106" s="5">
         <v>0</v>
       </c>
       <c r="G106" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H106" s="6">
         <v>350</v>
@@ -3919,28 +3919,28 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>DL215/60R16</t>
+          <t>HK215/60R16</t>
         </is>
       </c>
       <c r="D107" s="5">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E107" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F107" s="5">
         <v>0</v>
       </c>
       <c r="G107" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H107" s="6">
-        <v>350</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="108">
@@ -3951,25 +3951,25 @@
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>HK215/60R16</t>
+          <t>NX215/60R16</t>
         </is>
       </c>
       <c r="D108" s="5">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E108" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F108" s="5">
         <v>0</v>
       </c>
       <c r="G108" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H108" s="6">
         <v>330</v>
@@ -3978,65 +3978,65 @@
     <row outlineLevel="0" r="109">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>215/60R16</t>
+          <t>215/60R17</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>NX215/60R16</t>
+          <t>RD215/60R17</t>
         </is>
       </c>
       <c r="D109" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E109" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F109" s="5">
         <v>0</v>
       </c>
       <c r="G109" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H109" s="6">
-        <v>330</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="110">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>215/60R17</t>
+          <t>215/65R16</t>
         </is>
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>RD215/60R17</t>
+          <t>GD215/65R16</t>
         </is>
       </c>
       <c r="D110" s="5">
         <v>1</v>
       </c>
       <c r="E110" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F110" s="5">
         <v>0</v>
       </c>
       <c r="G110" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H110" s="6">
-        <v>300</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="111">
@@ -4047,44 +4047,44 @@
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>GD215/65R16</t>
+          <t>HK215/65R16</t>
         </is>
       </c>
       <c r="D111" s="5">
         <v>1</v>
       </c>
       <c r="E111" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F111" s="5">
         <v>0</v>
       </c>
       <c r="G111" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H111" s="6">
-        <v>380</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="112">
       <c r="A112" s="4" t="inlineStr">
         <is>
-          <t>215/65R16</t>
+          <t>215/65R17</t>
         </is>
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>MICHELIN</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>HK215/65R16</t>
+          <t>MC215/65R17</t>
         </is>
       </c>
       <c r="D112" s="5">
@@ -4100,39 +4100,39 @@
         <v>0</v>
       </c>
       <c r="H112" s="6">
-        <v>330</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="113">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>215/65R17</t>
+          <t>215/70R15C</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>MICHELIN</t>
+          <t>LINGLONG</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>MC215/65R17</t>
+          <t>LG215/70R15C</t>
         </is>
       </c>
       <c r="D113" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E113" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F113" s="5">
         <v>0</v>
       </c>
       <c r="G113" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H113" s="6">
-        <v>600</v>
+        <v>370</v>
       </c>
     </row>
     <row outlineLevel="0" r="114">
@@ -4143,51 +4143,51 @@
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>LINGLONG</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>LG215/70R15C</t>
+          <t>RD215/70R15C</t>
         </is>
       </c>
       <c r="D114" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E114" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F114" s="5">
         <v>0</v>
       </c>
       <c r="G114" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H114" s="6">
-        <v>370</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="115">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t>215/70R15C</t>
+          <t>225/40R18</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>BARUM</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>RD215/70R15C</t>
+          <t>BM225/40R18</t>
         </is>
       </c>
       <c r="D115" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E115" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F115" s="5">
         <v>0</v>
@@ -4196,7 +4196,7 @@
         <v>0</v>
       </c>
       <c r="H115" s="6">
-        <v>330</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="116">
@@ -4207,28 +4207,28 @@
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>BARUM</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>BM225/40R18</t>
+          <t>GD225/40R18</t>
         </is>
       </c>
       <c r="D116" s="5">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="E116" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F116" s="5">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G116" s="5">
         <v>0</v>
       </c>
       <c r="H116" s="6">
-        <v>420</v>
+        <v>480</v>
       </c>
     </row>
     <row outlineLevel="0" r="117">
@@ -4239,28 +4239,28 @@
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>GD225/40R18</t>
+          <t>HK225/40R18</t>
         </is>
       </c>
       <c r="D117" s="5">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="E117" s="5">
         <v>4</v>
       </c>
       <c r="F117" s="5">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G117" s="5">
         <v>0</v>
       </c>
       <c r="H117" s="6">
-        <v>480</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="118">
@@ -4271,28 +4271,28 @@
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>LASSA</t>
         </is>
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>HK225/40R18</t>
+          <t>LS225/40R18</t>
         </is>
       </c>
       <c r="D118" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E118" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F118" s="5">
         <v>0</v>
       </c>
       <c r="G118" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H118" s="6">
-        <v>450</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="119">
@@ -4303,28 +4303,28 @@
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>LASSA</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>LS225/40R18</t>
+          <t>NX225/40R18</t>
         </is>
       </c>
       <c r="D119" s="5">
         <v>1</v>
       </c>
       <c r="E119" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F119" s="5">
         <v>0</v>
       </c>
       <c r="G119" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H119" s="6">
-        <v>330</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="120">
@@ -4335,19 +4335,19 @@
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>SEMPERIT</t>
         </is>
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>NX225/40R18</t>
+          <t>SP225/40R18</t>
         </is>
       </c>
       <c r="D120" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E120" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F120" s="5">
         <v>0</v>
@@ -4356,30 +4356,30 @@
         <v>0</v>
       </c>
       <c r="H120" s="6">
-        <v>400</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="121">
       <c r="A121" s="4" t="inlineStr">
         <is>
-          <t>225/40R18</t>
+          <t>225/40R18RF</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>SEMPERIT</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>SP225/40R18</t>
+          <t>GD225/40R18RF</t>
         </is>
       </c>
       <c r="D121" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E121" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F121" s="5">
         <v>0</v>
@@ -4388,30 +4388,30 @@
         <v>0</v>
       </c>
       <c r="H121" s="6">
-        <v>450</v>
+        <v>590</v>
       </c>
     </row>
     <row outlineLevel="0" r="122">
       <c r="A122" s="4" t="inlineStr">
         <is>
-          <t>225/40R18RF</t>
+          <t>225/45R17</t>
         </is>
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>GD225/40R18RF</t>
+          <t>CT225/45R17</t>
         </is>
       </c>
       <c r="D122" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E122" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F122" s="5">
         <v>0</v>
@@ -4420,7 +4420,7 @@
         <v>0</v>
       </c>
       <c r="H122" s="6">
-        <v>590</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="123">
@@ -4431,28 +4431,28 @@
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>FULDA</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>CT225/45R17</t>
+          <t>FL225/45R17</t>
         </is>
       </c>
       <c r="D123" s="5">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="E123" s="5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F123" s="5">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G123" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H123" s="6">
-        <v>400</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="124">
@@ -4463,28 +4463,28 @@
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>FULDA</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>FL225/45R17</t>
+          <t>GD225/45R17</t>
         </is>
       </c>
       <c r="D124" s="5">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E124" s="5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F124" s="5">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G124" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H124" s="6">
-        <v>350</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="125">
@@ -4495,60 +4495,60 @@
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>GD225/45R17</t>
+          <t>HK225/45R17</t>
         </is>
       </c>
       <c r="D125" s="5">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="E125" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F125" s="5">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="G125" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H125" s="6">
-        <v>380</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="126">
       <c r="A126" s="4" t="inlineStr">
         <is>
-          <t>225/45R17</t>
+          <t>225/45R18</t>
         </is>
       </c>
       <c r="B126" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C126" s="4" t="inlineStr">
         <is>
-          <t>HK225/45R17</t>
+          <t>DL225/45R18</t>
         </is>
       </c>
       <c r="D126" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E126" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F126" s="5">
         <v>0</v>
       </c>
       <c r="G126" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H126" s="6">
-        <v>350</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="127">
@@ -4559,28 +4559,28 @@
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>DL225/45R18</t>
+          <t>GD225/45R18</t>
         </is>
       </c>
       <c r="D127" s="5">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E127" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F127" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G127" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H127" s="6">
-        <v>500</v>
+        <v>550</v>
       </c>
     </row>
     <row outlineLevel="0" r="128">
@@ -4591,108 +4591,108 @@
       </c>
       <c r="B128" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C128" s="4" t="inlineStr">
         <is>
-          <t>GD225/45R18</t>
+          <t>LF225/45R18</t>
         </is>
       </c>
       <c r="D128" s="5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E128" s="5">
         <v>4</v>
       </c>
       <c r="F128" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G128" s="5">
         <v>0</v>
       </c>
       <c r="H128" s="6">
-        <v>550</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="129">
       <c r="A129" s="4" t="inlineStr">
         <is>
-          <t>225/45R18</t>
+          <t>225/45R18RF</t>
         </is>
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>LF225/45R18</t>
+          <t>GD225/45R18RF</t>
         </is>
       </c>
       <c r="D129" s="5">
         <v>4</v>
       </c>
       <c r="E129" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F129" s="5">
         <v>0</v>
       </c>
       <c r="G129" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H129" s="6">
-        <v>420</v>
+        <v>720</v>
       </c>
     </row>
     <row outlineLevel="0" r="130">
       <c r="A130" s="4" t="inlineStr">
         <is>
-          <t>225/45R18RF</t>
+          <t>225/45R19</t>
         </is>
       </c>
       <c r="B130" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C130" s="4" t="inlineStr">
         <is>
-          <t>GD225/45R18RF</t>
+          <t>CT225/45R19</t>
         </is>
       </c>
       <c r="D130" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E130" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F130" s="5">
         <v>0</v>
       </c>
       <c r="G130" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H130" s="6">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row outlineLevel="0" r="131">
       <c r="A131" s="4" t="inlineStr">
         <is>
-          <t>225/45R19</t>
+          <t>225/50R17</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>CT225/45R19</t>
+          <t>BR225/50R17</t>
         </is>
       </c>
       <c r="D131" s="5">
@@ -4708,7 +4708,7 @@
         <v>0</v>
       </c>
       <c r="H131" s="6">
-        <v>780</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="132">
@@ -4719,28 +4719,28 @@
       </c>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C132" s="4" t="inlineStr">
         <is>
-          <t>BR225/50R17</t>
+          <t>GD225/50R17</t>
         </is>
       </c>
       <c r="D132" s="5">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E132" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F132" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G132" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H132" s="6">
-        <v>600</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="133">
@@ -4751,60 +4751,60 @@
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>GD225/50R17</t>
+          <t>HK225/50R17</t>
         </is>
       </c>
       <c r="D133" s="5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E133" s="5">
         <v>4</v>
       </c>
       <c r="F133" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G133" s="5">
         <v>2</v>
       </c>
       <c r="H133" s="6">
-        <v>500</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="134">
       <c r="A134" s="4" t="inlineStr">
         <is>
-          <t>225/50R17</t>
+          <t>225/55R16</t>
         </is>
       </c>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C134" s="4" t="inlineStr">
         <is>
-          <t>HK225/50R17</t>
+          <t>DL225/55R16</t>
         </is>
       </c>
       <c r="D134" s="5">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E134" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F134" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G134" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H134" s="6">
-        <v>400</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="135">
@@ -4815,19 +4815,19 @@
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>DL225/55R16</t>
+          <t>GD225/55R16</t>
         </is>
       </c>
       <c r="D135" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E135" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F135" s="5">
         <v>0</v>
@@ -4836,30 +4836,30 @@
         <v>0</v>
       </c>
       <c r="H135" s="6">
-        <v>450</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="136">
       <c r="A136" s="4" t="inlineStr">
         <is>
-          <t>225/55R16</t>
+          <t>225/55R17</t>
         </is>
       </c>
       <c r="B136" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C136" s="4" t="inlineStr">
         <is>
-          <t>GD225/55R16</t>
+          <t>HK225/55R17</t>
         </is>
       </c>
       <c r="D136" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E136" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F136" s="5">
         <v>0</v>
@@ -4868,71 +4868,71 @@
         <v>0</v>
       </c>
       <c r="H136" s="6">
-        <v>420</v>
+        <v>430</v>
       </c>
     </row>
     <row outlineLevel="0" r="137">
       <c r="A137" s="4" t="inlineStr">
         <is>
-          <t>225/55R17</t>
+          <t>225/55R17RF</t>
         </is>
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>HK225/55R17</t>
+          <t>GD225/55R17RF</t>
         </is>
       </c>
       <c r="D137" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E137" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F137" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G137" s="5">
         <v>0</v>
       </c>
       <c r="H137" s="6">
-        <v>430</v>
+        <v>700</v>
       </c>
     </row>
     <row outlineLevel="0" r="138">
       <c r="A138" s="4" t="inlineStr">
         <is>
-          <t>225/55R17RF</t>
+          <t>225/55R18</t>
         </is>
       </c>
       <c r="B138" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C138" s="4" t="inlineStr">
         <is>
-          <t>GD225/55R17RF</t>
+          <t>HK225/55R18</t>
         </is>
       </c>
       <c r="D138" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E138" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F138" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G138" s="5">
         <v>0</v>
       </c>
       <c r="H138" s="6">
-        <v>700</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="139">
@@ -4943,19 +4943,19 @@
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>KUMHO</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>HK225/55R18</t>
+          <t>KM225/55R18</t>
         </is>
       </c>
       <c r="D139" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E139" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F139" s="5">
         <v>0</v>
@@ -4964,30 +4964,30 @@
         <v>0</v>
       </c>
       <c r="H139" s="6">
-        <v>500</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="140">
       <c r="A140" s="4" t="inlineStr">
         <is>
-          <t>225/55R18</t>
+          <t>225/55R19</t>
         </is>
       </c>
       <c r="B140" s="4" t="inlineStr">
         <is>
-          <t>KUMHO</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C140" s="4" t="inlineStr">
         <is>
-          <t>KM225/55R18</t>
+          <t>BR225/55R19</t>
         </is>
       </c>
       <c r="D140" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E140" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F140" s="5">
         <v>0</v>
@@ -4996,7 +4996,7 @@
         <v>0</v>
       </c>
       <c r="H140" s="6">
-        <v>450</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="141">
@@ -5007,19 +5007,19 @@
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>BR225/55R19</t>
+          <t>GD225/55R19</t>
         </is>
       </c>
       <c r="D141" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E141" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F141" s="5">
         <v>0</v>
@@ -5034,21 +5034,21 @@
     <row outlineLevel="0" r="142">
       <c r="A142" s="4" t="inlineStr">
         <is>
-          <t>225/55R19</t>
+          <t>225/60R17</t>
         </is>
       </c>
       <c r="B142" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C142" s="4" t="inlineStr">
         <is>
-          <t>GD225/55R19</t>
+          <t>HK225/60R17</t>
         </is>
       </c>
       <c r="D142" s="5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E142" s="5">
         <v>4</v>
@@ -5057,65 +5057,65 @@
         <v>0</v>
       </c>
       <c r="G142" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H142" s="6">
-        <v>750</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="143">
       <c r="A143" s="4" t="inlineStr">
         <is>
-          <t>225/60R17</t>
+          <t>225/60R18</t>
         </is>
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>HK225/60R17</t>
+          <t>GD225/60R18</t>
         </is>
       </c>
       <c r="D143" s="5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E143" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F143" s="5">
         <v>0</v>
       </c>
       <c r="G143" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H143" s="6">
-        <v>400</v>
+        <v>700</v>
       </c>
     </row>
     <row outlineLevel="0" r="144">
       <c r="A144" s="4" t="inlineStr">
         <is>
-          <t>225/60R18</t>
+          <t>225/65R17</t>
         </is>
       </c>
       <c r="B144" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C144" s="4" t="inlineStr">
         <is>
-          <t>GD225/60R18</t>
+          <t>RD225/65R17</t>
         </is>
       </c>
       <c r="D144" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E144" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F144" s="5">
         <v>0</v>
@@ -5124,36 +5124,36 @@
         <v>0</v>
       </c>
       <c r="H144" s="6">
-        <v>700</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="145">
       <c r="A145" s="4" t="inlineStr">
         <is>
-          <t>225/65R17</t>
+          <t>225/70R15C</t>
         </is>
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>MATADOR</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>RD225/65R17</t>
+          <t>MT225/70R15C</t>
         </is>
       </c>
       <c r="D145" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E145" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F145" s="5">
         <v>0</v>
       </c>
       <c r="G145" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H145" s="6">
         <v>450</v>
@@ -5162,21 +5162,21 @@
     <row outlineLevel="0" r="146">
       <c r="A146" s="4" t="inlineStr">
         <is>
-          <t>225/70R15C</t>
+          <t>225/75R15C</t>
         </is>
       </c>
       <c r="B146" s="4" t="inlineStr">
         <is>
-          <t>MATADOR</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C146" s="4" t="inlineStr">
         <is>
-          <t>MT225/70R15C</t>
+          <t>RD225/75R15C</t>
         </is>
       </c>
       <c r="D146" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E146" s="5">
         <v>0</v>
@@ -5185,16 +5185,16 @@
         <v>0</v>
       </c>
       <c r="G146" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H146" s="6">
-        <v>450</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="147">
       <c r="A147" s="4" t="inlineStr">
         <is>
-          <t>225/75R15C</t>
+          <t>235/35R19</t>
         </is>
       </c>
       <c r="B147" s="4" t="inlineStr">
@@ -5204,61 +5204,61 @@
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>RD225/75R15C</t>
+          <t>RD235/35R19</t>
         </is>
       </c>
       <c r="D147" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E147" s="5">
         <v>0</v>
       </c>
       <c r="F147" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G147" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H147" s="6">
-        <v>330</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="148">
       <c r="A148" s="4" t="inlineStr">
         <is>
-          <t>235/35R19</t>
+          <t>235/40R19</t>
         </is>
       </c>
       <c r="B148" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C148" s="4" t="inlineStr">
         <is>
-          <t>RD235/35R19</t>
+          <t>GD235/40R19</t>
         </is>
       </c>
       <c r="D148" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E148" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F148" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G148" s="5">
         <v>0</v>
       </c>
       <c r="H148" s="6">
-        <v>600</v>
+        <v>850</v>
       </c>
     </row>
     <row outlineLevel="0" r="149">
       <c r="A149" s="4" t="inlineStr">
         <is>
-          <t>235/40R19</t>
+          <t>235/45R18</t>
         </is>
       </c>
       <c r="B149" s="4" t="inlineStr">
@@ -5268,14 +5268,14 @@
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>GD235/40R19</t>
+          <t>GD235/45R18</t>
         </is>
       </c>
       <c r="D149" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E149" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F149" s="5">
         <v>0</v>
@@ -5284,30 +5284,30 @@
         <v>0</v>
       </c>
       <c r="H149" s="6">
-        <v>850</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="150">
       <c r="A150" s="4" t="inlineStr">
         <is>
-          <t>235/45R18</t>
+          <t>235/50R18</t>
         </is>
       </c>
       <c r="B150" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C150" s="4" t="inlineStr">
         <is>
-          <t>GD235/45R18</t>
+          <t>HK235/50R18</t>
         </is>
       </c>
       <c r="D150" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E150" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F150" s="5">
         <v>0</v>
@@ -5316,30 +5316,30 @@
         <v>0</v>
       </c>
       <c r="H150" s="6">
-        <v>600</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="151">
       <c r="A151" s="4" t="inlineStr">
         <is>
-          <t>235/50R18</t>
+          <t>235/50R19</t>
         </is>
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>HK235/50R18</t>
+          <t>GD235/50R19</t>
         </is>
       </c>
       <c r="D151" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E151" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F151" s="5">
         <v>0</v>
@@ -5348,13 +5348,13 @@
         <v>0</v>
       </c>
       <c r="H151" s="6">
-        <v>500</v>
+        <v>800</v>
       </c>
     </row>
     <row outlineLevel="0" r="152">
       <c r="A152" s="4" t="inlineStr">
         <is>
-          <t>235/50R19</t>
+          <t>235/50R20</t>
         </is>
       </c>
       <c r="B152" s="4" t="inlineStr">
@@ -5364,78 +5364,78 @@
       </c>
       <c r="C152" s="4" t="inlineStr">
         <is>
-          <t>GD235/50R19</t>
+          <t>GD235/50R20</t>
         </is>
       </c>
       <c r="D152" s="5">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E152" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F152" s="5">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G152" s="5">
         <v>0</v>
       </c>
       <c r="H152" s="6">
-        <v>800</v>
+        <v>1180</v>
       </c>
     </row>
     <row outlineLevel="0" r="153">
       <c r="A153" s="4" t="inlineStr">
         <is>
-          <t>235/50R20</t>
+          <t>235/55R17</t>
         </is>
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>GD235/50R20</t>
+          <t>BR235/55R17</t>
         </is>
       </c>
       <c r="D153" s="5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E153" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F153" s="5">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G153" s="5">
         <v>0</v>
       </c>
       <c r="H153" s="6">
-        <v>1180</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="154">
       <c r="A154" s="4" t="inlineStr">
         <is>
-          <t>235/55R17</t>
+          <t>235/55R18</t>
         </is>
       </c>
       <c r="B154" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C154" s="4" t="inlineStr">
         <is>
-          <t>BR235/55R17</t>
+          <t>HK235/55R18</t>
         </is>
       </c>
       <c r="D154" s="5">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E154" s="5">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F154" s="5">
         <v>0</v>
@@ -5444,30 +5444,30 @@
         <v>0</v>
       </c>
       <c r="H154" s="6">
-        <v>450</v>
+        <v>480</v>
       </c>
     </row>
     <row outlineLevel="0" r="155">
       <c r="A155" s="4" t="inlineStr">
         <is>
-          <t>235/55R18</t>
+          <t>235/55R19</t>
         </is>
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>HK235/55R18</t>
+          <t>GD235/55R19</t>
         </is>
       </c>
       <c r="D155" s="5">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E155" s="5">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F155" s="5">
         <v>0</v>
@@ -5476,7 +5476,7 @@
         <v>0</v>
       </c>
       <c r="H155" s="6">
-        <v>480</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="156">
@@ -5487,19 +5487,19 @@
       </c>
       <c r="B156" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C156" s="4" t="inlineStr">
         <is>
-          <t>GD235/55R19</t>
+          <t>HK235/55R19</t>
         </is>
       </c>
       <c r="D156" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E156" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F156" s="5">
         <v>0</v>
@@ -5508,7 +5508,7 @@
         <v>0</v>
       </c>
       <c r="H156" s="6">
-        <v>750</v>
+        <v>630</v>
       </c>
     </row>
     <row outlineLevel="0" r="157">
@@ -5519,19 +5519,19 @@
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>HK235/55R19</t>
+          <t>LF235/55R19</t>
         </is>
       </c>
       <c r="D157" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E157" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F157" s="5">
         <v>0</v>
@@ -5540,7 +5540,7 @@
         <v>0</v>
       </c>
       <c r="H157" s="6">
-        <v>630</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="158">
@@ -5551,19 +5551,19 @@
       </c>
       <c r="B158" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C158" s="4" t="inlineStr">
         <is>
-          <t>LF235/55R19</t>
+          <t>NX235/55R19</t>
         </is>
       </c>
       <c r="D158" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E158" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F158" s="5">
         <v>0</v>
@@ -5572,7 +5572,7 @@
         <v>0</v>
       </c>
       <c r="H158" s="6">
-        <v>500</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="159">
@@ -5583,66 +5583,66 @@
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>NX235/55R19</t>
+          <t>RD235/55R19</t>
         </is>
       </c>
       <c r="D159" s="5">
         <v>2</v>
       </c>
       <c r="E159" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F159" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G159" s="5">
         <v>0</v>
       </c>
       <c r="H159" s="6">
-        <v>600</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="160">
       <c r="A160" s="4" t="inlineStr">
         <is>
-          <t>235/55R19</t>
+          <t>235/60R16</t>
         </is>
       </c>
       <c r="B160" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C160" s="4" t="inlineStr">
         <is>
-          <t>RD235/55R19</t>
+          <t>HK235/60R16</t>
         </is>
       </c>
       <c r="D160" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E160" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F160" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G160" s="5">
         <v>0</v>
       </c>
       <c r="H160" s="6">
-        <v>500</v>
+        <v>430</v>
       </c>
     </row>
     <row outlineLevel="0" r="161">
       <c r="A161" s="4" t="inlineStr">
         <is>
-          <t>235/60R16</t>
+          <t>235/60R17</t>
         </is>
       </c>
       <c r="B161" s="4" t="inlineStr">
@@ -5652,55 +5652,55 @@
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>HK235/60R16</t>
+          <t>HK235/60R17</t>
         </is>
       </c>
       <c r="D161" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E161" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F161" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G161" s="5">
         <v>0</v>
       </c>
       <c r="H161" s="6">
-        <v>430</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="162">
       <c r="A162" s="4" t="inlineStr">
         <is>
-          <t>235/60R17</t>
+          <t>235/60R18</t>
         </is>
       </c>
       <c r="B162" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C162" s="4" t="inlineStr">
         <is>
-          <t>HK235/60R17</t>
+          <t>GD235/60R18</t>
         </is>
       </c>
       <c r="D162" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E162" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F162" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G162" s="5">
         <v>0</v>
       </c>
       <c r="H162" s="6">
-        <v>500</v>
+        <v>680</v>
       </c>
     </row>
     <row outlineLevel="0" r="163">
@@ -5711,12 +5711,12 @@
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>GD235/60R18</t>
+          <t>HK235/60R18</t>
         </is>
       </c>
       <c r="D163" s="5">
@@ -5732,30 +5732,30 @@
         <v>0</v>
       </c>
       <c r="H163" s="6">
-        <v>680</v>
+        <v>550</v>
       </c>
     </row>
     <row outlineLevel="0" r="164">
       <c r="A164" s="4" t="inlineStr">
         <is>
-          <t>235/60R18</t>
+          <t>245/40R17</t>
         </is>
       </c>
       <c r="B164" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C164" s="4" t="inlineStr">
         <is>
-          <t>HK235/60R18</t>
+          <t>GD245/40R17</t>
         </is>
       </c>
       <c r="D164" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E164" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F164" s="5">
         <v>0</v>
@@ -5764,13 +5764,13 @@
         <v>0</v>
       </c>
       <c r="H164" s="6">
-        <v>550</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="165">
       <c r="A165" s="4" t="inlineStr">
         <is>
-          <t>245/40R17</t>
+          <t>245/40R18</t>
         </is>
       </c>
       <c r="B165" s="4" t="inlineStr">
@@ -5780,142 +5780,142 @@
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>GD245/40R17</t>
+          <t>GD245/40R18</t>
         </is>
       </c>
       <c r="D165" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E165" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F165" s="5">
         <v>0</v>
       </c>
       <c r="G165" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H165" s="6">
-        <v>400</v>
+        <v>620</v>
       </c>
     </row>
     <row outlineLevel="0" r="166">
       <c r="A166" s="4" t="inlineStr">
         <is>
-          <t>245/40R18</t>
+          <t>245/40R19</t>
         </is>
       </c>
       <c r="B166" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C166" s="4" t="inlineStr">
         <is>
-          <t>GD245/40R18</t>
+          <t>HK245/40R19</t>
         </is>
       </c>
       <c r="D166" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E166" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F166" s="5">
         <v>0</v>
       </c>
       <c r="G166" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H166" s="6">
-        <v>620</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="167">
       <c r="A167" s="4" t="inlineStr">
         <is>
-          <t>245/40R19</t>
+          <t>245/40R20</t>
         </is>
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>HK245/40R19</t>
+          <t>CT245/40R20</t>
         </is>
       </c>
       <c r="D167" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E167" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F167" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G167" s="5">
         <v>0</v>
       </c>
       <c r="H167" s="6">
-        <v>750</v>
+        <v>1050</v>
       </c>
     </row>
     <row outlineLevel="0" r="168">
       <c r="A168" s="4" t="inlineStr">
         <is>
-          <t>245/40R20</t>
+          <t>245/45R17</t>
         </is>
       </c>
       <c r="B168" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C168" s="4" t="inlineStr">
         <is>
-          <t>CT245/40R20</t>
+          <t>HK245/45R17</t>
         </is>
       </c>
       <c r="D168" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E168" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F168" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G168" s="5">
         <v>0</v>
       </c>
       <c r="H168" s="6">
-        <v>1050</v>
+        <v>430</v>
       </c>
     </row>
     <row outlineLevel="0" r="169">
       <c r="A169" s="4" t="inlineStr">
         <is>
-          <t>245/45R17</t>
+          <t>245/45R18</t>
         </is>
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>HK245/45R17</t>
+          <t>CT245/45R18</t>
         </is>
       </c>
       <c r="D169" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E169" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F169" s="5">
         <v>0</v>
@@ -5924,7 +5924,7 @@
         <v>0</v>
       </c>
       <c r="H169" s="6">
-        <v>430</v>
+        <v>650</v>
       </c>
     </row>
     <row outlineLevel="0" r="170">
@@ -5935,19 +5935,19 @@
       </c>
       <c r="B170" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C170" s="4" t="inlineStr">
         <is>
-          <t>CT245/45R18</t>
+          <t>GD245/45R18</t>
         </is>
       </c>
       <c r="D170" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E170" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F170" s="5">
         <v>0</v>
@@ -5956,7 +5956,7 @@
         <v>0</v>
       </c>
       <c r="H170" s="6">
-        <v>650</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="171">
@@ -5967,19 +5967,19 @@
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t>GD245/45R18</t>
+          <t>HK245/45R18</t>
         </is>
       </c>
       <c r="D171" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E171" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F171" s="5">
         <v>0</v>
@@ -5988,30 +5988,30 @@
         <v>0</v>
       </c>
       <c r="H171" s="6">
-        <v>600</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="172">
       <c r="A172" s="4" t="inlineStr">
         <is>
-          <t>245/45R18</t>
+          <t>245/45R18RF</t>
         </is>
       </c>
       <c r="B172" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C172" s="4" t="inlineStr">
         <is>
-          <t>HK245/45R18</t>
+          <t>GD245/45R18RF</t>
         </is>
       </c>
       <c r="D172" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E172" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F172" s="5">
         <v>0</v>
@@ -6020,23 +6020,23 @@
         <v>0</v>
       </c>
       <c r="H172" s="6">
-        <v>500</v>
+        <v>720</v>
       </c>
     </row>
     <row outlineLevel="0" r="173">
       <c r="A173" s="4" t="inlineStr">
         <is>
-          <t>245/45R18RF</t>
+          <t>245/45R19</t>
         </is>
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>GD245/45R18RF</t>
+          <t>BR245/45R19</t>
         </is>
       </c>
       <c r="D173" s="5">
@@ -6052,7 +6052,7 @@
         <v>0</v>
       </c>
       <c r="H173" s="6">
-        <v>720</v>
+        <v>790</v>
       </c>
     </row>
     <row outlineLevel="0" r="174">
@@ -6063,44 +6063,44 @@
       </c>
       <c r="B174" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C174" s="4" t="inlineStr">
         <is>
-          <t>BR245/45R19</t>
+          <t>RD245/45R19</t>
         </is>
       </c>
       <c r="D174" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E174" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F174" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G174" s="5">
         <v>0</v>
       </c>
       <c r="H174" s="6">
-        <v>790</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="175">
       <c r="A175" s="4" t="inlineStr">
         <is>
-          <t>245/45R19</t>
+          <t>245/45R20</t>
         </is>
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>RD245/45R19</t>
+          <t>HK245/45R20</t>
         </is>
       </c>
       <c r="D175" s="5">
@@ -6116,59 +6116,59 @@
         <v>0</v>
       </c>
       <c r="H175" s="6">
-        <v>450</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="176">
       <c r="A176" s="4" t="inlineStr">
         <is>
-          <t>245/45R20</t>
+          <t>245/65R17</t>
         </is>
       </c>
       <c r="B176" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C176" s="4" t="inlineStr">
         <is>
-          <t>HK245/45R20</t>
+          <t>NX245/65R17</t>
         </is>
       </c>
       <c r="D176" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E176" s="5">
         <v>0</v>
       </c>
       <c r="F176" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G176" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H176" s="6">
-        <v>750</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="177">
       <c r="A177" s="4" t="inlineStr">
         <is>
-          <t>245/65R17</t>
+          <t>245/70R16</t>
         </is>
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>LASSA</t>
         </is>
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>NX245/65R17</t>
+          <t>LS245/70R16</t>
         </is>
       </c>
       <c r="D177" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E177" s="5">
         <v>0</v>
@@ -6177,65 +6177,65 @@
         <v>0</v>
       </c>
       <c r="G177" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H177" s="6">
-        <v>600</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="178">
       <c r="A178" s="4" t="inlineStr">
         <is>
-          <t>245/70R16</t>
+          <t>255/35R19</t>
         </is>
       </c>
       <c r="B178" s="4" t="inlineStr">
         <is>
-          <t>LASSA</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C178" s="4" t="inlineStr">
         <is>
-          <t>LS245/70R16</t>
+          <t>DL255/35R19</t>
         </is>
       </c>
       <c r="D178" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E178" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F178" s="5">
         <v>0</v>
       </c>
       <c r="G178" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H178" s="6">
-        <v>500</v>
+        <v>700</v>
       </c>
     </row>
     <row outlineLevel="0" r="179">
       <c r="A179" s="4" t="inlineStr">
         <is>
-          <t>255/35R19</t>
+          <t>255/35R19RF</t>
         </is>
       </c>
       <c r="B179" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C179" s="4" t="inlineStr">
         <is>
-          <t>DL255/35R19</t>
+          <t>CT255/35R19RF</t>
         </is>
       </c>
       <c r="D179" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E179" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F179" s="5">
         <v>0</v>
@@ -6244,7 +6244,7 @@
         <v>0</v>
       </c>
       <c r="H179" s="6">
-        <v>700</v>
+        <v>950</v>
       </c>
     </row>
     <row outlineLevel="0" r="180">
@@ -6255,19 +6255,19 @@
       </c>
       <c r="B180" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C180" s="4" t="inlineStr">
         <is>
-          <t>CT255/35R19RF</t>
+          <t>GD255/35R19RF</t>
         </is>
       </c>
       <c r="D180" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E180" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F180" s="5">
         <v>0</v>
@@ -6282,39 +6282,39 @@
     <row outlineLevel="0" r="181">
       <c r="A181" s="4" t="inlineStr">
         <is>
-          <t>255/35R19RF</t>
+          <t>255/50R19</t>
         </is>
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C181" s="4" t="inlineStr">
         <is>
-          <t>GD255/35R19RF</t>
+          <t>CT255/50R19</t>
         </is>
       </c>
       <c r="D181" s="5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E181" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F181" s="5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G181" s="5">
         <v>0</v>
       </c>
       <c r="H181" s="6">
-        <v>950</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="182">
       <c r="A182" s="4" t="inlineStr">
         <is>
-          <t>255/50R19</t>
+          <t>255/50R20</t>
         </is>
       </c>
       <c r="B182" s="4" t="inlineStr">
@@ -6324,29 +6324,29 @@
       </c>
       <c r="C182" s="4" t="inlineStr">
         <is>
-          <t>CT255/50R19</t>
+          <t>CT255/50R20</t>
         </is>
       </c>
       <c r="D182" s="5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E182" s="5">
         <v>0</v>
       </c>
       <c r="F182" s="5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G182" s="5">
         <v>0</v>
       </c>
       <c r="H182" s="6">
-        <v>750</v>
+        <v>900</v>
       </c>
     </row>
     <row outlineLevel="0" r="183">
       <c r="A183" s="4" t="inlineStr">
         <is>
-          <t>255/50R20</t>
+          <t>255/55R19</t>
         </is>
       </c>
       <c r="B183" s="4" t="inlineStr">
@@ -6356,23 +6356,23 @@
       </c>
       <c r="C183" s="4" t="inlineStr">
         <is>
-          <t>CT255/50R20</t>
+          <t>CT255/55R19</t>
         </is>
       </c>
       <c r="D183" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E183" s="5">
         <v>0</v>
       </c>
       <c r="F183" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G183" s="5">
         <v>0</v>
       </c>
       <c r="H183" s="6">
-        <v>900</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="184">
@@ -6383,98 +6383,98 @@
       </c>
       <c r="B184" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C184" s="4" t="inlineStr">
         <is>
-          <t>CT255/55R19</t>
+          <t>DL255/55R19</t>
         </is>
       </c>
       <c r="D184" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E184" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F184" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G184" s="5">
         <v>0</v>
       </c>
       <c r="H184" s="6">
-        <v>750</v>
+        <v>700</v>
       </c>
     </row>
     <row outlineLevel="0" r="185">
       <c r="A185" s="4" t="inlineStr">
         <is>
-          <t>255/55R19</t>
+          <t>255/70R16</t>
         </is>
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C185" s="4" t="inlineStr">
         <is>
-          <t>DL255/55R19</t>
+          <t>RD255/70R16</t>
         </is>
       </c>
       <c r="D185" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E185" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F185" s="5">
         <v>0</v>
       </c>
       <c r="G185" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H185" s="6">
-        <v>700</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="186">
       <c r="A186" s="4" t="inlineStr">
         <is>
-          <t>255/70R16</t>
+          <t>265/35R18</t>
         </is>
       </c>
       <c r="B186" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C186" s="4" t="inlineStr">
         <is>
-          <t>RD255/70R16</t>
+          <t>GD265/35R18</t>
         </is>
       </c>
       <c r="D186" s="5">
         <v>1</v>
       </c>
       <c r="E186" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F186" s="5">
         <v>0</v>
       </c>
       <c r="G186" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H186" s="6">
-        <v>500</v>
+        <v>700</v>
       </c>
     </row>
     <row outlineLevel="0" r="187">
       <c r="A187" s="4" t="inlineStr">
         <is>
-          <t>265/35R18</t>
+          <t>265/50R20</t>
         </is>
       </c>
       <c r="B187" s="4" t="inlineStr">
@@ -6484,29 +6484,29 @@
       </c>
       <c r="C187" s="4" t="inlineStr">
         <is>
-          <t>GD265/35R18</t>
+          <t>GD265/50R20</t>
         </is>
       </c>
       <c r="D187" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E187" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F187" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G187" s="5">
         <v>0</v>
       </c>
       <c r="H187" s="6">
-        <v>700</v>
+        <v>1150</v>
       </c>
     </row>
     <row outlineLevel="0" r="188">
       <c r="A188" s="4" t="inlineStr">
         <is>
-          <t>265/50R20</t>
+          <t>275/35R19RF</t>
         </is>
       </c>
       <c r="B188" s="4" t="inlineStr">
@@ -6516,71 +6516,71 @@
       </c>
       <c r="C188" s="4" t="inlineStr">
         <is>
-          <t>GD265/50R20</t>
+          <t>GD275/35R19RF</t>
         </is>
       </c>
       <c r="D188" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E188" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F188" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G188" s="5">
         <v>0</v>
       </c>
       <c r="H188" s="6">
-        <v>1150</v>
+        <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="189">
       <c r="A189" s="4" t="inlineStr">
         <is>
-          <t>275/35R19RF</t>
+          <t>275/35R20</t>
         </is>
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C189" s="4" t="inlineStr">
         <is>
-          <t>GD275/35R19RF</t>
+          <t>CT275/35R20</t>
         </is>
       </c>
       <c r="D189" s="5">
         <v>2</v>
       </c>
       <c r="E189" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F189" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G189" s="5">
         <v>0</v>
       </c>
       <c r="H189" s="6">
-        <v>1</v>
+        <v>980</v>
       </c>
     </row>
     <row outlineLevel="0" r="190">
       <c r="A190" s="4" t="inlineStr">
         <is>
-          <t>275/35R20</t>
+          <t>275/40R20</t>
         </is>
       </c>
       <c r="B190" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C190" s="4" t="inlineStr">
         <is>
-          <t>CT275/35R20</t>
+          <t>HK275/40R20</t>
         </is>
       </c>
       <c r="D190" s="5">
@@ -6596,23 +6596,23 @@
         <v>0</v>
       </c>
       <c r="H190" s="6">
-        <v>980</v>
+        <v>770</v>
       </c>
     </row>
     <row outlineLevel="0" r="191">
       <c r="A191" s="4" t="inlineStr">
         <is>
-          <t>275/40R20</t>
+          <t>275/50R21</t>
         </is>
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C191" s="4" t="inlineStr">
         <is>
-          <t>HK275/40R20</t>
+          <t>GD275/50R21</t>
         </is>
       </c>
       <c r="D191" s="5">
@@ -6628,23 +6628,23 @@
         <v>0</v>
       </c>
       <c r="H191" s="6">
-        <v>770</v>
+        <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="192">
       <c r="A192" s="4" t="inlineStr">
         <is>
-          <t>275/50R21</t>
+          <t>295/35R21</t>
         </is>
       </c>
       <c r="B192" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C192" s="4" t="inlineStr">
         <is>
-          <t>GD275/50R21</t>
+          <t>CT295/35R21</t>
         </is>
       </c>
       <c r="D192" s="5">
@@ -6660,7 +6660,7 @@
         <v>0</v>
       </c>
       <c r="H192" s="6">
-        <v>1</v>
+        <v>1150</v>
       </c>
     </row>
     <row outlineLevel="0" r="193">
@@ -6671,91 +6671,59 @@
       </c>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C193" s="4" t="inlineStr">
         <is>
-          <t>CT295/35R21</t>
+          <t>GD295/35R21</t>
         </is>
       </c>
       <c r="D193" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E193" s="5">
         <v>0</v>
       </c>
       <c r="F193" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G193" s="5">
         <v>0</v>
       </c>
       <c r="H193" s="6">
-        <v>1150</v>
+        <v>980</v>
       </c>
     </row>
     <row outlineLevel="0" r="194">
       <c r="A194" s="4" t="inlineStr">
         <is>
-          <t>295/35R21</t>
+          <t>500R12</t>
         </is>
       </c>
       <c r="B194" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C194" s="4" t="inlineStr">
         <is>
-          <t>GD295/35R21</t>
+          <t>RD500R12</t>
         </is>
       </c>
       <c r="D194" s="5">
         <v>3</v>
       </c>
       <c r="E194" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F194" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G194" s="5">
         <v>0</v>
       </c>
       <c r="H194" s="6">
-        <v>980</v>
-      </c>
-    </row>
-    <row outlineLevel="0" r="195">
-      <c r="A195" s="4" t="inlineStr">
-        <is>
-          <t>500R12</t>
-        </is>
-      </c>
-      <c r="B195" s="4" t="inlineStr">
-        <is>
-          <t>RADIAL</t>
-        </is>
-      </c>
-      <c r="C195" s="4" t="inlineStr">
-        <is>
-          <t>RD500R12</t>
-        </is>
-      </c>
-      <c r="D195" s="5">
-        <v>3</v>
-      </c>
-      <c r="E195" s="5">
-        <v>3</v>
-      </c>
-      <c r="F195" s="5">
-        <v>0</v>
-      </c>
-      <c r="G195" s="5">
-        <v>0</v>
-      </c>
-      <c r="H195" s="6">
         <v>300</v>
       </c>
     </row>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -2200,10 +2200,10 @@
         </is>
       </c>
       <c r="D53" s="5">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E53" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F53" s="5">
         <v>6</v>
@@ -2776,10 +2776,10 @@
         </is>
       </c>
       <c r="D71" s="5">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E71" s="5">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F71" s="5">
         <v>23</v>
@@ -4152,10 +4152,10 @@
         </is>
       </c>
       <c r="D114" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E114" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F114" s="5">
         <v>0</v>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -496,7 +496,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H194"/>
+  <dimension ref="A1:H190"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col customWidth="true" min="1" max="1" width="13.8359375"/>
@@ -600,7 +600,7 @@
         </is>
       </c>
       <c r="D3" s="5">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E3" s="5">
         <v>5</v>
@@ -609,7 +609,7 @@
         <v>0</v>
       </c>
       <c r="G3" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H3" s="6">
         <v>180</v>
@@ -943,28 +943,28 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>AMINE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>AM175/65R14</t>
+          <t>GD175/65R14</t>
         </is>
       </c>
       <c r="D14" s="5">
-        <v>2</v>
+        <v>95</v>
       </c>
       <c r="E14" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F14" s="5">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="G14" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H14" s="6">
-        <v>170</v>
+        <v>220</v>
       </c>
     </row>
     <row outlineLevel="0" r="15">
@@ -975,28 +975,28 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>GD175/65R14</t>
+          <t>NX175/65R14</t>
         </is>
       </c>
       <c r="D15" s="5">
-        <v>97</v>
+        <v>1</v>
       </c>
       <c r="E15" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F15" s="5">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="G15" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H15" s="6">
-        <v>220</v>
+        <v>200</v>
       </c>
     </row>
     <row outlineLevel="0" r="16">
@@ -1007,28 +1007,28 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>NX175/65R14</t>
+          <t>RD175/65R14</t>
         </is>
       </c>
       <c r="D16" s="5">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E16" s="5">
         <v>1</v>
       </c>
       <c r="F16" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H16" s="6">
-        <v>200</v>
+        <v>180</v>
       </c>
     </row>
     <row outlineLevel="0" r="17">
@@ -1039,28 +1039,28 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>SEMPERIT</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>RD175/65R14</t>
+          <t>SP175/65R14</t>
         </is>
       </c>
       <c r="D17" s="5">
-        <v>7</v>
+        <v>59</v>
       </c>
       <c r="E17" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F17" s="5">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="G17" s="5">
         <v>5</v>
       </c>
       <c r="H17" s="6">
-        <v>180</v>
+        <v>190</v>
       </c>
     </row>
     <row outlineLevel="0" r="18">
@@ -1071,34 +1071,34 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>SEMPERIT</t>
+          <t>WESTLAKE</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>SP175/65R14</t>
+          <t>WL175/65R14</t>
         </is>
       </c>
       <c r="D18" s="5">
-        <v>59</v>
+        <v>93</v>
       </c>
       <c r="E18" s="5">
-        <v>4</v>
+        <v>81</v>
       </c>
       <c r="F18" s="5">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G18" s="5">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="H18" s="6">
-        <v>190</v>
+        <v>180</v>
       </c>
     </row>
     <row outlineLevel="0" r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>175/65R14</t>
+          <t>175/70R13</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
@@ -1108,39 +1108,39 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>WL175/65R14</t>
+          <t>WL175/70R13</t>
         </is>
       </c>
       <c r="D19" s="5">
-        <v>93</v>
+        <v>4</v>
       </c>
       <c r="E19" s="5">
-        <v>81</v>
+        <v>4</v>
       </c>
       <c r="F19" s="5">
         <v>0</v>
       </c>
       <c r="G19" s="5">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H19" s="6">
-        <v>180</v>
+        <v>200</v>
       </c>
     </row>
     <row outlineLevel="0" r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>175/70R13</t>
+          <t>175/70R14</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>WESTLAKE</t>
+          <t>MATADOR</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>WL175/70R13</t>
+          <t>MT175/70R14</t>
         </is>
       </c>
       <c r="D20" s="5">
@@ -1156,7 +1156,7 @@
         <v>0</v>
       </c>
       <c r="H20" s="6">
-        <v>200</v>
+        <v>230</v>
       </c>
     </row>
     <row outlineLevel="0" r="21">
@@ -1167,60 +1167,60 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>MATADOR</t>
+          <t>WESTLAKE</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>MT175/70R14</t>
+          <t>WL175/70R14</t>
         </is>
       </c>
       <c r="D21" s="5">
-        <v>4</v>
+        <v>43</v>
       </c>
       <c r="E21" s="5">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="F21" s="5">
         <v>0</v>
       </c>
       <c r="G21" s="5">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H21" s="6">
-        <v>230</v>
+        <v>200</v>
       </c>
     </row>
     <row outlineLevel="0" r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>175/70R14</t>
+          <t>185/55R15</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>WESTLAKE</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>WL175/70R14</t>
+          <t>BR185/55R15</t>
         </is>
       </c>
       <c r="D22" s="5">
-        <v>43</v>
+        <v>2</v>
       </c>
       <c r="E22" s="5">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="F22" s="5">
         <v>0</v>
       </c>
       <c r="G22" s="5">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H22" s="6">
-        <v>200</v>
+        <v>370</v>
       </c>
     </row>
     <row outlineLevel="0" r="23">
@@ -1231,34 +1231,34 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>BR185/55R15</t>
+          <t>GD185/55R15</t>
         </is>
       </c>
       <c r="D23" s="5">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="E23" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F23" s="5">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G23" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H23" s="6">
-        <v>370</v>
+        <v>340</v>
       </c>
     </row>
     <row outlineLevel="0" r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>185/55R15</t>
+          <t>185/55R16</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
@@ -1268,29 +1268,29 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>GD185/55R15</t>
+          <t>GD185/55R16</t>
         </is>
       </c>
       <c r="D24" s="5">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="E24" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F24" s="5">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="G24" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H24" s="6">
-        <v>340</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>185/55R16</t>
+          <t>185/60R14</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
@@ -1300,23 +1300,23 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>GD185/55R16</t>
+          <t>GD185/60R14</t>
         </is>
       </c>
       <c r="D25" s="5">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="E25" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F25" s="5">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G25" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H25" s="6">
-        <v>420</v>
+        <v>230</v>
       </c>
     </row>
     <row outlineLevel="0" r="26">
@@ -1327,25 +1327,25 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>GD185/60R14</t>
+          <t>NX185/60R14</t>
         </is>
       </c>
       <c r="D26" s="5">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="E26" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F26" s="5">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G26" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H26" s="6">
         <v>230</v>
@@ -1354,24 +1354,24 @@
     <row outlineLevel="0" r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>185/60R14</t>
+          <t>185/60R15</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>MATADOR</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>NX185/60R14</t>
+          <t>MT185/60R15</t>
         </is>
       </c>
       <c r="D27" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E27" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F27" s="5">
         <v>0</v>
@@ -1380,7 +1380,7 @@
         <v>0</v>
       </c>
       <c r="H27" s="6">
-        <v>230</v>
+        <v>280</v>
       </c>
     </row>
     <row outlineLevel="0" r="28">
@@ -1391,124 +1391,124 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>MATADOR</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>MT185/60R15</t>
+          <t>RD185/60R15</t>
         </is>
       </c>
       <c r="D28" s="5">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E28" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F28" s="5">
         <v>0</v>
       </c>
       <c r="G28" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H28" s="6">
-        <v>280</v>
+        <v>230</v>
       </c>
     </row>
     <row outlineLevel="0" r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>185/60R15</t>
+          <t>185/60R16</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>RD185/60R15</t>
+          <t>GD185/60R16</t>
         </is>
       </c>
       <c r="D29" s="5">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E29" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F29" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G29" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H29" s="6">
-        <v>230</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>185/60R16</t>
+          <t>185/65R14</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>GD185/60R16</t>
+          <t>RD185/65R14</t>
         </is>
       </c>
       <c r="D30" s="5">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E30" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F30" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G30" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H30" s="6">
-        <v>420</v>
+        <v>200</v>
       </c>
     </row>
     <row outlineLevel="0" r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>185/65R14</t>
+          <t>185/65R15</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>RD185/65R14</t>
+          <t>CT185/65R15</t>
         </is>
       </c>
       <c r="D31" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E31" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F31" s="5">
         <v>0</v>
       </c>
       <c r="G31" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H31" s="6">
-        <v>200</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="32">
@@ -1519,28 +1519,28 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>DOUBLESTAR</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>CT185/65R15</t>
+          <t>DS185/65R15</t>
         </is>
       </c>
       <c r="D32" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E32" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F32" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G32" s="5">
         <v>0</v>
       </c>
       <c r="H32" s="6">
-        <v>400</v>
+        <v>210</v>
       </c>
     </row>
     <row outlineLevel="0" r="33">
@@ -1551,28 +1551,28 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>DOUBLESTAR</t>
+          <t>FULDA</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>DS185/65R15</t>
+          <t>FL185/65R15</t>
         </is>
       </c>
       <c r="D33" s="5">
-        <v>5</v>
+        <v>136</v>
       </c>
       <c r="E33" s="5">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F33" s="5">
-        <v>5</v>
+        <v>109</v>
       </c>
       <c r="G33" s="5">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="H33" s="6">
-        <v>210</v>
+        <v>245</v>
       </c>
     </row>
     <row outlineLevel="0" r="34">
@@ -1583,28 +1583,28 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>FULDA</t>
+          <t>GOODRIDE</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>FL185/65R15</t>
+          <t>GR185/65R15</t>
         </is>
       </c>
       <c r="D34" s="5">
-        <v>136</v>
+        <v>11</v>
       </c>
       <c r="E34" s="5">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="F34" s="5">
-        <v>109</v>
+        <v>3</v>
       </c>
       <c r="G34" s="5">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="H34" s="6">
-        <v>245</v>
+        <v>230</v>
       </c>
     </row>
     <row outlineLevel="0" r="35">
@@ -1615,28 +1615,28 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>GOODRIDE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>GR185/65R15</t>
+          <t>GD185/65R15</t>
         </is>
       </c>
       <c r="D35" s="5">
-        <v>11</v>
+        <v>62</v>
       </c>
       <c r="E35" s="5">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F35" s="5">
-        <v>3</v>
+        <v>49</v>
       </c>
       <c r="G35" s="5">
         <v>4</v>
       </c>
       <c r="H35" s="6">
-        <v>230</v>
+        <v>260</v>
       </c>
     </row>
     <row outlineLevel="0" r="36">
@@ -1647,28 +1647,28 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>GD185/65R15</t>
+          <t>HK185/65R15</t>
         </is>
       </c>
       <c r="D36" s="5">
-        <v>64</v>
+        <v>5</v>
       </c>
       <c r="E36" s="5">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F36" s="5">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="G36" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H36" s="6">
-        <v>260</v>
+        <v>250</v>
       </c>
     </row>
     <row outlineLevel="0" r="37">
@@ -1679,16 +1679,16 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>HK185/65R15</t>
+          <t>LF185/65R15</t>
         </is>
       </c>
       <c r="D37" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E37" s="5">
         <v>4</v>
@@ -1697,7 +1697,7 @@
         <v>0</v>
       </c>
       <c r="G37" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H37" s="6">
         <v>250</v>
@@ -1711,25 +1711,25 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>SEMPERIT</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>LF185/65R15</t>
+          <t>SP185/65R15</t>
         </is>
       </c>
       <c r="D38" s="5">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="E38" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F38" s="5">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G38" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H38" s="6">
         <v>250</v>
@@ -1743,60 +1743,60 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>SEMPERIT</t>
+          <t>WESTLAKE</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>SP185/65R15</t>
+          <t>WL185/65R15</t>
         </is>
       </c>
       <c r="D39" s="5">
-        <v>30</v>
+        <v>81</v>
       </c>
       <c r="E39" s="5">
-        <v>5</v>
+        <v>75</v>
       </c>
       <c r="F39" s="5">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="G39" s="5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H39" s="6">
-        <v>250</v>
+        <v>220</v>
       </c>
     </row>
     <row outlineLevel="0" r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>185/65R15</t>
+          <t>185/70R14</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>WESTLAKE</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>WL185/65R15</t>
+          <t>RD185/70R14</t>
         </is>
       </c>
       <c r="D40" s="5">
-        <v>82</v>
+        <v>2</v>
       </c>
       <c r="E40" s="5">
-        <v>76</v>
+        <v>1</v>
       </c>
       <c r="F40" s="5">
         <v>0</v>
       </c>
       <c r="G40" s="5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H40" s="6">
-        <v>220</v>
+        <v>230</v>
       </c>
     </row>
     <row outlineLevel="0" r="41">
@@ -1807,60 +1807,60 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>WESTLAKE</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>RD185/70R14</t>
+          <t>WL185/70R14</t>
         </is>
       </c>
       <c r="D41" s="5">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E41" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F41" s="5">
         <v>0</v>
       </c>
       <c r="G41" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H41" s="6">
-        <v>230</v>
+        <v>220</v>
       </c>
     </row>
     <row outlineLevel="0" r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>185/70R14</t>
+          <t>195/50R15</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>WESTLAKE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>WL185/70R14</t>
+          <t>GD195/50R15</t>
         </is>
       </c>
       <c r="D42" s="5">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E42" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F42" s="5">
         <v>0</v>
       </c>
       <c r="G42" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H42" s="6">
-        <v>220</v>
+        <v>290</v>
       </c>
     </row>
     <row outlineLevel="0" r="43">
@@ -1871,28 +1871,28 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>SEMPERIT</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>GD195/50R15</t>
+          <t>SP195/50R15</t>
         </is>
       </c>
       <c r="D43" s="5">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="E43" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F43" s="5">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G43" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H43" s="6">
-        <v>290</v>
+        <v>260</v>
       </c>
     </row>
     <row outlineLevel="0" r="44">
@@ -1903,66 +1903,66 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>SEMPERIT</t>
+          <t>WESTLAKE</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>SP195/50R15</t>
+          <t>WL195/50R15</t>
         </is>
       </c>
       <c r="D44" s="5">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E44" s="5">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F44" s="5">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G44" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H44" s="6">
-        <v>260</v>
+        <v>225</v>
       </c>
     </row>
     <row outlineLevel="0" r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>195/50R15</t>
+          <t>195/50R16</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>WESTLAKE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>WL195/50R15</t>
+          <t>GD195/50R16</t>
         </is>
       </c>
       <c r="D45" s="5">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E45" s="5">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F45" s="5">
         <v>0</v>
       </c>
       <c r="G45" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H45" s="6">
-        <v>225</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>195/50R16</t>
+          <t>195/55R16</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
@@ -1972,23 +1972,23 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>GD195/50R16</t>
+          <t>GD195/55R16</t>
         </is>
       </c>
       <c r="D46" s="5">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="E46" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F46" s="5">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G46" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H46" s="6">
-        <v>330</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="47">
@@ -1999,28 +1999,28 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>GD195/55R16</t>
+          <t>HK195/55R16</t>
         </is>
       </c>
       <c r="D47" s="5">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E47" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F47" s="5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G47" s="5">
         <v>2</v>
       </c>
       <c r="H47" s="6">
-        <v>350</v>
+        <v>290</v>
       </c>
     </row>
     <row outlineLevel="0" r="48">
@@ -2031,28 +2031,28 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>LASSA</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>HK195/55R16</t>
+          <t>LS195/55R16</t>
         </is>
       </c>
       <c r="D48" s="5">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="E48" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F48" s="5">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G48" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H48" s="6">
-        <v>290</v>
+        <v>280</v>
       </c>
     </row>
     <row outlineLevel="0" r="49">
@@ -2063,19 +2063,19 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>LASSA</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>LS195/55R16</t>
+          <t>NX195/55R16</t>
         </is>
       </c>
       <c r="D49" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E49" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F49" s="5">
         <v>0</v>
@@ -2084,7 +2084,7 @@
         <v>0</v>
       </c>
       <c r="H49" s="6">
-        <v>280</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="50">
@@ -2095,92 +2095,92 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>NX195/55R16</t>
+          <t>RD195/55R16</t>
         </is>
       </c>
       <c r="D50" s="5">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E50" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F50" s="5">
         <v>0</v>
       </c>
       <c r="G50" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H50" s="6">
-        <v>300</v>
+        <v>250</v>
       </c>
     </row>
     <row outlineLevel="0" r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>195/55R16</t>
+          <t>195/60R16</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>RD195/55R16</t>
+          <t>GD195/60R16</t>
         </is>
       </c>
       <c r="D51" s="5">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="E51" s="5">
         <v>4</v>
       </c>
       <c r="F51" s="5">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G51" s="5">
         <v>3</v>
       </c>
       <c r="H51" s="6">
-        <v>250</v>
+        <v>355</v>
       </c>
     </row>
     <row outlineLevel="0" r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>195/60R16</t>
+          <t>195/65R15</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>DOUBLESTAR</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>GD195/60R16</t>
+          <t>DS195/65R15</t>
         </is>
       </c>
       <c r="D52" s="5">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="E52" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F52" s="5">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="G52" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H52" s="6">
-        <v>355</v>
+        <v>230</v>
       </c>
     </row>
     <row outlineLevel="0" r="53">
@@ -2191,22 +2191,22 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>DOUBLESTAR</t>
+          <t>GOODRIDE</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>DS195/65R15</t>
+          <t>GR195/65R15</t>
         </is>
       </c>
       <c r="D53" s="5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E53" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F53" s="5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G53" s="5">
         <v>0</v>
@@ -2223,28 +2223,28 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>GOODRIDE</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>GR195/65R15</t>
+          <t>HK195/65R15</t>
         </is>
       </c>
       <c r="D54" s="5">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E54" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F54" s="5">
         <v>0</v>
       </c>
       <c r="G54" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H54" s="6">
-        <v>230</v>
+        <v>260</v>
       </c>
     </row>
     <row outlineLevel="0" r="55">
@@ -2255,28 +2255,28 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>LASSA</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>HK195/65R15</t>
+          <t>LS195/65R15</t>
         </is>
       </c>
       <c r="D55" s="5">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E55" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F55" s="5">
         <v>0</v>
       </c>
       <c r="G55" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H55" s="6">
-        <v>260</v>
+        <v>250</v>
       </c>
     </row>
     <row outlineLevel="0" r="56">
@@ -2287,19 +2287,19 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>LASSA</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>LS195/65R15</t>
+          <t>NX195/65R15</t>
         </is>
       </c>
       <c r="D56" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E56" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F56" s="5">
         <v>0</v>
@@ -2308,7 +2308,7 @@
         <v>0</v>
       </c>
       <c r="H56" s="6">
-        <v>250</v>
+        <v>230</v>
       </c>
     </row>
     <row outlineLevel="0" r="57">
@@ -2319,25 +2319,25 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>NX195/65R15</t>
+          <t>RD195/65R15</t>
         </is>
       </c>
       <c r="D57" s="5">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E57" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F57" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G57" s="5">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H57" s="6">
         <v>230</v>
@@ -2351,92 +2351,92 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>SEMPERIT</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>RD195/65R15</t>
+          <t>SP195/65R15</t>
         </is>
       </c>
       <c r="D58" s="5">
-        <v>15</v>
+        <v>89</v>
       </c>
       <c r="E58" s="5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F58" s="5">
-        <v>1</v>
+        <v>69</v>
       </c>
       <c r="G58" s="5">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="H58" s="6">
-        <v>230</v>
+        <v>250</v>
       </c>
     </row>
     <row outlineLevel="0" r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>195/65R15</t>
+          <t>195/75R16C</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>SEMPERIT</t>
+          <t>GOODRIDE</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>SP195/65R15</t>
+          <t>GR195/75R16C</t>
         </is>
       </c>
       <c r="D59" s="5">
-        <v>89</v>
+        <v>12</v>
       </c>
       <c r="E59" s="5">
+        <v>3</v>
+      </c>
+      <c r="F59" s="5">
         <v>7</v>
       </c>
-      <c r="F59" s="5">
-        <v>69</v>
-      </c>
       <c r="G59" s="5">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="H59" s="6">
-        <v>250</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>195/75R16C</t>
+          <t>205/45R17</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>GOODRIDE</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>GR195/75R16C</t>
+          <t>CT205/45R17</t>
         </is>
       </c>
       <c r="D60" s="5">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E60" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F60" s="5">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G60" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H60" s="6">
-        <v>350</v>
+        <v>550</v>
       </c>
     </row>
     <row outlineLevel="0" r="61">
@@ -2447,28 +2447,28 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>FULDA</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>CT205/45R17</t>
+          <t>FL205/45R17</t>
         </is>
       </c>
       <c r="D61" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E61" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F61" s="5">
         <v>0</v>
       </c>
       <c r="G61" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H61" s="6">
-        <v>550</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="62">
@@ -2479,28 +2479,28 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>FULDA</t>
+          <t>GOODRIDE</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>FL205/45R17</t>
+          <t>GR205/45R17</t>
         </is>
       </c>
       <c r="D62" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E62" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F62" s="5">
         <v>0</v>
       </c>
       <c r="G62" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H62" s="6">
-        <v>380</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="63">
@@ -2511,28 +2511,28 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>GOODRIDE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>GR205/45R17</t>
+          <t>GD205/45R17</t>
         </is>
       </c>
       <c r="D63" s="5">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="E63" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F63" s="5">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G63" s="5">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H63" s="6">
-        <v>300</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="64">
@@ -2543,28 +2543,28 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>GD205/45R17</t>
+          <t>NX205/45R17</t>
         </is>
       </c>
       <c r="D64" s="5">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="E64" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F64" s="5">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G64" s="5">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H64" s="6">
-        <v>450</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="65">
@@ -2575,83 +2575,83 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>NX205/45R17</t>
+          <t>RD205/45R17</t>
         </is>
       </c>
       <c r="D65" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E65" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F65" s="5">
         <v>0</v>
       </c>
       <c r="G65" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H65" s="6">
-        <v>380</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>205/45R17</t>
+          <t>205/50R17</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>RD205/45R17</t>
+          <t>CT205/50R17</t>
         </is>
       </c>
       <c r="D66" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E66" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F66" s="5">
         <v>0</v>
       </c>
       <c r="G66" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H66" s="6">
-        <v>300</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>205/50R17</t>
+          <t>205/55R16</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>AMINE</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>CT205/50R17</t>
+          <t>AM205/55R16</t>
         </is>
       </c>
       <c r="D67" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E67" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F67" s="5">
         <v>0</v>
@@ -2660,7 +2660,7 @@
         <v>0</v>
       </c>
       <c r="H67" s="6">
-        <v>450</v>
+        <v>240</v>
       </c>
     </row>
     <row outlineLevel="0" r="68">
@@ -2671,28 +2671,28 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>AMINE</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>AM205/55R16</t>
+          <t>BR205/55R16</t>
         </is>
       </c>
       <c r="D68" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E68" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F68" s="5">
         <v>0</v>
       </c>
       <c r="G68" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H68" s="6">
-        <v>240</v>
+        <v>290</v>
       </c>
     </row>
     <row outlineLevel="0" r="69">
@@ -2703,28 +2703,28 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>DOUBLESTAR</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>BR205/55R16</t>
+          <t>DS205/55R16</t>
         </is>
       </c>
       <c r="D69" s="5">
         <v>4</v>
       </c>
       <c r="E69" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F69" s="5">
         <v>0</v>
       </c>
       <c r="G69" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H69" s="6">
-        <v>290</v>
+        <v>230</v>
       </c>
     </row>
     <row outlineLevel="0" r="70">
@@ -2735,28 +2735,28 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>DOUBLESTAR</t>
+          <t>FULDA</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>DS205/55R16</t>
+          <t>FL205/55R16</t>
         </is>
       </c>
       <c r="D70" s="5">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="E70" s="5">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F70" s="5">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G70" s="5">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H70" s="6">
-        <v>230</v>
+        <v>250</v>
       </c>
     </row>
     <row outlineLevel="0" r="71">
@@ -2767,25 +2767,25 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>FULDA</t>
+          <t>GOODRIDE</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>FL205/55R16</t>
+          <t>GR205/55R16</t>
         </is>
       </c>
       <c r="D71" s="5">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="E71" s="5">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F71" s="5">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="G71" s="5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H71" s="6">
         <v>250</v>
@@ -2799,28 +2799,28 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>GOODRIDE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>GR205/55R16</t>
+          <t>GD205/55R16</t>
         </is>
       </c>
       <c r="D72" s="5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E72" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F72" s="5">
         <v>0</v>
       </c>
       <c r="G72" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H72" s="6">
-        <v>250</v>
+        <v>280</v>
       </c>
     </row>
     <row outlineLevel="0" r="73">
@@ -2831,28 +2831,28 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>GD205/55R16</t>
+          <t>HK205/55R16</t>
         </is>
       </c>
       <c r="D73" s="5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E73" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F73" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G73" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H73" s="6">
-        <v>280</v>
+        <v>260</v>
       </c>
     </row>
     <row outlineLevel="0" r="74">
@@ -2863,48 +2863,48 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>HK205/55R16</t>
+          <t>RD205/55R16</t>
         </is>
       </c>
       <c r="D74" s="5">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E74" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F74" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G74" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H74" s="6">
-        <v>260</v>
+        <v>230</v>
       </c>
     </row>
     <row outlineLevel="0" r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>205/55R16</t>
+          <t>205/55R16RF</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>RD205/55R16</t>
+          <t>GD205/55R16RF</t>
         </is>
       </c>
       <c r="D75" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E75" s="5">
         <v>0</v>
@@ -2913,16 +2913,16 @@
         <v>0</v>
       </c>
       <c r="G75" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H75" s="6">
-        <v>230</v>
+        <v>480</v>
       </c>
     </row>
     <row outlineLevel="0" r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>205/55R16RF</t>
+          <t>205/55R17</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
@@ -2932,23 +2932,23 @@
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>GD205/55R16RF</t>
+          <t>GD205/55R17</t>
         </is>
       </c>
       <c r="D76" s="5">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="E76" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F76" s="5">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G76" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H76" s="6">
-        <v>480</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="77">
@@ -2959,44 +2959,44 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>GD205/55R17</t>
+          <t>NX205/55R17</t>
         </is>
       </c>
       <c r="D77" s="5">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="E77" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F77" s="5">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G77" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H77" s="6">
-        <v>450</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>205/55R17</t>
+          <t>205/60R16</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>NX205/55R17</t>
+          <t>DL205/60R16</t>
         </is>
       </c>
       <c r="D78" s="5">
@@ -3012,7 +3012,7 @@
         <v>0</v>
       </c>
       <c r="H78" s="6">
-        <v>400</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="79">
@@ -3023,28 +3023,28 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>DL205/60R16</t>
+          <t>GD205/60R16</t>
         </is>
       </c>
       <c r="D79" s="5">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="E79" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F79" s="5">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G79" s="5">
         <v>0</v>
       </c>
       <c r="H79" s="6">
-        <v>330</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="80">
@@ -3055,28 +3055,28 @@
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>GD205/60R16</t>
+          <t>HK205/60R16</t>
         </is>
       </c>
       <c r="D80" s="5">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E80" s="5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F80" s="5">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="G80" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H80" s="6">
-        <v>380</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="81">
@@ -3087,25 +3087,25 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>HK205/60R16</t>
+          <t>LF205/60R16</t>
         </is>
       </c>
       <c r="D81" s="5">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E81" s="5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F81" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G81" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H81" s="6">
         <v>300</v>
@@ -3114,17 +3114,17 @@
     <row outlineLevel="0" r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>205/60R16</t>
+          <t>205/65R15</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>LF205/60R16</t>
+          <t>HK205/65R15</t>
         </is>
       </c>
       <c r="D82" s="5">
@@ -3140,30 +3140,30 @@
         <v>0</v>
       </c>
       <c r="H82" s="6">
-        <v>300</v>
+        <v>270</v>
       </c>
     </row>
     <row outlineLevel="0" r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>205/65R15</t>
+          <t>205/65R16</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>HK205/65R15</t>
+          <t>BR205/65R16</t>
         </is>
       </c>
       <c r="D83" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E83" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F83" s="5">
         <v>0</v>
@@ -3172,7 +3172,7 @@
         <v>0</v>
       </c>
       <c r="H83" s="6">
-        <v>270</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="84">
@@ -3183,19 +3183,19 @@
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>BR205/65R16</t>
+          <t>HK205/65R16</t>
         </is>
       </c>
       <c r="D84" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E84" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F84" s="5">
         <v>0</v>
@@ -3204,39 +3204,39 @@
         <v>0</v>
       </c>
       <c r="H84" s="6">
-        <v>420</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>205/65R16</t>
+          <t>215/40R18</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>HK205/65R16</t>
+          <t>GD215/40R18</t>
         </is>
       </c>
       <c r="D85" s="5">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E85" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F85" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G85" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H85" s="6">
-        <v>380</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="86">
@@ -3247,44 +3247,44 @@
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>GD215/40R18</t>
+          <t>HK215/40R18</t>
         </is>
       </c>
       <c r="D86" s="5">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E86" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F86" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G86" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H86" s="6">
-        <v>600</v>
+        <v>490</v>
       </c>
     </row>
     <row outlineLevel="0" r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>215/40R18</t>
+          <t>215/45R16</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>HK215/40R18</t>
+          <t>GD215/45R16</t>
         </is>
       </c>
       <c r="D87" s="5">
@@ -3300,13 +3300,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="6">
-        <v>490</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>215/45R16</t>
+          <t>215/45R17</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
@@ -3316,14 +3316,14 @@
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>GD215/45R16</t>
+          <t>GD215/45R17</t>
         </is>
       </c>
       <c r="D88" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E88" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F88" s="5">
         <v>0</v>
@@ -3332,7 +3332,7 @@
         <v>0</v>
       </c>
       <c r="H88" s="6">
-        <v>450</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="89">
@@ -3343,25 +3343,25 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>GD215/45R17</t>
+          <t>HK215/45R17</t>
         </is>
       </c>
       <c r="D89" s="5">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E89" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F89" s="5">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G89" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H89" s="6">
         <v>400</v>
@@ -3375,28 +3375,28 @@
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>IRIS</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>HK215/45R17</t>
+          <t>IR215/45R17</t>
         </is>
       </c>
       <c r="D90" s="5">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="E90" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F90" s="5">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G90" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H90" s="6">
-        <v>400</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="91">
@@ -3407,28 +3407,28 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>IRIS</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>IR215/45R17</t>
+          <t>LF215/45R17</t>
         </is>
       </c>
       <c r="D91" s="5">
         <v>1</v>
       </c>
       <c r="E91" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F91" s="5">
         <v>0</v>
       </c>
       <c r="G91" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H91" s="6">
-        <v>300</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="92">
@@ -3439,83 +3439,83 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>LF215/45R17</t>
+          <t>NX215/45R17</t>
         </is>
       </c>
       <c r="D92" s="5">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E92" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F92" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G92" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H92" s="6">
-        <v>350</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>215/45R17</t>
+          <t>215/45R18</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>NX215/45R17</t>
+          <t>GD215/45R18</t>
         </is>
       </c>
       <c r="D93" s="5">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E93" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F93" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G93" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H93" s="6">
-        <v>380</v>
+        <v>550</v>
       </c>
     </row>
     <row outlineLevel="0" r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>215/45R18</t>
+          <t>215/50R17</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>GD215/45R18</t>
+          <t>BR215/50R17</t>
         </is>
       </c>
       <c r="D94" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E94" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F94" s="5">
         <v>0</v>
@@ -3524,7 +3524,7 @@
         <v>0</v>
       </c>
       <c r="H94" s="6">
-        <v>550</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="95">
@@ -3535,28 +3535,28 @@
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>BR215/50R17</t>
+          <t>GD215/50R17</t>
         </is>
       </c>
       <c r="D95" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E95" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F95" s="5">
         <v>0</v>
       </c>
       <c r="G95" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H95" s="6">
-        <v>450</v>
+        <v>470</v>
       </c>
     </row>
     <row outlineLevel="0" r="96">
@@ -3567,16 +3567,16 @@
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>GD215/50R17</t>
+          <t>HK215/50R17</t>
         </is>
       </c>
       <c r="D96" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E96" s="5">
         <v>3</v>
@@ -3585,33 +3585,33 @@
         <v>0</v>
       </c>
       <c r="G96" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H96" s="6">
-        <v>470</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>215/50R17</t>
+          <t>215/50R18</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>HK215/50R17</t>
+          <t>GD215/50R18</t>
         </is>
       </c>
       <c r="D97" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E97" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F97" s="5">
         <v>0</v>
@@ -3620,23 +3620,23 @@
         <v>0</v>
       </c>
       <c r="H97" s="6">
-        <v>400</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="98">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>215/50R17</t>
+          <t>215/55R16</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>LF215/50R17</t>
+          <t>GD215/55R16</t>
         </is>
       </c>
       <c r="D98" s="5">
@@ -3652,30 +3652,30 @@
         <v>0</v>
       </c>
       <c r="H98" s="6">
-        <v>420</v>
+        <v>440</v>
       </c>
     </row>
     <row outlineLevel="0" r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>215/50R18</t>
+          <t>215/55R16</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>GD215/50R18</t>
+          <t>LF215/55R16</t>
         </is>
       </c>
       <c r="D99" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E99" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F99" s="5">
         <v>0</v>
@@ -3684,23 +3684,23 @@
         <v>0</v>
       </c>
       <c r="H99" s="6">
-        <v>600</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="100">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>215/55R16</t>
+          <t>215/55R17</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>GD215/55R16</t>
+          <t>BR215/55R17</t>
         </is>
       </c>
       <c r="D100" s="5">
@@ -3716,30 +3716,30 @@
         <v>0</v>
       </c>
       <c r="H100" s="6">
-        <v>440</v>
+        <v>480</v>
       </c>
     </row>
     <row outlineLevel="0" r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>215/55R16</t>
+          <t>215/55R17</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>LF215/55R16</t>
+          <t>HK215/55R17</t>
         </is>
       </c>
       <c r="D101" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E101" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F101" s="5">
         <v>0</v>
@@ -3748,30 +3748,30 @@
         <v>0</v>
       </c>
       <c r="H101" s="6">
-        <v>350</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="102">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>215/55R17</t>
+          <t>215/55R18</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>BR215/55R17</t>
+          <t>GD215/55R18</t>
         </is>
       </c>
       <c r="D102" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E102" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F102" s="5">
         <v>0</v>
@@ -3780,23 +3780,23 @@
         <v>0</v>
       </c>
       <c r="H102" s="6">
-        <v>480</v>
+        <v>580</v>
       </c>
     </row>
     <row outlineLevel="0" r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>215/55R17</t>
+          <t>215/60R16</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>HK215/55R17</t>
+          <t>BR215/60R16</t>
         </is>
       </c>
       <c r="D103" s="5">
@@ -3812,39 +3812,39 @@
         <v>0</v>
       </c>
       <c r="H103" s="6">
-        <v>420</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="104">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>215/55R18</t>
+          <t>215/60R16</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>GD215/55R18</t>
+          <t>DL215/60R16</t>
         </is>
       </c>
       <c r="D104" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E104" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F104" s="5">
         <v>0</v>
       </c>
       <c r="G104" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H104" s="6">
-        <v>580</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="105">
@@ -3855,16 +3855,16 @@
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>BR215/60R16</t>
+          <t>HK215/60R16</t>
         </is>
       </c>
       <c r="D105" s="5">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E105" s="5">
         <v>4</v>
@@ -3873,10 +3873,10 @@
         <v>0</v>
       </c>
       <c r="G105" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H105" s="6">
-        <v>350</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="106">
@@ -3887,16 +3887,16 @@
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>DL215/60R16</t>
+          <t>NX215/60R16</t>
         </is>
       </c>
       <c r="D106" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E106" s="5">
         <v>0</v>
@@ -3905,62 +3905,62 @@
         <v>0</v>
       </c>
       <c r="G106" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H106" s="6">
-        <v>350</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>215/60R16</t>
+          <t>215/60R17</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>HK215/60R16</t>
+          <t>RD215/60R17</t>
         </is>
       </c>
       <c r="D107" s="5">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E107" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F107" s="5">
         <v>0</v>
       </c>
       <c r="G107" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H107" s="6">
-        <v>330</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="108">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>215/60R16</t>
+          <t>215/65R16</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>NX215/60R16</t>
+          <t>GD215/65R16</t>
         </is>
       </c>
       <c r="D108" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E108" s="5">
         <v>0</v>
@@ -3969,26 +3969,26 @@
         <v>0</v>
       </c>
       <c r="G108" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H108" s="6">
-        <v>330</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="109">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>215/60R17</t>
+          <t>215/65R16</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>RD215/60R17</t>
+          <t>HK215/65R16</t>
         </is>
       </c>
       <c r="D109" s="5">
@@ -4004,87 +4004,87 @@
         <v>0</v>
       </c>
       <c r="H109" s="6">
-        <v>300</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="110">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>215/65R16</t>
+          <t>215/65R17</t>
         </is>
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>MICHELIN</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>GD215/65R16</t>
+          <t>MC215/65R17</t>
         </is>
       </c>
       <c r="D110" s="5">
         <v>1</v>
       </c>
       <c r="E110" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F110" s="5">
         <v>0</v>
       </c>
       <c r="G110" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H110" s="6">
-        <v>380</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="111">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>215/65R16</t>
+          <t>215/70R15C</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>LINGLONG</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>HK215/65R16</t>
+          <t>LG215/70R15C</t>
         </is>
       </c>
       <c r="D111" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E111" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F111" s="5">
         <v>0</v>
       </c>
       <c r="G111" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H111" s="6">
-        <v>330</v>
+        <v>370</v>
       </c>
     </row>
     <row outlineLevel="0" r="112">
       <c r="A112" s="4" t="inlineStr">
         <is>
-          <t>215/65R17</t>
+          <t>225/40R18</t>
         </is>
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>MICHELIN</t>
+          <t>BARUM</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>MC215/65R17</t>
+          <t>BM225/40R18</t>
         </is>
       </c>
       <c r="D112" s="5">
@@ -4100,62 +4100,62 @@
         <v>0</v>
       </c>
       <c r="H112" s="6">
-        <v>600</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="113">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>215/70R15C</t>
+          <t>225/40R18</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>LINGLONG</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>LG215/70R15C</t>
+          <t>GD225/40R18</t>
         </is>
       </c>
       <c r="D113" s="5">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="E113" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F113" s="5">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G113" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H113" s="6">
-        <v>370</v>
+        <v>480</v>
       </c>
     </row>
     <row outlineLevel="0" r="114">
       <c r="A114" s="4" t="inlineStr">
         <is>
-          <t>215/70R15C</t>
+          <t>225/40R18</t>
         </is>
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>RD215/70R15C</t>
+          <t>HK225/40R18</t>
         </is>
       </c>
       <c r="D114" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E114" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F114" s="5">
         <v>0</v>
@@ -4164,7 +4164,7 @@
         <v>0</v>
       </c>
       <c r="H114" s="6">
-        <v>330</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="115">
@@ -4175,28 +4175,28 @@
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>BARUM</t>
+          <t>LASSA</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>BM225/40R18</t>
+          <t>LS225/40R18</t>
         </is>
       </c>
       <c r="D115" s="5">
         <v>1</v>
       </c>
       <c r="E115" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F115" s="5">
         <v>0</v>
       </c>
       <c r="G115" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H115" s="6">
-        <v>420</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="116">
@@ -4207,28 +4207,28 @@
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>GD225/40R18</t>
+          <t>NX225/40R18</t>
         </is>
       </c>
       <c r="D116" s="5">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="E116" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F116" s="5">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G116" s="5">
         <v>0</v>
       </c>
       <c r="H116" s="6">
-        <v>480</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="117">
@@ -4239,19 +4239,19 @@
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>SEMPERIT</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>HK225/40R18</t>
+          <t>SP225/40R18</t>
         </is>
       </c>
       <c r="D117" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E117" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F117" s="5">
         <v>0</v>
@@ -4266,49 +4266,49 @@
     <row outlineLevel="0" r="118">
       <c r="A118" s="4" t="inlineStr">
         <is>
-          <t>225/40R18</t>
+          <t>225/40R18RF</t>
         </is>
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>LASSA</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>LS225/40R18</t>
+          <t>GD225/40R18RF</t>
         </is>
       </c>
       <c r="D118" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E118" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F118" s="5">
         <v>0</v>
       </c>
       <c r="G118" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H118" s="6">
-        <v>330</v>
+        <v>590</v>
       </c>
     </row>
     <row outlineLevel="0" r="119">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t>225/40R18</t>
+          <t>225/45R17</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>NX225/40R18</t>
+          <t>CT225/45R17</t>
         </is>
       </c>
       <c r="D119" s="5">
@@ -4330,39 +4330,39 @@
     <row outlineLevel="0" r="120">
       <c r="A120" s="4" t="inlineStr">
         <is>
-          <t>225/40R18</t>
+          <t>225/45R17</t>
         </is>
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>SEMPERIT</t>
+          <t>FULDA</t>
         </is>
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>SP225/40R18</t>
+          <t>FL225/45R17</t>
         </is>
       </c>
       <c r="D120" s="5">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="E120" s="5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F120" s="5">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G120" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H120" s="6">
-        <v>450</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="121">
       <c r="A121" s="4" t="inlineStr">
         <is>
-          <t>225/40R18RF</t>
+          <t>225/45R17</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
@@ -4372,23 +4372,23 @@
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>GD225/40R18RF</t>
+          <t>GD225/45R17</t>
         </is>
       </c>
       <c r="D121" s="5">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="E121" s="5">
         <v>4</v>
       </c>
       <c r="F121" s="5">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G121" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H121" s="6">
-        <v>590</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="122">
@@ -4399,19 +4399,19 @@
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>CT225/45R17</t>
+          <t>HK225/45R17</t>
         </is>
       </c>
       <c r="D122" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E122" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F122" s="5">
         <v>0</v>
@@ -4420,45 +4420,45 @@
         <v>0</v>
       </c>
       <c r="H122" s="6">
-        <v>400</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="123">
       <c r="A123" s="4" t="inlineStr">
         <is>
-          <t>225/45R17</t>
+          <t>225/45R18</t>
         </is>
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>FULDA</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>FL225/45R17</t>
+          <t>DL225/45R18</t>
         </is>
       </c>
       <c r="D123" s="5">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="E123" s="5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F123" s="5">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G123" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H123" s="6">
-        <v>350</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="124">
       <c r="A124" s="4" t="inlineStr">
         <is>
-          <t>225/45R17</t>
+          <t>225/45R18</t>
         </is>
       </c>
       <c r="B124" s="4" t="inlineStr">
@@ -4468,46 +4468,46 @@
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>GD225/45R17</t>
+          <t>GD225/45R18</t>
         </is>
       </c>
       <c r="D124" s="5">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="E124" s="5">
         <v>4</v>
       </c>
       <c r="F124" s="5">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="G124" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H124" s="6">
-        <v>380</v>
+        <v>550</v>
       </c>
     </row>
     <row outlineLevel="0" r="125">
       <c r="A125" s="4" t="inlineStr">
         <is>
-          <t>225/45R17</t>
+          <t>225/45R18</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>HK225/45R17</t>
+          <t>LF225/45R18</t>
         </is>
       </c>
       <c r="D125" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E125" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F125" s="5">
         <v>0</v>
@@ -4516,30 +4516,30 @@
         <v>0</v>
       </c>
       <c r="H125" s="6">
-        <v>350</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="126">
       <c r="A126" s="4" t="inlineStr">
         <is>
-          <t>225/45R18</t>
+          <t>225/45R18RF</t>
         </is>
       </c>
       <c r="B126" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C126" s="4" t="inlineStr">
         <is>
-          <t>DL225/45R18</t>
+          <t>GD225/45R18RF</t>
         </is>
       </c>
       <c r="D126" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E126" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F126" s="5">
         <v>0</v>
@@ -4548,62 +4548,62 @@
         <v>2</v>
       </c>
       <c r="H126" s="6">
-        <v>500</v>
+        <v>720</v>
       </c>
     </row>
     <row outlineLevel="0" r="127">
       <c r="A127" s="4" t="inlineStr">
         <is>
-          <t>225/45R18</t>
+          <t>225/45R19</t>
         </is>
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>GD225/45R18</t>
+          <t>CT225/45R19</t>
         </is>
       </c>
       <c r="D127" s="5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E127" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F127" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G127" s="5">
         <v>0</v>
       </c>
       <c r="H127" s="6">
-        <v>550</v>
+        <v>780</v>
       </c>
     </row>
     <row outlineLevel="0" r="128">
       <c r="A128" s="4" t="inlineStr">
         <is>
-          <t>225/45R18</t>
+          <t>225/50R17</t>
         </is>
       </c>
       <c r="B128" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C128" s="4" t="inlineStr">
         <is>
-          <t>LF225/45R18</t>
+          <t>BR225/50R17</t>
         </is>
       </c>
       <c r="D128" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E128" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F128" s="5">
         <v>0</v>
@@ -4612,13 +4612,13 @@
         <v>0</v>
       </c>
       <c r="H128" s="6">
-        <v>420</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="129">
       <c r="A129" s="4" t="inlineStr">
         <is>
-          <t>225/45R18RF</t>
+          <t>225/50R17</t>
         </is>
       </c>
       <c r="B129" s="4" t="inlineStr">
@@ -4628,78 +4628,78 @@
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>GD225/45R18RF</t>
+          <t>GD225/50R17</t>
         </is>
       </c>
       <c r="D129" s="5">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E129" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F129" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G129" s="5">
         <v>2</v>
       </c>
       <c r="H129" s="6">
-        <v>720</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="130">
       <c r="A130" s="4" t="inlineStr">
         <is>
-          <t>225/45R19</t>
+          <t>225/50R17</t>
         </is>
       </c>
       <c r="B130" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C130" s="4" t="inlineStr">
         <is>
-          <t>CT225/45R19</t>
+          <t>HK225/50R17</t>
         </is>
       </c>
       <c r="D130" s="5">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E130" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F130" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G130" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H130" s="6">
-        <v>780</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="131">
       <c r="A131" s="4" t="inlineStr">
         <is>
-          <t>225/50R17</t>
+          <t>225/55R16</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>BR225/50R17</t>
+          <t>DL225/55R16</t>
         </is>
       </c>
       <c r="D131" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E131" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F131" s="5">
         <v>0</v>
@@ -4708,13 +4708,13 @@
         <v>0</v>
       </c>
       <c r="H131" s="6">
-        <v>600</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="132">
       <c r="A132" s="4" t="inlineStr">
         <is>
-          <t>225/50R17</t>
+          <t>225/55R16</t>
         </is>
       </c>
       <c r="B132" s="4" t="inlineStr">
@@ -4724,29 +4724,29 @@
       </c>
       <c r="C132" s="4" t="inlineStr">
         <is>
-          <t>GD225/50R17</t>
+          <t>GD225/55R16</t>
         </is>
       </c>
       <c r="D132" s="5">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E132" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F132" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G132" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H132" s="6">
-        <v>500</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="133">
       <c r="A133" s="4" t="inlineStr">
         <is>
-          <t>225/50R17</t>
+          <t>225/55R17</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
@@ -4756,78 +4756,78 @@
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>HK225/50R17</t>
+          <t>HK225/55R17</t>
         </is>
       </c>
       <c r="D133" s="5">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E133" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F133" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G133" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H133" s="6">
-        <v>400</v>
+        <v>430</v>
       </c>
     </row>
     <row outlineLevel="0" r="134">
       <c r="A134" s="4" t="inlineStr">
         <is>
-          <t>225/55R16</t>
+          <t>225/55R17RF</t>
         </is>
       </c>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C134" s="4" t="inlineStr">
         <is>
-          <t>DL225/55R16</t>
+          <t>GD225/55R17RF</t>
         </is>
       </c>
       <c r="D134" s="5">
         <v>5</v>
       </c>
       <c r="E134" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F134" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G134" s="5">
         <v>0</v>
       </c>
       <c r="H134" s="6">
-        <v>450</v>
+        <v>700</v>
       </c>
     </row>
     <row outlineLevel="0" r="135">
       <c r="A135" s="4" t="inlineStr">
         <is>
-          <t>225/55R16</t>
+          <t>225/55R18</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>GD225/55R16</t>
+          <t>HK225/55R18</t>
         </is>
       </c>
       <c r="D135" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E135" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F135" s="5">
         <v>0</v>
@@ -4836,30 +4836,30 @@
         <v>0</v>
       </c>
       <c r="H135" s="6">
-        <v>420</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="136">
       <c r="A136" s="4" t="inlineStr">
         <is>
-          <t>225/55R17</t>
+          <t>225/55R18</t>
         </is>
       </c>
       <c r="B136" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>KUMHO</t>
         </is>
       </c>
       <c r="C136" s="4" t="inlineStr">
         <is>
-          <t>HK225/55R17</t>
+          <t>KM225/55R18</t>
         </is>
       </c>
       <c r="D136" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E136" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F136" s="5">
         <v>0</v>
@@ -4868,62 +4868,62 @@
         <v>0</v>
       </c>
       <c r="H136" s="6">
-        <v>430</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="137">
       <c r="A137" s="4" t="inlineStr">
         <is>
-          <t>225/55R17RF</t>
+          <t>225/55R19</t>
         </is>
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>GD225/55R17RF</t>
+          <t>BR225/55R19</t>
         </is>
       </c>
       <c r="D137" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E137" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F137" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G137" s="5">
         <v>0</v>
       </c>
       <c r="H137" s="6">
-        <v>700</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="138">
       <c r="A138" s="4" t="inlineStr">
         <is>
-          <t>225/55R18</t>
+          <t>225/55R19</t>
         </is>
       </c>
       <c r="B138" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C138" s="4" t="inlineStr">
         <is>
-          <t>HK225/55R18</t>
+          <t>GD225/55R19</t>
         </is>
       </c>
       <c r="D138" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E138" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F138" s="5">
         <v>0</v>
@@ -4932,27 +4932,27 @@
         <v>0</v>
       </c>
       <c r="H138" s="6">
-        <v>500</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="139">
       <c r="A139" s="4" t="inlineStr">
         <is>
-          <t>225/55R18</t>
+          <t>225/60R17</t>
         </is>
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>KUMHO</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>KM225/55R18</t>
+          <t>HK225/60R17</t>
         </is>
       </c>
       <c r="D139" s="5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E139" s="5">
         <v>4</v>
@@ -4961,26 +4961,26 @@
         <v>0</v>
       </c>
       <c r="G139" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H139" s="6">
-        <v>450</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="140">
       <c r="A140" s="4" t="inlineStr">
         <is>
-          <t>225/55R19</t>
+          <t>225/60R18</t>
         </is>
       </c>
       <c r="B140" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C140" s="4" t="inlineStr">
         <is>
-          <t>BR225/55R19</t>
+          <t>GD225/60R18</t>
         </is>
       </c>
       <c r="D140" s="5">
@@ -4996,30 +4996,30 @@
         <v>0</v>
       </c>
       <c r="H140" s="6">
-        <v>750</v>
+        <v>700</v>
       </c>
     </row>
     <row outlineLevel="0" r="141">
       <c r="A141" s="4" t="inlineStr">
         <is>
-          <t>225/55R19</t>
+          <t>225/65R17</t>
         </is>
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>GD225/55R19</t>
+          <t>RD225/65R17</t>
         </is>
       </c>
       <c r="D141" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E141" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F141" s="5">
         <v>0</v>
@@ -5028,77 +5028,77 @@
         <v>0</v>
       </c>
       <c r="H141" s="6">
-        <v>750</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="142">
       <c r="A142" s="4" t="inlineStr">
         <is>
-          <t>225/60R17</t>
+          <t>225/70R15C</t>
         </is>
       </c>
       <c r="B142" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>MATADOR</t>
         </is>
       </c>
       <c r="C142" s="4" t="inlineStr">
         <is>
-          <t>HK225/60R17</t>
+          <t>MT225/70R15C</t>
         </is>
       </c>
       <c r="D142" s="5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E142" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F142" s="5">
         <v>0</v>
       </c>
       <c r="G142" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H142" s="6">
-        <v>400</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="143">
       <c r="A143" s="4" t="inlineStr">
         <is>
-          <t>225/60R18</t>
+          <t>225/75R15C</t>
         </is>
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>GD225/60R18</t>
+          <t>RD225/75R15C</t>
         </is>
       </c>
       <c r="D143" s="5">
         <v>1</v>
       </c>
       <c r="E143" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F143" s="5">
         <v>0</v>
       </c>
       <c r="G143" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H143" s="6">
-        <v>700</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="144">
       <c r="A144" s="4" t="inlineStr">
         <is>
-          <t>225/65R17</t>
+          <t>235/35R19</t>
         </is>
       </c>
       <c r="B144" s="4" t="inlineStr">
@@ -5108,125 +5108,125 @@
       </c>
       <c r="C144" s="4" t="inlineStr">
         <is>
-          <t>RD225/65R17</t>
+          <t>RD235/35R19</t>
         </is>
       </c>
       <c r="D144" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E144" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F144" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G144" s="5">
         <v>0</v>
       </c>
       <c r="H144" s="6">
-        <v>450</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="145">
       <c r="A145" s="4" t="inlineStr">
         <is>
-          <t>225/70R15C</t>
+          <t>235/40R19</t>
         </is>
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>MATADOR</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>MT225/70R15C</t>
+          <t>GD235/40R19</t>
         </is>
       </c>
       <c r="D145" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E145" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F145" s="5">
         <v>0</v>
       </c>
       <c r="G145" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H145" s="6">
-        <v>450</v>
+        <v>850</v>
       </c>
     </row>
     <row outlineLevel="0" r="146">
       <c r="A146" s="4" t="inlineStr">
         <is>
-          <t>225/75R15C</t>
+          <t>235/45R18</t>
         </is>
       </c>
       <c r="B146" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C146" s="4" t="inlineStr">
         <is>
-          <t>RD225/75R15C</t>
+          <t>GD235/45R18</t>
         </is>
       </c>
       <c r="D146" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E146" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F146" s="5">
         <v>0</v>
       </c>
       <c r="G146" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H146" s="6">
-        <v>330</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="147">
       <c r="A147" s="4" t="inlineStr">
         <is>
-          <t>235/35R19</t>
+          <t>235/50R18</t>
         </is>
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>RD235/35R19</t>
+          <t>HK235/50R18</t>
         </is>
       </c>
       <c r="D147" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E147" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F147" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G147" s="5">
         <v>0</v>
       </c>
       <c r="H147" s="6">
-        <v>600</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="148">
       <c r="A148" s="4" t="inlineStr">
         <is>
-          <t>235/40R19</t>
+          <t>235/50R19</t>
         </is>
       </c>
       <c r="B148" s="4" t="inlineStr">
@@ -5236,14 +5236,14 @@
       </c>
       <c r="C148" s="4" t="inlineStr">
         <is>
-          <t>GD235/40R19</t>
+          <t>GD235/50R19</t>
         </is>
       </c>
       <c r="D148" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E148" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F148" s="5">
         <v>0</v>
@@ -5252,13 +5252,13 @@
         <v>0</v>
       </c>
       <c r="H148" s="6">
-        <v>850</v>
+        <v>800</v>
       </c>
     </row>
     <row outlineLevel="0" r="149">
       <c r="A149" s="4" t="inlineStr">
         <is>
-          <t>235/45R18</t>
+          <t>235/50R20</t>
         </is>
       </c>
       <c r="B149" s="4" t="inlineStr">
@@ -5268,39 +5268,39 @@
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>GD235/45R18</t>
+          <t>GD235/50R20</t>
         </is>
       </c>
       <c r="D149" s="5">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E149" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F149" s="5">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G149" s="5">
         <v>0</v>
       </c>
       <c r="H149" s="6">
-        <v>600</v>
+        <v>1180</v>
       </c>
     </row>
     <row outlineLevel="0" r="150">
       <c r="A150" s="4" t="inlineStr">
         <is>
-          <t>235/50R18</t>
+          <t>235/55R17</t>
         </is>
       </c>
       <c r="B150" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C150" s="4" t="inlineStr">
         <is>
-          <t>HK235/50R18</t>
+          <t>BR235/55R17</t>
         </is>
       </c>
       <c r="D150" s="5">
@@ -5316,30 +5316,30 @@
         <v>0</v>
       </c>
       <c r="H150" s="6">
-        <v>500</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="151">
       <c r="A151" s="4" t="inlineStr">
         <is>
-          <t>235/50R19</t>
+          <t>235/55R18</t>
         </is>
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>GD235/50R19</t>
+          <t>HK235/55R18</t>
         </is>
       </c>
       <c r="D151" s="5">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E151" s="5">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F151" s="5">
         <v>0</v>
@@ -5348,13 +5348,13 @@
         <v>0</v>
       </c>
       <c r="H151" s="6">
-        <v>800</v>
+        <v>480</v>
       </c>
     </row>
     <row outlineLevel="0" r="152">
       <c r="A152" s="4" t="inlineStr">
         <is>
-          <t>235/50R20</t>
+          <t>235/55R19</t>
         </is>
       </c>
       <c r="B152" s="4" t="inlineStr">
@@ -5364,46 +5364,46 @@
       </c>
       <c r="C152" s="4" t="inlineStr">
         <is>
-          <t>GD235/50R20</t>
+          <t>GD235/55R19</t>
         </is>
       </c>
       <c r="D152" s="5">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E152" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F152" s="5">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G152" s="5">
         <v>0</v>
       </c>
       <c r="H152" s="6">
-        <v>1180</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="153">
       <c r="A153" s="4" t="inlineStr">
         <is>
-          <t>235/55R17</t>
+          <t>235/55R19</t>
         </is>
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>BR235/55R17</t>
+          <t>HK235/55R19</t>
         </is>
       </c>
       <c r="D153" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E153" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F153" s="5">
         <v>0</v>
@@ -5412,30 +5412,30 @@
         <v>0</v>
       </c>
       <c r="H153" s="6">
-        <v>450</v>
+        <v>630</v>
       </c>
     </row>
     <row outlineLevel="0" r="154">
       <c r="A154" s="4" t="inlineStr">
         <is>
-          <t>235/55R18</t>
+          <t>235/55R19</t>
         </is>
       </c>
       <c r="B154" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C154" s="4" t="inlineStr">
         <is>
-          <t>HK235/55R18</t>
+          <t>LF235/55R19</t>
         </is>
       </c>
       <c r="D154" s="5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E154" s="5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F154" s="5">
         <v>0</v>
@@ -5444,7 +5444,7 @@
         <v>0</v>
       </c>
       <c r="H154" s="6">
-        <v>480</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="155">
@@ -5455,12 +5455,12 @@
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>GD235/55R19</t>
+          <t>NX235/55R19</t>
         </is>
       </c>
       <c r="D155" s="5">
@@ -5476,7 +5476,7 @@
         <v>0</v>
       </c>
       <c r="H155" s="6">
-        <v>750</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="156">
@@ -5487,51 +5487,51 @@
       </c>
       <c r="B156" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C156" s="4" t="inlineStr">
         <is>
-          <t>HK235/55R19</t>
+          <t>RD235/55R19</t>
         </is>
       </c>
       <c r="D156" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E156" s="5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F156" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G156" s="5">
         <v>0</v>
       </c>
       <c r="H156" s="6">
-        <v>630</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="157">
       <c r="A157" s="4" t="inlineStr">
         <is>
-          <t>235/55R19</t>
+          <t>235/60R16</t>
         </is>
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>LF235/55R19</t>
+          <t>HK235/60R16</t>
         </is>
       </c>
       <c r="D157" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E157" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F157" s="5">
         <v>0</v>
@@ -5540,77 +5540,77 @@
         <v>0</v>
       </c>
       <c r="H157" s="6">
-        <v>500</v>
+        <v>430</v>
       </c>
     </row>
     <row outlineLevel="0" r="158">
       <c r="A158" s="4" t="inlineStr">
         <is>
-          <t>235/55R19</t>
+          <t>235/60R17</t>
         </is>
       </c>
       <c r="B158" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C158" s="4" t="inlineStr">
         <is>
-          <t>NX235/55R19</t>
+          <t>HK235/60R17</t>
         </is>
       </c>
       <c r="D158" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E158" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F158" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G158" s="5">
         <v>0</v>
       </c>
       <c r="H158" s="6">
-        <v>600</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="159">
       <c r="A159" s="4" t="inlineStr">
         <is>
-          <t>235/55R19</t>
+          <t>235/60R18</t>
         </is>
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>RD235/55R19</t>
+          <t>GD235/60R18</t>
         </is>
       </c>
       <c r="D159" s="5">
         <v>2</v>
       </c>
       <c r="E159" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F159" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G159" s="5">
         <v>0</v>
       </c>
       <c r="H159" s="6">
-        <v>500</v>
+        <v>680</v>
       </c>
     </row>
     <row outlineLevel="0" r="160">
       <c r="A160" s="4" t="inlineStr">
         <is>
-          <t>235/60R16</t>
+          <t>235/60R18</t>
         </is>
       </c>
       <c r="B160" s="4" t="inlineStr">
@@ -5620,14 +5620,14 @@
       </c>
       <c r="C160" s="4" t="inlineStr">
         <is>
-          <t>HK235/60R16</t>
+          <t>HK235/60R18</t>
         </is>
       </c>
       <c r="D160" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E160" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F160" s="5">
         <v>0</v>
@@ -5636,45 +5636,45 @@
         <v>0</v>
       </c>
       <c r="H160" s="6">
-        <v>430</v>
+        <v>550</v>
       </c>
     </row>
     <row outlineLevel="0" r="161">
       <c r="A161" s="4" t="inlineStr">
         <is>
-          <t>235/60R17</t>
+          <t>245/40R17</t>
         </is>
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>HK235/60R17</t>
+          <t>GD245/40R17</t>
         </is>
       </c>
       <c r="D161" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E161" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F161" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G161" s="5">
         <v>0</v>
       </c>
       <c r="H161" s="6">
-        <v>500</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="162">
       <c r="A162" s="4" t="inlineStr">
         <is>
-          <t>235/60R18</t>
+          <t>245/40R18</t>
         </is>
       </c>
       <c r="B162" s="4" t="inlineStr">
@@ -5684,11 +5684,11 @@
       </c>
       <c r="C162" s="4" t="inlineStr">
         <is>
-          <t>GD235/60R18</t>
+          <t>GD245/40R18</t>
         </is>
       </c>
       <c r="D162" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E162" s="5">
         <v>2</v>
@@ -5697,16 +5697,16 @@
         <v>0</v>
       </c>
       <c r="G162" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H162" s="6">
-        <v>680</v>
+        <v>620</v>
       </c>
     </row>
     <row outlineLevel="0" r="163">
       <c r="A163" s="4" t="inlineStr">
         <is>
-          <t>235/60R18</t>
+          <t>245/40R19</t>
         </is>
       </c>
       <c r="B163" s="4" t="inlineStr">
@@ -5716,14 +5716,14 @@
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>HK235/60R18</t>
+          <t>HK245/40R19</t>
         </is>
       </c>
       <c r="D163" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E163" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F163" s="5">
         <v>0</v>
@@ -5732,94 +5732,94 @@
         <v>0</v>
       </c>
       <c r="H163" s="6">
-        <v>550</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="164">
       <c r="A164" s="4" t="inlineStr">
         <is>
-          <t>245/40R17</t>
+          <t>245/40R20</t>
         </is>
       </c>
       <c r="B164" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C164" s="4" t="inlineStr">
         <is>
-          <t>GD245/40R17</t>
+          <t>CT245/40R20</t>
         </is>
       </c>
       <c r="D164" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E164" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F164" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G164" s="5">
         <v>0</v>
       </c>
       <c r="H164" s="6">
-        <v>400</v>
+        <v>1050</v>
       </c>
     </row>
     <row outlineLevel="0" r="165">
       <c r="A165" s="4" t="inlineStr">
         <is>
-          <t>245/40R18</t>
+          <t>245/45R17</t>
         </is>
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>GD245/40R18</t>
+          <t>HK245/45R17</t>
         </is>
       </c>
       <c r="D165" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E165" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F165" s="5">
         <v>0</v>
       </c>
       <c r="G165" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H165" s="6">
-        <v>620</v>
+        <v>430</v>
       </c>
     </row>
     <row outlineLevel="0" r="166">
       <c r="A166" s="4" t="inlineStr">
         <is>
-          <t>245/40R19</t>
+          <t>245/45R18</t>
         </is>
       </c>
       <c r="B166" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C166" s="4" t="inlineStr">
         <is>
-          <t>HK245/40R19</t>
+          <t>CT245/45R18</t>
         </is>
       </c>
       <c r="D166" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E166" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F166" s="5">
         <v>0</v>
@@ -5828,45 +5828,45 @@
         <v>0</v>
       </c>
       <c r="H166" s="6">
-        <v>750</v>
+        <v>650</v>
       </c>
     </row>
     <row outlineLevel="0" r="167">
       <c r="A167" s="4" t="inlineStr">
         <is>
-          <t>245/40R20</t>
+          <t>245/45R18</t>
         </is>
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>CT245/40R20</t>
+          <t>GD245/45R18</t>
         </is>
       </c>
       <c r="D167" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E167" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F167" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G167" s="5">
         <v>0</v>
       </c>
       <c r="H167" s="6">
-        <v>1050</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="168">
       <c r="A168" s="4" t="inlineStr">
         <is>
-          <t>245/45R17</t>
+          <t>245/45R18</t>
         </is>
       </c>
       <c r="B168" s="4" t="inlineStr">
@@ -5876,14 +5876,14 @@
       </c>
       <c r="C168" s="4" t="inlineStr">
         <is>
-          <t>HK245/45R17</t>
+          <t>HK245/45R18</t>
         </is>
       </c>
       <c r="D168" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E168" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F168" s="5">
         <v>0</v>
@@ -5892,30 +5892,30 @@
         <v>0</v>
       </c>
       <c r="H168" s="6">
-        <v>430</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="169">
       <c r="A169" s="4" t="inlineStr">
         <is>
-          <t>245/45R18</t>
+          <t>245/45R18RF</t>
         </is>
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>CT245/45R18</t>
+          <t>GD245/45R18RF</t>
         </is>
       </c>
       <c r="D169" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E169" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F169" s="5">
         <v>0</v>
@@ -5924,30 +5924,30 @@
         <v>0</v>
       </c>
       <c r="H169" s="6">
-        <v>650</v>
+        <v>720</v>
       </c>
     </row>
     <row outlineLevel="0" r="170">
       <c r="A170" s="4" t="inlineStr">
         <is>
-          <t>245/45R18</t>
+          <t>245/45R19</t>
         </is>
       </c>
       <c r="B170" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C170" s="4" t="inlineStr">
         <is>
-          <t>GD245/45R18</t>
+          <t>BR245/45R19</t>
         </is>
       </c>
       <c r="D170" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E170" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F170" s="5">
         <v>0</v>
@@ -5956,269 +5956,269 @@
         <v>0</v>
       </c>
       <c r="H170" s="6">
-        <v>600</v>
+        <v>790</v>
       </c>
     </row>
     <row outlineLevel="0" r="171">
       <c r="A171" s="4" t="inlineStr">
         <is>
-          <t>245/45R18</t>
+          <t>245/45R19</t>
         </is>
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t>HK245/45R18</t>
+          <t>RD245/45R19</t>
         </is>
       </c>
       <c r="D171" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E171" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F171" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G171" s="5">
         <v>0</v>
       </c>
       <c r="H171" s="6">
-        <v>500</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="172">
       <c r="A172" s="4" t="inlineStr">
         <is>
-          <t>245/45R18RF</t>
+          <t>245/45R20</t>
         </is>
       </c>
       <c r="B172" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C172" s="4" t="inlineStr">
         <is>
-          <t>GD245/45R18RF</t>
+          <t>HK245/45R20</t>
         </is>
       </c>
       <c r="D172" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E172" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F172" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G172" s="5">
         <v>0</v>
       </c>
       <c r="H172" s="6">
-        <v>720</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="173">
       <c r="A173" s="4" t="inlineStr">
         <is>
-          <t>245/45R19</t>
+          <t>245/65R17</t>
         </is>
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>BR245/45R19</t>
+          <t>NX245/65R17</t>
         </is>
       </c>
       <c r="D173" s="5">
         <v>4</v>
       </c>
       <c r="E173" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F173" s="5">
         <v>0</v>
       </c>
       <c r="G173" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H173" s="6">
-        <v>790</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="174">
       <c r="A174" s="4" t="inlineStr">
         <is>
-          <t>245/45R19</t>
+          <t>255/35R19</t>
         </is>
       </c>
       <c r="B174" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C174" s="4" t="inlineStr">
         <is>
-          <t>RD245/45R19</t>
+          <t>DL255/35R19</t>
         </is>
       </c>
       <c r="D174" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E174" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F174" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G174" s="5">
         <v>0</v>
       </c>
       <c r="H174" s="6">
-        <v>450</v>
+        <v>700</v>
       </c>
     </row>
     <row outlineLevel="0" r="175">
       <c r="A175" s="4" t="inlineStr">
         <is>
-          <t>245/45R20</t>
+          <t>255/35R19RF</t>
         </is>
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>HK245/45R20</t>
+          <t>CT255/35R19RF</t>
         </is>
       </c>
       <c r="D175" s="5">
         <v>2</v>
       </c>
       <c r="E175" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F175" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G175" s="5">
         <v>0</v>
       </c>
       <c r="H175" s="6">
-        <v>750</v>
+        <v>950</v>
       </c>
     </row>
     <row outlineLevel="0" r="176">
       <c r="A176" s="4" t="inlineStr">
         <is>
-          <t>245/65R17</t>
+          <t>255/35R19RF</t>
         </is>
       </c>
       <c r="B176" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C176" s="4" t="inlineStr">
         <is>
-          <t>NX245/65R17</t>
+          <t>GD255/35R19RF</t>
         </is>
       </c>
       <c r="D176" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E176" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F176" s="5">
         <v>0</v>
       </c>
       <c r="G176" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H176" s="6">
-        <v>600</v>
+        <v>950</v>
       </c>
     </row>
     <row outlineLevel="0" r="177">
       <c r="A177" s="4" t="inlineStr">
         <is>
-          <t>245/70R16</t>
+          <t>255/50R19</t>
         </is>
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>LASSA</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>LS245/70R16</t>
+          <t>CT255/50R19</t>
         </is>
       </c>
       <c r="D177" s="5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E177" s="5">
         <v>0</v>
       </c>
       <c r="F177" s="5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G177" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H177" s="6">
-        <v>500</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="178">
       <c r="A178" s="4" t="inlineStr">
         <is>
-          <t>255/35R19</t>
+          <t>255/50R20</t>
         </is>
       </c>
       <c r="B178" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C178" s="4" t="inlineStr">
         <is>
-          <t>DL255/35R19</t>
+          <t>CT255/50R20</t>
         </is>
       </c>
       <c r="D178" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E178" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F178" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G178" s="5">
         <v>0</v>
       </c>
       <c r="H178" s="6">
-        <v>700</v>
+        <v>900</v>
       </c>
     </row>
     <row outlineLevel="0" r="179">
       <c r="A179" s="4" t="inlineStr">
         <is>
-          <t>255/35R19RF</t>
+          <t>255/55R19</t>
         </is>
       </c>
       <c r="B179" s="4" t="inlineStr">
@@ -6228,46 +6228,46 @@
       </c>
       <c r="C179" s="4" t="inlineStr">
         <is>
-          <t>CT255/35R19RF</t>
+          <t>CT255/55R19</t>
         </is>
       </c>
       <c r="D179" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E179" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F179" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G179" s="5">
         <v>0</v>
       </c>
       <c r="H179" s="6">
-        <v>950</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="180">
       <c r="A180" s="4" t="inlineStr">
         <is>
-          <t>255/35R19RF</t>
+          <t>255/55R19</t>
         </is>
       </c>
       <c r="B180" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C180" s="4" t="inlineStr">
         <is>
-          <t>GD255/35R19RF</t>
+          <t>DL255/55R19</t>
         </is>
       </c>
       <c r="D180" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E180" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F180" s="5">
         <v>0</v>
@@ -6276,119 +6276,119 @@
         <v>0</v>
       </c>
       <c r="H180" s="6">
-        <v>950</v>
+        <v>700</v>
       </c>
     </row>
     <row outlineLevel="0" r="181">
       <c r="A181" s="4" t="inlineStr">
         <is>
-          <t>255/50R19</t>
+          <t>255/70R16</t>
         </is>
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C181" s="4" t="inlineStr">
         <is>
-          <t>CT255/50R19</t>
+          <t>RD255/70R16</t>
         </is>
       </c>
       <c r="D181" s="5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E181" s="5">
         <v>0</v>
       </c>
       <c r="F181" s="5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G181" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H181" s="6">
-        <v>750</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="182">
       <c r="A182" s="4" t="inlineStr">
         <is>
-          <t>255/50R20</t>
+          <t>265/35R18</t>
         </is>
       </c>
       <c r="B182" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C182" s="4" t="inlineStr">
         <is>
-          <t>CT255/50R20</t>
+          <t>GD265/35R18</t>
         </is>
       </c>
       <c r="D182" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E182" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F182" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G182" s="5">
         <v>0</v>
       </c>
       <c r="H182" s="6">
-        <v>900</v>
+        <v>700</v>
       </c>
     </row>
     <row outlineLevel="0" r="183">
       <c r="A183" s="4" t="inlineStr">
         <is>
-          <t>255/55R19</t>
+          <t>265/50R20</t>
         </is>
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C183" s="4" t="inlineStr">
         <is>
-          <t>CT255/55R19</t>
+          <t>GD265/50R20</t>
         </is>
       </c>
       <c r="D183" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E183" s="5">
         <v>0</v>
       </c>
       <c r="F183" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G183" s="5">
         <v>0</v>
       </c>
       <c r="H183" s="6">
-        <v>750</v>
+        <v>1150</v>
       </c>
     </row>
     <row outlineLevel="0" r="184">
       <c r="A184" s="4" t="inlineStr">
         <is>
-          <t>255/55R19</t>
+          <t>275/35R19RF</t>
         </is>
       </c>
       <c r="B184" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C184" s="4" t="inlineStr">
         <is>
-          <t>DL255/55R19</t>
+          <t>GD275/35R19RF</t>
         </is>
       </c>
       <c r="D184" s="5">
@@ -6404,77 +6404,77 @@
         <v>0</v>
       </c>
       <c r="H184" s="6">
-        <v>700</v>
+        <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="185">
       <c r="A185" s="4" t="inlineStr">
         <is>
-          <t>255/70R16</t>
+          <t>275/35R20</t>
         </is>
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C185" s="4" t="inlineStr">
         <is>
-          <t>RD255/70R16</t>
+          <t>CT275/35R20</t>
         </is>
       </c>
       <c r="D185" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E185" s="5">
         <v>0</v>
       </c>
       <c r="F185" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G185" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H185" s="6">
-        <v>500</v>
+        <v>980</v>
       </c>
     </row>
     <row outlineLevel="0" r="186">
       <c r="A186" s="4" t="inlineStr">
         <is>
-          <t>265/35R18</t>
+          <t>275/40R20</t>
         </is>
       </c>
       <c r="B186" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C186" s="4" t="inlineStr">
         <is>
-          <t>GD265/35R18</t>
+          <t>HK275/40R20</t>
         </is>
       </c>
       <c r="D186" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E186" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F186" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G186" s="5">
         <v>0</v>
       </c>
       <c r="H186" s="6">
-        <v>700</v>
+        <v>770</v>
       </c>
     </row>
     <row outlineLevel="0" r="187">
       <c r="A187" s="4" t="inlineStr">
         <is>
-          <t>265/50R20</t>
+          <t>275/50R21</t>
         </is>
       </c>
       <c r="B187" s="4" t="inlineStr">
@@ -6484,81 +6484,81 @@
       </c>
       <c r="C187" s="4" t="inlineStr">
         <is>
-          <t>GD265/50R20</t>
+          <t>GD275/50R21</t>
         </is>
       </c>
       <c r="D187" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E187" s="5">
         <v>0</v>
       </c>
       <c r="F187" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G187" s="5">
         <v>0</v>
       </c>
       <c r="H187" s="6">
-        <v>1150</v>
+        <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="188">
       <c r="A188" s="4" t="inlineStr">
         <is>
-          <t>275/35R19RF</t>
+          <t>295/35R21</t>
         </is>
       </c>
       <c r="B188" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C188" s="4" t="inlineStr">
         <is>
-          <t>GD275/35R19RF</t>
+          <t>CT295/35R21</t>
         </is>
       </c>
       <c r="D188" s="5">
         <v>2</v>
       </c>
       <c r="E188" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F188" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G188" s="5">
         <v>0</v>
       </c>
       <c r="H188" s="6">
-        <v>1</v>
+        <v>1150</v>
       </c>
     </row>
     <row outlineLevel="0" r="189">
       <c r="A189" s="4" t="inlineStr">
         <is>
-          <t>275/35R20</t>
+          <t>295/35R21</t>
         </is>
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C189" s="4" t="inlineStr">
         <is>
-          <t>CT275/35R20</t>
+          <t>GD295/35R21</t>
         </is>
       </c>
       <c r="D189" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E189" s="5">
         <v>0</v>
       </c>
       <c r="F189" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G189" s="5">
         <v>0</v>
@@ -6570,160 +6570,32 @@
     <row outlineLevel="0" r="190">
       <c r="A190" s="4" t="inlineStr">
         <is>
-          <t>275/40R20</t>
+          <t>500R12</t>
         </is>
       </c>
       <c r="B190" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C190" s="4" t="inlineStr">
         <is>
-          <t>HK275/40R20</t>
+          <t>RD500R12</t>
         </is>
       </c>
       <c r="D190" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E190" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F190" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G190" s="5">
         <v>0</v>
       </c>
       <c r="H190" s="6">
-        <v>770</v>
-      </c>
-    </row>
-    <row outlineLevel="0" r="191">
-      <c r="A191" s="4" t="inlineStr">
-        <is>
-          <t>275/50R21</t>
-        </is>
-      </c>
-      <c r="B191" s="4" t="inlineStr">
-        <is>
-          <t>GOODYEAR</t>
-        </is>
-      </c>
-      <c r="C191" s="4" t="inlineStr">
-        <is>
-          <t>GD275/50R21</t>
-        </is>
-      </c>
-      <c r="D191" s="5">
-        <v>2</v>
-      </c>
-      <c r="E191" s="5">
-        <v>0</v>
-      </c>
-      <c r="F191" s="5">
-        <v>2</v>
-      </c>
-      <c r="G191" s="5">
-        <v>0</v>
-      </c>
-      <c r="H191" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row outlineLevel="0" r="192">
-      <c r="A192" s="4" t="inlineStr">
-        <is>
-          <t>295/35R21</t>
-        </is>
-      </c>
-      <c r="B192" s="4" t="inlineStr">
-        <is>
-          <t>CONTINENTAL</t>
-        </is>
-      </c>
-      <c r="C192" s="4" t="inlineStr">
-        <is>
-          <t>CT295/35R21</t>
-        </is>
-      </c>
-      <c r="D192" s="5">
-        <v>2</v>
-      </c>
-      <c r="E192" s="5">
-        <v>0</v>
-      </c>
-      <c r="F192" s="5">
-        <v>2</v>
-      </c>
-      <c r="G192" s="5">
-        <v>0</v>
-      </c>
-      <c r="H192" s="6">
-        <v>1150</v>
-      </c>
-    </row>
-    <row outlineLevel="0" r="193">
-      <c r="A193" s="4" t="inlineStr">
-        <is>
-          <t>295/35R21</t>
-        </is>
-      </c>
-      <c r="B193" s="4" t="inlineStr">
-        <is>
-          <t>GOODYEAR</t>
-        </is>
-      </c>
-      <c r="C193" s="4" t="inlineStr">
-        <is>
-          <t>GD295/35R21</t>
-        </is>
-      </c>
-      <c r="D193" s="5">
-        <v>3</v>
-      </c>
-      <c r="E193" s="5">
-        <v>0</v>
-      </c>
-      <c r="F193" s="5">
-        <v>3</v>
-      </c>
-      <c r="G193" s="5">
-        <v>0</v>
-      </c>
-      <c r="H193" s="6">
-        <v>980</v>
-      </c>
-    </row>
-    <row outlineLevel="0" r="194">
-      <c r="A194" s="4" t="inlineStr">
-        <is>
-          <t>500R12</t>
-        </is>
-      </c>
-      <c r="B194" s="4" t="inlineStr">
-        <is>
-          <t>RADIAL</t>
-        </is>
-      </c>
-      <c r="C194" s="4" t="inlineStr">
-        <is>
-          <t>RD500R12</t>
-        </is>
-      </c>
-      <c r="D194" s="5">
-        <v>3</v>
-      </c>
-      <c r="E194" s="5">
-        <v>3</v>
-      </c>
-      <c r="F194" s="5">
-        <v>0</v>
-      </c>
-      <c r="G194" s="5">
-        <v>0</v>
-      </c>
-      <c r="H194" s="6">
         <v>300</v>
       </c>
     </row>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -496,7 +496,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H190"/>
+  <dimension ref="A1:H191"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col customWidth="true" min="1" max="1" width="13.8359375"/>
@@ -600,7 +600,7 @@
         </is>
       </c>
       <c r="D3" s="5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E3" s="5">
         <v>5</v>
@@ -609,7 +609,7 @@
         <v>0</v>
       </c>
       <c r="G3" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H3" s="6">
         <v>180</v>
@@ -830,10 +830,10 @@
         <v>3</v>
       </c>
       <c r="F10" s="5">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G10" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H10" s="6">
         <v>270</v>
@@ -891,10 +891,10 @@
         <v>22</v>
       </c>
       <c r="E12" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F12" s="5">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G12" s="5">
         <v>4</v>
@@ -920,13 +920,13 @@
         </is>
       </c>
       <c r="D13" s="5">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E13" s="5">
         <v>6</v>
       </c>
       <c r="F13" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G13" s="5">
         <v>4</v>
@@ -955,13 +955,13 @@
         <v>95</v>
       </c>
       <c r="E14" s="5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F14" s="5">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="G14" s="5">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H14" s="6">
         <v>220</v>
@@ -1048,16 +1048,16 @@
         </is>
       </c>
       <c r="D17" s="5">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="E17" s="5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F17" s="5">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="G17" s="5">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="H17" s="6">
         <v>190</v>
@@ -1080,16 +1080,16 @@
         </is>
       </c>
       <c r="D18" s="5">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="E18" s="5">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="F18" s="5">
         <v>0</v>
       </c>
       <c r="G18" s="5">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H18" s="6">
         <v>180</v>
@@ -1246,10 +1246,10 @@
         <v>3</v>
       </c>
       <c r="F23" s="5">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G23" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H23" s="6">
         <v>340</v>
@@ -1307,10 +1307,10 @@
         <v>19</v>
       </c>
       <c r="E25" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F25" s="5">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G25" s="5">
         <v>4</v>
@@ -1400,13 +1400,13 @@
         </is>
       </c>
       <c r="D28" s="5">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E28" s="5">
         <v>5</v>
       </c>
       <c r="F28" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G28" s="5">
         <v>5</v>
@@ -1432,10 +1432,10 @@
         </is>
       </c>
       <c r="D29" s="5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E29" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F29" s="5">
         <v>2</v>
@@ -1624,13 +1624,13 @@
         </is>
       </c>
       <c r="D35" s="5">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E35" s="5">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F35" s="5">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="G35" s="5">
         <v>4</v>
@@ -1720,13 +1720,13 @@
         </is>
       </c>
       <c r="D38" s="5">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E38" s="5">
         <v>5</v>
       </c>
       <c r="F38" s="5">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="G38" s="5">
         <v>4</v>
@@ -1819,13 +1819,13 @@
         <v>8</v>
       </c>
       <c r="E41" s="5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F41" s="5">
         <v>0</v>
       </c>
       <c r="G41" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H41" s="6">
         <v>220</v>
@@ -1886,10 +1886,10 @@
         <v>4</v>
       </c>
       <c r="F43" s="5">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G43" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H43" s="6">
         <v>260</v>
@@ -1982,10 +1982,10 @@
         <v>4</v>
       </c>
       <c r="F46" s="5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G46" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H46" s="6">
         <v>350</v>
@@ -2142,10 +2142,10 @@
         <v>4</v>
       </c>
       <c r="F51" s="5">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G51" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H51" s="6">
         <v>355</v>
@@ -2168,13 +2168,13 @@
         </is>
       </c>
       <c r="D52" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E52" s="5">
         <v>0</v>
       </c>
       <c r="F52" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G52" s="5">
         <v>0</v>
@@ -2363,13 +2363,13 @@
         <v>89</v>
       </c>
       <c r="E58" s="5">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F58" s="5">
         <v>69</v>
       </c>
       <c r="G58" s="5">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H58" s="6">
         <v>250</v>
@@ -2378,65 +2378,65 @@
     <row outlineLevel="0" r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>195/75R16C</t>
+          <t>195/70R15C</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>GOODRIDE</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>GR195/75R16C</t>
+          <t>LF195/70R15C</t>
         </is>
       </c>
       <c r="D59" s="5">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E59" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F59" s="5">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G59" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H59" s="6">
-        <v>350</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>205/45R17</t>
+          <t>195/75R16C</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>GOODRIDE</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>CT205/45R17</t>
+          <t>GR195/75R16C</t>
         </is>
       </c>
       <c r="D60" s="5">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E60" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F60" s="5">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G60" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H60" s="6">
-        <v>550</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="61">
@@ -2447,28 +2447,28 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>FULDA</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>FL205/45R17</t>
+          <t>CT205/45R17</t>
         </is>
       </c>
       <c r="D61" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E61" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F61" s="5">
         <v>0</v>
       </c>
       <c r="G61" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H61" s="6">
-        <v>380</v>
+        <v>550</v>
       </c>
     </row>
     <row outlineLevel="0" r="62">
@@ -2479,28 +2479,28 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>GOODRIDE</t>
+          <t>FULDA</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>GR205/45R17</t>
+          <t>FL205/45R17</t>
         </is>
       </c>
       <c r="D62" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E62" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F62" s="5">
         <v>0</v>
       </c>
       <c r="G62" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H62" s="6">
-        <v>300</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="63">
@@ -2511,28 +2511,28 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>GOODRIDE</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>GD205/45R17</t>
+          <t>GR205/45R17</t>
         </is>
       </c>
       <c r="D63" s="5">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="E63" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F63" s="5">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G63" s="5">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H63" s="6">
-        <v>450</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="64">
@@ -2543,28 +2543,28 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>NX205/45R17</t>
+          <t>GD205/45R17</t>
         </is>
       </c>
       <c r="D64" s="5">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="E64" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F64" s="5">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G64" s="5">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H64" s="6">
-        <v>380</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="65">
@@ -2575,83 +2575,83 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>RD205/45R17</t>
+          <t>NX205/45R17</t>
         </is>
       </c>
       <c r="D65" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E65" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F65" s="5">
         <v>0</v>
       </c>
       <c r="G65" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H65" s="6">
-        <v>300</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>205/50R17</t>
+          <t>205/45R17</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>CT205/50R17</t>
+          <t>RD205/45R17</t>
         </is>
       </c>
       <c r="D66" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E66" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F66" s="5">
         <v>0</v>
       </c>
       <c r="G66" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H66" s="6">
-        <v>450</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>205/55R16</t>
+          <t>205/50R17</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>AMINE</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>AM205/55R16</t>
+          <t>CT205/50R17</t>
         </is>
       </c>
       <c r="D67" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E67" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F67" s="5">
         <v>0</v>
@@ -2660,7 +2660,7 @@
         <v>0</v>
       </c>
       <c r="H67" s="6">
-        <v>240</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="68">
@@ -2671,28 +2671,28 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>AMINE</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>BR205/55R16</t>
+          <t>AM205/55R16</t>
         </is>
       </c>
       <c r="D68" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E68" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F68" s="5">
         <v>0</v>
       </c>
       <c r="G68" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H68" s="6">
-        <v>290</v>
+        <v>240</v>
       </c>
     </row>
     <row outlineLevel="0" r="69">
@@ -2703,28 +2703,28 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>DOUBLESTAR</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>DS205/55R16</t>
+          <t>BR205/55R16</t>
         </is>
       </c>
       <c r="D69" s="5">
         <v>4</v>
       </c>
       <c r="E69" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F69" s="5">
         <v>0</v>
       </c>
       <c r="G69" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H69" s="6">
-        <v>230</v>
+        <v>290</v>
       </c>
     </row>
     <row outlineLevel="0" r="70">
@@ -2735,28 +2735,28 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>FULDA</t>
+          <t>DOUBLESTAR</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>FL205/55R16</t>
+          <t>DS205/55R16</t>
         </is>
       </c>
       <c r="D70" s="5">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="E70" s="5">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F70" s="5">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="G70" s="5">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H70" s="6">
-        <v>250</v>
+        <v>230</v>
       </c>
     </row>
     <row outlineLevel="0" r="71">
@@ -2767,25 +2767,25 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>GOODRIDE</t>
+          <t>FULDA</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>GR205/55R16</t>
+          <t>FL205/55R16</t>
         </is>
       </c>
       <c r="D71" s="5">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="E71" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F71" s="5">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G71" s="5">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H71" s="6">
         <v>250</v>
@@ -2799,28 +2799,28 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>GOODRIDE</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>GD205/55R16</t>
+          <t>GR205/55R16</t>
         </is>
       </c>
       <c r="D72" s="5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E72" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F72" s="5">
         <v>0</v>
       </c>
       <c r="G72" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H72" s="6">
-        <v>280</v>
+        <v>250</v>
       </c>
     </row>
     <row outlineLevel="0" r="73">
@@ -2831,28 +2831,28 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>HK205/55R16</t>
+          <t>GD205/55R16</t>
         </is>
       </c>
       <c r="D73" s="5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E73" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F73" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G73" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H73" s="6">
-        <v>260</v>
+        <v>280</v>
       </c>
     </row>
     <row outlineLevel="0" r="74">
@@ -2863,48 +2863,48 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>RD205/55R16</t>
+          <t>HK205/55R16</t>
         </is>
       </c>
       <c r="D74" s="5">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E74" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F74" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G74" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H74" s="6">
-        <v>230</v>
+        <v>260</v>
       </c>
     </row>
     <row outlineLevel="0" r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>205/55R16RF</t>
+          <t>205/55R16</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>GD205/55R16RF</t>
+          <t>RD205/55R16</t>
         </is>
       </c>
       <c r="D75" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E75" s="5">
         <v>0</v>
@@ -2913,16 +2913,16 @@
         <v>0</v>
       </c>
       <c r="G75" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H75" s="6">
-        <v>480</v>
+        <v>230</v>
       </c>
     </row>
     <row outlineLevel="0" r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>205/55R17</t>
+          <t>205/55R16RF</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
@@ -2932,23 +2932,23 @@
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>GD205/55R17</t>
+          <t>GD205/55R16RF</t>
         </is>
       </c>
       <c r="D76" s="5">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="E76" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F76" s="5">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G76" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H76" s="6">
-        <v>450</v>
+        <v>480</v>
       </c>
     </row>
     <row outlineLevel="0" r="77">
@@ -2959,44 +2959,44 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>NX205/55R17</t>
+          <t>GD205/55R17</t>
         </is>
       </c>
       <c r="D77" s="5">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="E77" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F77" s="5">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G77" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H77" s="6">
-        <v>400</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>205/60R16</t>
+          <t>205/55R17</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>DL205/60R16</t>
+          <t>NX205/55R17</t>
         </is>
       </c>
       <c r="D78" s="5">
@@ -3012,7 +3012,7 @@
         <v>0</v>
       </c>
       <c r="H78" s="6">
-        <v>330</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="79">
@@ -3023,28 +3023,28 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>GD205/60R16</t>
+          <t>DL205/60R16</t>
         </is>
       </c>
       <c r="D79" s="5">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="E79" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F79" s="5">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G79" s="5">
         <v>0</v>
       </c>
       <c r="H79" s="6">
-        <v>380</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="80">
@@ -3055,28 +3055,28 @@
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>HK205/60R16</t>
+          <t>GD205/60R16</t>
         </is>
       </c>
       <c r="D80" s="5">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E80" s="5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F80" s="5">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="G80" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H80" s="6">
-        <v>300</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="81">
@@ -3087,25 +3087,25 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>LF205/60R16</t>
+          <t>HK205/60R16</t>
         </is>
       </c>
       <c r="D81" s="5">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E81" s="5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F81" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G81" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H81" s="6">
         <v>300</v>
@@ -3114,17 +3114,17 @@
     <row outlineLevel="0" r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>205/65R15</t>
+          <t>205/60R16</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>HK205/65R15</t>
+          <t>LF205/60R16</t>
         </is>
       </c>
       <c r="D82" s="5">
@@ -3140,30 +3140,30 @@
         <v>0</v>
       </c>
       <c r="H82" s="6">
-        <v>270</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>205/65R16</t>
+          <t>205/65R15</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>BR205/65R16</t>
+          <t>HK205/65R15</t>
         </is>
       </c>
       <c r="D83" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E83" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F83" s="5">
         <v>0</v>
@@ -3172,7 +3172,7 @@
         <v>0</v>
       </c>
       <c r="H83" s="6">
-        <v>420</v>
+        <v>270</v>
       </c>
     </row>
     <row outlineLevel="0" r="84">
@@ -3183,19 +3183,19 @@
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>HK205/65R16</t>
+          <t>BR205/65R16</t>
         </is>
       </c>
       <c r="D84" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E84" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F84" s="5">
         <v>0</v>
@@ -3204,39 +3204,39 @@
         <v>0</v>
       </c>
       <c r="H84" s="6">
-        <v>380</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>215/40R18</t>
+          <t>205/65R16</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>GD215/40R18</t>
+          <t>HK205/65R16</t>
         </is>
       </c>
       <c r="D85" s="5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E85" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F85" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G85" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H85" s="6">
-        <v>600</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="86">
@@ -3247,44 +3247,44 @@
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>HK215/40R18</t>
+          <t>GD215/40R18</t>
         </is>
       </c>
       <c r="D86" s="5">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E86" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F86" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G86" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H86" s="6">
-        <v>490</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>215/45R16</t>
+          <t>215/40R18</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>GD215/45R16</t>
+          <t>HK215/40R18</t>
         </is>
       </c>
       <c r="D87" s="5">
@@ -3300,13 +3300,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="6">
-        <v>450</v>
+        <v>490</v>
       </c>
     </row>
     <row outlineLevel="0" r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>215/45R17</t>
+          <t>215/45R16</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
@@ -3316,14 +3316,14 @@
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>GD215/45R17</t>
+          <t>GD215/45R16</t>
         </is>
       </c>
       <c r="D88" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E88" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F88" s="5">
         <v>0</v>
@@ -3332,7 +3332,7 @@
         <v>0</v>
       </c>
       <c r="H88" s="6">
-        <v>400</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="89">
@@ -3343,25 +3343,25 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>HK215/45R17</t>
+          <t>GD215/45R17</t>
         </is>
       </c>
       <c r="D89" s="5">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="E89" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F89" s="5">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G89" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H89" s="6">
         <v>400</v>
@@ -3375,28 +3375,28 @@
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>IRIS</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>IR215/45R17</t>
+          <t>HK215/45R17</t>
         </is>
       </c>
       <c r="D90" s="5">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E90" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F90" s="5">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G90" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H90" s="6">
-        <v>300</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="91">
@@ -3407,28 +3407,28 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>IRIS</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>LF215/45R17</t>
+          <t>IR215/45R17</t>
         </is>
       </c>
       <c r="D91" s="5">
         <v>1</v>
       </c>
       <c r="E91" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F91" s="5">
         <v>0</v>
       </c>
       <c r="G91" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H91" s="6">
-        <v>350</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="92">
@@ -3439,83 +3439,83 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>NX215/45R17</t>
+          <t>LF215/45R17</t>
         </is>
       </c>
       <c r="D92" s="5">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E92" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F92" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G92" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H92" s="6">
-        <v>380</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>215/45R18</t>
+          <t>215/45R17</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>GD215/45R18</t>
+          <t>NX215/45R17</t>
         </is>
       </c>
       <c r="D93" s="5">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E93" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F93" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G93" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H93" s="6">
-        <v>550</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>215/50R17</t>
+          <t>215/45R18</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>BR215/50R17</t>
+          <t>GD215/45R18</t>
         </is>
       </c>
       <c r="D94" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E94" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F94" s="5">
         <v>0</v>
@@ -3524,7 +3524,7 @@
         <v>0</v>
       </c>
       <c r="H94" s="6">
-        <v>450</v>
+        <v>550</v>
       </c>
     </row>
     <row outlineLevel="0" r="95">
@@ -3535,28 +3535,28 @@
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>GD215/50R17</t>
+          <t>BR215/50R17</t>
         </is>
       </c>
       <c r="D95" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E95" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F95" s="5">
         <v>0</v>
       </c>
       <c r="G95" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H95" s="6">
-        <v>470</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="96">
@@ -3567,16 +3567,16 @@
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>HK215/50R17</t>
+          <t>GD215/50R17</t>
         </is>
       </c>
       <c r="D96" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E96" s="5">
         <v>3</v>
@@ -3585,26 +3585,26 @@
         <v>0</v>
       </c>
       <c r="G96" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H96" s="6">
-        <v>400</v>
+        <v>470</v>
       </c>
     </row>
     <row outlineLevel="0" r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>215/50R18</t>
+          <t>215/50R17</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>GD215/50R18</t>
+          <t>HK215/50R17</t>
         </is>
       </c>
       <c r="D97" s="5">
@@ -3620,13 +3620,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="6">
-        <v>600</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="98">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>215/55R16</t>
+          <t>215/50R18</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
@@ -3636,14 +3636,14 @@
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>GD215/55R16</t>
+          <t>GD215/50R18</t>
         </is>
       </c>
       <c r="D98" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E98" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F98" s="5">
         <v>0</v>
@@ -3652,7 +3652,7 @@
         <v>0</v>
       </c>
       <c r="H98" s="6">
-        <v>440</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="99">
@@ -3663,12 +3663,12 @@
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>LF215/55R16</t>
+          <t>GD215/55R16</t>
         </is>
       </c>
       <c r="D99" s="5">
@@ -3684,23 +3684,23 @@
         <v>0</v>
       </c>
       <c r="H99" s="6">
-        <v>350</v>
+        <v>440</v>
       </c>
     </row>
     <row outlineLevel="0" r="100">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>215/55R17</t>
+          <t>215/55R16</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>BR215/55R17</t>
+          <t>LF215/55R16</t>
         </is>
       </c>
       <c r="D100" s="5">
@@ -3716,7 +3716,7 @@
         <v>0</v>
       </c>
       <c r="H100" s="6">
-        <v>480</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="101">
@@ -3727,19 +3727,19 @@
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>HK215/55R17</t>
+          <t>BR215/55R17</t>
         </is>
       </c>
       <c r="D101" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E101" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F101" s="5">
         <v>0</v>
@@ -3748,30 +3748,30 @@
         <v>0</v>
       </c>
       <c r="H101" s="6">
-        <v>420</v>
+        <v>480</v>
       </c>
     </row>
     <row outlineLevel="0" r="102">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>215/55R18</t>
+          <t>215/55R17</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>GD215/55R18</t>
+          <t>HK215/55R17</t>
         </is>
       </c>
       <c r="D102" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E102" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F102" s="5">
         <v>0</v>
@@ -3780,30 +3780,30 @@
         <v>0</v>
       </c>
       <c r="H102" s="6">
-        <v>580</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>215/60R16</t>
+          <t>215/55R18</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>BR215/60R16</t>
+          <t>GD215/55R18</t>
         </is>
       </c>
       <c r="D103" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E103" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F103" s="5">
         <v>0</v>
@@ -3812,7 +3812,7 @@
         <v>0</v>
       </c>
       <c r="H103" s="6">
-        <v>350</v>
+        <v>580</v>
       </c>
     </row>
     <row outlineLevel="0" r="104">
@@ -3823,25 +3823,25 @@
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>DL215/60R16</t>
+          <t>BR215/60R16</t>
         </is>
       </c>
       <c r="D104" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E104" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F104" s="5">
         <v>0</v>
       </c>
       <c r="G104" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H104" s="6">
         <v>350</v>
@@ -3855,28 +3855,28 @@
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>HK215/60R16</t>
+          <t>DL215/60R16</t>
         </is>
       </c>
       <c r="D105" s="5">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E105" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F105" s="5">
         <v>0</v>
       </c>
       <c r="G105" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H105" s="6">
-        <v>330</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="106">
@@ -3887,25 +3887,25 @@
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>NX215/60R16</t>
+          <t>HK215/60R16</t>
         </is>
       </c>
       <c r="D106" s="5">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E106" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F106" s="5">
         <v>0</v>
       </c>
       <c r="G106" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H106" s="6">
         <v>330</v>
@@ -3914,65 +3914,65 @@
     <row outlineLevel="0" r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>215/60R17</t>
+          <t>215/60R16</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>RD215/60R17</t>
+          <t>NX215/60R16</t>
         </is>
       </c>
       <c r="D107" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E107" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F107" s="5">
         <v>0</v>
       </c>
       <c r="G107" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H107" s="6">
-        <v>300</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="108">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>215/65R16</t>
+          <t>215/60R17</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>GD215/65R16</t>
+          <t>RD215/60R17</t>
         </is>
       </c>
       <c r="D108" s="5">
         <v>1</v>
       </c>
       <c r="E108" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F108" s="5">
         <v>0</v>
       </c>
       <c r="G108" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H108" s="6">
-        <v>380</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="109">
@@ -3983,44 +3983,44 @@
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>HK215/65R16</t>
+          <t>GD215/65R16</t>
         </is>
       </c>
       <c r="D109" s="5">
         <v>1</v>
       </c>
       <c r="E109" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F109" s="5">
         <v>0</v>
       </c>
       <c r="G109" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H109" s="6">
-        <v>330</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="110">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>215/65R17</t>
+          <t>215/65R16</t>
         </is>
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>MICHELIN</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>MC215/65R17</t>
+          <t>HK215/65R16</t>
         </is>
       </c>
       <c r="D110" s="5">
@@ -4036,103 +4036,103 @@
         <v>0</v>
       </c>
       <c r="H110" s="6">
-        <v>600</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="111">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>215/70R15C</t>
+          <t>215/65R17</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>LINGLONG</t>
+          <t>MICHELIN</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>LG215/70R15C</t>
+          <t>MC215/65R17</t>
         </is>
       </c>
       <c r="D111" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E111" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F111" s="5">
         <v>0</v>
       </c>
       <c r="G111" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H111" s="6">
-        <v>370</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="112">
       <c r="A112" s="4" t="inlineStr">
         <is>
-          <t>225/40R18</t>
+          <t>215/70R15C</t>
         </is>
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>BARUM</t>
+          <t>LINGLONG</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>BM225/40R18</t>
+          <t>LG215/70R15C</t>
         </is>
       </c>
       <c r="D112" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E112" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F112" s="5">
         <v>0</v>
       </c>
       <c r="G112" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H112" s="6">
-        <v>420</v>
+        <v>370</v>
       </c>
     </row>
     <row outlineLevel="0" r="113">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>225/40R18</t>
+          <t>215/70R15C</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>GD225/40R18</t>
+          <t>RD215/70R15C</t>
         </is>
       </c>
       <c r="D113" s="5">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="E113" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F113" s="5">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G113" s="5">
         <v>0</v>
       </c>
       <c r="H113" s="6">
-        <v>480</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="114">
@@ -4143,19 +4143,19 @@
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>BARUM</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>HK225/40R18</t>
+          <t>BM225/40R18</t>
         </is>
       </c>
       <c r="D114" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E114" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F114" s="5">
         <v>0</v>
@@ -4164,7 +4164,7 @@
         <v>0</v>
       </c>
       <c r="H114" s="6">
-        <v>450</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="115">
@@ -4175,28 +4175,28 @@
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>LASSA</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>LS225/40R18</t>
+          <t>GD225/40R18</t>
         </is>
       </c>
       <c r="D115" s="5">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="E115" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F115" s="5">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G115" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H115" s="6">
-        <v>330</v>
+        <v>480</v>
       </c>
     </row>
     <row outlineLevel="0" r="116">
@@ -4207,19 +4207,19 @@
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>NX225/40R18</t>
+          <t>HK225/40R18</t>
         </is>
       </c>
       <c r="D116" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E116" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F116" s="5">
         <v>0</v>
@@ -4228,7 +4228,7 @@
         <v>0</v>
       </c>
       <c r="H116" s="6">
-        <v>400</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="117">
@@ -4239,51 +4239,51 @@
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>SEMPERIT</t>
+          <t>LASSA</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>SP225/40R18</t>
+          <t>LS225/40R18</t>
         </is>
       </c>
       <c r="D117" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E117" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F117" s="5">
         <v>0</v>
       </c>
       <c r="G117" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H117" s="6">
-        <v>450</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="118">
       <c r="A118" s="4" t="inlineStr">
         <is>
-          <t>225/40R18RF</t>
+          <t>225/40R18</t>
         </is>
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>GD225/40R18RF</t>
+          <t>NX225/40R18</t>
         </is>
       </c>
       <c r="D118" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E118" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F118" s="5">
         <v>0</v>
@@ -4292,30 +4292,30 @@
         <v>0</v>
       </c>
       <c r="H118" s="6">
-        <v>590</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="119">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t>225/45R17</t>
+          <t>225/40R18</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>SEMPERIT</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>CT225/45R17</t>
+          <t>SP225/40R18</t>
         </is>
       </c>
       <c r="D119" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E119" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F119" s="5">
         <v>0</v>
@@ -4324,39 +4324,39 @@
         <v>0</v>
       </c>
       <c r="H119" s="6">
-        <v>400</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="120">
       <c r="A120" s="4" t="inlineStr">
         <is>
-          <t>225/45R17</t>
+          <t>225/40R18RF</t>
         </is>
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>FULDA</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>FL225/45R17</t>
+          <t>GD225/40R18RF</t>
         </is>
       </c>
       <c r="D120" s="5">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="E120" s="5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F120" s="5">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G120" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H120" s="6">
-        <v>350</v>
+        <v>590</v>
       </c>
     </row>
     <row outlineLevel="0" r="121">
@@ -4367,28 +4367,28 @@
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>GD225/45R17</t>
+          <t>CT225/45R17</t>
         </is>
       </c>
       <c r="D121" s="5">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="E121" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F121" s="5">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="G121" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H121" s="6">
-        <v>380</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="122">
@@ -4399,25 +4399,25 @@
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>FULDA</t>
         </is>
       </c>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>HK225/45R17</t>
+          <t>FL225/45R17</t>
         </is>
       </c>
       <c r="D122" s="5">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E122" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F122" s="5">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G122" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H122" s="6">
         <v>350</v>
@@ -4426,65 +4426,65 @@
     <row outlineLevel="0" r="123">
       <c r="A123" s="4" t="inlineStr">
         <is>
-          <t>225/45R18</t>
+          <t>225/45R17</t>
         </is>
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>DL225/45R18</t>
+          <t>GD225/45R17</t>
         </is>
       </c>
       <c r="D123" s="5">
+        <v>22</v>
+      </c>
+      <c r="E123" s="5">
+        <v>2</v>
+      </c>
+      <c r="F123" s="5">
+        <v>17</v>
+      </c>
+      <c r="G123" s="5">
         <v>3</v>
       </c>
-      <c r="E123" s="5">
-        <v>1</v>
-      </c>
-      <c r="F123" s="5">
-        <v>0</v>
-      </c>
-      <c r="G123" s="5">
-        <v>2</v>
-      </c>
       <c r="H123" s="6">
-        <v>500</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="124">
       <c r="A124" s="4" t="inlineStr">
         <is>
-          <t>225/45R18</t>
+          <t>225/45R17</t>
         </is>
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>GD225/45R18</t>
+          <t>HK225/45R17</t>
         </is>
       </c>
       <c r="D124" s="5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E124" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F124" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G124" s="5">
         <v>0</v>
       </c>
       <c r="H124" s="6">
-        <v>550</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="125">
@@ -4495,19 +4495,19 @@
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>LF225/45R18</t>
+          <t>DL225/45R18</t>
         </is>
       </c>
       <c r="D125" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E125" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F125" s="5">
         <v>0</v>
@@ -4516,13 +4516,13 @@
         <v>0</v>
       </c>
       <c r="H125" s="6">
-        <v>420</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="126">
       <c r="A126" s="4" t="inlineStr">
         <is>
-          <t>225/45R18RF</t>
+          <t>225/45R18</t>
         </is>
       </c>
       <c r="B126" s="4" t="inlineStr">
@@ -4532,46 +4532,46 @@
       </c>
       <c r="C126" s="4" t="inlineStr">
         <is>
-          <t>GD225/45R18RF</t>
+          <t>GD225/45R18</t>
         </is>
       </c>
       <c r="D126" s="5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E126" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F126" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G126" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H126" s="6">
-        <v>720</v>
+        <v>550</v>
       </c>
     </row>
     <row outlineLevel="0" r="127">
       <c r="A127" s="4" t="inlineStr">
         <is>
-          <t>225/45R19</t>
+          <t>225/45R18</t>
         </is>
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>CT225/45R19</t>
+          <t>LF225/45R18</t>
         </is>
       </c>
       <c r="D127" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E127" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F127" s="5">
         <v>0</v>
@@ -4580,71 +4580,71 @@
         <v>0</v>
       </c>
       <c r="H127" s="6">
-        <v>780</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="128">
       <c r="A128" s="4" t="inlineStr">
         <is>
-          <t>225/50R17</t>
+          <t>225/45R18RF</t>
         </is>
       </c>
       <c r="B128" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C128" s="4" t="inlineStr">
         <is>
-          <t>BR225/50R17</t>
+          <t>GD225/45R18RF</t>
         </is>
       </c>
       <c r="D128" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E128" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F128" s="5">
         <v>0</v>
       </c>
       <c r="G128" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H128" s="6">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row outlineLevel="0" r="129">
       <c r="A129" s="4" t="inlineStr">
         <is>
-          <t>225/50R17</t>
+          <t>225/45R19</t>
         </is>
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>GD225/50R17</t>
+          <t>CT225/45R19</t>
         </is>
       </c>
       <c r="D129" s="5">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E129" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F129" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G129" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H129" s="6">
-        <v>500</v>
+        <v>780</v>
       </c>
     </row>
     <row outlineLevel="0" r="130">
@@ -4655,115 +4655,115 @@
       </c>
       <c r="B130" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C130" s="4" t="inlineStr">
         <is>
-          <t>HK225/50R17</t>
+          <t>BR225/50R17</t>
         </is>
       </c>
       <c r="D130" s="5">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E130" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F130" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G130" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H130" s="6">
-        <v>400</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="131">
       <c r="A131" s="4" t="inlineStr">
         <is>
-          <t>225/55R16</t>
+          <t>225/50R17</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>DL225/55R16</t>
+          <t>GD225/50R17</t>
         </is>
       </c>
       <c r="D131" s="5">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E131" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F131" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G131" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H131" s="6">
-        <v>450</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="132">
       <c r="A132" s="4" t="inlineStr">
         <is>
-          <t>225/55R16</t>
+          <t>225/50R17</t>
         </is>
       </c>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C132" s="4" t="inlineStr">
         <is>
-          <t>GD225/55R16</t>
+          <t>HK225/50R17</t>
         </is>
       </c>
       <c r="D132" s="5">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E132" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F132" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G132" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H132" s="6">
-        <v>420</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="133">
       <c r="A133" s="4" t="inlineStr">
         <is>
-          <t>225/55R17</t>
+          <t>225/55R16</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>HK225/55R17</t>
+          <t>DL225/55R16</t>
         </is>
       </c>
       <c r="D133" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E133" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F133" s="5">
         <v>0</v>
@@ -4772,13 +4772,13 @@
         <v>0</v>
       </c>
       <c r="H133" s="6">
-        <v>430</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="134">
       <c r="A134" s="4" t="inlineStr">
         <is>
-          <t>225/55R17RF</t>
+          <t>225/55R16</t>
         </is>
       </c>
       <c r="B134" s="4" t="inlineStr">
@@ -4788,29 +4788,29 @@
       </c>
       <c r="C134" s="4" t="inlineStr">
         <is>
-          <t>GD225/55R17RF</t>
+          <t>GD225/55R16</t>
         </is>
       </c>
       <c r="D134" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E134" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F134" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G134" s="5">
         <v>0</v>
       </c>
       <c r="H134" s="6">
-        <v>700</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="135">
       <c r="A135" s="4" t="inlineStr">
         <is>
-          <t>225/55R18</t>
+          <t>225/55R17</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
@@ -4820,14 +4820,14 @@
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>HK225/55R18</t>
+          <t>HK225/55R17</t>
         </is>
       </c>
       <c r="D135" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E135" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F135" s="5">
         <v>0</v>
@@ -4836,62 +4836,62 @@
         <v>0</v>
       </c>
       <c r="H135" s="6">
-        <v>500</v>
+        <v>430</v>
       </c>
     </row>
     <row outlineLevel="0" r="136">
       <c r="A136" s="4" t="inlineStr">
         <is>
-          <t>225/55R18</t>
+          <t>225/55R17RF</t>
         </is>
       </c>
       <c r="B136" s="4" t="inlineStr">
         <is>
-          <t>KUMHO</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C136" s="4" t="inlineStr">
         <is>
-          <t>KM225/55R18</t>
+          <t>GD225/55R17RF</t>
         </is>
       </c>
       <c r="D136" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E136" s="5">
         <v>4</v>
       </c>
       <c r="F136" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G136" s="5">
         <v>0</v>
       </c>
       <c r="H136" s="6">
-        <v>450</v>
+        <v>700</v>
       </c>
     </row>
     <row outlineLevel="0" r="137">
       <c r="A137" s="4" t="inlineStr">
         <is>
-          <t>225/55R19</t>
+          <t>225/55R18</t>
         </is>
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>KUMHO</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>BR225/55R19</t>
+          <t>KM225/55R18</t>
         </is>
       </c>
       <c r="D137" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E137" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F137" s="5">
         <v>0</v>
@@ -4900,7 +4900,7 @@
         <v>0</v>
       </c>
       <c r="H137" s="6">
-        <v>750</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="138">
@@ -4911,19 +4911,19 @@
       </c>
       <c r="B138" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C138" s="4" t="inlineStr">
         <is>
-          <t>GD225/55R19</t>
+          <t>BR225/55R19</t>
         </is>
       </c>
       <c r="D138" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E138" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F138" s="5">
         <v>0</v>
@@ -4938,21 +4938,21 @@
     <row outlineLevel="0" r="139">
       <c r="A139" s="4" t="inlineStr">
         <is>
-          <t>225/60R17</t>
+          <t>225/55R19</t>
         </is>
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>HK225/60R17</t>
+          <t>GD225/55R19</t>
         </is>
       </c>
       <c r="D139" s="5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E139" s="5">
         <v>4</v>
@@ -4961,65 +4961,65 @@
         <v>0</v>
       </c>
       <c r="G139" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H139" s="6">
-        <v>400</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="140">
       <c r="A140" s="4" t="inlineStr">
         <is>
-          <t>225/60R18</t>
+          <t>225/60R17</t>
         </is>
       </c>
       <c r="B140" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C140" s="4" t="inlineStr">
         <is>
-          <t>GD225/60R18</t>
+          <t>HK225/60R17</t>
         </is>
       </c>
       <c r="D140" s="5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E140" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F140" s="5">
         <v>0</v>
       </c>
       <c r="G140" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H140" s="6">
-        <v>700</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="141">
       <c r="A141" s="4" t="inlineStr">
         <is>
-          <t>225/65R17</t>
+          <t>225/60R18</t>
         </is>
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>RD225/65R17</t>
+          <t>GD225/60R18</t>
         </is>
       </c>
       <c r="D141" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E141" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F141" s="5">
         <v>0</v>
@@ -5028,36 +5028,36 @@
         <v>0</v>
       </c>
       <c r="H141" s="6">
-        <v>450</v>
+        <v>700</v>
       </c>
     </row>
     <row outlineLevel="0" r="142">
       <c r="A142" s="4" t="inlineStr">
         <is>
-          <t>225/70R15C</t>
+          <t>225/65R17</t>
         </is>
       </c>
       <c r="B142" s="4" t="inlineStr">
         <is>
-          <t>MATADOR</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C142" s="4" t="inlineStr">
         <is>
-          <t>MT225/70R15C</t>
+          <t>RD225/65R17</t>
         </is>
       </c>
       <c r="D142" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E142" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F142" s="5">
         <v>0</v>
       </c>
       <c r="G142" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H142" s="6">
         <v>450</v>
@@ -5066,21 +5066,21 @@
     <row outlineLevel="0" r="143">
       <c r="A143" s="4" t="inlineStr">
         <is>
-          <t>225/75R15C</t>
+          <t>225/70R15C</t>
         </is>
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>MATADOR</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>RD225/75R15C</t>
+          <t>MT225/70R15C</t>
         </is>
       </c>
       <c r="D143" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E143" s="5">
         <v>0</v>
@@ -5089,16 +5089,16 @@
         <v>0</v>
       </c>
       <c r="G143" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H143" s="6">
-        <v>330</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="144">
       <c r="A144" s="4" t="inlineStr">
         <is>
-          <t>235/35R19</t>
+          <t>225/75R15C</t>
         </is>
       </c>
       <c r="B144" s="4" t="inlineStr">
@@ -5108,61 +5108,61 @@
       </c>
       <c r="C144" s="4" t="inlineStr">
         <is>
-          <t>RD235/35R19</t>
+          <t>RD225/75R15C</t>
         </is>
       </c>
       <c r="D144" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E144" s="5">
         <v>0</v>
       </c>
       <c r="F144" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G144" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H144" s="6">
-        <v>600</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="145">
       <c r="A145" s="4" t="inlineStr">
         <is>
-          <t>235/40R19</t>
+          <t>235/35R19</t>
         </is>
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>GD235/40R19</t>
+          <t>RD235/35R19</t>
         </is>
       </c>
       <c r="D145" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E145" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F145" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G145" s="5">
         <v>0</v>
       </c>
       <c r="H145" s="6">
-        <v>850</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="146">
       <c r="A146" s="4" t="inlineStr">
         <is>
-          <t>235/45R18</t>
+          <t>235/40R19</t>
         </is>
       </c>
       <c r="B146" s="4" t="inlineStr">
@@ -5172,14 +5172,14 @@
       </c>
       <c r="C146" s="4" t="inlineStr">
         <is>
-          <t>GD235/45R18</t>
+          <t>GD235/40R19</t>
         </is>
       </c>
       <c r="D146" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E146" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F146" s="5">
         <v>0</v>
@@ -5188,30 +5188,30 @@
         <v>0</v>
       </c>
       <c r="H146" s="6">
-        <v>600</v>
+        <v>850</v>
       </c>
     </row>
     <row outlineLevel="0" r="147">
       <c r="A147" s="4" t="inlineStr">
         <is>
-          <t>235/50R18</t>
+          <t>235/45R18</t>
         </is>
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>HK235/50R18</t>
+          <t>GD235/45R18</t>
         </is>
       </c>
       <c r="D147" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E147" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F147" s="5">
         <v>0</v>
@@ -5220,30 +5220,30 @@
         <v>0</v>
       </c>
       <c r="H147" s="6">
-        <v>500</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="148">
       <c r="A148" s="4" t="inlineStr">
         <is>
-          <t>235/50R19</t>
+          <t>235/50R18</t>
         </is>
       </c>
       <c r="B148" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C148" s="4" t="inlineStr">
         <is>
-          <t>GD235/50R19</t>
+          <t>HK235/50R18</t>
         </is>
       </c>
       <c r="D148" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E148" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F148" s="5">
         <v>0</v>
@@ -5252,13 +5252,13 @@
         <v>0</v>
       </c>
       <c r="H148" s="6">
-        <v>800</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="149">
       <c r="A149" s="4" t="inlineStr">
         <is>
-          <t>235/50R20</t>
+          <t>235/50R19</t>
         </is>
       </c>
       <c r="B149" s="4" t="inlineStr">
@@ -5268,78 +5268,78 @@
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>GD235/50R20</t>
+          <t>GD235/50R19</t>
         </is>
       </c>
       <c r="D149" s="5">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E149" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F149" s="5">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G149" s="5">
         <v>0</v>
       </c>
       <c r="H149" s="6">
-        <v>1180</v>
+        <v>800</v>
       </c>
     </row>
     <row outlineLevel="0" r="150">
       <c r="A150" s="4" t="inlineStr">
         <is>
-          <t>235/55R17</t>
+          <t>235/50R20</t>
         </is>
       </c>
       <c r="B150" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C150" s="4" t="inlineStr">
         <is>
-          <t>BR235/55R17</t>
+          <t>GD235/50R20</t>
         </is>
       </c>
       <c r="D150" s="5">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E150" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F150" s="5">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G150" s="5">
         <v>0</v>
       </c>
       <c r="H150" s="6">
-        <v>450</v>
+        <v>1180</v>
       </c>
     </row>
     <row outlineLevel="0" r="151">
       <c r="A151" s="4" t="inlineStr">
         <is>
-          <t>235/55R18</t>
+          <t>235/55R17</t>
         </is>
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>HK235/55R18</t>
+          <t>BR235/55R17</t>
         </is>
       </c>
       <c r="D151" s="5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E151" s="5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F151" s="5">
         <v>0</v>
@@ -5348,30 +5348,30 @@
         <v>0</v>
       </c>
       <c r="H151" s="6">
-        <v>480</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="152">
       <c r="A152" s="4" t="inlineStr">
         <is>
-          <t>235/55R19</t>
+          <t>235/55R18</t>
         </is>
       </c>
       <c r="B152" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C152" s="4" t="inlineStr">
         <is>
-          <t>GD235/55R19</t>
+          <t>HK235/55R18</t>
         </is>
       </c>
       <c r="D152" s="5">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E152" s="5">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F152" s="5">
         <v>0</v>
@@ -5380,7 +5380,7 @@
         <v>0</v>
       </c>
       <c r="H152" s="6">
-        <v>750</v>
+        <v>480</v>
       </c>
     </row>
     <row outlineLevel="0" r="153">
@@ -5391,19 +5391,19 @@
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>HK235/55R19</t>
+          <t>GD235/55R19</t>
         </is>
       </c>
       <c r="D153" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E153" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F153" s="5">
         <v>0</v>
@@ -5412,7 +5412,7 @@
         <v>0</v>
       </c>
       <c r="H153" s="6">
-        <v>630</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="154">
@@ -5423,19 +5423,19 @@
       </c>
       <c r="B154" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C154" s="4" t="inlineStr">
         <is>
-          <t>LF235/55R19</t>
+          <t>HK235/55R19</t>
         </is>
       </c>
       <c r="D154" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E154" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F154" s="5">
         <v>0</v>
@@ -5444,7 +5444,7 @@
         <v>0</v>
       </c>
       <c r="H154" s="6">
-        <v>500</v>
+        <v>630</v>
       </c>
     </row>
     <row outlineLevel="0" r="155">
@@ -5455,19 +5455,19 @@
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>NX235/55R19</t>
+          <t>LF235/55R19</t>
         </is>
       </c>
       <c r="D155" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E155" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F155" s="5">
         <v>0</v>
@@ -5476,7 +5476,7 @@
         <v>0</v>
       </c>
       <c r="H155" s="6">
-        <v>600</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="156">
@@ -5487,66 +5487,66 @@
       </c>
       <c r="B156" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C156" s="4" t="inlineStr">
         <is>
-          <t>RD235/55R19</t>
+          <t>NX235/55R19</t>
         </is>
       </c>
       <c r="D156" s="5">
         <v>2</v>
       </c>
       <c r="E156" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F156" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G156" s="5">
         <v>0</v>
       </c>
       <c r="H156" s="6">
-        <v>500</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="157">
       <c r="A157" s="4" t="inlineStr">
         <is>
-          <t>235/60R16</t>
+          <t>235/55R19</t>
         </is>
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>HK235/60R16</t>
+          <t>RD235/55R19</t>
         </is>
       </c>
       <c r="D157" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E157" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F157" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G157" s="5">
         <v>0</v>
       </c>
       <c r="H157" s="6">
-        <v>430</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="158">
       <c r="A158" s="4" t="inlineStr">
         <is>
-          <t>235/60R17</t>
+          <t>235/60R16</t>
         </is>
       </c>
       <c r="B158" s="4" t="inlineStr">
@@ -5556,55 +5556,55 @@
       </c>
       <c r="C158" s="4" t="inlineStr">
         <is>
-          <t>HK235/60R17</t>
+          <t>HK235/60R16</t>
         </is>
       </c>
       <c r="D158" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E158" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F158" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G158" s="5">
         <v>0</v>
       </c>
       <c r="H158" s="6">
-        <v>500</v>
+        <v>430</v>
       </c>
     </row>
     <row outlineLevel="0" r="159">
       <c r="A159" s="4" t="inlineStr">
         <is>
-          <t>235/60R18</t>
+          <t>235/60R17</t>
         </is>
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>GD235/60R18</t>
+          <t>HK235/60R17</t>
         </is>
       </c>
       <c r="D159" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E159" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F159" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G159" s="5">
         <v>0</v>
       </c>
       <c r="H159" s="6">
-        <v>680</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="160">
@@ -5615,12 +5615,12 @@
       </c>
       <c r="B160" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C160" s="4" t="inlineStr">
         <is>
-          <t>HK235/60R18</t>
+          <t>GD235/60R18</t>
         </is>
       </c>
       <c r="D160" s="5">
@@ -5636,30 +5636,30 @@
         <v>0</v>
       </c>
       <c r="H160" s="6">
-        <v>550</v>
+        <v>680</v>
       </c>
     </row>
     <row outlineLevel="0" r="161">
       <c r="A161" s="4" t="inlineStr">
         <is>
-          <t>245/40R17</t>
+          <t>235/60R18</t>
         </is>
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>GD245/40R17</t>
+          <t>HK235/60R18</t>
         </is>
       </c>
       <c r="D161" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E161" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F161" s="5">
         <v>0</v>
@@ -5668,13 +5668,13 @@
         <v>0</v>
       </c>
       <c r="H161" s="6">
-        <v>400</v>
+        <v>550</v>
       </c>
     </row>
     <row outlineLevel="0" r="162">
       <c r="A162" s="4" t="inlineStr">
         <is>
-          <t>245/40R18</t>
+          <t>245/40R17</t>
         </is>
       </c>
       <c r="B162" s="4" t="inlineStr">
@@ -5684,142 +5684,142 @@
       </c>
       <c r="C162" s="4" t="inlineStr">
         <is>
-          <t>GD245/40R18</t>
+          <t>GD245/40R17</t>
         </is>
       </c>
       <c r="D162" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E162" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F162" s="5">
         <v>0</v>
       </c>
       <c r="G162" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H162" s="6">
-        <v>620</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="163">
       <c r="A163" s="4" t="inlineStr">
         <is>
-          <t>245/40R19</t>
+          <t>245/40R18</t>
         </is>
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>HK245/40R19</t>
+          <t>GD245/40R18</t>
         </is>
       </c>
       <c r="D163" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E163" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F163" s="5">
         <v>0</v>
       </c>
       <c r="G163" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H163" s="6">
-        <v>750</v>
+        <v>620</v>
       </c>
     </row>
     <row outlineLevel="0" r="164">
       <c r="A164" s="4" t="inlineStr">
         <is>
-          <t>245/40R20</t>
+          <t>245/40R19</t>
         </is>
       </c>
       <c r="B164" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C164" s="4" t="inlineStr">
         <is>
-          <t>CT245/40R20</t>
+          <t>HK245/40R19</t>
         </is>
       </c>
       <c r="D164" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E164" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F164" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G164" s="5">
         <v>0</v>
       </c>
       <c r="H164" s="6">
-        <v>1050</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="165">
       <c r="A165" s="4" t="inlineStr">
         <is>
-          <t>245/45R17</t>
+          <t>245/40R20</t>
         </is>
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>HK245/45R17</t>
+          <t>CT245/40R20</t>
         </is>
       </c>
       <c r="D165" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E165" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F165" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G165" s="5">
         <v>0</v>
       </c>
       <c r="H165" s="6">
-        <v>430</v>
+        <v>1050</v>
       </c>
     </row>
     <row outlineLevel="0" r="166">
       <c r="A166" s="4" t="inlineStr">
         <is>
-          <t>245/45R18</t>
+          <t>245/45R17</t>
         </is>
       </c>
       <c r="B166" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C166" s="4" t="inlineStr">
         <is>
-          <t>CT245/45R18</t>
+          <t>HK245/45R17</t>
         </is>
       </c>
       <c r="D166" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E166" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F166" s="5">
         <v>0</v>
@@ -5828,7 +5828,7 @@
         <v>0</v>
       </c>
       <c r="H166" s="6">
-        <v>650</v>
+        <v>430</v>
       </c>
     </row>
     <row outlineLevel="0" r="167">
@@ -5839,19 +5839,19 @@
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>GD245/45R18</t>
+          <t>CT245/45R18</t>
         </is>
       </c>
       <c r="D167" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E167" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F167" s="5">
         <v>0</v>
@@ -5860,7 +5860,7 @@
         <v>0</v>
       </c>
       <c r="H167" s="6">
-        <v>600</v>
+        <v>650</v>
       </c>
     </row>
     <row outlineLevel="0" r="168">
@@ -5871,19 +5871,19 @@
       </c>
       <c r="B168" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C168" s="4" t="inlineStr">
         <is>
-          <t>HK245/45R18</t>
+          <t>GD245/45R18</t>
         </is>
       </c>
       <c r="D168" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E168" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F168" s="5">
         <v>0</v>
@@ -5892,30 +5892,30 @@
         <v>0</v>
       </c>
       <c r="H168" s="6">
-        <v>500</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="169">
       <c r="A169" s="4" t="inlineStr">
         <is>
-          <t>245/45R18RF</t>
+          <t>245/45R18</t>
         </is>
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>GD245/45R18RF</t>
+          <t>HK245/45R18</t>
         </is>
       </c>
       <c r="D169" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E169" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F169" s="5">
         <v>0</v>
@@ -5924,23 +5924,23 @@
         <v>0</v>
       </c>
       <c r="H169" s="6">
-        <v>720</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="170">
       <c r="A170" s="4" t="inlineStr">
         <is>
-          <t>245/45R19</t>
+          <t>245/45R18RF</t>
         </is>
       </c>
       <c r="B170" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C170" s="4" t="inlineStr">
         <is>
-          <t>BR245/45R19</t>
+          <t>GD245/45R18RF</t>
         </is>
       </c>
       <c r="D170" s="5">
@@ -5956,7 +5956,7 @@
         <v>0</v>
       </c>
       <c r="H170" s="6">
-        <v>790</v>
+        <v>720</v>
       </c>
     </row>
     <row outlineLevel="0" r="171">
@@ -5967,44 +5967,44 @@
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t>RD245/45R19</t>
+          <t>BR245/45R19</t>
         </is>
       </c>
       <c r="D171" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E171" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F171" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G171" s="5">
         <v>0</v>
       </c>
       <c r="H171" s="6">
-        <v>450</v>
+        <v>790</v>
       </c>
     </row>
     <row outlineLevel="0" r="172">
       <c r="A172" s="4" t="inlineStr">
         <is>
-          <t>245/45R20</t>
+          <t>245/45R19</t>
         </is>
       </c>
       <c r="B172" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C172" s="4" t="inlineStr">
         <is>
-          <t>HK245/45R20</t>
+          <t>RD245/45R19</t>
         </is>
       </c>
       <c r="D172" s="5">
@@ -6020,94 +6020,94 @@
         <v>0</v>
       </c>
       <c r="H172" s="6">
-        <v>750</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="173">
       <c r="A173" s="4" t="inlineStr">
         <is>
-          <t>245/65R17</t>
+          <t>245/45R20</t>
         </is>
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>NX245/65R17</t>
+          <t>HK245/45R20</t>
         </is>
       </c>
       <c r="D173" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E173" s="5">
         <v>0</v>
       </c>
       <c r="F173" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G173" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H173" s="6">
-        <v>600</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="174">
       <c r="A174" s="4" t="inlineStr">
         <is>
-          <t>255/35R19</t>
+          <t>245/65R17</t>
         </is>
       </c>
       <c r="B174" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C174" s="4" t="inlineStr">
         <is>
-          <t>DL255/35R19</t>
+          <t>NX245/65R17</t>
         </is>
       </c>
       <c r="D174" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E174" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F174" s="5">
         <v>0</v>
       </c>
       <c r="G174" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H174" s="6">
-        <v>700</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="175">
       <c r="A175" s="4" t="inlineStr">
         <is>
-          <t>255/35R19RF</t>
+          <t>255/35R19</t>
         </is>
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>CT255/35R19RF</t>
+          <t>DL255/35R19</t>
         </is>
       </c>
       <c r="D175" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E175" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F175" s="5">
         <v>0</v>
@@ -6116,7 +6116,7 @@
         <v>0</v>
       </c>
       <c r="H175" s="6">
-        <v>950</v>
+        <v>700</v>
       </c>
     </row>
     <row outlineLevel="0" r="176">
@@ -6127,19 +6127,19 @@
       </c>
       <c r="B176" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C176" s="4" t="inlineStr">
         <is>
-          <t>GD255/35R19RF</t>
+          <t>CT255/35R19RF</t>
         </is>
       </c>
       <c r="D176" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E176" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F176" s="5">
         <v>0</v>
@@ -6154,39 +6154,39 @@
     <row outlineLevel="0" r="177">
       <c r="A177" s="4" t="inlineStr">
         <is>
-          <t>255/50R19</t>
+          <t>255/35R19RF</t>
         </is>
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>CT255/50R19</t>
+          <t>GD255/35R19RF</t>
         </is>
       </c>
       <c r="D177" s="5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E177" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F177" s="5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G177" s="5">
         <v>0</v>
       </c>
       <c r="H177" s="6">
-        <v>750</v>
+        <v>950</v>
       </c>
     </row>
     <row outlineLevel="0" r="178">
       <c r="A178" s="4" t="inlineStr">
         <is>
-          <t>255/50R20</t>
+          <t>255/50R19</t>
         </is>
       </c>
       <c r="B178" s="4" t="inlineStr">
@@ -6196,29 +6196,29 @@
       </c>
       <c r="C178" s="4" t="inlineStr">
         <is>
-          <t>CT255/50R20</t>
+          <t>CT255/50R19</t>
         </is>
       </c>
       <c r="D178" s="5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E178" s="5">
         <v>0</v>
       </c>
       <c r="F178" s="5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G178" s="5">
         <v>0</v>
       </c>
       <c r="H178" s="6">
-        <v>900</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="179">
       <c r="A179" s="4" t="inlineStr">
         <is>
-          <t>255/55R19</t>
+          <t>255/50R20</t>
         </is>
       </c>
       <c r="B179" s="4" t="inlineStr">
@@ -6228,23 +6228,23 @@
       </c>
       <c r="C179" s="4" t="inlineStr">
         <is>
-          <t>CT255/55R19</t>
+          <t>CT255/50R20</t>
         </is>
       </c>
       <c r="D179" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E179" s="5">
         <v>0</v>
       </c>
       <c r="F179" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G179" s="5">
         <v>0</v>
       </c>
       <c r="H179" s="6">
-        <v>750</v>
+        <v>900</v>
       </c>
     </row>
     <row outlineLevel="0" r="180">
@@ -6255,98 +6255,98 @@
       </c>
       <c r="B180" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C180" s="4" t="inlineStr">
         <is>
-          <t>DL255/55R19</t>
+          <t>CT255/55R19</t>
         </is>
       </c>
       <c r="D180" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E180" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F180" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G180" s="5">
         <v>0</v>
       </c>
       <c r="H180" s="6">
-        <v>700</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="181">
       <c r="A181" s="4" t="inlineStr">
         <is>
-          <t>255/70R16</t>
+          <t>255/55R19</t>
         </is>
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C181" s="4" t="inlineStr">
         <is>
-          <t>RD255/70R16</t>
+          <t>DL255/55R19</t>
         </is>
       </c>
       <c r="D181" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E181" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F181" s="5">
         <v>0</v>
       </c>
       <c r="G181" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H181" s="6">
-        <v>500</v>
+        <v>700</v>
       </c>
     </row>
     <row outlineLevel="0" r="182">
       <c r="A182" s="4" t="inlineStr">
         <is>
-          <t>265/35R18</t>
+          <t>255/70R16</t>
         </is>
       </c>
       <c r="B182" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C182" s="4" t="inlineStr">
         <is>
-          <t>GD265/35R18</t>
+          <t>RD255/70R16</t>
         </is>
       </c>
       <c r="D182" s="5">
         <v>1</v>
       </c>
       <c r="E182" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F182" s="5">
         <v>0</v>
       </c>
       <c r="G182" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H182" s="6">
-        <v>700</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="183">
       <c r="A183" s="4" t="inlineStr">
         <is>
-          <t>265/50R20</t>
+          <t>265/35R18</t>
         </is>
       </c>
       <c r="B183" s="4" t="inlineStr">
@@ -6356,29 +6356,29 @@
       </c>
       <c r="C183" s="4" t="inlineStr">
         <is>
-          <t>GD265/50R20</t>
+          <t>GD265/35R18</t>
         </is>
       </c>
       <c r="D183" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E183" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F183" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G183" s="5">
         <v>0</v>
       </c>
       <c r="H183" s="6">
-        <v>1150</v>
+        <v>700</v>
       </c>
     </row>
     <row outlineLevel="0" r="184">
       <c r="A184" s="4" t="inlineStr">
         <is>
-          <t>275/35R19RF</t>
+          <t>265/50R20</t>
         </is>
       </c>
       <c r="B184" s="4" t="inlineStr">
@@ -6388,71 +6388,71 @@
       </c>
       <c r="C184" s="4" t="inlineStr">
         <is>
-          <t>GD275/35R19RF</t>
+          <t>GD265/50R20</t>
         </is>
       </c>
       <c r="D184" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E184" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F184" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G184" s="5">
         <v>0</v>
       </c>
       <c r="H184" s="6">
-        <v>1</v>
+        <v>1150</v>
       </c>
     </row>
     <row outlineLevel="0" r="185">
       <c r="A185" s="4" t="inlineStr">
         <is>
-          <t>275/35R20</t>
+          <t>275/35R19RF</t>
         </is>
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C185" s="4" t="inlineStr">
         <is>
-          <t>CT275/35R20</t>
+          <t>GD275/35R19RF</t>
         </is>
       </c>
       <c r="D185" s="5">
         <v>2</v>
       </c>
       <c r="E185" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F185" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G185" s="5">
         <v>0</v>
       </c>
       <c r="H185" s="6">
-        <v>980</v>
+        <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="186">
       <c r="A186" s="4" t="inlineStr">
         <is>
-          <t>275/40R20</t>
+          <t>275/35R20</t>
         </is>
       </c>
       <c r="B186" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C186" s="4" t="inlineStr">
         <is>
-          <t>HK275/40R20</t>
+          <t>CT275/35R20</t>
         </is>
       </c>
       <c r="D186" s="5">
@@ -6468,23 +6468,23 @@
         <v>0</v>
       </c>
       <c r="H186" s="6">
-        <v>770</v>
+        <v>980</v>
       </c>
     </row>
     <row outlineLevel="0" r="187">
       <c r="A187" s="4" t="inlineStr">
         <is>
-          <t>275/50R21</t>
+          <t>275/40R20</t>
         </is>
       </c>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C187" s="4" t="inlineStr">
         <is>
-          <t>GD275/50R21</t>
+          <t>HK275/40R20</t>
         </is>
       </c>
       <c r="D187" s="5">
@@ -6500,23 +6500,23 @@
         <v>0</v>
       </c>
       <c r="H187" s="6">
-        <v>1</v>
+        <v>770</v>
       </c>
     </row>
     <row outlineLevel="0" r="188">
       <c r="A188" s="4" t="inlineStr">
         <is>
-          <t>295/35R21</t>
+          <t>275/50R21</t>
         </is>
       </c>
       <c r="B188" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C188" s="4" t="inlineStr">
         <is>
-          <t>CT295/35R21</t>
+          <t>GD275/50R21</t>
         </is>
       </c>
       <c r="D188" s="5">
@@ -6532,7 +6532,7 @@
         <v>0</v>
       </c>
       <c r="H188" s="6">
-        <v>1150</v>
+        <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="189">
@@ -6543,59 +6543,91 @@
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C189" s="4" t="inlineStr">
         <is>
-          <t>GD295/35R21</t>
+          <t>CT295/35R21</t>
         </is>
       </c>
       <c r="D189" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E189" s="5">
         <v>0</v>
       </c>
       <c r="F189" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G189" s="5">
         <v>0</v>
       </c>
       <c r="H189" s="6">
-        <v>980</v>
+        <v>1150</v>
       </c>
     </row>
     <row outlineLevel="0" r="190">
       <c r="A190" s="4" t="inlineStr">
         <is>
-          <t>500R12</t>
+          <t>295/35R21</t>
         </is>
       </c>
       <c r="B190" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C190" s="4" t="inlineStr">
         <is>
-          <t>RD500R12</t>
+          <t>GD295/35R21</t>
         </is>
       </c>
       <c r="D190" s="5">
         <v>3</v>
       </c>
       <c r="E190" s="5">
+        <v>0</v>
+      </c>
+      <c r="F190" s="5">
         <v>3</v>
       </c>
-      <c r="F190" s="5">
-        <v>0</v>
-      </c>
       <c r="G190" s="5">
         <v>0</v>
       </c>
       <c r="H190" s="6">
+        <v>980</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="191">
+      <c r="A191" s="4" t="inlineStr">
+        <is>
+          <t>500R12</t>
+        </is>
+      </c>
+      <c r="B191" s="4" t="inlineStr">
+        <is>
+          <t>RADIAL</t>
+        </is>
+      </c>
+      <c r="C191" s="4" t="inlineStr">
+        <is>
+          <t>RD500R12</t>
+        </is>
+      </c>
+      <c r="D191" s="5">
+        <v>3</v>
+      </c>
+      <c r="E191" s="5">
+        <v>3</v>
+      </c>
+      <c r="F191" s="5">
+        <v>0</v>
+      </c>
+      <c r="G191" s="5">
+        <v>0</v>
+      </c>
+      <c r="H191" s="6">
         <v>300</v>
       </c>
     </row>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -638,10 +638,10 @@
         <v>4</v>
       </c>
       <c r="F4" s="5">
+        <v>0</v>
+      </c>
+      <c r="G4" s="5">
         <v>3</v>
-      </c>
-      <c r="G4" s="5">
-        <v>0</v>
       </c>
       <c r="H4" s="6">
         <v>230</v>
@@ -920,10 +920,10 @@
         </is>
       </c>
       <c r="D13" s="5">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E13" s="5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F13" s="5">
         <v>5</v>
@@ -952,13 +952,13 @@
         </is>
       </c>
       <c r="D14" s="5">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E14" s="5">
         <v>6</v>
       </c>
       <c r="F14" s="5">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="G14" s="5">
         <v>12</v>
@@ -1080,10 +1080,10 @@
         </is>
       </c>
       <c r="D18" s="5">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E18" s="5">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F18" s="5">
         <v>0</v>
@@ -1435,10 +1435,10 @@
         <v>5</v>
       </c>
       <c r="E29" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F29" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G29" s="5">
         <v>1</v>
@@ -1563,10 +1563,10 @@
         <v>136</v>
       </c>
       <c r="E33" s="5">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F33" s="5">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G33" s="5">
         <v>11</v>
@@ -1976,13 +1976,13 @@
         </is>
       </c>
       <c r="D46" s="5">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E46" s="5">
         <v>4</v>
       </c>
       <c r="F46" s="5">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G46" s="5">
         <v>4</v>
@@ -2014,10 +2014,10 @@
         <v>2</v>
       </c>
       <c r="F47" s="5">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G47" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H47" s="6">
         <v>290</v>
@@ -2430,10 +2430,10 @@
         <v>3</v>
       </c>
       <c r="F60" s="5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G60" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H60" s="6">
         <v>350</v>
@@ -2555,13 +2555,13 @@
         <v>16</v>
       </c>
       <c r="E64" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F64" s="5">
         <v>8</v>
       </c>
       <c r="G64" s="5">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H64" s="6">
         <v>450</v>
@@ -2776,16 +2776,16 @@
         </is>
       </c>
       <c r="D71" s="5">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E71" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F71" s="5">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="G71" s="5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H71" s="6">
         <v>250</v>
@@ -2878,10 +2878,10 @@
         <v>4</v>
       </c>
       <c r="F74" s="5">
+        <v>0</v>
+      </c>
+      <c r="G74" s="5">
         <v>3</v>
-      </c>
-      <c r="G74" s="5">
-        <v>0</v>
       </c>
       <c r="H74" s="6">
         <v>260</v>
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="D80" s="5">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E80" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F80" s="5">
         <v>15</v>
@@ -3384,16 +3384,16 @@
         </is>
       </c>
       <c r="D90" s="5">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E90" s="5">
         <v>3</v>
       </c>
       <c r="F90" s="5">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G90" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H90" s="6">
         <v>400</v>
@@ -4184,16 +4184,16 @@
         </is>
       </c>
       <c r="D115" s="5">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E115" s="5">
         <v>4</v>
       </c>
       <c r="F115" s="5">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="G115" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H115" s="6">
         <v>480</v>
@@ -4411,10 +4411,10 @@
         <v>19</v>
       </c>
       <c r="E122" s="5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F122" s="5">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G122" s="5">
         <v>4</v>
@@ -4443,13 +4443,13 @@
         <v>22</v>
       </c>
       <c r="E123" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F123" s="5">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G123" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H123" s="6">
         <v>380</v>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -496,7 +496,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H191"/>
+  <dimension ref="A1:H192"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col customWidth="true" min="1" max="1" width="13.8359375"/>
@@ -2442,33 +2442,33 @@
     <row outlineLevel="0" r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>205/45R17</t>
+          <t>195R15C</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>CT205/45R17</t>
+          <t>RD195R15C</t>
         </is>
       </c>
       <c r="D61" s="5">
         <v>1</v>
       </c>
       <c r="E61" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F61" s="5">
         <v>0</v>
       </c>
       <c r="G61" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H61" s="6">
-        <v>550</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="62">
@@ -2479,28 +2479,28 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>FULDA</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>FL205/45R17</t>
+          <t>CT205/45R17</t>
         </is>
       </c>
       <c r="D62" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E62" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F62" s="5">
         <v>0</v>
       </c>
       <c r="G62" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H62" s="6">
-        <v>380</v>
+        <v>550</v>
       </c>
     </row>
     <row outlineLevel="0" r="63">
@@ -2511,28 +2511,28 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>GOODRIDE</t>
+          <t>FULDA</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>GR205/45R17</t>
+          <t>FL205/45R17</t>
         </is>
       </c>
       <c r="D63" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E63" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F63" s="5">
         <v>0</v>
       </c>
       <c r="G63" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H63" s="6">
-        <v>300</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="64">
@@ -2543,28 +2543,28 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>GOODRIDE</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>GD205/45R17</t>
+          <t>GR205/45R17</t>
         </is>
       </c>
       <c r="D64" s="5">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="E64" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F64" s="5">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G64" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H64" s="6">
-        <v>450</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="65">
@@ -2575,28 +2575,28 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>NX205/45R17</t>
+          <t>GD205/45R17</t>
         </is>
       </c>
       <c r="D65" s="5">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="E65" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F65" s="5">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G65" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H65" s="6">
-        <v>380</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="66">
@@ -2607,83 +2607,83 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>RD205/45R17</t>
+          <t>NX205/45R17</t>
         </is>
       </c>
       <c r="D66" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E66" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F66" s="5">
         <v>0</v>
       </c>
       <c r="G66" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H66" s="6">
-        <v>300</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>205/50R17</t>
+          <t>205/45R17</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>CT205/50R17</t>
+          <t>RD205/45R17</t>
         </is>
       </c>
       <c r="D67" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E67" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F67" s="5">
         <v>0</v>
       </c>
       <c r="G67" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H67" s="6">
-        <v>450</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>205/55R16</t>
+          <t>205/50R17</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>AMINE</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>AM205/55R16</t>
+          <t>CT205/50R17</t>
         </is>
       </c>
       <c r="D68" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E68" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F68" s="5">
         <v>0</v>
@@ -2692,7 +2692,7 @@
         <v>0</v>
       </c>
       <c r="H68" s="6">
-        <v>240</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="69">
@@ -2703,28 +2703,28 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>AMINE</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>BR205/55R16</t>
+          <t>AM205/55R16</t>
         </is>
       </c>
       <c r="D69" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E69" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F69" s="5">
         <v>0</v>
       </c>
       <c r="G69" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H69" s="6">
-        <v>290</v>
+        <v>240</v>
       </c>
     </row>
     <row outlineLevel="0" r="70">
@@ -2735,28 +2735,28 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>DOUBLESTAR</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>DS205/55R16</t>
+          <t>BR205/55R16</t>
         </is>
       </c>
       <c r="D70" s="5">
         <v>4</v>
       </c>
       <c r="E70" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F70" s="5">
         <v>0</v>
       </c>
       <c r="G70" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H70" s="6">
-        <v>230</v>
+        <v>290</v>
       </c>
     </row>
     <row outlineLevel="0" r="71">
@@ -2767,28 +2767,28 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>FULDA</t>
+          <t>DOUBLESTAR</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>FL205/55R16</t>
+          <t>DS205/55R16</t>
         </is>
       </c>
       <c r="D71" s="5">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="E71" s="5">
         <v>4</v>
       </c>
       <c r="F71" s="5">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G71" s="5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H71" s="6">
-        <v>250</v>
+        <v>230</v>
       </c>
     </row>
     <row outlineLevel="0" r="72">
@@ -2799,25 +2799,25 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>GOODRIDE</t>
+          <t>FULDA</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>GR205/55R16</t>
+          <t>FL205/55R16</t>
         </is>
       </c>
       <c r="D72" s="5">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="E72" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F72" s="5">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G72" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H72" s="6">
         <v>250</v>
@@ -2831,28 +2831,28 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>GOODRIDE</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>GD205/55R16</t>
+          <t>GR205/55R16</t>
         </is>
       </c>
       <c r="D73" s="5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E73" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F73" s="5">
         <v>0</v>
       </c>
       <c r="G73" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H73" s="6">
-        <v>280</v>
+        <v>250</v>
       </c>
     </row>
     <row outlineLevel="0" r="74">
@@ -2863,28 +2863,28 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>HK205/55R16</t>
+          <t>GD205/55R16</t>
         </is>
       </c>
       <c r="D74" s="5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E74" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F74" s="5">
         <v>0</v>
       </c>
       <c r="G74" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H74" s="6">
-        <v>260</v>
+        <v>280</v>
       </c>
     </row>
     <row outlineLevel="0" r="75">
@@ -2895,48 +2895,48 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>RD205/55R16</t>
+          <t>HK205/55R16</t>
         </is>
       </c>
       <c r="D75" s="5">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E75" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F75" s="5">
         <v>0</v>
       </c>
       <c r="G75" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H75" s="6">
-        <v>230</v>
+        <v>260</v>
       </c>
     </row>
     <row outlineLevel="0" r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>205/55R16RF</t>
+          <t>205/55R16</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>GD205/55R16RF</t>
+          <t>RD205/55R16</t>
         </is>
       </c>
       <c r="D76" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E76" s="5">
         <v>0</v>
@@ -2945,16 +2945,16 @@
         <v>0</v>
       </c>
       <c r="G76" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H76" s="6">
-        <v>480</v>
+        <v>230</v>
       </c>
     </row>
     <row outlineLevel="0" r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>205/55R17</t>
+          <t>205/55R16RF</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
@@ -2964,23 +2964,23 @@
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>GD205/55R17</t>
+          <t>GD205/55R16RF</t>
         </is>
       </c>
       <c r="D77" s="5">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="E77" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F77" s="5">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G77" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H77" s="6">
-        <v>450</v>
+        <v>480</v>
       </c>
     </row>
     <row outlineLevel="0" r="78">
@@ -2991,44 +2991,44 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>NX205/55R17</t>
+          <t>GD205/55R17</t>
         </is>
       </c>
       <c r="D78" s="5">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="E78" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F78" s="5">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G78" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H78" s="6">
-        <v>400</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>205/60R16</t>
+          <t>205/55R17</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>DL205/60R16</t>
+          <t>NX205/55R17</t>
         </is>
       </c>
       <c r="D79" s="5">
@@ -3044,7 +3044,7 @@
         <v>0</v>
       </c>
       <c r="H79" s="6">
-        <v>330</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="80">
@@ -3055,28 +3055,28 @@
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>GD205/60R16</t>
+          <t>DL205/60R16</t>
         </is>
       </c>
       <c r="D80" s="5">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="E80" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F80" s="5">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G80" s="5">
         <v>0</v>
       </c>
       <c r="H80" s="6">
-        <v>380</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="81">
@@ -3087,28 +3087,28 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>HK205/60R16</t>
+          <t>GD205/60R16</t>
         </is>
       </c>
       <c r="D81" s="5">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E81" s="5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F81" s="5">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="G81" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H81" s="6">
-        <v>300</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="82">
@@ -3119,25 +3119,25 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>LF205/60R16</t>
+          <t>HK205/60R16</t>
         </is>
       </c>
       <c r="D82" s="5">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E82" s="5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F82" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G82" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H82" s="6">
         <v>300</v>
@@ -3146,17 +3146,17 @@
     <row outlineLevel="0" r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>205/65R15</t>
+          <t>205/60R16</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>HK205/65R15</t>
+          <t>LF205/60R16</t>
         </is>
       </c>
       <c r="D83" s="5">
@@ -3172,30 +3172,30 @@
         <v>0</v>
       </c>
       <c r="H83" s="6">
-        <v>270</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>205/65R16</t>
+          <t>205/65R15</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>BR205/65R16</t>
+          <t>HK205/65R15</t>
         </is>
       </c>
       <c r="D84" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E84" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F84" s="5">
         <v>0</v>
@@ -3204,7 +3204,7 @@
         <v>0</v>
       </c>
       <c r="H84" s="6">
-        <v>420</v>
+        <v>270</v>
       </c>
     </row>
     <row outlineLevel="0" r="85">
@@ -3215,19 +3215,19 @@
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>HK205/65R16</t>
+          <t>BR205/65R16</t>
         </is>
       </c>
       <c r="D85" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E85" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F85" s="5">
         <v>0</v>
@@ -3236,39 +3236,39 @@
         <v>0</v>
       </c>
       <c r="H85" s="6">
-        <v>380</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>215/40R18</t>
+          <t>205/65R16</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>GD215/40R18</t>
+          <t>HK205/65R16</t>
         </is>
       </c>
       <c r="D86" s="5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E86" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F86" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G86" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H86" s="6">
-        <v>600</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="87">
@@ -3279,44 +3279,44 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>HK215/40R18</t>
+          <t>GD215/40R18</t>
         </is>
       </c>
       <c r="D87" s="5">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E87" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F87" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G87" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H87" s="6">
-        <v>490</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>215/45R16</t>
+          <t>215/40R18</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>GD215/45R16</t>
+          <t>HK215/40R18</t>
         </is>
       </c>
       <c r="D88" s="5">
@@ -3332,13 +3332,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="6">
-        <v>450</v>
+        <v>490</v>
       </c>
     </row>
     <row outlineLevel="0" r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>215/45R17</t>
+          <t>215/45R16</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
@@ -3348,14 +3348,14 @@
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>GD215/45R17</t>
+          <t>GD215/45R16</t>
         </is>
       </c>
       <c r="D89" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E89" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F89" s="5">
         <v>0</v>
@@ -3364,7 +3364,7 @@
         <v>0</v>
       </c>
       <c r="H89" s="6">
-        <v>400</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="90">
@@ -3375,25 +3375,25 @@
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>HK215/45R17</t>
+          <t>GD215/45R17</t>
         </is>
       </c>
       <c r="D90" s="5">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="E90" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F90" s="5">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G90" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H90" s="6">
         <v>400</v>
@@ -3407,28 +3407,28 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>IRIS</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>IR215/45R17</t>
+          <t>HK215/45R17</t>
         </is>
       </c>
       <c r="D91" s="5">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="E91" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F91" s="5">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G91" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H91" s="6">
-        <v>300</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="92">
@@ -3439,28 +3439,28 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>IRIS</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>LF215/45R17</t>
+          <t>IR215/45R17</t>
         </is>
       </c>
       <c r="D92" s="5">
         <v>1</v>
       </c>
       <c r="E92" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F92" s="5">
         <v>0</v>
       </c>
       <c r="G92" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H92" s="6">
-        <v>350</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="93">
@@ -3471,83 +3471,83 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>NX215/45R17</t>
+          <t>LF215/45R17</t>
         </is>
       </c>
       <c r="D93" s="5">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E93" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F93" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G93" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H93" s="6">
-        <v>380</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>215/45R18</t>
+          <t>215/45R17</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>GD215/45R18</t>
+          <t>NX215/45R17</t>
         </is>
       </c>
       <c r="D94" s="5">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E94" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F94" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G94" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H94" s="6">
-        <v>550</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>215/50R17</t>
+          <t>215/45R18</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>BR215/50R17</t>
+          <t>GD215/45R18</t>
         </is>
       </c>
       <c r="D95" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E95" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F95" s="5">
         <v>0</v>
@@ -3556,7 +3556,7 @@
         <v>0</v>
       </c>
       <c r="H95" s="6">
-        <v>450</v>
+        <v>550</v>
       </c>
     </row>
     <row outlineLevel="0" r="96">
@@ -3567,28 +3567,28 @@
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>GD215/50R17</t>
+          <t>BR215/50R17</t>
         </is>
       </c>
       <c r="D96" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E96" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F96" s="5">
         <v>0</v>
       </c>
       <c r="G96" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H96" s="6">
-        <v>470</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="97">
@@ -3599,16 +3599,16 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>HK215/50R17</t>
+          <t>GD215/50R17</t>
         </is>
       </c>
       <c r="D97" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E97" s="5">
         <v>3</v>
@@ -3617,26 +3617,26 @@
         <v>0</v>
       </c>
       <c r="G97" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H97" s="6">
-        <v>400</v>
+        <v>470</v>
       </c>
     </row>
     <row outlineLevel="0" r="98">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>215/50R18</t>
+          <t>215/50R17</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>GD215/50R18</t>
+          <t>HK215/50R17</t>
         </is>
       </c>
       <c r="D98" s="5">
@@ -3652,13 +3652,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="6">
-        <v>600</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>215/55R16</t>
+          <t>215/50R18</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
@@ -3668,14 +3668,14 @@
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>GD215/55R16</t>
+          <t>GD215/50R18</t>
         </is>
       </c>
       <c r="D99" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E99" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F99" s="5">
         <v>0</v>
@@ -3684,7 +3684,7 @@
         <v>0</v>
       </c>
       <c r="H99" s="6">
-        <v>440</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="100">
@@ -3695,12 +3695,12 @@
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>LF215/55R16</t>
+          <t>GD215/55R16</t>
         </is>
       </c>
       <c r="D100" s="5">
@@ -3716,23 +3716,23 @@
         <v>0</v>
       </c>
       <c r="H100" s="6">
-        <v>350</v>
+        <v>440</v>
       </c>
     </row>
     <row outlineLevel="0" r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>215/55R17</t>
+          <t>215/55R16</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>BR215/55R17</t>
+          <t>LF215/55R16</t>
         </is>
       </c>
       <c r="D101" s="5">
@@ -3748,7 +3748,7 @@
         <v>0</v>
       </c>
       <c r="H101" s="6">
-        <v>480</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="102">
@@ -3759,19 +3759,19 @@
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>HK215/55R17</t>
+          <t>BR215/55R17</t>
         </is>
       </c>
       <c r="D102" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E102" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F102" s="5">
         <v>0</v>
@@ -3780,30 +3780,30 @@
         <v>0</v>
       </c>
       <c r="H102" s="6">
-        <v>420</v>
+        <v>480</v>
       </c>
     </row>
     <row outlineLevel="0" r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>215/55R18</t>
+          <t>215/55R17</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>GD215/55R18</t>
+          <t>HK215/55R17</t>
         </is>
       </c>
       <c r="D103" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E103" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F103" s="5">
         <v>0</v>
@@ -3812,30 +3812,30 @@
         <v>0</v>
       </c>
       <c r="H103" s="6">
-        <v>580</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="104">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>215/60R16</t>
+          <t>215/55R18</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>BR215/60R16</t>
+          <t>GD215/55R18</t>
         </is>
       </c>
       <c r="D104" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E104" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F104" s="5">
         <v>0</v>
@@ -3844,7 +3844,7 @@
         <v>0</v>
       </c>
       <c r="H104" s="6">
-        <v>350</v>
+        <v>580</v>
       </c>
     </row>
     <row outlineLevel="0" r="105">
@@ -3855,25 +3855,25 @@
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>DL215/60R16</t>
+          <t>BR215/60R16</t>
         </is>
       </c>
       <c r="D105" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E105" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F105" s="5">
         <v>0</v>
       </c>
       <c r="G105" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H105" s="6">
         <v>350</v>
@@ -3887,28 +3887,28 @@
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>HK215/60R16</t>
+          <t>DL215/60R16</t>
         </is>
       </c>
       <c r="D106" s="5">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E106" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F106" s="5">
         <v>0</v>
       </c>
       <c r="G106" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H106" s="6">
-        <v>330</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="107">
@@ -3919,25 +3919,25 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>NX215/60R16</t>
+          <t>HK215/60R16</t>
         </is>
       </c>
       <c r="D107" s="5">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E107" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F107" s="5">
         <v>0</v>
       </c>
       <c r="G107" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H107" s="6">
         <v>330</v>
@@ -3946,65 +3946,65 @@
     <row outlineLevel="0" r="108">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>215/60R17</t>
+          <t>215/60R16</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>RD215/60R17</t>
+          <t>NX215/60R16</t>
         </is>
       </c>
       <c r="D108" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E108" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F108" s="5">
         <v>0</v>
       </c>
       <c r="G108" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H108" s="6">
-        <v>300</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="109">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>215/65R16</t>
+          <t>215/60R17</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>GD215/65R16</t>
+          <t>RD215/60R17</t>
         </is>
       </c>
       <c r="D109" s="5">
         <v>1</v>
       </c>
       <c r="E109" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F109" s="5">
         <v>0</v>
       </c>
       <c r="G109" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H109" s="6">
-        <v>380</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="110">
@@ -4015,44 +4015,44 @@
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>HK215/65R16</t>
+          <t>GD215/65R16</t>
         </is>
       </c>
       <c r="D110" s="5">
         <v>1</v>
       </c>
       <c r="E110" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F110" s="5">
         <v>0</v>
       </c>
       <c r="G110" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H110" s="6">
-        <v>330</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="111">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>215/65R17</t>
+          <t>215/65R16</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>MICHELIN</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>MC215/65R17</t>
+          <t>HK215/65R16</t>
         </is>
       </c>
       <c r="D111" s="5">
@@ -4068,39 +4068,39 @@
         <v>0</v>
       </c>
       <c r="H111" s="6">
-        <v>600</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="112">
       <c r="A112" s="4" t="inlineStr">
         <is>
-          <t>215/70R15C</t>
+          <t>215/65R17</t>
         </is>
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>LINGLONG</t>
+          <t>MICHELIN</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>LG215/70R15C</t>
+          <t>MC215/65R17</t>
         </is>
       </c>
       <c r="D112" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E112" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F112" s="5">
         <v>0</v>
       </c>
       <c r="G112" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H112" s="6">
-        <v>370</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="113">
@@ -4111,44 +4111,44 @@
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>LINGLONG</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>RD215/70R15C</t>
+          <t>LG215/70R15C</t>
         </is>
       </c>
       <c r="D113" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E113" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F113" s="5">
         <v>0</v>
       </c>
       <c r="G113" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H113" s="6">
-        <v>330</v>
+        <v>370</v>
       </c>
     </row>
     <row outlineLevel="0" r="114">
       <c r="A114" s="4" t="inlineStr">
         <is>
-          <t>225/40R18</t>
+          <t>215/70R15C</t>
         </is>
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>BARUM</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>BM225/40R18</t>
+          <t>RD215/70R15C</t>
         </is>
       </c>
       <c r="D114" s="5">
@@ -4164,7 +4164,7 @@
         <v>0</v>
       </c>
       <c r="H114" s="6">
-        <v>420</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="115">
@@ -4175,28 +4175,28 @@
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>BARUM</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>GD225/40R18</t>
+          <t>BM225/40R18</t>
         </is>
       </c>
       <c r="D115" s="5">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="E115" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F115" s="5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G115" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H115" s="6">
-        <v>480</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="116">
@@ -4207,28 +4207,28 @@
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>HK225/40R18</t>
+          <t>GD225/40R18</t>
         </is>
       </c>
       <c r="D116" s="5">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="E116" s="5">
         <v>4</v>
       </c>
       <c r="F116" s="5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G116" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H116" s="6">
-        <v>450</v>
+        <v>480</v>
       </c>
     </row>
     <row outlineLevel="0" r="117">
@@ -4239,28 +4239,28 @@
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>LASSA</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>LS225/40R18</t>
+          <t>HK225/40R18</t>
         </is>
       </c>
       <c r="D117" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E117" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F117" s="5">
         <v>0</v>
       </c>
       <c r="G117" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H117" s="6">
-        <v>330</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="118">
@@ -4271,28 +4271,28 @@
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>LASSA</t>
         </is>
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>NX225/40R18</t>
+          <t>LS225/40R18</t>
         </is>
       </c>
       <c r="D118" s="5">
         <v>1</v>
       </c>
       <c r="E118" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F118" s="5">
         <v>0</v>
       </c>
       <c r="G118" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H118" s="6">
-        <v>400</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="119">
@@ -4303,19 +4303,19 @@
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>SEMPERIT</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>SP225/40R18</t>
+          <t>NX225/40R18</t>
         </is>
       </c>
       <c r="D119" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E119" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F119" s="5">
         <v>0</v>
@@ -4324,30 +4324,30 @@
         <v>0</v>
       </c>
       <c r="H119" s="6">
-        <v>450</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="120">
       <c r="A120" s="4" t="inlineStr">
         <is>
-          <t>225/40R18RF</t>
+          <t>225/40R18</t>
         </is>
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>SEMPERIT</t>
         </is>
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>GD225/40R18RF</t>
+          <t>SP225/40R18</t>
         </is>
       </c>
       <c r="D120" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E120" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F120" s="5">
         <v>0</v>
@@ -4356,30 +4356,30 @@
         <v>0</v>
       </c>
       <c r="H120" s="6">
-        <v>590</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="121">
       <c r="A121" s="4" t="inlineStr">
         <is>
-          <t>225/45R17</t>
+          <t>225/40R18RF</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>CT225/45R17</t>
+          <t>GD225/40R18RF</t>
         </is>
       </c>
       <c r="D121" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E121" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F121" s="5">
         <v>0</v>
@@ -4388,7 +4388,7 @@
         <v>0</v>
       </c>
       <c r="H121" s="6">
-        <v>400</v>
+        <v>590</v>
       </c>
     </row>
     <row outlineLevel="0" r="122">
@@ -4399,28 +4399,28 @@
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>FULDA</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>FL225/45R17</t>
+          <t>CT225/45R17</t>
         </is>
       </c>
       <c r="D122" s="5">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="E122" s="5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F122" s="5">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G122" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H122" s="6">
-        <v>350</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="123">
@@ -4431,28 +4431,28 @@
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>FULDA</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>GD225/45R17</t>
+          <t>FL225/45R17</t>
         </is>
       </c>
       <c r="D123" s="5">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E123" s="5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F123" s="5">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="G123" s="5">
         <v>4</v>
       </c>
       <c r="H123" s="6">
-        <v>380</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="124">
@@ -4463,44 +4463,44 @@
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>HK225/45R17</t>
+          <t>GD225/45R17</t>
         </is>
       </c>
       <c r="D124" s="5">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="E124" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F124" s="5">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G124" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H124" s="6">
-        <v>350</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="125">
       <c r="A125" s="4" t="inlineStr">
         <is>
-          <t>225/45R18</t>
+          <t>225/45R17</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>DL225/45R18</t>
+          <t>HK225/45R17</t>
         </is>
       </c>
       <c r="D125" s="5">
@@ -4516,7 +4516,7 @@
         <v>0</v>
       </c>
       <c r="H125" s="6">
-        <v>500</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="126">
@@ -4527,28 +4527,28 @@
       </c>
       <c r="B126" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C126" s="4" t="inlineStr">
         <is>
-          <t>GD225/45R18</t>
+          <t>DL225/45R18</t>
         </is>
       </c>
       <c r="D126" s="5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E126" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F126" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G126" s="5">
         <v>0</v>
       </c>
       <c r="H126" s="6">
-        <v>550</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="127">
@@ -4559,108 +4559,108 @@
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>LF225/45R18</t>
+          <t>GD225/45R18</t>
         </is>
       </c>
       <c r="D127" s="5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E127" s="5">
         <v>4</v>
       </c>
       <c r="F127" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G127" s="5">
         <v>0</v>
       </c>
       <c r="H127" s="6">
-        <v>420</v>
+        <v>550</v>
       </c>
     </row>
     <row outlineLevel="0" r="128">
       <c r="A128" s="4" t="inlineStr">
         <is>
-          <t>225/45R18RF</t>
+          <t>225/45R18</t>
         </is>
       </c>
       <c r="B128" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C128" s="4" t="inlineStr">
         <is>
-          <t>GD225/45R18RF</t>
+          <t>LF225/45R18</t>
         </is>
       </c>
       <c r="D128" s="5">
         <v>4</v>
       </c>
       <c r="E128" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F128" s="5">
         <v>0</v>
       </c>
       <c r="G128" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H128" s="6">
-        <v>720</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="129">
       <c r="A129" s="4" t="inlineStr">
         <is>
-          <t>225/45R19</t>
+          <t>225/45R18RF</t>
         </is>
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>CT225/45R19</t>
+          <t>GD225/45R18RF</t>
         </is>
       </c>
       <c r="D129" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E129" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F129" s="5">
         <v>0</v>
       </c>
       <c r="G129" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H129" s="6">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row outlineLevel="0" r="130">
       <c r="A130" s="4" t="inlineStr">
         <is>
-          <t>225/50R17</t>
+          <t>225/45R19</t>
         </is>
       </c>
       <c r="B130" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C130" s="4" t="inlineStr">
         <is>
-          <t>BR225/50R17</t>
+          <t>CT225/45R19</t>
         </is>
       </c>
       <c r="D130" s="5">
@@ -4676,7 +4676,7 @@
         <v>0</v>
       </c>
       <c r="H130" s="6">
-        <v>600</v>
+        <v>780</v>
       </c>
     </row>
     <row outlineLevel="0" r="131">
@@ -4687,28 +4687,28 @@
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>GD225/50R17</t>
+          <t>BR225/50R17</t>
         </is>
       </c>
       <c r="D131" s="5">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E131" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F131" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G131" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H131" s="6">
-        <v>500</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="132">
@@ -4719,60 +4719,60 @@
       </c>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C132" s="4" t="inlineStr">
         <is>
-          <t>HK225/50R17</t>
+          <t>GD225/50R17</t>
         </is>
       </c>
       <c r="D132" s="5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E132" s="5">
         <v>4</v>
       </c>
       <c r="F132" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G132" s="5">
         <v>2</v>
       </c>
       <c r="H132" s="6">
-        <v>400</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="133">
       <c r="A133" s="4" t="inlineStr">
         <is>
-          <t>225/55R16</t>
+          <t>225/50R17</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>DL225/55R16</t>
+          <t>HK225/50R17</t>
         </is>
       </c>
       <c r="D133" s="5">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E133" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F133" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G133" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H133" s="6">
-        <v>450</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="134">
@@ -4783,19 +4783,19 @@
       </c>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C134" s="4" t="inlineStr">
         <is>
-          <t>GD225/55R16</t>
+          <t>DL225/55R16</t>
         </is>
       </c>
       <c r="D134" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E134" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F134" s="5">
         <v>0</v>
@@ -4804,30 +4804,30 @@
         <v>0</v>
       </c>
       <c r="H134" s="6">
-        <v>420</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="135">
       <c r="A135" s="4" t="inlineStr">
         <is>
-          <t>225/55R17</t>
+          <t>225/55R16</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>HK225/55R17</t>
+          <t>GD225/55R16</t>
         </is>
       </c>
       <c r="D135" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E135" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F135" s="5">
         <v>0</v>
@@ -4836,94 +4836,94 @@
         <v>0</v>
       </c>
       <c r="H135" s="6">
-        <v>430</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="136">
       <c r="A136" s="4" t="inlineStr">
         <is>
-          <t>225/55R17RF</t>
+          <t>225/55R17</t>
         </is>
       </c>
       <c r="B136" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C136" s="4" t="inlineStr">
         <is>
-          <t>GD225/55R17RF</t>
+          <t>HK225/55R17</t>
         </is>
       </c>
       <c r="D136" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E136" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F136" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G136" s="5">
         <v>0</v>
       </c>
       <c r="H136" s="6">
-        <v>700</v>
+        <v>430</v>
       </c>
     </row>
     <row outlineLevel="0" r="137">
       <c r="A137" s="4" t="inlineStr">
         <is>
-          <t>225/55R18</t>
+          <t>225/55R17RF</t>
         </is>
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>KUMHO</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>KM225/55R18</t>
+          <t>GD225/55R17RF</t>
         </is>
       </c>
       <c r="D137" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E137" s="5">
         <v>4</v>
       </c>
       <c r="F137" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G137" s="5">
         <v>0</v>
       </c>
       <c r="H137" s="6">
-        <v>450</v>
+        <v>700</v>
       </c>
     </row>
     <row outlineLevel="0" r="138">
       <c r="A138" s="4" t="inlineStr">
         <is>
-          <t>225/55R19</t>
+          <t>225/55R18</t>
         </is>
       </c>
       <c r="B138" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>KUMHO</t>
         </is>
       </c>
       <c r="C138" s="4" t="inlineStr">
         <is>
-          <t>BR225/55R19</t>
+          <t>KM225/55R18</t>
         </is>
       </c>
       <c r="D138" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E138" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F138" s="5">
         <v>0</v>
@@ -4932,7 +4932,7 @@
         <v>0</v>
       </c>
       <c r="H138" s="6">
-        <v>750</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="139">
@@ -4943,19 +4943,19 @@
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>GD225/55R19</t>
+          <t>BR225/55R19</t>
         </is>
       </c>
       <c r="D139" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E139" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F139" s="5">
         <v>0</v>
@@ -4970,21 +4970,21 @@
     <row outlineLevel="0" r="140">
       <c r="A140" s="4" t="inlineStr">
         <is>
-          <t>225/60R17</t>
+          <t>225/55R19</t>
         </is>
       </c>
       <c r="B140" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C140" s="4" t="inlineStr">
         <is>
-          <t>HK225/60R17</t>
+          <t>GD225/55R19</t>
         </is>
       </c>
       <c r="D140" s="5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E140" s="5">
         <v>4</v>
@@ -4993,65 +4993,65 @@
         <v>0</v>
       </c>
       <c r="G140" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H140" s="6">
-        <v>400</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="141">
       <c r="A141" s="4" t="inlineStr">
         <is>
-          <t>225/60R18</t>
+          <t>225/60R17</t>
         </is>
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>GD225/60R18</t>
+          <t>HK225/60R17</t>
         </is>
       </c>
       <c r="D141" s="5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E141" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F141" s="5">
         <v>0</v>
       </c>
       <c r="G141" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H141" s="6">
-        <v>700</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="142">
       <c r="A142" s="4" t="inlineStr">
         <is>
-          <t>225/65R17</t>
+          <t>225/60R18</t>
         </is>
       </c>
       <c r="B142" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C142" s="4" t="inlineStr">
         <is>
-          <t>RD225/65R17</t>
+          <t>GD225/60R18</t>
         </is>
       </c>
       <c r="D142" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E142" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F142" s="5">
         <v>0</v>
@@ -5060,36 +5060,36 @@
         <v>0</v>
       </c>
       <c r="H142" s="6">
-        <v>450</v>
+        <v>700</v>
       </c>
     </row>
     <row outlineLevel="0" r="143">
       <c r="A143" s="4" t="inlineStr">
         <is>
-          <t>225/70R15C</t>
+          <t>225/65R17</t>
         </is>
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>MATADOR</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>MT225/70R15C</t>
+          <t>RD225/65R17</t>
         </is>
       </c>
       <c r="D143" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E143" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F143" s="5">
         <v>0</v>
       </c>
       <c r="G143" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H143" s="6">
         <v>450</v>
@@ -5098,21 +5098,21 @@
     <row outlineLevel="0" r="144">
       <c r="A144" s="4" t="inlineStr">
         <is>
-          <t>225/75R15C</t>
+          <t>225/70R15C</t>
         </is>
       </c>
       <c r="B144" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>MATADOR</t>
         </is>
       </c>
       <c r="C144" s="4" t="inlineStr">
         <is>
-          <t>RD225/75R15C</t>
+          <t>MT225/70R15C</t>
         </is>
       </c>
       <c r="D144" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E144" s="5">
         <v>0</v>
@@ -5121,16 +5121,16 @@
         <v>0</v>
       </c>
       <c r="G144" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H144" s="6">
-        <v>330</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="145">
       <c r="A145" s="4" t="inlineStr">
         <is>
-          <t>235/35R19</t>
+          <t>225/75R15C</t>
         </is>
       </c>
       <c r="B145" s="4" t="inlineStr">
@@ -5140,61 +5140,61 @@
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>RD235/35R19</t>
+          <t>RD225/75R15C</t>
         </is>
       </c>
       <c r="D145" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E145" s="5">
         <v>0</v>
       </c>
       <c r="F145" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G145" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H145" s="6">
-        <v>600</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="146">
       <c r="A146" s="4" t="inlineStr">
         <is>
-          <t>235/40R19</t>
+          <t>235/35R19</t>
         </is>
       </c>
       <c r="B146" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C146" s="4" t="inlineStr">
         <is>
-          <t>GD235/40R19</t>
+          <t>RD235/35R19</t>
         </is>
       </c>
       <c r="D146" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E146" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F146" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G146" s="5">
         <v>0</v>
       </c>
       <c r="H146" s="6">
-        <v>850</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="147">
       <c r="A147" s="4" t="inlineStr">
         <is>
-          <t>235/45R18</t>
+          <t>235/40R19</t>
         </is>
       </c>
       <c r="B147" s="4" t="inlineStr">
@@ -5204,14 +5204,14 @@
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>GD235/45R18</t>
+          <t>GD235/40R19</t>
         </is>
       </c>
       <c r="D147" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E147" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F147" s="5">
         <v>0</v>
@@ -5220,30 +5220,30 @@
         <v>0</v>
       </c>
       <c r="H147" s="6">
-        <v>600</v>
+        <v>850</v>
       </c>
     </row>
     <row outlineLevel="0" r="148">
       <c r="A148" s="4" t="inlineStr">
         <is>
-          <t>235/50R18</t>
+          <t>235/45R18</t>
         </is>
       </c>
       <c r="B148" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C148" s="4" t="inlineStr">
         <is>
-          <t>HK235/50R18</t>
+          <t>GD235/45R18</t>
         </is>
       </c>
       <c r="D148" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E148" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F148" s="5">
         <v>0</v>
@@ -5252,30 +5252,30 @@
         <v>0</v>
       </c>
       <c r="H148" s="6">
-        <v>500</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="149">
       <c r="A149" s="4" t="inlineStr">
         <is>
-          <t>235/50R19</t>
+          <t>235/50R18</t>
         </is>
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>GD235/50R19</t>
+          <t>HK235/50R18</t>
         </is>
       </c>
       <c r="D149" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E149" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F149" s="5">
         <v>0</v>
@@ -5284,13 +5284,13 @@
         <v>0</v>
       </c>
       <c r="H149" s="6">
-        <v>800</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="150">
       <c r="A150" s="4" t="inlineStr">
         <is>
-          <t>235/50R20</t>
+          <t>235/50R19</t>
         </is>
       </c>
       <c r="B150" s="4" t="inlineStr">
@@ -5300,78 +5300,78 @@
       </c>
       <c r="C150" s="4" t="inlineStr">
         <is>
-          <t>GD235/50R20</t>
+          <t>GD235/50R19</t>
         </is>
       </c>
       <c r="D150" s="5">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E150" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F150" s="5">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G150" s="5">
         <v>0</v>
       </c>
       <c r="H150" s="6">
-        <v>1180</v>
+        <v>800</v>
       </c>
     </row>
     <row outlineLevel="0" r="151">
       <c r="A151" s="4" t="inlineStr">
         <is>
-          <t>235/55R17</t>
+          <t>235/50R20</t>
         </is>
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>BR235/55R17</t>
+          <t>GD235/50R20</t>
         </is>
       </c>
       <c r="D151" s="5">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E151" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F151" s="5">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G151" s="5">
         <v>0</v>
       </c>
       <c r="H151" s="6">
-        <v>450</v>
+        <v>1180</v>
       </c>
     </row>
     <row outlineLevel="0" r="152">
       <c r="A152" s="4" t="inlineStr">
         <is>
-          <t>235/55R18</t>
+          <t>235/55R17</t>
         </is>
       </c>
       <c r="B152" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C152" s="4" t="inlineStr">
         <is>
-          <t>HK235/55R18</t>
+          <t>BR235/55R17</t>
         </is>
       </c>
       <c r="D152" s="5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E152" s="5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F152" s="5">
         <v>0</v>
@@ -5380,30 +5380,30 @@
         <v>0</v>
       </c>
       <c r="H152" s="6">
-        <v>480</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="153">
       <c r="A153" s="4" t="inlineStr">
         <is>
-          <t>235/55R19</t>
+          <t>235/55R18</t>
         </is>
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>GD235/55R19</t>
+          <t>HK235/55R18</t>
         </is>
       </c>
       <c r="D153" s="5">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E153" s="5">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F153" s="5">
         <v>0</v>
@@ -5412,7 +5412,7 @@
         <v>0</v>
       </c>
       <c r="H153" s="6">
-        <v>750</v>
+        <v>480</v>
       </c>
     </row>
     <row outlineLevel="0" r="154">
@@ -5423,19 +5423,19 @@
       </c>
       <c r="B154" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C154" s="4" t="inlineStr">
         <is>
-          <t>HK235/55R19</t>
+          <t>GD235/55R19</t>
         </is>
       </c>
       <c r="D154" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E154" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F154" s="5">
         <v>0</v>
@@ -5444,7 +5444,7 @@
         <v>0</v>
       </c>
       <c r="H154" s="6">
-        <v>630</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="155">
@@ -5455,19 +5455,19 @@
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>LF235/55R19</t>
+          <t>HK235/55R19</t>
         </is>
       </c>
       <c r="D155" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E155" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F155" s="5">
         <v>0</v>
@@ -5476,7 +5476,7 @@
         <v>0</v>
       </c>
       <c r="H155" s="6">
-        <v>500</v>
+        <v>630</v>
       </c>
     </row>
     <row outlineLevel="0" r="156">
@@ -5487,19 +5487,19 @@
       </c>
       <c r="B156" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C156" s="4" t="inlineStr">
         <is>
-          <t>NX235/55R19</t>
+          <t>LF235/55R19</t>
         </is>
       </c>
       <c r="D156" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E156" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F156" s="5">
         <v>0</v>
@@ -5508,7 +5508,7 @@
         <v>0</v>
       </c>
       <c r="H156" s="6">
-        <v>600</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="157">
@@ -5519,66 +5519,66 @@
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>RD235/55R19</t>
+          <t>NX235/55R19</t>
         </is>
       </c>
       <c r="D157" s="5">
         <v>2</v>
       </c>
       <c r="E157" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F157" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G157" s="5">
         <v>0</v>
       </c>
       <c r="H157" s="6">
-        <v>500</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="158">
       <c r="A158" s="4" t="inlineStr">
         <is>
-          <t>235/60R16</t>
+          <t>235/55R19</t>
         </is>
       </c>
       <c r="B158" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C158" s="4" t="inlineStr">
         <is>
-          <t>HK235/60R16</t>
+          <t>RD235/55R19</t>
         </is>
       </c>
       <c r="D158" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E158" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F158" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G158" s="5">
         <v>0</v>
       </c>
       <c r="H158" s="6">
-        <v>430</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="159">
       <c r="A159" s="4" t="inlineStr">
         <is>
-          <t>235/60R17</t>
+          <t>235/60R16</t>
         </is>
       </c>
       <c r="B159" s="4" t="inlineStr">
@@ -5588,55 +5588,55 @@
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>HK235/60R17</t>
+          <t>HK235/60R16</t>
         </is>
       </c>
       <c r="D159" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E159" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F159" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G159" s="5">
         <v>0</v>
       </c>
       <c r="H159" s="6">
-        <v>500</v>
+        <v>430</v>
       </c>
     </row>
     <row outlineLevel="0" r="160">
       <c r="A160" s="4" t="inlineStr">
         <is>
-          <t>235/60R18</t>
+          <t>235/60R17</t>
         </is>
       </c>
       <c r="B160" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C160" s="4" t="inlineStr">
         <is>
-          <t>GD235/60R18</t>
+          <t>HK235/60R17</t>
         </is>
       </c>
       <c r="D160" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E160" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F160" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G160" s="5">
         <v>0</v>
       </c>
       <c r="H160" s="6">
-        <v>680</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="161">
@@ -5647,12 +5647,12 @@
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>HK235/60R18</t>
+          <t>GD235/60R18</t>
         </is>
       </c>
       <c r="D161" s="5">
@@ -5668,30 +5668,30 @@
         <v>0</v>
       </c>
       <c r="H161" s="6">
-        <v>550</v>
+        <v>680</v>
       </c>
     </row>
     <row outlineLevel="0" r="162">
       <c r="A162" s="4" t="inlineStr">
         <is>
-          <t>245/40R17</t>
+          <t>235/60R18</t>
         </is>
       </c>
       <c r="B162" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C162" s="4" t="inlineStr">
         <is>
-          <t>GD245/40R17</t>
+          <t>HK235/60R18</t>
         </is>
       </c>
       <c r="D162" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E162" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F162" s="5">
         <v>0</v>
@@ -5700,13 +5700,13 @@
         <v>0</v>
       </c>
       <c r="H162" s="6">
-        <v>400</v>
+        <v>550</v>
       </c>
     </row>
     <row outlineLevel="0" r="163">
       <c r="A163" s="4" t="inlineStr">
         <is>
-          <t>245/40R18</t>
+          <t>245/40R17</t>
         </is>
       </c>
       <c r="B163" s="4" t="inlineStr">
@@ -5716,142 +5716,142 @@
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>GD245/40R18</t>
+          <t>GD245/40R17</t>
         </is>
       </c>
       <c r="D163" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E163" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F163" s="5">
         <v>0</v>
       </c>
       <c r="G163" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H163" s="6">
-        <v>620</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="164">
       <c r="A164" s="4" t="inlineStr">
         <is>
-          <t>245/40R19</t>
+          <t>245/40R18</t>
         </is>
       </c>
       <c r="B164" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C164" s="4" t="inlineStr">
         <is>
-          <t>HK245/40R19</t>
+          <t>GD245/40R18</t>
         </is>
       </c>
       <c r="D164" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E164" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F164" s="5">
         <v>0</v>
       </c>
       <c r="G164" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H164" s="6">
-        <v>750</v>
+        <v>620</v>
       </c>
     </row>
     <row outlineLevel="0" r="165">
       <c r="A165" s="4" t="inlineStr">
         <is>
-          <t>245/40R20</t>
+          <t>245/40R19</t>
         </is>
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>CT245/40R20</t>
+          <t>HK245/40R19</t>
         </is>
       </c>
       <c r="D165" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E165" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F165" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G165" s="5">
         <v>0</v>
       </c>
       <c r="H165" s="6">
-        <v>1050</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="166">
       <c r="A166" s="4" t="inlineStr">
         <is>
-          <t>245/45R17</t>
+          <t>245/40R20</t>
         </is>
       </c>
       <c r="B166" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C166" s="4" t="inlineStr">
         <is>
-          <t>HK245/45R17</t>
+          <t>CT245/40R20</t>
         </is>
       </c>
       <c r="D166" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E166" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F166" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G166" s="5">
         <v>0</v>
       </c>
       <c r="H166" s="6">
-        <v>430</v>
+        <v>1050</v>
       </c>
     </row>
     <row outlineLevel="0" r="167">
       <c r="A167" s="4" t="inlineStr">
         <is>
-          <t>245/45R18</t>
+          <t>245/45R17</t>
         </is>
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>CT245/45R18</t>
+          <t>HK245/45R17</t>
         </is>
       </c>
       <c r="D167" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E167" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F167" s="5">
         <v>0</v>
@@ -5860,7 +5860,7 @@
         <v>0</v>
       </c>
       <c r="H167" s="6">
-        <v>650</v>
+        <v>430</v>
       </c>
     </row>
     <row outlineLevel="0" r="168">
@@ -5871,19 +5871,19 @@
       </c>
       <c r="B168" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C168" s="4" t="inlineStr">
         <is>
-          <t>GD245/45R18</t>
+          <t>CT245/45R18</t>
         </is>
       </c>
       <c r="D168" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E168" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F168" s="5">
         <v>0</v>
@@ -5892,7 +5892,7 @@
         <v>0</v>
       </c>
       <c r="H168" s="6">
-        <v>600</v>
+        <v>650</v>
       </c>
     </row>
     <row outlineLevel="0" r="169">
@@ -5903,19 +5903,19 @@
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>HK245/45R18</t>
+          <t>GD245/45R18</t>
         </is>
       </c>
       <c r="D169" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E169" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F169" s="5">
         <v>0</v>
@@ -5924,30 +5924,30 @@
         <v>0</v>
       </c>
       <c r="H169" s="6">
-        <v>500</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="170">
       <c r="A170" s="4" t="inlineStr">
         <is>
-          <t>245/45R18RF</t>
+          <t>245/45R18</t>
         </is>
       </c>
       <c r="B170" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C170" s="4" t="inlineStr">
         <is>
-          <t>GD245/45R18RF</t>
+          <t>HK245/45R18</t>
         </is>
       </c>
       <c r="D170" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E170" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F170" s="5">
         <v>0</v>
@@ -5956,23 +5956,23 @@
         <v>0</v>
       </c>
       <c r="H170" s="6">
-        <v>720</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="171">
       <c r="A171" s="4" t="inlineStr">
         <is>
-          <t>245/45R19</t>
+          <t>245/45R18RF</t>
         </is>
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t>BR245/45R19</t>
+          <t>GD245/45R18RF</t>
         </is>
       </c>
       <c r="D171" s="5">
@@ -5988,7 +5988,7 @@
         <v>0</v>
       </c>
       <c r="H171" s="6">
-        <v>790</v>
+        <v>720</v>
       </c>
     </row>
     <row outlineLevel="0" r="172">
@@ -5999,44 +5999,44 @@
       </c>
       <c r="B172" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C172" s="4" t="inlineStr">
         <is>
-          <t>RD245/45R19</t>
+          <t>BR245/45R19</t>
         </is>
       </c>
       <c r="D172" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E172" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F172" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G172" s="5">
         <v>0</v>
       </c>
       <c r="H172" s="6">
-        <v>450</v>
+        <v>790</v>
       </c>
     </row>
     <row outlineLevel="0" r="173">
       <c r="A173" s="4" t="inlineStr">
         <is>
-          <t>245/45R20</t>
+          <t>245/45R19</t>
         </is>
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>HK245/45R20</t>
+          <t>RD245/45R19</t>
         </is>
       </c>
       <c r="D173" s="5">
@@ -6052,94 +6052,94 @@
         <v>0</v>
       </c>
       <c r="H173" s="6">
-        <v>750</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="174">
       <c r="A174" s="4" t="inlineStr">
         <is>
-          <t>245/65R17</t>
+          <t>245/45R20</t>
         </is>
       </c>
       <c r="B174" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C174" s="4" t="inlineStr">
         <is>
-          <t>NX245/65R17</t>
+          <t>HK245/45R20</t>
         </is>
       </c>
       <c r="D174" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E174" s="5">
         <v>0</v>
       </c>
       <c r="F174" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G174" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H174" s="6">
-        <v>600</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="175">
       <c r="A175" s="4" t="inlineStr">
         <is>
-          <t>255/35R19</t>
+          <t>245/65R17</t>
         </is>
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>DL255/35R19</t>
+          <t>NX245/65R17</t>
         </is>
       </c>
       <c r="D175" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E175" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F175" s="5">
         <v>0</v>
       </c>
       <c r="G175" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H175" s="6">
-        <v>700</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="176">
       <c r="A176" s="4" t="inlineStr">
         <is>
-          <t>255/35R19RF</t>
+          <t>255/35R19</t>
         </is>
       </c>
       <c r="B176" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C176" s="4" t="inlineStr">
         <is>
-          <t>CT255/35R19RF</t>
+          <t>DL255/35R19</t>
         </is>
       </c>
       <c r="D176" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E176" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F176" s="5">
         <v>0</v>
@@ -6148,7 +6148,7 @@
         <v>0</v>
       </c>
       <c r="H176" s="6">
-        <v>950</v>
+        <v>700</v>
       </c>
     </row>
     <row outlineLevel="0" r="177">
@@ -6159,19 +6159,19 @@
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>GD255/35R19RF</t>
+          <t>CT255/35R19RF</t>
         </is>
       </c>
       <c r="D177" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E177" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F177" s="5">
         <v>0</v>
@@ -6186,39 +6186,39 @@
     <row outlineLevel="0" r="178">
       <c r="A178" s="4" t="inlineStr">
         <is>
-          <t>255/50R19</t>
+          <t>255/35R19RF</t>
         </is>
       </c>
       <c r="B178" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C178" s="4" t="inlineStr">
         <is>
-          <t>CT255/50R19</t>
+          <t>GD255/35R19RF</t>
         </is>
       </c>
       <c r="D178" s="5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E178" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F178" s="5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G178" s="5">
         <v>0</v>
       </c>
       <c r="H178" s="6">
-        <v>750</v>
+        <v>950</v>
       </c>
     </row>
     <row outlineLevel="0" r="179">
       <c r="A179" s="4" t="inlineStr">
         <is>
-          <t>255/50R20</t>
+          <t>255/50R19</t>
         </is>
       </c>
       <c r="B179" s="4" t="inlineStr">
@@ -6228,29 +6228,29 @@
       </c>
       <c r="C179" s="4" t="inlineStr">
         <is>
-          <t>CT255/50R20</t>
+          <t>CT255/50R19</t>
         </is>
       </c>
       <c r="D179" s="5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E179" s="5">
         <v>0</v>
       </c>
       <c r="F179" s="5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G179" s="5">
         <v>0</v>
       </c>
       <c r="H179" s="6">
-        <v>900</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="180">
       <c r="A180" s="4" t="inlineStr">
         <is>
-          <t>255/55R19</t>
+          <t>255/50R20</t>
         </is>
       </c>
       <c r="B180" s="4" t="inlineStr">
@@ -6260,23 +6260,23 @@
       </c>
       <c r="C180" s="4" t="inlineStr">
         <is>
-          <t>CT255/55R19</t>
+          <t>CT255/50R20</t>
         </is>
       </c>
       <c r="D180" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E180" s="5">
         <v>0</v>
       </c>
       <c r="F180" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G180" s="5">
         <v>0</v>
       </c>
       <c r="H180" s="6">
-        <v>750</v>
+        <v>900</v>
       </c>
     </row>
     <row outlineLevel="0" r="181">
@@ -6287,98 +6287,98 @@
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C181" s="4" t="inlineStr">
         <is>
-          <t>DL255/55R19</t>
+          <t>CT255/55R19</t>
         </is>
       </c>
       <c r="D181" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E181" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F181" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G181" s="5">
         <v>0</v>
       </c>
       <c r="H181" s="6">
-        <v>700</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="182">
       <c r="A182" s="4" t="inlineStr">
         <is>
-          <t>255/70R16</t>
+          <t>255/55R19</t>
         </is>
       </c>
       <c r="B182" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C182" s="4" t="inlineStr">
         <is>
-          <t>RD255/70R16</t>
+          <t>DL255/55R19</t>
         </is>
       </c>
       <c r="D182" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E182" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F182" s="5">
         <v>0</v>
       </c>
       <c r="G182" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H182" s="6">
-        <v>500</v>
+        <v>700</v>
       </c>
     </row>
     <row outlineLevel="0" r="183">
       <c r="A183" s="4" t="inlineStr">
         <is>
-          <t>265/35R18</t>
+          <t>255/70R16</t>
         </is>
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C183" s="4" t="inlineStr">
         <is>
-          <t>GD265/35R18</t>
+          <t>RD255/70R16</t>
         </is>
       </c>
       <c r="D183" s="5">
         <v>1</v>
       </c>
       <c r="E183" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F183" s="5">
         <v>0</v>
       </c>
       <c r="G183" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H183" s="6">
-        <v>700</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="184">
       <c r="A184" s="4" t="inlineStr">
         <is>
-          <t>265/50R20</t>
+          <t>265/35R18</t>
         </is>
       </c>
       <c r="B184" s="4" t="inlineStr">
@@ -6388,29 +6388,29 @@
       </c>
       <c r="C184" s="4" t="inlineStr">
         <is>
-          <t>GD265/50R20</t>
+          <t>GD265/35R18</t>
         </is>
       </c>
       <c r="D184" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E184" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F184" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G184" s="5">
         <v>0</v>
       </c>
       <c r="H184" s="6">
-        <v>1150</v>
+        <v>700</v>
       </c>
     </row>
     <row outlineLevel="0" r="185">
       <c r="A185" s="4" t="inlineStr">
         <is>
-          <t>275/35R19RF</t>
+          <t>265/50R20</t>
         </is>
       </c>
       <c r="B185" s="4" t="inlineStr">
@@ -6420,71 +6420,71 @@
       </c>
       <c r="C185" s="4" t="inlineStr">
         <is>
-          <t>GD275/35R19RF</t>
+          <t>GD265/50R20</t>
         </is>
       </c>
       <c r="D185" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E185" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F185" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G185" s="5">
         <v>0</v>
       </c>
       <c r="H185" s="6">
-        <v>1</v>
+        <v>1150</v>
       </c>
     </row>
     <row outlineLevel="0" r="186">
       <c r="A186" s="4" t="inlineStr">
         <is>
-          <t>275/35R20</t>
+          <t>275/35R19RF</t>
         </is>
       </c>
       <c r="B186" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C186" s="4" t="inlineStr">
         <is>
-          <t>CT275/35R20</t>
+          <t>GD275/35R19RF</t>
         </is>
       </c>
       <c r="D186" s="5">
         <v>2</v>
       </c>
       <c r="E186" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F186" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G186" s="5">
         <v>0</v>
       </c>
       <c r="H186" s="6">
-        <v>980</v>
+        <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="187">
       <c r="A187" s="4" t="inlineStr">
         <is>
-          <t>275/40R20</t>
+          <t>275/35R20</t>
         </is>
       </c>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C187" s="4" t="inlineStr">
         <is>
-          <t>HK275/40R20</t>
+          <t>CT275/35R20</t>
         </is>
       </c>
       <c r="D187" s="5">
@@ -6500,23 +6500,23 @@
         <v>0</v>
       </c>
       <c r="H187" s="6">
-        <v>770</v>
+        <v>980</v>
       </c>
     </row>
     <row outlineLevel="0" r="188">
       <c r="A188" s="4" t="inlineStr">
         <is>
-          <t>275/50R21</t>
+          <t>275/40R20</t>
         </is>
       </c>
       <c r="B188" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C188" s="4" t="inlineStr">
         <is>
-          <t>GD275/50R21</t>
+          <t>HK275/40R20</t>
         </is>
       </c>
       <c r="D188" s="5">
@@ -6532,23 +6532,23 @@
         <v>0</v>
       </c>
       <c r="H188" s="6">
-        <v>1</v>
+        <v>770</v>
       </c>
     </row>
     <row outlineLevel="0" r="189">
       <c r="A189" s="4" t="inlineStr">
         <is>
-          <t>295/35R21</t>
+          <t>275/50R21</t>
         </is>
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C189" s="4" t="inlineStr">
         <is>
-          <t>CT295/35R21</t>
+          <t>GD275/50R21</t>
         </is>
       </c>
       <c r="D189" s="5">
@@ -6564,7 +6564,7 @@
         <v>0</v>
       </c>
       <c r="H189" s="6">
-        <v>1150</v>
+        <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="190">
@@ -6575,59 +6575,91 @@
       </c>
       <c r="B190" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C190" s="4" t="inlineStr">
         <is>
-          <t>GD295/35R21</t>
+          <t>CT295/35R21</t>
         </is>
       </c>
       <c r="D190" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E190" s="5">
         <v>0</v>
       </c>
       <c r="F190" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G190" s="5">
         <v>0</v>
       </c>
       <c r="H190" s="6">
-        <v>980</v>
+        <v>1150</v>
       </c>
     </row>
     <row outlineLevel="0" r="191">
       <c r="A191" s="4" t="inlineStr">
         <is>
-          <t>500R12</t>
+          <t>295/35R21</t>
         </is>
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C191" s="4" t="inlineStr">
         <is>
-          <t>RD500R12</t>
+          <t>GD295/35R21</t>
         </is>
       </c>
       <c r="D191" s="5">
         <v>3</v>
       </c>
       <c r="E191" s="5">
+        <v>0</v>
+      </c>
+      <c r="F191" s="5">
         <v>3</v>
       </c>
-      <c r="F191" s="5">
-        <v>0</v>
-      </c>
       <c r="G191" s="5">
         <v>0</v>
       </c>
       <c r="H191" s="6">
+        <v>980</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="192">
+      <c r="A192" s="4" t="inlineStr">
+        <is>
+          <t>500R12</t>
+        </is>
+      </c>
+      <c r="B192" s="4" t="inlineStr">
+        <is>
+          <t>RADIAL</t>
+        </is>
+      </c>
+      <c r="C192" s="4" t="inlineStr">
+        <is>
+          <t>RD500R12</t>
+        </is>
+      </c>
+      <c r="D192" s="5">
+        <v>3</v>
+      </c>
+      <c r="E192" s="5">
+        <v>3</v>
+      </c>
+      <c r="F192" s="5">
+        <v>0</v>
+      </c>
+      <c r="G192" s="5">
+        <v>0</v>
+      </c>
+      <c r="H192" s="6">
         <v>300</v>
       </c>
     </row>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -3134,10 +3134,10 @@
         <v>6</v>
       </c>
       <c r="F82" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G82" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H82" s="6">
         <v>300</v>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -600,10 +600,10 @@
         </is>
       </c>
       <c r="D3" s="5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E3" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F3" s="5">
         <v>0</v>
@@ -1080,10 +1080,10 @@
         </is>
       </c>
       <c r="D18" s="5">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E18" s="5">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F18" s="5">
         <v>0</v>
@@ -1752,7 +1752,7 @@
         </is>
       </c>
       <c r="D39" s="5">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E39" s="5">
         <v>75</v>
@@ -1761,7 +1761,7 @@
         <v>0</v>
       </c>
       <c r="G39" s="5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H39" s="6">
         <v>220</v>
@@ -2008,13 +2008,13 @@
         </is>
       </c>
       <c r="D47" s="5">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E47" s="5">
         <v>2</v>
       </c>
       <c r="F47" s="5">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G47" s="5">
         <v>4</v>
@@ -2744,7 +2744,7 @@
         </is>
       </c>
       <c r="D70" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E70" s="5">
         <v>0</v>
@@ -2753,7 +2753,7 @@
         <v>0</v>
       </c>
       <c r="G70" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H70" s="6">
         <v>290</v>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -600,7 +600,7 @@
         </is>
       </c>
       <c r="D3" s="5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E3" s="5">
         <v>4</v>
@@ -609,7 +609,7 @@
         <v>0</v>
       </c>
       <c r="G3" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H3" s="6">
         <v>180</v>
@@ -4472,10 +4472,10 @@
         </is>
       </c>
       <c r="D124" s="5">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E124" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F124" s="5">
         <v>14</v>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -496,7 +496,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H192"/>
+  <dimension ref="A1:H191"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col customWidth="true" min="1" max="1" width="13.8359375"/>
@@ -1048,16 +1048,16 @@
         </is>
       </c>
       <c r="D17" s="5">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="E17" s="5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F17" s="5">
         <v>35</v>
       </c>
       <c r="G17" s="5">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H17" s="6">
         <v>190</v>
@@ -1098,17 +1098,17 @@
     <row outlineLevel="0" r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>175/70R13</t>
+          <t>175/70R14</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>WESTLAKE</t>
+          <t>MATADOR</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>WL175/70R13</t>
+          <t>MT175/70R14</t>
         </is>
       </c>
       <c r="D19" s="5">
@@ -1124,7 +1124,7 @@
         <v>0</v>
       </c>
       <c r="H19" s="6">
-        <v>200</v>
+        <v>230</v>
       </c>
     </row>
     <row outlineLevel="0" r="20">
@@ -1135,60 +1135,60 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>MATADOR</t>
+          <t>WESTLAKE</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>MT175/70R14</t>
+          <t>WL175/70R14</t>
         </is>
       </c>
       <c r="D20" s="5">
-        <v>4</v>
+        <v>43</v>
       </c>
       <c r="E20" s="5">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="F20" s="5">
         <v>0</v>
       </c>
       <c r="G20" s="5">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H20" s="6">
-        <v>230</v>
+        <v>200</v>
       </c>
     </row>
     <row outlineLevel="0" r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>175/70R14</t>
+          <t>185/55R15</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>WESTLAKE</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>WL175/70R14</t>
+          <t>BR185/55R15</t>
         </is>
       </c>
       <c r="D21" s="5">
-        <v>43</v>
+        <v>2</v>
       </c>
       <c r="E21" s="5">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="F21" s="5">
         <v>0</v>
       </c>
       <c r="G21" s="5">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H21" s="6">
-        <v>200</v>
+        <v>370</v>
       </c>
     </row>
     <row outlineLevel="0" r="22">
@@ -1199,34 +1199,34 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>BR185/55R15</t>
+          <t>GD185/55R15</t>
         </is>
       </c>
       <c r="D22" s="5">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="E22" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F22" s="5">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G22" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H22" s="6">
-        <v>370</v>
+        <v>340</v>
       </c>
     </row>
     <row outlineLevel="0" r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>185/55R15</t>
+          <t>185/55R16</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
@@ -1236,29 +1236,29 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>GD185/55R15</t>
+          <t>GD185/55R16</t>
         </is>
       </c>
       <c r="D23" s="5">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="E23" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F23" s="5">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G23" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H23" s="6">
-        <v>340</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>185/55R16</t>
+          <t>185/60R14</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
@@ -1268,23 +1268,23 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>GD185/55R16</t>
+          <t>GD185/60R14</t>
         </is>
       </c>
       <c r="D24" s="5">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="E24" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F24" s="5">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G24" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H24" s="6">
-        <v>420</v>
+        <v>230</v>
       </c>
     </row>
     <row outlineLevel="0" r="25">
@@ -1295,25 +1295,25 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>GD185/60R14</t>
+          <t>NX185/60R14</t>
         </is>
       </c>
       <c r="D25" s="5">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="E25" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F25" s="5">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G25" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H25" s="6">
         <v>230</v>
@@ -1322,24 +1322,24 @@
     <row outlineLevel="0" r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>185/60R14</t>
+          <t>185/60R15</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>MATADOR</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>NX185/60R14</t>
+          <t>MT185/60R15</t>
         </is>
       </c>
       <c r="D26" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E26" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F26" s="5">
         <v>0</v>
@@ -1348,7 +1348,7 @@
         <v>0</v>
       </c>
       <c r="H26" s="6">
-        <v>230</v>
+        <v>280</v>
       </c>
     </row>
     <row outlineLevel="0" r="27">
@@ -1359,124 +1359,124 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>MATADOR</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>MT185/60R15</t>
+          <t>RD185/60R15</t>
         </is>
       </c>
       <c r="D27" s="5">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E27" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F27" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G27" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H27" s="6">
-        <v>280</v>
+        <v>230</v>
       </c>
     </row>
     <row outlineLevel="0" r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>185/60R15</t>
+          <t>185/60R16</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>RD185/60R15</t>
+          <t>GD185/60R16</t>
         </is>
       </c>
       <c r="D28" s="5">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E28" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F28" s="5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G28" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H28" s="6">
-        <v>230</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>185/60R16</t>
+          <t>185/65R14</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>GD185/60R16</t>
+          <t>RD185/65R14</t>
         </is>
       </c>
       <c r="D29" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E29" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F29" s="5">
         <v>0</v>
       </c>
       <c r="G29" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H29" s="6">
-        <v>420</v>
+        <v>200</v>
       </c>
     </row>
     <row outlineLevel="0" r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>185/65R14</t>
+          <t>185/65R15</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>RD185/65R14</t>
+          <t>CT185/65R15</t>
         </is>
       </c>
       <c r="D30" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E30" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F30" s="5">
         <v>0</v>
       </c>
       <c r="G30" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H30" s="6">
-        <v>200</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="31">
@@ -1487,28 +1487,28 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>DOUBLESTAR</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>CT185/65R15</t>
+          <t>DS185/65R15</t>
         </is>
       </c>
       <c r="D31" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E31" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F31" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G31" s="5">
         <v>0</v>
       </c>
       <c r="H31" s="6">
-        <v>400</v>
+        <v>210</v>
       </c>
     </row>
     <row outlineLevel="0" r="32">
@@ -1519,28 +1519,28 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>DOUBLESTAR</t>
+          <t>FULDA</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>DS185/65R15</t>
+          <t>FL185/65R15</t>
         </is>
       </c>
       <c r="D32" s="5">
-        <v>5</v>
+        <v>134</v>
       </c>
       <c r="E32" s="5">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F32" s="5">
-        <v>5</v>
+        <v>108</v>
       </c>
       <c r="G32" s="5">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="H32" s="6">
-        <v>210</v>
+        <v>245</v>
       </c>
     </row>
     <row outlineLevel="0" r="33">
@@ -1551,28 +1551,28 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>FULDA</t>
+          <t>GOODRIDE</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>FL185/65R15</t>
+          <t>GR185/65R15</t>
         </is>
       </c>
       <c r="D33" s="5">
-        <v>136</v>
+        <v>11</v>
       </c>
       <c r="E33" s="5">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F33" s="5">
-        <v>108</v>
+        <v>3</v>
       </c>
       <c r="G33" s="5">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="H33" s="6">
-        <v>245</v>
+        <v>230</v>
       </c>
     </row>
     <row outlineLevel="0" r="34">
@@ -1583,28 +1583,28 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>GOODRIDE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>GR185/65R15</t>
+          <t>GD185/65R15</t>
         </is>
       </c>
       <c r="D34" s="5">
-        <v>11</v>
+        <v>58</v>
       </c>
       <c r="E34" s="5">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F34" s="5">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="G34" s="5">
         <v>4</v>
       </c>
       <c r="H34" s="6">
-        <v>230</v>
+        <v>260</v>
       </c>
     </row>
     <row outlineLevel="0" r="35">
@@ -1615,28 +1615,28 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>GD185/65R15</t>
+          <t>HK185/65R15</t>
         </is>
       </c>
       <c r="D35" s="5">
-        <v>58</v>
+        <v>5</v>
       </c>
       <c r="E35" s="5">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F35" s="5">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G35" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H35" s="6">
-        <v>260</v>
+        <v>250</v>
       </c>
     </row>
     <row outlineLevel="0" r="36">
@@ -1647,16 +1647,16 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>HK185/65R15</t>
+          <t>LF185/65R15</t>
         </is>
       </c>
       <c r="D36" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E36" s="5">
         <v>4</v>
@@ -1665,7 +1665,7 @@
         <v>0</v>
       </c>
       <c r="G36" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H36" s="6">
         <v>250</v>
@@ -1679,25 +1679,25 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>SEMPERIT</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>LF185/65R15</t>
+          <t>SP185/65R15</t>
         </is>
       </c>
       <c r="D37" s="5">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="E37" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F37" s="5">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G37" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H37" s="6">
         <v>250</v>
@@ -1711,60 +1711,60 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>SEMPERIT</t>
+          <t>WESTLAKE</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>SP185/65R15</t>
+          <t>WL185/65R15</t>
         </is>
       </c>
       <c r="D38" s="5">
-        <v>26</v>
+        <v>77</v>
       </c>
       <c r="E38" s="5">
-        <v>5</v>
+        <v>75</v>
       </c>
       <c r="F38" s="5">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G38" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H38" s="6">
-        <v>250</v>
+        <v>220</v>
       </c>
     </row>
     <row outlineLevel="0" r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>185/65R15</t>
+          <t>185/70R14</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>WESTLAKE</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>WL185/65R15</t>
+          <t>RD185/70R14</t>
         </is>
       </c>
       <c r="D39" s="5">
-        <v>77</v>
+        <v>2</v>
       </c>
       <c r="E39" s="5">
-        <v>75</v>
+        <v>1</v>
       </c>
       <c r="F39" s="5">
         <v>0</v>
       </c>
       <c r="G39" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H39" s="6">
-        <v>220</v>
+        <v>230</v>
       </c>
     </row>
     <row outlineLevel="0" r="40">
@@ -1775,60 +1775,60 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>WESTLAKE</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>RD185/70R14</t>
+          <t>WL185/70R14</t>
         </is>
       </c>
       <c r="D40" s="5">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E40" s="5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F40" s="5">
         <v>0</v>
       </c>
       <c r="G40" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H40" s="6">
-        <v>230</v>
+        <v>220</v>
       </c>
     </row>
     <row outlineLevel="0" r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>185/70R14</t>
+          <t>195/50R15</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>WESTLAKE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>WL185/70R14</t>
+          <t>GD195/50R15</t>
         </is>
       </c>
       <c r="D41" s="5">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E41" s="5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F41" s="5">
         <v>0</v>
       </c>
       <c r="G41" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H41" s="6">
-        <v>220</v>
+        <v>290</v>
       </c>
     </row>
     <row outlineLevel="0" r="42">
@@ -1839,28 +1839,28 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>SEMPERIT</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>GD195/50R15</t>
+          <t>SP195/50R15</t>
         </is>
       </c>
       <c r="D42" s="5">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="E42" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F42" s="5">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G42" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H42" s="6">
-        <v>290</v>
+        <v>260</v>
       </c>
     </row>
     <row outlineLevel="0" r="43">
@@ -1871,66 +1871,66 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>SEMPERIT</t>
+          <t>WESTLAKE</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>SP195/50R15</t>
+          <t>WL195/50R15</t>
         </is>
       </c>
       <c r="D43" s="5">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E43" s="5">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F43" s="5">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G43" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H43" s="6">
-        <v>260</v>
+        <v>225</v>
       </c>
     </row>
     <row outlineLevel="0" r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>195/50R15</t>
+          <t>195/50R16</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>WESTLAKE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>WL195/50R15</t>
+          <t>GD195/50R16</t>
         </is>
       </c>
       <c r="D44" s="5">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E44" s="5">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F44" s="5">
         <v>0</v>
       </c>
       <c r="G44" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H44" s="6">
-        <v>225</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>195/50R16</t>
+          <t>195/55R16</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
@@ -1940,23 +1940,23 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>GD195/50R16</t>
+          <t>GD195/55R16</t>
         </is>
       </c>
       <c r="D45" s="5">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="E45" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F45" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G45" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H45" s="6">
-        <v>330</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="46">
@@ -1967,19 +1967,19 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>GD195/55R16</t>
+          <t>HK195/55R16</t>
         </is>
       </c>
       <c r="D46" s="5">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E46" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F46" s="5">
         <v>5</v>
@@ -1988,7 +1988,7 @@
         <v>4</v>
       </c>
       <c r="H46" s="6">
-        <v>350</v>
+        <v>290</v>
       </c>
     </row>
     <row outlineLevel="0" r="47">
@@ -1999,28 +1999,28 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>LASSA</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>HK195/55R16</t>
+          <t>LS195/55R16</t>
         </is>
       </c>
       <c r="D47" s="5">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E47" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F47" s="5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G47" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H47" s="6">
-        <v>290</v>
+        <v>280</v>
       </c>
     </row>
     <row outlineLevel="0" r="48">
@@ -2031,19 +2031,19 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>LASSA</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>LS195/55R16</t>
+          <t>NX195/55R16</t>
         </is>
       </c>
       <c r="D48" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E48" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F48" s="5">
         <v>0</v>
@@ -2052,7 +2052,7 @@
         <v>0</v>
       </c>
       <c r="H48" s="6">
-        <v>280</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="49">
@@ -2063,92 +2063,92 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>NX195/55R16</t>
+          <t>RD195/55R16</t>
         </is>
       </c>
       <c r="D49" s="5">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E49" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F49" s="5">
         <v>0</v>
       </c>
       <c r="G49" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H49" s="6">
-        <v>300</v>
+        <v>250</v>
       </c>
     </row>
     <row outlineLevel="0" r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>195/55R16</t>
+          <t>195/60R16</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>RD195/55R16</t>
+          <t>GD195/60R16</t>
         </is>
       </c>
       <c r="D50" s="5">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="E50" s="5">
         <v>4</v>
       </c>
       <c r="F50" s="5">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G50" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H50" s="6">
-        <v>250</v>
+        <v>355</v>
       </c>
     </row>
     <row outlineLevel="0" r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>195/60R16</t>
+          <t>195/65R15</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>DOUBLESTAR</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>GD195/60R16</t>
+          <t>DS195/65R15</t>
         </is>
       </c>
       <c r="D51" s="5">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E51" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F51" s="5">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="G51" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H51" s="6">
-        <v>355</v>
+        <v>230</v>
       </c>
     </row>
     <row outlineLevel="0" r="52">
@@ -2159,22 +2159,22 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>DOUBLESTAR</t>
+          <t>GOODRIDE</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>DS195/65R15</t>
+          <t>GR195/65R15</t>
         </is>
       </c>
       <c r="D52" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E52" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F52" s="5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G52" s="5">
         <v>0</v>
@@ -2191,28 +2191,28 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>GOODRIDE</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>GR195/65R15</t>
+          <t>HK195/65R15</t>
         </is>
       </c>
       <c r="D53" s="5">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E53" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F53" s="5">
         <v>0</v>
       </c>
       <c r="G53" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H53" s="6">
-        <v>230</v>
+        <v>260</v>
       </c>
     </row>
     <row outlineLevel="0" r="54">
@@ -2223,28 +2223,28 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>LASSA</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>HK195/65R15</t>
+          <t>LS195/65R15</t>
         </is>
       </c>
       <c r="D54" s="5">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E54" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F54" s="5">
         <v>0</v>
       </c>
       <c r="G54" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H54" s="6">
-        <v>260</v>
+        <v>250</v>
       </c>
     </row>
     <row outlineLevel="0" r="55">
@@ -2255,19 +2255,19 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>LASSA</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>LS195/65R15</t>
+          <t>NX195/65R15</t>
         </is>
       </c>
       <c r="D55" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E55" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F55" s="5">
         <v>0</v>
@@ -2276,7 +2276,7 @@
         <v>0</v>
       </c>
       <c r="H55" s="6">
-        <v>250</v>
+        <v>230</v>
       </c>
     </row>
     <row outlineLevel="0" r="56">
@@ -2287,25 +2287,25 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>NX195/65R15</t>
+          <t>RD195/65R15</t>
         </is>
       </c>
       <c r="D56" s="5">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E56" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F56" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G56" s="5">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H56" s="6">
         <v>230</v>
@@ -2319,121 +2319,121 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>SEMPERIT</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>RD195/65R15</t>
+          <t>SP195/65R15</t>
         </is>
       </c>
       <c r="D57" s="5">
-        <v>15</v>
+        <v>89</v>
       </c>
       <c r="E57" s="5">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F57" s="5">
-        <v>1</v>
+        <v>69</v>
       </c>
       <c r="G57" s="5">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H57" s="6">
-        <v>230</v>
+        <v>250</v>
       </c>
     </row>
     <row outlineLevel="0" r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>195/65R15</t>
+          <t>195/70R15C</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>SEMPERIT</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>SP195/65R15</t>
+          <t>LF195/70R15C</t>
         </is>
       </c>
       <c r="D58" s="5">
-        <v>89</v>
+        <v>4</v>
       </c>
       <c r="E58" s="5">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F58" s="5">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="G58" s="5">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H58" s="6">
-        <v>250</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>195/70R15C</t>
+          <t>195/75R16C</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>GOODRIDE</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>LF195/70R15C</t>
+          <t>GR195/75R16C</t>
         </is>
       </c>
       <c r="D59" s="5">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E59" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F59" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G59" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H59" s="6">
-        <v>300</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>195/75R16C</t>
+          <t>195R15C</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>GOODRIDE</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>GR195/75R16C</t>
+          <t>RD195R15C</t>
         </is>
       </c>
       <c r="D60" s="5">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E60" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F60" s="5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G60" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H60" s="6">
         <v>350</v>
@@ -2442,33 +2442,33 @@
     <row outlineLevel="0" r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>195R15C</t>
+          <t>205/45R17</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>RD195R15C</t>
+          <t>CT205/45R17</t>
         </is>
       </c>
       <c r="D61" s="5">
         <v>1</v>
       </c>
       <c r="E61" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F61" s="5">
         <v>0</v>
       </c>
       <c r="G61" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H61" s="6">
-        <v>350</v>
+        <v>550</v>
       </c>
     </row>
     <row outlineLevel="0" r="62">
@@ -2479,28 +2479,28 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>FULDA</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>CT205/45R17</t>
+          <t>FL205/45R17</t>
         </is>
       </c>
       <c r="D62" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E62" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F62" s="5">
         <v>0</v>
       </c>
       <c r="G62" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H62" s="6">
-        <v>550</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="63">
@@ -2511,28 +2511,28 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>FULDA</t>
+          <t>GOODRIDE</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>FL205/45R17</t>
+          <t>GR205/45R17</t>
         </is>
       </c>
       <c r="D63" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E63" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F63" s="5">
         <v>0</v>
       </c>
       <c r="G63" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H63" s="6">
-        <v>380</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="64">
@@ -2543,28 +2543,28 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>GOODRIDE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>GR205/45R17</t>
+          <t>GD205/45R17</t>
         </is>
       </c>
       <c r="D64" s="5">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="E64" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F64" s="5">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G64" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H64" s="6">
-        <v>300</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="65">
@@ -2575,28 +2575,28 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>GD205/45R17</t>
+          <t>NX205/45R17</t>
         </is>
       </c>
       <c r="D65" s="5">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="E65" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F65" s="5">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G65" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H65" s="6">
-        <v>450</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="66">
@@ -2607,83 +2607,83 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>NX205/45R17</t>
+          <t>RD205/45R17</t>
         </is>
       </c>
       <c r="D66" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E66" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F66" s="5">
         <v>0</v>
       </c>
       <c r="G66" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H66" s="6">
-        <v>380</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>205/45R17</t>
+          <t>205/50R17</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>RD205/45R17</t>
+          <t>CT205/50R17</t>
         </is>
       </c>
       <c r="D67" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E67" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F67" s="5">
         <v>0</v>
       </c>
       <c r="G67" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H67" s="6">
-        <v>300</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>205/50R17</t>
+          <t>205/55R16</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>AMINE</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>CT205/50R17</t>
+          <t>AM205/55R16</t>
         </is>
       </c>
       <c r="D68" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E68" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F68" s="5">
         <v>0</v>
@@ -2692,7 +2692,7 @@
         <v>0</v>
       </c>
       <c r="H68" s="6">
-        <v>450</v>
+        <v>240</v>
       </c>
     </row>
     <row outlineLevel="0" r="69">
@@ -2703,28 +2703,28 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>AMINE</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>AM205/55R16</t>
+          <t>BR205/55R16</t>
         </is>
       </c>
       <c r="D69" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E69" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F69" s="5">
         <v>0</v>
       </c>
       <c r="G69" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H69" s="6">
-        <v>240</v>
+        <v>290</v>
       </c>
     </row>
     <row outlineLevel="0" r="70">
@@ -2735,28 +2735,28 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>DOUBLESTAR</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>BR205/55R16</t>
+          <t>DS205/55R16</t>
         </is>
       </c>
       <c r="D70" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E70" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F70" s="5">
         <v>0</v>
       </c>
       <c r="G70" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H70" s="6">
-        <v>290</v>
+        <v>230</v>
       </c>
     </row>
     <row outlineLevel="0" r="71">
@@ -2767,28 +2767,28 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>DOUBLESTAR</t>
+          <t>FULDA</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>DS205/55R16</t>
+          <t>FL205/55R16</t>
         </is>
       </c>
       <c r="D71" s="5">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="E71" s="5">
         <v>4</v>
       </c>
       <c r="F71" s="5">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G71" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H71" s="6">
-        <v>230</v>
+        <v>250</v>
       </c>
     </row>
     <row outlineLevel="0" r="72">
@@ -2799,25 +2799,25 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>FULDA</t>
+          <t>GOODRIDE</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>FL205/55R16</t>
+          <t>GR205/55R16</t>
         </is>
       </c>
       <c r="D72" s="5">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="E72" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F72" s="5">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G72" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H72" s="6">
         <v>250</v>
@@ -2831,28 +2831,28 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>GOODRIDE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>GR205/55R16</t>
+          <t>GD205/55R16</t>
         </is>
       </c>
       <c r="D73" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E73" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" s="5">
         <v>0</v>
       </c>
       <c r="G73" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H73" s="6">
-        <v>250</v>
+        <v>280</v>
       </c>
     </row>
     <row outlineLevel="0" r="74">
@@ -2863,28 +2863,28 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>GD205/55R16</t>
+          <t>HK205/55R16</t>
         </is>
       </c>
       <c r="D74" s="5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E74" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F74" s="5">
         <v>0</v>
       </c>
       <c r="G74" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H74" s="6">
-        <v>280</v>
+        <v>260</v>
       </c>
     </row>
     <row outlineLevel="0" r="75">
@@ -2895,48 +2895,48 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>HK205/55R16</t>
+          <t>RD205/55R16</t>
         </is>
       </c>
       <c r="D75" s="5">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E75" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F75" s="5">
         <v>0</v>
       </c>
       <c r="G75" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H75" s="6">
-        <v>260</v>
+        <v>230</v>
       </c>
     </row>
     <row outlineLevel="0" r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>205/55R16</t>
+          <t>205/55R16RF</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>RD205/55R16</t>
+          <t>GD205/55R16RF</t>
         </is>
       </c>
       <c r="D76" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E76" s="5">
         <v>0</v>
@@ -2945,16 +2945,16 @@
         <v>0</v>
       </c>
       <c r="G76" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H76" s="6">
-        <v>230</v>
+        <v>480</v>
       </c>
     </row>
     <row outlineLevel="0" r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>205/55R16RF</t>
+          <t>205/55R17</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
@@ -2964,23 +2964,23 @@
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>GD205/55R16RF</t>
+          <t>GD205/55R17</t>
         </is>
       </c>
       <c r="D77" s="5">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="E77" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F77" s="5">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G77" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H77" s="6">
-        <v>480</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="78">
@@ -2991,44 +2991,44 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>GD205/55R17</t>
+          <t>NX205/55R17</t>
         </is>
       </c>
       <c r="D78" s="5">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="E78" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F78" s="5">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G78" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H78" s="6">
-        <v>450</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>205/55R17</t>
+          <t>205/60R16</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>NX205/55R17</t>
+          <t>DL205/60R16</t>
         </is>
       </c>
       <c r="D79" s="5">
@@ -3044,7 +3044,7 @@
         <v>0</v>
       </c>
       <c r="H79" s="6">
-        <v>400</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="80">
@@ -3055,28 +3055,28 @@
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>DL205/60R16</t>
+          <t>GD205/60R16</t>
         </is>
       </c>
       <c r="D80" s="5">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E80" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F80" s="5">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G80" s="5">
         <v>0</v>
       </c>
       <c r="H80" s="6">
-        <v>330</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="81">
@@ -3087,28 +3087,28 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>GD205/60R16</t>
+          <t>HK205/60R16</t>
         </is>
       </c>
       <c r="D81" s="5">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E81" s="5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F81" s="5">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G81" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H81" s="6">
-        <v>380</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="82">
@@ -3119,25 +3119,25 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>HK205/60R16</t>
+          <t>LF205/60R16</t>
         </is>
       </c>
       <c r="D82" s="5">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E82" s="5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F82" s="5">
         <v>0</v>
       </c>
       <c r="G82" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H82" s="6">
         <v>300</v>
@@ -3146,17 +3146,17 @@
     <row outlineLevel="0" r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>205/60R16</t>
+          <t>205/65R15</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>LF205/60R16</t>
+          <t>HK205/65R15</t>
         </is>
       </c>
       <c r="D83" s="5">
@@ -3172,30 +3172,30 @@
         <v>0</v>
       </c>
       <c r="H83" s="6">
-        <v>300</v>
+        <v>270</v>
       </c>
     </row>
     <row outlineLevel="0" r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>205/65R15</t>
+          <t>205/65R16</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>HK205/65R15</t>
+          <t>BR205/65R16</t>
         </is>
       </c>
       <c r="D84" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E84" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F84" s="5">
         <v>0</v>
@@ -3204,7 +3204,7 @@
         <v>0</v>
       </c>
       <c r="H84" s="6">
-        <v>270</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="85">
@@ -3215,19 +3215,19 @@
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>BR205/65R16</t>
+          <t>HK205/65R16</t>
         </is>
       </c>
       <c r="D85" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E85" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F85" s="5">
         <v>0</v>
@@ -3236,39 +3236,39 @@
         <v>0</v>
       </c>
       <c r="H85" s="6">
-        <v>420</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>205/65R16</t>
+          <t>215/40R18</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>HK205/65R16</t>
+          <t>GD215/40R18</t>
         </is>
       </c>
       <c r="D86" s="5">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E86" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F86" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G86" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H86" s="6">
-        <v>380</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="87">
@@ -3279,44 +3279,44 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>GD215/40R18</t>
+          <t>HK215/40R18</t>
         </is>
       </c>
       <c r="D87" s="5">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E87" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F87" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G87" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H87" s="6">
-        <v>600</v>
+        <v>490</v>
       </c>
     </row>
     <row outlineLevel="0" r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>215/40R18</t>
+          <t>215/45R16</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>HK215/40R18</t>
+          <t>GD215/45R16</t>
         </is>
       </c>
       <c r="D88" s="5">
@@ -3332,13 +3332,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="6">
-        <v>490</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>215/45R16</t>
+          <t>215/45R17</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
@@ -3348,14 +3348,14 @@
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>GD215/45R16</t>
+          <t>GD215/45R17</t>
         </is>
       </c>
       <c r="D89" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E89" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F89" s="5">
         <v>0</v>
@@ -3364,7 +3364,7 @@
         <v>0</v>
       </c>
       <c r="H89" s="6">
-        <v>450</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="90">
@@ -3375,25 +3375,25 @@
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>GD215/45R17</t>
+          <t>HK215/45R17</t>
         </is>
       </c>
       <c r="D90" s="5">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="E90" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F90" s="5">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G90" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H90" s="6">
         <v>400</v>
@@ -3407,28 +3407,28 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>IRIS</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>HK215/45R17</t>
+          <t>IR215/45R17</t>
         </is>
       </c>
       <c r="D91" s="5">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="E91" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F91" s="5">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G91" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H91" s="6">
-        <v>400</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="92">
@@ -3439,28 +3439,28 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>IRIS</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>IR215/45R17</t>
+          <t>LF215/45R17</t>
         </is>
       </c>
       <c r="D92" s="5">
         <v>1</v>
       </c>
       <c r="E92" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F92" s="5">
         <v>0</v>
       </c>
       <c r="G92" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H92" s="6">
-        <v>300</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="93">
@@ -3471,83 +3471,83 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>LF215/45R17</t>
+          <t>NX215/45R17</t>
         </is>
       </c>
       <c r="D93" s="5">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E93" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F93" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G93" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H93" s="6">
-        <v>350</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>215/45R17</t>
+          <t>215/45R18</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>NX215/45R17</t>
+          <t>GD215/45R18</t>
         </is>
       </c>
       <c r="D94" s="5">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E94" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F94" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G94" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H94" s="6">
-        <v>380</v>
+        <v>550</v>
       </c>
     </row>
     <row outlineLevel="0" r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>215/45R18</t>
+          <t>215/50R17</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>GD215/45R18</t>
+          <t>BR215/50R17</t>
         </is>
       </c>
       <c r="D95" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E95" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F95" s="5">
         <v>0</v>
@@ -3556,7 +3556,7 @@
         <v>0</v>
       </c>
       <c r="H95" s="6">
-        <v>550</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="96">
@@ -3567,28 +3567,28 @@
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>BR215/50R17</t>
+          <t>GD215/50R17</t>
         </is>
       </c>
       <c r="D96" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E96" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F96" s="5">
         <v>0</v>
       </c>
       <c r="G96" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H96" s="6">
-        <v>450</v>
+        <v>470</v>
       </c>
     </row>
     <row outlineLevel="0" r="97">
@@ -3599,16 +3599,16 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>GD215/50R17</t>
+          <t>HK215/50R17</t>
         </is>
       </c>
       <c r="D97" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E97" s="5">
         <v>3</v>
@@ -3617,26 +3617,26 @@
         <v>0</v>
       </c>
       <c r="G97" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H97" s="6">
-        <v>470</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="98">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>215/50R17</t>
+          <t>215/50R18</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>HK215/50R17</t>
+          <t>GD215/50R18</t>
         </is>
       </c>
       <c r="D98" s="5">
@@ -3652,13 +3652,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="6">
-        <v>400</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>215/50R18</t>
+          <t>215/55R16</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
@@ -3668,14 +3668,14 @@
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>GD215/50R18</t>
+          <t>GD215/55R16</t>
         </is>
       </c>
       <c r="D99" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E99" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F99" s="5">
         <v>0</v>
@@ -3684,7 +3684,7 @@
         <v>0</v>
       </c>
       <c r="H99" s="6">
-        <v>600</v>
+        <v>440</v>
       </c>
     </row>
     <row outlineLevel="0" r="100">
@@ -3695,12 +3695,12 @@
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>GD215/55R16</t>
+          <t>LF215/55R16</t>
         </is>
       </c>
       <c r="D100" s="5">
@@ -3716,23 +3716,23 @@
         <v>0</v>
       </c>
       <c r="H100" s="6">
-        <v>440</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>215/55R16</t>
+          <t>215/55R17</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>LF215/55R16</t>
+          <t>BR215/55R17</t>
         </is>
       </c>
       <c r="D101" s="5">
@@ -3748,7 +3748,7 @@
         <v>0</v>
       </c>
       <c r="H101" s="6">
-        <v>350</v>
+        <v>480</v>
       </c>
     </row>
     <row outlineLevel="0" r="102">
@@ -3759,19 +3759,19 @@
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>BR215/55R17</t>
+          <t>HK215/55R17</t>
         </is>
       </c>
       <c r="D102" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E102" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F102" s="5">
         <v>0</v>
@@ -3780,30 +3780,30 @@
         <v>0</v>
       </c>
       <c r="H102" s="6">
-        <v>480</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>215/55R17</t>
+          <t>215/55R18</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>HK215/55R17</t>
+          <t>GD215/55R18</t>
         </is>
       </c>
       <c r="D103" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E103" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F103" s="5">
         <v>0</v>
@@ -3812,30 +3812,30 @@
         <v>0</v>
       </c>
       <c r="H103" s="6">
-        <v>420</v>
+        <v>580</v>
       </c>
     </row>
     <row outlineLevel="0" r="104">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>215/55R18</t>
+          <t>215/60R16</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>GD215/55R18</t>
+          <t>BR215/60R16</t>
         </is>
       </c>
       <c r="D104" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E104" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F104" s="5">
         <v>0</v>
@@ -3844,7 +3844,7 @@
         <v>0</v>
       </c>
       <c r="H104" s="6">
-        <v>580</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="105">
@@ -3855,25 +3855,25 @@
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>BR215/60R16</t>
+          <t>DL215/60R16</t>
         </is>
       </c>
       <c r="D105" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E105" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F105" s="5">
         <v>0</v>
       </c>
       <c r="G105" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H105" s="6">
         <v>350</v>
@@ -3887,28 +3887,28 @@
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>DL215/60R16</t>
+          <t>HK215/60R16</t>
         </is>
       </c>
       <c r="D106" s="5">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E106" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F106" s="5">
         <v>0</v>
       </c>
       <c r="G106" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H106" s="6">
-        <v>350</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="107">
@@ -3919,25 +3919,25 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>HK215/60R16</t>
+          <t>NX215/60R16</t>
         </is>
       </c>
       <c r="D107" s="5">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E107" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F107" s="5">
         <v>0</v>
       </c>
       <c r="G107" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H107" s="6">
         <v>330</v>
@@ -3946,65 +3946,65 @@
     <row outlineLevel="0" r="108">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>215/60R16</t>
+          <t>215/60R17</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>NX215/60R16</t>
+          <t>RD215/60R17</t>
         </is>
       </c>
       <c r="D108" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E108" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F108" s="5">
         <v>0</v>
       </c>
       <c r="G108" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H108" s="6">
-        <v>330</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="109">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>215/60R17</t>
+          <t>215/65R16</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>RD215/60R17</t>
+          <t>GD215/65R16</t>
         </is>
       </c>
       <c r="D109" s="5">
         <v>1</v>
       </c>
       <c r="E109" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F109" s="5">
         <v>0</v>
       </c>
       <c r="G109" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H109" s="6">
-        <v>300</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="110">
@@ -4015,44 +4015,44 @@
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>GD215/65R16</t>
+          <t>HK215/65R16</t>
         </is>
       </c>
       <c r="D110" s="5">
         <v>1</v>
       </c>
       <c r="E110" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F110" s="5">
         <v>0</v>
       </c>
       <c r="G110" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H110" s="6">
-        <v>380</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="111">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>215/65R16</t>
+          <t>215/65R17</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>MICHELIN</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>HK215/65R16</t>
+          <t>MC215/65R17</t>
         </is>
       </c>
       <c r="D111" s="5">
@@ -4068,39 +4068,39 @@
         <v>0</v>
       </c>
       <c r="H111" s="6">
-        <v>330</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="112">
       <c r="A112" s="4" t="inlineStr">
         <is>
-          <t>215/65R17</t>
+          <t>215/70R15C</t>
         </is>
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>MICHELIN</t>
+          <t>LINGLONG</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>MC215/65R17</t>
+          <t>LG215/70R15C</t>
         </is>
       </c>
       <c r="D112" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E112" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F112" s="5">
         <v>0</v>
       </c>
       <c r="G112" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H112" s="6">
-        <v>600</v>
+        <v>370</v>
       </c>
     </row>
     <row outlineLevel="0" r="113">
@@ -4111,44 +4111,44 @@
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>LINGLONG</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>LG215/70R15C</t>
+          <t>RD215/70R15C</t>
         </is>
       </c>
       <c r="D113" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E113" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F113" s="5">
         <v>0</v>
       </c>
       <c r="G113" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H113" s="6">
-        <v>370</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="114">
       <c r="A114" s="4" t="inlineStr">
         <is>
-          <t>215/70R15C</t>
+          <t>225/40R18</t>
         </is>
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>BARUM</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>RD215/70R15C</t>
+          <t>BM225/40R18</t>
         </is>
       </c>
       <c r="D114" s="5">
@@ -4164,7 +4164,7 @@
         <v>0</v>
       </c>
       <c r="H114" s="6">
-        <v>330</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="115">
@@ -4175,28 +4175,28 @@
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>BARUM</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>BM225/40R18</t>
+          <t>GD225/40R18</t>
         </is>
       </c>
       <c r="D115" s="5">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="E115" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F115" s="5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G115" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H115" s="6">
-        <v>420</v>
+        <v>480</v>
       </c>
     </row>
     <row outlineLevel="0" r="116">
@@ -4207,28 +4207,28 @@
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>GD225/40R18</t>
+          <t>HK225/40R18</t>
         </is>
       </c>
       <c r="D116" s="5">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="E116" s="5">
         <v>4</v>
       </c>
       <c r="F116" s="5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G116" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H116" s="6">
-        <v>480</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="117">
@@ -4239,28 +4239,28 @@
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>LASSA</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>HK225/40R18</t>
+          <t>LS225/40R18</t>
         </is>
       </c>
       <c r="D117" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E117" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F117" s="5">
         <v>0</v>
       </c>
       <c r="G117" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H117" s="6">
-        <v>450</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="118">
@@ -4271,28 +4271,28 @@
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>LASSA</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>LS225/40R18</t>
+          <t>NX225/40R18</t>
         </is>
       </c>
       <c r="D118" s="5">
         <v>1</v>
       </c>
       <c r="E118" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F118" s="5">
         <v>0</v>
       </c>
       <c r="G118" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H118" s="6">
-        <v>330</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="119">
@@ -4303,12 +4303,12 @@
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>SEMPERIT</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>NX225/40R18</t>
+          <t>SP225/40R18</t>
         </is>
       </c>
       <c r="D119" s="5">
@@ -4324,30 +4324,30 @@
         <v>0</v>
       </c>
       <c r="H119" s="6">
-        <v>400</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="120">
       <c r="A120" s="4" t="inlineStr">
         <is>
-          <t>225/40R18</t>
+          <t>225/40R18RF</t>
         </is>
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>SEMPERIT</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>SP225/40R18</t>
+          <t>GD225/40R18RF</t>
         </is>
       </c>
       <c r="D120" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E120" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F120" s="5">
         <v>0</v>
@@ -4356,30 +4356,30 @@
         <v>0</v>
       </c>
       <c r="H120" s="6">
-        <v>450</v>
+        <v>590</v>
       </c>
     </row>
     <row outlineLevel="0" r="121">
       <c r="A121" s="4" t="inlineStr">
         <is>
-          <t>225/40R18RF</t>
+          <t>225/45R17</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>GD225/40R18RF</t>
+          <t>CT225/45R17</t>
         </is>
       </c>
       <c r="D121" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E121" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F121" s="5">
         <v>0</v>
@@ -4388,7 +4388,7 @@
         <v>0</v>
       </c>
       <c r="H121" s="6">
-        <v>590</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="122">
@@ -4399,28 +4399,28 @@
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>FULDA</t>
         </is>
       </c>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>CT225/45R17</t>
+          <t>FL225/45R17</t>
         </is>
       </c>
       <c r="D122" s="5">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="E122" s="5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F122" s="5">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G122" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H122" s="6">
-        <v>400</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="123">
@@ -4431,28 +4431,28 @@
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>FULDA</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>FL225/45R17</t>
+          <t>GD225/45R17</t>
         </is>
       </c>
       <c r="D123" s="5">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E123" s="5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F123" s="5">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G123" s="5">
         <v>4</v>
       </c>
       <c r="H123" s="6">
-        <v>350</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="124">
@@ -4463,44 +4463,44 @@
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>GD225/45R17</t>
+          <t>HK225/45R17</t>
         </is>
       </c>
       <c r="D124" s="5">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="E124" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F124" s="5">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G124" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H124" s="6">
-        <v>380</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="125">
       <c r="A125" s="4" t="inlineStr">
         <is>
-          <t>225/45R17</t>
+          <t>225/45R18</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>HK225/45R17</t>
+          <t>DL225/45R18</t>
         </is>
       </c>
       <c r="D125" s="5">
@@ -4516,7 +4516,7 @@
         <v>0</v>
       </c>
       <c r="H125" s="6">
-        <v>350</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="126">
@@ -4527,28 +4527,28 @@
       </c>
       <c r="B126" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C126" s="4" t="inlineStr">
         <is>
-          <t>DL225/45R18</t>
+          <t>GD225/45R18</t>
         </is>
       </c>
       <c r="D126" s="5">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E126" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F126" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G126" s="5">
         <v>0</v>
       </c>
       <c r="H126" s="6">
-        <v>500</v>
+        <v>550</v>
       </c>
     </row>
     <row outlineLevel="0" r="127">
@@ -4559,108 +4559,108 @@
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>GD225/45R18</t>
+          <t>LF225/45R18</t>
         </is>
       </c>
       <c r="D127" s="5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E127" s="5">
         <v>4</v>
       </c>
       <c r="F127" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G127" s="5">
         <v>0</v>
       </c>
       <c r="H127" s="6">
-        <v>550</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="128">
       <c r="A128" s="4" t="inlineStr">
         <is>
-          <t>225/45R18</t>
+          <t>225/45R18RF</t>
         </is>
       </c>
       <c r="B128" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C128" s="4" t="inlineStr">
         <is>
-          <t>LF225/45R18</t>
+          <t>GD225/45R18RF</t>
         </is>
       </c>
       <c r="D128" s="5">
         <v>4</v>
       </c>
       <c r="E128" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F128" s="5">
         <v>0</v>
       </c>
       <c r="G128" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H128" s="6">
-        <v>420</v>
+        <v>720</v>
       </c>
     </row>
     <row outlineLevel="0" r="129">
       <c r="A129" s="4" t="inlineStr">
         <is>
-          <t>225/45R18RF</t>
+          <t>225/45R19</t>
         </is>
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>GD225/45R18RF</t>
+          <t>CT225/45R19</t>
         </is>
       </c>
       <c r="D129" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E129" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F129" s="5">
         <v>0</v>
       </c>
       <c r="G129" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H129" s="6">
-        <v>720</v>
+        <v>780</v>
       </c>
     </row>
     <row outlineLevel="0" r="130">
       <c r="A130" s="4" t="inlineStr">
         <is>
-          <t>225/45R19</t>
+          <t>225/50R17</t>
         </is>
       </c>
       <c r="B130" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C130" s="4" t="inlineStr">
         <is>
-          <t>CT225/45R19</t>
+          <t>BR225/50R17</t>
         </is>
       </c>
       <c r="D130" s="5">
@@ -4676,7 +4676,7 @@
         <v>0</v>
       </c>
       <c r="H130" s="6">
-        <v>780</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="131">
@@ -4687,28 +4687,28 @@
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>BR225/50R17</t>
+          <t>GD225/50R17</t>
         </is>
       </c>
       <c r="D131" s="5">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E131" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F131" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G131" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H131" s="6">
-        <v>600</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="132">
@@ -4719,60 +4719,60 @@
       </c>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C132" s="4" t="inlineStr">
         <is>
-          <t>GD225/50R17</t>
+          <t>HK225/50R17</t>
         </is>
       </c>
       <c r="D132" s="5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E132" s="5">
         <v>4</v>
       </c>
       <c r="F132" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G132" s="5">
         <v>2</v>
       </c>
       <c r="H132" s="6">
-        <v>500</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="133">
       <c r="A133" s="4" t="inlineStr">
         <is>
-          <t>225/50R17</t>
+          <t>225/55R16</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>HK225/50R17</t>
+          <t>DL225/55R16</t>
         </is>
       </c>
       <c r="D133" s="5">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E133" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F133" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G133" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H133" s="6">
-        <v>400</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="134">
@@ -4783,19 +4783,19 @@
       </c>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C134" s="4" t="inlineStr">
         <is>
-          <t>DL225/55R16</t>
+          <t>GD225/55R16</t>
         </is>
       </c>
       <c r="D134" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E134" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F134" s="5">
         <v>0</v>
@@ -4804,30 +4804,30 @@
         <v>0</v>
       </c>
       <c r="H134" s="6">
-        <v>450</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="135">
       <c r="A135" s="4" t="inlineStr">
         <is>
-          <t>225/55R16</t>
+          <t>225/55R17</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>GD225/55R16</t>
+          <t>HK225/55R17</t>
         </is>
       </c>
       <c r="D135" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E135" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F135" s="5">
         <v>0</v>
@@ -4836,94 +4836,94 @@
         <v>0</v>
       </c>
       <c r="H135" s="6">
-        <v>420</v>
+        <v>430</v>
       </c>
     </row>
     <row outlineLevel="0" r="136">
       <c r="A136" s="4" t="inlineStr">
         <is>
-          <t>225/55R17</t>
+          <t>225/55R17RF</t>
         </is>
       </c>
       <c r="B136" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C136" s="4" t="inlineStr">
         <is>
-          <t>HK225/55R17</t>
+          <t>GD225/55R17RF</t>
         </is>
       </c>
       <c r="D136" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E136" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F136" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G136" s="5">
         <v>0</v>
       </c>
       <c r="H136" s="6">
-        <v>430</v>
+        <v>700</v>
       </c>
     </row>
     <row outlineLevel="0" r="137">
       <c r="A137" s="4" t="inlineStr">
         <is>
-          <t>225/55R17RF</t>
+          <t>225/55R18</t>
         </is>
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>KUMHO</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>GD225/55R17RF</t>
+          <t>KM225/55R18</t>
         </is>
       </c>
       <c r="D137" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E137" s="5">
         <v>4</v>
       </c>
       <c r="F137" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G137" s="5">
         <v>0</v>
       </c>
       <c r="H137" s="6">
-        <v>700</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="138">
       <c r="A138" s="4" t="inlineStr">
         <is>
-          <t>225/55R18</t>
+          <t>225/55R19</t>
         </is>
       </c>
       <c r="B138" s="4" t="inlineStr">
         <is>
-          <t>KUMHO</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C138" s="4" t="inlineStr">
         <is>
-          <t>KM225/55R18</t>
+          <t>BR225/55R19</t>
         </is>
       </c>
       <c r="D138" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E138" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F138" s="5">
         <v>0</v>
@@ -4932,7 +4932,7 @@
         <v>0</v>
       </c>
       <c r="H138" s="6">
-        <v>450</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="139">
@@ -4943,19 +4943,19 @@
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>BR225/55R19</t>
+          <t>GD225/55R19</t>
         </is>
       </c>
       <c r="D139" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E139" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F139" s="5">
         <v>0</v>
@@ -4970,21 +4970,21 @@
     <row outlineLevel="0" r="140">
       <c r="A140" s="4" t="inlineStr">
         <is>
-          <t>225/55R19</t>
+          <t>225/60R17</t>
         </is>
       </c>
       <c r="B140" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C140" s="4" t="inlineStr">
         <is>
-          <t>GD225/55R19</t>
+          <t>HK225/60R17</t>
         </is>
       </c>
       <c r="D140" s="5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E140" s="5">
         <v>4</v>
@@ -4993,65 +4993,65 @@
         <v>0</v>
       </c>
       <c r="G140" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H140" s="6">
-        <v>750</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="141">
       <c r="A141" s="4" t="inlineStr">
         <is>
-          <t>225/60R17</t>
+          <t>225/60R18</t>
         </is>
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>HK225/60R17</t>
+          <t>GD225/60R18</t>
         </is>
       </c>
       <c r="D141" s="5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E141" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F141" s="5">
         <v>0</v>
       </c>
       <c r="G141" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H141" s="6">
-        <v>400</v>
+        <v>700</v>
       </c>
     </row>
     <row outlineLevel="0" r="142">
       <c r="A142" s="4" t="inlineStr">
         <is>
-          <t>225/60R18</t>
+          <t>225/65R17</t>
         </is>
       </c>
       <c r="B142" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C142" s="4" t="inlineStr">
         <is>
-          <t>GD225/60R18</t>
+          <t>RD225/65R17</t>
         </is>
       </c>
       <c r="D142" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E142" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F142" s="5">
         <v>0</v>
@@ -5060,36 +5060,36 @@
         <v>0</v>
       </c>
       <c r="H142" s="6">
-        <v>700</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="143">
       <c r="A143" s="4" t="inlineStr">
         <is>
-          <t>225/65R17</t>
+          <t>225/70R15C</t>
         </is>
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>MATADOR</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>RD225/65R17</t>
+          <t>MT225/70R15C</t>
         </is>
       </c>
       <c r="D143" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E143" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F143" s="5">
         <v>0</v>
       </c>
       <c r="G143" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H143" s="6">
         <v>450</v>
@@ -5098,21 +5098,21 @@
     <row outlineLevel="0" r="144">
       <c r="A144" s="4" t="inlineStr">
         <is>
-          <t>225/70R15C</t>
+          <t>225/75R15C</t>
         </is>
       </c>
       <c r="B144" s="4" t="inlineStr">
         <is>
-          <t>MATADOR</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C144" s="4" t="inlineStr">
         <is>
-          <t>MT225/70R15C</t>
+          <t>RD225/75R15C</t>
         </is>
       </c>
       <c r="D144" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E144" s="5">
         <v>0</v>
@@ -5121,16 +5121,16 @@
         <v>0</v>
       </c>
       <c r="G144" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H144" s="6">
-        <v>450</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="145">
       <c r="A145" s="4" t="inlineStr">
         <is>
-          <t>225/75R15C</t>
+          <t>235/35R19</t>
         </is>
       </c>
       <c r="B145" s="4" t="inlineStr">
@@ -5140,61 +5140,61 @@
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>RD225/75R15C</t>
+          <t>RD235/35R19</t>
         </is>
       </c>
       <c r="D145" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E145" s="5">
         <v>0</v>
       </c>
       <c r="F145" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G145" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H145" s="6">
-        <v>330</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="146">
       <c r="A146" s="4" t="inlineStr">
         <is>
-          <t>235/35R19</t>
+          <t>235/40R19</t>
         </is>
       </c>
       <c r="B146" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C146" s="4" t="inlineStr">
         <is>
-          <t>RD235/35R19</t>
+          <t>GD235/40R19</t>
         </is>
       </c>
       <c r="D146" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E146" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F146" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G146" s="5">
         <v>0</v>
       </c>
       <c r="H146" s="6">
-        <v>600</v>
+        <v>850</v>
       </c>
     </row>
     <row outlineLevel="0" r="147">
       <c r="A147" s="4" t="inlineStr">
         <is>
-          <t>235/40R19</t>
+          <t>235/45R18</t>
         </is>
       </c>
       <c r="B147" s="4" t="inlineStr">
@@ -5204,14 +5204,14 @@
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>GD235/40R19</t>
+          <t>GD235/45R18</t>
         </is>
       </c>
       <c r="D147" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E147" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F147" s="5">
         <v>0</v>
@@ -5220,30 +5220,30 @@
         <v>0</v>
       </c>
       <c r="H147" s="6">
-        <v>850</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="148">
       <c r="A148" s="4" t="inlineStr">
         <is>
-          <t>235/45R18</t>
+          <t>235/50R18</t>
         </is>
       </c>
       <c r="B148" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C148" s="4" t="inlineStr">
         <is>
-          <t>GD235/45R18</t>
+          <t>HK235/50R18</t>
         </is>
       </c>
       <c r="D148" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E148" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F148" s="5">
         <v>0</v>
@@ -5252,30 +5252,30 @@
         <v>0</v>
       </c>
       <c r="H148" s="6">
-        <v>600</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="149">
       <c r="A149" s="4" t="inlineStr">
         <is>
-          <t>235/50R18</t>
+          <t>235/50R19</t>
         </is>
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>HK235/50R18</t>
+          <t>GD235/50R19</t>
         </is>
       </c>
       <c r="D149" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E149" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F149" s="5">
         <v>0</v>
@@ -5284,13 +5284,13 @@
         <v>0</v>
       </c>
       <c r="H149" s="6">
-        <v>500</v>
+        <v>800</v>
       </c>
     </row>
     <row outlineLevel="0" r="150">
       <c r="A150" s="4" t="inlineStr">
         <is>
-          <t>235/50R19</t>
+          <t>235/50R20</t>
         </is>
       </c>
       <c r="B150" s="4" t="inlineStr">
@@ -5300,78 +5300,78 @@
       </c>
       <c r="C150" s="4" t="inlineStr">
         <is>
-          <t>GD235/50R19</t>
+          <t>GD235/50R20</t>
         </is>
       </c>
       <c r="D150" s="5">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E150" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F150" s="5">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G150" s="5">
         <v>0</v>
       </c>
       <c r="H150" s="6">
-        <v>800</v>
+        <v>1180</v>
       </c>
     </row>
     <row outlineLevel="0" r="151">
       <c r="A151" s="4" t="inlineStr">
         <is>
-          <t>235/50R20</t>
+          <t>235/55R17</t>
         </is>
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>GD235/50R20</t>
+          <t>BR235/55R17</t>
         </is>
       </c>
       <c r="D151" s="5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E151" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F151" s="5">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G151" s="5">
         <v>0</v>
       </c>
       <c r="H151" s="6">
-        <v>1180</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="152">
       <c r="A152" s="4" t="inlineStr">
         <is>
-          <t>235/55R17</t>
+          <t>235/55R18</t>
         </is>
       </c>
       <c r="B152" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C152" s="4" t="inlineStr">
         <is>
-          <t>BR235/55R17</t>
+          <t>HK235/55R18</t>
         </is>
       </c>
       <c r="D152" s="5">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E152" s="5">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F152" s="5">
         <v>0</v>
@@ -5380,30 +5380,30 @@
         <v>0</v>
       </c>
       <c r="H152" s="6">
-        <v>450</v>
+        <v>480</v>
       </c>
     </row>
     <row outlineLevel="0" r="153">
       <c r="A153" s="4" t="inlineStr">
         <is>
-          <t>235/55R18</t>
+          <t>235/55R19</t>
         </is>
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>HK235/55R18</t>
+          <t>GD235/55R19</t>
         </is>
       </c>
       <c r="D153" s="5">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E153" s="5">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F153" s="5">
         <v>0</v>
@@ -5412,7 +5412,7 @@
         <v>0</v>
       </c>
       <c r="H153" s="6">
-        <v>480</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="154">
@@ -5423,19 +5423,19 @@
       </c>
       <c r="B154" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C154" s="4" t="inlineStr">
         <is>
-          <t>GD235/55R19</t>
+          <t>HK235/55R19</t>
         </is>
       </c>
       <c r="D154" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E154" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F154" s="5">
         <v>0</v>
@@ -5444,7 +5444,7 @@
         <v>0</v>
       </c>
       <c r="H154" s="6">
-        <v>750</v>
+        <v>630</v>
       </c>
     </row>
     <row outlineLevel="0" r="155">
@@ -5455,19 +5455,19 @@
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>HK235/55R19</t>
+          <t>LF235/55R19</t>
         </is>
       </c>
       <c r="D155" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E155" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F155" s="5">
         <v>0</v>
@@ -5476,7 +5476,7 @@
         <v>0</v>
       </c>
       <c r="H155" s="6">
-        <v>630</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="156">
@@ -5487,19 +5487,19 @@
       </c>
       <c r="B156" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C156" s="4" t="inlineStr">
         <is>
-          <t>LF235/55R19</t>
+          <t>NX235/55R19</t>
         </is>
       </c>
       <c r="D156" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E156" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F156" s="5">
         <v>0</v>
@@ -5508,7 +5508,7 @@
         <v>0</v>
       </c>
       <c r="H156" s="6">
-        <v>500</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="157">
@@ -5519,66 +5519,66 @@
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>NX235/55R19</t>
+          <t>RD235/55R19</t>
         </is>
       </c>
       <c r="D157" s="5">
         <v>2</v>
       </c>
       <c r="E157" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F157" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G157" s="5">
         <v>0</v>
       </c>
       <c r="H157" s="6">
-        <v>600</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="158">
       <c r="A158" s="4" t="inlineStr">
         <is>
-          <t>235/55R19</t>
+          <t>235/60R16</t>
         </is>
       </c>
       <c r="B158" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C158" s="4" t="inlineStr">
         <is>
-          <t>RD235/55R19</t>
+          <t>HK235/60R16</t>
         </is>
       </c>
       <c r="D158" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E158" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F158" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G158" s="5">
         <v>0</v>
       </c>
       <c r="H158" s="6">
-        <v>500</v>
+        <v>430</v>
       </c>
     </row>
     <row outlineLevel="0" r="159">
       <c r="A159" s="4" t="inlineStr">
         <is>
-          <t>235/60R16</t>
+          <t>235/60R17</t>
         </is>
       </c>
       <c r="B159" s="4" t="inlineStr">
@@ -5588,55 +5588,55 @@
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>HK235/60R16</t>
+          <t>HK235/60R17</t>
         </is>
       </c>
       <c r="D159" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E159" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F159" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G159" s="5">
         <v>0</v>
       </c>
       <c r="H159" s="6">
-        <v>430</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="160">
       <c r="A160" s="4" t="inlineStr">
         <is>
-          <t>235/60R17</t>
+          <t>235/60R18</t>
         </is>
       </c>
       <c r="B160" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C160" s="4" t="inlineStr">
         <is>
-          <t>HK235/60R17</t>
+          <t>GD235/60R18</t>
         </is>
       </c>
       <c r="D160" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E160" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F160" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G160" s="5">
         <v>0</v>
       </c>
       <c r="H160" s="6">
-        <v>500</v>
+        <v>680</v>
       </c>
     </row>
     <row outlineLevel="0" r="161">
@@ -5647,12 +5647,12 @@
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>GD235/60R18</t>
+          <t>HK235/60R18</t>
         </is>
       </c>
       <c r="D161" s="5">
@@ -5668,30 +5668,30 @@
         <v>0</v>
       </c>
       <c r="H161" s="6">
-        <v>680</v>
+        <v>550</v>
       </c>
     </row>
     <row outlineLevel="0" r="162">
       <c r="A162" s="4" t="inlineStr">
         <is>
-          <t>235/60R18</t>
+          <t>245/40R17</t>
         </is>
       </c>
       <c r="B162" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C162" s="4" t="inlineStr">
         <is>
-          <t>HK235/60R18</t>
+          <t>GD245/40R17</t>
         </is>
       </c>
       <c r="D162" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E162" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F162" s="5">
         <v>0</v>
@@ -5700,13 +5700,13 @@
         <v>0</v>
       </c>
       <c r="H162" s="6">
-        <v>550</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="163">
       <c r="A163" s="4" t="inlineStr">
         <is>
-          <t>245/40R17</t>
+          <t>245/40R18</t>
         </is>
       </c>
       <c r="B163" s="4" t="inlineStr">
@@ -5716,142 +5716,142 @@
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>GD245/40R17</t>
+          <t>GD245/40R18</t>
         </is>
       </c>
       <c r="D163" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E163" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F163" s="5">
         <v>0</v>
       </c>
       <c r="G163" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H163" s="6">
-        <v>400</v>
+        <v>620</v>
       </c>
     </row>
     <row outlineLevel="0" r="164">
       <c r="A164" s="4" t="inlineStr">
         <is>
-          <t>245/40R18</t>
+          <t>245/40R19</t>
         </is>
       </c>
       <c r="B164" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C164" s="4" t="inlineStr">
         <is>
-          <t>GD245/40R18</t>
+          <t>HK245/40R19</t>
         </is>
       </c>
       <c r="D164" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E164" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F164" s="5">
         <v>0</v>
       </c>
       <c r="G164" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H164" s="6">
-        <v>620</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="165">
       <c r="A165" s="4" t="inlineStr">
         <is>
-          <t>245/40R19</t>
+          <t>245/40R20</t>
         </is>
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>HK245/40R19</t>
+          <t>CT245/40R20</t>
         </is>
       </c>
       <c r="D165" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E165" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F165" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G165" s="5">
         <v>0</v>
       </c>
       <c r="H165" s="6">
-        <v>750</v>
+        <v>1050</v>
       </c>
     </row>
     <row outlineLevel="0" r="166">
       <c r="A166" s="4" t="inlineStr">
         <is>
-          <t>245/40R20</t>
+          <t>245/45R17</t>
         </is>
       </c>
       <c r="B166" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C166" s="4" t="inlineStr">
         <is>
-          <t>CT245/40R20</t>
+          <t>HK245/45R17</t>
         </is>
       </c>
       <c r="D166" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E166" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F166" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G166" s="5">
         <v>0</v>
       </c>
       <c r="H166" s="6">
-        <v>1050</v>
+        <v>430</v>
       </c>
     </row>
     <row outlineLevel="0" r="167">
       <c r="A167" s="4" t="inlineStr">
         <is>
-          <t>245/45R17</t>
+          <t>245/45R18</t>
         </is>
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>HK245/45R17</t>
+          <t>CT245/45R18</t>
         </is>
       </c>
       <c r="D167" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E167" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F167" s="5">
         <v>0</v>
@@ -5860,7 +5860,7 @@
         <v>0</v>
       </c>
       <c r="H167" s="6">
-        <v>430</v>
+        <v>650</v>
       </c>
     </row>
     <row outlineLevel="0" r="168">
@@ -5871,19 +5871,19 @@
       </c>
       <c r="B168" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C168" s="4" t="inlineStr">
         <is>
-          <t>CT245/45R18</t>
+          <t>GD245/45R18</t>
         </is>
       </c>
       <c r="D168" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E168" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F168" s="5">
         <v>0</v>
@@ -5892,7 +5892,7 @@
         <v>0</v>
       </c>
       <c r="H168" s="6">
-        <v>650</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="169">
@@ -5903,19 +5903,19 @@
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>GD245/45R18</t>
+          <t>HK245/45R18</t>
         </is>
       </c>
       <c r="D169" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E169" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F169" s="5">
         <v>0</v>
@@ -5924,30 +5924,30 @@
         <v>0</v>
       </c>
       <c r="H169" s="6">
-        <v>600</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="170">
       <c r="A170" s="4" t="inlineStr">
         <is>
-          <t>245/45R18</t>
+          <t>245/45R18RF</t>
         </is>
       </c>
       <c r="B170" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C170" s="4" t="inlineStr">
         <is>
-          <t>HK245/45R18</t>
+          <t>GD245/45R18RF</t>
         </is>
       </c>
       <c r="D170" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E170" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F170" s="5">
         <v>0</v>
@@ -5956,23 +5956,23 @@
         <v>0</v>
       </c>
       <c r="H170" s="6">
-        <v>500</v>
+        <v>720</v>
       </c>
     </row>
     <row outlineLevel="0" r="171">
       <c r="A171" s="4" t="inlineStr">
         <is>
-          <t>245/45R18RF</t>
+          <t>245/45R19</t>
         </is>
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t>GD245/45R18RF</t>
+          <t>BR245/45R19</t>
         </is>
       </c>
       <c r="D171" s="5">
@@ -5988,7 +5988,7 @@
         <v>0</v>
       </c>
       <c r="H171" s="6">
-        <v>720</v>
+        <v>790</v>
       </c>
     </row>
     <row outlineLevel="0" r="172">
@@ -5999,44 +5999,44 @@
       </c>
       <c r="B172" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C172" s="4" t="inlineStr">
         <is>
-          <t>BR245/45R19</t>
+          <t>RD245/45R19</t>
         </is>
       </c>
       <c r="D172" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E172" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F172" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G172" s="5">
         <v>0</v>
       </c>
       <c r="H172" s="6">
-        <v>790</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="173">
       <c r="A173" s="4" t="inlineStr">
         <is>
-          <t>245/45R19</t>
+          <t>245/45R20</t>
         </is>
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>RD245/45R19</t>
+          <t>HK245/45R20</t>
         </is>
       </c>
       <c r="D173" s="5">
@@ -6052,94 +6052,94 @@
         <v>0</v>
       </c>
       <c r="H173" s="6">
-        <v>450</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="174">
       <c r="A174" s="4" t="inlineStr">
         <is>
-          <t>245/45R20</t>
+          <t>245/65R17</t>
         </is>
       </c>
       <c r="B174" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C174" s="4" t="inlineStr">
         <is>
-          <t>HK245/45R20</t>
+          <t>NX245/65R17</t>
         </is>
       </c>
       <c r="D174" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E174" s="5">
         <v>0</v>
       </c>
       <c r="F174" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G174" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H174" s="6">
-        <v>750</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="175">
       <c r="A175" s="4" t="inlineStr">
         <is>
-          <t>245/65R17</t>
+          <t>255/35R19</t>
         </is>
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>NX245/65R17</t>
+          <t>DL255/35R19</t>
         </is>
       </c>
       <c r="D175" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E175" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F175" s="5">
         <v>0</v>
       </c>
       <c r="G175" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H175" s="6">
-        <v>600</v>
+        <v>700</v>
       </c>
     </row>
     <row outlineLevel="0" r="176">
       <c r="A176" s="4" t="inlineStr">
         <is>
-          <t>255/35R19</t>
+          <t>255/35R19RF</t>
         </is>
       </c>
       <c r="B176" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C176" s="4" t="inlineStr">
         <is>
-          <t>DL255/35R19</t>
+          <t>CT255/35R19RF</t>
         </is>
       </c>
       <c r="D176" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E176" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F176" s="5">
         <v>0</v>
@@ -6148,7 +6148,7 @@
         <v>0</v>
       </c>
       <c r="H176" s="6">
-        <v>700</v>
+        <v>950</v>
       </c>
     </row>
     <row outlineLevel="0" r="177">
@@ -6159,19 +6159,19 @@
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>CT255/35R19RF</t>
+          <t>GD255/35R19RF</t>
         </is>
       </c>
       <c r="D177" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E177" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F177" s="5">
         <v>0</v>
@@ -6186,39 +6186,39 @@
     <row outlineLevel="0" r="178">
       <c r="A178" s="4" t="inlineStr">
         <is>
-          <t>255/35R19RF</t>
+          <t>255/50R19</t>
         </is>
       </c>
       <c r="B178" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C178" s="4" t="inlineStr">
         <is>
-          <t>GD255/35R19RF</t>
+          <t>CT255/50R19</t>
         </is>
       </c>
       <c r="D178" s="5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E178" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F178" s="5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G178" s="5">
         <v>0</v>
       </c>
       <c r="H178" s="6">
-        <v>950</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="179">
       <c r="A179" s="4" t="inlineStr">
         <is>
-          <t>255/50R19</t>
+          <t>255/50R20</t>
         </is>
       </c>
       <c r="B179" s="4" t="inlineStr">
@@ -6228,29 +6228,29 @@
       </c>
       <c r="C179" s="4" t="inlineStr">
         <is>
-          <t>CT255/50R19</t>
+          <t>CT255/50R20</t>
         </is>
       </c>
       <c r="D179" s="5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E179" s="5">
         <v>0</v>
       </c>
       <c r="F179" s="5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G179" s="5">
         <v>0</v>
       </c>
       <c r="H179" s="6">
-        <v>750</v>
+        <v>900</v>
       </c>
     </row>
     <row outlineLevel="0" r="180">
       <c r="A180" s="4" t="inlineStr">
         <is>
-          <t>255/50R20</t>
+          <t>255/55R19</t>
         </is>
       </c>
       <c r="B180" s="4" t="inlineStr">
@@ -6260,23 +6260,23 @@
       </c>
       <c r="C180" s="4" t="inlineStr">
         <is>
-          <t>CT255/50R20</t>
+          <t>CT255/55R19</t>
         </is>
       </c>
       <c r="D180" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E180" s="5">
         <v>0</v>
       </c>
       <c r="F180" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G180" s="5">
         <v>0</v>
       </c>
       <c r="H180" s="6">
-        <v>900</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="181">
@@ -6287,98 +6287,98 @@
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C181" s="4" t="inlineStr">
         <is>
-          <t>CT255/55R19</t>
+          <t>DL255/55R19</t>
         </is>
       </c>
       <c r="D181" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E181" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F181" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G181" s="5">
         <v>0</v>
       </c>
       <c r="H181" s="6">
-        <v>750</v>
+        <v>700</v>
       </c>
     </row>
     <row outlineLevel="0" r="182">
       <c r="A182" s="4" t="inlineStr">
         <is>
-          <t>255/55R19</t>
+          <t>255/70R16</t>
         </is>
       </c>
       <c r="B182" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C182" s="4" t="inlineStr">
         <is>
-          <t>DL255/55R19</t>
+          <t>RD255/70R16</t>
         </is>
       </c>
       <c r="D182" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E182" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F182" s="5">
         <v>0</v>
       </c>
       <c r="G182" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H182" s="6">
-        <v>700</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="183">
       <c r="A183" s="4" t="inlineStr">
         <is>
-          <t>255/70R16</t>
+          <t>265/35R18</t>
         </is>
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C183" s="4" t="inlineStr">
         <is>
-          <t>RD255/70R16</t>
+          <t>GD265/35R18</t>
         </is>
       </c>
       <c r="D183" s="5">
         <v>1</v>
       </c>
       <c r="E183" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F183" s="5">
         <v>0</v>
       </c>
       <c r="G183" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H183" s="6">
-        <v>500</v>
+        <v>700</v>
       </c>
     </row>
     <row outlineLevel="0" r="184">
       <c r="A184" s="4" t="inlineStr">
         <is>
-          <t>265/35R18</t>
+          <t>265/50R20</t>
         </is>
       </c>
       <c r="B184" s="4" t="inlineStr">
@@ -6388,29 +6388,29 @@
       </c>
       <c r="C184" s="4" t="inlineStr">
         <is>
-          <t>GD265/35R18</t>
+          <t>GD265/50R20</t>
         </is>
       </c>
       <c r="D184" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E184" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F184" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G184" s="5">
         <v>0</v>
       </c>
       <c r="H184" s="6">
-        <v>700</v>
+        <v>1150</v>
       </c>
     </row>
     <row outlineLevel="0" r="185">
       <c r="A185" s="4" t="inlineStr">
         <is>
-          <t>265/50R20</t>
+          <t>275/35R19RF</t>
         </is>
       </c>
       <c r="B185" s="4" t="inlineStr">
@@ -6420,71 +6420,71 @@
       </c>
       <c r="C185" s="4" t="inlineStr">
         <is>
-          <t>GD265/50R20</t>
+          <t>GD275/35R19RF</t>
         </is>
       </c>
       <c r="D185" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E185" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F185" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G185" s="5">
         <v>0</v>
       </c>
       <c r="H185" s="6">
-        <v>1150</v>
+        <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="186">
       <c r="A186" s="4" t="inlineStr">
         <is>
-          <t>275/35R19RF</t>
+          <t>275/35R20</t>
         </is>
       </c>
       <c r="B186" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C186" s="4" t="inlineStr">
         <is>
-          <t>GD275/35R19RF</t>
+          <t>CT275/35R20</t>
         </is>
       </c>
       <c r="D186" s="5">
         <v>2</v>
       </c>
       <c r="E186" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F186" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G186" s="5">
         <v>0</v>
       </c>
       <c r="H186" s="6">
-        <v>1</v>
+        <v>980</v>
       </c>
     </row>
     <row outlineLevel="0" r="187">
       <c r="A187" s="4" t="inlineStr">
         <is>
-          <t>275/35R20</t>
+          <t>275/40R20</t>
         </is>
       </c>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C187" s="4" t="inlineStr">
         <is>
-          <t>CT275/35R20</t>
+          <t>HK275/40R20</t>
         </is>
       </c>
       <c r="D187" s="5">
@@ -6500,23 +6500,23 @@
         <v>0</v>
       </c>
       <c r="H187" s="6">
-        <v>980</v>
+        <v>770</v>
       </c>
     </row>
     <row outlineLevel="0" r="188">
       <c r="A188" s="4" t="inlineStr">
         <is>
-          <t>275/40R20</t>
+          <t>275/50R21</t>
         </is>
       </c>
       <c r="B188" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C188" s="4" t="inlineStr">
         <is>
-          <t>HK275/40R20</t>
+          <t>GD275/50R21</t>
         </is>
       </c>
       <c r="D188" s="5">
@@ -6532,23 +6532,23 @@
         <v>0</v>
       </c>
       <c r="H188" s="6">
-        <v>770</v>
+        <v>1</v>
       </c>
     </row>
     <row outlineLevel="0" r="189">
       <c r="A189" s="4" t="inlineStr">
         <is>
-          <t>275/50R21</t>
+          <t>295/35R21</t>
         </is>
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C189" s="4" t="inlineStr">
         <is>
-          <t>GD275/50R21</t>
+          <t>CT295/35R21</t>
         </is>
       </c>
       <c r="D189" s="5">
@@ -6564,7 +6564,7 @@
         <v>0</v>
       </c>
       <c r="H189" s="6">
-        <v>1</v>
+        <v>1150</v>
       </c>
     </row>
     <row outlineLevel="0" r="190">
@@ -6575,91 +6575,59 @@
       </c>
       <c r="B190" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C190" s="4" t="inlineStr">
         <is>
-          <t>CT295/35R21</t>
+          <t>GD295/35R21</t>
         </is>
       </c>
       <c r="D190" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E190" s="5">
         <v>0</v>
       </c>
       <c r="F190" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G190" s="5">
         <v>0</v>
       </c>
       <c r="H190" s="6">
-        <v>1150</v>
+        <v>980</v>
       </c>
     </row>
     <row outlineLevel="0" r="191">
       <c r="A191" s="4" t="inlineStr">
         <is>
-          <t>295/35R21</t>
+          <t>500R12</t>
         </is>
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C191" s="4" t="inlineStr">
         <is>
-          <t>GD295/35R21</t>
+          <t>RD500R12</t>
         </is>
       </c>
       <c r="D191" s="5">
         <v>3</v>
       </c>
       <c r="E191" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F191" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G191" s="5">
         <v>0</v>
       </c>
       <c r="H191" s="6">
-        <v>980</v>
-      </c>
-    </row>
-    <row outlineLevel="0" r="192">
-      <c r="A192" s="4" t="inlineStr">
-        <is>
-          <t>500R12</t>
-        </is>
-      </c>
-      <c r="B192" s="4" t="inlineStr">
-        <is>
-          <t>RADIAL</t>
-        </is>
-      </c>
-      <c r="C192" s="4" t="inlineStr">
-        <is>
-          <t>RD500R12</t>
-        </is>
-      </c>
-      <c r="D192" s="5">
-        <v>3</v>
-      </c>
-      <c r="E192" s="5">
-        <v>3</v>
-      </c>
-      <c r="F192" s="5">
-        <v>0</v>
-      </c>
-      <c r="G192" s="5">
-        <v>0</v>
-      </c>
-      <c r="H192" s="6">
         <v>300</v>
       </c>
     </row>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -2296,7 +2296,7 @@
         </is>
       </c>
       <c r="D56" s="5">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E56" s="5">
         <v>5</v>
@@ -2305,7 +2305,7 @@
         <v>1</v>
       </c>
       <c r="G56" s="5">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H56" s="6">
         <v>230</v>
@@ -2328,10 +2328,10 @@
         </is>
       </c>
       <c r="D57" s="5">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E57" s="5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F57" s="5">
         <v>69</v>
@@ -4408,10 +4408,10 @@
         </is>
       </c>
       <c r="D122" s="5">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E122" s="5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F122" s="5">
         <v>9</v>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -496,7 +496,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H191"/>
+  <dimension ref="A1:H242"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col customWidth="true" min="1" max="1" width="13.8359375"/>
@@ -687,19 +687,19 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>SEMPERIT</t>
+          <t>DOUBLESTAR</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>SP165/65R14</t>
+          <t>DS165/65R14</t>
         </is>
       </c>
       <c r="D6" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E6" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F6" s="5">
         <v>0</v>
@@ -708,7 +708,7 @@
         <v>0</v>
       </c>
       <c r="H6" s="6">
-        <v>200</v>
+        <v>190</v>
       </c>
     </row>
     <row outlineLevel="0" r="7">
@@ -719,19 +719,19 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>WESTLAKE</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>WL165/65R14</t>
+          <t>RD165/65R14</t>
         </is>
       </c>
       <c r="D7" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E7" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F7" s="5">
         <v>0</v>
@@ -746,24 +746,24 @@
     <row outlineLevel="0" r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>165/70R13</t>
+          <t>165/65R14</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>SEMPERIT</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>RD165/70R13</t>
+          <t>SP165/65R14</t>
         </is>
       </c>
       <c r="D8" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E8" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F8" s="5">
         <v>0</v>
@@ -772,94 +772,94 @@
         <v>0</v>
       </c>
       <c r="H8" s="6">
-        <v>180</v>
+        <v>200</v>
       </c>
     </row>
     <row outlineLevel="0" r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>165/70R14</t>
+          <t>165/65R14</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>SEMPERIT</t>
+          <t>WESTLAKE</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>SP165/70R14</t>
+          <t>WL165/65R14</t>
         </is>
       </c>
       <c r="D9" s="5">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E9" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F9" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G9" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H9" s="6">
-        <v>240</v>
+        <v>180</v>
       </c>
     </row>
     <row outlineLevel="0" r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>175/50R15</t>
+          <t>165/70R13</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>AMINE</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>HK175/50R15</t>
+          <t>AM165/70R13</t>
         </is>
       </c>
       <c r="D10" s="5">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E10" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F10" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G10" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H10" s="6">
-        <v>270</v>
+        <v>190</v>
       </c>
     </row>
     <row outlineLevel="0" r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>175/55R15</t>
+          <t>165/70R13</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>DOUBLESTAR</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>RD175/55R15</t>
+          <t>DS165/70R13</t>
         </is>
       </c>
       <c r="D11" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11" s="5">
         <v>0</v>
@@ -868,119 +868,119 @@
         <v>0</v>
       </c>
       <c r="H11" s="6">
-        <v>250</v>
+        <v>180</v>
       </c>
     </row>
     <row outlineLevel="0" r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>175/60R15</t>
+          <t>165/70R13</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>GD175/60R15</t>
+          <t>RD165/70R13</t>
         </is>
       </c>
       <c r="D12" s="5">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="E12" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F12" s="5">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G12" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H12" s="6">
-        <v>350</v>
+        <v>180</v>
       </c>
     </row>
     <row outlineLevel="0" r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>175/60R15</t>
+          <t>165/70R14</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>SEMPERIT</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>RD175/60R15</t>
+          <t>SP165/70R14</t>
         </is>
       </c>
       <c r="D13" s="5">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E13" s="5">
         <v>4</v>
       </c>
       <c r="F13" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G13" s="5">
         <v>4</v>
       </c>
       <c r="H13" s="6">
-        <v>230</v>
+        <v>240</v>
       </c>
     </row>
     <row outlineLevel="0" r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>175/65R14</t>
+          <t>175/50R15</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>GD175/65R14</t>
+          <t>HK175/50R15</t>
         </is>
       </c>
       <c r="D14" s="5">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="E14" s="5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F14" s="5">
-        <v>73</v>
+        <v>4</v>
       </c>
       <c r="G14" s="5">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="H14" s="6">
-        <v>220</v>
+        <v>270</v>
       </c>
     </row>
     <row outlineLevel="0" r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>175/65R14</t>
+          <t>175/55R15</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>NX175/65R14</t>
+          <t>RD175/55R15</t>
         </is>
       </c>
       <c r="D15" s="5">
@@ -996,71 +996,71 @@
         <v>0</v>
       </c>
       <c r="H15" s="6">
-        <v>200</v>
+        <v>250</v>
       </c>
     </row>
     <row outlineLevel="0" r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>175/65R14</t>
+          <t>175/60R15</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>RD175/65R14</t>
+          <t>GD175/60R15</t>
         </is>
       </c>
       <c r="D16" s="5">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="E16" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F16" s="5">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="G16" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H16" s="6">
-        <v>180</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>175/65R14</t>
+          <t>175/60R15</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>SEMPERIT</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>SP175/65R14</t>
+          <t>RD175/60R15</t>
         </is>
       </c>
       <c r="D17" s="5">
-        <v>48</v>
+        <v>13</v>
       </c>
       <c r="E17" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F17" s="5">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="G17" s="5">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="H17" s="6">
-        <v>190</v>
+        <v>230</v>
       </c>
     </row>
     <row outlineLevel="0" r="18">
@@ -1071,51 +1071,51 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>WESTLAKE</t>
+          <t>AMINE</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>WL175/65R14</t>
+          <t>AM175/65R14</t>
         </is>
       </c>
       <c r="D18" s="5">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="E18" s="5">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="F18" s="5">
         <v>0</v>
       </c>
       <c r="G18" s="5">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H18" s="6">
-        <v>180</v>
+        <v>170</v>
       </c>
     </row>
     <row outlineLevel="0" r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>175/70R14</t>
+          <t>175/65R14</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>MATADOR</t>
+          <t>DOUBLESTAR</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>MT175/70R14</t>
+          <t>DS175/65R14</t>
         </is>
       </c>
       <c r="D19" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E19" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F19" s="5">
         <v>0</v>
@@ -1124,222 +1124,222 @@
         <v>0</v>
       </c>
       <c r="H19" s="6">
-        <v>230</v>
+        <v>180</v>
       </c>
     </row>
     <row outlineLevel="0" r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>175/70R14</t>
+          <t>175/65R14</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>WESTLAKE</t>
+          <t>GOODRIDE</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>WL175/70R14</t>
+          <t>GR175/65R14</t>
         </is>
       </c>
       <c r="D20" s="5">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="E20" s="5">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="F20" s="5">
         <v>0</v>
       </c>
       <c r="G20" s="5">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H20" s="6">
-        <v>200</v>
+        <v>180</v>
       </c>
     </row>
     <row outlineLevel="0" r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>185/55R15</t>
+          <t>175/65R14</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>BR185/55R15</t>
+          <t>GD175/65R14</t>
         </is>
       </c>
       <c r="D21" s="5">
-        <v>2</v>
+        <v>91</v>
       </c>
       <c r="E21" s="5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F21" s="5">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="G21" s="5">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H21" s="6">
-        <v>370</v>
+        <v>220</v>
       </c>
     </row>
     <row outlineLevel="0" r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>185/55R15</t>
+          <t>175/65R14</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>GD185/55R15</t>
+          <t>NX175/65R14</t>
         </is>
       </c>
       <c r="D22" s="5">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="E22" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F22" s="5">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G22" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H22" s="6">
-        <v>340</v>
+        <v>200</v>
       </c>
     </row>
     <row outlineLevel="0" r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>185/55R16</t>
+          <t>175/65R14</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>GD185/55R16</t>
+          <t>RD175/65R14</t>
         </is>
       </c>
       <c r="D23" s="5">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E23" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F23" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H23" s="6">
-        <v>420</v>
+        <v>180</v>
       </c>
     </row>
     <row outlineLevel="0" r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>185/60R14</t>
+          <t>175/65R14</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>SEMPERIT</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>GD185/60R14</t>
+          <t>SP175/65R14</t>
         </is>
       </c>
       <c r="D24" s="5">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="E24" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F24" s="5">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="G24" s="5">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="H24" s="6">
-        <v>230</v>
+        <v>190</v>
       </c>
     </row>
     <row outlineLevel="0" r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>185/60R14</t>
+          <t>175/65R14</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>WESTLAKE</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>NX185/60R14</t>
+          <t>WL175/65R14</t>
         </is>
       </c>
       <c r="D25" s="5">
-        <v>1</v>
+        <v>84</v>
       </c>
       <c r="E25" s="5">
-        <v>1</v>
+        <v>74</v>
       </c>
       <c r="F25" s="5">
         <v>0</v>
       </c>
       <c r="G25" s="5">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H25" s="6">
-        <v>230</v>
+        <v>180</v>
       </c>
     </row>
     <row outlineLevel="0" r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>185/60R15</t>
+          <t>175/65R15</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>MATADOR</t>
+          <t>DOUBLESTAR</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>MT185/60R15</t>
+          <t>DS175/65R15</t>
         </is>
       </c>
       <c r="D26" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E26" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F26" s="5">
         <v>0</v>
@@ -1348,91 +1348,91 @@
         <v>0</v>
       </c>
       <c r="H26" s="6">
-        <v>280</v>
+        <v>200</v>
       </c>
     </row>
     <row outlineLevel="0" r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>185/60R15</t>
+          <t>175/70R13</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>DOUBLESTAR</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>RD185/60R15</t>
+          <t>DS175/70R13</t>
         </is>
       </c>
       <c r="D27" s="5">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E27" s="5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F27" s="5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G27" s="5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H27" s="6">
-        <v>230</v>
+        <v>200</v>
       </c>
     </row>
     <row outlineLevel="0" r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>185/60R16</t>
+          <t>175/70R13</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>WESTLAKE</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>GD185/60R16</t>
+          <t>WL175/70R13</t>
         </is>
       </c>
       <c r="D28" s="5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E28" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F28" s="5">
         <v>0</v>
       </c>
       <c r="G28" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H28" s="6">
-        <v>420</v>
+        <v>200</v>
       </c>
     </row>
     <row outlineLevel="0" r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>185/65R14</t>
+          <t>175/70R14</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>RD185/65R14</t>
+          <t>BR175/70R14</t>
         </is>
       </c>
       <c r="D29" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E29" s="5">
         <v>0</v>
@@ -1441,33 +1441,33 @@
         <v>0</v>
       </c>
       <c r="G29" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H29" s="6">
-        <v>200</v>
+        <v>295</v>
       </c>
     </row>
     <row outlineLevel="0" r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>185/65R15</t>
+          <t>175/70R14</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>DOUBLESTAR</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>CT185/65R15</t>
+          <t>DS175/70R14</t>
         </is>
       </c>
       <c r="D30" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E30" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F30" s="5">
         <v>0</v>
@@ -1476,190 +1476,190 @@
         <v>0</v>
       </c>
       <c r="H30" s="6">
-        <v>400</v>
+        <v>200</v>
       </c>
     </row>
     <row outlineLevel="0" r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>185/65R15</t>
+          <t>175/70R14</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>DOUBLESTAR</t>
+          <t>MATADOR</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>DS185/65R15</t>
+          <t>MT175/70R14</t>
         </is>
       </c>
       <c r="D31" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E31" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F31" s="5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G31" s="5">
         <v>0</v>
       </c>
       <c r="H31" s="6">
-        <v>210</v>
+        <v>230</v>
       </c>
     </row>
     <row outlineLevel="0" r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>185/65R15</t>
+          <t>175/70R14</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>FULDA</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>FL185/65R15</t>
+          <t>RD175/70R14</t>
         </is>
       </c>
       <c r="D32" s="5">
-        <v>134</v>
+        <v>0</v>
       </c>
       <c r="E32" s="5">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F32" s="5">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="G32" s="5">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H32" s="6">
-        <v>245</v>
+        <v>220</v>
       </c>
     </row>
     <row outlineLevel="0" r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>185/65R15</t>
+          <t>175/70R14</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>GOODRIDE</t>
+          <t>SEMPERIT</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>GR185/65R15</t>
+          <t>SP175/70R14</t>
         </is>
       </c>
       <c r="D33" s="5">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E33" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F33" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G33" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H33" s="6">
-        <v>230</v>
+        <v>250</v>
       </c>
     </row>
     <row outlineLevel="0" r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>185/65R15</t>
+          <t>175/70R14</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>WESTLAKE</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>GD185/65R15</t>
+          <t>WL175/70R14</t>
         </is>
       </c>
       <c r="D34" s="5">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="E34" s="5">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="F34" s="5">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G34" s="5">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H34" s="6">
-        <v>260</v>
+        <v>200</v>
       </c>
     </row>
     <row outlineLevel="0" r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>185/65R15</t>
+          <t>185/55R15</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>HK185/65R15</t>
+          <t>BR185/55R15</t>
         </is>
       </c>
       <c r="D35" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E35" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F35" s="5">
         <v>0</v>
       </c>
       <c r="G35" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H35" s="6">
-        <v>250</v>
+        <v>370</v>
       </c>
     </row>
     <row outlineLevel="0" r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>185/65R15</t>
+          <t>185/55R15</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>LF185/65R15</t>
+          <t>CT185/55R15</t>
         </is>
       </c>
       <c r="D36" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E36" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F36" s="5">
         <v>0</v>
@@ -1668,95 +1668,95 @@
         <v>0</v>
       </c>
       <c r="H36" s="6">
-        <v>250</v>
+        <v>240</v>
       </c>
     </row>
     <row outlineLevel="0" r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>185/65R15</t>
+          <t>185/55R15</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>SEMPERIT</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>SP185/65R15</t>
+          <t>GD185/55R15</t>
         </is>
       </c>
       <c r="D37" s="5">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="E37" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F37" s="5">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="G37" s="5">
         <v>4</v>
       </c>
       <c r="H37" s="6">
-        <v>250</v>
+        <v>340</v>
       </c>
     </row>
     <row outlineLevel="0" r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>185/65R15</t>
+          <t>185/55R15</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>WESTLAKE</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>WL185/65R15</t>
+          <t>RD185/55R15</t>
         </is>
       </c>
       <c r="D38" s="5">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="E38" s="5">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="F38" s="5">
         <v>0</v>
       </c>
       <c r="G38" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H38" s="6">
-        <v>220</v>
+        <v>270</v>
       </c>
     </row>
     <row outlineLevel="0" r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>185/70R14</t>
+          <t>185/55R16</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>RD185/70R14</t>
+          <t>GD185/55R16</t>
         </is>
       </c>
       <c r="D39" s="5">
+        <v>3</v>
+      </c>
+      <c r="E39" s="5">
         <v>2</v>
       </c>
-      <c r="E39" s="5">
-        <v>1</v>
-      </c>
       <c r="F39" s="5">
         <v>0</v>
       </c>
@@ -1764,55 +1764,55 @@
         <v>1</v>
       </c>
       <c r="H39" s="6">
-        <v>230</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>185/70R14</t>
+          <t>185/60R14</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>WESTLAKE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>WL185/70R14</t>
+          <t>GD185/60R14</t>
         </is>
       </c>
       <c r="D40" s="5">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E40" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F40" s="5">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G40" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H40" s="6">
-        <v>220</v>
+        <v>230</v>
       </c>
     </row>
     <row outlineLevel="0" r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>195/50R15</t>
+          <t>185/60R14</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>GD195/50R15</t>
+          <t>NX185/60R14</t>
         </is>
       </c>
       <c r="D41" s="5">
@@ -1828,222 +1828,222 @@
         <v>0</v>
       </c>
       <c r="H41" s="6">
-        <v>290</v>
+        <v>230</v>
       </c>
     </row>
     <row outlineLevel="0" r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>195/50R15</t>
+          <t>185/60R15</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>SEMPERIT</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>SP195/50R15</t>
+          <t>LF185/60R15</t>
         </is>
       </c>
       <c r="D42" s="5">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="E42" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F42" s="5">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G42" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H42" s="6">
-        <v>260</v>
+        <v>270</v>
       </c>
     </row>
     <row outlineLevel="0" r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>195/50R15</t>
+          <t>185/60R15</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>WESTLAKE</t>
+          <t>MATADOR</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>WL195/50R15</t>
+          <t>MT185/60R15</t>
         </is>
       </c>
       <c r="D43" s="5">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E43" s="5">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F43" s="5">
         <v>0</v>
       </c>
       <c r="G43" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H43" s="6">
-        <v>225</v>
+        <v>280</v>
       </c>
     </row>
     <row outlineLevel="0" r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>195/50R16</t>
+          <t>185/60R15</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>GD195/50R16</t>
+          <t>RD185/60R15</t>
         </is>
       </c>
       <c r="D44" s="5">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E44" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F44" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G44" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H44" s="6">
-        <v>330</v>
+        <v>230</v>
       </c>
     </row>
     <row outlineLevel="0" r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>195/55R16</t>
+          <t>185/60R15</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>WESTLAKE</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>GD195/55R16</t>
+          <t>WL185/60R15</t>
         </is>
       </c>
       <c r="D45" s="5">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E45" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F45" s="5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G45" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H45" s="6">
-        <v>350</v>
+        <v>230</v>
       </c>
     </row>
     <row outlineLevel="0" r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>195/55R16</t>
+          <t>185/60R16</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>HK195/55R16</t>
+          <t>GD185/60R16</t>
         </is>
       </c>
       <c r="D46" s="5">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E46" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F46" s="5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G46" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H46" s="6">
-        <v>290</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>195/55R16</t>
+          <t>185/65R14</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>LASSA</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>LS195/55R16</t>
+          <t>RD185/65R14</t>
         </is>
       </c>
       <c r="D47" s="5">
         <v>3</v>
       </c>
       <c r="E47" s="5">
+        <v>0</v>
+      </c>
+      <c r="F47" s="5">
+        <v>0</v>
+      </c>
+      <c r="G47" s="5">
         <v>3</v>
       </c>
-      <c r="F47" s="5">
-        <v>0</v>
-      </c>
-      <c r="G47" s="5">
-        <v>0</v>
-      </c>
       <c r="H47" s="6">
-        <v>280</v>
+        <v>200</v>
       </c>
     </row>
     <row outlineLevel="0" r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>195/55R16</t>
+          <t>185/65R15</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>AMINE</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>NX195/55R16</t>
+          <t>AM185/65R15</t>
         </is>
       </c>
       <c r="D48" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E48" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F48" s="5">
         <v>0</v>
@@ -2052,109 +2052,109 @@
         <v>0</v>
       </c>
       <c r="H48" s="6">
-        <v>300</v>
+        <v>200</v>
       </c>
     </row>
     <row outlineLevel="0" r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>195/55R16</t>
+          <t>185/65R15</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>RD195/55R16</t>
+          <t>CT185/65R15</t>
         </is>
       </c>
       <c r="D49" s="5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E49" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F49" s="5">
         <v>0</v>
       </c>
       <c r="G49" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H49" s="6">
-        <v>250</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>195/60R16</t>
+          <t>185/65R15</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>DOUBLESTAR</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>GD195/60R16</t>
+          <t>DS185/65R15</t>
         </is>
       </c>
       <c r="D50" s="5">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E50" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F50" s="5">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="G50" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H50" s="6">
-        <v>355</v>
+        <v>210</v>
       </c>
     </row>
     <row outlineLevel="0" r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>195/65R15</t>
+          <t>185/65R15</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>DOUBLESTAR</t>
+          <t>FULDA</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>DS195/65R15</t>
+          <t>FL185/65R15</t>
         </is>
       </c>
       <c r="D51" s="5">
-        <v>5</v>
+        <v>134</v>
       </c>
       <c r="E51" s="5">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F51" s="5">
-        <v>5</v>
+        <v>108</v>
       </c>
       <c r="G51" s="5">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="H51" s="6">
-        <v>230</v>
+        <v>245</v>
       </c>
     </row>
     <row outlineLevel="0" r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>195/65R15</t>
+          <t>185/65R15</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
@@ -2164,20 +2164,20 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>GR195/65R15</t>
+          <t>GR185/65R15</t>
         </is>
       </c>
       <c r="D52" s="5">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E52" s="5">
         <v>4</v>
       </c>
       <c r="F52" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G52" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H52" s="6">
         <v>230</v>
@@ -2186,27 +2186,27 @@
     <row outlineLevel="0" r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>195/65R15</t>
+          <t>185/65R15</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>HK195/65R15</t>
+          <t>GD185/65R15</t>
         </is>
       </c>
       <c r="D53" s="5">
-        <v>9</v>
+        <v>58</v>
       </c>
       <c r="E53" s="5">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F53" s="5">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="G53" s="5">
         <v>4</v>
@@ -2218,30 +2218,30 @@
     <row outlineLevel="0" r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>195/65R15</t>
+          <t>185/65R15</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>LASSA</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>LS195/65R15</t>
+          <t>HK185/65R15</t>
         </is>
       </c>
       <c r="D54" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E54" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F54" s="5">
         <v>0</v>
       </c>
       <c r="G54" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H54" s="6">
         <v>250</v>
@@ -2250,24 +2250,24 @@
     <row outlineLevel="0" r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>195/65R15</t>
+          <t>185/65R15</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>NX195/65R15</t>
+          <t>LF185/65R15</t>
         </is>
       </c>
       <c r="D55" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E55" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F55" s="5">
         <v>0</v>
@@ -2276,13 +2276,13 @@
         <v>0</v>
       </c>
       <c r="H55" s="6">
-        <v>230</v>
+        <v>250</v>
       </c>
     </row>
     <row outlineLevel="0" r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>195/65R15</t>
+          <t>185/65R15</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
@@ -2292,29 +2292,29 @@
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>RD195/65R15</t>
+          <t>RD185/65R15</t>
         </is>
       </c>
       <c r="D56" s="5">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E56" s="5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F56" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G56" s="5">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H56" s="6">
-        <v>230</v>
+        <v>200</v>
       </c>
     </row>
     <row outlineLevel="0" r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>195/65R15</t>
+          <t>185/65R15</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
@@ -2324,20 +2324,20 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>SP195/65R15</t>
+          <t>SP185/65R15</t>
         </is>
       </c>
       <c r="D57" s="5">
-        <v>88</v>
+        <v>26</v>
       </c>
       <c r="E57" s="5">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F57" s="5">
-        <v>69</v>
+        <v>17</v>
       </c>
       <c r="G57" s="5">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="H57" s="6">
         <v>250</v>
@@ -2346,85 +2346,85 @@
     <row outlineLevel="0" r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>195/70R15C</t>
+          <t>185/65R15</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>WESTLAKE</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>LF195/70R15C</t>
+          <t>WL185/65R15</t>
         </is>
       </c>
       <c r="D58" s="5">
-        <v>4</v>
+        <v>77</v>
       </c>
       <c r="E58" s="5">
-        <v>4</v>
+        <v>75</v>
       </c>
       <c r="F58" s="5">
         <v>0</v>
       </c>
       <c r="G58" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H58" s="6">
-        <v>300</v>
+        <v>220</v>
       </c>
     </row>
     <row outlineLevel="0" r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>195/75R16C</t>
+          <t>185/70R14</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>GOODRIDE</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>GR195/75R16C</t>
+          <t>RD185/70R14</t>
         </is>
       </c>
       <c r="D59" s="5">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E59" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F59" s="5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G59" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H59" s="6">
-        <v>350</v>
+        <v>230</v>
       </c>
     </row>
     <row outlineLevel="0" r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>195R15C</t>
+          <t>185/70R14</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>SEMPERIT</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>RD195R15C</t>
+          <t>SP185/70R14</t>
         </is>
       </c>
       <c r="D60" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E60" s="5">
         <v>0</v>
@@ -2433,62 +2433,62 @@
         <v>0</v>
       </c>
       <c r="G60" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H60" s="6">
-        <v>350</v>
+        <v>280</v>
       </c>
     </row>
     <row outlineLevel="0" r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>205/45R17</t>
+          <t>185/70R14</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>WESTLAKE</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>CT205/45R17</t>
+          <t>WL185/70R14</t>
         </is>
       </c>
       <c r="D61" s="5">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E61" s="5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F61" s="5">
         <v>0</v>
       </c>
       <c r="G61" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H61" s="6">
-        <v>550</v>
+        <v>220</v>
       </c>
     </row>
     <row outlineLevel="0" r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>205/45R17</t>
+          <t>195/50R15</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>FULDA</t>
+          <t>AMINE</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>FL205/45R17</t>
+          <t>AM195/50R15</t>
         </is>
       </c>
       <c r="D62" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E62" s="5">
         <v>0</v>
@@ -2497,33 +2497,33 @@
         <v>0</v>
       </c>
       <c r="G62" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H62" s="6">
-        <v>380</v>
+        <v>220</v>
       </c>
     </row>
     <row outlineLevel="0" r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>205/45R17</t>
+          <t>195/50R15</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>GOODRIDE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>GR205/45R17</t>
+          <t>GD195/50R15</t>
         </is>
       </c>
       <c r="D63" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E63" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F63" s="5">
         <v>0</v>
@@ -2532,126 +2532,126 @@
         <v>0</v>
       </c>
       <c r="H63" s="6">
-        <v>300</v>
+        <v>290</v>
       </c>
     </row>
     <row outlineLevel="0" r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>205/45R17</t>
+          <t>195/50R15</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>SEMPERIT</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>GD205/45R17</t>
+          <t>SP195/50R15</t>
         </is>
       </c>
       <c r="D64" s="5">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E64" s="5">
         <v>4</v>
       </c>
       <c r="F64" s="5">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="G64" s="5">
         <v>4</v>
       </c>
       <c r="H64" s="6">
-        <v>450</v>
+        <v>260</v>
       </c>
     </row>
     <row outlineLevel="0" r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>205/45R17</t>
+          <t>195/50R15</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>WESTLAKE</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>NX205/45R17</t>
+          <t>WL195/50R15</t>
         </is>
       </c>
       <c r="D65" s="5">
+        <v>10</v>
+      </c>
+      <c r="E65" s="5">
+        <v>8</v>
+      </c>
+      <c r="F65" s="5">
+        <v>0</v>
+      </c>
+      <c r="G65" s="5">
         <v>2</v>
       </c>
-      <c r="E65" s="5">
-        <v>2</v>
-      </c>
-      <c r="F65" s="5">
-        <v>0</v>
-      </c>
-      <c r="G65" s="5">
-        <v>0</v>
-      </c>
       <c r="H65" s="6">
-        <v>380</v>
+        <v>225</v>
       </c>
     </row>
     <row outlineLevel="0" r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>205/45R17</t>
+          <t>195/50R16</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>RD205/45R17</t>
+          <t>GD195/50R16</t>
         </is>
       </c>
       <c r="D66" s="5">
         <v>1</v>
       </c>
       <c r="E66" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F66" s="5">
         <v>0</v>
       </c>
       <c r="G66" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H66" s="6">
-        <v>300</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>205/50R17</t>
+          <t>195/55R16</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>AMINE</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>CT205/50R17</t>
+          <t>AM195/55R16</t>
         </is>
       </c>
       <c r="D67" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E67" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F67" s="5">
         <v>0</v>
@@ -2660,68 +2660,68 @@
         <v>0</v>
       </c>
       <c r="H67" s="6">
-        <v>450</v>
+        <v>270</v>
       </c>
     </row>
     <row outlineLevel="0" r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>205/55R16</t>
+          <t>195/55R16</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>AMINE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>AM205/55R16</t>
+          <t>GD195/55R16</t>
         </is>
       </c>
       <c r="D68" s="5">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="E68" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F68" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G68" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H68" s="6">
-        <v>240</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>205/55R16</t>
+          <t>195/55R16</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>BR205/55R16</t>
+          <t>HK195/55R16</t>
         </is>
       </c>
       <c r="D69" s="5">
+        <v>11</v>
+      </c>
+      <c r="E69" s="5">
         <v>2</v>
       </c>
-      <c r="E69" s="5">
-        <v>0</v>
-      </c>
       <c r="F69" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G69" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H69" s="6">
         <v>290</v>
@@ -2730,24 +2730,24 @@
     <row outlineLevel="0" r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>205/55R16</t>
+          <t>195/55R16</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>DOUBLESTAR</t>
+          <t>LASSA</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>DS205/55R16</t>
+          <t>LS195/55R16</t>
         </is>
       </c>
       <c r="D70" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E70" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F70" s="5">
         <v>0</v>
@@ -2756,68 +2756,68 @@
         <v>0</v>
       </c>
       <c r="H70" s="6">
-        <v>230</v>
+        <v>280</v>
       </c>
     </row>
     <row outlineLevel="0" r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>205/55R16</t>
+          <t>195/55R16</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>FULDA</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>FL205/55R16</t>
+          <t>NX195/55R16</t>
         </is>
       </c>
       <c r="D71" s="5">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="E71" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F71" s="5">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G71" s="5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H71" s="6">
-        <v>250</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>205/55R16</t>
+          <t>195/55R16</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>GOODRIDE</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>GR205/55R16</t>
+          <t>RD195/55R16</t>
         </is>
       </c>
       <c r="D72" s="5">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E72" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F72" s="5">
         <v>0</v>
       </c>
       <c r="G72" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H72" s="6">
         <v>250</v>
@@ -2826,7 +2826,7 @@
     <row outlineLevel="0" r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>205/55R16</t>
+          <t>195/60R16</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
@@ -2836,84 +2836,84 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>GD205/55R16</t>
+          <t>GD195/60R16</t>
         </is>
       </c>
       <c r="D73" s="5">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E73" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F73" s="5">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G73" s="5">
         <v>4</v>
       </c>
       <c r="H73" s="6">
-        <v>280</v>
+        <v>355</v>
       </c>
     </row>
     <row outlineLevel="0" r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>205/55R16</t>
+          <t>195/65R15</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>DOUBLESTAR</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>HK205/55R16</t>
+          <t>DS195/65R15</t>
         </is>
       </c>
       <c r="D74" s="5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E74" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F74" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G74" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H74" s="6">
-        <v>260</v>
+        <v>230</v>
       </c>
     </row>
     <row outlineLevel="0" r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>205/55R16</t>
+          <t>195/65R15</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>GOODRIDE</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>RD205/55R16</t>
+          <t>GR195/65R15</t>
         </is>
       </c>
       <c r="D75" s="5">
         <v>4</v>
       </c>
       <c r="E75" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F75" s="5">
         <v>0</v>
       </c>
       <c r="G75" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H75" s="6">
         <v>230</v>
@@ -2922,71 +2922,71 @@
     <row outlineLevel="0" r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>205/55R16RF</t>
+          <t>195/65R15</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>GD205/55R16RF</t>
+          <t>HK195/65R15</t>
         </is>
       </c>
       <c r="D76" s="5">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E76" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F76" s="5">
         <v>0</v>
       </c>
       <c r="G76" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H76" s="6">
-        <v>480</v>
+        <v>260</v>
       </c>
     </row>
     <row outlineLevel="0" r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>205/55R17</t>
+          <t>195/65R15</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>LASSA</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>GD205/55R17</t>
+          <t>LS195/65R15</t>
         </is>
       </c>
       <c r="D77" s="5">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="E77" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F77" s="5">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G77" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H77" s="6">
-        <v>450</v>
+        <v>250</v>
       </c>
     </row>
     <row outlineLevel="0" r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>205/55R17</t>
+          <t>195/65R15</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>NX205/55R17</t>
+          <t>NX195/65R15</t>
         </is>
       </c>
       <c r="D78" s="5">
@@ -3012,109 +3012,109 @@
         <v>0</v>
       </c>
       <c r="H78" s="6">
-        <v>400</v>
+        <v>230</v>
       </c>
     </row>
     <row outlineLevel="0" r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>205/60R16</t>
+          <t>195/65R15</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>DL205/60R16</t>
+          <t>RD195/65R15</t>
         </is>
       </c>
       <c r="D79" s="5">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="E79" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F79" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G79" s="5">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H79" s="6">
-        <v>330</v>
+        <v>230</v>
       </c>
     </row>
     <row outlineLevel="0" r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>205/60R16</t>
+          <t>195/65R15</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>SEMPERIT</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>GD205/60R16</t>
+          <t>SP195/65R15</t>
         </is>
       </c>
       <c r="D80" s="5">
-        <v>15</v>
+        <v>88</v>
       </c>
       <c r="E80" s="5">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F80" s="5">
-        <v>15</v>
+        <v>69</v>
       </c>
       <c r="G80" s="5">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="H80" s="6">
-        <v>380</v>
+        <v>250</v>
       </c>
     </row>
     <row outlineLevel="0" r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>205/60R16</t>
+          <t>195/70R15C</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>DAYTON</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>HK205/60R16</t>
+          <t>DT195/70R15C</t>
         </is>
       </c>
       <c r="D81" s="5">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E81" s="5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F81" s="5">
         <v>0</v>
       </c>
       <c r="G81" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H81" s="6">
-        <v>300</v>
+        <v>280</v>
       </c>
     </row>
     <row outlineLevel="0" r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>205/60R16</t>
+          <t>195/70R15C</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
@@ -3124,14 +3124,14 @@
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>LF205/60R16</t>
+          <t>LF195/70R15C</t>
         </is>
       </c>
       <c r="D82" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E82" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F82" s="5">
         <v>0</v>
@@ -3146,56 +3146,56 @@
     <row outlineLevel="0" r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>205/65R15</t>
+          <t>195/75R16C</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODRIDE</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>HK205/65R15</t>
+          <t>GR195/75R16C</t>
         </is>
       </c>
       <c r="D83" s="5">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E83" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F83" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G83" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H83" s="6">
-        <v>270</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>205/65R16</t>
+          <t>195R14C</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>BR205/65R16</t>
+          <t>RD195R14C</t>
         </is>
       </c>
       <c r="D84" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E84" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F84" s="5">
         <v>0</v>
@@ -3204,126 +3204,126 @@
         <v>0</v>
       </c>
       <c r="H84" s="6">
-        <v>420</v>
+        <v>280</v>
       </c>
     </row>
     <row outlineLevel="0" r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>205/65R16</t>
+          <t>195R15C</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>HK205/65R16</t>
+          <t>RD195R15C</t>
         </is>
       </c>
       <c r="D85" s="5">
         <v>1</v>
       </c>
       <c r="E85" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F85" s="5">
         <v>0</v>
       </c>
       <c r="G85" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H85" s="6">
-        <v>380</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>215/40R18</t>
+          <t>205/45R17</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>GD215/40R18</t>
+          <t>CT205/45R17</t>
         </is>
       </c>
       <c r="D86" s="5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E86" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F86" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G86" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H86" s="6">
-        <v>600</v>
+        <v>550</v>
       </c>
     </row>
     <row outlineLevel="0" r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>215/40R18</t>
+          <t>205/45R17</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>FULDA</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>HK215/40R18</t>
+          <t>FL205/45R17</t>
         </is>
       </c>
       <c r="D87" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E87" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F87" s="5">
         <v>0</v>
       </c>
       <c r="G87" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H87" s="6">
-        <v>490</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>215/45R16</t>
+          <t>205/45R17</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>GOODRIDE</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>GD215/45R16</t>
+          <t>GR205/45R17</t>
         </is>
       </c>
       <c r="D88" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E88" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F88" s="5">
         <v>0</v>
@@ -3332,13 +3332,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="6">
-        <v>450</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>215/45R17</t>
+          <t>205/45R17</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
@@ -3348,71 +3348,71 @@
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>GD215/45R17</t>
+          <t>GD205/45R17</t>
         </is>
       </c>
       <c r="D89" s="5">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="E89" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F89" s="5">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G89" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H89" s="6">
-        <v>400</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>215/45R17</t>
+          <t>205/45R17</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>HK215/45R17</t>
+          <t>NX205/45R17</t>
         </is>
       </c>
       <c r="D90" s="5">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="E90" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F90" s="5">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G90" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H90" s="6">
-        <v>400</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>215/45R17</t>
+          <t>205/45R17</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>IRIS</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>IR215/45R17</t>
+          <t>RD205/45R17</t>
         </is>
       </c>
       <c r="D91" s="5">
@@ -3434,24 +3434,24 @@
     <row outlineLevel="0" r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>215/45R17</t>
+          <t>205/50R17</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>LF215/45R17</t>
+          <t>CT205/50R17</t>
         </is>
       </c>
       <c r="D92" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E92" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F92" s="5">
         <v>0</v>
@@ -3460,62 +3460,62 @@
         <v>0</v>
       </c>
       <c r="H92" s="6">
-        <v>350</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>215/45R17</t>
+          <t>205/50R17</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>NX215/45R17</t>
+          <t>GD205/50R17</t>
         </is>
       </c>
       <c r="D93" s="5">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E93" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F93" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G93" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H93" s="6">
-        <v>380</v>
+        <v>480</v>
       </c>
     </row>
     <row outlineLevel="0" r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>215/45R18</t>
+          <t>205/55R16</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>AMINE</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>GD215/45R18</t>
+          <t>AM205/55R16</t>
         </is>
       </c>
       <c r="D94" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E94" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F94" s="5">
         <v>0</v>
@@ -3524,13 +3524,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="6">
-        <v>550</v>
+        <v>240</v>
       </c>
     </row>
     <row outlineLevel="0" r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>215/50R17</t>
+          <t>205/55R16</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
@@ -3540,125 +3540,125 @@
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>BR215/50R17</t>
+          <t>BR205/55R16</t>
         </is>
       </c>
       <c r="D95" s="5">
         <v>2</v>
       </c>
       <c r="E95" s="5">
+        <v>0</v>
+      </c>
+      <c r="F95" s="5">
+        <v>0</v>
+      </c>
+      <c r="G95" s="5">
         <v>2</v>
       </c>
-      <c r="F95" s="5">
-        <v>0</v>
-      </c>
-      <c r="G95" s="5">
-        <v>0</v>
-      </c>
       <c r="H95" s="6">
-        <v>450</v>
+        <v>290</v>
       </c>
     </row>
     <row outlineLevel="0" r="96">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>215/50R17</t>
+          <t>205/55R16</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>DOUBLESTAR</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>GD215/50R17</t>
+          <t>DS205/55R16</t>
         </is>
       </c>
       <c r="D96" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E96" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F96" s="5">
         <v>0</v>
       </c>
       <c r="G96" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H96" s="6">
-        <v>470</v>
+        <v>230</v>
       </c>
     </row>
     <row outlineLevel="0" r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>215/50R17</t>
+          <t>205/55R16</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>FULDA</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>HK215/50R17</t>
+          <t>FL205/55R16</t>
         </is>
       </c>
       <c r="D97" s="5">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="E97" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F97" s="5">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G97" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H97" s="6">
-        <v>400</v>
+        <v>250</v>
       </c>
     </row>
     <row outlineLevel="0" r="98">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>215/50R18</t>
+          <t>205/55R16</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>GOODRIDE</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>GD215/50R18</t>
+          <t>GR205/55R16</t>
         </is>
       </c>
       <c r="D98" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E98" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F98" s="5">
         <v>0</v>
       </c>
       <c r="G98" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H98" s="6">
-        <v>600</v>
+        <v>250</v>
       </c>
     </row>
     <row outlineLevel="0" r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>215/55R16</t>
+          <t>205/55R16</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
@@ -3668,11 +3668,11 @@
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>GD215/55R16</t>
+          <t>GD205/55R16</t>
         </is>
       </c>
       <c r="D99" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E99" s="5">
         <v>1</v>
@@ -3681,112 +3681,112 @@
         <v>0</v>
       </c>
       <c r="G99" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H99" s="6">
-        <v>440</v>
+        <v>280</v>
       </c>
     </row>
     <row outlineLevel="0" r="100">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>215/55R16</t>
+          <t>205/55R16</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>LF215/55R16</t>
+          <t>HK205/55R16</t>
         </is>
       </c>
       <c r="D100" s="5">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E100" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F100" s="5">
         <v>0</v>
       </c>
       <c r="G100" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H100" s="6">
-        <v>350</v>
+        <v>260</v>
       </c>
     </row>
     <row outlineLevel="0" r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>215/55R17</t>
+          <t>205/55R16</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>BR215/55R17</t>
+          <t>RD205/55R16</t>
         </is>
       </c>
       <c r="D101" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E101" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F101" s="5">
         <v>0</v>
       </c>
       <c r="G101" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H101" s="6">
-        <v>480</v>
+        <v>230</v>
       </c>
     </row>
     <row outlineLevel="0" r="102">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>215/55R17</t>
+          <t>205/55R16RF</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>HK215/55R17</t>
+          <t>GD205/55R16RF</t>
         </is>
       </c>
       <c r="D102" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E102" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F102" s="5">
         <v>0</v>
       </c>
       <c r="G102" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H102" s="6">
-        <v>420</v>
+        <v>480</v>
       </c>
     </row>
     <row outlineLevel="0" r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>215/55R18</t>
+          <t>205/55R17</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
@@ -3796,46 +3796,46 @@
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>GD215/55R18</t>
+          <t>GD205/55R17</t>
         </is>
       </c>
       <c r="D103" s="5">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="E103" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F103" s="5">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G103" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H103" s="6">
-        <v>580</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="104">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>215/60R16</t>
+          <t>205/55R17</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>BR215/60R16</t>
+          <t>NX205/55R17</t>
         </is>
       </c>
       <c r="D104" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E104" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F104" s="5">
         <v>0</v>
@@ -3844,27 +3844,27 @@
         <v>0</v>
       </c>
       <c r="H104" s="6">
-        <v>350</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>215/60R16</t>
+          <t>205/60R16</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>AMINE</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>DL215/60R16</t>
+          <t>AM205/60R16</t>
         </is>
       </c>
       <c r="D105" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E105" s="5">
         <v>0</v>
@@ -3873,71 +3873,71 @@
         <v>0</v>
       </c>
       <c r="G105" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H105" s="6">
-        <v>350</v>
+        <v>270</v>
       </c>
     </row>
     <row outlineLevel="0" r="106">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>215/60R16</t>
+          <t>205/60R16</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>BFGOODRICH</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>HK215/60R16</t>
+          <t>BF205/60R16</t>
         </is>
       </c>
       <c r="D106" s="5">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E106" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F106" s="5">
         <v>0</v>
       </c>
       <c r="G106" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H106" s="6">
-        <v>330</v>
+        <v>320</v>
       </c>
     </row>
     <row outlineLevel="0" r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>215/60R16</t>
+          <t>205/60R16</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>NX215/60R16</t>
+          <t>DL205/60R16</t>
         </is>
       </c>
       <c r="D107" s="5">
         <v>2</v>
       </c>
       <c r="E107" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F107" s="5">
         <v>0</v>
       </c>
       <c r="G107" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H107" s="6">
         <v>330</v>
@@ -3946,88 +3946,88 @@
     <row outlineLevel="0" r="108">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>215/60R17</t>
+          <t>205/60R16</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>RD215/60R17</t>
+          <t>GD205/60R16</t>
         </is>
       </c>
       <c r="D108" s="5">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E108" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F108" s="5">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G108" s="5">
         <v>0</v>
       </c>
       <c r="H108" s="6">
-        <v>300</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="109">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>215/65R16</t>
+          <t>205/60R16</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>GD215/65R16</t>
+          <t>HK205/60R16</t>
         </is>
       </c>
       <c r="D109" s="5">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E109" s="5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F109" s="5">
         <v>0</v>
       </c>
       <c r="G109" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H109" s="6">
-        <v>380</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="110">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>215/65R16</t>
+          <t>205/60R16</t>
         </is>
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>LASSA</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>HK215/65R16</t>
+          <t>LS205/60R16</t>
         </is>
       </c>
       <c r="D110" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E110" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F110" s="5">
         <v>0</v>
@@ -4036,23 +4036,23 @@
         <v>0</v>
       </c>
       <c r="H110" s="6">
-        <v>330</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="111">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>215/65R17</t>
+          <t>205/60R16</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>MICHELIN</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>MC215/65R17</t>
+          <t>LF205/60R16</t>
         </is>
       </c>
       <c r="D111" s="5">
@@ -4068,62 +4068,62 @@
         <v>0</v>
       </c>
       <c r="H111" s="6">
-        <v>600</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="112">
       <c r="A112" s="4" t="inlineStr">
         <is>
-          <t>215/70R15C</t>
+          <t>205/65R15</t>
         </is>
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>LINGLONG</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>LG215/70R15C</t>
+          <t>HK205/65R15</t>
         </is>
       </c>
       <c r="D112" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E112" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F112" s="5">
         <v>0</v>
       </c>
       <c r="G112" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H112" s="6">
-        <v>370</v>
+        <v>270</v>
       </c>
     </row>
     <row outlineLevel="0" r="113">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>215/70R15C</t>
+          <t>205/65R16</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>RD215/70R15C</t>
+          <t>BR205/65R16</t>
         </is>
       </c>
       <c r="D113" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E113" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F113" s="5">
         <v>0</v>
@@ -4132,23 +4132,23 @@
         <v>0</v>
       </c>
       <c r="H113" s="6">
-        <v>330</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="114">
       <c r="A114" s="4" t="inlineStr">
         <is>
-          <t>225/40R18</t>
+          <t>205/65R16</t>
         </is>
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>BARUM</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>BM225/40R18</t>
+          <t>HK205/65R16</t>
         </is>
       </c>
       <c r="D114" s="5">
@@ -4164,13 +4164,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="6">
-        <v>420</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="115">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t>225/40R18</t>
+          <t>215/40R18</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
@@ -4180,29 +4180,29 @@
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>GD225/40R18</t>
+          <t>GD215/40R18</t>
         </is>
       </c>
       <c r="D115" s="5">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E115" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F115" s="5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G115" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H115" s="6">
-        <v>480</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="116">
       <c r="A116" s="4" t="inlineStr">
         <is>
-          <t>225/40R18</t>
+          <t>215/40R18</t>
         </is>
       </c>
       <c r="B116" s="4" t="inlineStr">
@@ -4212,7 +4212,7 @@
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>HK225/40R18</t>
+          <t>HK215/40R18</t>
         </is>
       </c>
       <c r="D116" s="5">
@@ -4228,55 +4228,55 @@
         <v>0</v>
       </c>
       <c r="H116" s="6">
-        <v>450</v>
+        <v>490</v>
       </c>
     </row>
     <row outlineLevel="0" r="117">
       <c r="A117" s="4" t="inlineStr">
         <is>
-          <t>225/40R18</t>
+          <t>215/45R16</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>LASSA</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>LS225/40R18</t>
+          <t>GD215/45R16</t>
         </is>
       </c>
       <c r="D117" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E117" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F117" s="5">
         <v>0</v>
       </c>
       <c r="G117" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H117" s="6">
-        <v>330</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="118">
       <c r="A118" s="4" t="inlineStr">
         <is>
-          <t>225/40R18</t>
+          <t>215/45R17</t>
         </is>
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>NX225/40R18</t>
+          <t>GD215/45R17</t>
         </is>
       </c>
       <c r="D118" s="5">
@@ -4298,81 +4298,81 @@
     <row outlineLevel="0" r="119">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t>225/40R18</t>
+          <t>215/45R17</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>SEMPERIT</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>SP225/40R18</t>
+          <t>HK215/45R17</t>
         </is>
       </c>
       <c r="D119" s="5">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="E119" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F119" s="5">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G119" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H119" s="6">
-        <v>450</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="120">
       <c r="A120" s="4" t="inlineStr">
         <is>
-          <t>225/40R18RF</t>
+          <t>215/45R17</t>
         </is>
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>IRIS</t>
         </is>
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>GD225/40R18RF</t>
+          <t>IR215/45R17</t>
         </is>
       </c>
       <c r="D120" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E120" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F120" s="5">
         <v>0</v>
       </c>
       <c r="G120" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H120" s="6">
-        <v>590</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="121">
       <c r="A121" s="4" t="inlineStr">
         <is>
-          <t>225/45R17</t>
+          <t>215/45R17</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>CT225/45R17</t>
+          <t>LF215/45R17</t>
         </is>
       </c>
       <c r="D121" s="5">
@@ -4388,45 +4388,45 @@
         <v>0</v>
       </c>
       <c r="H121" s="6">
-        <v>400</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="122">
       <c r="A122" s="4" t="inlineStr">
         <is>
-          <t>225/45R17</t>
+          <t>215/45R17</t>
         </is>
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>FULDA</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>FL225/45R17</t>
+          <t>NX215/45R17</t>
         </is>
       </c>
       <c r="D122" s="5">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E122" s="5">
         <v>4</v>
       </c>
       <c r="F122" s="5">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G122" s="5">
         <v>4</v>
       </c>
       <c r="H122" s="6">
-        <v>350</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="123">
       <c r="A123" s="4" t="inlineStr">
         <is>
-          <t>225/45R17</t>
+          <t>215/45R18</t>
         </is>
       </c>
       <c r="B123" s="4" t="inlineStr">
@@ -4436,46 +4436,46 @@
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>GD225/45R17</t>
+          <t>GD215/45R18</t>
         </is>
       </c>
       <c r="D123" s="5">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="E123" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F123" s="5">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G123" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H123" s="6">
-        <v>380</v>
+        <v>550</v>
       </c>
     </row>
     <row outlineLevel="0" r="124">
       <c r="A124" s="4" t="inlineStr">
         <is>
-          <t>225/45R17</t>
+          <t>215/45R18</t>
         </is>
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>HK225/45R17</t>
+          <t>RD215/45R18</t>
         </is>
       </c>
       <c r="D124" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E124" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F124" s="5">
         <v>0</v>
@@ -4484,30 +4484,30 @@
         <v>0</v>
       </c>
       <c r="H124" s="6">
-        <v>350</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="125">
       <c r="A125" s="4" t="inlineStr">
         <is>
-          <t>225/45R18</t>
+          <t>215/50R17</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>DL225/45R18</t>
+          <t>BR215/50R17</t>
         </is>
       </c>
       <c r="D125" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E125" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F125" s="5">
         <v>0</v>
@@ -4516,13 +4516,13 @@
         <v>0</v>
       </c>
       <c r="H125" s="6">
-        <v>500</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="126">
       <c r="A126" s="4" t="inlineStr">
         <is>
-          <t>225/45R18</t>
+          <t>215/50R17</t>
         </is>
       </c>
       <c r="B126" s="4" t="inlineStr">
@@ -4532,46 +4532,46 @@
       </c>
       <c r="C126" s="4" t="inlineStr">
         <is>
-          <t>GD225/45R18</t>
+          <t>GD215/50R17</t>
         </is>
       </c>
       <c r="D126" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E126" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F126" s="5">
+        <v>0</v>
+      </c>
+      <c r="G126" s="5">
         <v>2</v>
       </c>
-      <c r="G126" s="5">
-        <v>0</v>
-      </c>
       <c r="H126" s="6">
-        <v>550</v>
+        <v>470</v>
       </c>
     </row>
     <row outlineLevel="0" r="127">
       <c r="A127" s="4" t="inlineStr">
         <is>
-          <t>225/45R18</t>
+          <t>215/50R17</t>
         </is>
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>LF225/45R18</t>
+          <t>HK215/50R17</t>
         </is>
       </c>
       <c r="D127" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E127" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F127" s="5">
         <v>0</v>
@@ -4580,62 +4580,62 @@
         <v>0</v>
       </c>
       <c r="H127" s="6">
-        <v>420</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="128">
       <c r="A128" s="4" t="inlineStr">
         <is>
-          <t>225/45R18RF</t>
+          <t>215/50R17</t>
         </is>
       </c>
       <c r="B128" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C128" s="4" t="inlineStr">
         <is>
-          <t>GD225/45R18RF</t>
+          <t>LF215/50R17</t>
         </is>
       </c>
       <c r="D128" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E128" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F128" s="5">
         <v>0</v>
       </c>
       <c r="G128" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H128" s="6">
-        <v>720</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="129">
       <c r="A129" s="4" t="inlineStr">
         <is>
-          <t>225/45R19</t>
+          <t>215/50R18</t>
         </is>
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>CT225/45R19</t>
+          <t>GD215/50R18</t>
         </is>
       </c>
       <c r="D129" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E129" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F129" s="5">
         <v>0</v>
@@ -4644,23 +4644,23 @@
         <v>0</v>
       </c>
       <c r="H129" s="6">
-        <v>780</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="130">
       <c r="A130" s="4" t="inlineStr">
         <is>
-          <t>225/50R17</t>
+          <t>215/55R16</t>
         </is>
       </c>
       <c r="B130" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C130" s="4" t="inlineStr">
         <is>
-          <t>BR225/50R17</t>
+          <t>GD215/55R16</t>
         </is>
       </c>
       <c r="D130" s="5">
@@ -4676,94 +4676,94 @@
         <v>0</v>
       </c>
       <c r="H130" s="6">
-        <v>600</v>
+        <v>440</v>
       </c>
     </row>
     <row outlineLevel="0" r="131">
       <c r="A131" s="4" t="inlineStr">
         <is>
-          <t>225/50R17</t>
+          <t>215/55R16</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>GD225/50R17</t>
+          <t>LF215/55R16</t>
         </is>
       </c>
       <c r="D131" s="5">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E131" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F131" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G131" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H131" s="6">
-        <v>500</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="132">
       <c r="A132" s="4" t="inlineStr">
         <is>
-          <t>225/50R17</t>
+          <t>215/55R17</t>
         </is>
       </c>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C132" s="4" t="inlineStr">
         <is>
-          <t>HK225/50R17</t>
+          <t>BR215/55R17</t>
         </is>
       </c>
       <c r="D132" s="5">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E132" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F132" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G132" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H132" s="6">
-        <v>400</v>
+        <v>480</v>
       </c>
     </row>
     <row outlineLevel="0" r="133">
       <c r="A133" s="4" t="inlineStr">
         <is>
-          <t>225/55R16</t>
+          <t>215/55R17</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>DL225/55R16</t>
+          <t>HK215/55R17</t>
         </is>
       </c>
       <c r="D133" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E133" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F133" s="5">
         <v>0</v>
@@ -4772,30 +4772,30 @@
         <v>0</v>
       </c>
       <c r="H133" s="6">
-        <v>450</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="134">
       <c r="A134" s="4" t="inlineStr">
         <is>
-          <t>225/55R16</t>
+          <t>215/55R17</t>
         </is>
       </c>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>SEMPERIT</t>
         </is>
       </c>
       <c r="C134" s="4" t="inlineStr">
         <is>
-          <t>GD225/55R16</t>
+          <t>SP215/55R17</t>
         </is>
       </c>
       <c r="D134" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E134" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F134" s="5">
         <v>0</v>
@@ -4810,17 +4810,17 @@
     <row outlineLevel="0" r="135">
       <c r="A135" s="4" t="inlineStr">
         <is>
-          <t>225/55R17</t>
+          <t>215/55R18</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>HK225/55R17</t>
+          <t>GD215/55R18</t>
         </is>
       </c>
       <c r="D135" s="5">
@@ -4836,183 +4836,183 @@
         <v>0</v>
       </c>
       <c r="H135" s="6">
-        <v>430</v>
+        <v>580</v>
       </c>
     </row>
     <row outlineLevel="0" r="136">
       <c r="A136" s="4" t="inlineStr">
         <is>
-          <t>225/55R17RF</t>
+          <t>215/60R16</t>
         </is>
       </c>
       <c r="B136" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C136" s="4" t="inlineStr">
         <is>
-          <t>GD225/55R17RF</t>
+          <t>BR215/60R16</t>
         </is>
       </c>
       <c r="D136" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E136" s="5">
         <v>4</v>
       </c>
       <c r="F136" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G136" s="5">
         <v>0</v>
       </c>
       <c r="H136" s="6">
-        <v>700</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="137">
       <c r="A137" s="4" t="inlineStr">
         <is>
-          <t>225/55R18</t>
+          <t>215/60R16</t>
         </is>
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>KUMHO</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>KM225/55R18</t>
+          <t>DL215/60R16</t>
         </is>
       </c>
       <c r="D137" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E137" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F137" s="5">
         <v>0</v>
       </c>
       <c r="G137" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H137" s="6">
-        <v>450</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="138">
       <c r="A138" s="4" t="inlineStr">
         <is>
-          <t>225/55R19</t>
+          <t>215/60R16</t>
         </is>
       </c>
       <c r="B138" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C138" s="4" t="inlineStr">
         <is>
-          <t>BR225/55R19</t>
+          <t>HK215/60R16</t>
         </is>
       </c>
       <c r="D138" s="5">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E138" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F138" s="5">
         <v>0</v>
       </c>
       <c r="G138" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H138" s="6">
-        <v>750</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="139">
       <c r="A139" s="4" t="inlineStr">
         <is>
-          <t>225/55R19</t>
+          <t>215/60R16</t>
         </is>
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>GD225/55R19</t>
+          <t>NX215/60R16</t>
         </is>
       </c>
       <c r="D139" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E139" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F139" s="5">
         <v>0</v>
       </c>
       <c r="G139" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H139" s="6">
-        <v>750</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="140">
       <c r="A140" s="4" t="inlineStr">
         <is>
-          <t>225/60R17</t>
+          <t>215/60R17</t>
         </is>
       </c>
       <c r="B140" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C140" s="4" t="inlineStr">
         <is>
-          <t>HK225/60R17</t>
+          <t>GD215/60R17</t>
         </is>
       </c>
       <c r="D140" s="5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E140" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F140" s="5">
         <v>0</v>
       </c>
       <c r="G140" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H140" s="6">
-        <v>400</v>
+        <v>480</v>
       </c>
     </row>
     <row outlineLevel="0" r="141">
       <c r="A141" s="4" t="inlineStr">
         <is>
-          <t>225/60R18</t>
+          <t>215/60R17</t>
         </is>
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>GD225/60R18</t>
+          <t>RD215/60R17</t>
         </is>
       </c>
       <c r="D141" s="5">
@@ -5028,158 +5028,158 @@
         <v>0</v>
       </c>
       <c r="H141" s="6">
-        <v>700</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="142">
       <c r="A142" s="4" t="inlineStr">
         <is>
-          <t>225/65R17</t>
+          <t>215/65R16</t>
         </is>
       </c>
       <c r="B142" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C142" s="4" t="inlineStr">
         <is>
-          <t>RD225/65R17</t>
+          <t>GD215/65R16</t>
         </is>
       </c>
       <c r="D142" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E142" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F142" s="5">
         <v>0</v>
       </c>
       <c r="G142" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H142" s="6">
-        <v>450</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="143">
       <c r="A143" s="4" t="inlineStr">
         <is>
-          <t>225/70R15C</t>
+          <t>215/65R16</t>
         </is>
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>MATADOR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>MT225/70R15C</t>
+          <t>HK215/65R16</t>
         </is>
       </c>
       <c r="D143" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E143" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F143" s="5">
         <v>0</v>
       </c>
       <c r="G143" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H143" s="6">
-        <v>450</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="144">
       <c r="A144" s="4" t="inlineStr">
         <is>
-          <t>225/75R15C</t>
+          <t>215/65R17</t>
         </is>
       </c>
       <c r="B144" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>MICHELIN</t>
         </is>
       </c>
       <c r="C144" s="4" t="inlineStr">
         <is>
-          <t>RD225/75R15C</t>
+          <t>MC215/65R17</t>
         </is>
       </c>
       <c r="D144" s="5">
         <v>1</v>
       </c>
       <c r="E144" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F144" s="5">
         <v>0</v>
       </c>
       <c r="G144" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H144" s="6">
-        <v>330</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="145">
       <c r="A145" s="4" t="inlineStr">
         <is>
-          <t>235/35R19</t>
+          <t>215/65R17</t>
         </is>
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>RD235/35R19</t>
+          <t>NX215/65R17</t>
         </is>
       </c>
       <c r="D145" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E145" s="5">
         <v>0</v>
       </c>
       <c r="F145" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G145" s="5">
         <v>0</v>
       </c>
       <c r="H145" s="6">
-        <v>600</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="146">
       <c r="A146" s="4" t="inlineStr">
         <is>
-          <t>235/40R19</t>
+          <t>215/70R15C</t>
         </is>
       </c>
       <c r="B146" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>DOUBLESTAR</t>
         </is>
       </c>
       <c r="C146" s="4" t="inlineStr">
         <is>
-          <t>GD235/40R19</t>
+          <t>DS215/70R15C</t>
         </is>
       </c>
       <c r="D146" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E146" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F146" s="5">
         <v>0</v>
@@ -5188,62 +5188,62 @@
         <v>0</v>
       </c>
       <c r="H146" s="6">
-        <v>850</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="147">
       <c r="A147" s="4" t="inlineStr">
         <is>
-          <t>235/45R18</t>
+          <t>215/70R15C</t>
         </is>
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>LINGLONG</t>
         </is>
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>GD235/45R18</t>
+          <t>LG215/70R15C</t>
         </is>
       </c>
       <c r="D147" s="5">
         <v>4</v>
       </c>
       <c r="E147" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F147" s="5">
         <v>0</v>
       </c>
       <c r="G147" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H147" s="6">
-        <v>600</v>
+        <v>370</v>
       </c>
     </row>
     <row outlineLevel="0" r="148">
       <c r="A148" s="4" t="inlineStr">
         <is>
-          <t>235/50R18</t>
+          <t>215/70R15C</t>
         </is>
       </c>
       <c r="B148" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>MICHELIN</t>
         </is>
       </c>
       <c r="C148" s="4" t="inlineStr">
         <is>
-          <t>HK235/50R18</t>
+          <t>MC215/70R15C</t>
         </is>
       </c>
       <c r="D148" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E148" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F148" s="5">
         <v>0</v>
@@ -5252,30 +5252,30 @@
         <v>0</v>
       </c>
       <c r="H148" s="6">
-        <v>500</v>
+        <v>590</v>
       </c>
     </row>
     <row outlineLevel="0" r="149">
       <c r="A149" s="4" t="inlineStr">
         <is>
-          <t>235/50R19</t>
+          <t>215/70R15C</t>
         </is>
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>GD235/50R19</t>
+          <t>RD215/70R15C</t>
         </is>
       </c>
       <c r="D149" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E149" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F149" s="5">
         <v>0</v>
@@ -5284,77 +5284,77 @@
         <v>0</v>
       </c>
       <c r="H149" s="6">
-        <v>800</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="150">
       <c r="A150" s="4" t="inlineStr">
         <is>
-          <t>235/50R20</t>
+          <t>225/40R18</t>
         </is>
       </c>
       <c r="B150" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>BARUM</t>
         </is>
       </c>
       <c r="C150" s="4" t="inlineStr">
         <is>
-          <t>GD235/50R20</t>
+          <t>BM225/40R18</t>
         </is>
       </c>
       <c r="D150" s="5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E150" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F150" s="5">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G150" s="5">
         <v>0</v>
       </c>
       <c r="H150" s="6">
-        <v>1180</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="151">
       <c r="A151" s="4" t="inlineStr">
         <is>
-          <t>235/55R17</t>
+          <t>225/40R18</t>
         </is>
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>BR235/55R17</t>
+          <t>GD225/40R18</t>
         </is>
       </c>
       <c r="D151" s="5">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="E151" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F151" s="5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G151" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H151" s="6">
-        <v>450</v>
+        <v>480</v>
       </c>
     </row>
     <row outlineLevel="0" r="152">
       <c r="A152" s="4" t="inlineStr">
         <is>
-          <t>235/55R18</t>
+          <t>225/40R18</t>
         </is>
       </c>
       <c r="B152" s="4" t="inlineStr">
@@ -5364,14 +5364,14 @@
       </c>
       <c r="C152" s="4" t="inlineStr">
         <is>
-          <t>HK235/55R18</t>
+          <t>HK225/40R18</t>
         </is>
       </c>
       <c r="D152" s="5">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E152" s="5">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F152" s="5">
         <v>0</v>
@@ -5380,62 +5380,62 @@
         <v>0</v>
       </c>
       <c r="H152" s="6">
-        <v>480</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="153">
       <c r="A153" s="4" t="inlineStr">
         <is>
-          <t>235/55R19</t>
+          <t>225/40R18</t>
         </is>
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>LASSA</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>GD235/55R19</t>
+          <t>LS225/40R18</t>
         </is>
       </c>
       <c r="D153" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E153" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F153" s="5">
         <v>0</v>
       </c>
       <c r="G153" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H153" s="6">
-        <v>750</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="154">
       <c r="A154" s="4" t="inlineStr">
         <is>
-          <t>235/55R19</t>
+          <t>225/40R18</t>
         </is>
       </c>
       <c r="B154" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C154" s="4" t="inlineStr">
         <is>
-          <t>HK235/55R19</t>
+          <t>NX225/40R18</t>
         </is>
       </c>
       <c r="D154" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E154" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F154" s="5">
         <v>0</v>
@@ -5444,23 +5444,23 @@
         <v>0</v>
       </c>
       <c r="H154" s="6">
-        <v>630</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="155">
       <c r="A155" s="4" t="inlineStr">
         <is>
-          <t>235/55R19</t>
+          <t>225/40R18</t>
         </is>
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>SEMPERIT</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>LF235/55R19</t>
+          <t>SP225/40R18</t>
         </is>
       </c>
       <c r="D155" s="5">
@@ -5476,30 +5476,30 @@
         <v>0</v>
       </c>
       <c r="H155" s="6">
-        <v>500</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="156">
       <c r="A156" s="4" t="inlineStr">
         <is>
-          <t>235/55R19</t>
+          <t>225/40R18RF</t>
         </is>
       </c>
       <c r="B156" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C156" s="4" t="inlineStr">
         <is>
-          <t>NX235/55R19</t>
+          <t>GD225/40R18RF</t>
         </is>
       </c>
       <c r="D156" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E156" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F156" s="5">
         <v>0</v>
@@ -5508,62 +5508,62 @@
         <v>0</v>
       </c>
       <c r="H156" s="6">
-        <v>600</v>
+        <v>590</v>
       </c>
     </row>
     <row outlineLevel="0" r="157">
       <c r="A157" s="4" t="inlineStr">
         <is>
-          <t>235/55R19</t>
+          <t>225/40R19RF</t>
         </is>
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>RD235/55R19</t>
+          <t>GD225/40R19RF</t>
         </is>
       </c>
       <c r="D157" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E157" s="5">
         <v>0</v>
       </c>
       <c r="F157" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G157" s="5">
         <v>0</v>
       </c>
       <c r="H157" s="6">
-        <v>500</v>
+        <v>1200</v>
       </c>
     </row>
     <row outlineLevel="0" r="158">
       <c r="A158" s="4" t="inlineStr">
         <is>
-          <t>235/60R16</t>
+          <t>225/45R17</t>
         </is>
       </c>
       <c r="B158" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C158" s="4" t="inlineStr">
         <is>
-          <t>HK235/60R16</t>
+          <t>CT225/45R17</t>
         </is>
       </c>
       <c r="D158" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E158" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F158" s="5">
         <v>0</v>
@@ -5572,45 +5572,45 @@
         <v>0</v>
       </c>
       <c r="H158" s="6">
-        <v>430</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="159">
       <c r="A159" s="4" t="inlineStr">
         <is>
-          <t>235/60R17</t>
+          <t>225/45R17</t>
         </is>
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>FULDA</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>HK235/60R17</t>
+          <t>FL225/45R17</t>
         </is>
       </c>
       <c r="D159" s="5">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="E159" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F159" s="5">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G159" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H159" s="6">
-        <v>500</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="160">
       <c r="A160" s="4" t="inlineStr">
         <is>
-          <t>235/60R18</t>
+          <t>225/45R17</t>
         </is>
       </c>
       <c r="B160" s="4" t="inlineStr">
@@ -5620,29 +5620,29 @@
       </c>
       <c r="C160" s="4" t="inlineStr">
         <is>
-          <t>GD235/60R18</t>
+          <t>GD225/45R17</t>
         </is>
       </c>
       <c r="D160" s="5">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="E160" s="5">
         <v>2</v>
       </c>
       <c r="F160" s="5">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G160" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H160" s="6">
-        <v>680</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="161">
       <c r="A161" s="4" t="inlineStr">
         <is>
-          <t>235/60R18</t>
+          <t>225/45R17</t>
         </is>
       </c>
       <c r="B161" s="4" t="inlineStr">
@@ -5652,14 +5652,14 @@
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>HK235/60R18</t>
+          <t>HK225/45R17</t>
         </is>
       </c>
       <c r="D161" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E161" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F161" s="5">
         <v>0</v>
@@ -5668,30 +5668,30 @@
         <v>0</v>
       </c>
       <c r="H161" s="6">
-        <v>550</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="162">
       <c r="A162" s="4" t="inlineStr">
         <is>
-          <t>245/40R17</t>
+          <t>225/45R18</t>
         </is>
       </c>
       <c r="B162" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C162" s="4" t="inlineStr">
         <is>
-          <t>GD245/40R17</t>
+          <t>DL225/45R18</t>
         </is>
       </c>
       <c r="D162" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E162" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F162" s="5">
         <v>0</v>
@@ -5700,13 +5700,13 @@
         <v>0</v>
       </c>
       <c r="H162" s="6">
-        <v>400</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="163">
       <c r="A163" s="4" t="inlineStr">
         <is>
-          <t>245/40R18</t>
+          <t>225/45R18</t>
         </is>
       </c>
       <c r="B163" s="4" t="inlineStr">
@@ -5716,29 +5716,29 @@
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>GD245/40R18</t>
+          <t>GD225/45R18</t>
         </is>
       </c>
       <c r="D163" s="5">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E163" s="5">
+        <v>4</v>
+      </c>
+      <c r="F163" s="5">
         <v>2</v>
       </c>
-      <c r="F163" s="5">
-        <v>0</v>
-      </c>
       <c r="G163" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H163" s="6">
-        <v>620</v>
+        <v>550</v>
       </c>
     </row>
     <row outlineLevel="0" r="164">
       <c r="A164" s="4" t="inlineStr">
         <is>
-          <t>245/40R19</t>
+          <t>225/45R18</t>
         </is>
       </c>
       <c r="B164" s="4" t="inlineStr">
@@ -5748,14 +5748,14 @@
       </c>
       <c r="C164" s="4" t="inlineStr">
         <is>
-          <t>HK245/40R19</t>
+          <t>HK225/45R18</t>
         </is>
       </c>
       <c r="D164" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E164" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F164" s="5">
         <v>0</v>
@@ -5764,77 +5764,77 @@
         <v>0</v>
       </c>
       <c r="H164" s="6">
-        <v>750</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="165">
       <c r="A165" s="4" t="inlineStr">
         <is>
-          <t>245/40R20</t>
+          <t>225/45R18</t>
         </is>
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>CT245/40R20</t>
+          <t>LF225/45R18</t>
         </is>
       </c>
       <c r="D165" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E165" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F165" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G165" s="5">
         <v>0</v>
       </c>
       <c r="H165" s="6">
-        <v>1050</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="166">
       <c r="A166" s="4" t="inlineStr">
         <is>
-          <t>245/45R17</t>
+          <t>225/45R18RF</t>
         </is>
       </c>
       <c r="B166" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C166" s="4" t="inlineStr">
         <is>
-          <t>HK245/45R17</t>
+          <t>GD225/45R18RF</t>
         </is>
       </c>
       <c r="D166" s="5">
         <v>4</v>
       </c>
       <c r="E166" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F166" s="5">
         <v>0</v>
       </c>
       <c r="G166" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H166" s="6">
-        <v>430</v>
+        <v>720</v>
       </c>
     </row>
     <row outlineLevel="0" r="167">
       <c r="A167" s="4" t="inlineStr">
         <is>
-          <t>245/45R18</t>
+          <t>225/45R19</t>
         </is>
       </c>
       <c r="B167" s="4" t="inlineStr">
@@ -5844,7 +5844,7 @@
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>CT245/45R18</t>
+          <t>CT225/45R19</t>
         </is>
       </c>
       <c r="D167" s="5">
@@ -5860,30 +5860,30 @@
         <v>0</v>
       </c>
       <c r="H167" s="6">
-        <v>650</v>
+        <v>780</v>
       </c>
     </row>
     <row outlineLevel="0" r="168">
       <c r="A168" s="4" t="inlineStr">
         <is>
-          <t>245/45R18</t>
+          <t>225/45R19</t>
         </is>
       </c>
       <c r="B168" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>LASSA</t>
         </is>
       </c>
       <c r="C168" s="4" t="inlineStr">
         <is>
-          <t>GD245/45R18</t>
+          <t>LS225/45R19</t>
         </is>
       </c>
       <c r="D168" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E168" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F168" s="5">
         <v>0</v>
@@ -5892,23 +5892,23 @@
         <v>0</v>
       </c>
       <c r="H168" s="6">
-        <v>600</v>
+        <v>520</v>
       </c>
     </row>
     <row outlineLevel="0" r="169">
       <c r="A169" s="4" t="inlineStr">
         <is>
-          <t>245/45R18</t>
+          <t>225/50R17</t>
         </is>
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>HK245/45R18</t>
+          <t>BR225/50R17</t>
         </is>
       </c>
       <c r="D169" s="5">
@@ -5924,13 +5924,13 @@
         <v>0</v>
       </c>
       <c r="H169" s="6">
-        <v>500</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="170">
       <c r="A170" s="4" t="inlineStr">
         <is>
-          <t>245/45R18RF</t>
+          <t>225/50R17</t>
         </is>
       </c>
       <c r="B170" s="4" t="inlineStr">
@@ -5940,81 +5940,81 @@
       </c>
       <c r="C170" s="4" t="inlineStr">
         <is>
-          <t>GD245/45R18RF</t>
+          <t>GD225/50R17</t>
         </is>
       </c>
       <c r="D170" s="5">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E170" s="5">
         <v>4</v>
       </c>
       <c r="F170" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G170" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H170" s="6">
-        <v>720</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="171">
       <c r="A171" s="4" t="inlineStr">
         <is>
-          <t>245/45R19</t>
+          <t>225/50R17</t>
         </is>
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t>BR245/45R19</t>
+          <t>HK225/50R17</t>
         </is>
       </c>
       <c r="D171" s="5">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E171" s="5">
         <v>4</v>
       </c>
       <c r="F171" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G171" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H171" s="6">
-        <v>790</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="172">
       <c r="A172" s="4" t="inlineStr">
         <is>
-          <t>245/45R19</t>
+          <t>225/55R16</t>
         </is>
       </c>
       <c r="B172" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C172" s="4" t="inlineStr">
         <is>
-          <t>RD245/45R19</t>
+          <t>DL225/55R16</t>
         </is>
       </c>
       <c r="D172" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E172" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F172" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G172" s="5">
         <v>0</v>
@@ -6026,91 +6026,91 @@
     <row outlineLevel="0" r="173">
       <c r="A173" s="4" t="inlineStr">
         <is>
-          <t>245/45R20</t>
+          <t>225/55R16</t>
         </is>
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>HK245/45R20</t>
+          <t>GD225/55R16</t>
         </is>
       </c>
       <c r="D173" s="5">
         <v>2</v>
       </c>
       <c r="E173" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F173" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G173" s="5">
         <v>0</v>
       </c>
       <c r="H173" s="6">
-        <v>750</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="174">
       <c r="A174" s="4" t="inlineStr">
         <is>
-          <t>245/65R17</t>
+          <t>225/55R17</t>
         </is>
       </c>
       <c r="B174" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C174" s="4" t="inlineStr">
         <is>
-          <t>NX245/65R17</t>
+          <t>HK225/55R17</t>
         </is>
       </c>
       <c r="D174" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E174" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F174" s="5">
         <v>0</v>
       </c>
       <c r="G174" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H174" s="6">
-        <v>600</v>
+        <v>430</v>
       </c>
     </row>
     <row outlineLevel="0" r="175">
       <c r="A175" s="4" t="inlineStr">
         <is>
-          <t>255/35R19</t>
+          <t>225/55R17RF</t>
         </is>
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>DL255/35R19</t>
+          <t>GD225/55R17RF</t>
         </is>
       </c>
       <c r="D175" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E175" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F175" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G175" s="5">
         <v>0</v>
@@ -6122,24 +6122,24 @@
     <row outlineLevel="0" r="176">
       <c r="A176" s="4" t="inlineStr">
         <is>
-          <t>255/35R19RF</t>
+          <t>225/55R18</t>
         </is>
       </c>
       <c r="B176" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C176" s="4" t="inlineStr">
         <is>
-          <t>CT255/35R19RF</t>
+          <t>HK225/55R18</t>
         </is>
       </c>
       <c r="D176" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E176" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F176" s="5">
         <v>0</v>
@@ -6148,30 +6148,30 @@
         <v>0</v>
       </c>
       <c r="H176" s="6">
-        <v>950</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="177">
       <c r="A177" s="4" t="inlineStr">
         <is>
-          <t>255/35R19RF</t>
+          <t>225/55R18</t>
         </is>
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>KUMHO</t>
         </is>
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>GD255/35R19RF</t>
+          <t>KM225/55R18</t>
         </is>
       </c>
       <c r="D177" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E177" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F177" s="5">
         <v>0</v>
@@ -6180,33 +6180,33 @@
         <v>0</v>
       </c>
       <c r="H177" s="6">
-        <v>950</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="178">
       <c r="A178" s="4" t="inlineStr">
         <is>
-          <t>255/50R19</t>
+          <t>225/55R19</t>
         </is>
       </c>
       <c r="B178" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C178" s="4" t="inlineStr">
         <is>
-          <t>CT255/50R19</t>
+          <t>BR225/55R19</t>
         </is>
       </c>
       <c r="D178" s="5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E178" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F178" s="5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G178" s="5">
         <v>0</v>
@@ -6218,152 +6218,152 @@
     <row outlineLevel="0" r="179">
       <c r="A179" s="4" t="inlineStr">
         <is>
-          <t>255/50R20</t>
+          <t>225/55R19</t>
         </is>
       </c>
       <c r="B179" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C179" s="4" t="inlineStr">
         <is>
-          <t>CT255/50R20</t>
+          <t>GD225/55R19</t>
         </is>
       </c>
       <c r="D179" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E179" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F179" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G179" s="5">
         <v>0</v>
       </c>
       <c r="H179" s="6">
-        <v>900</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="180">
       <c r="A180" s="4" t="inlineStr">
         <is>
-          <t>255/55R19</t>
+          <t>225/60R17</t>
         </is>
       </c>
       <c r="B180" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C180" s="4" t="inlineStr">
         <is>
-          <t>CT255/55R19</t>
+          <t>GD225/60R17</t>
         </is>
       </c>
       <c r="D180" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E180" s="5">
         <v>0</v>
       </c>
       <c r="F180" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G180" s="5">
         <v>0</v>
       </c>
       <c r="H180" s="6">
-        <v>750</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="181">
       <c r="A181" s="4" t="inlineStr">
         <is>
-          <t>255/55R19</t>
+          <t>225/60R17</t>
         </is>
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C181" s="4" t="inlineStr">
         <is>
-          <t>DL255/55R19</t>
+          <t>HK225/60R17</t>
         </is>
       </c>
       <c r="D181" s="5">
+        <v>6</v>
+      </c>
+      <c r="E181" s="5">
+        <v>4</v>
+      </c>
+      <c r="F181" s="5">
+        <v>0</v>
+      </c>
+      <c r="G181" s="5">
         <v>2</v>
       </c>
-      <c r="E181" s="5">
-        <v>2</v>
-      </c>
-      <c r="F181" s="5">
-        <v>0</v>
-      </c>
-      <c r="G181" s="5">
-        <v>0</v>
-      </c>
       <c r="H181" s="6">
-        <v>700</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="182">
       <c r="A182" s="4" t="inlineStr">
         <is>
-          <t>255/70R16</t>
+          <t>225/60R18</t>
         </is>
       </c>
       <c r="B182" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C182" s="4" t="inlineStr">
         <is>
-          <t>RD255/70R16</t>
+          <t>GD225/60R18</t>
         </is>
       </c>
       <c r="D182" s="5">
         <v>1</v>
       </c>
       <c r="E182" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F182" s="5">
         <v>0</v>
       </c>
       <c r="G182" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H182" s="6">
-        <v>500</v>
+        <v>700</v>
       </c>
     </row>
     <row outlineLevel="0" r="183">
       <c r="A183" s="4" t="inlineStr">
         <is>
-          <t>265/35R18</t>
+          <t>225/65R17</t>
         </is>
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C183" s="4" t="inlineStr">
         <is>
-          <t>GD265/35R18</t>
+          <t>RD225/65R17</t>
         </is>
       </c>
       <c r="D183" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E183" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F183" s="5">
         <v>0</v>
@@ -6372,23 +6372,23 @@
         <v>0</v>
       </c>
       <c r="H183" s="6">
-        <v>700</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="184">
       <c r="A184" s="4" t="inlineStr">
         <is>
-          <t>265/50R20</t>
+          <t>225/70R15C</t>
         </is>
       </c>
       <c r="B184" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>MATADOR</t>
         </is>
       </c>
       <c r="C184" s="4" t="inlineStr">
         <is>
-          <t>GD265/50R20</t>
+          <t>MT225/70R15C</t>
         </is>
       </c>
       <c r="D184" s="5">
@@ -6398,36 +6398,36 @@
         <v>0</v>
       </c>
       <c r="F184" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G184" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H184" s="6">
-        <v>1150</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="185">
       <c r="A185" s="4" t="inlineStr">
         <is>
-          <t>275/35R19RF</t>
+          <t>225/70R15C</t>
         </is>
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>SEMPERIT</t>
         </is>
       </c>
       <c r="C185" s="4" t="inlineStr">
         <is>
-          <t>GD275/35R19RF</t>
+          <t>SP225/70R15C</t>
         </is>
       </c>
       <c r="D185" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E185" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F185" s="5">
         <v>0</v>
@@ -6436,77 +6436,77 @@
         <v>0</v>
       </c>
       <c r="H185" s="6">
-        <v>1</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="186">
       <c r="A186" s="4" t="inlineStr">
         <is>
-          <t>275/35R20</t>
+          <t>225/75R15C</t>
         </is>
       </c>
       <c r="B186" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C186" s="4" t="inlineStr">
         <is>
-          <t>CT275/35R20</t>
+          <t>RD225/75R15C</t>
         </is>
       </c>
       <c r="D186" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E186" s="5">
         <v>0</v>
       </c>
       <c r="F186" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G186" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H186" s="6">
-        <v>980</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="187">
       <c r="A187" s="4" t="inlineStr">
         <is>
-          <t>275/40R20</t>
+          <t>235/35R19</t>
         </is>
       </c>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C187" s="4" t="inlineStr">
         <is>
-          <t>HK275/40R20</t>
+          <t>RD235/35R19</t>
         </is>
       </c>
       <c r="D187" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E187" s="5">
         <v>0</v>
       </c>
       <c r="F187" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G187" s="5">
         <v>0</v>
       </c>
       <c r="H187" s="6">
-        <v>770</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="188">
       <c r="A188" s="4" t="inlineStr">
         <is>
-          <t>275/50R21</t>
+          <t>235/40R19</t>
         </is>
       </c>
       <c r="B188" s="4" t="inlineStr">
@@ -6516,118 +6516,1750 @@
       </c>
       <c r="C188" s="4" t="inlineStr">
         <is>
-          <t>GD275/50R21</t>
+          <t>GD235/40R19</t>
         </is>
       </c>
       <c r="D188" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E188" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F188" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G188" s="5">
         <v>0</v>
       </c>
       <c r="H188" s="6">
-        <v>1</v>
+        <v>850</v>
       </c>
     </row>
     <row outlineLevel="0" r="189">
       <c r="A189" s="4" t="inlineStr">
         <is>
-          <t>295/35R21</t>
+          <t>235/45R18</t>
         </is>
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C189" s="4" t="inlineStr">
         <is>
-          <t>CT295/35R21</t>
+          <t>GD235/45R18</t>
         </is>
       </c>
       <c r="D189" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E189" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F189" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G189" s="5">
         <v>0</v>
       </c>
       <c r="H189" s="6">
-        <v>1150</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="190">
       <c r="A190" s="4" t="inlineStr">
         <is>
-          <t>295/35R21</t>
+          <t>235/50R18</t>
         </is>
       </c>
       <c r="B190" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C190" s="4" t="inlineStr">
         <is>
-          <t>GD295/35R21</t>
+          <t>HK235/50R18</t>
         </is>
       </c>
       <c r="D190" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E190" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F190" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G190" s="5">
         <v>0</v>
       </c>
       <c r="H190" s="6">
-        <v>980</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="191">
       <c r="A191" s="4" t="inlineStr">
         <is>
+          <t>235/50R19</t>
+        </is>
+      </c>
+      <c r="B191" s="4" t="inlineStr">
+        <is>
+          <t>GOODYEAR</t>
+        </is>
+      </c>
+      <c r="C191" s="4" t="inlineStr">
+        <is>
+          <t>GD235/50R19</t>
+        </is>
+      </c>
+      <c r="D191" s="5">
+        <v>4</v>
+      </c>
+      <c r="E191" s="5">
+        <v>4</v>
+      </c>
+      <c r="F191" s="5">
+        <v>0</v>
+      </c>
+      <c r="G191" s="5">
+        <v>0</v>
+      </c>
+      <c r="H191" s="6">
+        <v>800</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="192">
+      <c r="A192" s="4" t="inlineStr">
+        <is>
+          <t>235/50R20</t>
+        </is>
+      </c>
+      <c r="B192" s="4" t="inlineStr">
+        <is>
+          <t>GOODYEAR</t>
+        </is>
+      </c>
+      <c r="C192" s="4" t="inlineStr">
+        <is>
+          <t>GD235/50R20</t>
+        </is>
+      </c>
+      <c r="D192" s="5">
+        <v>7</v>
+      </c>
+      <c r="E192" s="5">
+        <v>0</v>
+      </c>
+      <c r="F192" s="5">
+        <v>7</v>
+      </c>
+      <c r="G192" s="5">
+        <v>0</v>
+      </c>
+      <c r="H192" s="6">
+        <v>1180</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="193">
+      <c r="A193" s="4" t="inlineStr">
+        <is>
+          <t>235/55R17</t>
+        </is>
+      </c>
+      <c r="B193" s="4" t="inlineStr">
+        <is>
+          <t>BRIDGESTONE</t>
+        </is>
+      </c>
+      <c r="C193" s="4" t="inlineStr">
+        <is>
+          <t>BR235/55R17</t>
+        </is>
+      </c>
+      <c r="D193" s="5">
+        <v>1</v>
+      </c>
+      <c r="E193" s="5">
+        <v>1</v>
+      </c>
+      <c r="F193" s="5">
+        <v>0</v>
+      </c>
+      <c r="G193" s="5">
+        <v>0</v>
+      </c>
+      <c r="H193" s="6">
+        <v>450</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="194">
+      <c r="A194" s="4" t="inlineStr">
+        <is>
+          <t>235/55R18</t>
+        </is>
+      </c>
+      <c r="B194" s="4" t="inlineStr">
+        <is>
+          <t>HANKOOK</t>
+        </is>
+      </c>
+      <c r="C194" s="4" t="inlineStr">
+        <is>
+          <t>HK235/55R18</t>
+        </is>
+      </c>
+      <c r="D194" s="5">
+        <v>7</v>
+      </c>
+      <c r="E194" s="5">
+        <v>7</v>
+      </c>
+      <c r="F194" s="5">
+        <v>0</v>
+      </c>
+      <c r="G194" s="5">
+        <v>0</v>
+      </c>
+      <c r="H194" s="6">
+        <v>480</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="195">
+      <c r="A195" s="4" t="inlineStr">
+        <is>
+          <t>235/55R19</t>
+        </is>
+      </c>
+      <c r="B195" s="4" t="inlineStr">
+        <is>
+          <t>GOODYEAR</t>
+        </is>
+      </c>
+      <c r="C195" s="4" t="inlineStr">
+        <is>
+          <t>GD235/55R19</t>
+        </is>
+      </c>
+      <c r="D195" s="5">
+        <v>2</v>
+      </c>
+      <c r="E195" s="5">
+        <v>2</v>
+      </c>
+      <c r="F195" s="5">
+        <v>0</v>
+      </c>
+      <c r="G195" s="5">
+        <v>0</v>
+      </c>
+      <c r="H195" s="6">
+        <v>750</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="196">
+      <c r="A196" s="4" t="inlineStr">
+        <is>
+          <t>235/55R19</t>
+        </is>
+      </c>
+      <c r="B196" s="4" t="inlineStr">
+        <is>
+          <t>HANKOOK</t>
+        </is>
+      </c>
+      <c r="C196" s="4" t="inlineStr">
+        <is>
+          <t>HK235/55R19</t>
+        </is>
+      </c>
+      <c r="D196" s="5">
+        <v>5</v>
+      </c>
+      <c r="E196" s="5">
+        <v>5</v>
+      </c>
+      <c r="F196" s="5">
+        <v>0</v>
+      </c>
+      <c r="G196" s="5">
+        <v>0</v>
+      </c>
+      <c r="H196" s="6">
+        <v>630</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="197">
+      <c r="A197" s="4" t="inlineStr">
+        <is>
+          <t>235/55R19</t>
+        </is>
+      </c>
+      <c r="B197" s="4" t="inlineStr">
+        <is>
+          <t>LUFEN</t>
+        </is>
+      </c>
+      <c r="C197" s="4" t="inlineStr">
+        <is>
+          <t>LF235/55R19</t>
+        </is>
+      </c>
+      <c r="D197" s="5">
+        <v>1</v>
+      </c>
+      <c r="E197" s="5">
+        <v>1</v>
+      </c>
+      <c r="F197" s="5">
+        <v>0</v>
+      </c>
+      <c r="G197" s="5">
+        <v>0</v>
+      </c>
+      <c r="H197" s="6">
+        <v>500</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="198">
+      <c r="A198" s="4" t="inlineStr">
+        <is>
+          <t>235/55R19</t>
+        </is>
+      </c>
+      <c r="B198" s="4" t="inlineStr">
+        <is>
+          <t>NEXEN</t>
+        </is>
+      </c>
+      <c r="C198" s="4" t="inlineStr">
+        <is>
+          <t>NX235/55R19</t>
+        </is>
+      </c>
+      <c r="D198" s="5">
+        <v>2</v>
+      </c>
+      <c r="E198" s="5">
+        <v>2</v>
+      </c>
+      <c r="F198" s="5">
+        <v>0</v>
+      </c>
+      <c r="G198" s="5">
+        <v>0</v>
+      </c>
+      <c r="H198" s="6">
+        <v>600</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="199">
+      <c r="A199" s="4" t="inlineStr">
+        <is>
+          <t>235/55R19</t>
+        </is>
+      </c>
+      <c r="B199" s="4" t="inlineStr">
+        <is>
+          <t>RADIAL</t>
+        </is>
+      </c>
+      <c r="C199" s="4" t="inlineStr">
+        <is>
+          <t>RD235/55R19</t>
+        </is>
+      </c>
+      <c r="D199" s="5">
+        <v>2</v>
+      </c>
+      <c r="E199" s="5">
+        <v>0</v>
+      </c>
+      <c r="F199" s="5">
+        <v>2</v>
+      </c>
+      <c r="G199" s="5">
+        <v>0</v>
+      </c>
+      <c r="H199" s="6">
+        <v>500</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="200">
+      <c r="A200" s="4" t="inlineStr">
+        <is>
+          <t>235/60R16</t>
+        </is>
+      </c>
+      <c r="B200" s="4" t="inlineStr">
+        <is>
+          <t>HANKOOK</t>
+        </is>
+      </c>
+      <c r="C200" s="4" t="inlineStr">
+        <is>
+          <t>HK235/60R16</t>
+        </is>
+      </c>
+      <c r="D200" s="5">
+        <v>4</v>
+      </c>
+      <c r="E200" s="5">
+        <v>4</v>
+      </c>
+      <c r="F200" s="5">
+        <v>0</v>
+      </c>
+      <c r="G200" s="5">
+        <v>0</v>
+      </c>
+      <c r="H200" s="6">
+        <v>430</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="201">
+      <c r="A201" s="4" t="inlineStr">
+        <is>
+          <t>235/60R17</t>
+        </is>
+      </c>
+      <c r="B201" s="4" t="inlineStr">
+        <is>
+          <t>HANKOOK</t>
+        </is>
+      </c>
+      <c r="C201" s="4" t="inlineStr">
+        <is>
+          <t>HK235/60R17</t>
+        </is>
+      </c>
+      <c r="D201" s="5">
+        <v>3</v>
+      </c>
+      <c r="E201" s="5">
+        <v>0</v>
+      </c>
+      <c r="F201" s="5">
+        <v>3</v>
+      </c>
+      <c r="G201" s="5">
+        <v>0</v>
+      </c>
+      <c r="H201" s="6">
+        <v>500</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="202">
+      <c r="A202" s="4" t="inlineStr">
+        <is>
+          <t>235/60R18</t>
+        </is>
+      </c>
+      <c r="B202" s="4" t="inlineStr">
+        <is>
+          <t>GOODYEAR</t>
+        </is>
+      </c>
+      <c r="C202" s="4" t="inlineStr">
+        <is>
+          <t>GD235/60R18</t>
+        </is>
+      </c>
+      <c r="D202" s="5">
+        <v>2</v>
+      </c>
+      <c r="E202" s="5">
+        <v>2</v>
+      </c>
+      <c r="F202" s="5">
+        <v>0</v>
+      </c>
+      <c r="G202" s="5">
+        <v>0</v>
+      </c>
+      <c r="H202" s="6">
+        <v>680</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="203">
+      <c r="A203" s="4" t="inlineStr">
+        <is>
+          <t>235/60R18</t>
+        </is>
+      </c>
+      <c r="B203" s="4" t="inlineStr">
+        <is>
+          <t>HANKOOK</t>
+        </is>
+      </c>
+      <c r="C203" s="4" t="inlineStr">
+        <is>
+          <t>HK235/60R18</t>
+        </is>
+      </c>
+      <c r="D203" s="5">
+        <v>2</v>
+      </c>
+      <c r="E203" s="5">
+        <v>2</v>
+      </c>
+      <c r="F203" s="5">
+        <v>0</v>
+      </c>
+      <c r="G203" s="5">
+        <v>0</v>
+      </c>
+      <c r="H203" s="6">
+        <v>550</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="204">
+      <c r="A204" s="4" t="inlineStr">
+        <is>
+          <t>245/40R17</t>
+        </is>
+      </c>
+      <c r="B204" s="4" t="inlineStr">
+        <is>
+          <t>GOODYEAR</t>
+        </is>
+      </c>
+      <c r="C204" s="4" t="inlineStr">
+        <is>
+          <t>GD245/40R17</t>
+        </is>
+      </c>
+      <c r="D204" s="5">
+        <v>1</v>
+      </c>
+      <c r="E204" s="5">
+        <v>1</v>
+      </c>
+      <c r="F204" s="5">
+        <v>0</v>
+      </c>
+      <c r="G204" s="5">
+        <v>0</v>
+      </c>
+      <c r="H204" s="6">
+        <v>400</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="205">
+      <c r="A205" s="4" t="inlineStr">
+        <is>
+          <t>245/40R18</t>
+        </is>
+      </c>
+      <c r="B205" s="4" t="inlineStr">
+        <is>
+          <t>GOODYEAR</t>
+        </is>
+      </c>
+      <c r="C205" s="4" t="inlineStr">
+        <is>
+          <t>GD245/40R18</t>
+        </is>
+      </c>
+      <c r="D205" s="5">
+        <v>3</v>
+      </c>
+      <c r="E205" s="5">
+        <v>2</v>
+      </c>
+      <c r="F205" s="5">
+        <v>0</v>
+      </c>
+      <c r="G205" s="5">
+        <v>1</v>
+      </c>
+      <c r="H205" s="6">
+        <v>620</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="206">
+      <c r="A206" s="4" t="inlineStr">
+        <is>
+          <t>245/40R19</t>
+        </is>
+      </c>
+      <c r="B206" s="4" t="inlineStr">
+        <is>
+          <t>HANKOOK</t>
+        </is>
+      </c>
+      <c r="C206" s="4" t="inlineStr">
+        <is>
+          <t>HK245/40R19</t>
+        </is>
+      </c>
+      <c r="D206" s="5">
+        <v>4</v>
+      </c>
+      <c r="E206" s="5">
+        <v>4</v>
+      </c>
+      <c r="F206" s="5">
+        <v>0</v>
+      </c>
+      <c r="G206" s="5">
+        <v>0</v>
+      </c>
+      <c r="H206" s="6">
+        <v>750</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="207">
+      <c r="A207" s="4" t="inlineStr">
+        <is>
+          <t>245/40R20</t>
+        </is>
+      </c>
+      <c r="B207" s="4" t="inlineStr">
+        <is>
+          <t>CONTINENTAL</t>
+        </is>
+      </c>
+      <c r="C207" s="4" t="inlineStr">
+        <is>
+          <t>CT245/40R20</t>
+        </is>
+      </c>
+      <c r="D207" s="5">
+        <v>2</v>
+      </c>
+      <c r="E207" s="5">
+        <v>0</v>
+      </c>
+      <c r="F207" s="5">
+        <v>2</v>
+      </c>
+      <c r="G207" s="5">
+        <v>0</v>
+      </c>
+      <c r="H207" s="6">
+        <v>1050</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="208">
+      <c r="A208" s="4" t="inlineStr">
+        <is>
+          <t>245/40R20</t>
+        </is>
+      </c>
+      <c r="B208" s="4" t="inlineStr">
+        <is>
+          <t>NEXEN</t>
+        </is>
+      </c>
+      <c r="C208" s="4" t="inlineStr">
+        <is>
+          <t>NX245/40R20</t>
+        </is>
+      </c>
+      <c r="D208" s="5">
+        <v>0</v>
+      </c>
+      <c r="E208" s="5">
+        <v>0</v>
+      </c>
+      <c r="F208" s="5">
+        <v>0</v>
+      </c>
+      <c r="G208" s="5">
+        <v>0</v>
+      </c>
+      <c r="H208" s="6">
+        <v>580</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="209">
+      <c r="A209" s="4" t="inlineStr">
+        <is>
+          <t>245/45R17</t>
+        </is>
+      </c>
+      <c r="B209" s="4" t="inlineStr">
+        <is>
+          <t>HANKOOK</t>
+        </is>
+      </c>
+      <c r="C209" s="4" t="inlineStr">
+        <is>
+          <t>HK245/45R17</t>
+        </is>
+      </c>
+      <c r="D209" s="5">
+        <v>4</v>
+      </c>
+      <c r="E209" s="5">
+        <v>4</v>
+      </c>
+      <c r="F209" s="5">
+        <v>0</v>
+      </c>
+      <c r="G209" s="5">
+        <v>0</v>
+      </c>
+      <c r="H209" s="6">
+        <v>430</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="210">
+      <c r="A210" s="4" t="inlineStr">
+        <is>
+          <t>245/45R18</t>
+        </is>
+      </c>
+      <c r="B210" s="4" t="inlineStr">
+        <is>
+          <t>CONTINENTAL</t>
+        </is>
+      </c>
+      <c r="C210" s="4" t="inlineStr">
+        <is>
+          <t>CT245/45R18</t>
+        </is>
+      </c>
+      <c r="D210" s="5">
+        <v>1</v>
+      </c>
+      <c r="E210" s="5">
+        <v>1</v>
+      </c>
+      <c r="F210" s="5">
+        <v>0</v>
+      </c>
+      <c r="G210" s="5">
+        <v>0</v>
+      </c>
+      <c r="H210" s="6">
+        <v>650</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="211">
+      <c r="A211" s="4" t="inlineStr">
+        <is>
+          <t>245/45R18</t>
+        </is>
+      </c>
+      <c r="B211" s="4" t="inlineStr">
+        <is>
+          <t>GOODYEAR</t>
+        </is>
+      </c>
+      <c r="C211" s="4" t="inlineStr">
+        <is>
+          <t>GD245/45R18</t>
+        </is>
+      </c>
+      <c r="D211" s="5">
+        <v>3</v>
+      </c>
+      <c r="E211" s="5">
+        <v>3</v>
+      </c>
+      <c r="F211" s="5">
+        <v>0</v>
+      </c>
+      <c r="G211" s="5">
+        <v>0</v>
+      </c>
+      <c r="H211" s="6">
+        <v>600</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="212">
+      <c r="A212" s="4" t="inlineStr">
+        <is>
+          <t>245/45R18</t>
+        </is>
+      </c>
+      <c r="B212" s="4" t="inlineStr">
+        <is>
+          <t>HANKOOK</t>
+        </is>
+      </c>
+      <c r="C212" s="4" t="inlineStr">
+        <is>
+          <t>HK245/45R18</t>
+        </is>
+      </c>
+      <c r="D212" s="5">
+        <v>1</v>
+      </c>
+      <c r="E212" s="5">
+        <v>1</v>
+      </c>
+      <c r="F212" s="5">
+        <v>0</v>
+      </c>
+      <c r="G212" s="5">
+        <v>0</v>
+      </c>
+      <c r="H212" s="6">
+        <v>500</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="213">
+      <c r="A213" s="4" t="inlineStr">
+        <is>
+          <t>245/45R18RF</t>
+        </is>
+      </c>
+      <c r="B213" s="4" t="inlineStr">
+        <is>
+          <t>GOODYEAR</t>
+        </is>
+      </c>
+      <c r="C213" s="4" t="inlineStr">
+        <is>
+          <t>GD245/45R18RF</t>
+        </is>
+      </c>
+      <c r="D213" s="5">
+        <v>4</v>
+      </c>
+      <c r="E213" s="5">
+        <v>4</v>
+      </c>
+      <c r="F213" s="5">
+        <v>0</v>
+      </c>
+      <c r="G213" s="5">
+        <v>0</v>
+      </c>
+      <c r="H213" s="6">
+        <v>720</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="214">
+      <c r="A214" s="4" t="inlineStr">
+        <is>
+          <t>245/45R19</t>
+        </is>
+      </c>
+      <c r="B214" s="4" t="inlineStr">
+        <is>
+          <t>BRIDGESTONE</t>
+        </is>
+      </c>
+      <c r="C214" s="4" t="inlineStr">
+        <is>
+          <t>BR245/45R19</t>
+        </is>
+      </c>
+      <c r="D214" s="5">
+        <v>4</v>
+      </c>
+      <c r="E214" s="5">
+        <v>4</v>
+      </c>
+      <c r="F214" s="5">
+        <v>0</v>
+      </c>
+      <c r="G214" s="5">
+        <v>0</v>
+      </c>
+      <c r="H214" s="6">
+        <v>790</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="215">
+      <c r="A215" s="4" t="inlineStr">
+        <is>
+          <t>245/45R19</t>
+        </is>
+      </c>
+      <c r="B215" s="4" t="inlineStr">
+        <is>
+          <t>RADIAL</t>
+        </is>
+      </c>
+      <c r="C215" s="4" t="inlineStr">
+        <is>
+          <t>RD245/45R19</t>
+        </is>
+      </c>
+      <c r="D215" s="5">
+        <v>2</v>
+      </c>
+      <c r="E215" s="5">
+        <v>0</v>
+      </c>
+      <c r="F215" s="5">
+        <v>2</v>
+      </c>
+      <c r="G215" s="5">
+        <v>0</v>
+      </c>
+      <c r="H215" s="6">
+        <v>450</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="216">
+      <c r="A216" s="4" t="inlineStr">
+        <is>
+          <t>245/45R20</t>
+        </is>
+      </c>
+      <c r="B216" s="4" t="inlineStr">
+        <is>
+          <t>HANKOOK</t>
+        </is>
+      </c>
+      <c r="C216" s="4" t="inlineStr">
+        <is>
+          <t>HK245/45R20</t>
+        </is>
+      </c>
+      <c r="D216" s="5">
+        <v>2</v>
+      </c>
+      <c r="E216" s="5">
+        <v>0</v>
+      </c>
+      <c r="F216" s="5">
+        <v>2</v>
+      </c>
+      <c r="G216" s="5">
+        <v>0</v>
+      </c>
+      <c r="H216" s="6">
+        <v>750</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="217">
+      <c r="A217" s="4" t="inlineStr">
+        <is>
+          <t>245/65R17</t>
+        </is>
+      </c>
+      <c r="B217" s="4" t="inlineStr">
+        <is>
+          <t>NEXEN</t>
+        </is>
+      </c>
+      <c r="C217" s="4" t="inlineStr">
+        <is>
+          <t>NX245/65R17</t>
+        </is>
+      </c>
+      <c r="D217" s="5">
+        <v>4</v>
+      </c>
+      <c r="E217" s="5">
+        <v>0</v>
+      </c>
+      <c r="F217" s="5">
+        <v>0</v>
+      </c>
+      <c r="G217" s="5">
+        <v>4</v>
+      </c>
+      <c r="H217" s="6">
+        <v>600</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="218">
+      <c r="A218" s="4" t="inlineStr">
+        <is>
+          <t>245/70R16</t>
+        </is>
+      </c>
+      <c r="B218" s="4" t="inlineStr">
+        <is>
+          <t>LASSA</t>
+        </is>
+      </c>
+      <c r="C218" s="4" t="inlineStr">
+        <is>
+          <t>LS245/70R16</t>
+        </is>
+      </c>
+      <c r="D218" s="5">
+        <v>0</v>
+      </c>
+      <c r="E218" s="5">
+        <v>0</v>
+      </c>
+      <c r="F218" s="5">
+        <v>0</v>
+      </c>
+      <c r="G218" s="5">
+        <v>0</v>
+      </c>
+      <c r="H218" s="6">
+        <v>500</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="219">
+      <c r="A219" s="4" t="inlineStr">
+        <is>
+          <t>255/35R19</t>
+        </is>
+      </c>
+      <c r="B219" s="4" t="inlineStr">
+        <is>
+          <t>DUNLOP</t>
+        </is>
+      </c>
+      <c r="C219" s="4" t="inlineStr">
+        <is>
+          <t>DL255/35R19</t>
+        </is>
+      </c>
+      <c r="D219" s="5">
+        <v>1</v>
+      </c>
+      <c r="E219" s="5">
+        <v>1</v>
+      </c>
+      <c r="F219" s="5">
+        <v>0</v>
+      </c>
+      <c r="G219" s="5">
+        <v>0</v>
+      </c>
+      <c r="H219" s="6">
+        <v>700</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="220">
+      <c r="A220" s="4" t="inlineStr">
+        <is>
+          <t>255/35R19RF</t>
+        </is>
+      </c>
+      <c r="B220" s="4" t="inlineStr">
+        <is>
+          <t>CONTINENTAL</t>
+        </is>
+      </c>
+      <c r="C220" s="4" t="inlineStr">
+        <is>
+          <t>CT255/35R19RF</t>
+        </is>
+      </c>
+      <c r="D220" s="5">
+        <v>2</v>
+      </c>
+      <c r="E220" s="5">
+        <v>2</v>
+      </c>
+      <c r="F220" s="5">
+        <v>0</v>
+      </c>
+      <c r="G220" s="5">
+        <v>0</v>
+      </c>
+      <c r="H220" s="6">
+        <v>950</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="221">
+      <c r="A221" s="4" t="inlineStr">
+        <is>
+          <t>255/35R19RF</t>
+        </is>
+      </c>
+      <c r="B221" s="4" t="inlineStr">
+        <is>
+          <t>GOODYEAR</t>
+        </is>
+      </c>
+      <c r="C221" s="4" t="inlineStr">
+        <is>
+          <t>GD255/35R19RF</t>
+        </is>
+      </c>
+      <c r="D221" s="5">
+        <v>1</v>
+      </c>
+      <c r="E221" s="5">
+        <v>1</v>
+      </c>
+      <c r="F221" s="5">
+        <v>0</v>
+      </c>
+      <c r="G221" s="5">
+        <v>0</v>
+      </c>
+      <c r="H221" s="6">
+        <v>950</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="222">
+      <c r="A222" s="4" t="inlineStr">
+        <is>
+          <t>255/45R18</t>
+        </is>
+      </c>
+      <c r="B222" s="4" t="inlineStr">
+        <is>
+          <t>HANKOOK</t>
+        </is>
+      </c>
+      <c r="C222" s="4" t="inlineStr">
+        <is>
+          <t>HK255/45R18</t>
+        </is>
+      </c>
+      <c r="D222" s="5">
+        <v>0</v>
+      </c>
+      <c r="E222" s="5">
+        <v>0</v>
+      </c>
+      <c r="F222" s="5">
+        <v>0</v>
+      </c>
+      <c r="G222" s="5">
+        <v>0</v>
+      </c>
+      <c r="H222" s="6">
+        <v>500</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="223">
+      <c r="A223" s="4" t="inlineStr">
+        <is>
+          <t>255/50R19</t>
+        </is>
+      </c>
+      <c r="B223" s="4" t="inlineStr">
+        <is>
+          <t>CONTINENTAL</t>
+        </is>
+      </c>
+      <c r="C223" s="4" t="inlineStr">
+        <is>
+          <t>CT255/50R19</t>
+        </is>
+      </c>
+      <c r="D223" s="5">
+        <v>6</v>
+      </c>
+      <c r="E223" s="5">
+        <v>0</v>
+      </c>
+      <c r="F223" s="5">
+        <v>6</v>
+      </c>
+      <c r="G223" s="5">
+        <v>0</v>
+      </c>
+      <c r="H223" s="6">
+        <v>750</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="224">
+      <c r="A224" s="4" t="inlineStr">
+        <is>
+          <t>255/50R20</t>
+        </is>
+      </c>
+      <c r="B224" s="4" t="inlineStr">
+        <is>
+          <t>CONTINENTAL</t>
+        </is>
+      </c>
+      <c r="C224" s="4" t="inlineStr">
+        <is>
+          <t>CT255/50R20</t>
+        </is>
+      </c>
+      <c r="D224" s="5">
+        <v>2</v>
+      </c>
+      <c r="E224" s="5">
+        <v>0</v>
+      </c>
+      <c r="F224" s="5">
+        <v>2</v>
+      </c>
+      <c r="G224" s="5">
+        <v>0</v>
+      </c>
+      <c r="H224" s="6">
+        <v>900</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="225">
+      <c r="A225" s="4" t="inlineStr">
+        <is>
+          <t>255/55R19</t>
+        </is>
+      </c>
+      <c r="B225" s="4" t="inlineStr">
+        <is>
+          <t>CONTINENTAL</t>
+        </is>
+      </c>
+      <c r="C225" s="4" t="inlineStr">
+        <is>
+          <t>CT255/55R19</t>
+        </is>
+      </c>
+      <c r="D225" s="5">
+        <v>1</v>
+      </c>
+      <c r="E225" s="5">
+        <v>0</v>
+      </c>
+      <c r="F225" s="5">
+        <v>1</v>
+      </c>
+      <c r="G225" s="5">
+        <v>0</v>
+      </c>
+      <c r="H225" s="6">
+        <v>750</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="226">
+      <c r="A226" s="4" t="inlineStr">
+        <is>
+          <t>255/55R19</t>
+        </is>
+      </c>
+      <c r="B226" s="4" t="inlineStr">
+        <is>
+          <t>DUNLOP</t>
+        </is>
+      </c>
+      <c r="C226" s="4" t="inlineStr">
+        <is>
+          <t>DL255/55R19</t>
+        </is>
+      </c>
+      <c r="D226" s="5">
+        <v>2</v>
+      </c>
+      <c r="E226" s="5">
+        <v>2</v>
+      </c>
+      <c r="F226" s="5">
+        <v>0</v>
+      </c>
+      <c r="G226" s="5">
+        <v>0</v>
+      </c>
+      <c r="H226" s="6">
+        <v>700</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="227">
+      <c r="A227" s="4" t="inlineStr">
+        <is>
+          <t>255/70R15</t>
+        </is>
+      </c>
+      <c r="B227" s="4" t="inlineStr">
+        <is>
+          <t>DUNLOP</t>
+        </is>
+      </c>
+      <c r="C227" s="4" t="inlineStr">
+        <is>
+          <t>DL255/70R15</t>
+        </is>
+      </c>
+      <c r="D227" s="5">
+        <v>0</v>
+      </c>
+      <c r="E227" s="5">
+        <v>0</v>
+      </c>
+      <c r="F227" s="5">
+        <v>0</v>
+      </c>
+      <c r="G227" s="5">
+        <v>0</v>
+      </c>
+      <c r="H227" s="6">
+        <v>550</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="228">
+      <c r="A228" s="4" t="inlineStr">
+        <is>
+          <t>255/70R16</t>
+        </is>
+      </c>
+      <c r="B228" s="4" t="inlineStr">
+        <is>
+          <t>RADIAL</t>
+        </is>
+      </c>
+      <c r="C228" s="4" t="inlineStr">
+        <is>
+          <t>RD255/70R16</t>
+        </is>
+      </c>
+      <c r="D228" s="5">
+        <v>1</v>
+      </c>
+      <c r="E228" s="5">
+        <v>0</v>
+      </c>
+      <c r="F228" s="5">
+        <v>0</v>
+      </c>
+      <c r="G228" s="5">
+        <v>1</v>
+      </c>
+      <c r="H228" s="6">
+        <v>500</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="229">
+      <c r="A229" s="4" t="inlineStr">
+        <is>
+          <t>265/35R18</t>
+        </is>
+      </c>
+      <c r="B229" s="4" t="inlineStr">
+        <is>
+          <t>GOODYEAR</t>
+        </is>
+      </c>
+      <c r="C229" s="4" t="inlineStr">
+        <is>
+          <t>GD265/35R18</t>
+        </is>
+      </c>
+      <c r="D229" s="5">
+        <v>1</v>
+      </c>
+      <c r="E229" s="5">
+        <v>1</v>
+      </c>
+      <c r="F229" s="5">
+        <v>0</v>
+      </c>
+      <c r="G229" s="5">
+        <v>0</v>
+      </c>
+      <c r="H229" s="6">
+        <v>700</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="230">
+      <c r="A230" s="4" t="inlineStr">
+        <is>
+          <t>265/50R20</t>
+        </is>
+      </c>
+      <c r="B230" s="4" t="inlineStr">
+        <is>
+          <t>GOODYEAR</t>
+        </is>
+      </c>
+      <c r="C230" s="4" t="inlineStr">
+        <is>
+          <t>GD265/50R20</t>
+        </is>
+      </c>
+      <c r="D230" s="5">
+        <v>4</v>
+      </c>
+      <c r="E230" s="5">
+        <v>0</v>
+      </c>
+      <c r="F230" s="5">
+        <v>4</v>
+      </c>
+      <c r="G230" s="5">
+        <v>0</v>
+      </c>
+      <c r="H230" s="6">
+        <v>1150</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="231">
+      <c r="A231" s="4" t="inlineStr">
+        <is>
+          <t>265/65R17</t>
+        </is>
+      </c>
+      <c r="B231" s="4" t="inlineStr">
+        <is>
+          <t>LASSA</t>
+        </is>
+      </c>
+      <c r="C231" s="4" t="inlineStr">
+        <is>
+          <t>LS265/65R17</t>
+        </is>
+      </c>
+      <c r="D231" s="5">
+        <v>0</v>
+      </c>
+      <c r="E231" s="5">
+        <v>0</v>
+      </c>
+      <c r="F231" s="5">
+        <v>0</v>
+      </c>
+      <c r="G231" s="5">
+        <v>0</v>
+      </c>
+      <c r="H231" s="6">
+        <v>650</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="232">
+      <c r="A232" s="4" t="inlineStr">
+        <is>
+          <t>275/35R19RF</t>
+        </is>
+      </c>
+      <c r="B232" s="4" t="inlineStr">
+        <is>
+          <t>GOODYEAR</t>
+        </is>
+      </c>
+      <c r="C232" s="4" t="inlineStr">
+        <is>
+          <t>GD275/35R19RF</t>
+        </is>
+      </c>
+      <c r="D232" s="5">
+        <v>2</v>
+      </c>
+      <c r="E232" s="5">
+        <v>2</v>
+      </c>
+      <c r="F232" s="5">
+        <v>0</v>
+      </c>
+      <c r="G232" s="5">
+        <v>0</v>
+      </c>
+      <c r="H232" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="233">
+      <c r="A233" s="4" t="inlineStr">
+        <is>
+          <t>275/35R20</t>
+        </is>
+      </c>
+      <c r="B233" s="4" t="inlineStr">
+        <is>
+          <t>CONTINENTAL</t>
+        </is>
+      </c>
+      <c r="C233" s="4" t="inlineStr">
+        <is>
+          <t>CT275/35R20</t>
+        </is>
+      </c>
+      <c r="D233" s="5">
+        <v>2</v>
+      </c>
+      <c r="E233" s="5">
+        <v>0</v>
+      </c>
+      <c r="F233" s="5">
+        <v>2</v>
+      </c>
+      <c r="G233" s="5">
+        <v>0</v>
+      </c>
+      <c r="H233" s="6">
+        <v>980</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="234">
+      <c r="A234" s="4" t="inlineStr">
+        <is>
+          <t>275/40R20</t>
+        </is>
+      </c>
+      <c r="B234" s="4" t="inlineStr">
+        <is>
+          <t>HANKOOK</t>
+        </is>
+      </c>
+      <c r="C234" s="4" t="inlineStr">
+        <is>
+          <t>HK275/40R20</t>
+        </is>
+      </c>
+      <c r="D234" s="5">
+        <v>2</v>
+      </c>
+      <c r="E234" s="5">
+        <v>0</v>
+      </c>
+      <c r="F234" s="5">
+        <v>2</v>
+      </c>
+      <c r="G234" s="5">
+        <v>0</v>
+      </c>
+      <c r="H234" s="6">
+        <v>770</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="235">
+      <c r="A235" s="4" t="inlineStr">
+        <is>
+          <t>275/40R22</t>
+        </is>
+      </c>
+      <c r="B235" s="4" t="inlineStr">
+        <is>
+          <t>GOODYEAR</t>
+        </is>
+      </c>
+      <c r="C235" s="4" t="inlineStr">
+        <is>
+          <t>GD275/40R22</t>
+        </is>
+      </c>
+      <c r="D235" s="5">
+        <v>0</v>
+      </c>
+      <c r="E235" s="5">
+        <v>0</v>
+      </c>
+      <c r="F235" s="5">
+        <v>0</v>
+      </c>
+      <c r="G235" s="5">
+        <v>0</v>
+      </c>
+      <c r="H235" s="6">
+        <v>1200</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="236">
+      <c r="A236" s="4" t="inlineStr">
+        <is>
+          <t>275/45R20</t>
+        </is>
+      </c>
+      <c r="B236" s="4" t="inlineStr">
+        <is>
+          <t>CONTINENTAL</t>
+        </is>
+      </c>
+      <c r="C236" s="4" t="inlineStr">
+        <is>
+          <t>CT275/45R20</t>
+        </is>
+      </c>
+      <c r="D236" s="5">
+        <v>0</v>
+      </c>
+      <c r="E236" s="5">
+        <v>0</v>
+      </c>
+      <c r="F236" s="5">
+        <v>0</v>
+      </c>
+      <c r="G236" s="5">
+        <v>0</v>
+      </c>
+      <c r="H236" s="6">
+        <v>900</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="237">
+      <c r="A237" s="4" t="inlineStr">
+        <is>
+          <t>275/50R21</t>
+        </is>
+      </c>
+      <c r="B237" s="4" t="inlineStr">
+        <is>
+          <t>GOODYEAR</t>
+        </is>
+      </c>
+      <c r="C237" s="4" t="inlineStr">
+        <is>
+          <t>GD275/50R21</t>
+        </is>
+      </c>
+      <c r="D237" s="5">
+        <v>2</v>
+      </c>
+      <c r="E237" s="5">
+        <v>0</v>
+      </c>
+      <c r="F237" s="5">
+        <v>2</v>
+      </c>
+      <c r="G237" s="5">
+        <v>0</v>
+      </c>
+      <c r="H237" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="238">
+      <c r="A238" s="4" t="inlineStr">
+        <is>
+          <t>285/35R22</t>
+        </is>
+      </c>
+      <c r="B238" s="4" t="inlineStr">
+        <is>
+          <t>CONTINENTAL</t>
+        </is>
+      </c>
+      <c r="C238" s="4" t="inlineStr">
+        <is>
+          <t>CT285/35R22</t>
+        </is>
+      </c>
+      <c r="D238" s="5">
+        <v>0</v>
+      </c>
+      <c r="E238" s="5">
+        <v>0</v>
+      </c>
+      <c r="F238" s="5">
+        <v>0</v>
+      </c>
+      <c r="G238" s="5">
+        <v>0</v>
+      </c>
+      <c r="H238" s="6">
+        <v>1600</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="239">
+      <c r="A239" s="4" t="inlineStr">
+        <is>
+          <t>295/35R21</t>
+        </is>
+      </c>
+      <c r="B239" s="4" t="inlineStr">
+        <is>
+          <t>CONTINENTAL</t>
+        </is>
+      </c>
+      <c r="C239" s="4" t="inlineStr">
+        <is>
+          <t>CT295/35R21</t>
+        </is>
+      </c>
+      <c r="D239" s="5">
+        <v>2</v>
+      </c>
+      <c r="E239" s="5">
+        <v>0</v>
+      </c>
+      <c r="F239" s="5">
+        <v>2</v>
+      </c>
+      <c r="G239" s="5">
+        <v>0</v>
+      </c>
+      <c r="H239" s="6">
+        <v>1150</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="240">
+      <c r="A240" s="4" t="inlineStr">
+        <is>
+          <t>295/35R21</t>
+        </is>
+      </c>
+      <c r="B240" s="4" t="inlineStr">
+        <is>
+          <t>GOODYEAR</t>
+        </is>
+      </c>
+      <c r="C240" s="4" t="inlineStr">
+        <is>
+          <t>GD295/35R21</t>
+        </is>
+      </c>
+      <c r="D240" s="5">
+        <v>3</v>
+      </c>
+      <c r="E240" s="5">
+        <v>0</v>
+      </c>
+      <c r="F240" s="5">
+        <v>3</v>
+      </c>
+      <c r="G240" s="5">
+        <v>0</v>
+      </c>
+      <c r="H240" s="6">
+        <v>980</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="241">
+      <c r="A241" s="4" t="inlineStr">
+        <is>
+          <t>315/30R22</t>
+        </is>
+      </c>
+      <c r="B241" s="4" t="inlineStr">
+        <is>
+          <t>CONTINENTAL</t>
+        </is>
+      </c>
+      <c r="C241" s="4" t="inlineStr">
+        <is>
+          <t>CT315/30R22</t>
+        </is>
+      </c>
+      <c r="D241" s="5">
+        <v>0</v>
+      </c>
+      <c r="E241" s="5">
+        <v>0</v>
+      </c>
+      <c r="F241" s="5">
+        <v>0</v>
+      </c>
+      <c r="G241" s="5">
+        <v>0</v>
+      </c>
+      <c r="H241" s="6">
+        <v>1700</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="242">
+      <c r="A242" s="4" t="inlineStr">
+        <is>
           <t>500R12</t>
         </is>
       </c>
-      <c r="B191" s="4" t="inlineStr">
+      <c r="B242" s="4" t="inlineStr">
         <is>
           <t>RADIAL</t>
         </is>
       </c>
-      <c r="C191" s="4" t="inlineStr">
+      <c r="C242" s="4" t="inlineStr">
         <is>
           <t>RD500R12</t>
         </is>
       </c>
-      <c r="D191" s="5">
+      <c r="D242" s="5">
         <v>3</v>
       </c>
-      <c r="E191" s="5">
+      <c r="E242" s="5">
         <v>3</v>
       </c>
-      <c r="F191" s="5">
-        <v>0</v>
-      </c>
-      <c r="G191" s="5">
-        <v>0</v>
-      </c>
-      <c r="H191" s="6">
+      <c r="F242" s="5">
+        <v>0</v>
+      </c>
+      <c r="G242" s="5">
+        <v>0</v>
+      </c>
+      <c r="H242" s="6">
         <v>300</v>
       </c>
     </row>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -568,10 +568,10 @@
         </is>
       </c>
       <c r="D2" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E2" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F2" s="5">
         <v>0</v>
@@ -1275,10 +1275,10 @@
         <v>48</v>
       </c>
       <c r="E24" s="5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F24" s="5">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="G24" s="5">
         <v>11</v>
@@ -1508,7 +1508,7 @@
         <v>0</v>
       </c>
       <c r="H31" s="6">
-        <v>230</v>
+        <v>240</v>
       </c>
     </row>
     <row outlineLevel="0" r="32">
@@ -1540,7 +1540,7 @@
         <v>0</v>
       </c>
       <c r="H32" s="6">
-        <v>220</v>
+        <v>200</v>
       </c>
     </row>
     <row outlineLevel="0" r="33">
@@ -1636,7 +1636,7 @@
         <v>0</v>
       </c>
       <c r="H35" s="6">
-        <v>370</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="36">
@@ -1668,7 +1668,7 @@
         <v>0</v>
       </c>
       <c r="H36" s="6">
-        <v>240</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="37">
@@ -2116,7 +2116,7 @@
         <v>0</v>
       </c>
       <c r="H50" s="6">
-        <v>210</v>
+        <v>230</v>
       </c>
     </row>
     <row outlineLevel="0" r="51">
@@ -2212,7 +2212,7 @@
         <v>4</v>
       </c>
       <c r="H53" s="6">
-        <v>260</v>
+        <v>270</v>
       </c>
     </row>
     <row outlineLevel="0" r="54">
@@ -2372,7 +2372,7 @@
         <v>2</v>
       </c>
       <c r="H58" s="6">
-        <v>220</v>
+        <v>225</v>
       </c>
     </row>
     <row outlineLevel="0" r="59">
@@ -2468,7 +2468,7 @@
         <v>2</v>
       </c>
       <c r="H61" s="6">
-        <v>220</v>
+        <v>240</v>
       </c>
     </row>
     <row outlineLevel="0" r="62">
@@ -2596,7 +2596,7 @@
         <v>2</v>
       </c>
       <c r="H65" s="6">
-        <v>225</v>
+        <v>240</v>
       </c>
     </row>
     <row outlineLevel="0" r="66">
@@ -2628,7 +2628,7 @@
         <v>0</v>
       </c>
       <c r="H66" s="6">
-        <v>330</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="67">
@@ -2712,10 +2712,10 @@
         </is>
       </c>
       <c r="D69" s="5">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E69" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F69" s="5">
         <v>5</v>
@@ -2724,7 +2724,7 @@
         <v>4</v>
       </c>
       <c r="H69" s="6">
-        <v>290</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="70">
@@ -2852,7 +2852,7 @@
         <v>4</v>
       </c>
       <c r="H73" s="6">
-        <v>355</v>
+        <v>360</v>
       </c>
     </row>
     <row outlineLevel="0" r="74">
@@ -3608,13 +3608,13 @@
         </is>
       </c>
       <c r="D97" s="5">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E97" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F97" s="5">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G97" s="5">
         <v>5</v>
@@ -3716,7 +3716,7 @@
         <v>3</v>
       </c>
       <c r="H100" s="6">
-        <v>260</v>
+        <v>270</v>
       </c>
     </row>
     <row outlineLevel="0" r="101">
@@ -4004,7 +4004,7 @@
         <v>4</v>
       </c>
       <c r="H109" s="6">
-        <v>300</v>
+        <v>320</v>
       </c>
     </row>
     <row outlineLevel="0" r="110">
@@ -4868,7 +4868,7 @@
         <v>0</v>
       </c>
       <c r="H136" s="6">
-        <v>350</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="137">
@@ -4920,10 +4920,10 @@
         </is>
       </c>
       <c r="D138" s="5">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E138" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F138" s="5">
         <v>0</v>
@@ -5092,7 +5092,7 @@
         <v>0</v>
       </c>
       <c r="H143" s="6">
-        <v>330</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="144">
@@ -5124,7 +5124,7 @@
         <v>0</v>
       </c>
       <c r="H144" s="6">
-        <v>600</v>
+        <v>680</v>
       </c>
     </row>
     <row outlineLevel="0" r="145">
@@ -5188,7 +5188,7 @@
         <v>0</v>
       </c>
       <c r="H146" s="6">
-        <v>330</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="147">
@@ -5627,10 +5627,10 @@
         <v>20</v>
       </c>
       <c r="E160" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F160" s="5">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G160" s="5">
         <v>4</v>
@@ -5668,7 +5668,7 @@
         <v>0</v>
       </c>
       <c r="H161" s="6">
-        <v>350</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="162">
@@ -6308,7 +6308,7 @@
         <v>2</v>
       </c>
       <c r="H181" s="6">
-        <v>400</v>
+        <v>425</v>
       </c>
     </row>
     <row outlineLevel="0" r="182">
@@ -6616,10 +6616,10 @@
         </is>
       </c>
       <c r="D191" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E191" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F191" s="5">
         <v>0</v>
@@ -7556,7 +7556,7 @@
         <v>0</v>
       </c>
       <c r="H220" s="6">
-        <v>950</v>
+        <v>1150</v>
       </c>
     </row>
     <row outlineLevel="0" r="221">
@@ -7588,7 +7588,7 @@
         <v>0</v>
       </c>
       <c r="H221" s="6">
-        <v>950</v>
+        <v>1150</v>
       </c>
     </row>
     <row outlineLevel="0" r="222">
@@ -7940,7 +7940,7 @@
         <v>0</v>
       </c>
       <c r="H232" s="6">
-        <v>1</v>
+        <v>1300</v>
       </c>
     </row>
     <row outlineLevel="0" r="233">
@@ -8100,7 +8100,7 @@
         <v>0</v>
       </c>
       <c r="H237" s="6">
-        <v>1</v>
+        <v>1300</v>
       </c>
     </row>
     <row outlineLevel="0" r="238">

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -496,7 +496,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H242"/>
+  <dimension ref="A1:H249"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col customWidth="true" min="1" max="1" width="13.8359375"/>
@@ -600,10 +600,10 @@
         </is>
       </c>
       <c r="D3" s="5">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E3" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F3" s="5">
         <v>0</v>
@@ -719,28 +719,28 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>FULDA</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>RD165/65R14</t>
+          <t>FL165/65R14</t>
         </is>
       </c>
       <c r="D7" s="5">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="E7" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F7" s="5">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="G7" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H7" s="6">
-        <v>180</v>
+        <v>190</v>
       </c>
     </row>
     <row outlineLevel="0" r="8">
@@ -751,19 +751,19 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>SEMPERIT</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>SP165/65R14</t>
+          <t>RD165/65R14</t>
         </is>
       </c>
       <c r="D8" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E8" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F8" s="5">
         <v>0</v>
@@ -772,7 +772,7 @@
         <v>0</v>
       </c>
       <c r="H8" s="6">
-        <v>200</v>
+        <v>180</v>
       </c>
     </row>
     <row outlineLevel="0" r="9">
@@ -783,51 +783,51 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>WESTLAKE</t>
+          <t>SEMPERIT</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>WL165/65R14</t>
+          <t>SP165/65R14</t>
         </is>
       </c>
       <c r="D9" s="5">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="E9" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F9" s="5">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G9" s="5">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H9" s="6">
-        <v>180</v>
+        <v>190</v>
       </c>
     </row>
     <row outlineLevel="0" r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>165/70R13</t>
+          <t>165/65R14</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>AMINE</t>
+          <t>WESTLAKE</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>AM165/70R13</t>
+          <t>WL165/65R14</t>
         </is>
       </c>
       <c r="D10" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E10" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F10" s="5">
         <v>0</v>
@@ -836,7 +836,7 @@
         <v>0</v>
       </c>
       <c r="H10" s="6">
-        <v>190</v>
+        <v>180</v>
       </c>
     </row>
     <row outlineLevel="0" r="11">
@@ -847,12 +847,12 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>DOUBLESTAR</t>
+          <t>AMINE</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>DS165/70R13</t>
+          <t>AM165/70R13</t>
         </is>
       </c>
       <c r="D11" s="5">
@@ -868,7 +868,7 @@
         <v>0</v>
       </c>
       <c r="H11" s="6">
-        <v>180</v>
+        <v>190</v>
       </c>
     </row>
     <row outlineLevel="0" r="12">
@@ -879,19 +879,19 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>DOUBLESTAR</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>RD165/70R13</t>
+          <t>DS165/70R13</t>
         </is>
       </c>
       <c r="D12" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12" s="5">
         <v>0</v>
@@ -906,129 +906,129 @@
     <row outlineLevel="0" r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>165/70R14</t>
+          <t>165/70R13</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>SEMPERIT</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>SP165/70R14</t>
+          <t>RD165/70R13</t>
         </is>
       </c>
       <c r="D13" s="5">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E13" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F13" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G13" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H13" s="6">
-        <v>240</v>
+        <v>180</v>
       </c>
     </row>
     <row outlineLevel="0" r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>175/50R15</t>
+          <t>165/70R14</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>SEMPERIT</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>HK175/50R15</t>
+          <t>SP165/70R14</t>
         </is>
       </c>
       <c r="D14" s="5">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E14" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F14" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G14" s="5">
         <v>4</v>
       </c>
       <c r="H14" s="6">
-        <v>270</v>
+        <v>240</v>
       </c>
     </row>
     <row outlineLevel="0" r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>175/55R15</t>
+          <t>175/50R15</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>RD175/55R15</t>
+          <t>HK175/50R15</t>
         </is>
       </c>
       <c r="D15" s="5">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E15" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F15" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G15" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H15" s="6">
-        <v>250</v>
+        <v>270</v>
       </c>
     </row>
     <row outlineLevel="0" r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>175/60R15</t>
+          <t>175/55R15</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>GD175/60R15</t>
+          <t>RD175/55R15</t>
         </is>
       </c>
       <c r="D16" s="5">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="E16" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F16" s="5">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G16" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H16" s="6">
-        <v>350</v>
+        <v>250</v>
       </c>
     </row>
     <row outlineLevel="0" r="17">
@@ -1039,60 +1039,60 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>RD175/60R15</t>
+          <t>GD175/60R15</t>
         </is>
       </c>
       <c r="D17" s="5">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="E17" s="5">
         <v>4</v>
       </c>
       <c r="F17" s="5">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="G17" s="5">
         <v>4</v>
       </c>
       <c r="H17" s="6">
-        <v>230</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>175/65R14</t>
+          <t>175/60R15</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>AMINE</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>AM175/65R14</t>
+          <t>RD175/60R15</t>
         </is>
       </c>
       <c r="D18" s="5">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E18" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F18" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G18" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H18" s="6">
-        <v>170</v>
+        <v>230</v>
       </c>
     </row>
     <row outlineLevel="0" r="19">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>DOUBLESTAR</t>
+          <t>AMINE</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>DS175/65R14</t>
+          <t>AM175/65R14</t>
         </is>
       </c>
       <c r="D19" s="5">
@@ -1124,7 +1124,7 @@
         <v>0</v>
       </c>
       <c r="H19" s="6">
-        <v>180</v>
+        <v>170</v>
       </c>
     </row>
     <row outlineLevel="0" r="20">
@@ -1135,12 +1135,12 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>GOODRIDE</t>
+          <t>DOUBLESTAR</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>GR175/65R14</t>
+          <t>DS175/65R14</t>
         </is>
       </c>
       <c r="D20" s="5">
@@ -1167,28 +1167,28 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>GOODRIDE</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>GD175/65R14</t>
+          <t>GR175/65R14</t>
         </is>
       </c>
       <c r="D21" s="5">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="E21" s="5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F21" s="5">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="G21" s="5">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H21" s="6">
-        <v>220</v>
+        <v>180</v>
       </c>
     </row>
     <row outlineLevel="0" r="22">
@@ -1199,28 +1199,28 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>NX175/65R14</t>
+          <t>GD175/65R14</t>
         </is>
       </c>
       <c r="D22" s="5">
-        <v>1</v>
+        <v>89</v>
       </c>
       <c r="E22" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F22" s="5">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="G22" s="5">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H22" s="6">
-        <v>200</v>
+        <v>220</v>
       </c>
     </row>
     <row outlineLevel="0" r="23">
@@ -1231,28 +1231,28 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>RD175/65R14</t>
+          <t>NX175/65R14</t>
         </is>
       </c>
       <c r="D23" s="5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E23" s="5">
         <v>1</v>
       </c>
       <c r="F23" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23" s="5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H23" s="6">
-        <v>180</v>
+        <v>200</v>
       </c>
     </row>
     <row outlineLevel="0" r="24">
@@ -1263,28 +1263,28 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>SEMPERIT</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>SP175/65R14</t>
+          <t>RD175/65R14</t>
         </is>
       </c>
       <c r="D24" s="5">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="E24" s="5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F24" s="5">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="G24" s="5">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="H24" s="6">
-        <v>190</v>
+        <v>180</v>
       </c>
     </row>
     <row outlineLevel="0" r="25">
@@ -1295,66 +1295,66 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>WESTLAKE</t>
+          <t>SEMPERIT</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>WL175/65R14</t>
+          <t>SP175/65R14</t>
         </is>
       </c>
       <c r="D25" s="5">
-        <v>84</v>
+        <v>47</v>
       </c>
       <c r="E25" s="5">
-        <v>74</v>
+        <v>6</v>
       </c>
       <c r="F25" s="5">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G25" s="5">
         <v>10</v>
       </c>
       <c r="H25" s="6">
-        <v>180</v>
+        <v>190</v>
       </c>
     </row>
     <row outlineLevel="0" r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>175/65R15</t>
+          <t>175/65R14</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>DOUBLESTAR</t>
+          <t>WESTLAKE</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>DS175/65R15</t>
+          <t>WL175/65R14</t>
         </is>
       </c>
       <c r="D26" s="5">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="E26" s="5">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="F26" s="5">
         <v>0</v>
       </c>
       <c r="G26" s="5">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="H26" s="6">
-        <v>200</v>
+        <v>180</v>
       </c>
     </row>
     <row outlineLevel="0" r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>175/70R13</t>
+          <t>175/65R15</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>DS175/70R13</t>
+          <t>DS175/65R15</t>
         </is>
       </c>
       <c r="D27" s="5">
@@ -1391,12 +1391,12 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>WESTLAKE</t>
+          <t>DOUBLESTAR</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>WL175/70R13</t>
+          <t>DS175/70R13</t>
         </is>
       </c>
       <c r="D28" s="5">
@@ -1418,17 +1418,17 @@
     <row outlineLevel="0" r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>175/70R14</t>
+          <t>175/70R13</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>WESTLAKE</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>BR175/70R14</t>
+          <t>WL175/70R13</t>
         </is>
       </c>
       <c r="D29" s="5">
@@ -1444,7 +1444,7 @@
         <v>0</v>
       </c>
       <c r="H29" s="6">
-        <v>295</v>
+        <v>200</v>
       </c>
     </row>
     <row outlineLevel="0" r="30">
@@ -1455,12 +1455,12 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>DOUBLESTAR</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>DS175/70R14</t>
+          <t>BR175/70R14</t>
         </is>
       </c>
       <c r="D30" s="5">
@@ -1476,7 +1476,7 @@
         <v>0</v>
       </c>
       <c r="H30" s="6">
-        <v>200</v>
+        <v>295</v>
       </c>
     </row>
     <row outlineLevel="0" r="31">
@@ -1487,19 +1487,19 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>MATADOR</t>
+          <t>DOUBLESTAR</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>MT175/70R14</t>
+          <t>DS175/70R14</t>
         </is>
       </c>
       <c r="D31" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E31" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F31" s="5">
         <v>0</v>
@@ -1508,7 +1508,7 @@
         <v>0</v>
       </c>
       <c r="H31" s="6">
-        <v>240</v>
+        <v>200</v>
       </c>
     </row>
     <row outlineLevel="0" r="32">
@@ -1519,19 +1519,19 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>MATADOR</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>RD175/70R14</t>
+          <t>MT175/70R14</t>
         </is>
       </c>
       <c r="D32" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E32" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F32" s="5">
         <v>0</v>
@@ -1540,7 +1540,7 @@
         <v>0</v>
       </c>
       <c r="H32" s="6">
-        <v>200</v>
+        <v>240</v>
       </c>
     </row>
     <row outlineLevel="0" r="33">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>SEMPERIT</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>SP175/70R14</t>
+          <t>RD175/70R14</t>
         </is>
       </c>
       <c r="D33" s="5">
@@ -1572,7 +1572,7 @@
         <v>0</v>
       </c>
       <c r="H33" s="6">
-        <v>250</v>
+        <v>200</v>
       </c>
     </row>
     <row outlineLevel="0" r="34">
@@ -1583,60 +1583,60 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>WESTLAKE</t>
+          <t>SEMPERIT</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>WL175/70R14</t>
+          <t>SP175/70R14</t>
         </is>
       </c>
       <c r="D34" s="5">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="E34" s="5">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="F34" s="5">
         <v>0</v>
       </c>
       <c r="G34" s="5">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H34" s="6">
-        <v>200</v>
+        <v>250</v>
       </c>
     </row>
     <row outlineLevel="0" r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>185/55R15</t>
+          <t>175/70R14</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>WESTLAKE</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>BR185/55R15</t>
+          <t>WL175/70R14</t>
         </is>
       </c>
       <c r="D35" s="5">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="E35" s="5">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="F35" s="5">
         <v>0</v>
       </c>
       <c r="G35" s="5">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H35" s="6">
-        <v>380</v>
+        <v>200</v>
       </c>
     </row>
     <row outlineLevel="0" r="36">
@@ -1647,19 +1647,19 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>CT185/55R15</t>
+          <t>BR185/55R15</t>
         </is>
       </c>
       <c r="D36" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E36" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F36" s="5">
         <v>0</v>
@@ -1668,7 +1668,7 @@
         <v>0</v>
       </c>
       <c r="H36" s="6">
-        <v>400</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="37">
@@ -1679,28 +1679,28 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>GD185/55R15</t>
+          <t>CT185/55R15</t>
         </is>
       </c>
       <c r="D37" s="5">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="E37" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F37" s="5">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G37" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H37" s="6">
-        <v>340</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="38">
@@ -1711,66 +1711,66 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>RD185/55R15</t>
+          <t>GD185/55R15</t>
         </is>
       </c>
       <c r="D38" s="5">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="E38" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F38" s="5">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G38" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H38" s="6">
-        <v>270</v>
+        <v>340</v>
       </c>
     </row>
     <row outlineLevel="0" r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>185/55R16</t>
+          <t>185/55R15</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>GD185/55R16</t>
+          <t>RD185/55R15</t>
         </is>
       </c>
       <c r="D39" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E39" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F39" s="5">
         <v>0</v>
       </c>
       <c r="G39" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H39" s="6">
-        <v>420</v>
+        <v>270</v>
       </c>
     </row>
     <row outlineLevel="0" r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>185/60R14</t>
+          <t>185/55R16</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
@@ -1780,23 +1780,23 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>GD185/60R14</t>
+          <t>GD185/55R16</t>
         </is>
       </c>
       <c r="D40" s="5">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="E40" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F40" s="5">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G40" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H40" s="6">
-        <v>230</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="41">
@@ -1807,25 +1807,25 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>NX185/60R14</t>
+          <t>GD185/60R14</t>
         </is>
       </c>
       <c r="D41" s="5">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="E41" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F41" s="5">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G41" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H41" s="6">
         <v>230</v>
@@ -1834,24 +1834,24 @@
     <row outlineLevel="0" r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>185/60R15</t>
+          <t>185/60R14</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>LF185/60R15</t>
+          <t>NX185/60R14</t>
         </is>
       </c>
       <c r="D42" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E42" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F42" s="5">
         <v>0</v>
@@ -1860,7 +1860,7 @@
         <v>0</v>
       </c>
       <c r="H42" s="6">
-        <v>270</v>
+        <v>230</v>
       </c>
     </row>
     <row outlineLevel="0" r="43">
@@ -1871,19 +1871,19 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>MATADOR</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>MT185/60R15</t>
+          <t>LF185/60R15</t>
         </is>
       </c>
       <c r="D43" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E43" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F43" s="5">
         <v>0</v>
@@ -1892,7 +1892,7 @@
         <v>0</v>
       </c>
       <c r="H43" s="6">
-        <v>280</v>
+        <v>270</v>
       </c>
     </row>
     <row outlineLevel="0" r="44">
@@ -1903,28 +1903,28 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>MATADOR</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>RD185/60R15</t>
+          <t>MT185/60R15</t>
         </is>
       </c>
       <c r="D44" s="5">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="E44" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F44" s="5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G44" s="5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H44" s="6">
-        <v>230</v>
+        <v>280</v>
       </c>
     </row>
     <row outlineLevel="0" r="45">
@@ -1935,25 +1935,25 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>WESTLAKE</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>WL185/60R15</t>
+          <t>RD185/60R15</t>
         </is>
       </c>
       <c r="D45" s="5">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E45" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F45" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G45" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H45" s="6">
         <v>230</v>
@@ -1962,85 +1962,85 @@
     <row outlineLevel="0" r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>185/60R16</t>
+          <t>185/60R15</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>WESTLAKE</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>GD185/60R16</t>
+          <t>WL185/60R15</t>
         </is>
       </c>
       <c r="D46" s="5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E46" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F46" s="5">
         <v>0</v>
       </c>
       <c r="G46" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H46" s="6">
-        <v>420</v>
+        <v>230</v>
       </c>
     </row>
     <row outlineLevel="0" r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>185/65R14</t>
+          <t>185/60R16</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>RD185/65R14</t>
+          <t>GD185/60R16</t>
         </is>
       </c>
       <c r="D47" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E47" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F47" s="5">
         <v>0</v>
       </c>
       <c r="G47" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H47" s="6">
-        <v>200</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>185/65R15</t>
+          <t>185/65R14</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>AMINE</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>AM185/65R15</t>
+          <t>RD185/65R14</t>
         </is>
       </c>
       <c r="D48" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E48" s="5">
         <v>0</v>
@@ -2049,7 +2049,7 @@
         <v>0</v>
       </c>
       <c r="G48" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H48" s="6">
         <v>200</v>
@@ -2063,19 +2063,19 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>AMINE</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>CT185/65R15</t>
+          <t>AM185/65R15</t>
         </is>
       </c>
       <c r="D49" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E49" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F49" s="5">
         <v>0</v>
@@ -2084,7 +2084,7 @@
         <v>0</v>
       </c>
       <c r="H49" s="6">
-        <v>400</v>
+        <v>200</v>
       </c>
     </row>
     <row outlineLevel="0" r="50">
@@ -2095,28 +2095,28 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>DOUBLESTAR</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>DS185/65R15</t>
+          <t>CT185/65R15</t>
         </is>
       </c>
       <c r="D50" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E50" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F50" s="5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G50" s="5">
         <v>0</v>
       </c>
       <c r="H50" s="6">
-        <v>230</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="51">
@@ -2127,28 +2127,28 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>FULDA</t>
+          <t>DOUBLESTAR</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>FL185/65R15</t>
+          <t>DS185/65R15</t>
         </is>
       </c>
       <c r="D51" s="5">
-        <v>134</v>
+        <v>5</v>
       </c>
       <c r="E51" s="5">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F51" s="5">
-        <v>108</v>
+        <v>5</v>
       </c>
       <c r="G51" s="5">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H51" s="6">
-        <v>245</v>
+        <v>230</v>
       </c>
     </row>
     <row outlineLevel="0" r="52">
@@ -2159,28 +2159,28 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>GOODRIDE</t>
+          <t>FULDA</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>GR185/65R15</t>
+          <t>FL185/65R15</t>
         </is>
       </c>
       <c r="D52" s="5">
+        <v>130</v>
+      </c>
+      <c r="E52" s="5">
         <v>11</v>
       </c>
-      <c r="E52" s="5">
-        <v>4</v>
-      </c>
       <c r="F52" s="5">
-        <v>3</v>
+        <v>108</v>
       </c>
       <c r="G52" s="5">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="H52" s="6">
-        <v>230</v>
+        <v>245</v>
       </c>
     </row>
     <row outlineLevel="0" r="53">
@@ -2191,28 +2191,28 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>GOODRIDE</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>GD185/65R15</t>
+          <t>GR185/65R15</t>
         </is>
       </c>
       <c r="D53" s="5">
-        <v>58</v>
+        <v>11</v>
       </c>
       <c r="E53" s="5">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F53" s="5">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="G53" s="5">
         <v>4</v>
       </c>
       <c r="H53" s="6">
-        <v>270</v>
+        <v>230</v>
       </c>
     </row>
     <row outlineLevel="0" r="54">
@@ -2223,28 +2223,28 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>HK185/65R15</t>
+          <t>GD185/65R15</t>
         </is>
       </c>
       <c r="D54" s="5">
-        <v>5</v>
+        <v>152</v>
       </c>
       <c r="E54" s="5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F54" s="5">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="G54" s="5">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="H54" s="6">
-        <v>250</v>
+        <v>270</v>
       </c>
     </row>
     <row outlineLevel="0" r="55">
@@ -2255,16 +2255,16 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>LF185/65R15</t>
+          <t>HK185/65R15</t>
         </is>
       </c>
       <c r="D55" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E55" s="5">
         <v>4</v>
@@ -2273,7 +2273,7 @@
         <v>0</v>
       </c>
       <c r="G55" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H55" s="6">
         <v>250</v>
@@ -2287,19 +2287,19 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>RD185/65R15</t>
+          <t>LF185/65R15</t>
         </is>
       </c>
       <c r="D56" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E56" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F56" s="5">
         <v>0</v>
@@ -2308,7 +2308,7 @@
         <v>0</v>
       </c>
       <c r="H56" s="6">
-        <v>200</v>
+        <v>250</v>
       </c>
     </row>
     <row outlineLevel="0" r="57">
@@ -2319,28 +2319,28 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>SEMPERIT</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>SP185/65R15</t>
+          <t>RD185/65R15</t>
         </is>
       </c>
       <c r="D57" s="5">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="E57" s="5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F57" s="5">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G57" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H57" s="6">
-        <v>250</v>
+        <v>200</v>
       </c>
     </row>
     <row outlineLevel="0" r="58">
@@ -2351,60 +2351,60 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>WESTLAKE</t>
+          <t>SEMPERIT</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>WL185/65R15</t>
+          <t>SP185/65R15</t>
         </is>
       </c>
       <c r="D58" s="5">
-        <v>77</v>
+        <v>26</v>
       </c>
       <c r="E58" s="5">
-        <v>75</v>
+        <v>5</v>
       </c>
       <c r="F58" s="5">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G58" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H58" s="6">
-        <v>225</v>
+        <v>250</v>
       </c>
     </row>
     <row outlineLevel="0" r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>185/70R14</t>
+          <t>185/65R15</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>WESTLAKE</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>RD185/70R14</t>
+          <t>WL185/65R15</t>
         </is>
       </c>
       <c r="D59" s="5">
+        <v>57</v>
+      </c>
+      <c r="E59" s="5">
+        <v>55</v>
+      </c>
+      <c r="F59" s="5">
+        <v>0</v>
+      </c>
+      <c r="G59" s="5">
         <v>2</v>
       </c>
-      <c r="E59" s="5">
-        <v>1</v>
-      </c>
-      <c r="F59" s="5">
-        <v>0</v>
-      </c>
-      <c r="G59" s="5">
-        <v>1</v>
-      </c>
       <c r="H59" s="6">
-        <v>230</v>
+        <v>225</v>
       </c>
     </row>
     <row outlineLevel="0" r="60">
@@ -2415,28 +2415,28 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>SEMPERIT</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>SP185/70R14</t>
+          <t>RD185/70R14</t>
         </is>
       </c>
       <c r="D60" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E60" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F60" s="5">
         <v>0</v>
       </c>
       <c r="G60" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H60" s="6">
-        <v>280</v>
+        <v>230</v>
       </c>
     </row>
     <row outlineLevel="0" r="61">
@@ -2447,60 +2447,60 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>WESTLAKE</t>
+          <t>SEMPERIT</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>WL185/70R14</t>
+          <t>SP185/70R14</t>
         </is>
       </c>
       <c r="D61" s="5">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E61" s="5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F61" s="5">
         <v>0</v>
       </c>
       <c r="G61" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H61" s="6">
-        <v>240</v>
+        <v>280</v>
       </c>
     </row>
     <row outlineLevel="0" r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>195/50R15</t>
+          <t>185/70R14</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>AMINE</t>
+          <t>WESTLAKE</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>AM195/50R15</t>
+          <t>WL185/70R14</t>
         </is>
       </c>
       <c r="D62" s="5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E62" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F62" s="5">
         <v>0</v>
       </c>
       <c r="G62" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H62" s="6">
-        <v>220</v>
+        <v>240</v>
       </c>
     </row>
     <row outlineLevel="0" r="63">
@@ -2511,19 +2511,19 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>AMINE</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>GD195/50R15</t>
+          <t>AM195/50R15</t>
         </is>
       </c>
       <c r="D63" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E63" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F63" s="5">
         <v>0</v>
@@ -2532,7 +2532,7 @@
         <v>0</v>
       </c>
       <c r="H63" s="6">
-        <v>290</v>
+        <v>220</v>
       </c>
     </row>
     <row outlineLevel="0" r="64">
@@ -2543,28 +2543,28 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>SEMPERIT</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>SP195/50R15</t>
+          <t>GD195/50R15</t>
         </is>
       </c>
       <c r="D64" s="5">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="E64" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F64" s="5">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G64" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H64" s="6">
-        <v>260</v>
+        <v>290</v>
       </c>
     </row>
     <row outlineLevel="0" r="65">
@@ -2575,83 +2575,83 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>WESTLAKE</t>
+          <t>SEMPERIT</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>WL195/50R15</t>
+          <t>SP195/50R15</t>
         </is>
       </c>
       <c r="D65" s="5">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E65" s="5">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F65" s="5">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G65" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H65" s="6">
-        <v>240</v>
+        <v>260</v>
       </c>
     </row>
     <row outlineLevel="0" r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>195/50R16</t>
+          <t>195/50R15</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>WESTLAKE</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>GD195/50R16</t>
+          <t>WL195/50R15</t>
         </is>
       </c>
       <c r="D66" s="5">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E66" s="5">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F66" s="5">
         <v>0</v>
       </c>
       <c r="G66" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H66" s="6">
-        <v>350</v>
+        <v>240</v>
       </c>
     </row>
     <row outlineLevel="0" r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>195/55R16</t>
+          <t>195/50R16</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>AMINE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>AM195/55R16</t>
+          <t>GD195/50R16</t>
         </is>
       </c>
       <c r="D67" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E67" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F67" s="5">
         <v>0</v>
@@ -2660,7 +2660,7 @@
         <v>0</v>
       </c>
       <c r="H67" s="6">
-        <v>270</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="68">
@@ -2671,28 +2671,28 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>AMINE</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>GD195/55R16</t>
+          <t>AM195/55R16</t>
         </is>
       </c>
       <c r="D68" s="5">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E68" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F68" s="5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G68" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H68" s="6">
-        <v>350</v>
+        <v>270</v>
       </c>
     </row>
     <row outlineLevel="0" r="69">
@@ -2703,19 +2703,19 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>HK195/55R16</t>
+          <t>GD195/55R16</t>
         </is>
       </c>
       <c r="D69" s="5">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E69" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F69" s="5">
         <v>5</v>
@@ -2724,7 +2724,7 @@
         <v>4</v>
       </c>
       <c r="H69" s="6">
-        <v>300</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="70">
@@ -2735,28 +2735,28 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>LASSA</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>LS195/55R16</t>
+          <t>HK195/55R16</t>
         </is>
       </c>
       <c r="D70" s="5">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E70" s="5">
         <v>3</v>
       </c>
       <c r="F70" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G70" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H70" s="6">
-        <v>280</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="71">
@@ -2767,19 +2767,19 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>LASSA</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>NX195/55R16</t>
+          <t>LS195/55R16</t>
         </is>
       </c>
       <c r="D71" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E71" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F71" s="5">
         <v>0</v>
@@ -2788,7 +2788,7 @@
         <v>0</v>
       </c>
       <c r="H71" s="6">
-        <v>300</v>
+        <v>280</v>
       </c>
     </row>
     <row outlineLevel="0" r="72">
@@ -2799,92 +2799,92 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>RD195/55R16</t>
+          <t>NX195/55R16</t>
         </is>
       </c>
       <c r="D72" s="5">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E72" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F72" s="5">
         <v>0</v>
       </c>
       <c r="G72" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H72" s="6">
-        <v>250</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>195/60R16</t>
+          <t>195/55R16</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>GD195/60R16</t>
+          <t>RD195/55R16</t>
         </is>
       </c>
       <c r="D73" s="5">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="E73" s="5">
         <v>4</v>
       </c>
       <c r="F73" s="5">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="G73" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H73" s="6">
-        <v>360</v>
+        <v>250</v>
       </c>
     </row>
     <row outlineLevel="0" r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>195/65R15</t>
+          <t>195/60R16</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>DOUBLESTAR</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>DS195/65R15</t>
+          <t>GD195/60R16</t>
         </is>
       </c>
       <c r="D74" s="5">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E74" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F74" s="5">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="G74" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H74" s="6">
-        <v>230</v>
+        <v>360</v>
       </c>
     </row>
     <row outlineLevel="0" r="75">
@@ -2895,22 +2895,22 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>GOODRIDE</t>
+          <t>DOUBLESTAR</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>GR195/65R15</t>
+          <t>DS195/65R15</t>
         </is>
       </c>
       <c r="D75" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E75" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F75" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G75" s="5">
         <v>0</v>
@@ -2927,28 +2927,28 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODRIDE</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>HK195/65R15</t>
+          <t>GR195/65R15</t>
         </is>
       </c>
       <c r="D76" s="5">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E76" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F76" s="5">
         <v>0</v>
       </c>
       <c r="G76" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H76" s="6">
-        <v>260</v>
+        <v>230</v>
       </c>
     </row>
     <row outlineLevel="0" r="77">
@@ -2959,28 +2959,28 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>LASSA</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>LS195/65R15</t>
+          <t>GD195/65R15</t>
         </is>
       </c>
       <c r="D77" s="5">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="E77" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F77" s="5">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="G77" s="5">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H77" s="6">
-        <v>250</v>
+        <v>275</v>
       </c>
     </row>
     <row outlineLevel="0" r="78">
@@ -2991,28 +2991,28 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>NX195/65R15</t>
+          <t>HK195/65R15</t>
         </is>
       </c>
       <c r="D78" s="5">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E78" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F78" s="5">
         <v>0</v>
       </c>
       <c r="G78" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H78" s="6">
-        <v>230</v>
+        <v>260</v>
       </c>
     </row>
     <row outlineLevel="0" r="79">
@@ -3023,28 +3023,28 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>LASSA</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>RD195/65R15</t>
+          <t>LS195/65R15</t>
         </is>
       </c>
       <c r="D79" s="5">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="E79" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F79" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G79" s="5">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H79" s="6">
-        <v>230</v>
+        <v>250</v>
       </c>
     </row>
     <row outlineLevel="0" r="80">
@@ -3055,147 +3055,147 @@
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>SEMPERIT</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>SP195/65R15</t>
+          <t>NX195/65R15</t>
         </is>
       </c>
       <c r="D80" s="5">
-        <v>88</v>
+        <v>2</v>
       </c>
       <c r="E80" s="5">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F80" s="5">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="G80" s="5">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H80" s="6">
-        <v>250</v>
+        <v>230</v>
       </c>
     </row>
     <row outlineLevel="0" r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>195/70R15C</t>
+          <t>195/65R15</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>DAYTON</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>DT195/70R15C</t>
+          <t>RD195/65R15</t>
         </is>
       </c>
       <c r="D81" s="5">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E81" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F81" s="5">
         <v>0</v>
       </c>
       <c r="G81" s="5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H81" s="6">
-        <v>280</v>
+        <v>230</v>
       </c>
     </row>
     <row outlineLevel="0" r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>195/70R15C</t>
+          <t>195/65R15</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>SEMPERIT</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>LF195/70R15C</t>
+          <t>SP195/65R15</t>
         </is>
       </c>
       <c r="D82" s="5">
-        <v>4</v>
+        <v>87</v>
       </c>
       <c r="E82" s="5">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F82" s="5">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="G82" s="5">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="H82" s="6">
-        <v>300</v>
+        <v>250</v>
       </c>
     </row>
     <row outlineLevel="0" r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>195/75R16C</t>
+          <t>195/70R15C</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>GOODRIDE</t>
+          <t>DAYTON</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>GR195/75R16C</t>
+          <t>DT195/70R15C</t>
         </is>
       </c>
       <c r="D83" s="5">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E83" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F83" s="5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G83" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H83" s="6">
-        <v>350</v>
+        <v>280</v>
       </c>
     </row>
     <row outlineLevel="0" r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>195R14C</t>
+          <t>195/70R15C</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>RD195R14C</t>
+          <t>LF195/70R15C</t>
         </is>
       </c>
       <c r="D84" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E84" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F84" s="5">
         <v>0</v>
@@ -3204,36 +3204,36 @@
         <v>0</v>
       </c>
       <c r="H84" s="6">
-        <v>280</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>195R15C</t>
+          <t>195/75R16C</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>GOODRIDE</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>RD195R15C</t>
+          <t>GR195/75R16C</t>
         </is>
       </c>
       <c r="D85" s="5">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E85" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F85" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G85" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H85" s="6">
         <v>350</v>
@@ -3242,24 +3242,24 @@
     <row outlineLevel="0" r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>205/45R17</t>
+          <t>195R14C</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>CT205/45R17</t>
+          <t>RD195R14C</t>
         </is>
       </c>
       <c r="D86" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E86" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F86" s="5">
         <v>0</v>
@@ -3268,27 +3268,27 @@
         <v>0</v>
       </c>
       <c r="H86" s="6">
-        <v>550</v>
+        <v>280</v>
       </c>
     </row>
     <row outlineLevel="0" r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>205/45R17</t>
+          <t>195R15C</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>FULDA</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>FL205/45R17</t>
+          <t>RD195R15C</t>
         </is>
       </c>
       <c r="D87" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E87" s="5">
         <v>0</v>
@@ -3297,10 +3297,10 @@
         <v>0</v>
       </c>
       <c r="G87" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H87" s="6">
-        <v>380</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="88">
@@ -3311,19 +3311,19 @@
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>GOODRIDE</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>GR205/45R17</t>
+          <t>CT205/45R17</t>
         </is>
       </c>
       <c r="D88" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E88" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F88" s="5">
         <v>0</v>
@@ -3332,7 +3332,7 @@
         <v>0</v>
       </c>
       <c r="H88" s="6">
-        <v>300</v>
+        <v>550</v>
       </c>
     </row>
     <row outlineLevel="0" r="89">
@@ -3343,28 +3343,28 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>FULDA</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>GD205/45R17</t>
+          <t>FL205/45R17</t>
         </is>
       </c>
       <c r="D89" s="5">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="E89" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F89" s="5">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G89" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H89" s="6">
-        <v>450</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="90">
@@ -3375,19 +3375,19 @@
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>GOODRIDE</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>NX205/45R17</t>
+          <t>GR205/45R17</t>
         </is>
       </c>
       <c r="D90" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E90" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F90" s="5">
         <v>0</v>
@@ -3396,7 +3396,7 @@
         <v>0</v>
       </c>
       <c r="H90" s="6">
-        <v>380</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="91">
@@ -3407,51 +3407,51 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>RD205/45R17</t>
+          <t>GD205/45R17</t>
         </is>
       </c>
       <c r="D91" s="5">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="E91" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F91" s="5">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G91" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H91" s="6">
-        <v>300</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>205/50R17</t>
+          <t>205/45R17</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>CT205/50R17</t>
+          <t>NX205/45R17</t>
         </is>
       </c>
       <c r="D92" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E92" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F92" s="5">
         <v>0</v>
@@ -3460,27 +3460,27 @@
         <v>0</v>
       </c>
       <c r="H92" s="6">
-        <v>450</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>205/50R17</t>
+          <t>205/45R17</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>GD205/50R17</t>
+          <t>RD205/45R17</t>
         </is>
       </c>
       <c r="D93" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E93" s="5">
         <v>0</v>
@@ -3489,33 +3489,33 @@
         <v>0</v>
       </c>
       <c r="G93" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H93" s="6">
-        <v>480</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>205/55R16</t>
+          <t>205/50R17</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>AMINE</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>AM205/55R16</t>
+          <t>CT205/50R17</t>
         </is>
       </c>
       <c r="D94" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E94" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F94" s="5">
         <v>0</v>
@@ -3524,27 +3524,27 @@
         <v>0</v>
       </c>
       <c r="H94" s="6">
-        <v>240</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>205/55R16</t>
+          <t>205/50R17</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>BR205/55R16</t>
+          <t>GD205/50R17</t>
         </is>
       </c>
       <c r="D95" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E95" s="5">
         <v>0</v>
@@ -3553,10 +3553,10 @@
         <v>0</v>
       </c>
       <c r="G95" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H95" s="6">
-        <v>290</v>
+        <v>480</v>
       </c>
     </row>
     <row outlineLevel="0" r="96">
@@ -3567,19 +3567,19 @@
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>DOUBLESTAR</t>
+          <t>AMINE</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>DS205/55R16</t>
+          <t>AM205/55R16</t>
         </is>
       </c>
       <c r="D96" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E96" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F96" s="5">
         <v>0</v>
@@ -3588,7 +3588,7 @@
         <v>0</v>
       </c>
       <c r="H96" s="6">
-        <v>230</v>
+        <v>240</v>
       </c>
     </row>
     <row outlineLevel="0" r="97">
@@ -3599,28 +3599,28 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>FULDA</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>FL205/55R16</t>
+          <t>BR205/55R16</t>
         </is>
       </c>
       <c r="D97" s="5">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="E97" s="5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F97" s="5">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G97" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H97" s="6">
-        <v>250</v>
+        <v>290</v>
       </c>
     </row>
     <row outlineLevel="0" r="98">
@@ -3631,28 +3631,28 @@
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>GOODRIDE</t>
+          <t>DOUBLESTAR</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>GR205/55R16</t>
+          <t>DS205/55R16</t>
         </is>
       </c>
       <c r="D98" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E98" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F98" s="5">
         <v>0</v>
       </c>
       <c r="G98" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H98" s="6">
-        <v>250</v>
+        <v>230</v>
       </c>
     </row>
     <row outlineLevel="0" r="99">
@@ -3663,28 +3663,28 @@
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>FULDA</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>GD205/55R16</t>
+          <t>FL205/55R16</t>
         </is>
       </c>
       <c r="D99" s="5">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="E99" s="5">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F99" s="5">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G99" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H99" s="6">
-        <v>280</v>
+        <v>250</v>
       </c>
     </row>
     <row outlineLevel="0" r="100">
@@ -3695,28 +3695,28 @@
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODRIDE</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>HK205/55R16</t>
+          <t>GR205/55R16</t>
         </is>
       </c>
       <c r="D100" s="5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E100" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F100" s="5">
         <v>0</v>
       </c>
       <c r="G100" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H100" s="6">
-        <v>270</v>
+        <v>250</v>
       </c>
     </row>
     <row outlineLevel="0" r="101">
@@ -3727,144 +3727,144 @@
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>RD205/55R16</t>
+          <t>GD205/55R16</t>
         </is>
       </c>
       <c r="D101" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E101" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F101" s="5">
         <v>0</v>
       </c>
       <c r="G101" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H101" s="6">
-        <v>230</v>
+        <v>280</v>
       </c>
     </row>
     <row outlineLevel="0" r="102">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>205/55R16RF</t>
+          <t>205/55R16</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>GD205/55R16RF</t>
+          <t>HK205/55R16</t>
         </is>
       </c>
       <c r="D102" s="5">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E102" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F102" s="5">
         <v>0</v>
       </c>
       <c r="G102" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H102" s="6">
-        <v>480</v>
+        <v>270</v>
       </c>
     </row>
     <row outlineLevel="0" r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>205/55R17</t>
+          <t>205/55R16</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>GD205/55R17</t>
+          <t>RD205/55R16</t>
         </is>
       </c>
       <c r="D103" s="5">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="E103" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F103" s="5">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G103" s="5">
         <v>4</v>
       </c>
       <c r="H103" s="6">
-        <v>450</v>
+        <v>230</v>
       </c>
     </row>
     <row outlineLevel="0" r="104">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>205/55R17</t>
+          <t>205/55R16</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>SEMPERIT</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>NX205/55R17</t>
+          <t>SP205/55R16</t>
         </is>
       </c>
       <c r="D104" s="5">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="E104" s="5">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F104" s="5">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G104" s="5">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H104" s="6">
-        <v>400</v>
+        <v>250</v>
       </c>
     </row>
     <row outlineLevel="0" r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>205/60R16</t>
+          <t>205/55R16RF</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>AMINE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>AM205/60R16</t>
+          <t>GD205/55R16RF</t>
         </is>
       </c>
       <c r="D105" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E105" s="5">
         <v>0</v>
@@ -3873,58 +3873,58 @@
         <v>0</v>
       </c>
       <c r="G105" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H105" s="6">
-        <v>270</v>
+        <v>480</v>
       </c>
     </row>
     <row outlineLevel="0" r="106">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>205/60R16</t>
+          <t>205/55R17</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>BFGOODRICH</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>BF205/60R16</t>
+          <t>GD205/55R17</t>
         </is>
       </c>
       <c r="D106" s="5">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="E106" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F106" s="5">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G106" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H106" s="6">
-        <v>320</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>205/60R16</t>
+          <t>205/55R17</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>DL205/60R16</t>
+          <t>NX205/55R17</t>
         </is>
       </c>
       <c r="D107" s="5">
@@ -3940,7 +3940,7 @@
         <v>0</v>
       </c>
       <c r="H107" s="6">
-        <v>330</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="108">
@@ -3951,28 +3951,28 @@
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>AMINE</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>GD205/60R16</t>
+          <t>AM205/60R16</t>
         </is>
       </c>
       <c r="D108" s="5">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E108" s="5">
         <v>0</v>
       </c>
       <c r="F108" s="5">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G108" s="5">
         <v>0</v>
       </c>
       <c r="H108" s="6">
-        <v>380</v>
+        <v>270</v>
       </c>
     </row>
     <row outlineLevel="0" r="109">
@@ -3983,25 +3983,25 @@
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>BFGOODRICH</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>HK205/60R16</t>
+          <t>BF205/60R16</t>
         </is>
       </c>
       <c r="D109" s="5">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E109" s="5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F109" s="5">
         <v>0</v>
       </c>
       <c r="G109" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H109" s="6">
         <v>320</v>
@@ -4015,19 +4015,19 @@
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>LASSA</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>LS205/60R16</t>
+          <t>DL205/60R16</t>
         </is>
       </c>
       <c r="D110" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E110" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F110" s="5">
         <v>0</v>
@@ -4036,7 +4036,7 @@
         <v>0</v>
       </c>
       <c r="H110" s="6">
-        <v>300</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="111">
@@ -4047,34 +4047,34 @@
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>LF205/60R16</t>
+          <t>GD205/60R16</t>
         </is>
       </c>
       <c r="D111" s="5">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="E111" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F111" s="5">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G111" s="5">
         <v>0</v>
       </c>
       <c r="H111" s="6">
-        <v>300</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="112">
       <c r="A112" s="4" t="inlineStr">
         <is>
-          <t>205/65R15</t>
+          <t>205/60R16</t>
         </is>
       </c>
       <c r="B112" s="4" t="inlineStr">
@@ -4084,46 +4084,46 @@
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>HK205/65R15</t>
+          <t>HK205/60R16</t>
         </is>
       </c>
       <c r="D112" s="5">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E112" s="5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F112" s="5">
         <v>0</v>
       </c>
       <c r="G112" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H112" s="6">
-        <v>270</v>
+        <v>320</v>
       </c>
     </row>
     <row outlineLevel="0" r="113">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>205/65R16</t>
+          <t>205/60R16</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>LASSA</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>BR205/65R16</t>
+          <t>LS205/60R16</t>
         </is>
       </c>
       <c r="D113" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E113" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F113" s="5">
         <v>0</v>
@@ -4132,23 +4132,23 @@
         <v>0</v>
       </c>
       <c r="H113" s="6">
-        <v>420</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="114">
       <c r="A114" s="4" t="inlineStr">
         <is>
-          <t>205/65R16</t>
+          <t>205/60R16</t>
         </is>
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>HK205/65R16</t>
+          <t>LF205/60R16</t>
         </is>
       </c>
       <c r="D114" s="5">
@@ -4164,62 +4164,62 @@
         <v>0</v>
       </c>
       <c r="H114" s="6">
-        <v>380</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="115">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t>215/40R18</t>
+          <t>205/65R15</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>GD215/40R18</t>
+          <t>HK205/65R15</t>
         </is>
       </c>
       <c r="D115" s="5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E115" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F115" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G115" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H115" s="6">
-        <v>600</v>
+        <v>270</v>
       </c>
     </row>
     <row outlineLevel="0" r="116">
       <c r="A116" s="4" t="inlineStr">
         <is>
-          <t>215/40R18</t>
+          <t>205/65R16</t>
         </is>
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>HK215/40R18</t>
+          <t>BR205/65R16</t>
         </is>
       </c>
       <c r="D116" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E116" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F116" s="5">
         <v>0</v>
@@ -4228,30 +4228,30 @@
         <v>0</v>
       </c>
       <c r="H116" s="6">
-        <v>490</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="117">
       <c r="A117" s="4" t="inlineStr">
         <is>
-          <t>215/45R16</t>
+          <t>205/65R16</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>GD215/45R16</t>
+          <t>HK205/65R16</t>
         </is>
       </c>
       <c r="D117" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E117" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F117" s="5">
         <v>0</v>
@@ -4260,13 +4260,13 @@
         <v>0</v>
       </c>
       <c r="H117" s="6">
-        <v>450</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="118">
       <c r="A118" s="4" t="inlineStr">
         <is>
-          <t>215/45R17</t>
+          <t>215/40R18</t>
         </is>
       </c>
       <c r="B118" s="4" t="inlineStr">
@@ -4276,29 +4276,29 @@
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>GD215/45R17</t>
+          <t>GD215/40R18</t>
         </is>
       </c>
       <c r="D118" s="5">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E118" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F118" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G118" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H118" s="6">
-        <v>400</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="119">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t>215/45R17</t>
+          <t>215/40R18</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
@@ -4308,55 +4308,55 @@
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>HK215/45R17</t>
+          <t>HK215/40R18</t>
         </is>
       </c>
       <c r="D119" s="5">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="E119" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F119" s="5">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G119" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H119" s="6">
-        <v>400</v>
+        <v>490</v>
       </c>
     </row>
     <row outlineLevel="0" r="120">
       <c r="A120" s="4" t="inlineStr">
         <is>
-          <t>215/45R17</t>
+          <t>215/45R16</t>
         </is>
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>IRIS</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>IR215/45R17</t>
+          <t>GD215/45R16</t>
         </is>
       </c>
       <c r="D120" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E120" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F120" s="5">
         <v>0</v>
       </c>
       <c r="G120" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H120" s="6">
-        <v>300</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="121">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>LF215/45R17</t>
+          <t>GD215/45R17</t>
         </is>
       </c>
       <c r="D121" s="5">
@@ -4388,7 +4388,7 @@
         <v>0</v>
       </c>
       <c r="H121" s="6">
-        <v>350</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="122">
@@ -4399,83 +4399,83 @@
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>NX215/45R17</t>
+          <t>HK215/45R17</t>
         </is>
       </c>
       <c r="D122" s="5">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E122" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F122" s="5">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="G122" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H122" s="6">
-        <v>380</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="123">
       <c r="A123" s="4" t="inlineStr">
         <is>
-          <t>215/45R18</t>
+          <t>215/45R17</t>
         </is>
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>IRIS</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>GD215/45R18</t>
+          <t>IR215/45R17</t>
         </is>
       </c>
       <c r="D123" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E123" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F123" s="5">
         <v>0</v>
       </c>
       <c r="G123" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H123" s="6">
-        <v>550</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="124">
       <c r="A124" s="4" t="inlineStr">
         <is>
-          <t>215/45R18</t>
+          <t>215/45R17</t>
         </is>
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>RD215/45R18</t>
+          <t>LF215/45R17</t>
         </is>
       </c>
       <c r="D124" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E124" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F124" s="5">
         <v>0</v>
@@ -4484,45 +4484,45 @@
         <v>0</v>
       </c>
       <c r="H124" s="6">
-        <v>450</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="125">
       <c r="A125" s="4" t="inlineStr">
         <is>
-          <t>215/50R17</t>
+          <t>215/45R17</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>BR215/50R17</t>
+          <t>NX215/45R17</t>
         </is>
       </c>
       <c r="D125" s="5">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E125" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F125" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G125" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H125" s="6">
-        <v>450</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="126">
       <c r="A126" s="4" t="inlineStr">
         <is>
-          <t>215/50R17</t>
+          <t>215/45R18</t>
         </is>
       </c>
       <c r="B126" s="4" t="inlineStr">
@@ -4532,11 +4532,11 @@
       </c>
       <c r="C126" s="4" t="inlineStr">
         <is>
-          <t>GD215/50R17</t>
+          <t>GD215/45R18</t>
         </is>
       </c>
       <c r="D126" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E126" s="5">
         <v>3</v>
@@ -4545,33 +4545,33 @@
         <v>0</v>
       </c>
       <c r="G126" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H126" s="6">
-        <v>470</v>
+        <v>550</v>
       </c>
     </row>
     <row outlineLevel="0" r="127">
       <c r="A127" s="4" t="inlineStr">
         <is>
-          <t>215/50R17</t>
+          <t>215/45R18</t>
         </is>
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>HK215/50R17</t>
+          <t>RD215/45R18</t>
         </is>
       </c>
       <c r="D127" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E127" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F127" s="5">
         <v>0</v>
@@ -4580,7 +4580,7 @@
         <v>0</v>
       </c>
       <c r="H127" s="6">
-        <v>400</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="128">
@@ -4591,19 +4591,19 @@
       </c>
       <c r="B128" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C128" s="4" t="inlineStr">
         <is>
-          <t>LF215/50R17</t>
+          <t>BR215/50R17</t>
         </is>
       </c>
       <c r="D128" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E128" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F128" s="5">
         <v>0</v>
@@ -4612,13 +4612,13 @@
         <v>0</v>
       </c>
       <c r="H128" s="6">
-        <v>420</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="129">
       <c r="A129" s="4" t="inlineStr">
         <is>
-          <t>215/50R18</t>
+          <t>215/50R17</t>
         </is>
       </c>
       <c r="B129" s="4" t="inlineStr">
@@ -4628,11 +4628,11 @@
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>GD215/50R18</t>
+          <t>GD215/50R17</t>
         </is>
       </c>
       <c r="D129" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E129" s="5">
         <v>3</v>
@@ -4641,33 +4641,33 @@
         <v>0</v>
       </c>
       <c r="G129" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H129" s="6">
-        <v>600</v>
+        <v>470</v>
       </c>
     </row>
     <row outlineLevel="0" r="130">
       <c r="A130" s="4" t="inlineStr">
         <is>
-          <t>215/55R16</t>
+          <t>215/50R17</t>
         </is>
       </c>
       <c r="B130" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C130" s="4" t="inlineStr">
         <is>
-          <t>GD215/55R16</t>
+          <t>HK215/50R17</t>
         </is>
       </c>
       <c r="D130" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E130" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F130" s="5">
         <v>0</v>
@@ -4676,13 +4676,13 @@
         <v>0</v>
       </c>
       <c r="H130" s="6">
-        <v>440</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="131">
       <c r="A131" s="4" t="inlineStr">
         <is>
-          <t>215/55R16</t>
+          <t>215/50R17</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr">
@@ -4692,14 +4692,14 @@
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>LF215/55R16</t>
+          <t>LF215/50R17</t>
         </is>
       </c>
       <c r="D131" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E131" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F131" s="5">
         <v>0</v>
@@ -4708,30 +4708,30 @@
         <v>0</v>
       </c>
       <c r="H131" s="6">
-        <v>350</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="132">
       <c r="A132" s="4" t="inlineStr">
         <is>
-          <t>215/55R17</t>
+          <t>215/50R18</t>
         </is>
       </c>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C132" s="4" t="inlineStr">
         <is>
-          <t>BR215/55R17</t>
+          <t>GD215/50R18</t>
         </is>
       </c>
       <c r="D132" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E132" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F132" s="5">
         <v>0</v>
@@ -4740,30 +4740,30 @@
         <v>0</v>
       </c>
       <c r="H132" s="6">
-        <v>480</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="133">
       <c r="A133" s="4" t="inlineStr">
         <is>
-          <t>215/55R17</t>
+          <t>215/55R16</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>HK215/55R17</t>
+          <t>GD215/55R16</t>
         </is>
       </c>
       <c r="D133" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E133" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F133" s="5">
         <v>0</v>
@@ -4772,30 +4772,30 @@
         <v>0</v>
       </c>
       <c r="H133" s="6">
-        <v>420</v>
+        <v>440</v>
       </c>
     </row>
     <row outlineLevel="0" r="134">
       <c r="A134" s="4" t="inlineStr">
         <is>
-          <t>215/55R17</t>
+          <t>215/55R16</t>
         </is>
       </c>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>SEMPERIT</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C134" s="4" t="inlineStr">
         <is>
-          <t>SP215/55R17</t>
+          <t>LF215/55R16</t>
         </is>
       </c>
       <c r="D134" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E134" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F134" s="5">
         <v>0</v>
@@ -4804,30 +4804,30 @@
         <v>0</v>
       </c>
       <c r="H134" s="6">
-        <v>420</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="135">
       <c r="A135" s="4" t="inlineStr">
         <is>
-          <t>215/55R18</t>
+          <t>215/55R17</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>GD215/55R18</t>
+          <t>BR215/55R17</t>
         </is>
       </c>
       <c r="D135" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E135" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F135" s="5">
         <v>0</v>
@@ -4836,23 +4836,23 @@
         <v>0</v>
       </c>
       <c r="H135" s="6">
-        <v>580</v>
+        <v>480</v>
       </c>
     </row>
     <row outlineLevel="0" r="136">
       <c r="A136" s="4" t="inlineStr">
         <is>
-          <t>215/60R16</t>
+          <t>215/55R17</t>
         </is>
       </c>
       <c r="B136" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C136" s="4" t="inlineStr">
         <is>
-          <t>BR215/60R16</t>
+          <t>HK215/55R17</t>
         </is>
       </c>
       <c r="D136" s="5">
@@ -4868,27 +4868,27 @@
         <v>0</v>
       </c>
       <c r="H136" s="6">
-        <v>380</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="137">
       <c r="A137" s="4" t="inlineStr">
         <is>
-          <t>215/60R16</t>
+          <t>215/55R17</t>
         </is>
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>SEMPERIT</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>DL215/60R16</t>
+          <t>SP215/55R17</t>
         </is>
       </c>
       <c r="D137" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E137" s="5">
         <v>0</v>
@@ -4897,42 +4897,42 @@
         <v>0</v>
       </c>
       <c r="G137" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H137" s="6">
-        <v>350</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="138">
       <c r="A138" s="4" t="inlineStr">
         <is>
-          <t>215/60R16</t>
+          <t>215/55R18</t>
         </is>
       </c>
       <c r="B138" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C138" s="4" t="inlineStr">
         <is>
-          <t>HK215/60R16</t>
+          <t>GD215/55R18</t>
         </is>
       </c>
       <c r="D138" s="5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E138" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F138" s="5">
         <v>0</v>
       </c>
       <c r="G138" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H138" s="6">
-        <v>330</v>
+        <v>580</v>
       </c>
     </row>
     <row outlineLevel="0" r="139">
@@ -4943,48 +4943,48 @@
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>NX215/60R16</t>
+          <t>BR215/60R16</t>
         </is>
       </c>
       <c r="D139" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E139" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F139" s="5">
         <v>0</v>
       </c>
       <c r="G139" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H139" s="6">
-        <v>330</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="140">
       <c r="A140" s="4" t="inlineStr">
         <is>
-          <t>215/60R17</t>
+          <t>215/60R16</t>
         </is>
       </c>
       <c r="B140" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C140" s="4" t="inlineStr">
         <is>
-          <t>GD215/60R17</t>
+          <t>DL215/60R16</t>
         </is>
       </c>
       <c r="D140" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E140" s="5">
         <v>0</v>
@@ -4993,62 +4993,62 @@
         <v>0</v>
       </c>
       <c r="G140" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H140" s="6">
-        <v>480</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="141">
       <c r="A141" s="4" t="inlineStr">
         <is>
-          <t>215/60R17</t>
+          <t>215/60R16</t>
         </is>
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>RD215/60R17</t>
+          <t>HK215/60R16</t>
         </is>
       </c>
       <c r="D141" s="5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E141" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F141" s="5">
         <v>0</v>
       </c>
       <c r="G141" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H141" s="6">
-        <v>300</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="142">
       <c r="A142" s="4" t="inlineStr">
         <is>
-          <t>215/65R16</t>
+          <t>215/60R16</t>
         </is>
       </c>
       <c r="B142" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C142" s="4" t="inlineStr">
         <is>
-          <t>GD215/65R16</t>
+          <t>NX215/60R16</t>
         </is>
       </c>
       <c r="D142" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E142" s="5">
         <v>0</v>
@@ -5057,33 +5057,33 @@
         <v>0</v>
       </c>
       <c r="G142" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H142" s="6">
-        <v>380</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="143">
       <c r="A143" s="4" t="inlineStr">
         <is>
-          <t>215/65R16</t>
+          <t>215/60R17</t>
         </is>
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>HK215/65R16</t>
+          <t>GD215/60R17</t>
         </is>
       </c>
       <c r="D143" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E143" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F143" s="5">
         <v>0</v>
@@ -5092,23 +5092,23 @@
         <v>0</v>
       </c>
       <c r="H143" s="6">
-        <v>350</v>
+        <v>480</v>
       </c>
     </row>
     <row outlineLevel="0" r="144">
       <c r="A144" s="4" t="inlineStr">
         <is>
-          <t>215/65R17</t>
+          <t>215/60R17</t>
         </is>
       </c>
       <c r="B144" s="4" t="inlineStr">
         <is>
-          <t>MICHELIN</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C144" s="4" t="inlineStr">
         <is>
-          <t>MC215/65R17</t>
+          <t>RD215/60R17</t>
         </is>
       </c>
       <c r="D144" s="5">
@@ -5124,27 +5124,27 @@
         <v>0</v>
       </c>
       <c r="H144" s="6">
-        <v>680</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="145">
       <c r="A145" s="4" t="inlineStr">
         <is>
-          <t>215/65R17</t>
+          <t>215/65R16</t>
         </is>
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>NX215/65R17</t>
+          <t>GD215/65R16</t>
         </is>
       </c>
       <c r="D145" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E145" s="5">
         <v>0</v>
@@ -5153,33 +5153,33 @@
         <v>0</v>
       </c>
       <c r="G145" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H145" s="6">
-        <v>420</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="146">
       <c r="A146" s="4" t="inlineStr">
         <is>
-          <t>215/70R15C</t>
+          <t>215/65R16</t>
         </is>
       </c>
       <c r="B146" s="4" t="inlineStr">
         <is>
-          <t>DOUBLESTAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C146" s="4" t="inlineStr">
         <is>
-          <t>DS215/70R15C</t>
+          <t>HK215/65R16</t>
         </is>
       </c>
       <c r="D146" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E146" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F146" s="5">
         <v>0</v>
@@ -5194,49 +5194,49 @@
     <row outlineLevel="0" r="147">
       <c r="A147" s="4" t="inlineStr">
         <is>
-          <t>215/70R15C</t>
+          <t>215/65R17</t>
         </is>
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>LINGLONG</t>
+          <t>MICHELIN</t>
         </is>
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>LG215/70R15C</t>
+          <t>MC215/65R17</t>
         </is>
       </c>
       <c r="D147" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E147" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F147" s="5">
         <v>0</v>
       </c>
       <c r="G147" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H147" s="6">
-        <v>370</v>
+        <v>680</v>
       </c>
     </row>
     <row outlineLevel="0" r="148">
       <c r="A148" s="4" t="inlineStr">
         <is>
-          <t>215/70R15C</t>
+          <t>215/65R17</t>
         </is>
       </c>
       <c r="B148" s="4" t="inlineStr">
         <is>
-          <t>MICHELIN</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C148" s="4" t="inlineStr">
         <is>
-          <t>MC215/70R15C</t>
+          <t>NX215/65R17</t>
         </is>
       </c>
       <c r="D148" s="5">
@@ -5252,7 +5252,7 @@
         <v>0</v>
       </c>
       <c r="H148" s="6">
-        <v>590</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="149">
@@ -5263,19 +5263,19 @@
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>DOUBLESTAR</t>
         </is>
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>RD215/70R15C</t>
+          <t>DS215/70R15C</t>
         </is>
       </c>
       <c r="D149" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E149" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F149" s="5">
         <v>0</v>
@@ -5284,94 +5284,94 @@
         <v>0</v>
       </c>
       <c r="H149" s="6">
-        <v>330</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="150">
       <c r="A150" s="4" t="inlineStr">
         <is>
-          <t>225/40R18</t>
+          <t>215/70R15C</t>
         </is>
       </c>
       <c r="B150" s="4" t="inlineStr">
         <is>
-          <t>BARUM</t>
+          <t>LINGLONG</t>
         </is>
       </c>
       <c r="C150" s="4" t="inlineStr">
         <is>
-          <t>BM225/40R18</t>
+          <t>LG215/70R15C</t>
         </is>
       </c>
       <c r="D150" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E150" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F150" s="5">
         <v>0</v>
       </c>
       <c r="G150" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H150" s="6">
-        <v>420</v>
+        <v>370</v>
       </c>
     </row>
     <row outlineLevel="0" r="151">
       <c r="A151" s="4" t="inlineStr">
         <is>
-          <t>225/40R18</t>
+          <t>215/70R15C</t>
         </is>
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>MICHELIN</t>
         </is>
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>GD225/40R18</t>
+          <t>MC215/70R15C</t>
         </is>
       </c>
       <c r="D151" s="5">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E151" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F151" s="5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G151" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H151" s="6">
-        <v>480</v>
+        <v>590</v>
       </c>
     </row>
     <row outlineLevel="0" r="152">
       <c r="A152" s="4" t="inlineStr">
         <is>
-          <t>225/40R18</t>
+          <t>215/70R15C</t>
         </is>
       </c>
       <c r="B152" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C152" s="4" t="inlineStr">
         <is>
-          <t>HK225/40R18</t>
+          <t>RD215/70R15C</t>
         </is>
       </c>
       <c r="D152" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E152" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F152" s="5">
         <v>0</v>
@@ -5380,7 +5380,7 @@
         <v>0</v>
       </c>
       <c r="H152" s="6">
-        <v>450</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="153">
@@ -5391,28 +5391,28 @@
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>LASSA</t>
+          <t>BARUM</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>LS225/40R18</t>
+          <t>BM225/40R18</t>
         </is>
       </c>
       <c r="D153" s="5">
         <v>1</v>
       </c>
       <c r="E153" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F153" s="5">
         <v>0</v>
       </c>
       <c r="G153" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H153" s="6">
-        <v>330</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="154">
@@ -5423,28 +5423,28 @@
       </c>
       <c r="B154" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C154" s="4" t="inlineStr">
         <is>
-          <t>NX225/40R18</t>
+          <t>GD225/40R18</t>
         </is>
       </c>
       <c r="D154" s="5">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="E154" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F154" s="5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G154" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H154" s="6">
-        <v>400</v>
+        <v>480</v>
       </c>
     </row>
     <row outlineLevel="0" r="155">
@@ -5455,19 +5455,19 @@
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>SEMPERIT</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>SP225/40R18</t>
+          <t>HK225/40R18</t>
         </is>
       </c>
       <c r="D155" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E155" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F155" s="5">
         <v>0</v>
@@ -5482,24 +5482,24 @@
     <row outlineLevel="0" r="156">
       <c r="A156" s="4" t="inlineStr">
         <is>
-          <t>225/40R18RF</t>
+          <t>225/40R18</t>
         </is>
       </c>
       <c r="B156" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>LASSA</t>
         </is>
       </c>
       <c r="C156" s="4" t="inlineStr">
         <is>
-          <t>GD225/40R18RF</t>
+          <t>LS225/40R18</t>
         </is>
       </c>
       <c r="D156" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E156" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F156" s="5">
         <v>0</v>
@@ -5508,30 +5508,30 @@
         <v>0</v>
       </c>
       <c r="H156" s="6">
-        <v>590</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="157">
       <c r="A157" s="4" t="inlineStr">
         <is>
-          <t>225/40R19RF</t>
+          <t>225/40R18</t>
         </is>
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>GD225/40R19RF</t>
+          <t>NX225/40R18</t>
         </is>
       </c>
       <c r="D157" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E157" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F157" s="5">
         <v>0</v>
@@ -5540,23 +5540,23 @@
         <v>0</v>
       </c>
       <c r="H157" s="6">
-        <v>1200</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="158">
       <c r="A158" s="4" t="inlineStr">
         <is>
-          <t>225/45R17</t>
+          <t>225/40R18</t>
         </is>
       </c>
       <c r="B158" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>SEMPERIT</t>
         </is>
       </c>
       <c r="C158" s="4" t="inlineStr">
         <is>
-          <t>CT225/45R17</t>
+          <t>SP225/40R18</t>
         </is>
       </c>
       <c r="D158" s="5">
@@ -5572,45 +5572,45 @@
         <v>0</v>
       </c>
       <c r="H158" s="6">
-        <v>400</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="159">
       <c r="A159" s="4" t="inlineStr">
         <is>
-          <t>225/45R17</t>
+          <t>225/40R18RF</t>
         </is>
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>FULDA</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>FL225/45R17</t>
+          <t>GD225/40R18RF</t>
         </is>
       </c>
       <c r="D159" s="5">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="E159" s="5">
         <v>4</v>
       </c>
       <c r="F159" s="5">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G159" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H159" s="6">
-        <v>350</v>
+        <v>590</v>
       </c>
     </row>
     <row outlineLevel="0" r="160">
       <c r="A160" s="4" t="inlineStr">
         <is>
-          <t>225/45R17</t>
+          <t>225/40R19RF</t>
         </is>
       </c>
       <c r="B160" s="4" t="inlineStr">
@@ -5620,23 +5620,23 @@
       </c>
       <c r="C160" s="4" t="inlineStr">
         <is>
-          <t>GD225/45R17</t>
+          <t>GD225/40R19RF</t>
         </is>
       </c>
       <c r="D160" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E160" s="5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F160" s="5">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G160" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H160" s="6">
-        <v>380</v>
+        <v>1200</v>
       </c>
     </row>
     <row outlineLevel="0" r="161">
@@ -5647,19 +5647,19 @@
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>HK225/45R17</t>
+          <t>CT225/45R17</t>
         </is>
       </c>
       <c r="D161" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E161" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F161" s="5">
         <v>0</v>
@@ -5668,45 +5668,45 @@
         <v>0</v>
       </c>
       <c r="H161" s="6">
-        <v>380</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="162">
       <c r="A162" s="4" t="inlineStr">
         <is>
-          <t>225/45R18</t>
+          <t>225/45R17</t>
         </is>
       </c>
       <c r="B162" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>FULDA</t>
         </is>
       </c>
       <c r="C162" s="4" t="inlineStr">
         <is>
-          <t>DL225/45R18</t>
+          <t>FL225/45R17</t>
         </is>
       </c>
       <c r="D162" s="5">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="E162" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F162" s="5">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G162" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H162" s="6">
-        <v>500</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="163">
       <c r="A163" s="4" t="inlineStr">
         <is>
-          <t>225/45R18</t>
+          <t>225/45R17</t>
         </is>
       </c>
       <c r="B163" s="4" t="inlineStr">
@@ -5716,29 +5716,29 @@
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>GD225/45R18</t>
+          <t>GD225/45R17</t>
         </is>
       </c>
       <c r="D163" s="5">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E163" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F163" s="5">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="G163" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H163" s="6">
-        <v>550</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="164">
       <c r="A164" s="4" t="inlineStr">
         <is>
-          <t>225/45R18</t>
+          <t>225/45R17</t>
         </is>
       </c>
       <c r="B164" s="4" t="inlineStr">
@@ -5748,14 +5748,14 @@
       </c>
       <c r="C164" s="4" t="inlineStr">
         <is>
-          <t>HK225/45R18</t>
+          <t>HK225/45R17</t>
         </is>
       </c>
       <c r="D164" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E164" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F164" s="5">
         <v>0</v>
@@ -5764,7 +5764,7 @@
         <v>0</v>
       </c>
       <c r="H164" s="6">
-        <v>450</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="165">
@@ -5775,19 +5775,19 @@
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>LF225/45R18</t>
+          <t>DL225/45R18</t>
         </is>
       </c>
       <c r="D165" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E165" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F165" s="5">
         <v>0</v>
@@ -5796,13 +5796,13 @@
         <v>0</v>
       </c>
       <c r="H165" s="6">
-        <v>420</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="166">
       <c r="A166" s="4" t="inlineStr">
         <is>
-          <t>225/45R18RF</t>
+          <t>225/45R18</t>
         </is>
       </c>
       <c r="B166" s="4" t="inlineStr">
@@ -5812,46 +5812,46 @@
       </c>
       <c r="C166" s="4" t="inlineStr">
         <is>
-          <t>GD225/45R18RF</t>
+          <t>GD225/45R18</t>
         </is>
       </c>
       <c r="D166" s="5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E166" s="5">
+        <v>4</v>
+      </c>
+      <c r="F166" s="5">
         <v>2</v>
       </c>
-      <c r="F166" s="5">
-        <v>0</v>
-      </c>
       <c r="G166" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H166" s="6">
-        <v>720</v>
+        <v>550</v>
       </c>
     </row>
     <row outlineLevel="0" r="167">
       <c r="A167" s="4" t="inlineStr">
         <is>
-          <t>225/45R19</t>
+          <t>225/45R18</t>
         </is>
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>CT225/45R19</t>
+          <t>HK225/45R18</t>
         </is>
       </c>
       <c r="D167" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E167" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F167" s="5">
         <v>0</v>
@@ -5860,30 +5860,30 @@
         <v>0</v>
       </c>
       <c r="H167" s="6">
-        <v>780</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="168">
       <c r="A168" s="4" t="inlineStr">
         <is>
-          <t>225/45R19</t>
+          <t>225/45R18</t>
         </is>
       </c>
       <c r="B168" s="4" t="inlineStr">
         <is>
-          <t>LASSA</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C168" s="4" t="inlineStr">
         <is>
-          <t>LS225/45R19</t>
+          <t>LF225/45R18</t>
         </is>
       </c>
       <c r="D168" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E168" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F168" s="5">
         <v>0</v>
@@ -5892,126 +5892,126 @@
         <v>0</v>
       </c>
       <c r="H168" s="6">
-        <v>520</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="169">
       <c r="A169" s="4" t="inlineStr">
         <is>
-          <t>225/50R17</t>
+          <t>225/45R18RF</t>
         </is>
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>BR225/50R17</t>
+          <t>GD225/45R18RF</t>
         </is>
       </c>
       <c r="D169" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E169" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F169" s="5">
         <v>0</v>
       </c>
       <c r="G169" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H169" s="6">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row outlineLevel="0" r="170">
       <c r="A170" s="4" t="inlineStr">
         <is>
-          <t>225/50R17</t>
+          <t>225/45R19</t>
         </is>
       </c>
       <c r="B170" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C170" s="4" t="inlineStr">
         <is>
-          <t>GD225/50R17</t>
+          <t>CT225/45R19</t>
         </is>
       </c>
       <c r="D170" s="5">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E170" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F170" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G170" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H170" s="6">
-        <v>500</v>
+        <v>780</v>
       </c>
     </row>
     <row outlineLevel="0" r="171">
       <c r="A171" s="4" t="inlineStr">
         <is>
-          <t>225/50R17</t>
+          <t>225/45R19</t>
         </is>
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t>HK225/50R17</t>
+          <t>GD225/45R19</t>
         </is>
       </c>
       <c r="D171" s="5">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E171" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F171" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G171" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H171" s="6">
-        <v>400</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="172">
       <c r="A172" s="4" t="inlineStr">
         <is>
-          <t>225/55R16</t>
+          <t>225/45R19</t>
         </is>
       </c>
       <c r="B172" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>LASSA</t>
         </is>
       </c>
       <c r="C172" s="4" t="inlineStr">
         <is>
-          <t>DL225/55R16</t>
+          <t>LS225/45R19</t>
         </is>
       </c>
       <c r="D172" s="5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E172" s="5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F172" s="5">
         <v>0</v>
@@ -6020,30 +6020,30 @@
         <v>0</v>
       </c>
       <c r="H172" s="6">
-        <v>450</v>
+        <v>520</v>
       </c>
     </row>
     <row outlineLevel="0" r="173">
       <c r="A173" s="4" t="inlineStr">
         <is>
-          <t>225/55R16</t>
+          <t>225/50R17</t>
         </is>
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>GD225/55R16</t>
+          <t>BR225/50R17</t>
         </is>
       </c>
       <c r="D173" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E173" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F173" s="5">
         <v>0</v>
@@ -6052,94 +6052,94 @@
         <v>0</v>
       </c>
       <c r="H173" s="6">
-        <v>420</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="174">
       <c r="A174" s="4" t="inlineStr">
         <is>
-          <t>225/55R17</t>
+          <t>225/50R17</t>
         </is>
       </c>
       <c r="B174" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C174" s="4" t="inlineStr">
         <is>
-          <t>HK225/55R17</t>
+          <t>GD225/50R17</t>
         </is>
       </c>
       <c r="D174" s="5">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E174" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F174" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G174" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H174" s="6">
-        <v>430</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="175">
       <c r="A175" s="4" t="inlineStr">
         <is>
-          <t>225/55R17RF</t>
+          <t>225/50R17</t>
         </is>
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>GD225/55R17RF</t>
+          <t>HK225/50R17</t>
         </is>
       </c>
       <c r="D175" s="5">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E175" s="5">
         <v>4</v>
       </c>
       <c r="F175" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G175" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H175" s="6">
-        <v>700</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="176">
       <c r="A176" s="4" t="inlineStr">
         <is>
-          <t>225/55R18</t>
+          <t>225/55R16</t>
         </is>
       </c>
       <c r="B176" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C176" s="4" t="inlineStr">
         <is>
-          <t>HK225/55R18</t>
+          <t>DL225/55R16</t>
         </is>
       </c>
       <c r="D176" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E176" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F176" s="5">
         <v>0</v>
@@ -6148,30 +6148,30 @@
         <v>0</v>
       </c>
       <c r="H176" s="6">
-        <v>500</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="177">
       <c r="A177" s="4" t="inlineStr">
         <is>
-          <t>225/55R18</t>
+          <t>225/55R16</t>
         </is>
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>KUMHO</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>KM225/55R18</t>
+          <t>GD225/55R16</t>
         </is>
       </c>
       <c r="D177" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E177" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F177" s="5">
         <v>0</v>
@@ -6180,30 +6180,30 @@
         <v>0</v>
       </c>
       <c r="H177" s="6">
-        <v>450</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="178">
       <c r="A178" s="4" t="inlineStr">
         <is>
-          <t>225/55R19</t>
+          <t>225/55R17</t>
         </is>
       </c>
       <c r="B178" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C178" s="4" t="inlineStr">
         <is>
-          <t>BR225/55R19</t>
+          <t>HK225/55R17</t>
         </is>
       </c>
       <c r="D178" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E178" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F178" s="5">
         <v>0</v>
@@ -6212,13 +6212,13 @@
         <v>0</v>
       </c>
       <c r="H178" s="6">
-        <v>750</v>
+        <v>430</v>
       </c>
     </row>
     <row outlineLevel="0" r="179">
       <c r="A179" s="4" t="inlineStr">
         <is>
-          <t>225/55R19</t>
+          <t>225/55R17RF</t>
         </is>
       </c>
       <c r="B179" s="4" t="inlineStr">
@@ -6228,39 +6228,39 @@
       </c>
       <c r="C179" s="4" t="inlineStr">
         <is>
-          <t>GD225/55R19</t>
+          <t>GD225/55R17RF</t>
         </is>
       </c>
       <c r="D179" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E179" s="5">
         <v>4</v>
       </c>
       <c r="F179" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G179" s="5">
         <v>0</v>
       </c>
       <c r="H179" s="6">
-        <v>750</v>
+        <v>700</v>
       </c>
     </row>
     <row outlineLevel="0" r="180">
       <c r="A180" s="4" t="inlineStr">
         <is>
-          <t>225/60R17</t>
+          <t>225/55R18</t>
         </is>
       </c>
       <c r="B180" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C180" s="4" t="inlineStr">
         <is>
-          <t>GD225/60R17</t>
+          <t>HK225/55R18</t>
         </is>
       </c>
       <c r="D180" s="5">
@@ -6282,21 +6282,21 @@
     <row outlineLevel="0" r="181">
       <c r="A181" s="4" t="inlineStr">
         <is>
-          <t>225/60R17</t>
+          <t>225/55R18</t>
         </is>
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>KUMHO</t>
         </is>
       </c>
       <c r="C181" s="4" t="inlineStr">
         <is>
-          <t>HK225/60R17</t>
+          <t>KM225/55R18</t>
         </is>
       </c>
       <c r="D181" s="5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E181" s="5">
         <v>4</v>
@@ -6305,26 +6305,26 @@
         <v>0</v>
       </c>
       <c r="G181" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H181" s="6">
-        <v>425</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="182">
       <c r="A182" s="4" t="inlineStr">
         <is>
-          <t>225/60R18</t>
+          <t>225/55R19</t>
         </is>
       </c>
       <c r="B182" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C182" s="4" t="inlineStr">
         <is>
-          <t>GD225/60R18</t>
+          <t>BR225/55R19</t>
         </is>
       </c>
       <c r="D182" s="5">
@@ -6340,30 +6340,30 @@
         <v>0</v>
       </c>
       <c r="H182" s="6">
-        <v>700</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="183">
       <c r="A183" s="4" t="inlineStr">
         <is>
-          <t>225/65R17</t>
+          <t>225/55R19</t>
         </is>
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C183" s="4" t="inlineStr">
         <is>
-          <t>RD225/65R17</t>
+          <t>GD225/55R19</t>
         </is>
       </c>
       <c r="D183" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E183" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F183" s="5">
         <v>0</v>
@@ -6372,27 +6372,27 @@
         <v>0</v>
       </c>
       <c r="H183" s="6">
-        <v>450</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="184">
       <c r="A184" s="4" t="inlineStr">
         <is>
-          <t>225/70R15C</t>
+          <t>225/60R17</t>
         </is>
       </c>
       <c r="B184" s="4" t="inlineStr">
         <is>
-          <t>MATADOR</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C184" s="4" t="inlineStr">
         <is>
-          <t>MT225/70R15C</t>
+          <t>GD225/60R17</t>
         </is>
       </c>
       <c r="D184" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E184" s="5">
         <v>0</v>
@@ -6401,80 +6401,80 @@
         <v>0</v>
       </c>
       <c r="G184" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H184" s="6">
-        <v>450</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="185">
       <c r="A185" s="4" t="inlineStr">
         <is>
-          <t>225/70R15C</t>
+          <t>225/60R17</t>
         </is>
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>SEMPERIT</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C185" s="4" t="inlineStr">
         <is>
-          <t>SP225/70R15C</t>
+          <t>HK225/60R17</t>
         </is>
       </c>
       <c r="D185" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E185" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F185" s="5">
         <v>0</v>
       </c>
       <c r="G185" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H185" s="6">
-        <v>450</v>
+        <v>425</v>
       </c>
     </row>
     <row outlineLevel="0" r="186">
       <c r="A186" s="4" t="inlineStr">
         <is>
-          <t>225/75R15C</t>
+          <t>225/60R18</t>
         </is>
       </c>
       <c r="B186" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C186" s="4" t="inlineStr">
         <is>
-          <t>RD225/75R15C</t>
+          <t>GD225/60R18</t>
         </is>
       </c>
       <c r="D186" s="5">
         <v>1</v>
       </c>
       <c r="E186" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F186" s="5">
         <v>0</v>
       </c>
       <c r="G186" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H186" s="6">
-        <v>330</v>
+        <v>700</v>
       </c>
     </row>
     <row outlineLevel="0" r="187">
       <c r="A187" s="4" t="inlineStr">
         <is>
-          <t>235/35R19</t>
+          <t>225/65R17</t>
         </is>
       </c>
       <c r="B187" s="4" t="inlineStr">
@@ -6484,78 +6484,78 @@
       </c>
       <c r="C187" s="4" t="inlineStr">
         <is>
-          <t>RD235/35R19</t>
+          <t>RD225/65R17</t>
         </is>
       </c>
       <c r="D187" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E187" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F187" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G187" s="5">
         <v>0</v>
       </c>
       <c r="H187" s="6">
-        <v>600</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="188">
       <c r="A188" s="4" t="inlineStr">
         <is>
-          <t>235/40R19</t>
+          <t>225/70R15C</t>
         </is>
       </c>
       <c r="B188" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>MATADOR</t>
         </is>
       </c>
       <c r="C188" s="4" t="inlineStr">
         <is>
-          <t>GD235/40R19</t>
+          <t>MT225/70R15C</t>
         </is>
       </c>
       <c r="D188" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E188" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F188" s="5">
         <v>0</v>
       </c>
       <c r="G188" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H188" s="6">
-        <v>850</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="189">
       <c r="A189" s="4" t="inlineStr">
         <is>
-          <t>235/45R18</t>
+          <t>225/70R15C</t>
         </is>
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>SEMPERIT</t>
         </is>
       </c>
       <c r="C189" s="4" t="inlineStr">
         <is>
-          <t>GD235/45R18</t>
+          <t>SP225/70R15C</t>
         </is>
       </c>
       <c r="D189" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E189" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F189" s="5">
         <v>0</v>
@@ -6564,77 +6564,77 @@
         <v>0</v>
       </c>
       <c r="H189" s="6">
-        <v>600</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="190">
       <c r="A190" s="4" t="inlineStr">
         <is>
-          <t>235/50R18</t>
+          <t>225/75R15C</t>
         </is>
       </c>
       <c r="B190" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C190" s="4" t="inlineStr">
         <is>
-          <t>HK235/50R18</t>
+          <t>RD225/75R15C</t>
         </is>
       </c>
       <c r="D190" s="5">
         <v>1</v>
       </c>
       <c r="E190" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F190" s="5">
         <v>0</v>
       </c>
       <c r="G190" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H190" s="6">
-        <v>500</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="191">
       <c r="A191" s="4" t="inlineStr">
         <is>
-          <t>235/50R19</t>
+          <t>235/35R19</t>
         </is>
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C191" s="4" t="inlineStr">
         <is>
-          <t>GD235/50R19</t>
+          <t>RD235/35R19</t>
         </is>
       </c>
       <c r="D191" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E191" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F191" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G191" s="5">
         <v>0</v>
       </c>
       <c r="H191" s="6">
-        <v>800</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="192">
       <c r="A192" s="4" t="inlineStr">
         <is>
-          <t>235/50R20</t>
+          <t>235/40R19</t>
         </is>
       </c>
       <c r="B192" s="4" t="inlineStr">
@@ -6644,46 +6644,46 @@
       </c>
       <c r="C192" s="4" t="inlineStr">
         <is>
-          <t>GD235/50R20</t>
+          <t>GD235/40R19</t>
         </is>
       </c>
       <c r="D192" s="5">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E192" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F192" s="5">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G192" s="5">
         <v>0</v>
       </c>
       <c r="H192" s="6">
-        <v>1180</v>
+        <v>850</v>
       </c>
     </row>
     <row outlineLevel="0" r="193">
       <c r="A193" s="4" t="inlineStr">
         <is>
-          <t>235/55R17</t>
+          <t>235/45R18</t>
         </is>
       </c>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C193" s="4" t="inlineStr">
         <is>
-          <t>BR235/55R17</t>
+          <t>GD235/45R18</t>
         </is>
       </c>
       <c r="D193" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E193" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F193" s="5">
         <v>0</v>
@@ -6692,13 +6692,13 @@
         <v>0</v>
       </c>
       <c r="H193" s="6">
-        <v>450</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="194">
       <c r="A194" s="4" t="inlineStr">
         <is>
-          <t>235/55R18</t>
+          <t>235/50R18</t>
         </is>
       </c>
       <c r="B194" s="4" t="inlineStr">
@@ -6708,14 +6708,14 @@
       </c>
       <c r="C194" s="4" t="inlineStr">
         <is>
-          <t>HK235/55R18</t>
+          <t>HK235/50R18</t>
         </is>
       </c>
       <c r="D194" s="5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E194" s="5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F194" s="5">
         <v>0</v>
@@ -6724,13 +6724,13 @@
         <v>0</v>
       </c>
       <c r="H194" s="6">
-        <v>480</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="195">
       <c r="A195" s="4" t="inlineStr">
         <is>
-          <t>235/55R19</t>
+          <t>235/50R19</t>
         </is>
       </c>
       <c r="B195" s="4" t="inlineStr">
@@ -6740,14 +6740,14 @@
       </c>
       <c r="C195" s="4" t="inlineStr">
         <is>
-          <t>GD235/55R19</t>
+          <t>GD235/50R19</t>
         </is>
       </c>
       <c r="D195" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E195" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F195" s="5">
         <v>0</v>
@@ -6756,55 +6756,55 @@
         <v>0</v>
       </c>
       <c r="H195" s="6">
-        <v>750</v>
+        <v>800</v>
       </c>
     </row>
     <row outlineLevel="0" r="196">
       <c r="A196" s="4" t="inlineStr">
         <is>
-          <t>235/55R19</t>
+          <t>235/50R20</t>
         </is>
       </c>
       <c r="B196" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C196" s="4" t="inlineStr">
         <is>
-          <t>HK235/55R19</t>
+          <t>GD235/50R20</t>
         </is>
       </c>
       <c r="D196" s="5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E196" s="5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F196" s="5">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G196" s="5">
         <v>0</v>
       </c>
       <c r="H196" s="6">
-        <v>630</v>
+        <v>1180</v>
       </c>
     </row>
     <row outlineLevel="0" r="197">
       <c r="A197" s="4" t="inlineStr">
         <is>
-          <t>235/55R19</t>
+          <t>235/55R17</t>
         </is>
       </c>
       <c r="B197" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C197" s="4" t="inlineStr">
         <is>
-          <t>LF235/55R19</t>
+          <t>BR235/55R17</t>
         </is>
       </c>
       <c r="D197" s="5">
@@ -6820,30 +6820,30 @@
         <v>0</v>
       </c>
       <c r="H197" s="6">
-        <v>500</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="198">
       <c r="A198" s="4" t="inlineStr">
         <is>
-          <t>235/55R19</t>
+          <t>235/55R18</t>
         </is>
       </c>
       <c r="B198" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C198" s="4" t="inlineStr">
         <is>
-          <t>NX235/55R19</t>
+          <t>HK235/55R18</t>
         </is>
       </c>
       <c r="D198" s="5">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E198" s="5">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F198" s="5">
         <v>0</v>
@@ -6852,7 +6852,7 @@
         <v>0</v>
       </c>
       <c r="H198" s="6">
-        <v>600</v>
+        <v>480</v>
       </c>
     </row>
     <row outlineLevel="0" r="199">
@@ -6863,34 +6863,34 @@
       </c>
       <c r="B199" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C199" s="4" t="inlineStr">
         <is>
-          <t>RD235/55R19</t>
+          <t>GD235/55R19</t>
         </is>
       </c>
       <c r="D199" s="5">
         <v>2</v>
       </c>
       <c r="E199" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F199" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G199" s="5">
         <v>0</v>
       </c>
       <c r="H199" s="6">
-        <v>500</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="200">
       <c r="A200" s="4" t="inlineStr">
         <is>
-          <t>235/60R16</t>
+          <t>235/55R19</t>
         </is>
       </c>
       <c r="B200" s="4" t="inlineStr">
@@ -6900,14 +6900,14 @@
       </c>
       <c r="C200" s="4" t="inlineStr">
         <is>
-          <t>HK235/60R16</t>
+          <t>HK235/55R19</t>
         </is>
       </c>
       <c r="D200" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E200" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F200" s="5">
         <v>0</v>
@@ -6916,33 +6916,33 @@
         <v>0</v>
       </c>
       <c r="H200" s="6">
-        <v>430</v>
+        <v>630</v>
       </c>
     </row>
     <row outlineLevel="0" r="201">
       <c r="A201" s="4" t="inlineStr">
         <is>
-          <t>235/60R17</t>
+          <t>235/55R19</t>
         </is>
       </c>
       <c r="B201" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C201" s="4" t="inlineStr">
         <is>
-          <t>HK235/60R17</t>
+          <t>LF235/55R19</t>
         </is>
       </c>
       <c r="D201" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E201" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F201" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G201" s="5">
         <v>0</v>
@@ -6954,17 +6954,17 @@
     <row outlineLevel="0" r="202">
       <c r="A202" s="4" t="inlineStr">
         <is>
-          <t>235/60R18</t>
+          <t>235/55R19</t>
         </is>
       </c>
       <c r="B202" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C202" s="4" t="inlineStr">
         <is>
-          <t>GD235/60R18</t>
+          <t>NX235/55R19</t>
         </is>
       </c>
       <c r="D202" s="5">
@@ -6980,62 +6980,62 @@
         <v>0</v>
       </c>
       <c r="H202" s="6">
-        <v>680</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="203">
       <c r="A203" s="4" t="inlineStr">
         <is>
-          <t>235/60R18</t>
+          <t>235/55R19</t>
         </is>
       </c>
       <c r="B203" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C203" s="4" t="inlineStr">
         <is>
-          <t>HK235/60R18</t>
+          <t>RD235/55R19</t>
         </is>
       </c>
       <c r="D203" s="5">
         <v>2</v>
       </c>
       <c r="E203" s="5">
+        <v>0</v>
+      </c>
+      <c r="F203" s="5">
         <v>2</v>
       </c>
-      <c r="F203" s="5">
-        <v>0</v>
-      </c>
       <c r="G203" s="5">
         <v>0</v>
       </c>
       <c r="H203" s="6">
-        <v>550</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="204">
       <c r="A204" s="4" t="inlineStr">
         <is>
-          <t>245/40R17</t>
+          <t>235/60R16</t>
         </is>
       </c>
       <c r="B204" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C204" s="4" t="inlineStr">
         <is>
-          <t>GD245/40R17</t>
+          <t>HK235/60R16</t>
         </is>
       </c>
       <c r="D204" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E204" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F204" s="5">
         <v>0</v>
@@ -7044,62 +7044,62 @@
         <v>0</v>
       </c>
       <c r="H204" s="6">
-        <v>400</v>
+        <v>430</v>
       </c>
     </row>
     <row outlineLevel="0" r="205">
       <c r="A205" s="4" t="inlineStr">
         <is>
-          <t>245/40R18</t>
+          <t>235/60R17</t>
         </is>
       </c>
       <c r="B205" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C205" s="4" t="inlineStr">
         <is>
-          <t>GD245/40R18</t>
+          <t>HK235/60R17</t>
         </is>
       </c>
       <c r="D205" s="5">
         <v>3</v>
       </c>
       <c r="E205" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F205" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G205" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H205" s="6">
-        <v>620</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="206">
       <c r="A206" s="4" t="inlineStr">
         <is>
-          <t>245/40R19</t>
+          <t>235/60R18</t>
         </is>
       </c>
       <c r="B206" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C206" s="4" t="inlineStr">
         <is>
-          <t>HK245/40R19</t>
+          <t>GD235/60R18</t>
         </is>
       </c>
       <c r="D206" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E206" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F206" s="5">
         <v>0</v>
@@ -7108,62 +7108,62 @@
         <v>0</v>
       </c>
       <c r="H206" s="6">
-        <v>750</v>
+        <v>680</v>
       </c>
     </row>
     <row outlineLevel="0" r="207">
       <c r="A207" s="4" t="inlineStr">
         <is>
-          <t>245/40R20</t>
+          <t>235/60R18</t>
         </is>
       </c>
       <c r="B207" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C207" s="4" t="inlineStr">
         <is>
-          <t>CT245/40R20</t>
+          <t>HK235/60R18</t>
         </is>
       </c>
       <c r="D207" s="5">
         <v>2</v>
       </c>
       <c r="E207" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F207" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G207" s="5">
         <v>0</v>
       </c>
       <c r="H207" s="6">
-        <v>1050</v>
+        <v>550</v>
       </c>
     </row>
     <row outlineLevel="0" r="208">
       <c r="A208" s="4" t="inlineStr">
         <is>
-          <t>245/40R20</t>
+          <t>245/40R17</t>
         </is>
       </c>
       <c r="B208" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C208" s="4" t="inlineStr">
         <is>
-          <t>NX245/40R20</t>
+          <t>GD245/40R17</t>
         </is>
       </c>
       <c r="D208" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E208" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F208" s="5">
         <v>0</v>
@@ -7172,30 +7172,30 @@
         <v>0</v>
       </c>
       <c r="H208" s="6">
-        <v>580</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="209">
       <c r="A209" s="4" t="inlineStr">
         <is>
-          <t>245/45R17</t>
+          <t>245/40R18</t>
         </is>
       </c>
       <c r="B209" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C209" s="4" t="inlineStr">
         <is>
-          <t>HK245/45R17</t>
+          <t>GD245/40R18</t>
         </is>
       </c>
       <c r="D209" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E209" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F209" s="5">
         <v>0</v>
@@ -7204,30 +7204,30 @@
         <v>0</v>
       </c>
       <c r="H209" s="6">
-        <v>430</v>
+        <v>620</v>
       </c>
     </row>
     <row outlineLevel="0" r="210">
       <c r="A210" s="4" t="inlineStr">
         <is>
-          <t>245/45R18</t>
+          <t>245/40R19</t>
         </is>
       </c>
       <c r="B210" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C210" s="4" t="inlineStr">
         <is>
-          <t>CT245/45R18</t>
+          <t>HK245/40R19</t>
         </is>
       </c>
       <c r="D210" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E210" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F210" s="5">
         <v>0</v>
@@ -7236,62 +7236,62 @@
         <v>0</v>
       </c>
       <c r="H210" s="6">
-        <v>650</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="211">
       <c r="A211" s="4" t="inlineStr">
         <is>
-          <t>245/45R18</t>
+          <t>245/40R20</t>
         </is>
       </c>
       <c r="B211" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C211" s="4" t="inlineStr">
         <is>
-          <t>GD245/45R18</t>
+          <t>CT245/40R20</t>
         </is>
       </c>
       <c r="D211" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E211" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F211" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G211" s="5">
         <v>0</v>
       </c>
       <c r="H211" s="6">
-        <v>600</v>
+        <v>1050</v>
       </c>
     </row>
     <row outlineLevel="0" r="212">
       <c r="A212" s="4" t="inlineStr">
         <is>
-          <t>245/45R18</t>
+          <t>245/40R20</t>
         </is>
       </c>
       <c r="B212" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C212" s="4" t="inlineStr">
         <is>
-          <t>HK245/45R18</t>
+          <t>NX245/40R20</t>
         </is>
       </c>
       <c r="D212" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E212" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F212" s="5">
         <v>0</v>
@@ -7300,23 +7300,23 @@
         <v>0</v>
       </c>
       <c r="H212" s="6">
-        <v>500</v>
+        <v>580</v>
       </c>
     </row>
     <row outlineLevel="0" r="213">
       <c r="A213" s="4" t="inlineStr">
         <is>
-          <t>245/45R18RF</t>
+          <t>245/45R17</t>
         </is>
       </c>
       <c r="B213" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C213" s="4" t="inlineStr">
         <is>
-          <t>GD245/45R18RF</t>
+          <t>HK245/45R17</t>
         </is>
       </c>
       <c r="D213" s="5">
@@ -7332,30 +7332,30 @@
         <v>0</v>
       </c>
       <c r="H213" s="6">
-        <v>720</v>
+        <v>430</v>
       </c>
     </row>
     <row outlineLevel="0" r="214">
       <c r="A214" s="4" t="inlineStr">
         <is>
-          <t>245/45R19</t>
+          <t>245/45R18</t>
         </is>
       </c>
       <c r="B214" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C214" s="4" t="inlineStr">
         <is>
-          <t>BR245/45R19</t>
+          <t>CT245/45R18</t>
         </is>
       </c>
       <c r="D214" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E214" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F214" s="5">
         <v>0</v>
@@ -7364,45 +7364,45 @@
         <v>0</v>
       </c>
       <c r="H214" s="6">
-        <v>790</v>
+        <v>650</v>
       </c>
     </row>
     <row outlineLevel="0" r="215">
       <c r="A215" s="4" t="inlineStr">
         <is>
-          <t>245/45R19</t>
+          <t>245/45R18</t>
         </is>
       </c>
       <c r="B215" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C215" s="4" t="inlineStr">
         <is>
-          <t>RD245/45R19</t>
+          <t>GD245/45R18</t>
         </is>
       </c>
       <c r="D215" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E215" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F215" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G215" s="5">
         <v>0</v>
       </c>
       <c r="H215" s="6">
-        <v>450</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="216">
       <c r="A216" s="4" t="inlineStr">
         <is>
-          <t>245/45R20</t>
+          <t>245/45R18</t>
         </is>
       </c>
       <c r="B216" s="4" t="inlineStr">
@@ -7412,78 +7412,78 @@
       </c>
       <c r="C216" s="4" t="inlineStr">
         <is>
-          <t>HK245/45R20</t>
+          <t>HK245/45R18</t>
         </is>
       </c>
       <c r="D216" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E216" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F216" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G216" s="5">
         <v>0</v>
       </c>
       <c r="H216" s="6">
-        <v>750</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="217">
       <c r="A217" s="4" t="inlineStr">
         <is>
-          <t>245/65R17</t>
+          <t>245/45R18RF</t>
         </is>
       </c>
       <c r="B217" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C217" s="4" t="inlineStr">
         <is>
-          <t>NX245/65R17</t>
+          <t>GD245/45R18RF</t>
         </is>
       </c>
       <c r="D217" s="5">
         <v>4</v>
       </c>
       <c r="E217" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F217" s="5">
         <v>0</v>
       </c>
       <c r="G217" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H217" s="6">
-        <v>600</v>
+        <v>720</v>
       </c>
     </row>
     <row outlineLevel="0" r="218">
       <c r="A218" s="4" t="inlineStr">
         <is>
-          <t>245/70R16</t>
+          <t>245/45R19</t>
         </is>
       </c>
       <c r="B218" s="4" t="inlineStr">
         <is>
-          <t>LASSA</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C218" s="4" t="inlineStr">
         <is>
-          <t>LS245/70R16</t>
+          <t>BR245/45R19</t>
         </is>
       </c>
       <c r="D218" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E218" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F218" s="5">
         <v>0</v>
@@ -7492,119 +7492,119 @@
         <v>0</v>
       </c>
       <c r="H218" s="6">
-        <v>500</v>
+        <v>790</v>
       </c>
     </row>
     <row outlineLevel="0" r="219">
       <c r="A219" s="4" t="inlineStr">
         <is>
-          <t>255/35R19</t>
+          <t>245/45R19</t>
         </is>
       </c>
       <c r="B219" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C219" s="4" t="inlineStr">
         <is>
-          <t>DL255/35R19</t>
+          <t>RD245/45R19</t>
         </is>
       </c>
       <c r="D219" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E219" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F219" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G219" s="5">
         <v>0</v>
       </c>
       <c r="H219" s="6">
-        <v>700</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="220">
       <c r="A220" s="4" t="inlineStr">
         <is>
-          <t>255/35R19RF</t>
+          <t>245/45R20</t>
         </is>
       </c>
       <c r="B220" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C220" s="4" t="inlineStr">
         <is>
-          <t>CT255/35R19RF</t>
+          <t>HK245/45R20</t>
         </is>
       </c>
       <c r="D220" s="5">
         <v>2</v>
       </c>
       <c r="E220" s="5">
+        <v>0</v>
+      </c>
+      <c r="F220" s="5">
         <v>2</v>
       </c>
-      <c r="F220" s="5">
-        <v>0</v>
-      </c>
       <c r="G220" s="5">
         <v>0</v>
       </c>
       <c r="H220" s="6">
-        <v>1150</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="221">
       <c r="A221" s="4" t="inlineStr">
         <is>
-          <t>255/35R19RF</t>
+          <t>245/65R17</t>
         </is>
       </c>
       <c r="B221" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C221" s="4" t="inlineStr">
         <is>
-          <t>GD255/35R19RF</t>
+          <t>NX245/65R17</t>
         </is>
       </c>
       <c r="D221" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E221" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F221" s="5">
         <v>0</v>
       </c>
       <c r="G221" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H221" s="6">
-        <v>1150</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="222">
       <c r="A222" s="4" t="inlineStr">
         <is>
-          <t>255/45R18</t>
+          <t>245/70R16</t>
         </is>
       </c>
       <c r="B222" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>LASSA</t>
         </is>
       </c>
       <c r="C222" s="4" t="inlineStr">
         <is>
-          <t>HK255/45R18</t>
+          <t>LS245/70R16</t>
         </is>
       </c>
       <c r="D222" s="5">
@@ -7626,39 +7626,39 @@
     <row outlineLevel="0" r="223">
       <c r="A223" s="4" t="inlineStr">
         <is>
-          <t>255/50R19</t>
+          <t>255/35R19</t>
         </is>
       </c>
       <c r="B223" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C223" s="4" t="inlineStr">
         <is>
-          <t>CT255/50R19</t>
+          <t>DL255/35R19</t>
         </is>
       </c>
       <c r="D223" s="5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E223" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F223" s="5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G223" s="5">
         <v>0</v>
       </c>
       <c r="H223" s="6">
-        <v>750</v>
+        <v>700</v>
       </c>
     </row>
     <row outlineLevel="0" r="224">
       <c r="A224" s="4" t="inlineStr">
         <is>
-          <t>255/50R20</t>
+          <t>255/35R19RF</t>
         </is>
       </c>
       <c r="B224" s="4" t="inlineStr">
@@ -7668,78 +7668,78 @@
       </c>
       <c r="C224" s="4" t="inlineStr">
         <is>
-          <t>CT255/50R20</t>
+          <t>CT255/35R19RF</t>
         </is>
       </c>
       <c r="D224" s="5">
         <v>2</v>
       </c>
       <c r="E224" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F224" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G224" s="5">
         <v>0</v>
       </c>
       <c r="H224" s="6">
-        <v>900</v>
+        <v>1150</v>
       </c>
     </row>
     <row outlineLevel="0" r="225">
       <c r="A225" s="4" t="inlineStr">
         <is>
-          <t>255/55R19</t>
+          <t>255/35R19RF</t>
         </is>
       </c>
       <c r="B225" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C225" s="4" t="inlineStr">
         <is>
-          <t>CT255/55R19</t>
+          <t>GD255/35R19RF</t>
         </is>
       </c>
       <c r="D225" s="5">
         <v>1</v>
       </c>
       <c r="E225" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F225" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G225" s="5">
         <v>0</v>
       </c>
       <c r="H225" s="6">
-        <v>750</v>
+        <v>1150</v>
       </c>
     </row>
     <row outlineLevel="0" r="226">
       <c r="A226" s="4" t="inlineStr">
         <is>
-          <t>255/55R19</t>
+          <t>255/40R20</t>
         </is>
       </c>
       <c r="B226" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C226" s="4" t="inlineStr">
         <is>
-          <t>DL255/55R19</t>
+          <t>GD255/40R20</t>
         </is>
       </c>
       <c r="D226" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E226" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F226" s="5">
         <v>0</v>
@@ -7748,23 +7748,23 @@
         <v>0</v>
       </c>
       <c r="H226" s="6">
-        <v>700</v>
+        <v>1080</v>
       </c>
     </row>
     <row outlineLevel="0" r="227">
       <c r="A227" s="4" t="inlineStr">
         <is>
-          <t>255/70R15</t>
+          <t>255/45R18</t>
         </is>
       </c>
       <c r="B227" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C227" s="4" t="inlineStr">
         <is>
-          <t>DL255/70R15</t>
+          <t>HK255/45R18</t>
         </is>
       </c>
       <c r="D227" s="5">
@@ -7780,126 +7780,126 @@
         <v>0</v>
       </c>
       <c r="H227" s="6">
-        <v>550</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="228">
       <c r="A228" s="4" t="inlineStr">
         <is>
-          <t>255/70R16</t>
+          <t>255/50R19</t>
         </is>
       </c>
       <c r="B228" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C228" s="4" t="inlineStr">
         <is>
-          <t>RD255/70R16</t>
+          <t>CT255/50R19</t>
         </is>
       </c>
       <c r="D228" s="5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E228" s="5">
         <v>0</v>
       </c>
       <c r="F228" s="5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G228" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H228" s="6">
-        <v>500</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="229">
       <c r="A229" s="4" t="inlineStr">
         <is>
-          <t>265/35R18</t>
+          <t>255/50R20</t>
         </is>
       </c>
       <c r="B229" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C229" s="4" t="inlineStr">
         <is>
-          <t>GD265/35R18</t>
+          <t>CT255/50R20</t>
         </is>
       </c>
       <c r="D229" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E229" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F229" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G229" s="5">
         <v>0</v>
       </c>
       <c r="H229" s="6">
-        <v>700</v>
+        <v>900</v>
       </c>
     </row>
     <row outlineLevel="0" r="230">
       <c r="A230" s="4" t="inlineStr">
         <is>
-          <t>265/50R20</t>
+          <t>255/55R19</t>
         </is>
       </c>
       <c r="B230" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C230" s="4" t="inlineStr">
         <is>
-          <t>GD265/50R20</t>
+          <t>CT255/55R19</t>
         </is>
       </c>
       <c r="D230" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E230" s="5">
         <v>0</v>
       </c>
       <c r="F230" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G230" s="5">
         <v>0</v>
       </c>
       <c r="H230" s="6">
-        <v>1150</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="231">
       <c r="A231" s="4" t="inlineStr">
         <is>
-          <t>265/65R17</t>
+          <t>255/55R19</t>
         </is>
       </c>
       <c r="B231" s="4" t="inlineStr">
         <is>
-          <t>LASSA</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C231" s="4" t="inlineStr">
         <is>
-          <t>LS265/65R17</t>
+          <t>DL255/55R19</t>
         </is>
       </c>
       <c r="D231" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E231" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F231" s="5">
         <v>0</v>
@@ -7908,109 +7908,109 @@
         <v>0</v>
       </c>
       <c r="H231" s="6">
-        <v>650</v>
+        <v>700</v>
       </c>
     </row>
     <row outlineLevel="0" r="232">
       <c r="A232" s="4" t="inlineStr">
         <is>
-          <t>275/35R19RF</t>
+          <t>255/70R15</t>
         </is>
       </c>
       <c r="B232" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C232" s="4" t="inlineStr">
         <is>
-          <t>GD275/35R19RF</t>
+          <t>DL255/70R15</t>
         </is>
       </c>
       <c r="D232" s="5">
         <v>2</v>
       </c>
       <c r="E232" s="5">
+        <v>0</v>
+      </c>
+      <c r="F232" s="5">
+        <v>0</v>
+      </c>
+      <c r="G232" s="5">
         <v>2</v>
       </c>
-      <c r="F232" s="5">
-        <v>0</v>
-      </c>
-      <c r="G232" s="5">
-        <v>0</v>
-      </c>
       <c r="H232" s="6">
-        <v>1300</v>
+        <v>550</v>
       </c>
     </row>
     <row outlineLevel="0" r="233">
       <c r="A233" s="4" t="inlineStr">
         <is>
-          <t>275/35R20</t>
+          <t>255/70R16</t>
         </is>
       </c>
       <c r="B233" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C233" s="4" t="inlineStr">
         <is>
-          <t>CT275/35R20</t>
+          <t>RD255/70R16</t>
         </is>
       </c>
       <c r="D233" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E233" s="5">
         <v>0</v>
       </c>
       <c r="F233" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G233" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H233" s="6">
-        <v>980</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="234">
       <c r="A234" s="4" t="inlineStr">
         <is>
-          <t>275/40R20</t>
+          <t>265/35R18</t>
         </is>
       </c>
       <c r="B234" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C234" s="4" t="inlineStr">
         <is>
-          <t>HK275/40R20</t>
+          <t>GD265/35R18</t>
         </is>
       </c>
       <c r="D234" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E234" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F234" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G234" s="5">
         <v>0</v>
       </c>
       <c r="H234" s="6">
-        <v>770</v>
+        <v>700</v>
       </c>
     </row>
     <row outlineLevel="0" r="235">
       <c r="A235" s="4" t="inlineStr">
         <is>
-          <t>275/40R22</t>
+          <t>265/50R20</t>
         </is>
       </c>
       <c r="B235" s="4" t="inlineStr">
@@ -8020,39 +8020,39 @@
       </c>
       <c r="C235" s="4" t="inlineStr">
         <is>
-          <t>GD275/40R22</t>
+          <t>GD265/50R20</t>
         </is>
       </c>
       <c r="D235" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E235" s="5">
         <v>0</v>
       </c>
       <c r="F235" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G235" s="5">
         <v>0</v>
       </c>
       <c r="H235" s="6">
-        <v>1200</v>
+        <v>1150</v>
       </c>
     </row>
     <row outlineLevel="0" r="236">
       <c r="A236" s="4" t="inlineStr">
         <is>
-          <t>275/45R20</t>
+          <t>265/65R17</t>
         </is>
       </c>
       <c r="B236" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C236" s="4" t="inlineStr">
         <is>
-          <t>CT275/45R20</t>
+          <t>GD265/65R17</t>
         </is>
       </c>
       <c r="D236" s="5">
@@ -8068,62 +8068,62 @@
         <v>0</v>
       </c>
       <c r="H236" s="6">
-        <v>900</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="237">
       <c r="A237" s="4" t="inlineStr">
         <is>
-          <t>275/50R21</t>
+          <t>265/65R17</t>
         </is>
       </c>
       <c r="B237" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>LASSA</t>
         </is>
       </c>
       <c r="C237" s="4" t="inlineStr">
         <is>
-          <t>GD275/50R21</t>
+          <t>LS265/65R17</t>
         </is>
       </c>
       <c r="D237" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E237" s="5">
         <v>0</v>
       </c>
       <c r="F237" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G237" s="5">
         <v>0</v>
       </c>
       <c r="H237" s="6">
-        <v>1300</v>
+        <v>650</v>
       </c>
     </row>
     <row outlineLevel="0" r="238">
       <c r="A238" s="4" t="inlineStr">
         <is>
-          <t>285/35R22</t>
+          <t>275/35R19RF</t>
         </is>
       </c>
       <c r="B238" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C238" s="4" t="inlineStr">
         <is>
-          <t>CT285/35R22</t>
+          <t>GD275/35R19RF</t>
         </is>
       </c>
       <c r="D238" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E238" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F238" s="5">
         <v>0</v>
@@ -8132,13 +8132,13 @@
         <v>0</v>
       </c>
       <c r="H238" s="6">
-        <v>1600</v>
+        <v>1300</v>
       </c>
     </row>
     <row outlineLevel="0" r="239">
       <c r="A239" s="4" t="inlineStr">
         <is>
-          <t>295/35R21</t>
+          <t>275/35R20</t>
         </is>
       </c>
       <c r="B239" s="4" t="inlineStr">
@@ -8148,7 +8148,7 @@
       </c>
       <c r="C239" s="4" t="inlineStr">
         <is>
-          <t>CT295/35R21</t>
+          <t>CT275/35R20</t>
         </is>
       </c>
       <c r="D239" s="5">
@@ -8164,55 +8164,55 @@
         <v>0</v>
       </c>
       <c r="H239" s="6">
-        <v>1150</v>
+        <v>980</v>
       </c>
     </row>
     <row outlineLevel="0" r="240">
       <c r="A240" s="4" t="inlineStr">
         <is>
-          <t>295/35R21</t>
+          <t>275/40R20</t>
         </is>
       </c>
       <c r="B240" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C240" s="4" t="inlineStr">
         <is>
-          <t>GD295/35R21</t>
+          <t>HK275/40R20</t>
         </is>
       </c>
       <c r="D240" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E240" s="5">
         <v>0</v>
       </c>
       <c r="F240" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G240" s="5">
         <v>0</v>
       </c>
       <c r="H240" s="6">
-        <v>980</v>
+        <v>770</v>
       </c>
     </row>
     <row outlineLevel="0" r="241">
       <c r="A241" s="4" t="inlineStr">
         <is>
-          <t>315/30R22</t>
+          <t>275/40R22</t>
         </is>
       </c>
       <c r="B241" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C241" s="4" t="inlineStr">
         <is>
-          <t>CT315/30R22</t>
+          <t>GD275/40R22</t>
         </is>
       </c>
       <c r="D241" s="5">
@@ -8228,38 +8228,262 @@
         <v>0</v>
       </c>
       <c r="H241" s="6">
-        <v>1700</v>
+        <v>1200</v>
       </c>
     </row>
     <row outlineLevel="0" r="242">
       <c r="A242" s="4" t="inlineStr">
         <is>
+          <t>275/45R20</t>
+        </is>
+      </c>
+      <c r="B242" s="4" t="inlineStr">
+        <is>
+          <t>CONTINENTAL</t>
+        </is>
+      </c>
+      <c r="C242" s="4" t="inlineStr">
+        <is>
+          <t>CT275/45R20</t>
+        </is>
+      </c>
+      <c r="D242" s="5">
+        <v>0</v>
+      </c>
+      <c r="E242" s="5">
+        <v>0</v>
+      </c>
+      <c r="F242" s="5">
+        <v>0</v>
+      </c>
+      <c r="G242" s="5">
+        <v>0</v>
+      </c>
+      <c r="H242" s="6">
+        <v>900</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="243">
+      <c r="A243" s="4" t="inlineStr">
+        <is>
+          <t>275/45R21</t>
+        </is>
+      </c>
+      <c r="B243" s="4" t="inlineStr">
+        <is>
+          <t>GOODYEAR</t>
+        </is>
+      </c>
+      <c r="C243" s="4" t="inlineStr">
+        <is>
+          <t>GD275/45R21</t>
+        </is>
+      </c>
+      <c r="D243" s="5">
+        <v>0</v>
+      </c>
+      <c r="E243" s="5">
+        <v>0</v>
+      </c>
+      <c r="F243" s="5">
+        <v>0</v>
+      </c>
+      <c r="G243" s="5">
+        <v>0</v>
+      </c>
+      <c r="H243" s="6">
+        <v>1100</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="244">
+      <c r="A244" s="4" t="inlineStr">
+        <is>
+          <t>275/50R21</t>
+        </is>
+      </c>
+      <c r="B244" s="4" t="inlineStr">
+        <is>
+          <t>GOODYEAR</t>
+        </is>
+      </c>
+      <c r="C244" s="4" t="inlineStr">
+        <is>
+          <t>GD275/50R21</t>
+        </is>
+      </c>
+      <c r="D244" s="5">
+        <v>2</v>
+      </c>
+      <c r="E244" s="5">
+        <v>0</v>
+      </c>
+      <c r="F244" s="5">
+        <v>2</v>
+      </c>
+      <c r="G244" s="5">
+        <v>0</v>
+      </c>
+      <c r="H244" s="6">
+        <v>1300</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="245">
+      <c r="A245" s="4" t="inlineStr">
+        <is>
+          <t>285/35R22</t>
+        </is>
+      </c>
+      <c r="B245" s="4" t="inlineStr">
+        <is>
+          <t>CONTINENTAL</t>
+        </is>
+      </c>
+      <c r="C245" s="4" t="inlineStr">
+        <is>
+          <t>CT285/35R22</t>
+        </is>
+      </c>
+      <c r="D245" s="5">
+        <v>0</v>
+      </c>
+      <c r="E245" s="5">
+        <v>0</v>
+      </c>
+      <c r="F245" s="5">
+        <v>0</v>
+      </c>
+      <c r="G245" s="5">
+        <v>0</v>
+      </c>
+      <c r="H245" s="6">
+        <v>1600</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="246">
+      <c r="A246" s="4" t="inlineStr">
+        <is>
+          <t>295/35R21</t>
+        </is>
+      </c>
+      <c r="B246" s="4" t="inlineStr">
+        <is>
+          <t>CONTINENTAL</t>
+        </is>
+      </c>
+      <c r="C246" s="4" t="inlineStr">
+        <is>
+          <t>CT295/35R21</t>
+        </is>
+      </c>
+      <c r="D246" s="5">
+        <v>2</v>
+      </c>
+      <c r="E246" s="5">
+        <v>0</v>
+      </c>
+      <c r="F246" s="5">
+        <v>2</v>
+      </c>
+      <c r="G246" s="5">
+        <v>0</v>
+      </c>
+      <c r="H246" s="6">
+        <v>1150</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="247">
+      <c r="A247" s="4" t="inlineStr">
+        <is>
+          <t>295/35R21</t>
+        </is>
+      </c>
+      <c r="B247" s="4" t="inlineStr">
+        <is>
+          <t>GOODYEAR</t>
+        </is>
+      </c>
+      <c r="C247" s="4" t="inlineStr">
+        <is>
+          <t>GD295/35R21</t>
+        </is>
+      </c>
+      <c r="D247" s="5">
+        <v>3</v>
+      </c>
+      <c r="E247" s="5">
+        <v>0</v>
+      </c>
+      <c r="F247" s="5">
+        <v>3</v>
+      </c>
+      <c r="G247" s="5">
+        <v>0</v>
+      </c>
+      <c r="H247" s="6">
+        <v>980</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="248">
+      <c r="A248" s="4" t="inlineStr">
+        <is>
+          <t>315/30R22</t>
+        </is>
+      </c>
+      <c r="B248" s="4" t="inlineStr">
+        <is>
+          <t>CONTINENTAL</t>
+        </is>
+      </c>
+      <c r="C248" s="4" t="inlineStr">
+        <is>
+          <t>CT315/30R22</t>
+        </is>
+      </c>
+      <c r="D248" s="5">
+        <v>0</v>
+      </c>
+      <c r="E248" s="5">
+        <v>0</v>
+      </c>
+      <c r="F248" s="5">
+        <v>0</v>
+      </c>
+      <c r="G248" s="5">
+        <v>0</v>
+      </c>
+      <c r="H248" s="6">
+        <v>1700</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="249">
+      <c r="A249" s="4" t="inlineStr">
+        <is>
           <t>500R12</t>
         </is>
       </c>
-      <c r="B242" s="4" t="inlineStr">
+      <c r="B249" s="4" t="inlineStr">
         <is>
           <t>RADIAL</t>
         </is>
       </c>
-      <c r="C242" s="4" t="inlineStr">
+      <c r="C249" s="4" t="inlineStr">
         <is>
           <t>RD500R12</t>
         </is>
       </c>
-      <c r="D242" s="5">
+      <c r="D249" s="5">
         <v>3</v>
       </c>
-      <c r="E242" s="5">
+      <c r="E249" s="5">
         <v>3</v>
       </c>
-      <c r="F242" s="5">
-        <v>0</v>
-      </c>
-      <c r="G242" s="5">
-        <v>0</v>
-      </c>
-      <c r="H242" s="6">
+      <c r="F249" s="5">
+        <v>0</v>
+      </c>
+      <c r="G249" s="5">
+        <v>0</v>
+      </c>
+      <c r="H249" s="6">
         <v>300</v>
       </c>
     </row>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -600,7 +600,7 @@
         </is>
       </c>
       <c r="D3" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E3" s="5">
         <v>1</v>
@@ -609,7 +609,7 @@
         <v>0</v>
       </c>
       <c r="G3" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H3" s="6">
         <v>180</v>
@@ -792,10 +792,10 @@
         </is>
       </c>
       <c r="D9" s="5">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E9" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F9" s="5">
         <v>31</v>
@@ -1080,10 +1080,10 @@
         </is>
       </c>
       <c r="D18" s="5">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E18" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F18" s="5">
         <v>5</v>
@@ -1304,13 +1304,13 @@
         </is>
       </c>
       <c r="D25" s="5">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E25" s="5">
         <v>6</v>
       </c>
       <c r="F25" s="5">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="G25" s="5">
         <v>10</v>
@@ -1336,7 +1336,7 @@
         </is>
       </c>
       <c r="D26" s="5">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E26" s="5">
         <v>53</v>
@@ -1345,7 +1345,7 @@
         <v>0</v>
       </c>
       <c r="G26" s="5">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H26" s="6">
         <v>180</v>
@@ -2232,16 +2232,16 @@
         </is>
       </c>
       <c r="D54" s="5">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="E54" s="5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F54" s="5">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G54" s="5">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H54" s="6">
         <v>270</v>
@@ -2584,7 +2584,7 @@
         </is>
       </c>
       <c r="D65" s="5">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E65" s="5">
         <v>4</v>
@@ -2593,7 +2593,7 @@
         <v>14</v>
       </c>
       <c r="G65" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H65" s="6">
         <v>260</v>
@@ -2616,10 +2616,10 @@
         </is>
       </c>
       <c r="D66" s="5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E66" s="5">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F66" s="5">
         <v>0</v>
@@ -2712,10 +2712,10 @@
         </is>
       </c>
       <c r="D69" s="5">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E69" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F69" s="5">
         <v>5</v>
@@ -2872,13 +2872,13 @@
         </is>
       </c>
       <c r="D74" s="5">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E74" s="5">
         <v>4</v>
       </c>
       <c r="F74" s="5">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G74" s="5">
         <v>4</v>
@@ -3672,7 +3672,7 @@
         </is>
       </c>
       <c r="D99" s="5">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E99" s="5">
         <v>7</v>
@@ -3681,7 +3681,7 @@
         <v>13</v>
       </c>
       <c r="G99" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H99" s="6">
         <v>250</v>
@@ -4440,7 +4440,7 @@
         </is>
       </c>
       <c r="D123" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E123" s="5">
         <v>0</v>
@@ -4449,7 +4449,7 @@
         <v>0</v>
       </c>
       <c r="G123" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H123" s="6">
         <v>300</v>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -496,7 +496,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H249"/>
+  <dimension ref="A1:H251"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col customWidth="true" min="1" max="1" width="13.8359375"/>
@@ -1560,10 +1560,10 @@
         </is>
       </c>
       <c r="D33" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E33" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F33" s="5">
         <v>0</v>
@@ -1720,7 +1720,7 @@
         </is>
       </c>
       <c r="D38" s="5">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E38" s="5">
         <v>4</v>
@@ -1729,7 +1729,7 @@
         <v>29</v>
       </c>
       <c r="G38" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H38" s="6">
         <v>340</v>
@@ -2232,16 +2232,16 @@
         </is>
       </c>
       <c r="D54" s="5">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="E54" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F54" s="5">
         <v>133</v>
       </c>
       <c r="G54" s="5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H54" s="6">
         <v>270</v>
@@ -2392,10 +2392,10 @@
         </is>
       </c>
       <c r="D59" s="5">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="E59" s="5">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="F59" s="5">
         <v>0</v>
@@ -2424,10 +2424,10 @@
         </is>
       </c>
       <c r="D60" s="5">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E60" s="5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F60" s="5">
         <v>0</v>
@@ -2506,24 +2506,24 @@
     <row outlineLevel="0" r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>195/50R15</t>
+          <t>185R14C</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>AMINE</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>AM195/50R15</t>
+          <t>RD185R14C</t>
         </is>
       </c>
       <c r="D63" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E63" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F63" s="5">
         <v>0</v>
@@ -2532,7 +2532,7 @@
         <v>0</v>
       </c>
       <c r="H63" s="6">
-        <v>220</v>
+        <v>270</v>
       </c>
     </row>
     <row outlineLevel="0" r="64">
@@ -2543,19 +2543,19 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>AMINE</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>GD195/50R15</t>
+          <t>AM195/50R15</t>
         </is>
       </c>
       <c r="D64" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E64" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F64" s="5">
         <v>0</v>
@@ -2564,7 +2564,7 @@
         <v>0</v>
       </c>
       <c r="H64" s="6">
-        <v>290</v>
+        <v>220</v>
       </c>
     </row>
     <row outlineLevel="0" r="65">
@@ -2575,28 +2575,28 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>SEMPERIT</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>SP195/50R15</t>
+          <t>GD195/50R15</t>
         </is>
       </c>
       <c r="D65" s="5">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="E65" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F65" s="5">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G65" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H65" s="6">
-        <v>260</v>
+        <v>290</v>
       </c>
     </row>
     <row outlineLevel="0" r="66">
@@ -2607,83 +2607,83 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>WESTLAKE</t>
+          <t>SEMPERIT</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>WL195/50R15</t>
+          <t>SP195/50R15</t>
         </is>
       </c>
       <c r="D66" s="5">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="E66" s="5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F66" s="5">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G66" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H66" s="6">
-        <v>240</v>
+        <v>260</v>
       </c>
     </row>
     <row outlineLevel="0" r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>195/50R16</t>
+          <t>195/50R15</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>WESTLAKE</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>GD195/50R16</t>
+          <t>WL195/50R15</t>
         </is>
       </c>
       <c r="D67" s="5">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E67" s="5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F67" s="5">
         <v>0</v>
       </c>
       <c r="G67" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H67" s="6">
-        <v>350</v>
+        <v>240</v>
       </c>
     </row>
     <row outlineLevel="0" r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>195/55R16</t>
+          <t>195/50R16</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>AMINE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>AM195/55R16</t>
+          <t>GD195/50R16</t>
         </is>
       </c>
       <c r="D68" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E68" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F68" s="5">
         <v>0</v>
@@ -2692,7 +2692,7 @@
         <v>0</v>
       </c>
       <c r="H68" s="6">
-        <v>270</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="69">
@@ -2703,28 +2703,28 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>AMINE</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>GD195/55R16</t>
+          <t>AM195/55R16</t>
         </is>
       </c>
       <c r="D69" s="5">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E69" s="5">
         <v>0</v>
       </c>
       <c r="F69" s="5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G69" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H69" s="6">
-        <v>350</v>
+        <v>270</v>
       </c>
     </row>
     <row outlineLevel="0" r="70">
@@ -2735,28 +2735,28 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>HK195/55R16</t>
+          <t>GD195/55R16</t>
         </is>
       </c>
       <c r="D70" s="5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E70" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F70" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G70" s="5">
         <v>4</v>
       </c>
       <c r="H70" s="6">
-        <v>300</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="71">
@@ -2767,28 +2767,28 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>LASSA</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>LS195/55R16</t>
+          <t>HK195/55R16</t>
         </is>
       </c>
       <c r="D71" s="5">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E71" s="5">
         <v>3</v>
       </c>
       <c r="F71" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G71" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H71" s="6">
-        <v>280</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="72">
@@ -2799,19 +2799,19 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>LASSA</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>NX195/55R16</t>
+          <t>LS195/55R16</t>
         </is>
       </c>
       <c r="D72" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E72" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F72" s="5">
         <v>0</v>
@@ -2820,7 +2820,7 @@
         <v>0</v>
       </c>
       <c r="H72" s="6">
-        <v>300</v>
+        <v>280</v>
       </c>
     </row>
     <row outlineLevel="0" r="73">
@@ -2831,92 +2831,92 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>RD195/55R16</t>
+          <t>NX195/55R16</t>
         </is>
       </c>
       <c r="D73" s="5">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E73" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F73" s="5">
         <v>0</v>
       </c>
       <c r="G73" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H73" s="6">
-        <v>250</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>195/60R16</t>
+          <t>195/55R16</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>GD195/60R16</t>
+          <t>RD195/55R16</t>
         </is>
       </c>
       <c r="D74" s="5">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="E74" s="5">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F74" s="5">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="G74" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H74" s="6">
-        <v>360</v>
+        <v>250</v>
       </c>
     </row>
     <row outlineLevel="0" r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>195/65R15</t>
+          <t>195/60R16</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>DOUBLESTAR</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>DS195/65R15</t>
+          <t>GD195/60R16</t>
         </is>
       </c>
       <c r="D75" s="5">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="E75" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F75" s="5">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="G75" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H75" s="6">
-        <v>230</v>
+        <v>360</v>
       </c>
     </row>
     <row outlineLevel="0" r="76">
@@ -2927,22 +2927,22 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>GOODRIDE</t>
+          <t>DOUBLESTAR</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>GR195/65R15</t>
+          <t>DS195/65R15</t>
         </is>
       </c>
       <c r="D76" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E76" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F76" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G76" s="5">
         <v>0</v>
@@ -2959,28 +2959,28 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>GOODRIDE</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>GD195/65R15</t>
+          <t>GR195/65R15</t>
         </is>
       </c>
       <c r="D77" s="5">
-        <v>60</v>
+        <v>4</v>
       </c>
       <c r="E77" s="5">
         <v>4</v>
       </c>
       <c r="F77" s="5">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="G77" s="5">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H77" s="6">
-        <v>275</v>
+        <v>230</v>
       </c>
     </row>
     <row outlineLevel="0" r="78">
@@ -2991,28 +2991,28 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>HK195/65R15</t>
+          <t>GD195/65R15</t>
         </is>
       </c>
       <c r="D78" s="5">
-        <v>9</v>
+        <v>60</v>
       </c>
       <c r="E78" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F78" s="5">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="G78" s="5">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H78" s="6">
-        <v>260</v>
+        <v>275</v>
       </c>
     </row>
     <row outlineLevel="0" r="79">
@@ -3023,28 +3023,28 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>LASSA</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>LS195/65R15</t>
+          <t>HK195/65R15</t>
         </is>
       </c>
       <c r="D79" s="5">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E79" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F79" s="5">
         <v>0</v>
       </c>
       <c r="G79" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H79" s="6">
-        <v>250</v>
+        <v>260</v>
       </c>
     </row>
     <row outlineLevel="0" r="80">
@@ -3055,19 +3055,19 @@
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>LASSA</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>NX195/65R15</t>
+          <t>LS195/65R15</t>
         </is>
       </c>
       <c r="D80" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E80" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F80" s="5">
         <v>0</v>
@@ -3076,7 +3076,7 @@
         <v>0</v>
       </c>
       <c r="H80" s="6">
-        <v>230</v>
+        <v>250</v>
       </c>
     </row>
     <row outlineLevel="0" r="81">
@@ -3087,25 +3087,25 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>RD195/65R15</t>
+          <t>NX195/65R15</t>
         </is>
       </c>
       <c r="D81" s="5">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E81" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F81" s="5">
         <v>0</v>
       </c>
       <c r="G81" s="5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H81" s="6">
         <v>230</v>
@@ -3119,60 +3119,60 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>SEMPERIT</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>SP195/65R15</t>
+          <t>RD195/65R15</t>
         </is>
       </c>
       <c r="D82" s="5">
-        <v>87</v>
+        <v>11</v>
       </c>
       <c r="E82" s="5">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F82" s="5">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="G82" s="5">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="H82" s="6">
-        <v>250</v>
+        <v>230</v>
       </c>
     </row>
     <row outlineLevel="0" r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>195/70R15C</t>
+          <t>195/65R15</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>DAYTON</t>
+          <t>SEMPERIT</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>DT195/70R15C</t>
+          <t>SP195/65R15</t>
         </is>
       </c>
       <c r="D83" s="5">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="E83" s="5">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F83" s="5">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="G83" s="5">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="H83" s="6">
-        <v>280</v>
+        <v>250</v>
       </c>
     </row>
     <row outlineLevel="0" r="84">
@@ -3183,19 +3183,19 @@
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>DAYTON</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>LF195/70R15C</t>
+          <t>DT195/70R15C</t>
         </is>
       </c>
       <c r="D84" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E84" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F84" s="5">
         <v>0</v>
@@ -3204,77 +3204,77 @@
         <v>0</v>
       </c>
       <c r="H84" s="6">
-        <v>300</v>
+        <v>280</v>
       </c>
     </row>
     <row outlineLevel="0" r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>195/75R16C</t>
+          <t>195/70R15C</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>GOODRIDE</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>GR195/75R16C</t>
+          <t>LF195/70R15C</t>
         </is>
       </c>
       <c r="D85" s="5">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E85" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F85" s="5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G85" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H85" s="6">
-        <v>350</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>195R14C</t>
+          <t>195/75R16C</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>GOODRIDE</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>RD195R14C</t>
+          <t>GR195/75R16C</t>
         </is>
       </c>
       <c r="D86" s="5">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E86" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F86" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G86" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H86" s="6">
-        <v>280</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>195R15C</t>
+          <t>195R14C</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
@@ -3284,7 +3284,7 @@
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>RD195R15C</t>
+          <t>RD195R14C</t>
         </is>
       </c>
       <c r="D87" s="5">
@@ -3300,30 +3300,30 @@
         <v>0</v>
       </c>
       <c r="H87" s="6">
-        <v>350</v>
+        <v>280</v>
       </c>
     </row>
     <row outlineLevel="0" r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>205/45R17</t>
+          <t>195R15C</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>CT205/45R17</t>
+          <t>RD195R15C</t>
         </is>
       </c>
       <c r="D88" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E88" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F88" s="5">
         <v>0</v>
@@ -3332,7 +3332,7 @@
         <v>0</v>
       </c>
       <c r="H88" s="6">
-        <v>550</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="89">
@@ -3343,28 +3343,28 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>FULDA</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>FL205/45R17</t>
+          <t>CT205/45R17</t>
         </is>
       </c>
       <c r="D89" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E89" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F89" s="5">
         <v>0</v>
       </c>
       <c r="G89" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H89" s="6">
-        <v>380</v>
+        <v>550</v>
       </c>
     </row>
     <row outlineLevel="0" r="90">
@@ -3375,28 +3375,28 @@
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>GOODRIDE</t>
+          <t>FULDA</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>GR205/45R17</t>
+          <t>FL205/45R17</t>
         </is>
       </c>
       <c r="D90" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E90" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F90" s="5">
         <v>0</v>
       </c>
       <c r="G90" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H90" s="6">
-        <v>300</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="91">
@@ -3407,28 +3407,28 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>GOODRIDE</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>GD205/45R17</t>
+          <t>GR205/45R17</t>
         </is>
       </c>
       <c r="D91" s="5">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="E91" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F91" s="5">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G91" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H91" s="6">
-        <v>450</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="92">
@@ -3439,28 +3439,28 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>NX205/45R17</t>
+          <t>GD205/45R17</t>
         </is>
       </c>
       <c r="D92" s="5">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="E92" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F92" s="5">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G92" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H92" s="6">
-        <v>380</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="93">
@@ -3471,60 +3471,60 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>RD205/45R17</t>
+          <t>NX205/45R17</t>
         </is>
       </c>
       <c r="D93" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E93" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F93" s="5">
         <v>0</v>
       </c>
       <c r="G93" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H93" s="6">
-        <v>300</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>205/50R17</t>
+          <t>205/45R17</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>CT205/50R17</t>
+          <t>RD205/45R17</t>
         </is>
       </c>
       <c r="D94" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E94" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F94" s="5">
         <v>0</v>
       </c>
       <c r="G94" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H94" s="6">
-        <v>450</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="95">
@@ -3535,19 +3535,19 @@
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>GD205/50R17</t>
+          <t>CT205/50R17</t>
         </is>
       </c>
       <c r="D95" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E95" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F95" s="5">
         <v>0</v>
@@ -3556,30 +3556,30 @@
         <v>0</v>
       </c>
       <c r="H95" s="6">
-        <v>480</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="96">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>205/55R16</t>
+          <t>205/50R17</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>AMINE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>AM205/55R16</t>
+          <t>GD205/50R17</t>
         </is>
       </c>
       <c r="D96" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E96" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F96" s="5">
         <v>0</v>
@@ -3588,7 +3588,7 @@
         <v>0</v>
       </c>
       <c r="H96" s="6">
-        <v>240</v>
+        <v>480</v>
       </c>
     </row>
     <row outlineLevel="0" r="97">
@@ -3599,28 +3599,28 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>AMINE</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>BR205/55R16</t>
+          <t>AM205/55R16</t>
         </is>
       </c>
       <c r="D97" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E97" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F97" s="5">
         <v>0</v>
       </c>
       <c r="G97" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H97" s="6">
-        <v>290</v>
+        <v>240</v>
       </c>
     </row>
     <row outlineLevel="0" r="98">
@@ -3631,28 +3631,28 @@
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>DOUBLESTAR</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>DS205/55R16</t>
+          <t>BR205/55R16</t>
         </is>
       </c>
       <c r="D98" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E98" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F98" s="5">
         <v>0</v>
       </c>
       <c r="G98" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H98" s="6">
-        <v>230</v>
+        <v>290</v>
       </c>
     </row>
     <row outlineLevel="0" r="99">
@@ -3663,28 +3663,28 @@
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>FULDA</t>
+          <t>DOUBLESTAR</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>FL205/55R16</t>
+          <t>DS205/55R16</t>
         </is>
       </c>
       <c r="D99" s="5">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="E99" s="5">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F99" s="5">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G99" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H99" s="6">
-        <v>250</v>
+        <v>230</v>
       </c>
     </row>
     <row outlineLevel="0" r="100">
@@ -3695,25 +3695,25 @@
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>GOODRIDE</t>
+          <t>FULDA</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>GR205/55R16</t>
+          <t>FL205/55R16</t>
         </is>
       </c>
       <c r="D100" s="5">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="E100" s="5">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F100" s="5">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G100" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H100" s="6">
         <v>250</v>
@@ -3727,28 +3727,28 @@
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>GOODRIDE</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>GD205/55R16</t>
+          <t>GR205/55R16</t>
         </is>
       </c>
       <c r="D101" s="5">
         <v>1</v>
       </c>
       <c r="E101" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F101" s="5">
         <v>0</v>
       </c>
       <c r="G101" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H101" s="6">
-        <v>280</v>
+        <v>250</v>
       </c>
     </row>
     <row outlineLevel="0" r="102">
@@ -3759,28 +3759,28 @@
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>HK205/55R16</t>
+          <t>GD205/55R16</t>
         </is>
       </c>
       <c r="D102" s="5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E102" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F102" s="5">
         <v>0</v>
       </c>
       <c r="G102" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H102" s="6">
-        <v>270</v>
+        <v>280</v>
       </c>
     </row>
     <row outlineLevel="0" r="103">
@@ -3791,28 +3791,28 @@
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>RD205/55R16</t>
+          <t>HK205/55R16</t>
         </is>
       </c>
       <c r="D103" s="5">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E103" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F103" s="5">
         <v>0</v>
       </c>
       <c r="G103" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H103" s="6">
-        <v>230</v>
+        <v>270</v>
       </c>
     </row>
     <row outlineLevel="0" r="104">
@@ -3823,66 +3823,66 @@
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>SEMPERIT</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>SP205/55R16</t>
+          <t>RD205/55R16</t>
         </is>
       </c>
       <c r="D104" s="5">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E104" s="5">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F104" s="5">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="G104" s="5">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H104" s="6">
-        <v>250</v>
+        <v>230</v>
       </c>
     </row>
     <row outlineLevel="0" r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>205/55R16RF</t>
+          <t>205/55R16</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>SEMPERIT</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>GD205/55R16RF</t>
+          <t>SP205/55R16</t>
         </is>
       </c>
       <c r="D105" s="5">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="E105" s="5">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F105" s="5">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G105" s="5">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H105" s="6">
-        <v>480</v>
+        <v>250</v>
       </c>
     </row>
     <row outlineLevel="0" r="106">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>205/55R17</t>
+          <t>205/55R16RF</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
@@ -3892,23 +3892,23 @@
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>GD205/55R17</t>
+          <t>GD205/55R16RF</t>
         </is>
       </c>
       <c r="D106" s="5">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="E106" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F106" s="5">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G106" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H106" s="6">
-        <v>450</v>
+        <v>480</v>
       </c>
     </row>
     <row outlineLevel="0" r="107">
@@ -3919,51 +3919,51 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>NX205/55R17</t>
+          <t>GD205/55R17</t>
         </is>
       </c>
       <c r="D107" s="5">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="E107" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F107" s="5">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G107" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H107" s="6">
-        <v>400</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="108">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>205/60R16</t>
+          <t>205/55R17</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>AMINE</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>AM205/60R16</t>
+          <t>NX205/55R17</t>
         </is>
       </c>
       <c r="D108" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E108" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F108" s="5">
         <v>0</v>
@@ -3972,7 +3972,7 @@
         <v>0</v>
       </c>
       <c r="H108" s="6">
-        <v>270</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="109">
@@ -3983,12 +3983,12 @@
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>BFGOODRICH</t>
+          <t>AMINE</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>BF205/60R16</t>
+          <t>AM205/60R16</t>
         </is>
       </c>
       <c r="D109" s="5">
@@ -4004,7 +4004,7 @@
         <v>0</v>
       </c>
       <c r="H109" s="6">
-        <v>320</v>
+        <v>270</v>
       </c>
     </row>
     <row outlineLevel="0" r="110">
@@ -4015,19 +4015,19 @@
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>BFGOODRICH</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>DL205/60R16</t>
+          <t>BF205/60R16</t>
         </is>
       </c>
       <c r="D110" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E110" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F110" s="5">
         <v>0</v>
@@ -4036,7 +4036,7 @@
         <v>0</v>
       </c>
       <c r="H110" s="6">
-        <v>330</v>
+        <v>320</v>
       </c>
     </row>
     <row outlineLevel="0" r="111">
@@ -4047,28 +4047,28 @@
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>GD205/60R16</t>
+          <t>DL205/60R16</t>
         </is>
       </c>
       <c r="D111" s="5">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="E111" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F111" s="5">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G111" s="5">
         <v>0</v>
       </c>
       <c r="H111" s="6">
-        <v>380</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="112">
@@ -4079,28 +4079,28 @@
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>HK205/60R16</t>
+          <t>GD205/60R16</t>
         </is>
       </c>
       <c r="D112" s="5">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E112" s="5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F112" s="5">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G112" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H112" s="6">
-        <v>320</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="113">
@@ -4111,28 +4111,28 @@
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>LASSA</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>LS205/60R16</t>
+          <t>HK205/60R16</t>
         </is>
       </c>
       <c r="D113" s="5">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E113" s="5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F113" s="5">
         <v>0</v>
       </c>
       <c r="G113" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H113" s="6">
-        <v>300</v>
+        <v>320</v>
       </c>
     </row>
     <row outlineLevel="0" r="114">
@@ -4143,19 +4143,19 @@
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>LASSA</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>LF205/60R16</t>
+          <t>LS205/60R16</t>
         </is>
       </c>
       <c r="D114" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E114" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F114" s="5">
         <v>0</v>
@@ -4170,24 +4170,24 @@
     <row outlineLevel="0" r="115">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t>205/65R15</t>
+          <t>205/60R16</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>HK205/65R15</t>
+          <t>LF205/60R16</t>
         </is>
       </c>
       <c r="D115" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E115" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F115" s="5">
         <v>0</v>
@@ -4196,30 +4196,30 @@
         <v>0</v>
       </c>
       <c r="H115" s="6">
-        <v>270</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="116">
       <c r="A116" s="4" t="inlineStr">
         <is>
-          <t>205/65R16</t>
+          <t>205/65R15</t>
         </is>
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>BR205/65R16</t>
+          <t>HK205/65R15</t>
         </is>
       </c>
       <c r="D116" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E116" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F116" s="5">
         <v>0</v>
@@ -4228,7 +4228,7 @@
         <v>0</v>
       </c>
       <c r="H116" s="6">
-        <v>420</v>
+        <v>270</v>
       </c>
     </row>
     <row outlineLevel="0" r="117">
@@ -4239,19 +4239,19 @@
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>HK205/65R16</t>
+          <t>BR205/65R16</t>
         </is>
       </c>
       <c r="D117" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E117" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F117" s="5">
         <v>0</v>
@@ -4260,39 +4260,39 @@
         <v>0</v>
       </c>
       <c r="H117" s="6">
-        <v>380</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="118">
       <c r="A118" s="4" t="inlineStr">
         <is>
-          <t>215/40R18</t>
+          <t>205/65R16</t>
         </is>
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>GD215/40R18</t>
+          <t>HK205/65R16</t>
         </is>
       </c>
       <c r="D118" s="5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E118" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F118" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G118" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H118" s="6">
-        <v>600</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="119">
@@ -4303,44 +4303,44 @@
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>HK215/40R18</t>
+          <t>GD215/40R18</t>
         </is>
       </c>
       <c r="D119" s="5">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E119" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F119" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G119" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H119" s="6">
-        <v>490</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="120">
       <c r="A120" s="4" t="inlineStr">
         <is>
-          <t>215/45R16</t>
+          <t>215/40R18</t>
         </is>
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>GD215/45R16</t>
+          <t>HK215/40R18</t>
         </is>
       </c>
       <c r="D120" s="5">
@@ -4356,13 +4356,13 @@
         <v>0</v>
       </c>
       <c r="H120" s="6">
-        <v>450</v>
+        <v>490</v>
       </c>
     </row>
     <row outlineLevel="0" r="121">
       <c r="A121" s="4" t="inlineStr">
         <is>
-          <t>215/45R17</t>
+          <t>215/45R16</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
@@ -4372,14 +4372,14 @@
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>GD215/45R17</t>
+          <t>GD215/45R16</t>
         </is>
       </c>
       <c r="D121" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E121" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F121" s="5">
         <v>0</v>
@@ -4388,7 +4388,7 @@
         <v>0</v>
       </c>
       <c r="H121" s="6">
-        <v>400</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="122">
@@ -4399,25 +4399,25 @@
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>HK215/45R17</t>
+          <t>GD215/45R17</t>
         </is>
       </c>
       <c r="D122" s="5">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="E122" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F122" s="5">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G122" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H122" s="6">
         <v>400</v>
@@ -4431,28 +4431,28 @@
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>IRIS</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>IR215/45R17</t>
+          <t>HK215/45R17</t>
         </is>
       </c>
       <c r="D123" s="5">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="E123" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F123" s="5">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G123" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H123" s="6">
-        <v>300</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="124">
@@ -4463,19 +4463,19 @@
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>IRIS</t>
         </is>
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>LF215/45R17</t>
+          <t>IR215/45R17</t>
         </is>
       </c>
       <c r="D124" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E124" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F124" s="5">
         <v>0</v>
@@ -4484,7 +4484,7 @@
         <v>0</v>
       </c>
       <c r="H124" s="6">
-        <v>350</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="125">
@@ -4495,60 +4495,60 @@
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>NX215/45R17</t>
+          <t>LF215/45R17</t>
         </is>
       </c>
       <c r="D125" s="5">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E125" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F125" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G125" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H125" s="6">
-        <v>380</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="126">
       <c r="A126" s="4" t="inlineStr">
         <is>
-          <t>215/45R18</t>
+          <t>215/45R17</t>
         </is>
       </c>
       <c r="B126" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C126" s="4" t="inlineStr">
         <is>
-          <t>GD215/45R18</t>
+          <t>NX215/45R17</t>
         </is>
       </c>
       <c r="D126" s="5">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E126" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F126" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G126" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H126" s="6">
-        <v>550</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="127">
@@ -4559,19 +4559,19 @@
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>RD215/45R18</t>
+          <t>GD215/45R18</t>
         </is>
       </c>
       <c r="D127" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E127" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F127" s="5">
         <v>0</v>
@@ -4580,30 +4580,30 @@
         <v>0</v>
       </c>
       <c r="H127" s="6">
-        <v>450</v>
+        <v>550</v>
       </c>
     </row>
     <row outlineLevel="0" r="128">
       <c r="A128" s="4" t="inlineStr">
         <is>
-          <t>215/50R17</t>
+          <t>215/45R18</t>
         </is>
       </c>
       <c r="B128" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C128" s="4" t="inlineStr">
         <is>
-          <t>BR215/50R17</t>
+          <t>RD215/45R18</t>
         </is>
       </c>
       <c r="D128" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E128" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F128" s="5">
         <v>0</v>
@@ -4623,28 +4623,28 @@
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>GD215/50R17</t>
+          <t>BR215/50R17</t>
         </is>
       </c>
       <c r="D129" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E129" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F129" s="5">
         <v>0</v>
       </c>
       <c r="G129" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H129" s="6">
-        <v>470</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="130">
@@ -4655,16 +4655,16 @@
       </c>
       <c r="B130" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C130" s="4" t="inlineStr">
         <is>
-          <t>HK215/50R17</t>
+          <t>GD215/50R17</t>
         </is>
       </c>
       <c r="D130" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E130" s="5">
         <v>3</v>
@@ -4673,10 +4673,10 @@
         <v>0</v>
       </c>
       <c r="G130" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H130" s="6">
-        <v>400</v>
+        <v>470</v>
       </c>
     </row>
     <row outlineLevel="0" r="131">
@@ -4687,19 +4687,19 @@
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>LF215/50R17</t>
+          <t>HK215/50R17</t>
         </is>
       </c>
       <c r="D131" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E131" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F131" s="5">
         <v>0</v>
@@ -4708,30 +4708,30 @@
         <v>0</v>
       </c>
       <c r="H131" s="6">
-        <v>420</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="132">
       <c r="A132" s="4" t="inlineStr">
         <is>
-          <t>215/50R18</t>
+          <t>215/50R17</t>
         </is>
       </c>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C132" s="4" t="inlineStr">
         <is>
-          <t>GD215/50R18</t>
+          <t>LF215/50R17</t>
         </is>
       </c>
       <c r="D132" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E132" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F132" s="5">
         <v>0</v>
@@ -4740,13 +4740,13 @@
         <v>0</v>
       </c>
       <c r="H132" s="6">
-        <v>600</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="133">
       <c r="A133" s="4" t="inlineStr">
         <is>
-          <t>215/55R16</t>
+          <t>215/50R18</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
@@ -4756,14 +4756,14 @@
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>GD215/55R16</t>
+          <t>GD215/50R18</t>
         </is>
       </c>
       <c r="D133" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E133" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F133" s="5">
         <v>0</v>
@@ -4772,7 +4772,7 @@
         <v>0</v>
       </c>
       <c r="H133" s="6">
-        <v>440</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="134">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C134" s="4" t="inlineStr">
         <is>
-          <t>LF215/55R16</t>
+          <t>GD215/55R16</t>
         </is>
       </c>
       <c r="D134" s="5">
@@ -4804,23 +4804,23 @@
         <v>0</v>
       </c>
       <c r="H134" s="6">
-        <v>350</v>
+        <v>440</v>
       </c>
     </row>
     <row outlineLevel="0" r="135">
       <c r="A135" s="4" t="inlineStr">
         <is>
-          <t>215/55R17</t>
+          <t>215/55R16</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>BR215/55R17</t>
+          <t>LF215/55R16</t>
         </is>
       </c>
       <c r="D135" s="5">
@@ -4836,7 +4836,7 @@
         <v>0</v>
       </c>
       <c r="H135" s="6">
-        <v>480</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="136">
@@ -4847,19 +4847,19 @@
       </c>
       <c r="B136" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C136" s="4" t="inlineStr">
         <is>
-          <t>HK215/55R17</t>
+          <t>BR215/55R17</t>
         </is>
       </c>
       <c r="D136" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E136" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F136" s="5">
         <v>0</v>
@@ -4868,7 +4868,7 @@
         <v>0</v>
       </c>
       <c r="H136" s="6">
-        <v>420</v>
+        <v>480</v>
       </c>
     </row>
     <row outlineLevel="0" r="137">
@@ -4879,19 +4879,19 @@
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>SEMPERIT</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>SP215/55R17</t>
+          <t>HK215/55R17</t>
         </is>
       </c>
       <c r="D137" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E137" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F137" s="5">
         <v>0</v>
@@ -4906,24 +4906,24 @@
     <row outlineLevel="0" r="138">
       <c r="A138" s="4" t="inlineStr">
         <is>
-          <t>215/55R18</t>
+          <t>215/55R17</t>
         </is>
       </c>
       <c r="B138" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>SEMPERIT</t>
         </is>
       </c>
       <c r="C138" s="4" t="inlineStr">
         <is>
-          <t>GD215/55R18</t>
+          <t>SP215/55R17</t>
         </is>
       </c>
       <c r="D138" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E138" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F138" s="5">
         <v>0</v>
@@ -4932,30 +4932,30 @@
         <v>0</v>
       </c>
       <c r="H138" s="6">
-        <v>580</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="139">
       <c r="A139" s="4" t="inlineStr">
         <is>
-          <t>215/60R16</t>
+          <t>215/55R18</t>
         </is>
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>BR215/60R16</t>
+          <t>GD215/55R18</t>
         </is>
       </c>
       <c r="D139" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E139" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F139" s="5">
         <v>0</v>
@@ -4964,7 +4964,7 @@
         <v>0</v>
       </c>
       <c r="H139" s="6">
-        <v>380</v>
+        <v>580</v>
       </c>
     </row>
     <row outlineLevel="0" r="140">
@@ -4975,28 +4975,28 @@
       </c>
       <c r="B140" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C140" s="4" t="inlineStr">
         <is>
-          <t>DL215/60R16</t>
+          <t>BR215/60R16</t>
         </is>
       </c>
       <c r="D140" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E140" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F140" s="5">
         <v>0</v>
       </c>
       <c r="G140" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H140" s="6">
-        <v>350</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="141">
@@ -5007,28 +5007,28 @@
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>HK215/60R16</t>
+          <t>DL215/60R16</t>
         </is>
       </c>
       <c r="D141" s="5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E141" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F141" s="5">
         <v>0</v>
       </c>
       <c r="G141" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H141" s="6">
-        <v>330</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="142">
@@ -5039,25 +5039,25 @@
       </c>
       <c r="B142" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C142" s="4" t="inlineStr">
         <is>
-          <t>NX215/60R16</t>
+          <t>HK215/60R16</t>
         </is>
       </c>
       <c r="D142" s="5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E142" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F142" s="5">
         <v>0</v>
       </c>
       <c r="G142" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H142" s="6">
         <v>330</v>
@@ -5066,21 +5066,21 @@
     <row outlineLevel="0" r="143">
       <c r="A143" s="4" t="inlineStr">
         <is>
-          <t>215/60R17</t>
+          <t>215/60R16</t>
         </is>
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>GD215/60R17</t>
+          <t>NX215/60R16</t>
         </is>
       </c>
       <c r="D143" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E143" s="5">
         <v>0</v>
@@ -5089,10 +5089,10 @@
         <v>0</v>
       </c>
       <c r="G143" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H143" s="6">
-        <v>480</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="144">
@@ -5103,19 +5103,19 @@
       </c>
       <c r="B144" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C144" s="4" t="inlineStr">
         <is>
-          <t>RD215/60R17</t>
+          <t>GD215/60R17</t>
         </is>
       </c>
       <c r="D144" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E144" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F144" s="5">
         <v>0</v>
@@ -5124,39 +5124,39 @@
         <v>0</v>
       </c>
       <c r="H144" s="6">
-        <v>300</v>
+        <v>480</v>
       </c>
     </row>
     <row outlineLevel="0" r="145">
       <c r="A145" s="4" t="inlineStr">
         <is>
-          <t>215/65R16</t>
+          <t>215/60R17</t>
         </is>
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>GD215/65R16</t>
+          <t>RD215/60R17</t>
         </is>
       </c>
       <c r="D145" s="5">
         <v>1</v>
       </c>
       <c r="E145" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F145" s="5">
         <v>0</v>
       </c>
       <c r="G145" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H145" s="6">
-        <v>380</v>
+        <v>300</v>
       </c>
     </row>
     <row outlineLevel="0" r="146">
@@ -5167,44 +5167,44 @@
       </c>
       <c r="B146" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C146" s="4" t="inlineStr">
         <is>
-          <t>HK215/65R16</t>
+          <t>GD215/65R16</t>
         </is>
       </c>
       <c r="D146" s="5">
         <v>1</v>
       </c>
       <c r="E146" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F146" s="5">
         <v>0</v>
       </c>
       <c r="G146" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H146" s="6">
-        <v>350</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="147">
       <c r="A147" s="4" t="inlineStr">
         <is>
-          <t>215/65R17</t>
+          <t>215/65R16</t>
         </is>
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>MICHELIN</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>MC215/65R17</t>
+          <t>HK215/65R16</t>
         </is>
       </c>
       <c r="D147" s="5">
@@ -5220,30 +5220,30 @@
         <v>0</v>
       </c>
       <c r="H147" s="6">
-        <v>680</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="148">
       <c r="A148" s="4" t="inlineStr">
         <is>
-          <t>215/65R17</t>
+          <t>215/65R16</t>
         </is>
       </c>
       <c r="B148" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C148" s="4" t="inlineStr">
         <is>
-          <t>NX215/65R17</t>
+          <t>RD215/65R16</t>
         </is>
       </c>
       <c r="D148" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E148" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F148" s="5">
         <v>0</v>
@@ -5252,30 +5252,30 @@
         <v>0</v>
       </c>
       <c r="H148" s="6">
-        <v>420</v>
+        <v>280</v>
       </c>
     </row>
     <row outlineLevel="0" r="149">
       <c r="A149" s="4" t="inlineStr">
         <is>
-          <t>215/70R15C</t>
+          <t>215/65R17</t>
         </is>
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>DOUBLESTAR</t>
+          <t>MICHELIN</t>
         </is>
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>DS215/70R15C</t>
+          <t>MC215/65R17</t>
         </is>
       </c>
       <c r="D149" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E149" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F149" s="5">
         <v>0</v>
@@ -5284,27 +5284,27 @@
         <v>0</v>
       </c>
       <c r="H149" s="6">
-        <v>350</v>
+        <v>680</v>
       </c>
     </row>
     <row outlineLevel="0" r="150">
       <c r="A150" s="4" t="inlineStr">
         <is>
-          <t>215/70R15C</t>
+          <t>215/65R17</t>
         </is>
       </c>
       <c r="B150" s="4" t="inlineStr">
         <is>
-          <t>LINGLONG</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C150" s="4" t="inlineStr">
         <is>
-          <t>LG215/70R15C</t>
+          <t>NX215/65R17</t>
         </is>
       </c>
       <c r="D150" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E150" s="5">
         <v>0</v>
@@ -5313,10 +5313,10 @@
         <v>0</v>
       </c>
       <c r="G150" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H150" s="6">
-        <v>370</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="151">
@@ -5327,12 +5327,12 @@
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>MICHELIN</t>
+          <t>DOUBLESTAR</t>
         </is>
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>MC215/70R15C</t>
+          <t>DS215/70R15C</t>
         </is>
       </c>
       <c r="D151" s="5">
@@ -5348,7 +5348,7 @@
         <v>0</v>
       </c>
       <c r="H151" s="6">
-        <v>590</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="152">
@@ -5359,51 +5359,51 @@
       </c>
       <c r="B152" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>LINGLONG</t>
         </is>
       </c>
       <c r="C152" s="4" t="inlineStr">
         <is>
-          <t>RD215/70R15C</t>
+          <t>LG215/70R15C</t>
         </is>
       </c>
       <c r="D152" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E152" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F152" s="5">
         <v>0</v>
       </c>
       <c r="G152" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H152" s="6">
-        <v>330</v>
+        <v>370</v>
       </c>
     </row>
     <row outlineLevel="0" r="153">
       <c r="A153" s="4" t="inlineStr">
         <is>
-          <t>225/40R18</t>
+          <t>215/70R15C</t>
         </is>
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>BARUM</t>
+          <t>MICHELIN</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>BM225/40R18</t>
+          <t>MC215/70R15C</t>
         </is>
       </c>
       <c r="D153" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E153" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F153" s="5">
         <v>0</v>
@@ -5412,39 +5412,39 @@
         <v>0</v>
       </c>
       <c r="H153" s="6">
-        <v>420</v>
+        <v>590</v>
       </c>
     </row>
     <row outlineLevel="0" r="154">
       <c r="A154" s="4" t="inlineStr">
         <is>
-          <t>225/40R18</t>
+          <t>215/70R15C</t>
         </is>
       </c>
       <c r="B154" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C154" s="4" t="inlineStr">
         <is>
-          <t>GD225/40R18</t>
+          <t>RD215/70R15C</t>
         </is>
       </c>
       <c r="D154" s="5">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="E154" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F154" s="5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G154" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H154" s="6">
-        <v>480</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="155">
@@ -5455,19 +5455,19 @@
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>BARUM</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>HK225/40R18</t>
+          <t>BM225/40R18</t>
         </is>
       </c>
       <c r="D155" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E155" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F155" s="5">
         <v>0</v>
@@ -5476,7 +5476,7 @@
         <v>0</v>
       </c>
       <c r="H155" s="6">
-        <v>450</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="156">
@@ -5487,28 +5487,28 @@
       </c>
       <c r="B156" s="4" t="inlineStr">
         <is>
-          <t>LASSA</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C156" s="4" t="inlineStr">
         <is>
-          <t>LS225/40R18</t>
+          <t>GD225/40R18</t>
         </is>
       </c>
       <c r="D156" s="5">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E156" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F156" s="5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G156" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H156" s="6">
-        <v>330</v>
+        <v>480</v>
       </c>
     </row>
     <row outlineLevel="0" r="157">
@@ -5519,19 +5519,19 @@
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>NX225/40R18</t>
+          <t>HK225/40R18</t>
         </is>
       </c>
       <c r="D157" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E157" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F157" s="5">
         <v>0</v>
@@ -5540,7 +5540,7 @@
         <v>0</v>
       </c>
       <c r="H157" s="6">
-        <v>400</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="158">
@@ -5551,19 +5551,19 @@
       </c>
       <c r="B158" s="4" t="inlineStr">
         <is>
-          <t>SEMPERIT</t>
+          <t>LASSA</t>
         </is>
       </c>
       <c r="C158" s="4" t="inlineStr">
         <is>
-          <t>SP225/40R18</t>
+          <t>LS225/40R18</t>
         </is>
       </c>
       <c r="D158" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E158" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F158" s="5">
         <v>0</v>
@@ -5572,30 +5572,30 @@
         <v>0</v>
       </c>
       <c r="H158" s="6">
-        <v>450</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="159">
       <c r="A159" s="4" t="inlineStr">
         <is>
-          <t>225/40R18RF</t>
+          <t>225/40R18</t>
         </is>
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>GD225/40R18RF</t>
+          <t>NX225/40R18</t>
         </is>
       </c>
       <c r="D159" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E159" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F159" s="5">
         <v>0</v>
@@ -5604,30 +5604,30 @@
         <v>0</v>
       </c>
       <c r="H159" s="6">
-        <v>590</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="160">
       <c r="A160" s="4" t="inlineStr">
         <is>
-          <t>225/40R19RF</t>
+          <t>225/40R18</t>
         </is>
       </c>
       <c r="B160" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>SEMPERIT</t>
         </is>
       </c>
       <c r="C160" s="4" t="inlineStr">
         <is>
-          <t>GD225/40R19RF</t>
+          <t>SP225/40R18</t>
         </is>
       </c>
       <c r="D160" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E160" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F160" s="5">
         <v>0</v>
@@ -5636,30 +5636,30 @@
         <v>0</v>
       </c>
       <c r="H160" s="6">
-        <v>1200</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="161">
       <c r="A161" s="4" t="inlineStr">
         <is>
-          <t>225/45R17</t>
+          <t>225/40R18RF</t>
         </is>
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>CT225/45R17</t>
+          <t>GD225/40R18RF</t>
         </is>
       </c>
       <c r="D161" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E161" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F161" s="5">
         <v>0</v>
@@ -5668,39 +5668,39 @@
         <v>0</v>
       </c>
       <c r="H161" s="6">
-        <v>400</v>
+        <v>590</v>
       </c>
     </row>
     <row outlineLevel="0" r="162">
       <c r="A162" s="4" t="inlineStr">
         <is>
-          <t>225/45R17</t>
+          <t>225/40R19RF</t>
         </is>
       </c>
       <c r="B162" s="4" t="inlineStr">
         <is>
-          <t>FULDA</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C162" s="4" t="inlineStr">
         <is>
-          <t>FL225/45R17</t>
+          <t>GD225/40R19RF</t>
         </is>
       </c>
       <c r="D162" s="5">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="E162" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F162" s="5">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G162" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H162" s="6">
-        <v>350</v>
+        <v>1200</v>
       </c>
     </row>
     <row outlineLevel="0" r="163">
@@ -5711,28 +5711,28 @@
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>GD225/45R17</t>
+          <t>CT225/45R17</t>
         </is>
       </c>
       <c r="D163" s="5">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="E163" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F163" s="5">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G163" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H163" s="6">
-        <v>380</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="164">
@@ -5743,92 +5743,92 @@
       </c>
       <c r="B164" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>FULDA</t>
         </is>
       </c>
       <c r="C164" s="4" t="inlineStr">
         <is>
-          <t>HK225/45R17</t>
+          <t>FL225/45R17</t>
         </is>
       </c>
       <c r="D164" s="5">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="E164" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F164" s="5">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G164" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H164" s="6">
-        <v>380</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="165">
       <c r="A165" s="4" t="inlineStr">
         <is>
-          <t>225/45R18</t>
+          <t>225/45R17</t>
         </is>
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>DL225/45R18</t>
+          <t>GD225/45R17</t>
         </is>
       </c>
       <c r="D165" s="5">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="E165" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F165" s="5">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G165" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H165" s="6">
-        <v>500</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="166">
       <c r="A166" s="4" t="inlineStr">
         <is>
-          <t>225/45R18</t>
+          <t>225/45R17</t>
         </is>
       </c>
       <c r="B166" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C166" s="4" t="inlineStr">
         <is>
-          <t>GD225/45R18</t>
+          <t>HK225/45R17</t>
         </is>
       </c>
       <c r="D166" s="5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E166" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F166" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G166" s="5">
         <v>0</v>
       </c>
       <c r="H166" s="6">
-        <v>550</v>
+        <v>380</v>
       </c>
     </row>
     <row outlineLevel="0" r="167">
@@ -5839,19 +5839,19 @@
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>HK225/45R18</t>
+          <t>DL225/45R18</t>
         </is>
       </c>
       <c r="D167" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E167" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F167" s="5">
         <v>0</v>
@@ -5860,7 +5860,7 @@
         <v>0</v>
       </c>
       <c r="H167" s="6">
-        <v>450</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="168">
@@ -5871,83 +5871,83 @@
       </c>
       <c r="B168" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C168" s="4" t="inlineStr">
         <is>
-          <t>LF225/45R18</t>
+          <t>GD225/45R18</t>
         </is>
       </c>
       <c r="D168" s="5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E168" s="5">
         <v>4</v>
       </c>
       <c r="F168" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G168" s="5">
         <v>0</v>
       </c>
       <c r="H168" s="6">
-        <v>420</v>
+        <v>550</v>
       </c>
     </row>
     <row outlineLevel="0" r="169">
       <c r="A169" s="4" t="inlineStr">
         <is>
-          <t>225/45R18RF</t>
+          <t>225/45R18</t>
         </is>
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>GD225/45R18RF</t>
+          <t>HK225/45R18</t>
         </is>
       </c>
       <c r="D169" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E169" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F169" s="5">
         <v>0</v>
       </c>
       <c r="G169" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H169" s="6">
-        <v>720</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="170">
       <c r="A170" s="4" t="inlineStr">
         <is>
-          <t>225/45R19</t>
+          <t>225/45R18</t>
         </is>
       </c>
       <c r="B170" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C170" s="4" t="inlineStr">
         <is>
-          <t>CT225/45R19</t>
+          <t>LF225/45R18</t>
         </is>
       </c>
       <c r="D170" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E170" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F170" s="5">
         <v>0</v>
@@ -5956,13 +5956,13 @@
         <v>0</v>
       </c>
       <c r="H170" s="6">
-        <v>780</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="171">
       <c r="A171" s="4" t="inlineStr">
         <is>
-          <t>225/45R19</t>
+          <t>225/45R18RF</t>
         </is>
       </c>
       <c r="B171" s="4" t="inlineStr">
@@ -5972,23 +5972,23 @@
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t>GD225/45R19</t>
+          <t>GD225/45R18RF</t>
         </is>
       </c>
       <c r="D171" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E171" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F171" s="5">
         <v>0</v>
       </c>
       <c r="G171" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H171" s="6">
-        <v>750</v>
+        <v>720</v>
       </c>
     </row>
     <row outlineLevel="0" r="172">
@@ -5999,19 +5999,19 @@
       </c>
       <c r="B172" s="4" t="inlineStr">
         <is>
-          <t>LASSA</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C172" s="4" t="inlineStr">
         <is>
-          <t>LS225/45R19</t>
+          <t>CT225/45R19</t>
         </is>
       </c>
       <c r="D172" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E172" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F172" s="5">
         <v>0</v>
@@ -6020,30 +6020,30 @@
         <v>0</v>
       </c>
       <c r="H172" s="6">
-        <v>520</v>
+        <v>780</v>
       </c>
     </row>
     <row outlineLevel="0" r="173">
       <c r="A173" s="4" t="inlineStr">
         <is>
-          <t>225/50R17</t>
+          <t>225/45R19</t>
         </is>
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>BR225/50R17</t>
+          <t>GD225/45R19</t>
         </is>
       </c>
       <c r="D173" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E173" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F173" s="5">
         <v>0</v>
@@ -6052,39 +6052,39 @@
         <v>0</v>
       </c>
       <c r="H173" s="6">
-        <v>600</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="174">
       <c r="A174" s="4" t="inlineStr">
         <is>
-          <t>225/50R17</t>
+          <t>225/45R19</t>
         </is>
       </c>
       <c r="B174" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>LASSA</t>
         </is>
       </c>
       <c r="C174" s="4" t="inlineStr">
         <is>
-          <t>GD225/50R17</t>
+          <t>LS225/45R19</t>
         </is>
       </c>
       <c r="D174" s="5">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E174" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F174" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G174" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H174" s="6">
-        <v>500</v>
+        <v>520</v>
       </c>
     </row>
     <row outlineLevel="0" r="175">
@@ -6095,115 +6095,115 @@
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>HK225/50R17</t>
+          <t>BR225/50R17</t>
         </is>
       </c>
       <c r="D175" s="5">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E175" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F175" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G175" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H175" s="6">
-        <v>400</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="176">
       <c r="A176" s="4" t="inlineStr">
         <is>
-          <t>225/55R16</t>
+          <t>225/50R17</t>
         </is>
       </c>
       <c r="B176" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C176" s="4" t="inlineStr">
         <is>
-          <t>DL225/55R16</t>
+          <t>GD225/50R17</t>
         </is>
       </c>
       <c r="D176" s="5">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E176" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F176" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G176" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H176" s="6">
-        <v>450</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="177">
       <c r="A177" s="4" t="inlineStr">
         <is>
-          <t>225/55R16</t>
+          <t>225/50R17</t>
         </is>
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>GD225/55R16</t>
+          <t>HK225/50R17</t>
         </is>
       </c>
       <c r="D177" s="5">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E177" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F177" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G177" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H177" s="6">
-        <v>420</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="178">
       <c r="A178" s="4" t="inlineStr">
         <is>
-          <t>225/55R17</t>
+          <t>225/55R16</t>
         </is>
       </c>
       <c r="B178" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C178" s="4" t="inlineStr">
         <is>
-          <t>HK225/55R17</t>
+          <t>DL225/55R16</t>
         </is>
       </c>
       <c r="D178" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E178" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F178" s="5">
         <v>0</v>
@@ -6212,13 +6212,13 @@
         <v>0</v>
       </c>
       <c r="H178" s="6">
-        <v>430</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="179">
       <c r="A179" s="4" t="inlineStr">
         <is>
-          <t>225/55R17RF</t>
+          <t>225/55R16</t>
         </is>
       </c>
       <c r="B179" s="4" t="inlineStr">
@@ -6228,29 +6228,29 @@
       </c>
       <c r="C179" s="4" t="inlineStr">
         <is>
-          <t>GD225/55R17RF</t>
+          <t>GD225/55R16</t>
         </is>
       </c>
       <c r="D179" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E179" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F179" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G179" s="5">
         <v>0</v>
       </c>
       <c r="H179" s="6">
-        <v>700</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="180">
       <c r="A180" s="4" t="inlineStr">
         <is>
-          <t>225/55R18</t>
+          <t>225/55R17</t>
         </is>
       </c>
       <c r="B180" s="4" t="inlineStr">
@@ -6260,14 +6260,14 @@
       </c>
       <c r="C180" s="4" t="inlineStr">
         <is>
-          <t>HK225/55R18</t>
+          <t>HK225/55R17</t>
         </is>
       </c>
       <c r="D180" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E180" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F180" s="5">
         <v>0</v>
@@ -6276,62 +6276,62 @@
         <v>0</v>
       </c>
       <c r="H180" s="6">
-        <v>500</v>
+        <v>430</v>
       </c>
     </row>
     <row outlineLevel="0" r="181">
       <c r="A181" s="4" t="inlineStr">
         <is>
-          <t>225/55R18</t>
+          <t>225/55R17RF</t>
         </is>
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>KUMHO</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C181" s="4" t="inlineStr">
         <is>
-          <t>KM225/55R18</t>
+          <t>GD225/55R17RF</t>
         </is>
       </c>
       <c r="D181" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E181" s="5">
         <v>4</v>
       </c>
       <c r="F181" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G181" s="5">
         <v>0</v>
       </c>
       <c r="H181" s="6">
-        <v>450</v>
+        <v>700</v>
       </c>
     </row>
     <row outlineLevel="0" r="182">
       <c r="A182" s="4" t="inlineStr">
         <is>
-          <t>225/55R19</t>
+          <t>225/55R18</t>
         </is>
       </c>
       <c r="B182" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C182" s="4" t="inlineStr">
         <is>
-          <t>BR225/55R19</t>
+          <t>HK225/55R18</t>
         </is>
       </c>
       <c r="D182" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E182" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F182" s="5">
         <v>0</v>
@@ -6340,23 +6340,23 @@
         <v>0</v>
       </c>
       <c r="H182" s="6">
-        <v>750</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="183">
       <c r="A183" s="4" t="inlineStr">
         <is>
-          <t>225/55R19</t>
+          <t>225/55R18</t>
         </is>
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>KUMHO</t>
         </is>
       </c>
       <c r="C183" s="4" t="inlineStr">
         <is>
-          <t>GD225/55R19</t>
+          <t>KM225/55R18</t>
         </is>
       </c>
       <c r="D183" s="5">
@@ -6372,30 +6372,30 @@
         <v>0</v>
       </c>
       <c r="H183" s="6">
-        <v>750</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="184">
       <c r="A184" s="4" t="inlineStr">
         <is>
-          <t>225/60R17</t>
+          <t>225/55R19</t>
         </is>
       </c>
       <c r="B184" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C184" s="4" t="inlineStr">
         <is>
-          <t>GD225/60R17</t>
+          <t>BR225/55R19</t>
         </is>
       </c>
       <c r="D184" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E184" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F184" s="5">
         <v>0</v>
@@ -6404,45 +6404,45 @@
         <v>0</v>
       </c>
       <c r="H184" s="6">
-        <v>500</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="185">
       <c r="A185" s="4" t="inlineStr">
         <is>
-          <t>225/60R17</t>
+          <t>225/55R19</t>
         </is>
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C185" s="4" t="inlineStr">
         <is>
-          <t>HK225/60R17</t>
+          <t>GD225/55R19</t>
         </is>
       </c>
       <c r="D185" s="5">
         <v>4</v>
       </c>
       <c r="E185" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F185" s="5">
         <v>0</v>
       </c>
       <c r="G185" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H185" s="6">
-        <v>425</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="186">
       <c r="A186" s="4" t="inlineStr">
         <is>
-          <t>225/60R18</t>
+          <t>225/60R17</t>
         </is>
       </c>
       <c r="B186" s="4" t="inlineStr">
@@ -6452,14 +6452,14 @@
       </c>
       <c r="C186" s="4" t="inlineStr">
         <is>
-          <t>GD225/60R18</t>
+          <t>GD225/60R17</t>
         </is>
       </c>
       <c r="D186" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E186" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F186" s="5">
         <v>0</v>
@@ -6468,94 +6468,94 @@
         <v>0</v>
       </c>
       <c r="H186" s="6">
-        <v>700</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="187">
       <c r="A187" s="4" t="inlineStr">
         <is>
-          <t>225/65R17</t>
+          <t>225/60R17</t>
         </is>
       </c>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C187" s="4" t="inlineStr">
         <is>
-          <t>RD225/65R17</t>
+          <t>HK225/60R17</t>
         </is>
       </c>
       <c r="D187" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E187" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F187" s="5">
         <v>0</v>
       </c>
       <c r="G187" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H187" s="6">
-        <v>450</v>
+        <v>425</v>
       </c>
     </row>
     <row outlineLevel="0" r="188">
       <c r="A188" s="4" t="inlineStr">
         <is>
-          <t>225/70R15C</t>
+          <t>225/60R18</t>
         </is>
       </c>
       <c r="B188" s="4" t="inlineStr">
         <is>
-          <t>MATADOR</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C188" s="4" t="inlineStr">
         <is>
-          <t>MT225/70R15C</t>
+          <t>GD225/60R18</t>
         </is>
       </c>
       <c r="D188" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E188" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F188" s="5">
         <v>0</v>
       </c>
       <c r="G188" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H188" s="6">
-        <v>450</v>
+        <v>700</v>
       </c>
     </row>
     <row outlineLevel="0" r="189">
       <c r="A189" s="4" t="inlineStr">
         <is>
-          <t>225/70R15C</t>
+          <t>225/65R17</t>
         </is>
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>SEMPERIT</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C189" s="4" t="inlineStr">
         <is>
-          <t>SP225/70R15C</t>
+          <t>RD225/65R17</t>
         </is>
       </c>
       <c r="D189" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E189" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F189" s="5">
         <v>0</v>
@@ -6570,21 +6570,21 @@
     <row outlineLevel="0" r="190">
       <c r="A190" s="4" t="inlineStr">
         <is>
-          <t>225/75R15C</t>
+          <t>225/70R15C</t>
         </is>
       </c>
       <c r="B190" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>MATADOR</t>
         </is>
       </c>
       <c r="C190" s="4" t="inlineStr">
         <is>
-          <t>RD225/75R15C</t>
+          <t>MT225/70R15C</t>
         </is>
       </c>
       <c r="D190" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E190" s="5">
         <v>0</v>
@@ -6593,100 +6593,100 @@
         <v>0</v>
       </c>
       <c r="G190" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H190" s="6">
-        <v>330</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="191">
       <c r="A191" s="4" t="inlineStr">
         <is>
-          <t>235/35R19</t>
+          <t>225/70R15C</t>
         </is>
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>SEMPERIT</t>
         </is>
       </c>
       <c r="C191" s="4" t="inlineStr">
         <is>
-          <t>RD235/35R19</t>
+          <t>SP225/70R15C</t>
         </is>
       </c>
       <c r="D191" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E191" s="5">
         <v>0</v>
       </c>
       <c r="F191" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G191" s="5">
         <v>0</v>
       </c>
       <c r="H191" s="6">
-        <v>600</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="192">
       <c r="A192" s="4" t="inlineStr">
         <is>
-          <t>235/40R19</t>
+          <t>225/75R15C</t>
         </is>
       </c>
       <c r="B192" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C192" s="4" t="inlineStr">
         <is>
-          <t>GD235/40R19</t>
+          <t>RD225/75R15C</t>
         </is>
       </c>
       <c r="D192" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E192" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F192" s="5">
         <v>0</v>
       </c>
       <c r="G192" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H192" s="6">
-        <v>850</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="193">
       <c r="A193" s="4" t="inlineStr">
         <is>
-          <t>235/45R18</t>
+          <t>235/35R19</t>
         </is>
       </c>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C193" s="4" t="inlineStr">
         <is>
-          <t>GD235/45R18</t>
+          <t>RD235/35R19</t>
         </is>
       </c>
       <c r="D193" s="5">
         <v>4</v>
       </c>
       <c r="E193" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F193" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G193" s="5">
         <v>0</v>
@@ -6698,24 +6698,24 @@
     <row outlineLevel="0" r="194">
       <c r="A194" s="4" t="inlineStr">
         <is>
-          <t>235/50R18</t>
+          <t>235/40R19</t>
         </is>
       </c>
       <c r="B194" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C194" s="4" t="inlineStr">
         <is>
-          <t>HK235/50R18</t>
+          <t>GD235/40R19</t>
         </is>
       </c>
       <c r="D194" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E194" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F194" s="5">
         <v>0</v>
@@ -6724,13 +6724,13 @@
         <v>0</v>
       </c>
       <c r="H194" s="6">
-        <v>500</v>
+        <v>850</v>
       </c>
     </row>
     <row outlineLevel="0" r="195">
       <c r="A195" s="4" t="inlineStr">
         <is>
-          <t>235/50R19</t>
+          <t>235/45R18</t>
         </is>
       </c>
       <c r="B195" s="4" t="inlineStr">
@@ -6740,14 +6740,14 @@
       </c>
       <c r="C195" s="4" t="inlineStr">
         <is>
-          <t>GD235/50R19</t>
+          <t>GD235/45R18</t>
         </is>
       </c>
       <c r="D195" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E195" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F195" s="5">
         <v>0</v>
@@ -6756,62 +6756,62 @@
         <v>0</v>
       </c>
       <c r="H195" s="6">
-        <v>800</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="196">
       <c r="A196" s="4" t="inlineStr">
         <is>
-          <t>235/50R20</t>
+          <t>235/50R18</t>
         </is>
       </c>
       <c r="B196" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C196" s="4" t="inlineStr">
         <is>
-          <t>GD235/50R20</t>
+          <t>HK235/50R18</t>
         </is>
       </c>
       <c r="D196" s="5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E196" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F196" s="5">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G196" s="5">
         <v>0</v>
       </c>
       <c r="H196" s="6">
-        <v>1180</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="197">
       <c r="A197" s="4" t="inlineStr">
         <is>
-          <t>235/55R17</t>
+          <t>235/50R19</t>
         </is>
       </c>
       <c r="B197" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C197" s="4" t="inlineStr">
         <is>
-          <t>BR235/55R17</t>
+          <t>GD235/50R19</t>
         </is>
       </c>
       <c r="D197" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E197" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F197" s="5">
         <v>0</v>
@@ -6820,62 +6820,62 @@
         <v>0</v>
       </c>
       <c r="H197" s="6">
-        <v>450</v>
+        <v>800</v>
       </c>
     </row>
     <row outlineLevel="0" r="198">
       <c r="A198" s="4" t="inlineStr">
         <is>
-          <t>235/55R18</t>
+          <t>235/50R20</t>
         </is>
       </c>
       <c r="B198" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C198" s="4" t="inlineStr">
         <is>
-          <t>HK235/55R18</t>
+          <t>GD235/50R20</t>
         </is>
       </c>
       <c r="D198" s="5">
         <v>7</v>
       </c>
       <c r="E198" s="5">
+        <v>0</v>
+      </c>
+      <c r="F198" s="5">
         <v>7</v>
       </c>
-      <c r="F198" s="5">
-        <v>0</v>
-      </c>
       <c r="G198" s="5">
         <v>0</v>
       </c>
       <c r="H198" s="6">
-        <v>480</v>
+        <v>1180</v>
       </c>
     </row>
     <row outlineLevel="0" r="199">
       <c r="A199" s="4" t="inlineStr">
         <is>
-          <t>235/55R19</t>
+          <t>235/55R17</t>
         </is>
       </c>
       <c r="B199" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C199" s="4" t="inlineStr">
         <is>
-          <t>GD235/55R19</t>
+          <t>BR235/55R17</t>
         </is>
       </c>
       <c r="D199" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E199" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F199" s="5">
         <v>0</v>
@@ -6884,13 +6884,13 @@
         <v>0</v>
       </c>
       <c r="H199" s="6">
-        <v>750</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="200">
       <c r="A200" s="4" t="inlineStr">
         <is>
-          <t>235/55R19</t>
+          <t>235/55R18</t>
         </is>
       </c>
       <c r="B200" s="4" t="inlineStr">
@@ -6900,14 +6900,14 @@
       </c>
       <c r="C200" s="4" t="inlineStr">
         <is>
-          <t>HK235/55R19</t>
+          <t>HK235/55R18</t>
         </is>
       </c>
       <c r="D200" s="5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E200" s="5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F200" s="5">
         <v>0</v>
@@ -6916,7 +6916,7 @@
         <v>0</v>
       </c>
       <c r="H200" s="6">
-        <v>630</v>
+        <v>480</v>
       </c>
     </row>
     <row outlineLevel="0" r="201">
@@ -6927,19 +6927,19 @@
       </c>
       <c r="B201" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C201" s="4" t="inlineStr">
         <is>
-          <t>LF235/55R19</t>
+          <t>GD235/55R19</t>
         </is>
       </c>
       <c r="D201" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E201" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F201" s="5">
         <v>0</v>
@@ -6948,7 +6948,7 @@
         <v>0</v>
       </c>
       <c r="H201" s="6">
-        <v>500</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="202">
@@ -6959,19 +6959,19 @@
       </c>
       <c r="B202" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C202" s="4" t="inlineStr">
         <is>
-          <t>NX235/55R19</t>
+          <t>HK235/55R19</t>
         </is>
       </c>
       <c r="D202" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E202" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F202" s="5">
         <v>0</v>
@@ -6980,7 +6980,7 @@
         <v>0</v>
       </c>
       <c r="H202" s="6">
-        <v>600</v>
+        <v>630</v>
       </c>
     </row>
     <row outlineLevel="0" r="203">
@@ -6991,22 +6991,22 @@
       </c>
       <c r="B203" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C203" s="4" t="inlineStr">
         <is>
-          <t>RD235/55R19</t>
+          <t>LF235/55R19</t>
         </is>
       </c>
       <c r="D203" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E203" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F203" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G203" s="5">
         <v>0</v>
@@ -7018,24 +7018,24 @@
     <row outlineLevel="0" r="204">
       <c r="A204" s="4" t="inlineStr">
         <is>
-          <t>235/60R16</t>
+          <t>235/55R19</t>
         </is>
       </c>
       <c r="B204" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C204" s="4" t="inlineStr">
         <is>
-          <t>HK235/60R16</t>
+          <t>NX235/55R19</t>
         </is>
       </c>
       <c r="D204" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E204" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F204" s="5">
         <v>0</v>
@@ -7044,33 +7044,33 @@
         <v>0</v>
       </c>
       <c r="H204" s="6">
-        <v>430</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="205">
       <c r="A205" s="4" t="inlineStr">
         <is>
-          <t>235/60R17</t>
+          <t>235/55R19</t>
         </is>
       </c>
       <c r="B205" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C205" s="4" t="inlineStr">
         <is>
-          <t>HK235/60R17</t>
+          <t>RD235/55R19</t>
         </is>
       </c>
       <c r="D205" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E205" s="5">
         <v>0</v>
       </c>
       <c r="F205" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G205" s="5">
         <v>0</v>
@@ -7082,24 +7082,24 @@
     <row outlineLevel="0" r="206">
       <c r="A206" s="4" t="inlineStr">
         <is>
-          <t>235/60R18</t>
+          <t>235/60R16</t>
         </is>
       </c>
       <c r="B206" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C206" s="4" t="inlineStr">
         <is>
-          <t>GD235/60R18</t>
+          <t>HK235/60R16</t>
         </is>
       </c>
       <c r="D206" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E206" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F206" s="5">
         <v>0</v>
@@ -7108,13 +7108,13 @@
         <v>0</v>
       </c>
       <c r="H206" s="6">
-        <v>680</v>
+        <v>430</v>
       </c>
     </row>
     <row outlineLevel="0" r="207">
       <c r="A207" s="4" t="inlineStr">
         <is>
-          <t>235/60R18</t>
+          <t>235/60R17</t>
         </is>
       </c>
       <c r="B207" s="4" t="inlineStr">
@@ -7124,29 +7124,29 @@
       </c>
       <c r="C207" s="4" t="inlineStr">
         <is>
-          <t>HK235/60R18</t>
+          <t>HK235/60R17</t>
         </is>
       </c>
       <c r="D207" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E207" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F207" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G207" s="5">
         <v>0</v>
       </c>
       <c r="H207" s="6">
-        <v>550</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="208">
       <c r="A208" s="4" t="inlineStr">
         <is>
-          <t>245/40R17</t>
+          <t>235/60R18</t>
         </is>
       </c>
       <c r="B208" s="4" t="inlineStr">
@@ -7156,14 +7156,14 @@
       </c>
       <c r="C208" s="4" t="inlineStr">
         <is>
-          <t>GD245/40R17</t>
+          <t>GD235/60R18</t>
         </is>
       </c>
       <c r="D208" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E208" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F208" s="5">
         <v>0</v>
@@ -7172,23 +7172,23 @@
         <v>0</v>
       </c>
       <c r="H208" s="6">
-        <v>400</v>
+        <v>680</v>
       </c>
     </row>
     <row outlineLevel="0" r="209">
       <c r="A209" s="4" t="inlineStr">
         <is>
-          <t>245/40R18</t>
+          <t>235/60R18</t>
         </is>
       </c>
       <c r="B209" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C209" s="4" t="inlineStr">
         <is>
-          <t>GD245/40R18</t>
+          <t>HK235/60R18</t>
         </is>
       </c>
       <c r="D209" s="5">
@@ -7204,30 +7204,30 @@
         <v>0</v>
       </c>
       <c r="H209" s="6">
-        <v>620</v>
+        <v>550</v>
       </c>
     </row>
     <row outlineLevel="0" r="210">
       <c r="A210" s="4" t="inlineStr">
         <is>
-          <t>245/40R19</t>
+          <t>245/40R17</t>
         </is>
       </c>
       <c r="B210" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C210" s="4" t="inlineStr">
         <is>
-          <t>HK245/40R19</t>
+          <t>GD245/40R17</t>
         </is>
       </c>
       <c r="D210" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E210" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F210" s="5">
         <v>0</v>
@@ -7236,62 +7236,62 @@
         <v>0</v>
       </c>
       <c r="H210" s="6">
-        <v>750</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="211">
       <c r="A211" s="4" t="inlineStr">
         <is>
-          <t>245/40R20</t>
+          <t>245/40R18</t>
         </is>
       </c>
       <c r="B211" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C211" s="4" t="inlineStr">
         <is>
-          <t>CT245/40R20</t>
+          <t>GD245/40R18</t>
         </is>
       </c>
       <c r="D211" s="5">
         <v>2</v>
       </c>
       <c r="E211" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F211" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G211" s="5">
         <v>0</v>
       </c>
       <c r="H211" s="6">
-        <v>1050</v>
+        <v>620</v>
       </c>
     </row>
     <row outlineLevel="0" r="212">
       <c r="A212" s="4" t="inlineStr">
         <is>
-          <t>245/40R20</t>
+          <t>245/40R19</t>
         </is>
       </c>
       <c r="B212" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C212" s="4" t="inlineStr">
         <is>
-          <t>NX245/40R20</t>
+          <t>HK245/40R19</t>
         </is>
       </c>
       <c r="D212" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E212" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F212" s="5">
         <v>0</v>
@@ -7300,62 +7300,62 @@
         <v>0</v>
       </c>
       <c r="H212" s="6">
-        <v>580</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="213">
       <c r="A213" s="4" t="inlineStr">
         <is>
-          <t>245/45R17</t>
+          <t>245/40R20</t>
         </is>
       </c>
       <c r="B213" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C213" s="4" t="inlineStr">
         <is>
-          <t>HK245/45R17</t>
+          <t>CT245/40R20</t>
         </is>
       </c>
       <c r="D213" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E213" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F213" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G213" s="5">
         <v>0</v>
       </c>
       <c r="H213" s="6">
-        <v>430</v>
+        <v>1050</v>
       </c>
     </row>
     <row outlineLevel="0" r="214">
       <c r="A214" s="4" t="inlineStr">
         <is>
-          <t>245/45R18</t>
+          <t>245/40R20</t>
         </is>
       </c>
       <c r="B214" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C214" s="4" t="inlineStr">
         <is>
-          <t>CT245/45R18</t>
+          <t>NX245/40R20</t>
         </is>
       </c>
       <c r="D214" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E214" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F214" s="5">
         <v>0</v>
@@ -7364,30 +7364,30 @@
         <v>0</v>
       </c>
       <c r="H214" s="6">
-        <v>650</v>
+        <v>580</v>
       </c>
     </row>
     <row outlineLevel="0" r="215">
       <c r="A215" s="4" t="inlineStr">
         <is>
-          <t>245/45R18</t>
+          <t>245/45R17</t>
         </is>
       </c>
       <c r="B215" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C215" s="4" t="inlineStr">
         <is>
-          <t>GD245/45R18</t>
+          <t>HK245/45R17</t>
         </is>
       </c>
       <c r="D215" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E215" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F215" s="5">
         <v>0</v>
@@ -7396,7 +7396,7 @@
         <v>0</v>
       </c>
       <c r="H215" s="6">
-        <v>600</v>
+        <v>430</v>
       </c>
     </row>
     <row outlineLevel="0" r="216">
@@ -7407,12 +7407,12 @@
       </c>
       <c r="B216" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C216" s="4" t="inlineStr">
         <is>
-          <t>HK245/45R18</t>
+          <t>CT245/45R18</t>
         </is>
       </c>
       <c r="D216" s="5">
@@ -7428,13 +7428,13 @@
         <v>0</v>
       </c>
       <c r="H216" s="6">
-        <v>500</v>
+        <v>650</v>
       </c>
     </row>
     <row outlineLevel="0" r="217">
       <c r="A217" s="4" t="inlineStr">
         <is>
-          <t>245/45R18RF</t>
+          <t>245/45R18</t>
         </is>
       </c>
       <c r="B217" s="4" t="inlineStr">
@@ -7444,14 +7444,14 @@
       </c>
       <c r="C217" s="4" t="inlineStr">
         <is>
-          <t>GD245/45R18RF</t>
+          <t>GD245/45R18</t>
         </is>
       </c>
       <c r="D217" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E217" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F217" s="5">
         <v>0</v>
@@ -7460,30 +7460,30 @@
         <v>0</v>
       </c>
       <c r="H217" s="6">
-        <v>720</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="218">
       <c r="A218" s="4" t="inlineStr">
         <is>
-          <t>245/45R19</t>
+          <t>245/45R18</t>
         </is>
       </c>
       <c r="B218" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C218" s="4" t="inlineStr">
         <is>
-          <t>BR245/45R19</t>
+          <t>HK245/45R18</t>
         </is>
       </c>
       <c r="D218" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E218" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F218" s="5">
         <v>0</v>
@@ -7492,190 +7492,190 @@
         <v>0</v>
       </c>
       <c r="H218" s="6">
-        <v>790</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="219">
       <c r="A219" s="4" t="inlineStr">
         <is>
-          <t>245/45R19</t>
+          <t>245/45R18RF</t>
         </is>
       </c>
       <c r="B219" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C219" s="4" t="inlineStr">
         <is>
-          <t>RD245/45R19</t>
+          <t>GD245/45R18RF</t>
         </is>
       </c>
       <c r="D219" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E219" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F219" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G219" s="5">
         <v>0</v>
       </c>
       <c r="H219" s="6">
-        <v>450</v>
+        <v>720</v>
       </c>
     </row>
     <row outlineLevel="0" r="220">
       <c r="A220" s="4" t="inlineStr">
         <is>
-          <t>245/45R20</t>
+          <t>245/45R19</t>
         </is>
       </c>
       <c r="B220" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C220" s="4" t="inlineStr">
         <is>
-          <t>HK245/45R20</t>
+          <t>BR245/45R19</t>
         </is>
       </c>
       <c r="D220" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E220" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F220" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G220" s="5">
         <v>0</v>
       </c>
       <c r="H220" s="6">
-        <v>750</v>
+        <v>790</v>
       </c>
     </row>
     <row outlineLevel="0" r="221">
       <c r="A221" s="4" t="inlineStr">
         <is>
-          <t>245/65R17</t>
+          <t>245/45R19</t>
         </is>
       </c>
       <c r="B221" s="4" t="inlineStr">
         <is>
-          <t>NEXEN</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C221" s="4" t="inlineStr">
         <is>
-          <t>NX245/65R17</t>
+          <t>RD245/45R19</t>
         </is>
       </c>
       <c r="D221" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E221" s="5">
         <v>0</v>
       </c>
       <c r="F221" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G221" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H221" s="6">
-        <v>600</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="222">
       <c r="A222" s="4" t="inlineStr">
         <is>
-          <t>245/70R16</t>
+          <t>245/45R20</t>
         </is>
       </c>
       <c r="B222" s="4" t="inlineStr">
         <is>
-          <t>LASSA</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C222" s="4" t="inlineStr">
         <is>
-          <t>LS245/70R16</t>
+          <t>HK245/45R20</t>
         </is>
       </c>
       <c r="D222" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E222" s="5">
         <v>0</v>
       </c>
       <c r="F222" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G222" s="5">
         <v>0</v>
       </c>
       <c r="H222" s="6">
-        <v>500</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="223">
       <c r="A223" s="4" t="inlineStr">
         <is>
-          <t>255/35R19</t>
+          <t>245/65R17</t>
         </is>
       </c>
       <c r="B223" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>NEXEN</t>
         </is>
       </c>
       <c r="C223" s="4" t="inlineStr">
         <is>
-          <t>DL255/35R19</t>
+          <t>NX245/65R17</t>
         </is>
       </c>
       <c r="D223" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E223" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F223" s="5">
         <v>0</v>
       </c>
       <c r="G223" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H223" s="6">
-        <v>700</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="224">
       <c r="A224" s="4" t="inlineStr">
         <is>
-          <t>255/35R19RF</t>
+          <t>245/70R16</t>
         </is>
       </c>
       <c r="B224" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>LASSA</t>
         </is>
       </c>
       <c r="C224" s="4" t="inlineStr">
         <is>
-          <t>CT255/35R19RF</t>
+          <t>LS245/70R16</t>
         </is>
       </c>
       <c r="D224" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E224" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F224" s="5">
         <v>0</v>
@@ -7684,23 +7684,23 @@
         <v>0</v>
       </c>
       <c r="H224" s="6">
-        <v>1150</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="225">
       <c r="A225" s="4" t="inlineStr">
         <is>
-          <t>255/35R19RF</t>
+          <t>255/35R19</t>
         </is>
       </c>
       <c r="B225" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C225" s="4" t="inlineStr">
         <is>
-          <t>GD255/35R19RF</t>
+          <t>DL255/35R19</t>
         </is>
       </c>
       <c r="D225" s="5">
@@ -7716,30 +7716,30 @@
         <v>0</v>
       </c>
       <c r="H225" s="6">
-        <v>1150</v>
+        <v>700</v>
       </c>
     </row>
     <row outlineLevel="0" r="226">
       <c r="A226" s="4" t="inlineStr">
         <is>
-          <t>255/40R20</t>
+          <t>255/35R19RF</t>
         </is>
       </c>
       <c r="B226" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C226" s="4" t="inlineStr">
         <is>
-          <t>GD255/40R20</t>
+          <t>CT255/35R19RF</t>
         </is>
       </c>
       <c r="D226" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E226" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F226" s="5">
         <v>0</v>
@@ -7748,30 +7748,30 @@
         <v>0</v>
       </c>
       <c r="H226" s="6">
-        <v>1080</v>
+        <v>1150</v>
       </c>
     </row>
     <row outlineLevel="0" r="227">
       <c r="A227" s="4" t="inlineStr">
         <is>
-          <t>255/45R18</t>
+          <t>255/35R19RF</t>
         </is>
       </c>
       <c r="B227" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C227" s="4" t="inlineStr">
         <is>
-          <t>HK255/45R18</t>
+          <t>GD255/35R19RF</t>
         </is>
       </c>
       <c r="D227" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E227" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F227" s="5">
         <v>0</v>
@@ -7780,77 +7780,77 @@
         <v>0</v>
       </c>
       <c r="H227" s="6">
-        <v>500</v>
+        <v>1150</v>
       </c>
     </row>
     <row outlineLevel="0" r="228">
       <c r="A228" s="4" t="inlineStr">
         <is>
-          <t>255/50R19</t>
+          <t>255/40R20</t>
         </is>
       </c>
       <c r="B228" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C228" s="4" t="inlineStr">
         <is>
-          <t>CT255/50R19</t>
+          <t>GD255/40R20</t>
         </is>
       </c>
       <c r="D228" s="5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E228" s="5">
         <v>0</v>
       </c>
       <c r="F228" s="5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G228" s="5">
         <v>0</v>
       </c>
       <c r="H228" s="6">
-        <v>750</v>
+        <v>1080</v>
       </c>
     </row>
     <row outlineLevel="0" r="229">
       <c r="A229" s="4" t="inlineStr">
         <is>
-          <t>255/50R20</t>
+          <t>255/45R18</t>
         </is>
       </c>
       <c r="B229" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C229" s="4" t="inlineStr">
         <is>
-          <t>CT255/50R20</t>
+          <t>HK255/45R18</t>
         </is>
       </c>
       <c r="D229" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E229" s="5">
         <v>0</v>
       </c>
       <c r="F229" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G229" s="5">
         <v>0</v>
       </c>
       <c r="H229" s="6">
-        <v>900</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="230">
       <c r="A230" s="4" t="inlineStr">
         <is>
-          <t>255/55R19</t>
+          <t>255/50R19</t>
         </is>
       </c>
       <c r="B230" s="4" t="inlineStr">
@@ -7860,17 +7860,17 @@
       </c>
       <c r="C230" s="4" t="inlineStr">
         <is>
-          <t>CT255/55R19</t>
+          <t>CT255/50R19</t>
         </is>
       </c>
       <c r="D230" s="5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E230" s="5">
         <v>0</v>
       </c>
       <c r="F230" s="5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G230" s="5">
         <v>0</v>
@@ -7882,167 +7882,167 @@
     <row outlineLevel="0" r="231">
       <c r="A231" s="4" t="inlineStr">
         <is>
-          <t>255/55R19</t>
+          <t>255/50R20</t>
         </is>
       </c>
       <c r="B231" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C231" s="4" t="inlineStr">
         <is>
-          <t>DL255/55R19</t>
+          <t>CT255/50R20</t>
         </is>
       </c>
       <c r="D231" s="5">
         <v>2</v>
       </c>
       <c r="E231" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F231" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G231" s="5">
         <v>0</v>
       </c>
       <c r="H231" s="6">
-        <v>700</v>
+        <v>900</v>
       </c>
     </row>
     <row outlineLevel="0" r="232">
       <c r="A232" s="4" t="inlineStr">
         <is>
-          <t>255/70R15</t>
+          <t>255/55R19</t>
         </is>
       </c>
       <c r="B232" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C232" s="4" t="inlineStr">
         <is>
-          <t>DL255/70R15</t>
+          <t>CT255/55R19</t>
         </is>
       </c>
       <c r="D232" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E232" s="5">
         <v>0</v>
       </c>
       <c r="F232" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G232" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H232" s="6">
-        <v>550</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="233">
       <c r="A233" s="4" t="inlineStr">
         <is>
-          <t>255/70R16</t>
+          <t>255/55R19</t>
         </is>
       </c>
       <c r="B233" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C233" s="4" t="inlineStr">
         <is>
-          <t>RD255/70R16</t>
+          <t>DL255/55R19</t>
         </is>
       </c>
       <c r="D233" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E233" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F233" s="5">
         <v>0</v>
       </c>
       <c r="G233" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H233" s="6">
-        <v>500</v>
+        <v>700</v>
       </c>
     </row>
     <row outlineLevel="0" r="234">
       <c r="A234" s="4" t="inlineStr">
         <is>
-          <t>265/35R18</t>
+          <t>255/70R15</t>
         </is>
       </c>
       <c r="B234" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C234" s="4" t="inlineStr">
         <is>
-          <t>GD265/35R18</t>
+          <t>DL255/70R15</t>
         </is>
       </c>
       <c r="D234" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E234" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F234" s="5">
         <v>0</v>
       </c>
       <c r="G234" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H234" s="6">
-        <v>700</v>
+        <v>550</v>
       </c>
     </row>
     <row outlineLevel="0" r="235">
       <c r="A235" s="4" t="inlineStr">
         <is>
-          <t>265/50R20</t>
+          <t>255/70R16</t>
         </is>
       </c>
       <c r="B235" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C235" s="4" t="inlineStr">
         <is>
-          <t>GD265/50R20</t>
+          <t>RD255/70R16</t>
         </is>
       </c>
       <c r="D235" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E235" s="5">
         <v>0</v>
       </c>
       <c r="F235" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G235" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H235" s="6">
-        <v>1150</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="236">
       <c r="A236" s="4" t="inlineStr">
         <is>
-          <t>265/65R17</t>
+          <t>265/35R18</t>
         </is>
       </c>
       <c r="B236" s="4" t="inlineStr">
@@ -8052,14 +8052,14 @@
       </c>
       <c r="C236" s="4" t="inlineStr">
         <is>
-          <t>GD265/65R17</t>
+          <t>GD265/35R18</t>
         </is>
       </c>
       <c r="D236" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E236" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F236" s="5">
         <v>0</v>
@@ -8068,45 +8068,45 @@
         <v>0</v>
       </c>
       <c r="H236" s="6">
-        <v>750</v>
+        <v>700</v>
       </c>
     </row>
     <row outlineLevel="0" r="237">
       <c r="A237" s="4" t="inlineStr">
         <is>
-          <t>265/65R17</t>
+          <t>265/50R20</t>
         </is>
       </c>
       <c r="B237" s="4" t="inlineStr">
         <is>
-          <t>LASSA</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C237" s="4" t="inlineStr">
         <is>
-          <t>LS265/65R17</t>
+          <t>GD265/50R20</t>
         </is>
       </c>
       <c r="D237" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E237" s="5">
         <v>0</v>
       </c>
       <c r="F237" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G237" s="5">
         <v>0</v>
       </c>
       <c r="H237" s="6">
-        <v>650</v>
+        <v>1150</v>
       </c>
     </row>
     <row outlineLevel="0" r="238">
       <c r="A238" s="4" t="inlineStr">
         <is>
-          <t>275/35R19RF</t>
+          <t>265/65R17</t>
         </is>
       </c>
       <c r="B238" s="4" t="inlineStr">
@@ -8116,14 +8116,14 @@
       </c>
       <c r="C238" s="4" t="inlineStr">
         <is>
-          <t>GD275/35R19RF</t>
+          <t>GD265/65R17</t>
         </is>
       </c>
       <c r="D238" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E238" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F238" s="5">
         <v>0</v>
@@ -8132,141 +8132,141 @@
         <v>0</v>
       </c>
       <c r="H238" s="6">
-        <v>1300</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="239">
       <c r="A239" s="4" t="inlineStr">
         <is>
-          <t>275/35R20</t>
+          <t>265/65R17</t>
         </is>
       </c>
       <c r="B239" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>LASSA</t>
         </is>
       </c>
       <c r="C239" s="4" t="inlineStr">
         <is>
-          <t>CT275/35R20</t>
+          <t>LS265/65R17</t>
         </is>
       </c>
       <c r="D239" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E239" s="5">
         <v>0</v>
       </c>
       <c r="F239" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G239" s="5">
         <v>0</v>
       </c>
       <c r="H239" s="6">
-        <v>980</v>
+        <v>650</v>
       </c>
     </row>
     <row outlineLevel="0" r="240">
       <c r="A240" s="4" t="inlineStr">
         <is>
-          <t>275/40R20</t>
+          <t>275/35R19RF</t>
         </is>
       </c>
       <c r="B240" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C240" s="4" t="inlineStr">
         <is>
-          <t>HK275/40R20</t>
+          <t>GD275/35R19RF</t>
         </is>
       </c>
       <c r="D240" s="5">
         <v>2</v>
       </c>
       <c r="E240" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F240" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G240" s="5">
         <v>0</v>
       </c>
       <c r="H240" s="6">
-        <v>770</v>
+        <v>1300</v>
       </c>
     </row>
     <row outlineLevel="0" r="241">
       <c r="A241" s="4" t="inlineStr">
         <is>
-          <t>275/40R22</t>
+          <t>275/35R20</t>
         </is>
       </c>
       <c r="B241" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C241" s="4" t="inlineStr">
         <is>
-          <t>GD275/40R22</t>
+          <t>CT275/35R20</t>
         </is>
       </c>
       <c r="D241" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E241" s="5">
         <v>0</v>
       </c>
       <c r="F241" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G241" s="5">
         <v>0</v>
       </c>
       <c r="H241" s="6">
-        <v>1200</v>
+        <v>980</v>
       </c>
     </row>
     <row outlineLevel="0" r="242">
       <c r="A242" s="4" t="inlineStr">
         <is>
-          <t>275/45R20</t>
+          <t>275/40R20</t>
         </is>
       </c>
       <c r="B242" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C242" s="4" t="inlineStr">
         <is>
-          <t>CT275/45R20</t>
+          <t>HK275/40R20</t>
         </is>
       </c>
       <c r="D242" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E242" s="5">
         <v>0</v>
       </c>
       <c r="F242" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G242" s="5">
         <v>0</v>
       </c>
       <c r="H242" s="6">
-        <v>900</v>
+        <v>770</v>
       </c>
     </row>
     <row outlineLevel="0" r="243">
       <c r="A243" s="4" t="inlineStr">
         <is>
-          <t>275/45R21</t>
+          <t>275/40R22</t>
         </is>
       </c>
       <c r="B243" s="4" t="inlineStr">
@@ -8276,7 +8276,7 @@
       </c>
       <c r="C243" s="4" t="inlineStr">
         <is>
-          <t>GD275/45R21</t>
+          <t>GD275/40R22</t>
         </is>
       </c>
       <c r="D243" s="5">
@@ -8292,55 +8292,55 @@
         <v>0</v>
       </c>
       <c r="H243" s="6">
-        <v>1100</v>
+        <v>1200</v>
       </c>
     </row>
     <row outlineLevel="0" r="244">
       <c r="A244" s="4" t="inlineStr">
         <is>
-          <t>275/50R21</t>
+          <t>275/45R20</t>
         </is>
       </c>
       <c r="B244" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C244" s="4" t="inlineStr">
         <is>
-          <t>GD275/50R21</t>
+          <t>CT275/45R20</t>
         </is>
       </c>
       <c r="D244" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E244" s="5">
         <v>0</v>
       </c>
       <c r="F244" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G244" s="5">
         <v>0</v>
       </c>
       <c r="H244" s="6">
-        <v>1300</v>
+        <v>900</v>
       </c>
     </row>
     <row outlineLevel="0" r="245">
       <c r="A245" s="4" t="inlineStr">
         <is>
-          <t>285/35R22</t>
+          <t>275/45R21</t>
         </is>
       </c>
       <c r="B245" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C245" s="4" t="inlineStr">
         <is>
-          <t>CT285/35R22</t>
+          <t>GD275/45R21</t>
         </is>
       </c>
       <c r="D245" s="5">
@@ -8356,23 +8356,23 @@
         <v>0</v>
       </c>
       <c r="H245" s="6">
-        <v>1600</v>
+        <v>1100</v>
       </c>
     </row>
     <row outlineLevel="0" r="246">
       <c r="A246" s="4" t="inlineStr">
         <is>
-          <t>295/35R21</t>
+          <t>275/50R21</t>
         </is>
       </c>
       <c r="B246" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C246" s="4" t="inlineStr">
         <is>
-          <t>CT295/35R21</t>
+          <t>GD275/50R21</t>
         </is>
       </c>
       <c r="D246" s="5">
@@ -8388,45 +8388,45 @@
         <v>0</v>
       </c>
       <c r="H246" s="6">
-        <v>1150</v>
+        <v>1300</v>
       </c>
     </row>
     <row outlineLevel="0" r="247">
       <c r="A247" s="4" t="inlineStr">
         <is>
-          <t>295/35R21</t>
+          <t>285/35R22</t>
         </is>
       </c>
       <c r="B247" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C247" s="4" t="inlineStr">
         <is>
-          <t>GD295/35R21</t>
+          <t>CT285/35R22</t>
         </is>
       </c>
       <c r="D247" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E247" s="5">
         <v>0</v>
       </c>
       <c r="F247" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G247" s="5">
         <v>0</v>
       </c>
       <c r="H247" s="6">
-        <v>980</v>
+        <v>1600</v>
       </c>
     </row>
     <row outlineLevel="0" r="248">
       <c r="A248" s="4" t="inlineStr">
         <is>
-          <t>315/30R22</t>
+          <t>295/35R21</t>
         </is>
       </c>
       <c r="B248" s="4" t="inlineStr">
@@ -8436,54 +8436,118 @@
       </c>
       <c r="C248" s="4" t="inlineStr">
         <is>
-          <t>CT315/30R22</t>
+          <t>CT295/35R21</t>
         </is>
       </c>
       <c r="D248" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E248" s="5">
         <v>0</v>
       </c>
       <c r="F248" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G248" s="5">
         <v>0</v>
       </c>
       <c r="H248" s="6">
-        <v>1700</v>
+        <v>1150</v>
       </c>
     </row>
     <row outlineLevel="0" r="249">
       <c r="A249" s="4" t="inlineStr">
         <is>
-          <t>500R12</t>
+          <t>295/35R21</t>
         </is>
       </c>
       <c r="B249" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C249" s="4" t="inlineStr">
         <is>
-          <t>RD500R12</t>
+          <t>GD295/35R21</t>
         </is>
       </c>
       <c r="D249" s="5">
         <v>3</v>
       </c>
       <c r="E249" s="5">
+        <v>0</v>
+      </c>
+      <c r="F249" s="5">
         <v>3</v>
       </c>
-      <c r="F249" s="5">
-        <v>0</v>
-      </c>
       <c r="G249" s="5">
         <v>0</v>
       </c>
       <c r="H249" s="6">
+        <v>980</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="250">
+      <c r="A250" s="4" t="inlineStr">
+        <is>
+          <t>315/30R22</t>
+        </is>
+      </c>
+      <c r="B250" s="4" t="inlineStr">
+        <is>
+          <t>CONTINENTAL</t>
+        </is>
+      </c>
+      <c r="C250" s="4" t="inlineStr">
+        <is>
+          <t>CT315/30R22</t>
+        </is>
+      </c>
+      <c r="D250" s="5">
+        <v>0</v>
+      </c>
+      <c r="E250" s="5">
+        <v>0</v>
+      </c>
+      <c r="F250" s="5">
+        <v>0</v>
+      </c>
+      <c r="G250" s="5">
+        <v>0</v>
+      </c>
+      <c r="H250" s="6">
+        <v>1700</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="251">
+      <c r="A251" s="4" t="inlineStr">
+        <is>
+          <t>500R12</t>
+        </is>
+      </c>
+      <c r="B251" s="4" t="inlineStr">
+        <is>
+          <t>RADIAL</t>
+        </is>
+      </c>
+      <c r="C251" s="4" t="inlineStr">
+        <is>
+          <t>RD500R12</t>
+        </is>
+      </c>
+      <c r="D251" s="5">
+        <v>3</v>
+      </c>
+      <c r="E251" s="5">
+        <v>3</v>
+      </c>
+      <c r="F251" s="5">
+        <v>0</v>
+      </c>
+      <c r="G251" s="5">
+        <v>0</v>
+      </c>
+      <c r="H251" s="6">
         <v>300</v>
       </c>
     </row>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -731,10 +731,10 @@
         <v>49</v>
       </c>
       <c r="E7" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F7" s="5">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G7" s="5">
         <v>4</v>
@@ -795,10 +795,10 @@
         <v>41</v>
       </c>
       <c r="E9" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F9" s="5">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G9" s="5">
         <v>8</v>
@@ -1339,10 +1339,10 @@
         <v>63</v>
       </c>
       <c r="E26" s="5">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F26" s="5">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G26" s="5">
         <v>10</v>
@@ -1720,7 +1720,7 @@
         </is>
       </c>
       <c r="D38" s="5">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E38" s="5">
         <v>4</v>
@@ -1729,7 +1729,7 @@
         <v>29</v>
       </c>
       <c r="G38" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H38" s="6">
         <v>340</v>
@@ -1944,13 +1944,13 @@
         </is>
       </c>
       <c r="D45" s="5">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E45" s="5">
         <v>5</v>
       </c>
       <c r="F45" s="5">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G45" s="5">
         <v>5</v>
@@ -2171,10 +2171,10 @@
         <v>130</v>
       </c>
       <c r="E52" s="5">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F52" s="5">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="G52" s="5">
         <v>11</v>
@@ -2235,10 +2235,10 @@
         <v>139</v>
       </c>
       <c r="E54" s="5">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F54" s="5">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="G54" s="5">
         <v>6</v>
@@ -2424,16 +2424,16 @@
         </is>
       </c>
       <c r="D60" s="5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E60" s="5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F60" s="5">
         <v>0</v>
       </c>
       <c r="G60" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H60" s="6">
         <v>230</v>
@@ -2488,7 +2488,7 @@
         </is>
       </c>
       <c r="D62" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E62" s="5">
         <v>4</v>
@@ -2497,7 +2497,7 @@
         <v>0</v>
       </c>
       <c r="G62" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H62" s="6">
         <v>240</v>
@@ -2523,13 +2523,13 @@
         <v>5</v>
       </c>
       <c r="E63" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F63" s="5">
         <v>0</v>
       </c>
       <c r="G63" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H63" s="6">
         <v>270</v>
@@ -2872,13 +2872,13 @@
         </is>
       </c>
       <c r="D74" s="5">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E74" s="5">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F74" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G74" s="5">
         <v>3</v>
@@ -3000,10 +3000,10 @@
         </is>
       </c>
       <c r="D78" s="5">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E78" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F78" s="5">
         <v>48</v>
@@ -3707,10 +3707,10 @@
         <v>22</v>
       </c>
       <c r="E100" s="5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F100" s="5">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G100" s="5">
         <v>2</v>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -792,10 +792,10 @@
         </is>
       </c>
       <c r="D9" s="5">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E9" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F9" s="5">
         <v>29</v>
@@ -1720,10 +1720,10 @@
         </is>
       </c>
       <c r="D38" s="5">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E38" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F38" s="5">
         <v>29</v>
@@ -2392,10 +2392,10 @@
         </is>
       </c>
       <c r="D59" s="5">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E59" s="5">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F59" s="5">
         <v>0</v>
@@ -3256,7 +3256,7 @@
         </is>
       </c>
       <c r="D86" s="5">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E86" s="5">
         <v>3</v>
@@ -3265,7 +3265,7 @@
         <v>5</v>
       </c>
       <c r="G86" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H86" s="6">
         <v>350</v>
@@ -3864,10 +3864,10 @@
         </is>
       </c>
       <c r="D105" s="5">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E105" s="5">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F105" s="5">
         <v>34</v>
@@ -4888,10 +4888,10 @@
         </is>
       </c>
       <c r="D137" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E137" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F137" s="5">
         <v>0</v>
@@ -5496,13 +5496,13 @@
         </is>
       </c>
       <c r="D156" s="5">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E156" s="5">
         <v>4</v>
       </c>
       <c r="F156" s="5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G156" s="5">
         <v>4</v>
@@ -5976,10 +5976,10 @@
         </is>
       </c>
       <c r="D171" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E171" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F171" s="5">
         <v>0</v>
@@ -6168,10 +6168,10 @@
         </is>
       </c>
       <c r="D177" s="5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E177" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F177" s="5">
         <v>3</v>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -2232,10 +2232,10 @@
         </is>
       </c>
       <c r="D54" s="5">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E54" s="5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F54" s="5">
         <v>125</v>
@@ -2616,7 +2616,7 @@
         </is>
       </c>
       <c r="D66" s="5">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E66" s="5">
         <v>4</v>
@@ -2625,7 +2625,7 @@
         <v>14</v>
       </c>
       <c r="G66" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H66" s="6">
         <v>260</v>
@@ -4984,10 +4984,10 @@
         </is>
       </c>
       <c r="D140" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E140" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F140" s="5">
         <v>0</v>
@@ -5784,10 +5784,10 @@
         </is>
       </c>
       <c r="D165" s="5">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E165" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F165" s="5">
         <v>11</v>

--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -496,7 +496,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H251"/>
+  <dimension ref="A1:H252"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col customWidth="true" min="1" max="1" width="13.8359375"/>
@@ -795,10 +795,10 @@
         <v>37</v>
       </c>
       <c r="E9" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F9" s="5">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G9" s="5">
         <v>8</v>
@@ -1211,10 +1211,10 @@
         <v>89</v>
       </c>
       <c r="E22" s="5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F22" s="5">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G22" s="5">
         <v>12</v>
@@ -1723,10 +1723,10 @@
         <v>34</v>
       </c>
       <c r="E38" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F38" s="5">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G38" s="5">
         <v>2</v>
@@ -2171,10 +2171,10 @@
         <v>130</v>
       </c>
       <c r="E52" s="5">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="F52" s="5">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="G52" s="5">
         <v>11</v>
@@ -2235,10 +2235,10 @@
         <v>138</v>
       </c>
       <c r="E54" s="5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F54" s="5">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G54" s="5">
         <v>6</v>
@@ -2363,10 +2363,10 @@
         <v>26</v>
       </c>
       <c r="E58" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F58" s="5">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G58" s="5">
         <v>4</v>
@@ -2456,16 +2456,16 @@
         </is>
       </c>
       <c r="D61" s="5">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E61" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F61" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G61" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H61" s="6">
         <v>280</v>
@@ -3003,10 +3003,10 @@
         <v>59</v>
       </c>
       <c r="E78" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F78" s="5">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G78" s="5">
         <v>8</v>
@@ -3163,10 +3163,10 @@
         <v>87</v>
       </c>
       <c r="E83" s="5">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F83" s="5">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G83" s="5">
         <v>11</v>
@@ -3256,13 +3256,13 @@
         </is>
       </c>
       <c r="D86" s="5">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E86" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F86" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G86" s="5">
         <v>1</v>
@@ -3896,10 +3896,10 @@
         </is>
       </c>
       <c r="D106" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E106" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F106" s="5">
         <v>0</v>
@@ -4315,10 +4315,10 @@
         <v>7</v>
       </c>
       <c r="E119" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F119" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G119" s="5">
         <v>1</v>
@@ -4667,13 +4667,13 @@
         <v>5</v>
       </c>
       <c r="E130" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F130" s="5">
         <v>0</v>
       </c>
       <c r="G130" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H130" s="6">
         <v>470</v>
@@ -4760,10 +4760,10 @@
         </is>
       </c>
       <c r="D133" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E133" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F133" s="5">
         <v>0</v>
@@ -4952,10 +4952,10 @@
         </is>
       </c>
       <c r="D139" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E139" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F139" s="5">
         <v>0</v>
@@ -5019,13 +5019,13 @@
         <v>1</v>
       </c>
       <c r="E141" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F141" s="5">
         <v>0</v>
       </c>
       <c r="G141" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H141" s="6">
         <v>350</v>
@@ -5051,13 +5051,13 @@
         <v>6</v>
       </c>
       <c r="E142" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F142" s="5">
         <v>0</v>
       </c>
       <c r="G142" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H142" s="6">
         <v>330</v>
@@ -5179,13 +5179,13 @@
         <v>1</v>
       </c>
       <c r="E146" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F146" s="5">
         <v>0</v>
       </c>
       <c r="G146" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H146" s="6">
         <v>380</v>
@@ -5624,13 +5624,13 @@
         </is>
       </c>
       <c r="D160" s="5">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="E160" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F160" s="5">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G160" s="5">
         <v>0</v>
@@ -5784,13 +5784,13 @@
         </is>
       </c>
       <c r="D165" s="5">
-        <v>19</v>
+        <v>69</v>
       </c>
       <c r="E165" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F165" s="5">
-        <v>11</v>
+        <v>60</v>
       </c>
       <c r="G165" s="5">
         <v>4</v>
@@ -5816,10 +5816,10 @@
         </is>
       </c>
       <c r="D166" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E166" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F166" s="5">
         <v>0</v>
@@ -5834,33 +5834,33 @@
     <row outlineLevel="0" r="167">
       <c r="A167" s="4" t="inlineStr">
         <is>
-          <t>225/45R18</t>
+          <t>225/45R17</t>
         </is>
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>SEMPERIT</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>DL225/45R18</t>
+          <t>SP225/45R17</t>
         </is>
       </c>
       <c r="D167" s="5">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="E167" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F167" s="5">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G167" s="5">
         <v>0</v>
       </c>
       <c r="H167" s="6">
-        <v>500</v>
+        <v>350</v>
       </c>
     </row>
     <row outlineLevel="0" r="168">
@@ -5871,28 +5871,28 @@
       </c>
       <c r="B168" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C168" s="4" t="inlineStr">
         <is>
-          <t>GD225/45R18</t>
+          <t>DL225/45R18</t>
         </is>
       </c>
       <c r="D168" s="5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E168" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F168" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G168" s="5">
         <v>0</v>
       </c>
       <c r="H168" s="6">
-        <v>550</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="169">
@@ -5903,28 +5903,28 @@
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>HK225/45R18</t>
+          <t>GD225/45R18</t>
         </is>
       </c>
       <c r="D169" s="5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E169" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F169" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G169" s="5">
         <v>0</v>
       </c>
       <c r="H169" s="6">
-        <v>450</v>
+        <v>550</v>
       </c>
     </row>
     <row outlineLevel="0" r="170">
@@ -5935,19 +5935,19 @@
       </c>
       <c r="B170" s="4" t="inlineStr">
         <is>
-          <t>LUFEN</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C170" s="4" t="inlineStr">
         <is>
-          <t>LF225/45R18</t>
+          <t>HK225/45R18</t>
         </is>
       </c>
       <c r="D170" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E170" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F170" s="5">
         <v>0</v>
@@ -5956,59 +5956,59 @@
         <v>0</v>
       </c>
       <c r="H170" s="6">
-        <v>420</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="171">
       <c r="A171" s="4" t="inlineStr">
         <is>
-          <t>225/45R18RF</t>
+          <t>225/45R18</t>
         </is>
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>LUFEN</t>
         </is>
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t>GD225/45R18RF</t>
+          <t>LF225/45R18</t>
         </is>
       </c>
       <c r="D171" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E171" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F171" s="5">
         <v>0</v>
       </c>
       <c r="G171" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H171" s="6">
-        <v>720</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="172">
       <c r="A172" s="4" t="inlineStr">
         <is>
-          <t>225/45R19</t>
+          <t>225/45R18RF</t>
         </is>
       </c>
       <c r="B172" s="4" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C172" s="4" t="inlineStr">
         <is>
-          <t>CT225/45R19</t>
+          <t>GD225/45R18RF</t>
         </is>
       </c>
       <c r="D172" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E172" s="5">
         <v>1</v>
@@ -6017,10 +6017,10 @@
         <v>0</v>
       </c>
       <c r="G172" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H172" s="6">
-        <v>780</v>
+        <v>720</v>
       </c>
     </row>
     <row outlineLevel="0" r="173">
@@ -6031,19 +6031,19 @@
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>GD225/45R19</t>
+          <t>CT225/45R19</t>
         </is>
       </c>
       <c r="D173" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E173" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F173" s="5">
         <v>0</v>
@@ -6052,7 +6052,7 @@
         <v>0</v>
       </c>
       <c r="H173" s="6">
-        <v>750</v>
+        <v>780</v>
       </c>
     </row>
     <row outlineLevel="0" r="174">
@@ -6063,51 +6063,51 @@
       </c>
       <c r="B174" s="4" t="inlineStr">
         <is>
-          <t>LASSA</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C174" s="4" t="inlineStr">
         <is>
-          <t>LS225/45R19</t>
+          <t>GD225/45R19</t>
         </is>
       </c>
       <c r="D174" s="5">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E174" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F174" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G174" s="5">
         <v>0</v>
       </c>
       <c r="H174" s="6">
-        <v>520</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="175">
       <c r="A175" s="4" t="inlineStr">
         <is>
-          <t>225/50R17</t>
+          <t>225/45R19</t>
         </is>
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>LASSA</t>
         </is>
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>BR225/50R17</t>
+          <t>LS225/45R19</t>
         </is>
       </c>
       <c r="D175" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E175" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F175" s="5">
         <v>0</v>
@@ -6116,7 +6116,7 @@
         <v>0</v>
       </c>
       <c r="H175" s="6">
-        <v>600</v>
+        <v>520</v>
       </c>
     </row>
     <row outlineLevel="0" r="176">
@@ -6127,28 +6127,28 @@
       </c>
       <c r="B176" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C176" s="4" t="inlineStr">
         <is>
-          <t>GD225/50R17</t>
+          <t>BR225/50R17</t>
         </is>
       </c>
       <c r="D176" s="5">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E176" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F176" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G176" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H176" s="6">
-        <v>500</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="177">
@@ -6159,60 +6159,60 @@
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>HK225/50R17</t>
+          <t>GD225/50R17</t>
         </is>
       </c>
       <c r="D177" s="5">
         <v>8</v>
       </c>
       <c r="E177" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F177" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G177" s="5">
         <v>2</v>
       </c>
       <c r="H177" s="6">
-        <v>400</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="178">
       <c r="A178" s="4" t="inlineStr">
         <is>
-          <t>225/55R16</t>
+          <t>225/50R17</t>
         </is>
       </c>
       <c r="B178" s="4" t="inlineStr">
         <is>
-          <t>DUNLOP</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C178" s="4" t="inlineStr">
         <is>
-          <t>DL225/55R16</t>
+          <t>HK225/50R17</t>
         </is>
       </c>
       <c r="D178" s="5">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E178" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F178" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G178" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H178" s="6">
-        <v>450</v>
+        <v>400</v>
       </c>
     </row>
     <row outlineLevel="0" r="179">
@@ -6223,19 +6223,19 @@
       </c>
       <c r="B179" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>DUNLOP</t>
         </is>
       </c>
       <c r="C179" s="4" t="inlineStr">
         <is>
-          <t>GD225/55R16</t>
+          <t>DL225/55R16</t>
         </is>
       </c>
       <c r="D179" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E179" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F179" s="5">
         <v>0</v>
@@ -6244,30 +6244,30 @@
         <v>0</v>
       </c>
       <c r="H179" s="6">
-        <v>420</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="180">
       <c r="A180" s="4" t="inlineStr">
         <is>
-          <t>225/55R17</t>
+          <t>225/55R16</t>
         </is>
       </c>
       <c r="B180" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C180" s="4" t="inlineStr">
         <is>
-          <t>HK225/55R17</t>
+          <t>GD225/55R16</t>
         </is>
       </c>
       <c r="D180" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E180" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F180" s="5">
         <v>0</v>
@@ -6276,71 +6276,71 @@
         <v>0</v>
       </c>
       <c r="H180" s="6">
-        <v>430</v>
+        <v>420</v>
       </c>
     </row>
     <row outlineLevel="0" r="181">
       <c r="A181" s="4" t="inlineStr">
         <is>
-          <t>225/55R17RF</t>
+          <t>225/55R17</t>
         </is>
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C181" s="4" t="inlineStr">
         <is>
-          <t>GD225/55R17RF</t>
+          <t>HK225/55R17</t>
         </is>
       </c>
       <c r="D181" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E181" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F181" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G181" s="5">
         <v>0</v>
       </c>
       <c r="H181" s="6">
-        <v>700</v>
+        <v>430</v>
       </c>
     </row>
     <row outlineLevel="0" r="182">
       <c r="A182" s="4" t="inlineStr">
         <is>
-          <t>225/55R18</t>
+          <t>225/55R17RF</t>
         </is>
       </c>
       <c r="B182" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C182" s="4" t="inlineStr">
         <is>
-          <t>HK225/55R18</t>
+          <t>GD225/55R17RF</t>
         </is>
       </c>
       <c r="D182" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E182" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F182" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G182" s="5">
         <v>0</v>
       </c>
       <c r="H182" s="6">
-        <v>500</v>
+        <v>700</v>
       </c>
     </row>
     <row outlineLevel="0" r="183">
@@ -6351,19 +6351,19 @@
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>KUMHO</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C183" s="4" t="inlineStr">
         <is>
-          <t>KM225/55R18</t>
+          <t>HK225/55R18</t>
         </is>
       </c>
       <c r="D183" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E183" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F183" s="5">
         <v>0</v>
@@ -6372,30 +6372,30 @@
         <v>0</v>
       </c>
       <c r="H183" s="6">
-        <v>450</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="184">
       <c r="A184" s="4" t="inlineStr">
         <is>
-          <t>225/55R19</t>
+          <t>225/55R18</t>
         </is>
       </c>
       <c r="B184" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>KUMHO</t>
         </is>
       </c>
       <c r="C184" s="4" t="inlineStr">
         <is>
-          <t>BR225/55R19</t>
+          <t>KM225/55R18</t>
         </is>
       </c>
       <c r="D184" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E184" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F184" s="5">
         <v>0</v>
@@ -6404,7 +6404,7 @@
         <v>0</v>
       </c>
       <c r="H184" s="6">
-        <v>750</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="185">
@@ -6415,19 +6415,19 @@
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C185" s="4" t="inlineStr">
         <is>
-          <t>GD225/55R19</t>
+          <t>BR225/55R19</t>
         </is>
       </c>
       <c r="D185" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E185" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F185" s="5">
         <v>0</v>
@@ -6442,7 +6442,7 @@
     <row outlineLevel="0" r="186">
       <c r="A186" s="4" t="inlineStr">
         <is>
-          <t>225/60R17</t>
+          <t>225/55R19</t>
         </is>
       </c>
       <c r="B186" s="4" t="inlineStr">
@@ -6452,14 +6452,14 @@
       </c>
       <c r="C186" s="4" t="inlineStr">
         <is>
-          <t>GD225/60R17</t>
+          <t>GD225/55R19</t>
         </is>
       </c>
       <c r="D186" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E186" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F186" s="5">
         <v>0</v>
@@ -6468,7 +6468,7 @@
         <v>0</v>
       </c>
       <c r="H186" s="6">
-        <v>500</v>
+        <v>750</v>
       </c>
     </row>
     <row outlineLevel="0" r="187">
@@ -6479,51 +6479,51 @@
       </c>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C187" s="4" t="inlineStr">
         <is>
-          <t>HK225/60R17</t>
+          <t>GD225/60R17</t>
         </is>
       </c>
       <c r="D187" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E187" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F187" s="5">
         <v>0</v>
       </c>
       <c r="G187" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H187" s="6">
-        <v>425</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="188">
       <c r="A188" s="4" t="inlineStr">
         <is>
-          <t>225/60R18</t>
+          <t>225/60R17</t>
         </is>
       </c>
       <c r="B188" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C188" s="4" t="inlineStr">
         <is>
-          <t>GD225/60R18</t>
+          <t>HK225/60R17</t>
         </is>
       </c>
       <c r="D188" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E188" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F188" s="5">
         <v>0</v>
@@ -6532,30 +6532,30 @@
         <v>0</v>
       </c>
       <c r="H188" s="6">
-        <v>700</v>
+        <v>425</v>
       </c>
     </row>
     <row outlineLevel="0" r="189">
       <c r="A189" s="4" t="inlineStr">
         <is>
-          <t>225/65R17</t>
+          <t>225/60R18</t>
         </is>
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C189" s="4" t="inlineStr">
         <is>
-          <t>RD225/65R17</t>
+          <t>GD225/60R18</t>
         </is>
       </c>
       <c r="D189" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E189" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F189" s="5">
         <v>0</v>
@@ -6564,36 +6564,36 @@
         <v>0</v>
       </c>
       <c r="H189" s="6">
-        <v>450</v>
+        <v>700</v>
       </c>
     </row>
     <row outlineLevel="0" r="190">
       <c r="A190" s="4" t="inlineStr">
         <is>
-          <t>225/70R15C</t>
+          <t>225/65R17</t>
         </is>
       </c>
       <c r="B190" s="4" t="inlineStr">
         <is>
-          <t>MATADOR</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C190" s="4" t="inlineStr">
         <is>
-          <t>MT225/70R15C</t>
+          <t>RD225/65R17</t>
         </is>
       </c>
       <c r="D190" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E190" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F190" s="5">
         <v>0</v>
       </c>
       <c r="G190" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H190" s="6">
         <v>450</v>
@@ -6607,16 +6607,16 @@
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>SEMPERIT</t>
+          <t>MATADOR</t>
         </is>
       </c>
       <c r="C191" s="4" t="inlineStr">
         <is>
-          <t>SP225/70R15C</t>
+          <t>MT225/70R15C</t>
         </is>
       </c>
       <c r="D191" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E191" s="5">
         <v>0</v>
@@ -6625,7 +6625,7 @@
         <v>0</v>
       </c>
       <c r="G191" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H191" s="6">
         <v>450</v>
@@ -6634,39 +6634,39 @@
     <row outlineLevel="0" r="192">
       <c r="A192" s="4" t="inlineStr">
         <is>
-          <t>225/75R15C</t>
+          <t>225/70R15C</t>
         </is>
       </c>
       <c r="B192" s="4" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>SEMPERIT</t>
         </is>
       </c>
       <c r="C192" s="4" t="inlineStr">
         <is>
-          <t>RD225/75R15C</t>
+          <t>SP225/70R15C</t>
         </is>
       </c>
       <c r="D192" s="5">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E192" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F192" s="5">
         <v>0</v>
       </c>
       <c r="G192" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H192" s="6">
-        <v>330</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="193">
       <c r="A193" s="4" t="inlineStr">
         <is>
-          <t>235/35R19</t>
+          <t>225/75R15C</t>
         </is>
       </c>
       <c r="B193" s="4" t="inlineStr">
@@ -6676,61 +6676,61 @@
       </c>
       <c r="C193" s="4" t="inlineStr">
         <is>
-          <t>RD235/35R19</t>
+          <t>RD225/75R15C</t>
         </is>
       </c>
       <c r="D193" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E193" s="5">
         <v>0</v>
       </c>
       <c r="F193" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G193" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H193" s="6">
-        <v>600</v>
+        <v>330</v>
       </c>
     </row>
     <row outlineLevel="0" r="194">
       <c r="A194" s="4" t="inlineStr">
         <is>
-          <t>235/40R19</t>
+          <t>235/35R19</t>
         </is>
       </c>
       <c r="B194" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="C194" s="4" t="inlineStr">
         <is>
-          <t>GD235/40R19</t>
+          <t>RD235/35R19</t>
         </is>
       </c>
       <c r="D194" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E194" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F194" s="5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G194" s="5">
         <v>0</v>
       </c>
       <c r="H194" s="6">
-        <v>850</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="195">
       <c r="A195" s="4" t="inlineStr">
         <is>
-          <t>235/45R18</t>
+          <t>235/40R19</t>
         </is>
       </c>
       <c r="B195" s="4" t="inlineStr">
@@ -6740,14 +6740,14 @@
       </c>
       <c r="C195" s="4" t="inlineStr">
         <is>
-          <t>GD235/45R18</t>
+          <t>GD235/40R19</t>
         </is>
       </c>
       <c r="D195" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E195" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F195" s="5">
         <v>0</v>
@@ -6756,30 +6756,30 @@
         <v>0</v>
       </c>
       <c r="H195" s="6">
-        <v>600</v>
+        <v>850</v>
       </c>
     </row>
     <row outlineLevel="0" r="196">
       <c r="A196" s="4" t="inlineStr">
         <is>
-          <t>235/50R18</t>
+          <t>235/45R18</t>
         </is>
       </c>
       <c r="B196" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C196" s="4" t="inlineStr">
         <is>
-          <t>HK235/50R18</t>
+          <t>GD235/45R18</t>
         </is>
       </c>
       <c r="D196" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E196" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F196" s="5">
         <v>0</v>
@@ -6788,30 +6788,30 @@
         <v>0</v>
       </c>
       <c r="H196" s="6">
-        <v>500</v>
+        <v>600</v>
       </c>
     </row>
     <row outlineLevel="0" r="197">
       <c r="A197" s="4" t="inlineStr">
         <is>
-          <t>235/50R19</t>
+          <t>235/50R18</t>
         </is>
       </c>
       <c r="B197" s="4" t="inlineStr">
         <is>
-          <t>GOODYEAR</t>
+          <t>HANKOOK</t>
         </is>
       </c>
       <c r="C197" s="4" t="inlineStr">
         <is>
-          <t>GD235/50R19</t>
+          <t>HK235/50R18</t>
         </is>
       </c>
       <c r="D197" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E197" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F197" s="5">
         <v>0</v>
@@ -6820,13 +6820,13 @@
         <v>0</v>
       </c>
       <c r="H197" s="6">
-        <v>800</v>
+        <v>500</v>
       </c>
     </row>
     <row outlineLevel="0" r="198">
       <c r="A198" s="4" t="inlineStr">
         <is>
-          <t>235/50R20</t>
+          <t>235/50R19</t>
         </is>
       </c>
       <c r="B198" s="4" t="inlineStr">
@@ -6836,78 +6836,78 @@
       </c>
       <c r="C198" s="4" t="inlineStr">
         <is>
-          <t>GD235/50R20</t>
+          <t>GD235/50R19</t>
         </is>
       </c>
       <c r="D198" s="5">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E198" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F198" s="5">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G198" s="5">
         <v>0</v>
       </c>
       <c r="H198" s="6">
-        <v>1180</v>
+        <v>800</v>
       </c>
     </row>
     <row outlineLevel="0" r="199">
       <c r="A199" s="4" t="inlineStr">
         <is>
-          <t>235/55R17</t>
+          <t>235/50R20</t>
         </is>
       </c>
       <c r="B199" s="4" t="inlineStr">
         <is>
-          <t>BRIDGESTONE</t>
+          <t>GOODYEAR</t>
         </is>
       </c>
       <c r="C199" s="4" t="inlineStr">
         <is>
-          <t>BR235/55R17</t>
+          <t>GD235/50R20</t>
         </is>
       </c>
       <c r="D199" s="5">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E199" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F199" s="5">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G199" s="5">
         <v>0</v>
       </c>
       <c r="H199" s="6">
-        <v>450</v>
+        <v>1180</v>
       </c>
     </row>
     <row outlineLevel="0" r="200">
       <c r="A200" s="4" t="inlineStr">
         <is>
-          <t>235/55R18</t>
+          <t>235/55R17</t>
         </is>
       </c>
       <c r="B200" s="4" t="inlineStr">
         <is>
-          <t>HANKOOK</t>
+          <t>BRIDGESTONE</t>
         </is>
       </c>
       <c r="C200" s="4" t="inlineStr">
         <is>
-          <t>HK235/55R18</t>
+          <t>BR235/55R17</t>
         </is>
       </c>
       <c r="D200" s="5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E200" s="5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F200" s="5">
         <v>0</v>
@@ -6916,30 +6916,30 @@
         <v>0</v>
       </c>
       <c r="H200" s="6">
-        <v>480</v>
+        <v>450</v>
       </c>
     </row>
     <row outlineLevel="0" r="201">
       <c r="A201" s="4" t="inlineStr">
         <is>
-          <t>235/55R19</t>
+          <t>235/55R18</